--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="452">
   <si>
     <t>trade_time</t>
   </si>
@@ -301,12 +301,12 @@
     <t>2021-07-08</t>
   </si>
   <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
     <t>2021-07-23</t>
   </si>
   <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
     <t>2021-07-21</t>
   </si>
   <si>
@@ -646,7 +646,7 @@
     <t>2021-02-04</t>
   </si>
   <si>
-    <t>2021-08-09</t>
+    <t>2021-08-11</t>
   </si>
   <si>
     <t>2016-03-03</t>
@@ -1360,48 +1360,9 @@
     <t>2021-02-26</t>
   </si>
   <si>
-    <t>2021-03-01</t>
-  </si>
-  <si>
-    <t>2021-03-02</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
     <t>2021-03-04</t>
   </si>
   <si>
-    <t>2021-03-05</t>
-  </si>
-  <si>
-    <t>2021-03-08</t>
-  </si>
-  <si>
-    <t>2021-03-09</t>
-  </si>
-  <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
-    <t>2021-03-11</t>
-  </si>
-  <si>
-    <t>2021-03-12</t>
-  </si>
-  <si>
-    <t>2021-03-15</t>
-  </si>
-  <si>
-    <t>2021-03-16</t>
-  </si>
-  <si>
-    <t>2021-03-17</t>
-  </si>
-  <si>
-    <t>2021-03-18</t>
-  </si>
-  <si>
     <t>2021-03-19</t>
   </si>
   <si>
@@ -1409,33 +1370,6 @@
   </si>
   <si>
     <t>2021-03-23</t>
-  </si>
-  <si>
-    <t>2021-03-24</t>
-  </si>
-  <si>
-    <t>2021-03-25</t>
-  </si>
-  <si>
-    <t>2021-03-26</t>
-  </si>
-  <si>
-    <t>2021-03-29</t>
-  </si>
-  <si>
-    <t>2021-03-30</t>
-  </si>
-  <si>
-    <t>2021-03-31</t>
-  </si>
-  <si>
-    <t>2021-04-01</t>
-  </si>
-  <si>
-    <t>2021-04-07</t>
-  </si>
-  <si>
-    <t>2021-04-08</t>
   </si>
 </sst>
 </file>
@@ -1793,7 +1727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P627"/>
+  <dimension ref="A1:P590"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28857,7 +28791,7 @@
         <v>210</v>
       </c>
       <c r="E542">
-        <v>-11.93227179073405</v>
+        <v>-12.14002282815848</v>
       </c>
       <c r="F542">
         <v>-1</v>
@@ -28866,10 +28800,10 @@
         <v>0.07585434025592445</v>
       </c>
       <c r="H542">
-        <v>0.06895227179073406</v>
+        <v>0.06974002282815847</v>
       </c>
       <c r="I542">
-        <v>1.177931534809584</v>
+        <v>1.385682572234007</v>
       </c>
       <c r="J542">
         <v>3.11094398390262</v>
@@ -28881,10 +28815,10 @@
         <v>32.55</v>
       </c>
       <c r="M542">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N542">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28907,7 +28841,7 @@
         <v>210</v>
       </c>
       <c r="E543">
-        <v>-14.585601884314</v>
+        <v>-14.82600929212095</v>
       </c>
       <c r="F543">
         <v>-1</v>
@@ -28916,10 +28850,10 @@
         <v>0.07869544447920392</v>
       </c>
       <c r="H543">
-        <v>0.071605601884314</v>
+        <v>0.07242600929212095</v>
       </c>
       <c r="I543">
-        <v>0.9901574051100788</v>
+        <v>1.230564812917027</v>
       </c>
       <c r="J543">
         <v>3.315046298793385</v>
@@ -28931,10 +28865,10 @@
         <v>32.55</v>
       </c>
       <c r="M543">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N543">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28951,40 +28885,40 @@
         <v>95</v>
       </c>
       <c r="C544">
-        <v>-13.7520278116383</v>
+        <v>-13.66738892065186</v>
       </c>
       <c r="D544" t="s">
         <v>210</v>
       </c>
       <c r="E544">
-        <v>-14.585601884314</v>
+        <v>-14.82600929212095</v>
       </c>
       <c r="F544">
         <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.07615202781163831</v>
+        <v>0.07066738892065186</v>
       </c>
       <c r="H544">
-        <v>0.071605601884314</v>
+        <v>0.07242600929212095</v>
       </c>
       <c r="I544">
-        <v>0.8335740726756953</v>
+        <v>1.158620371469087</v>
       </c>
       <c r="J544">
         <v>3.315046298793385</v>
       </c>
       <c r="K544">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="L544">
-        <v>31.2</v>
+        <v>28.5</v>
       </c>
       <c r="M544">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N544">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28995,96 +28929,96 @@
     </row>
     <row r="545" spans="1:16">
       <c r="A545" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B545" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C545">
-        <v>-13.66738892065186</v>
+        <v>-15.79783720974794</v>
       </c>
       <c r="D545" t="s">
         <v>210</v>
       </c>
       <c r="E545">
-        <v>-14.585601884314</v>
+        <v>-16.90815644254905</v>
       </c>
       <c r="F545">
         <v>-1</v>
       </c>
       <c r="G545">
-        <v>0.07066738892065186</v>
+        <v>0.08089783720974794</v>
       </c>
       <c r="H545">
-        <v>0.071605601884314</v>
+        <v>0.07450815644254906</v>
       </c>
       <c r="I545">
-        <v>0.918212963662139</v>
+        <v>1.110319232801114</v>
       </c>
       <c r="J545">
-        <v>3.315046298793385</v>
+        <v>3.47326416736695</v>
       </c>
       <c r="K545">
-        <v>12.72</v>
+        <v>13.92</v>
       </c>
       <c r="L545">
-        <v>28.5</v>
+        <v>32.55</v>
       </c>
       <c r="M545">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N545">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="546" spans="1:16">
       <c r="A546" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B546" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C546">
-        <v>-15.79783720974794</v>
+        <v>-15.6799202089076</v>
       </c>
       <c r="D546" t="s">
         <v>210</v>
       </c>
       <c r="E546">
-        <v>-16.64243417577034</v>
+        <v>-16.90815644254905</v>
       </c>
       <c r="F546">
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.08089783720974794</v>
+        <v>0.07267992020890761</v>
       </c>
       <c r="H546">
-        <v>0.07366243417577034</v>
+        <v>0.07450815644254906</v>
       </c>
       <c r="I546">
-        <v>0.8445969660224044</v>
+        <v>1.22823623364145</v>
       </c>
       <c r="J546">
         <v>3.47326416736695</v>
       </c>
       <c r="K546">
-        <v>13.92</v>
+        <v>12.72</v>
       </c>
       <c r="L546">
-        <v>32.55</v>
+        <v>28.5</v>
       </c>
       <c r="M546">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N546">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -29095,84 +29029,84 @@
     </row>
     <row r="547" spans="1:16">
       <c r="A547" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B547" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C547">
-        <v>-15.94906625945382</v>
+        <v>-18.79800968736629</v>
       </c>
       <c r="D547" t="s">
         <v>210</v>
       </c>
       <c r="E547">
-        <v>-16.64243417577034</v>
+        <v>-19.74452639983766</v>
       </c>
       <c r="F547">
         <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.07782906625945382</v>
+        <v>0.08389800968736628</v>
       </c>
       <c r="H547">
-        <v>0.07366243417577034</v>
+        <v>0.07734452639983766</v>
       </c>
       <c r="I547">
-        <v>0.6933679163165252</v>
+        <v>0.9465167124713751</v>
       </c>
       <c r="J547">
-        <v>3.47326416736695</v>
+        <v>3.688793799379762</v>
       </c>
       <c r="K547">
-        <v>13.5</v>
+        <v>13.92</v>
       </c>
       <c r="L547">
-        <v>30.94</v>
+        <v>32.55</v>
       </c>
       <c r="M547">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N547">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="548" spans="1:16">
       <c r="A548" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B548" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C548">
-        <v>-15.89746210949584</v>
+        <v>-18.82004391958958</v>
       </c>
       <c r="D548" t="s">
         <v>210</v>
       </c>
       <c r="E548">
-        <v>-16.64243417577034</v>
+        <v>-19.74452639983766</v>
       </c>
       <c r="F548">
         <v>-1</v>
       </c>
       <c r="G548">
-        <v>0.07829746210949584</v>
+        <v>0.08122004391958958</v>
       </c>
       <c r="H548">
-        <v>0.07366243417577034</v>
+        <v>0.07734452639983766</v>
       </c>
       <c r="I548">
-        <v>0.7449720662745065</v>
+        <v>0.9244824802480878</v>
       </c>
       <c r="J548">
-        <v>3.47326416736695</v>
+        <v>3.688793799379762</v>
       </c>
       <c r="K548">
         <v>13.56</v>
@@ -29181,48 +29115,48 @@
         <v>31.2</v>
       </c>
       <c r="M548">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N548">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="549" spans="1:16">
       <c r="A549" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B549" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C549">
-        <v>-15.6799202089076</v>
+        <v>-18.42145712811057</v>
       </c>
       <c r="D549" t="s">
         <v>210</v>
       </c>
       <c r="E549">
-        <v>-16.64243417577034</v>
+        <v>-19.74452639983766</v>
       </c>
       <c r="F549">
         <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.07267992020890761</v>
+        <v>0.07542145712811058</v>
       </c>
       <c r="H549">
-        <v>0.07366243417577034</v>
+        <v>0.07734452639983766</v>
       </c>
       <c r="I549">
-        <v>0.9625139668627405</v>
+        <v>1.323069271727089</v>
       </c>
       <c r="J549">
-        <v>3.47326416736695</v>
+        <v>3.688793799379762</v>
       </c>
       <c r="K549">
         <v>12.72</v>
@@ -29231,16 +29165,16 @@
         <v>28.5</v>
       </c>
       <c r="M549">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N549">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O549">
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29248,49 +29182,49 @@
         <v>0</v>
       </c>
       <c r="B550" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C550">
-        <v>-18.79800968736629</v>
+        <v>-21.55769767012594</v>
       </c>
       <c r="D550" t="s">
         <v>210</v>
       </c>
       <c r="E550">
-        <v>-19.4443193919369</v>
+        <v>-22.37553343250795</v>
       </c>
       <c r="F550">
         <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.08389800968736628</v>
+        <v>0.08343769767012595</v>
       </c>
       <c r="H550">
-        <v>0.07646431939193692</v>
+        <v>0.07997553343250796</v>
       </c>
       <c r="I550">
-        <v>0.6463097045706157</v>
+        <v>0.8178357623820105</v>
       </c>
       <c r="J550">
-        <v>3.688793799379762</v>
+        <v>3.888718345935255</v>
       </c>
       <c r="K550">
-        <v>13.92</v>
+        <v>13.5</v>
       </c>
       <c r="L550">
-        <v>32.55</v>
+        <v>30.94</v>
       </c>
       <c r="M550">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N550">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29298,49 +29232,49 @@
         <v>1</v>
       </c>
       <c r="B551" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C551">
-        <v>-18.85871629162679</v>
+        <v>-21.53102077088206</v>
       </c>
       <c r="D551" t="s">
         <v>210</v>
       </c>
       <c r="E551">
-        <v>-19.4443193919369</v>
+        <v>-22.37553343250795</v>
       </c>
       <c r="F551">
         <v>-1</v>
       </c>
       <c r="G551">
-        <v>0.08073871629162679</v>
+        <v>0.08393102077088206</v>
       </c>
       <c r="H551">
-        <v>0.07646431939193692</v>
+        <v>0.07997553343250796</v>
       </c>
       <c r="I551">
-        <v>0.5856031003101165</v>
+        <v>0.8445126616258918</v>
       </c>
       <c r="J551">
-        <v>3.688793799379762</v>
+        <v>3.888718345935255</v>
       </c>
       <c r="K551">
-        <v>13.5</v>
+        <v>13.56</v>
       </c>
       <c r="L551">
-        <v>30.94</v>
+        <v>31.2</v>
       </c>
       <c r="M551">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N551">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29351,46 +29285,46 @@
         <v>95</v>
       </c>
       <c r="C552">
-        <v>-18.82004391958958</v>
+        <v>-20.96449736029645</v>
       </c>
       <c r="D552" t="s">
         <v>210</v>
       </c>
       <c r="E552">
-        <v>-19.4443193919369</v>
+        <v>-22.37553343250795</v>
       </c>
       <c r="F552">
         <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.08122004391958958</v>
+        <v>0.07796449736029645</v>
       </c>
       <c r="H552">
-        <v>0.07646431939193692</v>
+        <v>0.07997553343250796</v>
       </c>
       <c r="I552">
-        <v>0.6242754723473283</v>
+        <v>1.411036072211505</v>
       </c>
       <c r="J552">
-        <v>3.688793799379762</v>
+        <v>3.888718345935255</v>
       </c>
       <c r="K552">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="L552">
-        <v>31.2</v>
+        <v>28.5</v>
       </c>
       <c r="M552">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N552">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O552">
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29398,49 +29332,49 @@
         <v>0</v>
       </c>
       <c r="B553" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C553">
-        <v>-21.58095937541875</v>
+        <v>-22.93851338812074</v>
       </c>
       <c r="D553" t="s">
         <v>210</v>
       </c>
       <c r="E553">
-        <v>-22.04333849715831</v>
+        <v>-23.72157305093844</v>
       </c>
       <c r="F553">
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.08668095937541875</v>
+        <v>0.08481851338812076</v>
       </c>
       <c r="H553">
-        <v>0.07906333849715831</v>
+        <v>0.08132157305093844</v>
       </c>
       <c r="I553">
-        <v>0.4623791217395627</v>
+        <v>0.7830596628176991</v>
       </c>
       <c r="J553">
-        <v>3.888718345935255</v>
+        <v>3.991000991712648</v>
       </c>
       <c r="K553">
-        <v>13.92</v>
+        <v>13.5</v>
       </c>
       <c r="L553">
-        <v>32.55</v>
+        <v>30.94</v>
       </c>
       <c r="M553">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N553">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O553">
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29448,249 +29382,249 @@
         <v>1</v>
       </c>
       <c r="B554" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C554">
-        <v>-21.55769767012594</v>
+        <v>-22.91797344762351</v>
       </c>
       <c r="D554" t="s">
         <v>210</v>
       </c>
       <c r="E554">
-        <v>-22.04333849715831</v>
+        <v>-23.72157305093844</v>
       </c>
       <c r="F554">
         <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.08343769767012595</v>
+        <v>0.0853179734476235</v>
       </c>
       <c r="H554">
-        <v>0.07906333849715831</v>
+        <v>0.08132157305093844</v>
       </c>
       <c r="I554">
-        <v>0.4856408270323698</v>
+        <v>0.803599603314936</v>
       </c>
       <c r="J554">
-        <v>3.888718345935255</v>
+        <v>3.991000991712648</v>
       </c>
       <c r="K554">
-        <v>13.5</v>
+        <v>13.56</v>
       </c>
       <c r="L554">
-        <v>30.94</v>
+        <v>31.2</v>
       </c>
       <c r="M554">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N554">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O554">
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="555" spans="1:16">
       <c r="A555" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B555" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C555">
-        <v>-21.53102077088206</v>
+        <v>-24.13261389329169</v>
       </c>
       <c r="D555" t="s">
         <v>210</v>
       </c>
       <c r="E555">
-        <v>-22.04333849715831</v>
+        <v>-24.88559991375694</v>
       </c>
       <c r="F555">
         <v>-1</v>
       </c>
       <c r="G555">
-        <v>0.08393102077088206</v>
+        <v>0.08601261389329169</v>
       </c>
       <c r="H555">
-        <v>0.07906333849715831</v>
+        <v>0.08248559991375694</v>
       </c>
       <c r="I555">
-        <v>0.5123177262762511</v>
+        <v>0.7529860204652508</v>
       </c>
       <c r="J555">
-        <v>3.888718345935255</v>
+        <v>4.07945288098457</v>
       </c>
       <c r="K555">
-        <v>13.56</v>
+        <v>13.5</v>
       </c>
       <c r="L555">
-        <v>31.2</v>
+        <v>30.94</v>
       </c>
       <c r="M555">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N555">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O555">
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="556" spans="1:16">
       <c r="A556" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B556" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C556">
-        <v>-23.00473380464006</v>
+        <v>-24.11738106615077</v>
       </c>
       <c r="D556" t="s">
         <v>210</v>
       </c>
       <c r="E556">
-        <v>-23.37301289226442</v>
+        <v>-24.88559991375694</v>
       </c>
       <c r="F556">
         <v>-1</v>
       </c>
       <c r="G556">
-        <v>0.08810473380464007</v>
+        <v>0.08651738106615077</v>
       </c>
       <c r="H556">
-        <v>0.08039301289226443</v>
+        <v>0.08248559991375694</v>
       </c>
       <c r="I556">
-        <v>0.3682790876243551</v>
+        <v>0.7682188476061711</v>
       </c>
       <c r="J556">
-        <v>3.991000991712648</v>
+        <v>4.07945288098457</v>
       </c>
       <c r="K556">
-        <v>13.92</v>
+        <v>13.56</v>
       </c>
       <c r="L556">
-        <v>32.55</v>
+        <v>31.2</v>
       </c>
       <c r="M556">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N556">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O556">
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="557" spans="1:16">
       <c r="A557" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B557" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C557">
-        <v>-22.93851338812074</v>
+        <v>-25.70935268145322</v>
       </c>
       <c r="D557" t="s">
         <v>210</v>
       </c>
       <c r="E557">
-        <v>-23.37301289226442</v>
+        <v>-26.52752143962838</v>
       </c>
       <c r="F557">
         <v>-1</v>
       </c>
       <c r="G557">
-        <v>0.08481851338812076</v>
+        <v>0.08460935268145321</v>
       </c>
       <c r="H557">
-        <v>0.08039301289226443</v>
+        <v>0.08412752143962839</v>
       </c>
       <c r="I557">
-        <v>0.4344995041436732</v>
+        <v>0.8181687581751618</v>
       </c>
       <c r="J557">
-        <v>3.991000991712648</v>
+        <v>4.204218954379057</v>
       </c>
       <c r="K557">
-        <v>13.5</v>
+        <v>13.12</v>
       </c>
       <c r="L557">
-        <v>30.94</v>
+        <v>29.45</v>
       </c>
       <c r="M557">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N557">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O557">
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="558" spans="1:16">
       <c r="A558" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B558" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C558">
-        <v>-22.91797344762351</v>
+        <v>-27.80136179827025</v>
       </c>
       <c r="D558" t="s">
         <v>210</v>
       </c>
       <c r="E558">
-        <v>-23.37301289226442</v>
+        <v>-28.62590863302107</v>
       </c>
       <c r="F558">
         <v>-1</v>
       </c>
       <c r="G558">
-        <v>0.0853179734476235</v>
+        <v>0.08670136179827025</v>
       </c>
       <c r="H558">
-        <v>0.08039301289226443</v>
+        <v>0.08622590863302108</v>
       </c>
       <c r="I558">
-        <v>0.4550394446409101</v>
+        <v>0.8245468347508265</v>
       </c>
       <c r="J558">
-        <v>3.991000991712648</v>
+        <v>4.363670868770599</v>
       </c>
       <c r="K558">
-        <v>13.56</v>
+        <v>13.12</v>
       </c>
       <c r="L558">
-        <v>31.2</v>
+        <v>29.45</v>
       </c>
       <c r="M558">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N558">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O558">
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29698,149 +29632,149 @@
         <v>0</v>
       </c>
       <c r="B559" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C559">
-        <v>-24.23598410330521</v>
+        <v>-30.02905768709702</v>
       </c>
       <c r="D559" t="s">
         <v>210</v>
       </c>
       <c r="E559">
-        <v>-24.52288745279941</v>
+        <v>-30.86039627760647</v>
       </c>
       <c r="F559">
         <v>-1</v>
       </c>
       <c r="G559">
-        <v>0.0893359841033052</v>
+        <v>0.08892905768709701</v>
       </c>
       <c r="H559">
-        <v>0.0815428874527994</v>
+        <v>0.08846039627760646</v>
       </c>
       <c r="I559">
-        <v>0.2869033494941924</v>
+        <v>0.8313385905094464</v>
       </c>
       <c r="J559">
-        <v>4.07945288098457</v>
+        <v>4.533464762736053</v>
       </c>
       <c r="K559">
-        <v>13.92</v>
+        <v>13.12</v>
       </c>
       <c r="L559">
-        <v>32.55</v>
+        <v>29.45</v>
       </c>
       <c r="M559">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N559">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O559">
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="560" spans="1:16">
       <c r="A560" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B560" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C560">
-        <v>-24.13261389329169</v>
+        <v>-30.8292967796032</v>
       </c>
       <c r="D560" t="s">
         <v>210</v>
       </c>
       <c r="E560">
-        <v>-24.52288745279941</v>
+        <v>-31.66307512344345</v>
       </c>
       <c r="F560">
         <v>-1</v>
       </c>
       <c r="G560">
-        <v>0.08601261389329169</v>
+        <v>0.0897292967796032</v>
       </c>
       <c r="H560">
-        <v>0.0815428874527994</v>
+        <v>0.08926307512344346</v>
       </c>
       <c r="I560">
-        <v>0.3902735595077189</v>
+        <v>0.8337783438402511</v>
       </c>
       <c r="J560">
-        <v>4.07945288098457</v>
+        <v>4.594458596006342</v>
       </c>
       <c r="K560">
-        <v>13.5</v>
+        <v>13.12</v>
       </c>
       <c r="L560">
-        <v>30.94</v>
+        <v>29.45</v>
       </c>
       <c r="M560">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N560">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O560">
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="561" spans="1:16">
       <c r="A561" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B561" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C561">
-        <v>-24.11738106615077</v>
+        <v>-31.33823575745694</v>
       </c>
       <c r="D561" t="s">
         <v>210</v>
       </c>
       <c r="E561">
-        <v>-24.52288745279941</v>
+        <v>-32.17356574452236</v>
       </c>
       <c r="F561">
         <v>-1</v>
       </c>
       <c r="G561">
-        <v>0.08651738106615077</v>
+        <v>0.09023823575745693</v>
       </c>
       <c r="H561">
-        <v>0.0815428874527994</v>
+        <v>0.08977356574452236</v>
       </c>
       <c r="I561">
-        <v>0.4055063866486392</v>
+        <v>0.8353299870654247</v>
       </c>
       <c r="J561">
-        <v>4.07945288098457</v>
+        <v>4.633249676635438</v>
       </c>
       <c r="K561">
-        <v>13.56</v>
+        <v>13.12</v>
       </c>
       <c r="L561">
-        <v>31.2</v>
+        <v>29.45</v>
       </c>
       <c r="M561">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N561">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O561">
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>419</v>
+        <v>93</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29848,149 +29782,149 @@
         <v>0</v>
       </c>
       <c r="B562" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C562">
-        <v>-25.97272784495647</v>
+        <v>-31.65732543525032</v>
       </c>
       <c r="D562" t="s">
         <v>210</v>
       </c>
       <c r="E562">
-        <v>-26.14484640692774</v>
+        <v>-32.49362825669927</v>
       </c>
       <c r="F562">
         <v>-1</v>
       </c>
       <c r="G562">
-        <v>0.09107272784495646</v>
+        <v>0.09055732543525032</v>
       </c>
       <c r="H562">
-        <v>0.08316484640692774</v>
+        <v>0.09009362825669927</v>
       </c>
       <c r="I562">
-        <v>0.1721185619712635</v>
+        <v>0.8363028214489425</v>
       </c>
       <c r="J562">
-        <v>4.204218954379057</v>
+        <v>4.657570536223348</v>
       </c>
       <c r="K562">
-        <v>13.92</v>
+        <v>13.12</v>
       </c>
       <c r="L562">
-        <v>32.55</v>
+        <v>29.45</v>
       </c>
       <c r="M562">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N562">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O562">
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="563" spans="1:16">
       <c r="A563" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B563" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C563">
-        <v>-25.81695588411727</v>
+        <v>-32.13066901461242</v>
       </c>
       <c r="D563" t="s">
         <v>210</v>
       </c>
       <c r="E563">
-        <v>-26.14484640692774</v>
+        <v>-32.96841495673014</v>
       </c>
       <c r="F563">
         <v>-1</v>
       </c>
       <c r="G563">
-        <v>0.08769695588411727</v>
+        <v>0.09103066901461242</v>
       </c>
       <c r="H563">
-        <v>0.08316484640692774</v>
+        <v>0.09056841495673014</v>
       </c>
       <c r="I563">
-        <v>0.3278905228104705</v>
+        <v>0.8377459421177207</v>
       </c>
       <c r="J563">
-        <v>4.204218954379057</v>
+        <v>4.69364855294302</v>
       </c>
       <c r="K563">
-        <v>13.5</v>
+        <v>13.12</v>
       </c>
       <c r="L563">
-        <v>30.94</v>
+        <v>29.45</v>
       </c>
       <c r="M563">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N563">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O563">
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="564" spans="1:16">
       <c r="A564" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B564" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C564">
-        <v>-25.80920902138001</v>
+        <v>-31.9995182467945</v>
       </c>
       <c r="D564" t="s">
         <v>210</v>
       </c>
       <c r="E564">
-        <v>-26.14484640692774</v>
+        <v>-32.83686433901033</v>
       </c>
       <c r="F564">
         <v>-1</v>
       </c>
       <c r="G564">
-        <v>0.08820920902138001</v>
+        <v>0.0908995182467945</v>
       </c>
       <c r="H564">
-        <v>0.08316484640692774</v>
+        <v>0.09043686433901034</v>
       </c>
       <c r="I564">
-        <v>0.3356373855477273</v>
+        <v>0.8373460922158351</v>
       </c>
       <c r="J564">
-        <v>4.204218954379057</v>
+        <v>4.683652305395922</v>
       </c>
       <c r="K564">
-        <v>13.56</v>
+        <v>13.12</v>
       </c>
       <c r="L564">
-        <v>31.2</v>
+        <v>29.45</v>
       </c>
       <c r="M564">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N564">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O564">
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -29998,99 +29932,99 @@
         <v>0</v>
       </c>
       <c r="B565" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C565">
-        <v>-27.96955672840308</v>
+        <v>-31.14816682390665</v>
       </c>
       <c r="D565" t="s">
         <v>210</v>
       </c>
       <c r="E565">
-        <v>-28.21772129401778</v>
+        <v>-31.98291733251612</v>
       </c>
       <c r="F565">
         <v>-1</v>
       </c>
       <c r="G565">
-        <v>0.08984955672840308</v>
+        <v>0.09004816682390664</v>
       </c>
       <c r="H565">
-        <v>0.08523772129401778</v>
+        <v>0.08958291733251612</v>
       </c>
       <c r="I565">
-        <v>0.2481645656147009</v>
+        <v>0.8347505086094742</v>
       </c>
       <c r="J565">
-        <v>4.363670868770599</v>
+        <v>4.618762715236787</v>
       </c>
       <c r="K565">
-        <v>13.5</v>
+        <v>13.12</v>
       </c>
       <c r="L565">
-        <v>30.94</v>
+        <v>29.45</v>
       </c>
       <c r="M565">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N565">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O565">
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="566" spans="1:16">
       <c r="A566" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B566" t="s">
         <v>95</v>
       </c>
       <c r="C566">
-        <v>-27.97137698052932</v>
+        <v>-28.48555321698337</v>
       </c>
       <c r="D566" t="s">
         <v>210</v>
       </c>
       <c r="E566">
-        <v>-28.21772129401778</v>
+        <v>-30.15675159870291</v>
       </c>
       <c r="F566">
         <v>-1</v>
       </c>
       <c r="G566">
-        <v>0.09037137698052933</v>
+        <v>0.08548555321698337</v>
       </c>
       <c r="H566">
-        <v>0.08523772129401778</v>
+        <v>0.08775675159870291</v>
       </c>
       <c r="I566">
-        <v>0.2463443134884642</v>
+        <v>1.671198381719545</v>
       </c>
       <c r="J566">
-        <v>4.363670868770599</v>
+        <v>4.479996322089887</v>
       </c>
       <c r="K566">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="L566">
-        <v>31.2</v>
+        <v>28.5</v>
       </c>
       <c r="M566">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N566">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O566">
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30098,99 +30032,99 @@
         <v>0</v>
       </c>
       <c r="B567" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C567">
-        <v>-30.26177429693672</v>
+        <v>-28.69349087972021</v>
       </c>
       <c r="D567" t="s">
         <v>210</v>
       </c>
       <c r="E567">
-        <v>-30.42504191556869</v>
+        <v>-30.37188207367279</v>
       </c>
       <c r="F567">
         <v>-1</v>
       </c>
       <c r="G567">
-        <v>0.09214177429693672</v>
+        <v>0.0856934908797202</v>
       </c>
       <c r="H567">
-        <v>0.08744504191556869</v>
+        <v>0.08797188207367279</v>
       </c>
       <c r="I567">
-        <v>0.163267618631977</v>
+        <v>1.678391193952582</v>
       </c>
       <c r="J567">
-        <v>4.533464762736053</v>
+        <v>4.496343622619513</v>
       </c>
       <c r="K567">
-        <v>13.5</v>
+        <v>12.72</v>
       </c>
       <c r="L567">
-        <v>30.94</v>
+        <v>28.5</v>
       </c>
       <c r="M567">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N567">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O567">
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="568" spans="1:16">
       <c r="A568" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B568" t="s">
         <v>95</v>
       </c>
       <c r="C568">
-        <v>-30.27378218270089</v>
+        <v>-28.72399400585454</v>
       </c>
       <c r="D568" t="s">
         <v>210</v>
       </c>
       <c r="E568">
-        <v>-30.42504191556869</v>
+        <v>-30.40344033939038</v>
       </c>
       <c r="F568">
         <v>-1</v>
       </c>
       <c r="G568">
-        <v>0.09267378218270089</v>
+        <v>0.08572399400585454</v>
       </c>
       <c r="H568">
-        <v>0.08744504191556869</v>
+        <v>0.08800344033939038</v>
       </c>
       <c r="I568">
-        <v>0.1512597328678069</v>
+        <v>1.679446333535846</v>
       </c>
       <c r="J568">
-        <v>4.533464762736053</v>
+        <v>4.498741667126929</v>
       </c>
       <c r="K568">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="L568">
-        <v>31.2</v>
+        <v>28.5</v>
       </c>
       <c r="M568">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N568">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O568">
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30198,99 +30132,99 @@
         <v>0</v>
       </c>
       <c r="B569" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C569">
-        <v>-31.08519104608561</v>
+        <v>-29.04997068031175</v>
       </c>
       <c r="D569" t="s">
         <v>210</v>
       </c>
       <c r="E569">
-        <v>-31.21796174808244</v>
+        <v>-30.74069293654894</v>
       </c>
       <c r="F569">
         <v>-1</v>
       </c>
       <c r="G569">
-        <v>0.09296519104608561</v>
+        <v>0.08604997068031175</v>
       </c>
       <c r="H569">
-        <v>0.08823796174808245</v>
+        <v>0.08834069293654895</v>
       </c>
       <c r="I569">
-        <v>0.1327707019968329</v>
+        <v>1.690722256237191</v>
       </c>
       <c r="J569">
-        <v>4.594458596006342</v>
+        <v>4.524368764175452</v>
       </c>
       <c r="K569">
-        <v>13.5</v>
+        <v>12.72</v>
       </c>
       <c r="L569">
-        <v>30.94</v>
+        <v>28.5</v>
       </c>
       <c r="M569">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N569">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O569">
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="570" spans="1:16">
       <c r="A570" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B570" t="s">
         <v>95</v>
       </c>
       <c r="C570">
-        <v>-31.10085856184599</v>
+        <v>-29.43168959025828</v>
       </c>
       <c r="D570" t="s">
         <v>210</v>
       </c>
       <c r="E570">
-        <v>-31.21796174808244</v>
+        <v>-31.13561595973262</v>
       </c>
       <c r="F570">
         <v>-1</v>
       </c>
       <c r="G570">
-        <v>0.09350085856184599</v>
+        <v>0.08643168959025829</v>
       </c>
       <c r="H570">
-        <v>0.08823796174808245</v>
+        <v>0.08873561595973263</v>
       </c>
       <c r="I570">
-        <v>0.1171031862364487</v>
+        <v>1.703926369474342</v>
       </c>
       <c r="J570">
-        <v>4.594458596006342</v>
+        <v>4.554378112441689</v>
       </c>
       <c r="K570">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="L570">
-        <v>31.2</v>
+        <v>28.5</v>
       </c>
       <c r="M570">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N570">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O570">
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30298,99 +30232,99 @@
         <v>0</v>
       </c>
       <c r="B571" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C571">
-        <v>-31.60887063457841</v>
+        <v>-30.72131869184545</v>
       </c>
       <c r="D571" t="s">
         <v>210</v>
       </c>
       <c r="E571">
-        <v>-31.72224579626069</v>
+        <v>-32.46985487300991</v>
       </c>
       <c r="F571">
         <v>-1</v>
       </c>
       <c r="G571">
-        <v>0.09348887063457841</v>
+        <v>0.08772131869184546</v>
       </c>
       <c r="H571">
-        <v>0.08874224579626069</v>
+        <v>0.09006985487300992</v>
       </c>
       <c r="I571">
-        <v>0.1133751616822849</v>
+        <v>1.748536181164461</v>
       </c>
       <c r="J571">
-        <v>4.633249676635438</v>
+        <v>4.655764048101057</v>
       </c>
       <c r="K571">
-        <v>13.5</v>
+        <v>12.72</v>
       </c>
       <c r="L571">
-        <v>30.94</v>
+        <v>28.5</v>
       </c>
       <c r="M571">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N571">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O571">
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>93</v>
+        <v>433</v>
       </c>
     </row>
     <row r="572" spans="1:16">
       <c r="A572" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B572" t="s">
         <v>95</v>
       </c>
       <c r="C572">
-        <v>-31.62686561517654</v>
+        <v>-32.3547496665294</v>
       </c>
       <c r="D572" t="s">
         <v>210</v>
       </c>
       <c r="E572">
-        <v>-31.72224579626069</v>
+        <v>-34.15978817700683</v>
       </c>
       <c r="F572">
         <v>-1</v>
       </c>
       <c r="G572">
-        <v>0.09402686561517654</v>
+        <v>0.0893547496665294</v>
       </c>
       <c r="H572">
-        <v>0.08874224579626069</v>
+        <v>0.09175978817700682</v>
       </c>
       <c r="I572">
-        <v>0.09538018108415258</v>
+        <v>1.805038510477431</v>
       </c>
       <c r="J572">
-        <v>4.633249676635438</v>
+        <v>4.784178432903254</v>
       </c>
       <c r="K572">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="L572">
-        <v>31.2</v>
+        <v>28.5</v>
       </c>
       <c r="M572">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N572">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O572">
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>93</v>
+        <v>434</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30398,99 +30332,99 @@
         <v>0</v>
       </c>
       <c r="B573" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C573">
-        <v>-31.9372022390152</v>
+        <v>-33.15849324376438</v>
       </c>
       <c r="D573" t="s">
         <v>210</v>
       </c>
       <c r="E573">
-        <v>-32.03841697090353</v>
+        <v>-34.99133420502666</v>
       </c>
       <c r="F573">
         <v>-1</v>
       </c>
       <c r="G573">
-        <v>0.0938172022390152</v>
+        <v>0.09015849324376439</v>
       </c>
       <c r="H573">
-        <v>0.08905841697090353</v>
+        <v>0.09259133420502667</v>
       </c>
       <c r="I573">
-        <v>0.1012147318883301</v>
+        <v>1.832840961262285</v>
       </c>
       <c r="J573">
-        <v>4.657570536223348</v>
+        <v>4.847365821050658</v>
       </c>
       <c r="K573">
-        <v>13.5</v>
+        <v>12.72</v>
       </c>
       <c r="L573">
-        <v>30.94</v>
+        <v>28.5</v>
       </c>
       <c r="M573">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N573">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O573">
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
     </row>
     <row r="574" spans="1:16">
       <c r="A574" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B574" t="s">
         <v>95</v>
       </c>
       <c r="C574">
-        <v>-31.95665647118861</v>
+        <v>-34.25698087216963</v>
       </c>
       <c r="D574" t="s">
         <v>210</v>
       </c>
       <c r="E574">
-        <v>-32.03841697090353</v>
+        <v>-36.12781983315662</v>
       </c>
       <c r="F574">
         <v>-1</v>
       </c>
       <c r="G574">
-        <v>0.0943566564711886</v>
+        <v>0.09125698087216964</v>
       </c>
       <c r="H574">
-        <v>0.08905841697090353</v>
+        <v>0.09372781983315662</v>
       </c>
       <c r="I574">
-        <v>0.08176049971492105</v>
+        <v>1.870838960986994</v>
       </c>
       <c r="J574">
-        <v>4.657570536223348</v>
+        <v>4.93372491133409</v>
       </c>
       <c r="K574">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="L574">
-        <v>31.2</v>
+        <v>28.5</v>
       </c>
       <c r="M574">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N574">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O574">
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30498,99 +30432,99 @@
         <v>0</v>
       </c>
       <c r="B575" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C575">
-        <v>-32.42425546473076</v>
+        <v>-35.16617096130667</v>
       </c>
       <c r="D575" t="s">
         <v>210</v>
       </c>
       <c r="E575">
-        <v>-32.50743118825926</v>
+        <v>-37.06845989393048</v>
       </c>
       <c r="F575">
         <v>-1</v>
       </c>
       <c r="G575">
-        <v>0.09430425546473077</v>
+        <v>0.09216617096130668</v>
       </c>
       <c r="H575">
-        <v>0.08952743118825926</v>
+        <v>0.09466845989393048</v>
       </c>
       <c r="I575">
-        <v>0.08317572352849822</v>
+        <v>1.902288932623811</v>
       </c>
       <c r="J575">
-        <v>4.69364855294302</v>
+        <v>5.005202119599581</v>
       </c>
       <c r="K575">
-        <v>13.5</v>
+        <v>12.72</v>
       </c>
       <c r="L575">
-        <v>30.94</v>
+        <v>28.5</v>
       </c>
       <c r="M575">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N575">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O575">
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>425</v>
+        <v>209</v>
       </c>
     </row>
     <row r="576" spans="1:16">
       <c r="A576" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B576" t="s">
         <v>95</v>
       </c>
       <c r="C576">
-        <v>-32.44587437790736</v>
+        <v>-35.90561619919141</v>
       </c>
       <c r="D576" t="s">
         <v>210</v>
       </c>
       <c r="E576">
-        <v>-32.50743118825926</v>
+        <v>-37.83348342620747</v>
       </c>
       <c r="F576">
         <v>-1</v>
       </c>
       <c r="G576">
-        <v>0.09484587437790735</v>
+        <v>0.09290561619919141</v>
       </c>
       <c r="H576">
-        <v>0.08952743118825926</v>
+        <v>0.09543348342620746</v>
       </c>
       <c r="I576">
-        <v>0.06155681035190241</v>
+        <v>1.927867227016051</v>
       </c>
       <c r="J576">
-        <v>4.69364855294302</v>
+        <v>5.063334606854671</v>
       </c>
       <c r="K576">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="L576">
-        <v>31.2</v>
+        <v>28.5</v>
       </c>
       <c r="M576">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N576">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O576">
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -30598,99 +30532,99 @@
         <v>0</v>
       </c>
       <c r="B577" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C577">
-        <v>-32.28930612284495</v>
+        <v>-36.18997893562975</v>
       </c>
       <c r="D577" t="s">
         <v>210</v>
       </c>
       <c r="E577">
-        <v>-32.37747997014699</v>
+        <v>-38.12768260950374</v>
       </c>
       <c r="F577">
         <v>-1</v>
       </c>
       <c r="G577">
-        <v>0.09416930612284496</v>
+        <v>0.09318997893562976</v>
       </c>
       <c r="H577">
-        <v>0.08939747997014699</v>
+        <v>0.09572768260950373</v>
       </c>
       <c r="I577">
-        <v>0.08817384730204481</v>
+        <v>1.937703673873983</v>
       </c>
       <c r="J577">
-        <v>4.683652305395922</v>
+        <v>5.085690167895421</v>
       </c>
       <c r="K577">
-        <v>13.5</v>
+        <v>12.72</v>
       </c>
       <c r="L577">
-        <v>30.94</v>
+        <v>28.5</v>
       </c>
       <c r="M577">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N577">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O577">
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
     </row>
     <row r="578" spans="1:16">
       <c r="A578" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B578" t="s">
         <v>95</v>
       </c>
       <c r="C578">
-        <v>-32.31032526116871</v>
+        <v>-36.79440237149454</v>
       </c>
       <c r="D578" t="s">
         <v>210</v>
       </c>
       <c r="E578">
-        <v>-32.37747997014699</v>
+        <v>-38.75301377428208</v>
       </c>
       <c r="F578">
         <v>-1</v>
       </c>
       <c r="G578">
-        <v>0.09471032526116871</v>
+        <v>0.09379440237149454</v>
       </c>
       <c r="H578">
-        <v>0.08939747997014699</v>
+        <v>0.09635301377428208</v>
       </c>
       <c r="I578">
-        <v>0.06715470897827913</v>
+        <v>1.95861140278754</v>
       </c>
       <c r="J578">
-        <v>4.683652305395922</v>
+        <v>5.133207733608061</v>
       </c>
       <c r="K578">
-        <v>13.56</v>
+        <v>12.72</v>
       </c>
       <c r="L578">
-        <v>31.2</v>
+        <v>28.5</v>
       </c>
       <c r="M578">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N578">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O578">
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -30698,99 +30632,99 @@
         <v>0</v>
       </c>
       <c r="B579" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C579">
-        <v>-31.41329665569663</v>
+        <v>-36.55608045442354</v>
       </c>
       <c r="D579" t="s">
         <v>210</v>
       </c>
       <c r="E579">
-        <v>-31.53391529807823</v>
+        <v>-38.50644801731239</v>
       </c>
       <c r="F579">
         <v>-1</v>
       </c>
       <c r="G579">
-        <v>0.09329329665569663</v>
+        <v>0.09355608045442354</v>
       </c>
       <c r="H579">
-        <v>0.08855391529807824</v>
+        <v>0.09610644801731238</v>
       </c>
       <c r="I579">
-        <v>0.1206186423816007</v>
+        <v>1.950367562888857</v>
       </c>
       <c r="J579">
-        <v>4.618762715236787</v>
+        <v>5.114471733838328</v>
       </c>
       <c r="K579">
-        <v>13.5</v>
+        <v>12.72</v>
       </c>
       <c r="L579">
-        <v>30.94</v>
+        <v>28.5</v>
       </c>
       <c r="M579">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N579">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O579">
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
     </row>
     <row r="580" spans="1:16">
       <c r="A580" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B580" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C580">
-        <v>-31.14816682390665</v>
+        <v>-36.02878397309011</v>
       </c>
       <c r="D580" t="s">
         <v>210</v>
       </c>
       <c r="E580">
-        <v>-31.53391529807823</v>
+        <v>-37.96091172058695</v>
       </c>
       <c r="F580">
         <v>-1</v>
       </c>
       <c r="G580">
-        <v>0.09004816682390664</v>
+        <v>0.09302878397309011</v>
       </c>
       <c r="H580">
-        <v>0.08855391529807824</v>
+        <v>0.09556091172058695</v>
       </c>
       <c r="I580">
-        <v>0.3857484741715851</v>
+        <v>1.932127747496835</v>
       </c>
       <c r="J580">
-        <v>4.618762715236787</v>
+        <v>5.073017607947336</v>
       </c>
       <c r="K580">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L580">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M580">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N580">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O580">
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -30798,49 +30732,49 @@
         <v>0</v>
       </c>
       <c r="B581" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C581">
-        <v>-29.32755174581932</v>
+        <v>-35.32789307633533</v>
       </c>
       <c r="D581" t="s">
         <v>210</v>
       </c>
       <c r="E581">
-        <v>-29.72995218716853</v>
+        <v>-37.23577617017082</v>
       </c>
       <c r="F581">
         <v>-1</v>
       </c>
       <c r="G581">
-        <v>0.08822755174581931</v>
+        <v>0.09232789307633534</v>
       </c>
       <c r="H581">
-        <v>0.08674995218716854</v>
+        <v>0.09483577617017082</v>
       </c>
       <c r="I581">
-        <v>0.402400441349215</v>
+        <v>1.907883093835494</v>
       </c>
       <c r="J581">
-        <v>4.479996322089887</v>
+        <v>5.017916122353406</v>
       </c>
       <c r="K581">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L581">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M581">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N581">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O581">
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -30848,49 +30782,49 @@
         <v>0</v>
       </c>
       <c r="B582" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C582">
-        <v>-29.54202832876801</v>
+        <v>-34.50492295847297</v>
       </c>
       <c r="D582" t="s">
         <v>210</v>
       </c>
       <c r="E582">
-        <v>-29.94246709405367</v>
+        <v>-36.3843385325082</v>
       </c>
       <c r="F582">
         <v>-1</v>
       </c>
       <c r="G582">
-        <v>0.088442028328768</v>
+        <v>0.09150492295847297</v>
       </c>
       <c r="H582">
-        <v>0.08696246709405367</v>
+        <v>0.09398433853250819</v>
       </c>
       <c r="I582">
-        <v>0.4004387652856565</v>
+        <v>1.879415574035228</v>
       </c>
       <c r="J582">
-        <v>4.496343622619513</v>
+        <v>4.953217213716428</v>
       </c>
       <c r="K582">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L582">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M582">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N582">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O582">
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -30898,49 +30832,49 @@
         <v>0</v>
       </c>
       <c r="B583" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C583">
-        <v>-29.5734906727053</v>
+        <v>-32.25915643789906</v>
       </c>
       <c r="D583" t="s">
         <v>210</v>
       </c>
       <c r="E583">
-        <v>-29.97364167265007</v>
+        <v>-34.06088826436726</v>
       </c>
       <c r="F583">
         <v>-1</v>
       </c>
       <c r="G583">
-        <v>0.0884734906727053</v>
+        <v>0.08925915643789907</v>
       </c>
       <c r="H583">
-        <v>0.08699364167265007</v>
+        <v>0.09166088826436726</v>
       </c>
       <c r="I583">
-        <v>0.4001509999447705</v>
+        <v>1.801731826468206</v>
       </c>
       <c r="J583">
-        <v>4.498741667126929</v>
+        <v>4.776663241973196</v>
       </c>
       <c r="K583">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L583">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M583">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N583">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O583">
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -30948,49 +30882,49 @@
         <v>0</v>
       </c>
       <c r="B584" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C584">
-        <v>-29.90971818598193</v>
+        <v>-30.22487523110544</v>
       </c>
       <c r="D584" t="s">
         <v>210</v>
       </c>
       <c r="E584">
-        <v>-30.30679393428087</v>
+        <v>-31.95623883972857</v>
       </c>
       <c r="F584">
         <v>-1</v>
       </c>
       <c r="G584">
-        <v>0.08880971818598192</v>
+        <v>0.08722487523110545</v>
       </c>
       <c r="H584">
-        <v>0.08732679393428087</v>
+        <v>0.08955623883972857</v>
       </c>
       <c r="I584">
-        <v>0.3970757482989455</v>
+        <v>1.731363608623138</v>
       </c>
       <c r="J584">
-        <v>4.524368764175452</v>
+        <v>4.616735474143509</v>
       </c>
       <c r="K584">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L584">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M584">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N584">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O584">
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -30998,49 +30932,49 @@
         <v>0</v>
       </c>
       <c r="B585" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C585">
-        <v>-30.30344083523496</v>
+        <v>-30.27024884026075</v>
       </c>
       <c r="D585" t="s">
         <v>210</v>
       </c>
       <c r="E585">
-        <v>-30.69691546174195</v>
+        <v>-32.0031819762446</v>
       </c>
       <c r="F585">
         <v>-1</v>
       </c>
       <c r="G585">
-        <v>0.08920344083523496</v>
+        <v>0.08727024884026074</v>
       </c>
       <c r="H585">
-        <v>0.08771691546174196</v>
+        <v>0.08960318197624462</v>
       </c>
       <c r="I585">
-        <v>0.3934746265069933</v>
+        <v>1.732933135983856</v>
       </c>
       <c r="J585">
-        <v>4.554378112441689</v>
+        <v>4.620302581781505</v>
       </c>
       <c r="K585">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L585">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M585">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N585">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O585">
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31048,49 +30982,49 @@
         <v>0</v>
       </c>
       <c r="B586" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C586">
-        <v>-31.63362431108586</v>
+        <v>-28.39148072431525</v>
       </c>
       <c r="D586" t="s">
         <v>210</v>
       </c>
       <c r="E586">
-        <v>-32.01493262531373</v>
+        <v>-30.05942502609973</v>
       </c>
       <c r="F586">
         <v>-1</v>
       </c>
       <c r="G586">
-        <v>0.09053362431108586</v>
+        <v>0.08539148072431525</v>
       </c>
       <c r="H586">
-        <v>0.08903493262531374</v>
+        <v>0.08765942502609975</v>
       </c>
       <c r="I586">
-        <v>0.3813083142278693</v>
+        <v>1.667944301784484</v>
       </c>
       <c r="J586">
-        <v>4.655764048101057</v>
+        <v>4.47260068587384</v>
       </c>
       <c r="K586">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L586">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M586">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N586">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O586">
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31098,49 +31032,49 @@
         <v>0</v>
       </c>
       <c r="B587" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C587">
-        <v>-33.31842103969069</v>
+        <v>-31.37073517503052</v>
       </c>
       <c r="D587" t="s">
         <v>210</v>
       </c>
       <c r="E587">
-        <v>-33.68431962774231</v>
+        <v>-33.14173544838063</v>
       </c>
       <c r="F587">
         <v>-1</v>
       </c>
       <c r="G587">
-        <v>0.0922184210396907</v>
+        <v>0.08837073517503052</v>
       </c>
       <c r="H587">
-        <v>0.09070431962774231</v>
+        <v>0.09074173544838063</v>
       </c>
       <c r="I587">
-        <v>0.3658985880516212</v>
+        <v>1.771000273350111</v>
       </c>
       <c r="J587">
-        <v>4.784178432903254</v>
+        <v>4.706818803068437</v>
       </c>
       <c r="K587">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L587">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M587">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N587">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O587">
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31148,49 +31082,49 @@
         <v>0</v>
       </c>
       <c r="B588" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C588">
-        <v>-34.14743957218464</v>
+        <v>-39.64900636492419</v>
       </c>
       <c r="D588" t="s">
         <v>210</v>
       </c>
       <c r="E588">
-        <v>-34.50575567365856</v>
+        <v>-41.70636193100647</v>
       </c>
       <c r="F588">
         <v>-1</v>
       </c>
       <c r="G588">
-        <v>0.09304743957218463</v>
+        <v>0.0966490063649242</v>
       </c>
       <c r="H588">
-        <v>0.09152575567365857</v>
+        <v>0.09930636193100646</v>
       </c>
       <c r="I588">
-        <v>0.3583161014739176</v>
+        <v>2.057355566082279</v>
       </c>
       <c r="J588">
-        <v>4.847365821050658</v>
+        <v>5.357626286550643</v>
       </c>
       <c r="K588">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L588">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M588">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N588">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O588">
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31198,49 +31132,49 @@
         <v>0</v>
       </c>
       <c r="B589" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C589">
-        <v>-35.28047083670324</v>
+        <v>-40.52640967279994</v>
       </c>
       <c r="D589" t="s">
         <v>210</v>
       </c>
       <c r="E589">
-        <v>-35.62842384734316</v>
+        <v>-42.614115667771</v>
       </c>
       <c r="F589">
         <v>-1</v>
       </c>
       <c r="G589">
-        <v>0.09418047083670325</v>
+        <v>0.09752640967279995</v>
       </c>
       <c r="H589">
-        <v>0.09264842384734318</v>
+        <v>0.100214115667771</v>
       </c>
       <c r="I589">
-        <v>0.3479530106399125</v>
+        <v>2.08770599497106</v>
       </c>
       <c r="J589">
-        <v>4.93372491133409</v>
+        <v>5.426604534025152</v>
       </c>
       <c r="K589">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L589">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M589">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N589">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O589">
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31248,1899 +31182,49 @@
         <v>0</v>
       </c>
       <c r="B590" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C590">
-        <v>-36.21825180914649</v>
+        <v>-40.50608277182309</v>
       </c>
       <c r="D590" t="s">
         <v>210</v>
       </c>
       <c r="E590">
-        <v>-36.55762755479454</v>
+        <v>-42.59308563499937</v>
       </c>
       <c r="F590">
         <v>-1</v>
       </c>
       <c r="G590">
-        <v>0.0951182518091465</v>
+        <v>0.09750608277182309</v>
       </c>
       <c r="H590">
-        <v>0.09357762755479455</v>
+        <v>0.1001930856349994</v>
       </c>
       <c r="I590">
-        <v>0.3393757456480415</v>
+        <v>2.087002863176281</v>
       </c>
       <c r="J590">
-        <v>5.005202119599581</v>
+        <v>5.425006507218797</v>
       </c>
       <c r="K590">
-        <v>13.12</v>
+        <v>12.72</v>
       </c>
       <c r="L590">
-        <v>29.45</v>
+        <v>28.5</v>
       </c>
       <c r="M590">
-        <v>13</v>
+        <v>13.16</v>
       </c>
       <c r="N590">
-        <v>28.51</v>
+        <v>28.8</v>
       </c>
       <c r="O590">
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="591" spans="1:16">
-      <c r="A591" s="1">
-        <v>0</v>
-      </c>
-      <c r="B591" t="s">
-        <v>98</v>
-      </c>
-      <c r="C591">
-        <v>-36.98095004193327</v>
-      </c>
-      <c r="D591" t="s">
-        <v>210</v>
-      </c>
-      <c r="E591">
-        <v>-37.31334988911071</v>
-      </c>
-      <c r="F591">
-        <v>-1</v>
-      </c>
-      <c r="G591">
-        <v>0.09588095004193328</v>
-      </c>
-      <c r="H591">
-        <v>0.09433334988911073</v>
-      </c>
-      <c r="I591">
-        <v>0.3323998471774416</v>
-      </c>
-      <c r="J591">
-        <v>5.063334606854671</v>
-      </c>
-      <c r="K591">
-        <v>13.12</v>
-      </c>
-      <c r="L591">
-        <v>29.45</v>
-      </c>
-      <c r="M591">
-        <v>13</v>
-      </c>
-      <c r="N591">
-        <v>28.51</v>
-      </c>
-      <c r="O591">
-        <v>1</v>
-      </c>
-      <c r="P591" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="592" spans="1:16">
-      <c r="A592" s="1">
-        <v>0</v>
-      </c>
-      <c r="B592" t="s">
-        <v>96</v>
-      </c>
-      <c r="C592">
-        <v>-36.18997893562975</v>
-      </c>
-      <c r="D592" t="s">
-        <v>210</v>
-      </c>
-      <c r="E592">
-        <v>-37.60397218264046</v>
-      </c>
-      <c r="F592">
-        <v>-1</v>
-      </c>
-      <c r="G592">
-        <v>0.09318997893562976</v>
-      </c>
-      <c r="H592">
-        <v>0.09462397218264047</v>
-      </c>
-      <c r="I592">
-        <v>1.413993247010708</v>
-      </c>
-      <c r="J592">
-        <v>5.085690167895421</v>
-      </c>
-      <c r="K592">
-        <v>12.72</v>
-      </c>
-      <c r="L592">
-        <v>28.5</v>
-      </c>
-      <c r="M592">
-        <v>13</v>
-      </c>
-      <c r="N592">
-        <v>28.51</v>
-      </c>
-      <c r="O592">
-        <v>1</v>
-      </c>
-      <c r="P592" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="593" spans="1:16">
-      <c r="A593" s="1">
-        <v>0</v>
-      </c>
-      <c r="B593" t="s">
-        <v>96</v>
-      </c>
-      <c r="C593">
-        <v>-36.79440237149454</v>
-      </c>
-      <c r="D593" t="s">
-        <v>210</v>
-      </c>
-      <c r="E593">
-        <v>-38.22170053690479</v>
-      </c>
-      <c r="F593">
-        <v>-1</v>
-      </c>
-      <c r="G593">
-        <v>0.09379440237149454</v>
-      </c>
-      <c r="H593">
-        <v>0.0952417005369048</v>
-      </c>
-      <c r="I593">
-        <v>1.427298165410249</v>
-      </c>
-      <c r="J593">
-        <v>5.133207733608061</v>
-      </c>
-      <c r="K593">
-        <v>12.72</v>
-      </c>
-      <c r="L593">
-        <v>28.5</v>
-      </c>
-      <c r="M593">
-        <v>13</v>
-      </c>
-      <c r="N593">
-        <v>28.51</v>
-      </c>
-      <c r="O593">
-        <v>1</v>
-      </c>
-      <c r="P593" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="594" spans="1:16">
-      <c r="A594" s="1">
-        <v>0</v>
-      </c>
-      <c r="B594" t="s">
-        <v>96</v>
-      </c>
-      <c r="C594">
-        <v>-36.55608045442354</v>
-      </c>
-      <c r="D594" t="s">
-        <v>210</v>
-      </c>
-      <c r="E594">
-        <v>-37.97813253989825</v>
-      </c>
-      <c r="F594">
-        <v>-1</v>
-      </c>
-      <c r="G594">
-        <v>0.09355608045442354</v>
-      </c>
-      <c r="H594">
-        <v>0.09499813253989826</v>
-      </c>
-      <c r="I594">
-        <v>1.422052085474718</v>
-      </c>
-      <c r="J594">
-        <v>5.114471733838328</v>
-      </c>
-      <c r="K594">
-        <v>12.72</v>
-      </c>
-      <c r="L594">
-        <v>28.5</v>
-      </c>
-      <c r="M594">
-        <v>13</v>
-      </c>
-      <c r="N594">
-        <v>28.51</v>
-      </c>
-      <c r="O594">
-        <v>1</v>
-      </c>
-      <c r="P594" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="595" spans="1:16">
-      <c r="A595" s="1">
-        <v>0</v>
-      </c>
-      <c r="B595" t="s">
-        <v>96</v>
-      </c>
-      <c r="C595">
-        <v>-36.02878397309011</v>
-      </c>
-      <c r="D595" t="s">
-        <v>210</v>
-      </c>
-      <c r="E595">
-        <v>-37.43922890331537</v>
-      </c>
-      <c r="F595">
-        <v>-1</v>
-      </c>
-      <c r="G595">
-        <v>0.09302878397309011</v>
-      </c>
-      <c r="H595">
-        <v>0.09445922890331537</v>
-      </c>
-      <c r="I595">
-        <v>1.410444930225253</v>
-      </c>
-      <c r="J595">
-        <v>5.073017607947336</v>
-      </c>
-      <c r="K595">
-        <v>12.72</v>
-      </c>
-      <c r="L595">
-        <v>28.5</v>
-      </c>
-      <c r="M595">
-        <v>13</v>
-      </c>
-      <c r="N595">
-        <v>28.51</v>
-      </c>
-      <c r="O595">
-        <v>1</v>
-      </c>
-      <c r="P595" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="596" spans="1:16">
-      <c r="A596" s="1">
-        <v>0</v>
-      </c>
-      <c r="B596" t="s">
-        <v>96</v>
-      </c>
-      <c r="C596">
-        <v>-35.32789307633533</v>
-      </c>
-      <c r="D596" t="s">
-        <v>210</v>
-      </c>
-      <c r="E596">
-        <v>-36.72290959059427</v>
-      </c>
-      <c r="F596">
-        <v>-1</v>
-      </c>
-      <c r="G596">
-        <v>0.09232789307633534</v>
-      </c>
-      <c r="H596">
-        <v>0.09374290959059428</v>
-      </c>
-      <c r="I596">
-        <v>1.395016514258941</v>
-      </c>
-      <c r="J596">
-        <v>5.017916122353406</v>
-      </c>
-      <c r="K596">
-        <v>12.72</v>
-      </c>
-      <c r="L596">
-        <v>28.5</v>
-      </c>
-      <c r="M596">
-        <v>13</v>
-      </c>
-      <c r="N596">
-        <v>28.51</v>
-      </c>
-      <c r="O596">
-        <v>1</v>
-      </c>
-      <c r="P596" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="597" spans="1:16">
-      <c r="A597" s="1">
-        <v>0</v>
-      </c>
-      <c r="B597" t="s">
-        <v>96</v>
-      </c>
-      <c r="C597">
-        <v>-34.50492295847297</v>
-      </c>
-      <c r="D597" t="s">
-        <v>210</v>
-      </c>
-      <c r="E597">
-        <v>-35.88182377831356</v>
-      </c>
-      <c r="F597">
-        <v>-1</v>
-      </c>
-      <c r="G597">
-        <v>0.09150492295847297</v>
-      </c>
-      <c r="H597">
-        <v>0.09290182377831357</v>
-      </c>
-      <c r="I597">
-        <v>1.376900819840593</v>
-      </c>
-      <c r="J597">
-        <v>4.953217213716428</v>
-      </c>
-      <c r="K597">
-        <v>12.72</v>
-      </c>
-      <c r="L597">
-        <v>28.5</v>
-      </c>
-      <c r="M597">
-        <v>13</v>
-      </c>
-      <c r="N597">
-        <v>28.51</v>
-      </c>
-      <c r="O597">
-        <v>1</v>
-      </c>
-      <c r="P597" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="598" spans="1:16">
-      <c r="A598" s="1">
-        <v>0</v>
-      </c>
-      <c r="B598" t="s">
-        <v>96</v>
-      </c>
-      <c r="C598">
-        <v>-32.25915643789906</v>
-      </c>
-      <c r="D598" t="s">
-        <v>210</v>
-      </c>
-      <c r="E598">
-        <v>-33.58662214565155</v>
-      </c>
-      <c r="F598">
-        <v>-1</v>
-      </c>
-      <c r="G598">
-        <v>0.08925915643789907</v>
-      </c>
-      <c r="H598">
-        <v>0.09060662214565156</v>
-      </c>
-      <c r="I598">
-        <v>1.327465707752488</v>
-      </c>
-      <c r="J598">
-        <v>4.776663241973196</v>
-      </c>
-      <c r="K598">
-        <v>12.72</v>
-      </c>
-      <c r="L598">
-        <v>28.5</v>
-      </c>
-      <c r="M598">
-        <v>13</v>
-      </c>
-      <c r="N598">
-        <v>28.51</v>
-      </c>
-      <c r="O598">
-        <v>1</v>
-      </c>
-      <c r="P598" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="599" spans="1:16">
-      <c r="A599" s="1">
-        <v>0</v>
-      </c>
-      <c r="B599" t="s">
-        <v>96</v>
-      </c>
-      <c r="C599">
-        <v>-30.22487523110544</v>
-      </c>
-      <c r="D599" t="s">
-        <v>210</v>
-      </c>
-      <c r="E599">
-        <v>-31.50756116386561</v>
-      </c>
-      <c r="F599">
-        <v>-1</v>
-      </c>
-      <c r="G599">
-        <v>0.08722487523110545</v>
-      </c>
-      <c r="H599">
-        <v>0.08852756116386562</v>
-      </c>
-      <c r="I599">
-        <v>1.282685932760177</v>
-      </c>
-      <c r="J599">
-        <v>4.616735474143509</v>
-      </c>
-      <c r="K599">
-        <v>12.72</v>
-      </c>
-      <c r="L599">
-        <v>28.5</v>
-      </c>
-      <c r="M599">
-        <v>13</v>
-      </c>
-      <c r="N599">
-        <v>28.51</v>
-      </c>
-      <c r="O599">
-        <v>1</v>
-      </c>
-      <c r="P599" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="600" spans="1:16">
-      <c r="A600" s="1">
-        <v>0</v>
-      </c>
-      <c r="B600" t="s">
-        <v>96</v>
-      </c>
-      <c r="C600">
-        <v>-30.27024884026075</v>
-      </c>
-      <c r="D600" t="s">
-        <v>210</v>
-      </c>
-      <c r="E600">
-        <v>-31.55393356315956</v>
-      </c>
-      <c r="F600">
-        <v>-1</v>
-      </c>
-      <c r="G600">
-        <v>0.08727024884026074</v>
-      </c>
-      <c r="H600">
-        <v>0.08857393356315957</v>
-      </c>
-      <c r="I600">
-        <v>1.283684722898816</v>
-      </c>
-      <c r="J600">
-        <v>4.620302581781505</v>
-      </c>
-      <c r="K600">
-        <v>12.72</v>
-      </c>
-      <c r="L600">
-        <v>28.5</v>
-      </c>
-      <c r="M600">
-        <v>13</v>
-      </c>
-      <c r="N600">
-        <v>28.51</v>
-      </c>
-      <c r="O600">
-        <v>1</v>
-      </c>
-      <c r="P600" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="601" spans="1:16">
-      <c r="A601" s="1">
-        <v>0</v>
-      </c>
-      <c r="B601" t="s">
-        <v>96</v>
-      </c>
-      <c r="C601">
-        <v>-28.39148072431525</v>
-      </c>
-      <c r="D601" t="s">
-        <v>210</v>
-      </c>
-      <c r="E601">
-        <v>-29.63380891635992</v>
-      </c>
-      <c r="F601">
-        <v>-1</v>
-      </c>
-      <c r="G601">
-        <v>0.08539148072431525</v>
-      </c>
-      <c r="H601">
-        <v>0.08665380891635992</v>
-      </c>
-      <c r="I601">
-        <v>1.24232819204467</v>
-      </c>
-      <c r="J601">
-        <v>4.47260068587384</v>
-      </c>
-      <c r="K601">
-        <v>12.72</v>
-      </c>
-      <c r="L601">
-        <v>28.5</v>
-      </c>
-      <c r="M601">
-        <v>13</v>
-      </c>
-      <c r="N601">
-        <v>28.51</v>
-      </c>
-      <c r="O601">
-        <v>1</v>
-      </c>
-      <c r="P601" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="602" spans="1:16">
-      <c r="A602" s="1">
-        <v>0</v>
-      </c>
-      <c r="B602" t="s">
-        <v>96</v>
-      </c>
-      <c r="C602">
-        <v>-26.98841867725971</v>
-      </c>
-      <c r="D602" t="s">
-        <v>210</v>
-      </c>
-      <c r="E602">
-        <v>-28.19986185568995</v>
-      </c>
-      <c r="F602">
-        <v>-1</v>
-      </c>
-      <c r="G602">
-        <v>0.08398841867725972</v>
-      </c>
-      <c r="H602">
-        <v>0.08521986185568996</v>
-      </c>
-      <c r="I602">
-        <v>1.21144317843024</v>
-      </c>
-      <c r="J602">
-        <v>4.362297065822304</v>
-      </c>
-      <c r="K602">
-        <v>12.72</v>
-      </c>
-      <c r="L602">
-        <v>28.5</v>
-      </c>
-      <c r="M602">
-        <v>13</v>
-      </c>
-      <c r="N602">
-        <v>28.51</v>
-      </c>
-      <c r="O602">
-        <v>1</v>
-      </c>
-      <c r="P602" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="603" spans="1:16">
-      <c r="A603" s="1">
-        <v>0</v>
-      </c>
-      <c r="B603" t="s">
-        <v>96</v>
-      </c>
-      <c r="C603">
-        <v>-26.85373737373742</v>
-      </c>
-      <c r="D603" t="s">
-        <v>210</v>
-      </c>
-      <c r="E603">
-        <v>-28.06221586938572</v>
-      </c>
-      <c r="F603">
-        <v>-1</v>
-      </c>
-      <c r="G603">
-        <v>0.08385373737373741</v>
-      </c>
-      <c r="H603">
-        <v>0.08508221586938572</v>
-      </c>
-      <c r="I603">
-        <v>1.208478495648304</v>
-      </c>
-      <c r="J603">
-        <v>4.351708913029671</v>
-      </c>
-      <c r="K603">
-        <v>12.72</v>
-      </c>
-      <c r="L603">
-        <v>28.5</v>
-      </c>
-      <c r="M603">
-        <v>13</v>
-      </c>
-      <c r="N603">
-        <v>28.51</v>
-      </c>
-      <c r="O603">
-        <v>1</v>
-      </c>
-      <c r="P603" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="604" spans="1:16">
-      <c r="A604" s="1">
-        <v>0</v>
-      </c>
-      <c r="B604" t="s">
-        <v>96</v>
-      </c>
-      <c r="C604">
-        <v>-29.21936414694369</v>
-      </c>
-      <c r="D604" t="s">
-        <v>210</v>
-      </c>
-      <c r="E604">
-        <v>-30.47991618791415</v>
-      </c>
-      <c r="F604">
-        <v>-1</v>
-      </c>
-      <c r="G604">
-        <v>0.08621936414694369</v>
-      </c>
-      <c r="H604">
-        <v>0.08749991618791415</v>
-      </c>
-      <c r="I604">
-        <v>1.260552040970456</v>
-      </c>
-      <c r="J604">
-        <v>4.53768586060878</v>
-      </c>
-      <c r="K604">
-        <v>12.72</v>
-      </c>
-      <c r="L604">
-        <v>28.5</v>
-      </c>
-      <c r="M604">
-        <v>13</v>
-      </c>
-      <c r="N604">
-        <v>28.51</v>
-      </c>
-      <c r="O604">
-        <v>1</v>
-      </c>
-      <c r="P604" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="605" spans="1:16">
-      <c r="A605" s="1">
-        <v>0</v>
-      </c>
-      <c r="B605" t="s">
-        <v>96</v>
-      </c>
-      <c r="C605">
-        <v>-31.37073517503052</v>
-      </c>
-      <c r="D605" t="s">
-        <v>210</v>
-      </c>
-      <c r="E605">
-        <v>-32.67864443988968</v>
-      </c>
-      <c r="F605">
-        <v>-1</v>
-      </c>
-      <c r="G605">
-        <v>0.08837073517503052</v>
-      </c>
-      <c r="H605">
-        <v>0.08969864443988967</v>
-      </c>
-      <c r="I605">
-        <v>1.307909264859163</v>
-      </c>
-      <c r="J605">
-        <v>4.706818803068437</v>
-      </c>
-      <c r="K605">
-        <v>12.72</v>
-      </c>
-      <c r="L605">
-        <v>28.5</v>
-      </c>
-      <c r="M605">
-        <v>13</v>
-      </c>
-      <c r="N605">
-        <v>28.51</v>
-      </c>
-      <c r="O605">
-        <v>1</v>
-      </c>
-      <c r="P605" t="s">
         <v>451</v>
-      </c>
-    </row>
-    <row r="606" spans="1:16">
-      <c r="A606" s="1">
-        <v>0</v>
-      </c>
-      <c r="B606" t="s">
-        <v>96</v>
-      </c>
-      <c r="C606">
-        <v>-31.15333929689864</v>
-      </c>
-      <c r="D606" t="s">
-        <v>210</v>
-      </c>
-      <c r="E606">
-        <v>-32.45646311789955</v>
-      </c>
-      <c r="F606">
-        <v>-1</v>
-      </c>
-      <c r="G606">
-        <v>0.08815333929689864</v>
-      </c>
-      <c r="H606">
-        <v>0.08947646311789954</v>
-      </c>
-      <c r="I606">
-        <v>1.303123821000909</v>
-      </c>
-      <c r="J606">
-        <v>4.689727932146119</v>
-      </c>
-      <c r="K606">
-        <v>12.72</v>
-      </c>
-      <c r="L606">
-        <v>28.5</v>
-      </c>
-      <c r="M606">
-        <v>13</v>
-      </c>
-      <c r="N606">
-        <v>28.51</v>
-      </c>
-      <c r="O606">
-        <v>1</v>
-      </c>
-      <c r="P606" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="607" spans="1:16">
-      <c r="A607" s="1">
-        <v>0</v>
-      </c>
-      <c r="B607" t="s">
-        <v>96</v>
-      </c>
-      <c r="C607">
-        <v>-31.96484703340393</v>
-      </c>
-      <c r="D607" t="s">
-        <v>210</v>
-      </c>
-      <c r="E607">
-        <v>-33.28583423225244</v>
-      </c>
-      <c r="F607">
-        <v>-1</v>
-      </c>
-      <c r="G607">
-        <v>0.08896484703340395</v>
-      </c>
-      <c r="H607">
-        <v>0.09030583423225245</v>
-      </c>
-      <c r="I607">
-        <v>1.320987198848506</v>
-      </c>
-      <c r="J607">
-        <v>4.753525710173265</v>
-      </c>
-      <c r="K607">
-        <v>12.72</v>
-      </c>
-      <c r="L607">
-        <v>28.5</v>
-      </c>
-      <c r="M607">
-        <v>13</v>
-      </c>
-      <c r="N607">
-        <v>28.51</v>
-      </c>
-      <c r="O607">
-        <v>1</v>
-      </c>
-      <c r="P607" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="608" spans="1:16">
-      <c r="A608" s="1">
-        <v>0</v>
-      </c>
-      <c r="B608" t="s">
-        <v>96</v>
-      </c>
-      <c r="C608">
-        <v>-32.50581065619588</v>
-      </c>
-      <c r="D608" t="s">
-        <v>210</v>
-      </c>
-      <c r="E608">
-        <v>-33.83870585931967</v>
-      </c>
-      <c r="F608">
-        <v>-1</v>
-      </c>
-      <c r="G608">
-        <v>0.08950581065619588</v>
-      </c>
-      <c r="H608">
-        <v>0.09085870585931968</v>
-      </c>
-      <c r="I608">
-        <v>1.332895203123798</v>
-      </c>
-      <c r="J608">
-        <v>4.796054296870745</v>
-      </c>
-      <c r="K608">
-        <v>12.72</v>
-      </c>
-      <c r="L608">
-        <v>28.5</v>
-      </c>
-      <c r="M608">
-        <v>13</v>
-      </c>
-      <c r="N608">
-        <v>28.51</v>
-      </c>
-      <c r="O608">
-        <v>1</v>
-      </c>
-      <c r="P608" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="609" spans="1:16">
-      <c r="A609" s="1">
-        <v>0</v>
-      </c>
-      <c r="B609" t="s">
-        <v>96</v>
-      </c>
-      <c r="C609">
-        <v>-33.06316671563285</v>
-      </c>
-      <c r="D609" t="s">
-        <v>210</v>
-      </c>
-      <c r="E609">
-        <v>-34.40833076283231</v>
-      </c>
-      <c r="F609">
-        <v>-1</v>
-      </c>
-      <c r="G609">
-        <v>0.09006316671563284</v>
-      </c>
-      <c r="H609">
-        <v>0.09142833076283231</v>
-      </c>
-      <c r="I609">
-        <v>1.345164047199461</v>
-      </c>
-      <c r="J609">
-        <v>4.839871597140947</v>
-      </c>
-      <c r="K609">
-        <v>12.72</v>
-      </c>
-      <c r="L609">
-        <v>28.5</v>
-      </c>
-      <c r="M609">
-        <v>13</v>
-      </c>
-      <c r="N609">
-        <v>28.51</v>
-      </c>
-      <c r="O609">
-        <v>1</v>
-      </c>
-      <c r="P609" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="610" spans="1:16">
-      <c r="A610" s="1">
-        <v>0</v>
-      </c>
-      <c r="B610" t="s">
-        <v>96</v>
-      </c>
-      <c r="C610">
-        <v>-33.83766552761887</v>
-      </c>
-      <c r="D610" t="s">
-        <v>210</v>
-      </c>
-      <c r="E610">
-        <v>-35.19987829080544</v>
-      </c>
-      <c r="F610">
-        <v>-1</v>
-      </c>
-      <c r="G610">
-        <v>0.09083766552761886</v>
-      </c>
-      <c r="H610">
-        <v>0.09221987829080544</v>
-      </c>
-      <c r="I610">
-        <v>1.362212763186577</v>
-      </c>
-      <c r="J610">
-        <v>4.900759868523496</v>
-      </c>
-      <c r="K610">
-        <v>12.72</v>
-      </c>
-      <c r="L610">
-        <v>28.5</v>
-      </c>
-      <c r="M610">
-        <v>13</v>
-      </c>
-      <c r="N610">
-        <v>28.51</v>
-      </c>
-      <c r="O610">
-        <v>1</v>
-      </c>
-      <c r="P610" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="611" spans="1:16">
-      <c r="A611" s="1">
-        <v>0</v>
-      </c>
-      <c r="B611" t="s">
-        <v>96</v>
-      </c>
-      <c r="C611">
-        <v>-34.61375836901416</v>
-      </c>
-      <c r="D611" t="s">
-        <v>210</v>
-      </c>
-      <c r="E611">
-        <v>-35.99305493688554</v>
-      </c>
-      <c r="F611">
-        <v>-1</v>
-      </c>
-      <c r="G611">
-        <v>0.09161375836901417</v>
-      </c>
-      <c r="H611">
-        <v>0.09301305493688555</v>
-      </c>
-      <c r="I611">
-        <v>1.379296567871378</v>
-      </c>
-      <c r="J611">
-        <v>4.961773456683503</v>
-      </c>
-      <c r="K611">
-        <v>12.72</v>
-      </c>
-      <c r="L611">
-        <v>28.5</v>
-      </c>
-      <c r="M611">
-        <v>13</v>
-      </c>
-      <c r="N611">
-        <v>28.51</v>
-      </c>
-      <c r="O611">
-        <v>1</v>
-      </c>
-      <c r="P611" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="612" spans="1:16">
-      <c r="A612" s="1">
-        <v>0</v>
-      </c>
-      <c r="B612" t="s">
-        <v>96</v>
-      </c>
-      <c r="C612">
-        <v>-35.78190054745771</v>
-      </c>
-      <c r="D612" t="s">
-        <v>210</v>
-      </c>
-      <c r="E612">
-        <v>-37.18691093686714</v>
-      </c>
-      <c r="F612">
-        <v>-1</v>
-      </c>
-      <c r="G612">
-        <v>0.0927819005474577</v>
-      </c>
-      <c r="H612">
-        <v>0.09420691093686714</v>
-      </c>
-      <c r="I612">
-        <v>1.405010389409426</v>
-      </c>
-      <c r="J612">
-        <v>5.053608533605165</v>
-      </c>
-      <c r="K612">
-        <v>12.72</v>
-      </c>
-      <c r="L612">
-        <v>28.5</v>
-      </c>
-      <c r="M612">
-        <v>13</v>
-      </c>
-      <c r="N612">
-        <v>28.51</v>
-      </c>
-      <c r="O612">
-        <v>1</v>
-      </c>
-      <c r="P612" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="613" spans="1:16">
-      <c r="A613" s="1">
-        <v>0</v>
-      </c>
-      <c r="B613" t="s">
-        <v>96</v>
-      </c>
-      <c r="C613">
-        <v>-37.00566172157619</v>
-      </c>
-      <c r="D613" t="s">
-        <v>210</v>
-      </c>
-      <c r="E613">
-        <v>-38.43761025003855</v>
-      </c>
-      <c r="F613">
-        <v>-1</v>
-      </c>
-      <c r="G613">
-        <v>0.09400566172157619</v>
-      </c>
-      <c r="H613">
-        <v>0.09545761025003856</v>
-      </c>
-      <c r="I613">
-        <v>1.431948528462357</v>
-      </c>
-      <c r="J613">
-        <v>5.149816173079889</v>
-      </c>
-      <c r="K613">
-        <v>12.72</v>
-      </c>
-      <c r="L613">
-        <v>28.5</v>
-      </c>
-      <c r="M613">
-        <v>13</v>
-      </c>
-      <c r="N613">
-        <v>28.51</v>
-      </c>
-      <c r="O613">
-        <v>1</v>
-      </c>
-      <c r="P613" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="614" spans="1:16">
-      <c r="A614" s="1">
-        <v>0</v>
-      </c>
-      <c r="B614" t="s">
-        <v>96</v>
-      </c>
-      <c r="C614">
-        <v>-37.48482250437436</v>
-      </c>
-      <c r="D614" t="s">
-        <v>210</v>
-      </c>
-      <c r="E614">
-        <v>-38.92731859723794</v>
-      </c>
-      <c r="F614">
-        <v>-1</v>
-      </c>
-      <c r="G614">
-        <v>0.09448482250437437</v>
-      </c>
-      <c r="H614">
-        <v>0.09594731859723796</v>
-      </c>
-      <c r="I614">
-        <v>1.442496092863578</v>
-      </c>
-      <c r="J614">
-        <v>5.18748604594138</v>
-      </c>
-      <c r="K614">
-        <v>12.72</v>
-      </c>
-      <c r="L614">
-        <v>28.5</v>
-      </c>
-      <c r="M614">
-        <v>13</v>
-      </c>
-      <c r="N614">
-        <v>28.51</v>
-      </c>
-      <c r="O614">
-        <v>1</v>
-      </c>
-      <c r="P614" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="615" spans="1:16">
-      <c r="A615" s="1">
-        <v>0</v>
-      </c>
-      <c r="B615" t="s">
-        <v>96</v>
-      </c>
-      <c r="C615">
-        <v>-38.41804439849064</v>
-      </c>
-      <c r="D615" t="s">
-        <v>210</v>
-      </c>
-      <c r="E615">
-        <v>-39.88108311166495</v>
-      </c>
-      <c r="F615">
-        <v>-1</v>
-      </c>
-      <c r="G615">
-        <v>0.09541804439849064</v>
-      </c>
-      <c r="H615">
-        <v>0.09690108311166497</v>
-      </c>
-      <c r="I615">
-        <v>1.463038713174313</v>
-      </c>
-      <c r="J615">
-        <v>5.26085254705115</v>
-      </c>
-      <c r="K615">
-        <v>12.72</v>
-      </c>
-      <c r="L615">
-        <v>28.5</v>
-      </c>
-      <c r="M615">
-        <v>13</v>
-      </c>
-      <c r="N615">
-        <v>28.51</v>
-      </c>
-      <c r="O615">
-        <v>1</v>
-      </c>
-      <c r="P615" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="616" spans="1:16">
-      <c r="A616" s="1">
-        <v>0</v>
-      </c>
-      <c r="B616" t="s">
-        <v>96</v>
-      </c>
-      <c r="C616">
-        <v>-39.64900636492419</v>
-      </c>
-      <c r="D616" t="s">
-        <v>210</v>
-      </c>
-      <c r="E616">
-        <v>-41.13914172515835</v>
-      </c>
-      <c r="F616">
-        <v>-1</v>
-      </c>
-      <c r="G616">
-        <v>0.0966490063649242</v>
-      </c>
-      <c r="H616">
-        <v>0.09815914172515837</v>
-      </c>
-      <c r="I616">
-        <v>1.490135360234163</v>
-      </c>
-      <c r="J616">
-        <v>5.357626286550643</v>
-      </c>
-      <c r="K616">
-        <v>12.72</v>
-      </c>
-      <c r="L616">
-        <v>28.5</v>
-      </c>
-      <c r="M616">
-        <v>13</v>
-      </c>
-      <c r="N616">
-        <v>28.51</v>
-      </c>
-      <c r="O616">
-        <v>1</v>
-      </c>
-      <c r="P616" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="617" spans="1:16">
-      <c r="A617" s="1">
-        <v>0</v>
-      </c>
-      <c r="B617" t="s">
-        <v>96</v>
-      </c>
-      <c r="C617">
-        <v>-40.52640967279994</v>
-      </c>
-      <c r="D617" t="s">
-        <v>210</v>
-      </c>
-      <c r="E617">
-        <v>-42.03585894232698</v>
-      </c>
-      <c r="F617">
-        <v>-1</v>
-      </c>
-      <c r="G617">
-        <v>0.09752640967279995</v>
-      </c>
-      <c r="H617">
-        <v>0.09905585894232699</v>
-      </c>
-      <c r="I617">
-        <v>1.509449269527039</v>
-      </c>
-      <c r="J617">
-        <v>5.426604534025152</v>
-      </c>
-      <c r="K617">
-        <v>12.72</v>
-      </c>
-      <c r="L617">
-        <v>28.5</v>
-      </c>
-      <c r="M617">
-        <v>13</v>
-      </c>
-      <c r="N617">
-        <v>28.51</v>
-      </c>
-      <c r="O617">
-        <v>1</v>
-      </c>
-      <c r="P617" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="618" spans="1:16">
-      <c r="A618" s="1">
-        <v>0</v>
-      </c>
-      <c r="B618" t="s">
-        <v>96</v>
-      </c>
-      <c r="C618">
-        <v>-40.50608277182309</v>
-      </c>
-      <c r="D618" t="s">
-        <v>210</v>
-      </c>
-      <c r="E618">
-        <v>-42.01508459384435</v>
-      </c>
-      <c r="F618">
-        <v>-1</v>
-      </c>
-      <c r="G618">
-        <v>0.09750608277182309</v>
-      </c>
-      <c r="H618">
-        <v>0.09903508459384436</v>
-      </c>
-      <c r="I618">
-        <v>1.509001822021261</v>
-      </c>
-      <c r="J618">
-        <v>5.425006507218797</v>
-      </c>
-      <c r="K618">
-        <v>12.72</v>
-      </c>
-      <c r="L618">
-        <v>28.5</v>
-      </c>
-      <c r="M618">
-        <v>13</v>
-      </c>
-      <c r="N618">
-        <v>28.51</v>
-      </c>
-      <c r="O618">
-        <v>1</v>
-      </c>
-      <c r="P618" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="619" spans="1:16">
-      <c r="A619" s="1">
-        <v>0</v>
-      </c>
-      <c r="B619" t="s">
-        <v>96</v>
-      </c>
-      <c r="C619">
-        <v>-40.35990057732023</v>
-      </c>
-      <c r="D619" t="s">
-        <v>210</v>
-      </c>
-      <c r="E619">
-        <v>-41.86568455229268</v>
-      </c>
-      <c r="F619">
-        <v>-1</v>
-      </c>
-      <c r="G619">
-        <v>0.09735990057732023</v>
-      </c>
-      <c r="H619">
-        <v>0.09888568455229269</v>
-      </c>
-      <c r="I619">
-        <v>1.505783974972445</v>
-      </c>
-      <c r="J619">
-        <v>5.413514196330206</v>
-      </c>
-      <c r="K619">
-        <v>12.72</v>
-      </c>
-      <c r="L619">
-        <v>28.5</v>
-      </c>
-      <c r="M619">
-        <v>13</v>
-      </c>
-      <c r="N619">
-        <v>28.51</v>
-      </c>
-      <c r="O619">
-        <v>1</v>
-      </c>
-      <c r="P619" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="620" spans="1:16">
-      <c r="A620" s="1">
-        <v>0</v>
-      </c>
-      <c r="B620" t="s">
-        <v>96</v>
-      </c>
-      <c r="C620">
-        <v>-39.98178479977238</v>
-      </c>
-      <c r="D620" t="s">
-        <v>210</v>
-      </c>
-      <c r="E620">
-        <v>-41.47924547146548</v>
-      </c>
-      <c r="F620">
-        <v>-1</v>
-      </c>
-      <c r="G620">
-        <v>0.09698178479977239</v>
-      </c>
-      <c r="H620">
-        <v>0.09849924547146549</v>
-      </c>
-      <c r="I620">
-        <v>1.497460671693091</v>
-      </c>
-      <c r="J620">
-        <v>5.383788113189652</v>
-      </c>
-      <c r="K620">
-        <v>12.72</v>
-      </c>
-      <c r="L620">
-        <v>28.5</v>
-      </c>
-      <c r="M620">
-        <v>13</v>
-      </c>
-      <c r="N620">
-        <v>28.51</v>
-      </c>
-      <c r="O620">
-        <v>1</v>
-      </c>
-      <c r="P620" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="621" spans="1:16">
-      <c r="A621" s="1">
-        <v>0</v>
-      </c>
-      <c r="B621" t="s">
-        <v>96</v>
-      </c>
-      <c r="C621">
-        <v>-39.79641827454073</v>
-      </c>
-      <c r="D621" t="s">
-        <v>210</v>
-      </c>
-      <c r="E621">
-        <v>-41.28979855102432</v>
-      </c>
-      <c r="F621">
-        <v>-1</v>
-      </c>
-      <c r="G621">
-        <v>0.09679641827454073</v>
-      </c>
-      <c r="H621">
-        <v>0.09830979855102433</v>
-      </c>
-      <c r="I621">
-        <v>1.493380276483592</v>
-      </c>
-      <c r="J621">
-        <v>5.369215273155717</v>
-      </c>
-      <c r="K621">
-        <v>12.72</v>
-      </c>
-      <c r="L621">
-        <v>28.5</v>
-      </c>
-      <c r="M621">
-        <v>13</v>
-      </c>
-      <c r="N621">
-        <v>28.51</v>
-      </c>
-      <c r="O621">
-        <v>1</v>
-      </c>
-      <c r="P621" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="622" spans="1:16">
-      <c r="A622" s="1">
-        <v>0</v>
-      </c>
-      <c r="B622" t="s">
-        <v>96</v>
-      </c>
-      <c r="C622">
-        <v>-39.18627406801045</v>
-      </c>
-      <c r="D622" t="s">
-        <v>210</v>
-      </c>
-      <c r="E622">
-        <v>-40.66622349718048</v>
-      </c>
-      <c r="F622">
-        <v>-1</v>
-      </c>
-      <c r="G622">
-        <v>0.09618627406801045</v>
-      </c>
-      <c r="H622">
-        <v>0.09768622349718049</v>
-      </c>
-      <c r="I622">
-        <v>1.479949429170034</v>
-      </c>
-      <c r="J622">
-        <v>5.321247961321576</v>
-      </c>
-      <c r="K622">
-        <v>12.72</v>
-      </c>
-      <c r="L622">
-        <v>28.5</v>
-      </c>
-      <c r="M622">
-        <v>13</v>
-      </c>
-      <c r="N622">
-        <v>28.51</v>
-      </c>
-      <c r="O622">
-        <v>1</v>
-      </c>
-      <c r="P622" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="623" spans="1:16">
-      <c r="A623" s="1">
-        <v>0</v>
-      </c>
-      <c r="B623" t="s">
-        <v>96</v>
-      </c>
-      <c r="C623">
-        <v>-39.56929989238911</v>
-      </c>
-      <c r="D623" t="s">
-        <v>210</v>
-      </c>
-      <c r="E623">
-        <v>-41.05768070763037</v>
-      </c>
-      <c r="F623">
-        <v>-1</v>
-      </c>
-      <c r="G623">
-        <v>0.09656929989238912</v>
-      </c>
-      <c r="H623">
-        <v>0.09807768070763039</v>
-      </c>
-      <c r="I623">
-        <v>1.488380815241257</v>
-      </c>
-      <c r="J623">
-        <v>5.351360054433106</v>
-      </c>
-      <c r="K623">
-        <v>12.72</v>
-      </c>
-      <c r="L623">
-        <v>28.5</v>
-      </c>
-      <c r="M623">
-        <v>13</v>
-      </c>
-      <c r="N623">
-        <v>28.51</v>
-      </c>
-      <c r="O623">
-        <v>1</v>
-      </c>
-      <c r="P623" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="624" spans="1:16">
-      <c r="A624" s="1">
-        <v>0</v>
-      </c>
-      <c r="B624" t="s">
-        <v>96</v>
-      </c>
-      <c r="C624">
-        <v>-41.81870093469173</v>
-      </c>
-      <c r="D624" t="s">
-        <v>210</v>
-      </c>
-      <c r="E624">
-        <v>-43.35659686721638</v>
-      </c>
-      <c r="F624">
-        <v>-1</v>
-      </c>
-      <c r="G624">
-        <v>0.09881870093469174</v>
-      </c>
-      <c r="H624">
-        <v>0.1003765968672164</v>
-      </c>
-      <c r="I624">
-        <v>1.537895932524648</v>
-      </c>
-      <c r="J624">
-        <v>5.528199759016645</v>
-      </c>
-      <c r="K624">
-        <v>12.72</v>
-      </c>
-      <c r="L624">
-        <v>28.5</v>
-      </c>
-      <c r="M624">
-        <v>13</v>
-      </c>
-      <c r="N624">
-        <v>28.51</v>
-      </c>
-      <c r="O624">
-        <v>1</v>
-      </c>
-      <c r="P624" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="625" spans="1:16">
-      <c r="A625" s="1">
-        <v>0</v>
-      </c>
-      <c r="B625" t="s">
-        <v>96</v>
-      </c>
-      <c r="C625">
-        <v>-41.20868023105166</v>
-      </c>
-      <c r="D625" t="s">
-        <v>210</v>
-      </c>
-      <c r="E625">
-        <v>-42.73314803487983</v>
-      </c>
-      <c r="F625">
-        <v>-1</v>
-      </c>
-      <c r="G625">
-        <v>0.09820868023105166</v>
-      </c>
-      <c r="H625">
-        <v>0.09975314803487985</v>
-      </c>
-      <c r="I625">
-        <v>1.524467803828173</v>
-      </c>
-      <c r="J625">
-        <v>5.480242156529219</v>
-      </c>
-      <c r="K625">
-        <v>12.72</v>
-      </c>
-      <c r="L625">
-        <v>28.5</v>
-      </c>
-      <c r="M625">
-        <v>13</v>
-      </c>
-      <c r="N625">
-        <v>28.51</v>
-      </c>
-      <c r="O625">
-        <v>1</v>
-      </c>
-      <c r="P625" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="626" spans="1:16">
-      <c r="A626" s="1">
-        <v>0</v>
-      </c>
-      <c r="B626" t="s">
-        <v>96</v>
-      </c>
-      <c r="C626">
-        <v>-41.13941639465475</v>
-      </c>
-      <c r="D626" t="s">
-        <v>210</v>
-      </c>
-      <c r="E626">
-        <v>-42.66235952283897</v>
-      </c>
-      <c r="F626">
-        <v>-1</v>
-      </c>
-      <c r="G626">
-        <v>0.09813941639465475</v>
-      </c>
-      <c r="H626">
-        <v>0.09968235952283898</v>
-      </c>
-      <c r="I626">
-        <v>1.522943128184224</v>
-      </c>
-      <c r="J626">
-        <v>5.474796886372228</v>
-      </c>
-      <c r="K626">
-        <v>12.72</v>
-      </c>
-      <c r="L626">
-        <v>28.5</v>
-      </c>
-      <c r="M626">
-        <v>13</v>
-      </c>
-      <c r="N626">
-        <v>28.51</v>
-      </c>
-      <c r="O626">
-        <v>1</v>
-      </c>
-      <c r="P626" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="627" spans="1:16">
-      <c r="A627" s="1">
-        <v>0</v>
-      </c>
-      <c r="B627" t="s">
-        <v>96</v>
-      </c>
-      <c r="C627">
-        <v>-41.39412179315502</v>
-      </c>
-      <c r="D627" t="s">
-        <v>210</v>
-      </c>
-      <c r="E627">
-        <v>-42.92267164394774</v>
-      </c>
-      <c r="F627">
-        <v>-1</v>
-      </c>
-      <c r="G627">
-        <v>0.09839412179315503</v>
-      </c>
-      <c r="H627">
-        <v>0.09994267164394775</v>
-      </c>
-      <c r="I627">
-        <v>1.528549850792714</v>
-      </c>
-      <c r="J627">
-        <v>5.494820895688288</v>
-      </c>
-      <c r="K627">
-        <v>12.72</v>
-      </c>
-      <c r="L627">
-        <v>28.5</v>
-      </c>
-      <c r="M627">
-        <v>13</v>
-      </c>
-      <c r="N627">
-        <v>28.51</v>
-      </c>
-      <c r="O627">
-        <v>1</v>
-      </c>
-      <c r="P627" t="s">
-        <v>473</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="432">
   <si>
     <t>trade_time</t>
   </si>
@@ -628,7 +628,7 @@
     <t>2021-02-04</t>
   </si>
   <si>
-    <t>2021-08-16</t>
+    <t>2021-08-17</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1237,9 +1237,6 @@
     <t>2020-12-18</t>
   </si>
   <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
     <t>2021-01-05</t>
   </si>
   <si>
@@ -1313,15 +1310,6 @@
   </si>
   <si>
     <t>2021-02-10</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>2021-02-19</t>
-  </si>
-  <si>
-    <t>2021-02-22</t>
   </si>
 </sst>
 </file>
@@ -1679,7 +1667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P568"/>
+  <dimension ref="A1:P564"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28537,28 +28525,28 @@
         <v>93</v>
       </c>
       <c r="C538">
-        <v>-15.6799202089076</v>
+        <v>-18.42145712811057</v>
       </c>
       <c r="D538" t="s">
         <v>204</v>
       </c>
       <c r="E538">
-        <v>-16.79922587585438</v>
+        <v>-19.30431939193691</v>
       </c>
       <c r="F538">
         <v>-1</v>
       </c>
       <c r="G538">
-        <v>0.07267992020890761</v>
+        <v>0.07542145712811058</v>
       </c>
       <c r="H538">
-        <v>0.07433922587585438</v>
+        <v>0.07660431939193692</v>
       </c>
       <c r="I538">
-        <v>1.119305666946776</v>
+        <v>0.8828622638263326</v>
       </c>
       <c r="J538">
-        <v>3.47326416736695</v>
+        <v>3.688793799379762</v>
       </c>
       <c r="K538">
         <v>12.72</v>
@@ -28567,10 +28555,10 @@
         <v>28.5</v>
       </c>
       <c r="M538">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N538">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28587,28 +28575,28 @@
         <v>93</v>
       </c>
       <c r="C539">
-        <v>-18.42145712811057</v>
+        <v>-20.96449736029645</v>
       </c>
       <c r="D539" t="s">
         <v>204</v>
       </c>
       <c r="E539">
-        <v>-19.62697464786247</v>
+        <v>-21.90333849715832</v>
       </c>
       <c r="F539">
         <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.07542145712811058</v>
+        <v>0.07796449736029645</v>
       </c>
       <c r="H539">
-        <v>0.07716697464786247</v>
+        <v>0.07920333849715831</v>
       </c>
       <c r="I539">
-        <v>1.205517519751897</v>
+        <v>0.9388411368618677</v>
       </c>
       <c r="J539">
-        <v>3.688793799379762</v>
+        <v>3.888718345935255</v>
       </c>
       <c r="K539">
         <v>12.72</v>
@@ -28617,10 +28605,10 @@
         <v>28.5</v>
       </c>
       <c r="M539">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N539">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28637,28 +28625,28 @@
         <v>93</v>
       </c>
       <c r="C540">
-        <v>-20.96449736029645</v>
+        <v>-22.26553261458488</v>
       </c>
       <c r="D540" t="s">
         <v>204</v>
       </c>
       <c r="E540">
-        <v>-22.24998469867054</v>
+        <v>-23.23301289226442</v>
       </c>
       <c r="F540">
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.07796449736029645</v>
+        <v>0.07926553261458488</v>
       </c>
       <c r="H540">
-        <v>0.07978998469867053</v>
+        <v>0.08053301289226443</v>
       </c>
       <c r="I540">
-        <v>1.285487338374093</v>
+        <v>0.9674802776795417</v>
       </c>
       <c r="J540">
-        <v>3.888718345935255</v>
+        <v>3.991000991712648</v>
       </c>
       <c r="K540">
         <v>12.72</v>
@@ -28667,10 +28655,10 @@
         <v>28.5</v>
       </c>
       <c r="M540">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N540">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28687,28 +28675,28 @@
         <v>93</v>
       </c>
       <c r="C541">
-        <v>-22.26553261458488</v>
+        <v>-23.39064064612373</v>
       </c>
       <c r="D541" t="s">
         <v>204</v>
       </c>
       <c r="E541">
-        <v>-23.59193301126993</v>
+        <v>-24.38288745279941</v>
       </c>
       <c r="F541">
         <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.07926553261458488</v>
+        <v>0.08039064064612372</v>
       </c>
       <c r="H541">
-        <v>0.08113193301126993</v>
+        <v>0.0816828874527994</v>
       </c>
       <c r="I541">
-        <v>1.326400396685056</v>
+        <v>0.9922468066756807</v>
       </c>
       <c r="J541">
-        <v>3.991000991712648</v>
+        <v>4.07945288098457</v>
       </c>
       <c r="K541">
         <v>12.72</v>
@@ -28717,10 +28705,10 @@
         <v>28.5</v>
       </c>
       <c r="M541">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N541">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28737,28 +28725,28 @@
         <v>93</v>
       </c>
       <c r="C542">
-        <v>-23.39064064612373</v>
+        <v>-24.9776650997016</v>
       </c>
       <c r="D542" t="s">
         <v>204</v>
       </c>
       <c r="E542">
-        <v>-24.75242179851755</v>
+        <v>-26.00484640692774</v>
       </c>
       <c r="F542">
         <v>-1</v>
       </c>
       <c r="G542">
-        <v>0.08039064064612372</v>
+        <v>0.0819776650997016</v>
       </c>
       <c r="H542">
-        <v>0.08229242179851755</v>
+        <v>0.08330484640692774</v>
       </c>
       <c r="I542">
-        <v>1.361781152393821</v>
+        <v>1.027181307226137</v>
       </c>
       <c r="J542">
-        <v>4.07945288098457</v>
+        <v>4.204218954379057</v>
       </c>
       <c r="K542">
         <v>12.72</v>
@@ -28767,10 +28755,10 @@
         <v>28.5</v>
       </c>
       <c r="M542">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N542">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28787,28 +28775,28 @@
         <v>93</v>
       </c>
       <c r="C543">
-        <v>-24.9776650997016</v>
+        <v>-27.00589345076202</v>
       </c>
       <c r="D543" t="s">
         <v>204</v>
       </c>
       <c r="E543">
-        <v>-26.38935268145322</v>
+        <v>-28.07772129401778</v>
       </c>
       <c r="F543">
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.0819776650997016</v>
+        <v>0.08400589345076202</v>
       </c>
       <c r="H543">
-        <v>0.08392935268145323</v>
+        <v>0.08537772129401779</v>
       </c>
       <c r="I543">
-        <v>1.411687581751618</v>
+        <v>1.071827843255768</v>
       </c>
       <c r="J543">
-        <v>4.204218954379057</v>
+        <v>4.363670868770599</v>
       </c>
       <c r="K543">
         <v>12.72</v>
@@ -28817,10 +28805,10 @@
         <v>28.5</v>
       </c>
       <c r="M543">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N543">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28837,28 +28825,28 @@
         <v>93</v>
       </c>
       <c r="C544">
-        <v>-27.00589345076202</v>
+        <v>-29.1656717820026</v>
       </c>
       <c r="D544" t="s">
         <v>204</v>
       </c>
       <c r="E544">
-        <v>-28.48136179827025</v>
+        <v>-30.2850419155687</v>
       </c>
       <c r="F544">
         <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.08400589345076202</v>
+        <v>0.0861656717820026</v>
       </c>
       <c r="H544">
-        <v>0.08602136179827025</v>
+        <v>0.08758504191556869</v>
       </c>
       <c r="I544">
-        <v>1.47546834750823</v>
+        <v>1.119370133566093</v>
       </c>
       <c r="J544">
-        <v>4.363670868770599</v>
+        <v>4.533464762736053</v>
       </c>
       <c r="K544">
         <v>12.72</v>
@@ -28867,10 +28855,10 @@
         <v>28.5</v>
       </c>
       <c r="M544">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N544">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28887,28 +28875,28 @@
         <v>93</v>
       </c>
       <c r="C545">
-        <v>-29.1656717820026</v>
+        <v>-29.94151334120067</v>
       </c>
       <c r="D545" t="s">
         <v>204</v>
       </c>
       <c r="E545">
-        <v>-30.70905768709702</v>
+        <v>-31.07796174808244</v>
       </c>
       <c r="F545">
         <v>-1</v>
       </c>
       <c r="G545">
-        <v>0.0861656717820026</v>
+        <v>0.08694151334120068</v>
       </c>
       <c r="H545">
-        <v>0.08824905768709702</v>
+        <v>0.08837796174808245</v>
       </c>
       <c r="I545">
-        <v>1.543385905094414</v>
+        <v>1.136448406881776</v>
       </c>
       <c r="J545">
-        <v>4.533464762736053</v>
+        <v>4.594458596006342</v>
       </c>
       <c r="K545">
         <v>12.72</v>
@@ -28917,10 +28905,10 @@
         <v>28.5</v>
       </c>
       <c r="M545">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N545">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28937,28 +28925,28 @@
         <v>93</v>
       </c>
       <c r="C546">
-        <v>-29.94151334120067</v>
+        <v>-30.43493588680277</v>
       </c>
       <c r="D546" t="s">
         <v>204</v>
       </c>
       <c r="E546">
-        <v>-31.5092967796032</v>
+        <v>-31.58224579626069</v>
       </c>
       <c r="F546">
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.08694151334120068</v>
+        <v>0.08743493588680278</v>
       </c>
       <c r="H546">
-        <v>0.0890492967796032</v>
+        <v>0.08888224579626069</v>
       </c>
       <c r="I546">
-        <v>1.567783438402532</v>
+        <v>1.147309909457924</v>
       </c>
       <c r="J546">
-        <v>4.594458596006342</v>
+        <v>4.633249676635438</v>
       </c>
       <c r="K546">
         <v>12.72</v>
@@ -28967,16 +28955,16 @@
         <v>28.5</v>
       </c>
       <c r="M546">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N546">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>415</v>
+        <v>92</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28987,28 +28975,28 @@
         <v>93</v>
       </c>
       <c r="C547">
-        <v>-30.43493588680277</v>
+        <v>-30.74429722076099</v>
       </c>
       <c r="D547" t="s">
         <v>204</v>
       </c>
       <c r="E547">
-        <v>-32.01823575745694</v>
+        <v>-31.89841697090353</v>
       </c>
       <c r="F547">
         <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.08743493588680278</v>
+        <v>0.08774429722076099</v>
       </c>
       <c r="H547">
-        <v>0.08955823575745694</v>
+        <v>0.08919841697090353</v>
       </c>
       <c r="I547">
-        <v>1.583299870654166</v>
+        <v>1.154119750142534</v>
       </c>
       <c r="J547">
-        <v>4.633249676635438</v>
+        <v>4.657570536223348</v>
       </c>
       <c r="K547">
         <v>12.72</v>
@@ -29017,16 +29005,16 @@
         <v>28.5</v>
       </c>
       <c r="M547">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N547">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>92</v>
+        <v>415</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29037,28 +29025,28 @@
         <v>93</v>
       </c>
       <c r="C548">
-        <v>-30.74429722076099</v>
+        <v>-31.20320959343522</v>
       </c>
       <c r="D548" t="s">
         <v>204</v>
       </c>
       <c r="E548">
-        <v>-32.33732543525032</v>
+        <v>-32.36743118825926</v>
       </c>
       <c r="F548">
         <v>-1</v>
       </c>
       <c r="G548">
-        <v>0.08774429722076099</v>
+        <v>0.08820320959343522</v>
       </c>
       <c r="H548">
-        <v>0.08987732543525033</v>
+        <v>0.08966743118825926</v>
       </c>
       <c r="I548">
-        <v>1.59302821448933</v>
+        <v>1.164221594824042</v>
       </c>
       <c r="J548">
-        <v>4.657570536223348</v>
+        <v>4.69364855294302</v>
       </c>
       <c r="K548">
         <v>12.72</v>
@@ -29067,10 +29055,10 @@
         <v>28.5</v>
       </c>
       <c r="M548">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N548">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O548">
         <v>1</v>
@@ -29087,28 +29075,28 @@
         <v>93</v>
       </c>
       <c r="C549">
-        <v>-31.20320959343522</v>
+        <v>-31.07605732463613</v>
       </c>
       <c r="D549" t="s">
         <v>204</v>
       </c>
       <c r="E549">
-        <v>-32.81066901461242</v>
+        <v>-32.23747997014699</v>
       </c>
       <c r="F549">
         <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.08820320959343522</v>
+        <v>0.08807605732463614</v>
       </c>
       <c r="H549">
-        <v>0.09035066901461242</v>
+        <v>0.08953747997014699</v>
       </c>
       <c r="I549">
-        <v>1.607459421177197</v>
+        <v>1.161422645510861</v>
       </c>
       <c r="J549">
-        <v>4.69364855294302</v>
+        <v>4.683652305395922</v>
       </c>
       <c r="K549">
         <v>12.72</v>
@@ -29117,10 +29105,10 @@
         <v>28.5</v>
       </c>
       <c r="M549">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N549">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O549">
         <v>1</v>
@@ -29137,28 +29125,28 @@
         <v>93</v>
       </c>
       <c r="C550">
-        <v>-31.07605732463613</v>
+        <v>-30.25066173781194</v>
       </c>
       <c r="D550" t="s">
         <v>204</v>
       </c>
       <c r="E550">
-        <v>-32.6795182467945</v>
+        <v>-31.39391529807823</v>
       </c>
       <c r="F550">
         <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.08807605732463614</v>
+        <v>0.08725066173781194</v>
       </c>
       <c r="H550">
-        <v>0.0902195182467945</v>
+        <v>0.08869391529807823</v>
       </c>
       <c r="I550">
-        <v>1.603460922158369</v>
+        <v>1.143253560266295</v>
       </c>
       <c r="J550">
-        <v>4.683652305395922</v>
+        <v>4.618762715236787</v>
       </c>
       <c r="K550">
         <v>12.72</v>
@@ -29167,10 +29155,10 @@
         <v>28.5</v>
       </c>
       <c r="M550">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N550">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O550">
         <v>1</v>
@@ -29187,28 +29175,28 @@
         <v>93</v>
       </c>
       <c r="C551">
-        <v>-30.25066173781194</v>
+        <v>-28.48555321698337</v>
       </c>
       <c r="D551" t="s">
         <v>204</v>
       </c>
       <c r="E551">
-        <v>-31.82816682390665</v>
+        <v>-29.58995218716854</v>
       </c>
       <c r="F551">
         <v>-1</v>
       </c>
       <c r="G551">
-        <v>0.08725066173781194</v>
+        <v>0.08548555321698337</v>
       </c>
       <c r="H551">
-        <v>0.08936816682390665</v>
+        <v>0.08688995218716854</v>
       </c>
       <c r="I551">
-        <v>1.577505086094707</v>
+        <v>1.104398970185166</v>
       </c>
       <c r="J551">
-        <v>4.618762715236787</v>
+        <v>4.479996322089887</v>
       </c>
       <c r="K551">
         <v>12.72</v>
@@ -29217,10 +29205,10 @@
         <v>28.5</v>
       </c>
       <c r="M551">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N551">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O551">
         <v>1</v>
@@ -29237,28 +29225,28 @@
         <v>93</v>
       </c>
       <c r="C552">
-        <v>-28.48555321698337</v>
+        <v>-28.69349087972021</v>
       </c>
       <c r="D552" t="s">
         <v>204</v>
       </c>
       <c r="E552">
-        <v>-30.00755174581932</v>
+        <v>-29.80246709405367</v>
       </c>
       <c r="F552">
         <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.08548555321698337</v>
+        <v>0.0856934908797202</v>
       </c>
       <c r="H552">
-        <v>0.08754755174581932</v>
+        <v>0.08710246709405367</v>
       </c>
       <c r="I552">
-        <v>1.521998528835947</v>
+        <v>1.10897621433346</v>
       </c>
       <c r="J552">
-        <v>4.479996322089887</v>
+        <v>4.496343622619513</v>
       </c>
       <c r="K552">
         <v>12.72</v>
@@ -29267,10 +29255,10 @@
         <v>28.5</v>
       </c>
       <c r="M552">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N552">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O552">
         <v>1</v>
@@ -29287,28 +29275,28 @@
         <v>93</v>
       </c>
       <c r="C553">
-        <v>-28.69349087972021</v>
+        <v>-28.72399400585454</v>
       </c>
       <c r="D553" t="s">
         <v>204</v>
       </c>
       <c r="E553">
-        <v>-30.22202832876801</v>
+        <v>-29.83364167265007</v>
       </c>
       <c r="F553">
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.0856934908797202</v>
+        <v>0.08572399400585454</v>
       </c>
       <c r="H553">
-        <v>0.08776202832876802</v>
+        <v>0.08713364167265007</v>
       </c>
       <c r="I553">
-        <v>1.5285374490478</v>
+        <v>1.109647666795539</v>
       </c>
       <c r="J553">
-        <v>4.496343622619513</v>
+        <v>4.498741667126929</v>
       </c>
       <c r="K553">
         <v>12.72</v>
@@ -29317,10 +29305,10 @@
         <v>28.5</v>
       </c>
       <c r="M553">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N553">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O553">
         <v>1</v>
@@ -29337,28 +29325,28 @@
         <v>93</v>
       </c>
       <c r="C554">
-        <v>-28.72399400585454</v>
+        <v>-29.04997068031175</v>
       </c>
       <c r="D554" t="s">
         <v>204</v>
       </c>
       <c r="E554">
-        <v>-30.2534906727053</v>
+        <v>-30.16679393428088</v>
       </c>
       <c r="F554">
         <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.08572399400585454</v>
+        <v>0.08604997068031175</v>
       </c>
       <c r="H554">
-        <v>0.08779349067270531</v>
+        <v>0.08746679393428088</v>
       </c>
       <c r="I554">
-        <v>1.529496666850765</v>
+        <v>1.116823253969123</v>
       </c>
       <c r="J554">
-        <v>4.498741667126929</v>
+        <v>4.524368764175452</v>
       </c>
       <c r="K554">
         <v>12.72</v>
@@ -29367,10 +29355,10 @@
         <v>28.5</v>
       </c>
       <c r="M554">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N554">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O554">
         <v>1</v>
@@ -29387,28 +29375,28 @@
         <v>93</v>
       </c>
       <c r="C555">
-        <v>-29.04997068031175</v>
+        <v>-29.43168959025828</v>
       </c>
       <c r="D555" t="s">
         <v>204</v>
       </c>
       <c r="E555">
-        <v>-30.58971818598193</v>
+        <v>-30.55691546174195</v>
       </c>
       <c r="F555">
         <v>-1</v>
       </c>
       <c r="G555">
-        <v>0.08604997068031175</v>
+        <v>0.08643168959025829</v>
       </c>
       <c r="H555">
-        <v>0.08812971818598193</v>
+        <v>0.08785691546174194</v>
       </c>
       <c r="I555">
-        <v>1.539747505670174</v>
+        <v>1.125225871483671</v>
       </c>
       <c r="J555">
-        <v>4.524368764175452</v>
+        <v>4.554378112441689</v>
       </c>
       <c r="K555">
         <v>12.72</v>
@@ -29417,10 +29405,10 @@
         <v>28.5</v>
       </c>
       <c r="M555">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N555">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O555">
         <v>1</v>
@@ -29437,28 +29425,28 @@
         <v>93</v>
       </c>
       <c r="C556">
-        <v>-29.43168959025828</v>
+        <v>-30.72131869184545</v>
       </c>
       <c r="D556" t="s">
         <v>204</v>
       </c>
       <c r="E556">
-        <v>-30.98344083523495</v>
+        <v>-31.87493262531374</v>
       </c>
       <c r="F556">
         <v>-1</v>
       </c>
       <c r="G556">
-        <v>0.08643168959025829</v>
+        <v>0.08772131869184546</v>
       </c>
       <c r="H556">
-        <v>0.08852344083523495</v>
+        <v>0.08917493262531374</v>
       </c>
       <c r="I556">
-        <v>1.551751244976675</v>
+        <v>1.153613933468293</v>
       </c>
       <c r="J556">
-        <v>4.554378112441689</v>
+        <v>4.655764048101057</v>
       </c>
       <c r="K556">
         <v>12.72</v>
@@ -29467,10 +29455,10 @@
         <v>28.5</v>
       </c>
       <c r="M556">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N556">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O556">
         <v>1</v>
@@ -29487,28 +29475,28 @@
         <v>93</v>
       </c>
       <c r="C557">
-        <v>-30.72131869184545</v>
+        <v>-32.3547496665294</v>
       </c>
       <c r="D557" t="s">
         <v>204</v>
       </c>
       <c r="E557">
-        <v>-32.31362431108586</v>
+        <v>-33.54431962774231</v>
       </c>
       <c r="F557">
         <v>-1</v>
       </c>
       <c r="G557">
-        <v>0.08772131869184546</v>
+        <v>0.0893547496665294</v>
       </c>
       <c r="H557">
-        <v>0.08985362431108587</v>
+        <v>0.09084431962774231</v>
       </c>
       <c r="I557">
-        <v>1.592305619240413</v>
+        <v>1.189569961212911</v>
       </c>
       <c r="J557">
-        <v>4.655764048101057</v>
+        <v>4.784178432903254</v>
       </c>
       <c r="K557">
         <v>12.72</v>
@@ -29517,10 +29505,10 @@
         <v>28.5</v>
       </c>
       <c r="M557">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N557">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O557">
         <v>1</v>
@@ -29537,28 +29525,28 @@
         <v>93</v>
       </c>
       <c r="C558">
-        <v>-32.3547496665294</v>
+        <v>-33.15849324376438</v>
       </c>
       <c r="D558" t="s">
         <v>204</v>
       </c>
       <c r="E558">
-        <v>-33.9984210396907</v>
+        <v>-34.36575567365856</v>
       </c>
       <c r="F558">
         <v>-1</v>
       </c>
       <c r="G558">
-        <v>0.0893547496665294</v>
+        <v>0.09015849324376439</v>
       </c>
       <c r="H558">
-        <v>0.09153842103969069</v>
+        <v>0.09166575567365857</v>
       </c>
       <c r="I558">
-        <v>1.643671373161297</v>
+        <v>1.207262429894186</v>
       </c>
       <c r="J558">
-        <v>4.784178432903254</v>
+        <v>4.847365821050658</v>
       </c>
       <c r="K558">
         <v>12.72</v>
@@ -29567,10 +29555,10 @@
         <v>28.5</v>
       </c>
       <c r="M558">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N558">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O558">
         <v>1</v>
@@ -29587,28 +29575,28 @@
         <v>93</v>
       </c>
       <c r="C559">
-        <v>-33.15849324376438</v>
+        <v>-34.25698087216963</v>
       </c>
       <c r="D559" t="s">
         <v>204</v>
       </c>
       <c r="E559">
-        <v>-34.82743957218463</v>
+        <v>-35.48842384734316</v>
       </c>
       <c r="F559">
         <v>-1</v>
       </c>
       <c r="G559">
-        <v>0.09015849324376439</v>
+        <v>0.09125698087216964</v>
       </c>
       <c r="H559">
-        <v>0.09236743957218464</v>
+        <v>0.09278842384734315</v>
       </c>
       <c r="I559">
-        <v>1.668946328420255</v>
+        <v>1.231442975173536</v>
       </c>
       <c r="J559">
-        <v>4.847365821050658</v>
+        <v>4.93372491133409</v>
       </c>
       <c r="K559">
         <v>12.72</v>
@@ -29617,10 +29605,10 @@
         <v>28.5</v>
       </c>
       <c r="M559">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N559">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O559">
         <v>1</v>
@@ -29637,28 +29625,28 @@
         <v>93</v>
       </c>
       <c r="C560">
-        <v>-34.25698087216963</v>
+        <v>-35.16617096130667</v>
       </c>
       <c r="D560" t="s">
         <v>204</v>
       </c>
       <c r="E560">
-        <v>-35.96047083670325</v>
+        <v>-36.41762755479454</v>
       </c>
       <c r="F560">
         <v>-1</v>
       </c>
       <c r="G560">
-        <v>0.09125698087216964</v>
+        <v>0.09216617096130668</v>
       </c>
       <c r="H560">
-        <v>0.09350047083670325</v>
+        <v>0.09371762755479456</v>
       </c>
       <c r="I560">
-        <v>1.703489964533624</v>
+        <v>1.251456593487873</v>
       </c>
       <c r="J560">
-        <v>4.93372491133409</v>
+        <v>5.005202119599581</v>
       </c>
       <c r="K560">
         <v>12.72</v>
@@ -29667,16 +29655,16 @@
         <v>28.5</v>
       </c>
       <c r="M560">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N560">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O560">
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>428</v>
+        <v>203</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29687,28 +29675,28 @@
         <v>93</v>
       </c>
       <c r="C561">
-        <v>-35.16617096130667</v>
+        <v>-35.90561619919141</v>
       </c>
       <c r="D561" t="s">
         <v>204</v>
       </c>
       <c r="E561">
-        <v>-36.8982518091465</v>
+        <v>-37.17334988911072</v>
       </c>
       <c r="F561">
         <v>-1</v>
       </c>
       <c r="G561">
-        <v>0.09216617096130668</v>
+        <v>0.09290561619919141</v>
       </c>
       <c r="H561">
-        <v>0.0944382518091465</v>
+        <v>0.09447334988911073</v>
       </c>
       <c r="I561">
-        <v>1.732080847839832</v>
+        <v>1.267733689919304</v>
       </c>
       <c r="J561">
-        <v>5.005202119599581</v>
+        <v>5.063334606854671</v>
       </c>
       <c r="K561">
         <v>12.72</v>
@@ -29717,16 +29705,16 @@
         <v>28.5</v>
       </c>
       <c r="M561">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N561">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O561">
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>203</v>
+        <v>428</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29737,28 +29725,28 @@
         <v>93</v>
       </c>
       <c r="C562">
-        <v>-35.90561619919141</v>
+        <v>-36.18997893562975</v>
       </c>
       <c r="D562" t="s">
         <v>204</v>
       </c>
       <c r="E562">
-        <v>-37.66095004193328</v>
+        <v>-37.46397218264047</v>
       </c>
       <c r="F562">
         <v>-1</v>
       </c>
       <c r="G562">
-        <v>0.09290561619919141</v>
+        <v>0.09318997893562976</v>
       </c>
       <c r="H562">
-        <v>0.09520095004193327</v>
+        <v>0.09476397218264046</v>
       </c>
       <c r="I562">
-        <v>1.755333842741862</v>
+        <v>1.273993247010715</v>
       </c>
       <c r="J562">
-        <v>5.063334606854671</v>
+        <v>5.085690167895421</v>
       </c>
       <c r="K562">
         <v>12.72</v>
@@ -29767,10 +29755,10 @@
         <v>28.5</v>
       </c>
       <c r="M562">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N562">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O562">
         <v>1</v>
@@ -29787,28 +29775,28 @@
         <v>93</v>
       </c>
       <c r="C563">
-        <v>-36.18997893562975</v>
+        <v>-36.79440237149454</v>
       </c>
       <c r="D563" t="s">
         <v>204</v>
       </c>
       <c r="E563">
-        <v>-37.95425500278792</v>
+        <v>-38.0817005369048</v>
       </c>
       <c r="F563">
         <v>-1</v>
       </c>
       <c r="G563">
-        <v>0.09318997893562976</v>
+        <v>0.09379440237149454</v>
       </c>
       <c r="H563">
-        <v>0.09549425500278791</v>
+        <v>0.09538170053690478</v>
       </c>
       <c r="I563">
-        <v>1.764276067158164</v>
+        <v>1.287298165410256</v>
       </c>
       <c r="J563">
-        <v>5.085690167895421</v>
+        <v>5.133207733608061</v>
       </c>
       <c r="K563">
         <v>12.72</v>
@@ -29817,10 +29805,10 @@
         <v>28.5</v>
       </c>
       <c r="M563">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N563">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O563">
         <v>1</v>
@@ -29837,28 +29825,28 @@
         <v>93</v>
       </c>
       <c r="C564">
-        <v>-36.79440237149454</v>
+        <v>-36.55608045442354</v>
       </c>
       <c r="D564" t="s">
         <v>204</v>
       </c>
       <c r="E564">
-        <v>-38.57768546493776</v>
+        <v>-37.83813253989826</v>
       </c>
       <c r="F564">
         <v>-1</v>
       </c>
       <c r="G564">
-        <v>0.09379440237149454</v>
+        <v>0.09355608045442354</v>
       </c>
       <c r="H564">
-        <v>0.09611768546493775</v>
+        <v>0.09513813253989827</v>
       </c>
       <c r="I564">
-        <v>1.783283093443217</v>
+        <v>1.282052085474724</v>
       </c>
       <c r="J564">
-        <v>5.133207733608061</v>
+        <v>5.114471733838328</v>
       </c>
       <c r="K564">
         <v>12.72</v>
@@ -29867,216 +29855,16 @@
         <v>28.5</v>
       </c>
       <c r="M564">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="N564">
-        <v>28.77</v>
+        <v>28.65</v>
       </c>
       <c r="O564">
         <v>1</v>
       </c>
       <c r="P564" t="s">
         <v>431</v>
-      </c>
-    </row>
-    <row r="565" spans="1:16">
-      <c r="A565" s="1">
-        <v>0</v>
-      </c>
-      <c r="B565" t="s">
-        <v>93</v>
-      </c>
-      <c r="C565">
-        <v>-36.55608045442354</v>
-      </c>
-      <c r="D565" t="s">
-        <v>204</v>
-      </c>
-      <c r="E565">
-        <v>-38.33186914795886</v>
-      </c>
-      <c r="F565">
-        <v>-1</v>
-      </c>
-      <c r="G565">
-        <v>0.09355608045442354</v>
-      </c>
-      <c r="H565">
-        <v>0.09587186914795885</v>
-      </c>
-      <c r="I565">
-        <v>1.775788693535318</v>
-      </c>
-      <c r="J565">
-        <v>5.114471733838328</v>
-      </c>
-      <c r="K565">
-        <v>12.72</v>
-      </c>
-      <c r="L565">
-        <v>28.5</v>
-      </c>
-      <c r="M565">
-        <v>13.12</v>
-      </c>
-      <c r="N565">
-        <v>28.77</v>
-      </c>
-      <c r="O565">
-        <v>1</v>
-      </c>
-      <c r="P565" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="566" spans="1:16">
-      <c r="A566" s="1">
-        <v>0</v>
-      </c>
-      <c r="B566" t="s">
-        <v>93</v>
-      </c>
-      <c r="C566">
-        <v>-36.02878397309011</v>
-      </c>
-      <c r="D566" t="s">
-        <v>204</v>
-      </c>
-      <c r="E566">
-        <v>-37.78799101626905</v>
-      </c>
-      <c r="F566">
-        <v>-1</v>
-      </c>
-      <c r="G566">
-        <v>0.09302878397309011</v>
-      </c>
-      <c r="H566">
-        <v>0.09532799101626904</v>
-      </c>
-      <c r="I566">
-        <v>1.759207043178932</v>
-      </c>
-      <c r="J566">
-        <v>5.073017607947336</v>
-      </c>
-      <c r="K566">
-        <v>12.72</v>
-      </c>
-      <c r="L566">
-        <v>28.5</v>
-      </c>
-      <c r="M566">
-        <v>13.12</v>
-      </c>
-      <c r="N566">
-        <v>28.77</v>
-      </c>
-      <c r="O566">
-        <v>1</v>
-      </c>
-      <c r="P566" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="567" spans="1:16">
-      <c r="A567" s="1">
-        <v>0</v>
-      </c>
-      <c r="B567" t="s">
-        <v>93</v>
-      </c>
-      <c r="C567">
-        <v>-35.32789307633533</v>
-      </c>
-      <c r="D567" t="s">
-        <v>204</v>
-      </c>
-      <c r="E567">
-        <v>-37.06505952527669</v>
-      </c>
-      <c r="F567">
-        <v>-1</v>
-      </c>
-      <c r="G567">
-        <v>0.09232789307633534</v>
-      </c>
-      <c r="H567">
-        <v>0.09460505952527669</v>
-      </c>
-      <c r="I567">
-        <v>1.737166448941366</v>
-      </c>
-      <c r="J567">
-        <v>5.017916122353406</v>
-      </c>
-      <c r="K567">
-        <v>12.72</v>
-      </c>
-      <c r="L567">
-        <v>28.5</v>
-      </c>
-      <c r="M567">
-        <v>13.12</v>
-      </c>
-      <c r="N567">
-        <v>28.77</v>
-      </c>
-      <c r="O567">
-        <v>1</v>
-      </c>
-      <c r="P567" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="568" spans="1:16">
-      <c r="A568" s="1">
-        <v>0</v>
-      </c>
-      <c r="B568" t="s">
-        <v>93</v>
-      </c>
-      <c r="C568">
-        <v>-34.50492295847297</v>
-      </c>
-      <c r="D568" t="s">
-        <v>204</v>
-      </c>
-      <c r="E568">
-        <v>-36.21620984395953</v>
-      </c>
-      <c r="F568">
-        <v>-1</v>
-      </c>
-      <c r="G568">
-        <v>0.09150492295847297</v>
-      </c>
-      <c r="H568">
-        <v>0.09375620984395952</v>
-      </c>
-      <c r="I568">
-        <v>1.711286885486565</v>
-      </c>
-      <c r="J568">
-        <v>4.953217213716428</v>
-      </c>
-      <c r="K568">
-        <v>12.72</v>
-      </c>
-      <c r="L568">
-        <v>28.5</v>
-      </c>
-      <c r="M568">
-        <v>13.12</v>
-      </c>
-      <c r="N568">
-        <v>28.77</v>
-      </c>
-      <c r="O568">
-        <v>1</v>
-      </c>
-      <c r="P568" t="s">
-        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="431">
   <si>
     <t>trade_time</t>
   </si>
@@ -295,6 +295,9 @@
     <t>2021-01-15</t>
   </si>
   <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
     <t>2021-07-27</t>
   </si>
   <si>
@@ -628,7 +631,10 @@
     <t>2021-02-04</t>
   </si>
   <si>
-    <t>2021-08-17</t>
+    <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2021-08-18</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1301,15 +1307,6 @@
   </si>
   <si>
     <t>2021-02-05</t>
-  </si>
-  <si>
-    <t>2021-02-08</t>
-  </si>
-  <si>
-    <t>2021-02-09</t>
-  </si>
-  <si>
-    <t>2021-02-10</t>
   </si>
 </sst>
 </file>
@@ -1667,7 +1664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P564"/>
+  <dimension ref="A1:P562"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1728,7 +1725,7 @@
         <v>7.937839468679289</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E2">
         <v>5.219520382832306</v>
@@ -1764,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1778,7 +1775,7 @@
         <v>3.136690364271253</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3">
         <v>5.635410691649231</v>
@@ -1814,7 +1811,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1828,7 +1825,7 @@
         <v>2.638216954758501</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E4">
         <v>5.635410691649231</v>
@@ -1864,7 +1861,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1878,7 +1875,7 @@
         <v>3.237530821347761</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E5">
         <v>5.635410691649231</v>
@@ -1914,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1928,7 +1925,7 @@
         <v>3.230584002322257</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6">
         <v>5.635410691649231</v>
@@ -1964,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1978,7 +1975,7 @@
         <v>3.256004230860512</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7">
         <v>5.635410691649231</v>
@@ -2014,7 +2011,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2028,7 +2025,7 @@
         <v>3.286004230860513</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E8">
         <v>5.635410691649231</v>
@@ -2064,7 +2061,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2078,7 +2075,7 @@
         <v>7.640037484949179</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>4.941353694732751</v>
@@ -2114,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2128,7 +2125,7 @@
         <v>2.786527592192993</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>5.320918706633144</v>
@@ -2164,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2178,7 +2175,7 @@
         <v>2.28641790804436</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E11">
         <v>5.320918706633144</v>
@@ -2214,7 +2211,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2228,7 +2225,7 @@
         <v>2.897185697084776</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12">
         <v>5.320918706633144</v>
@@ -2264,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2278,7 +2275,7 @@
         <v>2.886966328787512</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E13">
         <v>5.320918706633144</v>
@@ -2314,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2328,7 +2325,7 @@
         <v>2.917295381233409</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E14">
         <v>5.320918706633144</v>
@@ -2364,7 +2361,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2378,7 +2375,7 @@
         <v>2.94729538123341</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E15">
         <v>5.320918706633144</v>
@@ -2414,7 +2411,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2428,7 +2425,7 @@
         <v>7.265164792922025</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E16">
         <v>4.591197883498596</v>
@@ -2464,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2478,7 +2475,7 @@
         <v>2.345743218051176</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E17">
         <v>4.925036665931941</v>
@@ -2514,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2528,7 +2525,7 @@
         <v>1.843573793836459</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E18">
         <v>4.925036665931941</v>
@@ -2564,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2578,7 +2575,7 @@
         <v>2.468759763339456</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E19">
         <v>4.925036665931941</v>
@@ -2614,7 +2611,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2628,7 +2625,7 @@
         <v>2.454420914910028</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E20">
         <v>4.925036665931941</v>
@@ -2664,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2678,7 +2675,7 @@
         <v>2.490929187554173</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E21">
         <v>4.925036665931941</v>
@@ -2714,7 +2711,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2728,7 +2725,7 @@
         <v>2.520929187554174</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E22">
         <v>4.925036665931941</v>
@@ -2764,7 +2761,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2778,7 +2775,7 @@
         <v>1.980046625394046</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E23">
         <v>4.596593277573533</v>
@@ -2828,7 +2825,7 @@
         <v>1.476168338596821</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E24">
         <v>4.596593277573533</v>
@@ -2878,7 +2875,7 @@
         <v>2.113316346177388</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E25">
         <v>4.596593277573533</v>
@@ -2928,7 +2925,7 @@
         <v>2.095559772582941</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E26">
         <v>4.596593277573533</v>
@@ -2978,7 +2975,7 @@
         <v>2.137194632974616</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E27">
         <v>4.596593277573533</v>
@@ -3028,7 +3025,7 @@
         <v>2.167194632974617</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E28">
         <v>4.596593277573533</v>
@@ -3078,7 +3075,7 @@
         <v>2.844772647031224</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E29">
         <v>5.373230386726174</v>
@@ -3114,7 +3111,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3128,7 +3125,7 @@
         <v>2.344935136036042</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E30">
         <v>5.373230386726174</v>
@@ -3164,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3178,7 +3175,7 @@
         <v>2.953797713002309</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E31">
         <v>5.373230386726174</v>
@@ -3214,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3228,7 +3225,7 @@
         <v>2.944122691011945</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E32">
         <v>5.373230386726174</v>
@@ -3264,7 +3261,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3278,7 +3275,7 @@
         <v>2.973635223997491</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E33">
         <v>5.373230386726174</v>
@@ -3314,7 +3311,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3328,7 +3325,7 @@
         <v>3.003635223997492</v>
       </c>
       <c r="D34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E34">
         <v>5.373230386726174</v>
@@ -3364,7 +3361,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3378,7 +3375,7 @@
         <v>7.289203935514355</v>
       </c>
       <c r="D35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E35">
         <v>5.128184916132415</v>
@@ -3414,7 +3411,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3428,7 +3425,7 @@
         <v>-2.117497474419014</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E36">
         <v>0.8991929718719938</v>
@@ -3464,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3478,7 +3475,7 @@
         <v>-2.80975033090947</v>
       </c>
       <c r="D37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E37">
         <v>0.2758434229577951</v>
@@ -3514,7 +3511,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3528,7 +3525,7 @@
         <v>-2.902998496046035</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E38">
         <v>0.1918767030952893</v>
@@ -3564,7 +3561,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3578,7 +3575,7 @@
         <v>-2.830339867902396</v>
       </c>
       <c r="D39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E39">
         <v>0.2573032631353307</v>
@@ -3614,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3628,7 +3625,7 @@
         <v>-2.537341046304341</v>
       </c>
       <c r="D40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E40">
         <v>0.5211384810952531</v>
@@ -3664,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3678,7 +3675,7 @@
         <v>-2.336644974997025</v>
       </c>
       <c r="D41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E41">
         <v>0.7018582922817487</v>
@@ -3714,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3728,7 +3725,7 @@
         <v>-2.249226521683095</v>
       </c>
       <c r="D42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E42">
         <v>0.7018582922817487</v>
@@ -3764,7 +3761,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3778,7 +3775,7 @@
         <v>-1.845740644766149</v>
       </c>
       <c r="D43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E43">
         <v>1.143900517084994</v>
@@ -3814,7 +3811,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3828,7 +3825,7 @@
         <v>-1.76174710538406</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E44">
         <v>1.143900517084994</v>
@@ -3864,7 +3861,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3914,7 +3911,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3928,7 +3925,7 @@
         <v>-1.483754394543759</v>
       </c>
       <c r="D46" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E46">
         <v>1.469856507982922</v>
@@ -3964,7 +3961,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3978,7 +3975,7 @@
         <v>-1.402286340628343</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E47">
         <v>1.469856507982922</v>
@@ -4014,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4064,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4078,7 +4075,7 @@
         <v>-1.119201343261796</v>
       </c>
       <c r="D49" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E49">
         <v>1.798123813695423</v>
@@ -4114,7 +4111,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4128,7 +4125,7 @@
         <v>-1.040276682727416</v>
       </c>
       <c r="D50" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E50">
         <v>1.798123813695423</v>
@@ -4164,7 +4161,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4178,7 +4175,7 @@
         <v>-0.970418309242234</v>
       </c>
       <c r="D51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E51">
         <v>-1.315795006570312</v>
@@ -4214,7 +4211,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4228,7 +4225,7 @@
         <v>-1.094604783790125</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E52">
         <v>1.627274602785022</v>
@@ -4264,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4278,7 +4275,7 @@
         <v>-1.015851727159035</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E53">
         <v>1.627274602785022</v>
@@ -4314,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4328,7 +4325,7 @@
         <v>-1.190513514023774</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E54">
         <v>-1.147995174237213</v>
@@ -4364,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4378,7 +4375,7 @@
         <v>-1.15006863091817</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E55">
         <v>1.577640908889972</v>
@@ -4414,7 +4411,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4428,7 +4425,7 @@
         <v>-1.255522302285485</v>
       </c>
       <c r="D56" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E56">
         <v>-0.5624021926528435</v>
@@ -4464,7 +4461,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4478,7 +4475,7 @@
         <v>-1.320960230949986</v>
       </c>
       <c r="D57" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E57">
         <v>1.424712797977779</v>
@@ -4514,7 +4511,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4528,7 +4525,7 @@
         <v>-1.455823154415796</v>
       </c>
       <c r="D58" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E58">
         <v>-0.3493885347260317</v>
@@ -4564,7 +4561,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4578,7 +4575,7 @@
         <v>-1.605480846937454</v>
       </c>
       <c r="D59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E59">
         <v>-0.7894370781288025</v>
@@ -4614,7 +4611,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4628,7 +4625,7 @@
         <v>-1.761773123733541</v>
       </c>
       <c r="D60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E60">
         <v>-1.128596969277446</v>
@@ -4664,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4678,7 +4675,7 @@
         <v>-1.457944364792599</v>
       </c>
       <c r="D61" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E61">
         <v>-0.8017368070151889</v>
@@ -4714,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4728,7 +4725,7 @@
         <v>-1.234076514305805</v>
       </c>
       <c r="D62" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E62">
         <v>0.01703472753200685</v>
@@ -4764,7 +4761,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4778,7 +4775,7 @@
         <v>-0.7963224235233177</v>
       </c>
       <c r="D63" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E63">
         <v>0.2870665855800212</v>
@@ -4814,7 +4811,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4828,7 +4825,7 @@
         <v>-0.8942517780380754</v>
       </c>
       <c r="D64" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E64">
         <v>0.59890656545236</v>
@@ -4864,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4878,7 +4875,7 @@
         <v>-0.899307304101125</v>
       </c>
       <c r="D65" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E65">
         <v>0.6876116265245429</v>
@@ -4914,7 +4911,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4928,7 +4925,7 @@
         <v>-0.8589383918075626</v>
       </c>
       <c r="D66" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E66">
         <v>0.8335609313842731</v>
@@ -4964,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4978,7 +4975,7 @@
         <v>-0.6533981903373771</v>
       </c>
       <c r="D67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E67">
         <v>1.169788560028703</v>
@@ -5014,7 +5011,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5028,7 +5025,7 @@
         <v>4.835153534210221</v>
       </c>
       <c r="D68" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E68">
         <v>2.04429947322755</v>
@@ -5064,7 +5061,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5078,7 +5075,7 @@
         <v>-0.406918334342155</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E69">
         <v>1.312995819177061</v>
@@ -5114,7 +5111,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5128,7 +5125,7 @@
         <v>0.04130730968482865</v>
       </c>
       <c r="D70" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E70">
         <v>2.64378384364354</v>
@@ -5164,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5178,7 +5175,7 @@
         <v>5.033791575296075</v>
       </c>
       <c r="D71" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E71">
         <v>2.275021568455536</v>
@@ -5214,7 +5211,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5228,7 +5225,7 @@
         <v>-0.1691188742298735</v>
       </c>
       <c r="D72" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E72">
         <v>1.79275039480164</v>
@@ -5264,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5278,7 +5275,7 @@
         <v>0.2293541709380591</v>
       </c>
       <c r="D73" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E73">
         <v>2.812063918551083</v>
@@ -5314,7 +5311,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5328,7 +5325,7 @@
         <v>5.217902572011447</v>
       </c>
       <c r="D74" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E74">
         <v>2.488870208345837</v>
@@ -5364,7 +5361,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5378,7 +5375,7 @@
         <v>0.0512895398901918</v>
       </c>
       <c r="D75" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E75">
         <v>1.57274123510015</v>
@@ -5414,7 +5411,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5428,7 +5425,7 @@
         <v>0.3237189931323456</v>
       </c>
       <c r="D76" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E76">
         <v>2.896509461761223</v>
@@ -5464,7 +5461,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5478,7 +5475,7 @@
         <v>5.3102923165319</v>
       </c>
       <c r="D77" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E77">
         <v>2.596182761957483</v>
@@ -5514,7 +5511,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5528,7 +5525,7 @@
         <v>0.161893889624892</v>
       </c>
       <c r="D78" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E78">
         <v>1.501333830022219</v>
@@ -5564,7 +5561,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5578,7 +5575,7 @@
         <v>5.33023415169577</v>
       </c>
       <c r="D79" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E79">
         <v>2.619345606126444</v>
@@ -5614,7 +5611,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5628,7 +5625,7 @@
         <v>0.1857672504861512</v>
       </c>
       <c r="D80" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E80">
         <v>1.155646098159064</v>
@@ -5664,7 +5661,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5678,7 +5675,7 @@
         <v>5.37850629613547</v>
       </c>
       <c r="D81" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E81">
         <v>2.675414676508897</v>
@@ -5714,7 +5711,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5728,7 +5725,7 @@
         <v>0.243556231003037</v>
       </c>
       <c r="D82" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E82">
         <v>1.799674337820232</v>
@@ -5764,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5778,7 +5775,7 @@
         <v>5.505970450595548</v>
       </c>
       <c r="D83" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E83">
         <v>2.823466865418581</v>
@@ -5814,7 +5811,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5828,7 +5825,7 @@
         <v>0.3961498981001377</v>
       </c>
       <c r="D84" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E84">
         <v>1.846556155176511</v>
@@ -5864,7 +5861,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5878,7 +5875,7 @@
         <v>5.552898822755296</v>
       </c>
       <c r="D85" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E85">
         <v>2.877975117167079</v>
@@ -5914,7 +5911,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5928,7 +5925,7 @@
         <v>0.4523301821108561</v>
       </c>
       <c r="D86" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E86">
         <v>2.714577056552891</v>
@@ -5964,7 +5961,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5978,7 +5975,7 @@
         <v>0.844003460842476</v>
       </c>
       <c r="D87" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E87">
         <v>3.182739844457025</v>
@@ -6014,7 +6011,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6028,7 +6025,7 @@
         <v>5.819687109336471</v>
       </c>
       <c r="D88" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E88">
         <v>2.897855098492958</v>
@@ -6064,7 +6061,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6078,7 +6075,7 @@
         <v>0.7717156843363</v>
       </c>
       <c r="D89" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E89">
         <v>3.232403806926722</v>
@@ -6114,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6128,7 +6125,7 @@
         <v>2.174557955758587</v>
       </c>
       <c r="D90" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E90">
         <v>4.552795119478848</v>
@@ -6164,7 +6161,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6178,7 +6175,7 @@
         <v>2.230502900253292</v>
       </c>
       <c r="D91" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E91">
         <v>4.552795119478848</v>
@@ -6214,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6228,7 +6225,7 @@
         <v>7.122392789242706</v>
       </c>
       <c r="D92" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E92">
         <v>4.410974047362672</v>
@@ -6264,7 +6261,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6278,7 +6275,7 @@
         <v>3.377229031968387</v>
       </c>
       <c r="D93" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E93">
         <v>5.847002514367812</v>
@@ -6314,7 +6311,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6328,7 +6325,7 @@
         <v>3.424783248024418</v>
       </c>
       <c r="D94" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E94">
         <v>5.847002514367812</v>
@@ -6364,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6378,7 +6375,7 @@
         <v>8.29989168013649</v>
       </c>
       <c r="D95" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E95">
         <v>5.631180854885052</v>
@@ -6414,7 +6411,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6428,7 +6425,7 @@
         <v>4.683694888843547</v>
       </c>
       <c r="D96" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E96">
         <v>7.023429444093537</v>
@@ -6464,7 +6461,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6478,7 +6475,7 @@
         <v>4.722134226828356</v>
       </c>
       <c r="D97" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E97">
         <v>7.023429444093537</v>
@@ -6514,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6528,7 +6525,7 @@
         <v>9.579012902797984</v>
       </c>
       <c r="D98" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E98">
         <v>6.893347467132109</v>
@@ -6564,7 +6561,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6578,7 +6575,7 @@
         <v>3.961474621504259</v>
       </c>
       <c r="D99" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E99">
         <v>6.476706188649629</v>
@@ -6614,7 +6611,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6628,7 +6625,7 @@
         <v>8.320444610292363</v>
       </c>
       <c r="D100" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E100">
         <v>7.021567248362409</v>
@@ -6664,7 +6661,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6678,7 +6675,7 @@
         <v>8.530866989040167</v>
       </c>
       <c r="D101" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E101">
         <v>7.021567248362409</v>
@@ -6714,7 +6711,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6728,7 +6725,7 @@
         <v>3.2890165208482</v>
       </c>
       <c r="D102" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E102">
         <v>5.857937357507026</v>
@@ -6764,7 +6761,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6778,7 +6775,7 @@
         <v>7.698991315674085</v>
       </c>
       <c r="D103" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E103">
         <v>6.277165792762322</v>
@@ -6814,7 +6811,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6828,7 +6825,7 @@
         <v>7.862435583597616</v>
       </c>
       <c r="D104" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E104">
         <v>6.277165792762322</v>
@@ -6864,7 +6861,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6878,7 +6875,7 @@
         <v>2.706415003086228</v>
       </c>
       <c r="D105" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E105">
         <v>5.321850930983533</v>
@@ -6914,7 +6911,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6928,7 +6925,7 @@
         <v>7.160579134588669</v>
       </c>
       <c r="D106" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E106">
         <v>5.783497068837448</v>
@@ -6964,7 +6961,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6978,7 +6975,7 @@
         <v>7.283322697678528</v>
       </c>
       <c r="D107" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E107">
         <v>5.783497068837448</v>
@@ -7014,7 +7011,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7028,7 +7025,7 @@
         <v>2.25250194719996</v>
       </c>
       <c r="D108" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E108">
         <v>4.90417843844148</v>
@@ -7064,7 +7061,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7078,7 +7075,7 @@
         <v>6.741094613879405</v>
       </c>
       <c r="D109" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E109">
         <v>5.766049754225914</v>
@@ -7114,7 +7111,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7128,7 +7125,7 @@
         <v>6.83212768404308</v>
       </c>
       <c r="D110" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E110">
         <v>5.766049754225914</v>
@@ -7164,7 +7161,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7178,7 +7175,7 @@
         <v>1.648635956687475</v>
       </c>
       <c r="D111" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E111">
         <v>4.348525301462924</v>
@@ -7214,7 +7211,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7228,7 +7225,7 @@
         <v>6.183030834224155</v>
       </c>
       <c r="D112" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E112">
         <v>5.350064030791522</v>
@@ -7264,7 +7261,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7278,7 +7275,7 @@
         <v>6.231877657545638</v>
       </c>
       <c r="D113" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E113">
         <v>5.350064030791522</v>
@@ -7314,7 +7311,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7328,7 +7325,7 @@
         <v>1.432518806234409</v>
       </c>
       <c r="D114" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E114">
         <v>4.149663013321483</v>
@@ -7364,7 +7361,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7378,7 +7375,7 @@
         <v>5.983305802967131</v>
       </c>
       <c r="D115" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E115">
         <v>4.577912304600769</v>
@@ -7414,7 +7411,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7428,7 +7425,7 @@
         <v>6.017054621765944</v>
       </c>
       <c r="D116" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E116">
         <v>4.577912304600769</v>
@@ -7464,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7478,7 +7475,7 @@
         <v>1.226728012835469</v>
       </c>
       <c r="D117" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E117">
         <v>3.960302622589126</v>
@@ -7514,7 +7511,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7528,7 +7525,7 @@
         <v>5.793123892101445</v>
       </c>
       <c r="D118" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E118">
         <v>4.612872778687663</v>
@@ -7564,7 +7561,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7578,7 +7575,7 @@
         <v>5.812496108566997</v>
       </c>
       <c r="D119" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E119">
         <v>4.612872778687663</v>
@@ -7614,7 +7611,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7628,7 +7625,7 @@
         <v>1.216947853386511</v>
       </c>
       <c r="D120" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E120">
         <v>3.951303314193975</v>
@@ -7664,7 +7661,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7678,7 +7675,7 @@
         <v>5.802774512947074</v>
       </c>
       <c r="D121" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E121">
         <v>4.403561129870987</v>
@@ -7714,7 +7711,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7728,7 +7725,7 @@
         <v>1.177523163430447</v>
       </c>
       <c r="D122" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E122">
         <v>3.915026304074722</v>
@@ -7764,7 +7761,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7778,7 +7775,7 @@
         <v>5.763585898978771</v>
       </c>
       <c r="D123" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E123">
         <v>4.466025047817013</v>
@@ -7814,7 +7811,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7828,7 +7825,7 @@
         <v>0.9680478903759173</v>
       </c>
       <c r="D124" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E124">
         <v>3.722275603719158</v>
@@ -7864,7 +7861,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7878,7 +7875,7 @@
         <v>0.8515262832029507</v>
       </c>
       <c r="D125" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E125">
         <v>3.61505711887537</v>
@@ -7914,7 +7911,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7928,7 +7925,7 @@
         <v>0.6675490824101864</v>
       </c>
       <c r="D126" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E126">
         <v>3.445768716549093</v>
@@ -7964,7 +7961,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7978,7 +7975,7 @@
         <v>0.2453647773980379</v>
       </c>
       <c r="D127" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E127">
         <v>3.057291741278434</v>
@@ -8014,7 +8011,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8028,7 +8025,7 @@
         <v>-0.1442597189068877</v>
       </c>
       <c r="D128" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E128">
         <v>2.69877498918947</v>
@@ -8064,7 +8061,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8078,7 +8075,7 @@
         <v>3.671796227407118</v>
       </c>
       <c r="D129" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E129">
         <v>1.089748757437874</v>
@@ -8114,7 +8111,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8128,7 +8125,7 @@
         <v>-1.239097601114093</v>
       </c>
       <c r="D130" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E130">
         <v>1.261882831716061</v>
@@ -8164,7 +8161,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8178,7 +8175,7 @@
         <v>3.066548753992304</v>
       </c>
       <c r="D131" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E131">
         <v>0.4140568037443764</v>
@@ -8214,7 +8211,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8228,7 +8225,7 @@
         <v>-1.959356470902271</v>
       </c>
       <c r="D132" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E132">
         <v>0.6034425874785647</v>
@@ -8264,7 +8261,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8278,7 +8275,7 @@
         <v>2.434653904799742</v>
       </c>
       <c r="D133" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E133">
         <v>-0.2913840017675113</v>
@@ -8314,7 +8311,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8328,7 +8325,7 @@
         <v>-2.711326350820261</v>
       </c>
       <c r="D134" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E134">
         <v>-0.08398696342450762</v>
@@ -8364,7 +8361,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8378,7 +8375,7 @@
         <v>2.046949385277987</v>
       </c>
       <c r="D135" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E135">
         <v>-0.7242132753428656</v>
@@ -8414,7 +8411,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8428,7 +8425,7 @@
         <v>-3.172703938184629</v>
       </c>
       <c r="D136" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E136">
         <v>-0.5057652768234711</v>
@@ -8464,7 +8461,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8478,7 +8475,7 @@
         <v>1.727381390460117</v>
       </c>
       <c r="D137" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E137">
         <v>0.5925973930511788</v>
@@ -8514,7 +8511,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8528,7 +8525,7 @@
         <v>1.685047495782005</v>
       </c>
       <c r="D138" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E138">
         <v>-1.128236762428639</v>
@@ -8564,7 +8561,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8578,7 +8575,7 @@
         <v>-3.603375782929252</v>
       </c>
       <c r="D139" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E139">
         <v>-0.8994732706219501</v>
@@ -8614,7 +8611,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8628,7 +8625,7 @@
         <v>1.329375274458599</v>
       </c>
       <c r="D140" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E140">
         <v>-0.02169112718700106</v>
@@ -8664,7 +8661,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8678,7 +8675,7 @@
         <v>1.370767088004978</v>
       </c>
       <c r="D141" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E141">
         <v>-1.479096125030072</v>
@@ -8714,7 +8711,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8728,7 +8725,7 @@
         <v>-3.977376933276734</v>
       </c>
       <c r="D142" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E142">
         <v>-1.241374521837809</v>
@@ -8764,7 +8761,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8778,7 +8775,7 @@
         <v>0.9837414768320834</v>
       </c>
       <c r="D143" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E143">
         <v>-0.5624929319466254</v>
@@ -8814,7 +8811,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8828,7 +8825,7 @@
         <v>-4.274892307557078</v>
       </c>
       <c r="D144" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E144">
         <v>-1.513354644433413</v>
@@ -8878,7 +8875,7 @@
         <v>0.7087921389242986</v>
       </c>
       <c r="D145" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E145">
         <v>-0.01219137097330147</v>
@@ -8928,7 +8925,7 @@
         <v>-6.600419867221269</v>
       </c>
       <c r="D146" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E146">
         <v>-3.935750603200287</v>
@@ -8964,7 +8961,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8978,7 +8975,7 @@
         <v>-1.740049190571469</v>
       </c>
       <c r="D147" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E147">
         <v>-3.803035064283293</v>
@@ -9014,7 +9011,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9028,7 +9025,7 @@
         <v>-7.356943655480499</v>
       </c>
       <c r="D148" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E148">
         <v>-4.634314907681588</v>
@@ -9064,7 +9061,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9078,7 +9075,7 @@
         <v>-2.446239742918287</v>
       </c>
       <c r="D149" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E149">
         <v>-3.284642996427294</v>
@@ -9114,7 +9111,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9128,7 +9125,7 @@
         <v>-2.764549545202325</v>
       </c>
       <c r="D150" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E150">
         <v>-3.284642996427294</v>
@@ -9164,7 +9161,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9178,7 +9175,7 @@
         <v>-8.273062059554213</v>
       </c>
       <c r="D151" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E151">
         <v>-5.480246821120623</v>
@@ -9214,7 +9211,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9228,7 +9225,7 @@
         <v>-3.301406720914517</v>
       </c>
       <c r="D152" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E152">
         <v>-3.80770165872979</v>
@@ -9264,7 +9261,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9278,7 +9275,7 @@
         <v>-3.640798600667189</v>
       </c>
       <c r="D153" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E153">
         <v>-3.80770165872979</v>
@@ -9314,7 +9311,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9328,7 +9325,7 @@
         <v>-9.028638086965721</v>
       </c>
       <c r="D154" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E154">
         <v>-6.177935975464312</v>
@@ -9364,7 +9361,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9378,7 +9375,7 @@
         <v>-4.006712569082914</v>
       </c>
       <c r="D155" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E155">
         <v>-5.764446572941544</v>
@@ -9414,7 +9411,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9428,7 +9425,7 @@
         <v>-4.355244481425245</v>
       </c>
       <c r="D156" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E156">
         <v>-5.764446572941544</v>
@@ -9464,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9478,7 +9475,7 @@
         <v>-9.288472736223071</v>
       </c>
       <c r="D157" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E157">
         <v>-6.4178639378834</v>
@@ -9514,7 +9511,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9528,7 +9525,7 @@
         <v>-4.249259832401776</v>
       </c>
       <c r="D158" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E158">
         <v>-5.572990039214197</v>
@@ -9564,7 +9561,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9578,7 +9575,7 @@
         <v>-4.600934905823827</v>
       </c>
       <c r="D159" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E159">
         <v>-5.572990039214197</v>
@@ -9614,7 +9611,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9628,7 +9625,7 @@
         <v>-8.391360480599353</v>
       </c>
       <c r="D160" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E160">
         <v>-5.589482056682467</v>
@@ -9664,7 +9661,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9678,7 +9675,7 @@
         <v>-3.41183448088206</v>
       </c>
       <c r="D161" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E161">
         <v>-4.236414237755341</v>
@@ -9714,7 +9711,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9728,7 +9725,7 @@
         <v>-3.752657389921566</v>
       </c>
       <c r="D162" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E162">
         <v>-4.236414237755341</v>
@@ -9764,7 +9761,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9778,7 +9775,7 @@
         <v>-7.284701623181299</v>
       </c>
       <c r="D163" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E163">
         <v>-4.567607547211761</v>
@@ -9814,7 +9811,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9828,7 +9825,7 @@
         <v>-2.378804136155122</v>
       </c>
       <c r="D164" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E164">
         <v>-3.182992288094191</v>
@@ -9864,7 +9861,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9914,7 +9911,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9964,7 +9961,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9978,7 +9975,7 @@
         <v>15.30025538505301</v>
       </c>
       <c r="D167" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E167">
         <v>12.2194473505381</v>
@@ -10014,7 +10011,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10028,7 +10025,7 @@
         <v>16.08154605938966</v>
       </c>
       <c r="D168" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E168">
         <v>12.2194473505381</v>
@@ -10064,7 +10061,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10114,7 +10111,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10164,7 +10161,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10214,7 +10211,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10264,7 +10261,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10314,7 +10311,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10364,7 +10361,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10414,7 +10411,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10464,7 +10461,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10514,7 +10511,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10564,7 +10561,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10578,7 +10575,7 @@
         <v>-2.965774048910724</v>
       </c>
       <c r="D179" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E179">
         <v>-6.323583762599906</v>
@@ -10614,7 +10611,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10628,7 +10625,7 @@
         <v>-3.841273412039687</v>
       </c>
       <c r="D180" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E180">
         <v>-6.323583762599906</v>
@@ -10664,7 +10661,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10714,7 +10711,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10728,7 +10725,7 @@
         <v>-4.596644143057084</v>
       </c>
       <c r="D182" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E182">
         <v>-7.87451662725034</v>
@@ -10764,7 +10761,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10778,7 +10775,7 @@
         <v>-5.499155847289916</v>
       </c>
       <c r="D183" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E183">
         <v>-7.87451662725034</v>
@@ -10814,7 +10811,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10864,7 +10861,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10878,7 +10875,7 @@
         <v>-6.176260919928573</v>
       </c>
       <c r="D185" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E185">
         <v>-9.588220956609884</v>
@@ -10914,7 +10911,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10928,7 +10925,7 @@
         <v>-7.104936049037125</v>
       </c>
       <c r="D186" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E186">
         <v>-9.588220956609884</v>
@@ -10964,7 +10961,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11014,7 +11011,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11064,7 +11061,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11078,7 +11075,7 @@
         <v>-5.957065888688689</v>
       </c>
       <c r="D189" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E189">
         <v>-9.35041930781134</v>
@@ -11114,7 +11111,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11128,7 +11125,7 @@
         <v>-6.882110458273605</v>
       </c>
       <c r="D190" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E190">
         <v>-9.35041930781134</v>
@@ -11164,7 +11161,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11178,7 +11175,7 @@
         <v>-5.75373473480284</v>
       </c>
       <c r="D191" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E191">
         <v>-9.129828159496252</v>
@@ -11228,7 +11225,7 @@
         <v>-6.675411500596677</v>
       </c>
       <c r="D192" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E192">
         <v>-9.129828159496252</v>
@@ -11278,7 +11275,7 @@
         <v>4.036863233290944</v>
       </c>
       <c r="D193" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E193">
         <v>1.091137151603181</v>
@@ -11328,7 +11325,7 @@
         <v>4.353212181898559</v>
       </c>
       <c r="D194" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E194">
         <v>1.091137151603181</v>
@@ -11378,7 +11375,7 @@
         <v>4.092859462531468</v>
       </c>
       <c r="D195" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E195">
         <v>1.091137151603181</v>
@@ -11464,7 +11461,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11514,7 +11511,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11664,7 +11661,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11714,7 +11711,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11764,7 +11761,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11814,7 +11811,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11864,7 +11861,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11914,7 +11911,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11964,7 +11961,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12014,7 +12011,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12064,7 +12061,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12114,7 +12111,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12164,7 +12161,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12214,7 +12211,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12264,7 +12261,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12314,7 +12311,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12364,7 +12361,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12378,7 +12375,7 @@
         <v>2.797016608461103</v>
       </c>
       <c r="D215" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E215">
         <v>-0.1302387600075896</v>
@@ -12414,7 +12411,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12428,7 +12425,7 @@
         <v>3.23804287129742</v>
       </c>
       <c r="D216" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E216">
         <v>-0.1302387600075896</v>
@@ -12464,7 +12461,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12478,7 +12475,7 @@
         <v>2.97076363447318</v>
       </c>
       <c r="D217" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E217">
         <v>-0.1302387600075896</v>
@@ -12514,7 +12511,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12528,7 +12525,7 @@
         <v>-2.735537076225839</v>
       </c>
       <c r="D218" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E218">
         <v>-0.06446785034954416</v>
@@ -12564,7 +12561,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12578,7 +12575,7 @@
         <v>2.142297248198716</v>
       </c>
       <c r="D219" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E219">
         <v>-0.7752043867837592</v>
@@ -12614,7 +12611,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12628,7 +12625,7 @@
         <v>2.649161212067007</v>
       </c>
       <c r="D220" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E220">
         <v>-0.7752043867837592</v>
@@ -12664,7 +12661,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12678,7 +12675,7 @@
         <v>1.866662847049479</v>
       </c>
       <c r="D221" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E221">
         <v>-0.7752043867837592</v>
@@ -12714,7 +12711,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12728,7 +12725,7 @@
         <v>-3.292719101626048</v>
       </c>
       <c r="D222" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E222">
         <v>-0.5316716843393898</v>
@@ -12764,7 +12761,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12778,7 +12775,7 @@
         <v>0.7343076746441</v>
       </c>
       <c r="D223" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E223">
         <v>-2.162218324233283</v>
@@ -12828,7 +12825,7 @@
         <v>1.382757182221791</v>
       </c>
       <c r="D224" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E224">
         <v>-2.162218324233283</v>
@@ -12878,7 +12875,7 @@
         <v>0.5792831810991643</v>
       </c>
       <c r="D225" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E225">
         <v>-2.162218324233283</v>
@@ -12928,7 +12925,7 @@
         <v>-4.4909523141297</v>
       </c>
       <c r="D226" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E226">
         <v>-1.797099453998044</v>
@@ -12978,7 +12975,7 @@
         <v>-0.5271433345479153</v>
       </c>
       <c r="D227" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E227">
         <v>-3.404876767180344</v>
@@ -13028,7 +13025,7 @@
         <v>0.2481559951831649</v>
       </c>
       <c r="D228" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E228">
         <v>-3.404876767180344</v>
@@ -13078,7 +13075,7 @@
         <v>-0.5741105721844058</v>
       </c>
       <c r="D229" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E229">
         <v>-3.404876767180344</v>
@@ -13128,7 +13125,7 @@
         <v>-5.289194339951301</v>
       </c>
       <c r="D230" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E230">
         <v>-2.93597803324387</v>
@@ -13178,7 +13175,7 @@
         <v>-1.521590007004434</v>
       </c>
       <c r="D231" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E231">
         <v>-4.774748703164175</v>
@@ -13214,7 +13211,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13228,7 +13225,7 @@
         <v>-2.373169137555241</v>
       </c>
       <c r="D232" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E232">
         <v>-4.774748703164175</v>
@@ -13264,7 +13261,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13278,7 +13275,7 @@
         <v>-6.960010441395497</v>
       </c>
       <c r="D233" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E233">
         <v>-4.500536093148853</v>
@@ -13314,7 +13311,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13328,7 +13325,7 @@
         <v>-2.452340392521911</v>
       </c>
       <c r="D234" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E234">
         <v>-5.548191233294997</v>
@@ -13378,7 +13375,7 @@
         <v>-2.754963624773605</v>
       </c>
       <c r="D235" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E235">
         <v>-5.548191233294997</v>
@@ -13428,7 +13425,7 @@
         <v>-7.838731302256715</v>
       </c>
       <c r="D236" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E236">
         <v>-5.323373390490392</v>
@@ -13478,7 +13475,7 @@
         <v>-4.58678078170076</v>
       </c>
       <c r="D237" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E237">
         <v>-7.667945163513835</v>
@@ -13514,7 +13511,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13528,7 +13525,7 @@
         <v>-5.270890369576151</v>
       </c>
       <c r="D238" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E238">
         <v>-7.667945163513835</v>
@@ -13564,7 +13561,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13578,7 +13575,7 @@
         <v>-4.902661407674056</v>
       </c>
       <c r="D239" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E239">
         <v>-7.667945163513835</v>
@@ -13614,7 +13611,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13628,7 +13625,7 @@
         <v>-9.853855147941093</v>
       </c>
       <c r="D240" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E240">
         <v>-7.21034243019923</v>
@@ -13664,7 +13661,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13678,7 +13675,7 @@
         <v>-5.59817458645032</v>
       </c>
       <c r="D241" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E241">
         <v>-8.513312611948162</v>
@@ -13714,7 +13711,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13728,7 +13725,7 @@
         <v>-5.920337161521442</v>
       </c>
       <c r="D242" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E242">
         <v>-8.513312611948162</v>
@@ -13764,7 +13761,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13778,7 +13775,7 @@
         <v>-10.78187598777789</v>
       </c>
       <c r="D243" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E243">
         <v>-7.189437361711093</v>
@@ -13814,7 +13811,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13828,7 +13825,7 @@
         <v>-10.80871141081024</v>
       </c>
       <c r="D244" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E244">
         <v>-8.104473185122753</v>
@@ -13864,7 +13861,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13878,7 +13875,7 @@
         <v>-5.98278744209609</v>
       </c>
       <c r="D245" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E245">
         <v>-8.914647765665489</v>
@@ -13914,7 +13911,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13928,7 +13925,7 @@
         <v>-6.30733891689172</v>
       </c>
       <c r="D246" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E246">
         <v>-8.914647765665489</v>
@@ -13964,7 +13961,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13978,7 +13975,7 @@
         <v>-11.21108163828114</v>
       </c>
       <c r="D247" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E247">
         <v>-7.582809516346728</v>
@@ -14014,7 +14011,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14028,7 +14025,7 @@
         <v>-11.09924338896238</v>
       </c>
       <c r="D248" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E248">
         <v>-7.582809516346728</v>
@@ -14064,7 +14061,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14078,7 +14075,7 @@
         <v>-11.17182416893544</v>
       </c>
       <c r="D249" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E249">
         <v>-8.444493245911037</v>
@@ -14114,7 +14111,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14128,7 +14125,7 @@
         <v>-6.197743032286496</v>
       </c>
       <c r="D250" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E250">
         <v>-9.138949251081566</v>
@@ -14164,7 +14161,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14178,7 +14175,7 @@
         <v>-6.52362963497151</v>
       </c>
       <c r="D251" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E251">
         <v>-9.138949251081566</v>
@@ -14214,7 +14211,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14228,7 +14225,7 @@
         <v>-11.45095961574</v>
       </c>
       <c r="D252" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E252">
         <v>-7.802660575464863</v>
@@ -14264,7 +14261,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14278,7 +14275,7 @@
         <v>-11.33467094012331</v>
       </c>
       <c r="D253" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E253">
         <v>-7.802660575464863</v>
@@ -14314,7 +14311,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14328,7 +14325,7 @@
         <v>-11.37476360812142</v>
       </c>
       <c r="D254" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E254">
         <v>-8.63452644883299</v>
@@ -14364,7 +14361,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14378,7 +14375,7 @@
         <v>-6.365423262694474</v>
       </c>
       <c r="D255" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E255">
         <v>-6.712841826990488</v>
@@ -14414,7 +14411,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14428,7 +14425,7 @@
         <v>-6.180679040630039</v>
       </c>
       <c r="D256" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E256">
         <v>-9.121143346744393</v>
@@ -14464,7 +14461,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14478,7 +14475,7 @@
         <v>-6.506459655789232</v>
       </c>
       <c r="D257" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E257">
         <v>-9.121143346744393</v>
@@ -14514,7 +14511,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14528,7 +14525,7 @@
         <v>-11.43191719026831</v>
       </c>
       <c r="D258" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E258">
         <v>-7.785207962880413</v>
@@ -14564,7 +14561,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14578,7 +14575,7 @@
         <v>-11.31598180640433</v>
       </c>
       <c r="D259" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E259">
         <v>-7.785207962880413</v>
@@ -14614,7 +14611,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14628,7 +14625,7 @@
         <v>-11.3586535041973</v>
       </c>
       <c r="D260" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E260">
         <v>-8.619440890991779</v>
@@ -14664,7 +14661,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14678,7 +14675,7 @@
         <v>-6.352422126194313</v>
       </c>
       <c r="D261" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E261">
         <v>-7.002545941158143</v>
@@ -14714,7 +14711,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14728,7 +14725,7 @@
         <v>-6.259072586714403</v>
       </c>
       <c r="D262" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E262">
         <v>-9.202945307875904</v>
@@ -14764,7 +14761,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14778,7 +14775,7 @@
         <v>-6.58534011830891</v>
       </c>
       <c r="D263" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E263">
         <v>-9.202945307875904</v>
@@ -14814,7 +14811,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14828,7 +14825,7 @@
         <v>-11.51939984314506</v>
       </c>
       <c r="D264" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E264">
         <v>-7.865386869227571</v>
@@ -14864,7 +14861,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14878,7 +14875,7 @@
         <v>-11.40184140449673</v>
       </c>
       <c r="D265" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E265">
         <v>-7.865386869227571</v>
@@ -14914,7 +14911,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14928,7 +14925,7 @@
         <v>-11.43266480236391</v>
       </c>
       <c r="D266" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E266">
         <v>-8.688745330283755</v>
@@ -14964,7 +14961,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14978,7 +14975,7 @@
         <v>-6.412150542258594</v>
       </c>
       <c r="D267" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E267">
         <v>-6.792666905080129</v>
@@ -15014,7 +15011,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15028,7 +15025,7 @@
         <v>-6.321920167701883</v>
       </c>
       <c r="D268" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E268">
         <v>-9.268525392384579</v>
@@ -15064,7 +15061,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15078,7 +15075,7 @@
         <v>-11.58953410018906</v>
       </c>
       <c r="D269" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E269">
         <v>-7.929665761583294</v>
@@ -15114,7 +15111,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15128,7 +15125,7 @@
         <v>-11.47067446938778</v>
       </c>
       <c r="D270" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E270">
         <v>-7.929665761583294</v>
@@ -15164,7 +15161,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15178,7 +15175,7 @@
         <v>-11.49199916453843</v>
       </c>
       <c r="D271" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E271">
         <v>-8.744306235214712</v>
@@ -15214,7 +15211,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15228,7 +15225,7 @@
         <v>-6.460034413487151</v>
       </c>
       <c r="D272" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E272">
         <v>-6.681381790702538</v>
@@ -15264,7 +15261,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15278,7 +15275,7 @@
         <v>-6.550476318984671</v>
       </c>
       <c r="D273" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E273">
         <v>-9.507018767636186</v>
@@ -15314,7 +15311,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15328,7 +15325,7 @@
         <v>-11.8445895153887</v>
       </c>
       <c r="D274" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E274">
         <v>-8.16342712542118</v>
@@ -15364,7 +15361,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15378,7 +15375,7 @@
         <v>-11.72099787317369</v>
       </c>
       <c r="D275" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E275">
         <v>-8.16342712542118</v>
@@ -15414,7 +15411,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15428,7 +15425,7 @@
         <v>-11.70777888500417</v>
       </c>
       <c r="D276" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E276">
         <v>-8.94636312258066</v>
@@ -15464,7 +15461,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15514,7 +15511,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15528,7 +15525,7 @@
         <v>-6.704638136207883</v>
       </c>
       <c r="D278" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E278">
         <v>-9.667883272564755</v>
@@ -15564,7 +15561,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15578,7 +15575,7 @@
         <v>-12.01662516649286</v>
       </c>
       <c r="D279" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E279">
         <v>-8.321099874299577</v>
@@ -15614,7 +15611,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15628,7 +15625,7 @@
         <v>-11.88984176822768</v>
       </c>
       <c r="D280" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E280">
         <v>-8.321099874299577</v>
@@ -15664,7 +15661,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15678,7 +15675,7 @@
         <v>-12.14300130071843</v>
       </c>
       <c r="D281" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E281">
         <v>-9.082651105922917</v>
@@ -15714,7 +15711,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15728,7 +15725,7 @@
         <v>-6.751629056158386</v>
       </c>
       <c r="D282" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E282">
         <v>-6.181746306378969</v>
@@ -15764,7 +15761,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15778,7 +15775,7 @@
         <v>-6.169874970448358</v>
       </c>
       <c r="D283" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E283">
         <v>-6.181746306378969</v>
@@ -15814,7 +15811,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15828,7 +15825,7 @@
         <v>-6.791555990766213</v>
       </c>
       <c r="D284" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E284">
         <v>-9.758580164277792</v>
@@ -15864,7 +15861,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15878,7 +15875,7 @@
         <v>-12.11362045346375</v>
       </c>
       <c r="D285" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E285">
         <v>-8.40999722451037</v>
@@ -15914,7 +15911,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15928,7 +15925,7 @@
         <v>-12.22524034737093</v>
       </c>
       <c r="D286" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E286">
         <v>-9.159491528068681</v>
@@ -15964,7 +15961,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15978,7 +15975,7 @@
         <v>-6.817852183440923</v>
       </c>
       <c r="D287" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E287">
         <v>-6.265382608492114</v>
@@ -16014,7 +16011,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16028,7 +16025,7 @@
         <v>-6.233722702947933</v>
       </c>
       <c r="D288" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E288">
         <v>-6.265382608492114</v>
@@ -16064,7 +16061,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16078,7 +16075,7 @@
         <v>-12.15514825489226</v>
       </c>
       <c r="D289" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E289">
         <v>-8.448057955318696</v>
@@ -16114,7 +16111,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16128,7 +16125,7 @@
         <v>-12.26045037566933</v>
       </c>
       <c r="D290" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E290">
         <v>-9.192390175953609</v>
@@ -16164,7 +16161,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16178,7 +16175,7 @@
         <v>-6.261058628637798</v>
       </c>
       <c r="D291" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E291">
         <v>-6.075524180706029</v>
@@ -16214,7 +16211,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16228,7 +16225,7 @@
         <v>-12.2145658985059</v>
       </c>
       <c r="D292" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E292">
         <v>-8.502514942229901</v>
@@ -16278,7 +16275,7 @@
         <v>-12.31082860040297</v>
       </c>
       <c r="D293" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E293">
         <v>-9.239461296218966</v>
@@ -16328,7 +16325,7 @@
         <v>-6.300170650816128</v>
       </c>
       <c r="D294" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E294">
         <v>-5.649532575530262</v>
@@ -16378,7 +16375,7 @@
         <v>-11.84108439837907</v>
       </c>
       <c r="D295" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E295">
         <v>-8.80055369389029</v>
@@ -16414,7 +16411,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16428,7 +16425,7 @@
         <v>-5.935476465087291</v>
       </c>
       <c r="D296" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E296">
         <v>-5.137979270573577</v>
@@ -16464,7 +16461,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16514,7 +16511,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16564,7 +16561,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16614,7 +16611,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16664,7 +16661,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16714,7 +16711,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16764,7 +16761,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16814,7 +16811,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16828,7 +16825,7 @@
         <v>-0.3501812538917548</v>
       </c>
       <c r="D304" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E304">
         <v>-4.299167540216818</v>
@@ -16864,7 +16861,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16914,7 +16911,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16928,7 +16925,7 @@
         <v>-0.2510998261771533</v>
       </c>
       <c r="D306" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E306">
         <v>-4.192512218904984</v>
@@ -16964,7 +16961,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17014,7 +17011,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17028,7 +17025,7 @@
         <v>-0.1528009024453745</v>
       </c>
       <c r="D308" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E308">
         <v>-4.086699217043329</v>
@@ -17064,7 +17061,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17114,7 +17111,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17128,7 +17125,7 @@
         <v>0.06625268284449959</v>
       </c>
       <c r="D310" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E310">
         <v>-3.850900934131047</v>
@@ -17164,7 +17161,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17214,7 +17211,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17264,7 +17261,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17314,7 +17311,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17364,7 +17361,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17414,7 +17411,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17428,7 +17425,7 @@
         <v>1.82693717047681</v>
       </c>
       <c r="D316" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E316">
         <v>0.6963720300954037</v>
@@ -17464,7 +17461,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17514,7 +17511,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17528,7 +17525,7 @@
         <v>2.198341117699623</v>
       </c>
       <c r="D318" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E318">
         <v>0.5276096580294123</v>
@@ -17564,7 +17561,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17578,7 +17575,7 @@
         <v>12.7271211800604</v>
       </c>
       <c r="D319" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E319">
         <v>10.466793520675</v>
@@ -17614,7 +17611,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17628,7 +17625,7 @@
         <v>13.26860393649666</v>
       </c>
       <c r="D320" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E320">
         <v>10.466793520675</v>
@@ -17664,7 +17661,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17678,7 +17675,7 @@
         <v>12.90082807115104</v>
       </c>
       <c r="D321" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E321">
         <v>10.466793520675</v>
@@ -17714,7 +17711,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17728,7 +17725,7 @@
         <v>12.60281108867061</v>
       </c>
       <c r="D322" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E322">
         <v>10.00917894691048</v>
@@ -17764,7 +17761,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17778,7 +17775,7 @@
         <v>13.14484756489033</v>
       </c>
       <c r="D323" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E323">
         <v>10.00917894691048</v>
@@ -17814,7 +17811,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17828,7 +17825,7 @@
         <v>12.77790227921993</v>
       </c>
       <c r="D324" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E324">
         <v>10.00917894691048</v>
@@ -17864,7 +17861,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17878,7 +17875,7 @@
         <v>12.94031582834918</v>
       </c>
       <c r="D325" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E325">
         <v>10.4990798111086</v>
@@ -17914,7 +17911,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17928,7 +17925,7 @@
         <v>13.48084894269951</v>
       </c>
       <c r="D326" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E326">
         <v>10.4990798111086</v>
@@ -17964,7 +17961,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17978,7 +17975,7 @@
         <v>13.11164861422502</v>
       </c>
       <c r="D327" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E327">
         <v>10.4990798111086</v>
@@ -18014,7 +18011,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18028,7 +18025,7 @@
         <v>12.89880385150152</v>
       </c>
       <c r="D328" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E328">
         <v>10.62546343074822</v>
@@ -18064,7 +18061,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18078,7 +18075,7 @@
         <v>13.4395218744347</v>
       </c>
       <c r="D329" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E329">
         <v>10.62546343074822</v>
@@ -18114,7 +18111,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18128,7 +18125,7 @@
         <v>13.07059890883446</v>
       </c>
       <c r="D330" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E330">
         <v>10.62546343074822</v>
@@ -18164,7 +18161,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18178,7 +18175,7 @@
         <v>12.9234363080082</v>
       </c>
       <c r="D331" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E331">
         <v>11.0537757639692</v>
@@ -18214,7 +18211,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18228,7 +18225,7 @@
         <v>13.46404460953155</v>
       </c>
       <c r="D332" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E332">
         <v>11.0537757639692</v>
@@ -18264,7 +18261,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18278,7 +18275,7 @@
         <v>13.09495706181657</v>
       </c>
       <c r="D333" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E333">
         <v>11.0537757639692</v>
@@ -18314,7 +18311,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18328,7 +18325,7 @@
         <v>13.44227382778946</v>
       </c>
       <c r="D334" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E334">
         <v>11.03770193240324</v>
@@ -18364,7 +18361,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18378,7 +18375,7 @@
         <v>13.07333239270363</v>
       </c>
       <c r="D335" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E335">
         <v>11.03770193240324</v>
@@ -18414,7 +18411,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18428,7 +18425,7 @@
         <v>13.47049330154028</v>
       </c>
       <c r="D336" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E336">
         <v>12.2200768479712</v>
@@ -18464,7 +18461,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18478,7 +18475,7 @@
         <v>13.10136247401317</v>
       </c>
       <c r="D337" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E337">
         <v>12.2200768479712</v>
@@ -18514,7 +18511,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18528,7 +18525,7 @@
         <v>13.41024108188445</v>
       </c>
       <c r="D338" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E338">
         <v>11.606966539383</v>
@@ -18564,7 +18561,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18578,7 +18575,7 @@
         <v>13.04151463167046</v>
       </c>
       <c r="D339" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E339">
         <v>11.606966539383</v>
@@ -18614,7 +18611,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18628,7 +18625,7 @@
         <v>15.99098556432473</v>
       </c>
       <c r="D340" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E340">
         <v>12.49688805745362</v>
@@ -18664,7 +18661,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18678,7 +18675,7 @@
         <v>15.82125527263218</v>
       </c>
       <c r="D341" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E341">
         <v>12.49688805745362</v>
@@ -18714,7 +18711,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18728,7 +18725,7 @@
         <v>16.12796689068343</v>
       </c>
       <c r="D342" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E342">
         <v>12.49688805745362</v>
@@ -18764,7 +18761,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18778,7 +18775,7 @@
         <v>16.05759498721028</v>
       </c>
       <c r="D343" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E343">
         <v>12.56617445478137</v>
@@ -18814,7 +18811,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18828,7 +18825,7 @@
         <v>15.8869198810087</v>
       </c>
       <c r="D344" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E344">
         <v>12.56617445478137</v>
@@ -18864,7 +18861,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18878,7 +18875,7 @@
         <v>16.19347402997512</v>
       </c>
       <c r="D345" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E345">
         <v>12.56617445478137</v>
@@ -18914,7 +18911,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18928,7 +18925,7 @@
         <v>16.08852224791477</v>
       </c>
       <c r="D346" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E346">
         <v>12.59834465504137</v>
@@ -18964,7 +18961,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18978,7 +18975,7 @@
         <v>15.9174084571642</v>
       </c>
       <c r="D347" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E347">
         <v>12.59834465504137</v>
@@ -19014,7 +19011,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19028,7 +19025,7 @@
         <v>16.22388949203912</v>
       </c>
       <c r="D348" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E348">
         <v>12.59834465504137</v>
@@ -19064,7 +19061,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19078,7 +19075,7 @@
         <v>15.99827269225045</v>
       </c>
       <c r="D349" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E349">
         <v>12.50446804867659</v>
@@ -19114,7 +19111,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19128,7 +19125,7 @@
         <v>15.82843903704122</v>
       </c>
       <c r="D350" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E350">
         <v>12.50446804867659</v>
@@ -19164,7 +19161,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19178,7 +19175,7 @@
         <v>16.13513342783969</v>
       </c>
       <c r="D351" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E351">
         <v>12.50446804867659</v>
@@ -19214,7 +19211,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19228,7 +19225,7 @@
         <v>10.5571576031199</v>
       </c>
       <c r="D352" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E352">
         <v>11.2357781978979</v>
@@ -19278,7 +19275,7 @@
         <v>10.4146275818384</v>
       </c>
       <c r="D353" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E353">
         <v>11.2357781978979</v>
@@ -19328,7 +19325,7 @@
         <v>11.02395259544049</v>
       </c>
       <c r="D354" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E354">
         <v>11.2357781978979</v>
@@ -19414,7 +19411,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19464,7 +19461,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19514,7 +19511,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19564,7 +19561,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19614,7 +19611,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19664,7 +19661,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19714,7 +19711,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19764,7 +19761,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19778,7 +19775,7 @@
         <v>7.109582508392513</v>
       </c>
       <c r="D363" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E363">
         <v>10.1191386498793</v>
@@ -19828,7 +19825,7 @@
         <v>8.320739177217412</v>
       </c>
       <c r="D364" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E364">
         <v>10.1191386498793</v>
@@ -19914,7 +19911,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19964,7 +19961,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19978,7 +19975,7 @@
         <v>5.429328338517664</v>
       </c>
       <c r="D367" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E367">
         <v>6.453570540990412</v>
@@ -20014,7 +20011,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20028,7 +20025,7 @@
         <v>4.28114123100805</v>
       </c>
       <c r="D368" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E368">
         <v>5.201857907737669</v>
@@ -20064,7 +20061,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20078,7 +20075,7 @@
         <v>3.478556159579213</v>
       </c>
       <c r="D369" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E369">
         <v>4.355782779043444</v>
@@ -20114,7 +20111,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20128,7 +20125,7 @@
         <v>2.542133382528917</v>
       </c>
       <c r="D370" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E370">
         <v>3.611162052395251</v>
@@ -20164,7 +20161,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20214,7 +20211,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20228,7 +20225,7 @@
         <v>3.166397470697689</v>
       </c>
       <c r="D372" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E372">
         <v>2.50604388321451</v>
@@ -20264,7 +20261,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20314,7 +20311,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20364,7 +20361,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20414,7 +20411,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20428,7 +20425,7 @@
         <v>0.5258114362592394</v>
       </c>
       <c r="D376" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E376">
         <v>0.9640594525915418</v>
@@ -20464,7 +20461,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20478,7 +20475,7 @@
         <v>1.029412028487577</v>
       </c>
       <c r="D377" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E377">
         <v>0.9640594525915418</v>
@@ -20514,7 +20511,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20528,7 +20525,7 @@
         <v>0.5230738845135647</v>
       </c>
       <c r="D378" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E378">
         <v>0.9640594525915418</v>
@@ -20564,7 +20561,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20578,7 +20575,7 @@
         <v>0.2932995584235911</v>
       </c>
       <c r="D379" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E379">
         <v>-0.2507339019854058</v>
@@ -20614,7 +20611,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20628,7 +20625,7 @@
         <v>0.8110931833932682</v>
       </c>
       <c r="D380" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E380">
         <v>-0.2507339019854058</v>
@@ -20664,7 +20661,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20678,7 +20675,7 @@
         <v>0.3063705065605404</v>
       </c>
       <c r="D381" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E381">
         <v>-0.2507339019854058</v>
@@ -20714,7 +20711,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20728,7 +20725,7 @@
         <v>0.25081902425989</v>
       </c>
       <c r="D382" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E382">
         <v>-1.810462939778127</v>
@@ -20764,7 +20761,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20778,7 +20775,7 @@
         <v>0.7712057537963801</v>
       </c>
       <c r="D383" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E383">
         <v>-1.810462939778127</v>
@@ -20814,7 +20811,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20828,7 +20825,7 @@
         <v>0.266778227076955</v>
       </c>
       <c r="D384" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E384">
         <v>-1.810462939778127</v>
@@ -20864,7 +20861,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20878,7 +20875,7 @@
         <v>0.2555858995649842</v>
       </c>
       <c r="D385" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E385">
         <v>-0.5322733758888774</v>
@@ -20914,7 +20911,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20928,7 +20925,7 @@
         <v>0.7756816486237952</v>
       </c>
       <c r="D386" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E386">
         <v>-0.5322733758888774</v>
@@ -20964,7 +20961,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20978,7 +20975,7 @@
         <v>0.2712210021752028</v>
       </c>
       <c r="D387" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E387">
         <v>-0.5322733758888774</v>
@@ -21014,7 +21011,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21064,7 +21061,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21114,7 +21111,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21164,7 +21161,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21214,7 +21211,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21228,7 +21225,7 @@
         <v>2.068109497945251</v>
       </c>
       <c r="D392" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E392">
         <v>1.103589803610085</v>
@@ -21264,7 +21261,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21278,7 +21275,7 @@
         <v>1.130775764308638</v>
       </c>
       <c r="D393" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E393">
         <v>1.103589803610085</v>
@@ -21314,7 +21311,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21328,7 +21325,7 @@
         <v>1.848060841515313</v>
       </c>
       <c r="D394" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E394">
         <v>0.99412281255767</v>
@@ -21364,7 +21361,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21378,7 +21375,7 @@
         <v>0.9315277271432265</v>
       </c>
       <c r="D395" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E395">
         <v>0.99412281255767</v>
@@ -21414,7 +21411,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21428,7 +21425,7 @@
         <v>1.694201531226533</v>
       </c>
       <c r="D396" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E396">
         <v>0.6700023738905614</v>
@@ -21464,7 +21461,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21478,7 +21475,7 @@
         <v>0.7922123317573622</v>
       </c>
       <c r="D397" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E397">
         <v>0.6700023738905614</v>
@@ -21514,7 +21511,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21528,7 +21525,7 @@
         <v>1.513646695334067</v>
       </c>
       <c r="D398" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E398">
         <v>0.5589534979668187</v>
@@ -21564,7 +21561,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21578,7 +21575,7 @@
         <v>0.6287248684119433</v>
       </c>
       <c r="D399" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E399">
         <v>0.5589534979668187</v>
@@ -21614,7 +21611,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21664,7 +21661,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21714,7 +21711,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21728,7 +21725,7 @@
         <v>1.430312383569088</v>
       </c>
       <c r="D402" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E402">
         <v>2.785832606944602</v>
@@ -21764,7 +21761,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21778,7 +21775,7 @@
         <v>1.015447344707901</v>
       </c>
       <c r="D403" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E403">
         <v>2.785832606944602</v>
@@ -21814,7 +21811,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21828,7 +21825,7 @@
         <v>2.872497404927479</v>
       </c>
       <c r="D404" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E404">
         <v>2.785832606944602</v>
@@ -21864,7 +21861,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21878,7 +21875,7 @@
         <v>1.657667083906176</v>
       </c>
       <c r="D405" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E405">
         <v>3.010263722734074</v>
@@ -21914,7 +21911,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21928,7 +21925,7 @@
         <v>3.082432889417845</v>
       </c>
       <c r="D406" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E406">
         <v>3.010263722734074</v>
@@ -21964,7 +21961,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21978,7 +21975,7 @@
         <v>1.760495757853356</v>
       </c>
       <c r="D407" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E407">
         <v>2.967064908431617</v>
@@ -22014,7 +22011,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22028,7 +22025,7 @@
         <v>3.177383147550167</v>
       </c>
       <c r="D408" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E408">
         <v>2.967064908431617</v>
@@ -22064,7 +22061,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22078,7 +22075,7 @@
         <v>3.419213206004784</v>
       </c>
       <c r="D409" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E409">
         <v>4.96095189349581</v>
@@ -22114,7 +22111,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22128,7 +22125,7 @@
         <v>30.71910142906406</v>
       </c>
       <c r="D410" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E410">
         <v>17.77124839717711</v>
@@ -22164,7 +22161,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22178,7 +22175,7 @@
         <v>30.74457906406285</v>
       </c>
       <c r="D411" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E411">
         <v>18.07805575594424</v>
@@ -22214,7 +22211,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22228,7 +22225,7 @@
         <v>30.94531632533681</v>
       </c>
       <c r="D412" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E412">
         <v>18.41220109884297</v>
@@ -22264,7 +22261,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22278,7 +22275,7 @@
         <v>31.10162189647678</v>
       </c>
       <c r="D413" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E413">
         <v>18.55328210136541</v>
@@ -22314,7 +22311,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22328,7 +22325,7 @@
         <v>31.28406714947664</v>
       </c>
       <c r="D414" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E414">
         <v>18.71795671283931</v>
@@ -22364,7 +22361,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22378,7 +22375,7 @@
         <v>31.41016164358475</v>
       </c>
       <c r="D415" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E415">
         <v>18.83176927570312</v>
@@ -22414,7 +22411,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22428,7 +22425,7 @@
         <v>31.50687459786862</v>
       </c>
       <c r="D416" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E416">
         <v>18.91906213703726</v>
@@ -22464,7 +22461,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22478,7 +22475,7 @@
         <v>31.56465330836859</v>
       </c>
       <c r="D417" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E417">
         <v>18.97121305105996</v>
@@ -22514,7 +22511,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22528,7 +22525,7 @@
         <v>31.59842308925229</v>
       </c>
       <c r="D418" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E418">
         <v>19.00169356757187</v>
@@ -22564,7 +22561,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22578,7 +22575,7 @@
         <v>31.66012131009328</v>
       </c>
       <c r="D419" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E419">
         <v>19.05738222144783</v>
@@ -22614,7 +22611,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22628,7 +22625,7 @@
         <v>31.70713316886447</v>
       </c>
       <c r="D420" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E420">
         <v>19.09981500306598</v>
@@ -22664,7 +22661,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22678,7 +22675,7 @@
         <v>31.87762108191551</v>
       </c>
       <c r="D421" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E421">
         <v>19.25369695056011</v>
@@ -22714,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22728,7 +22725,7 @@
         <v>32.04993923346682</v>
       </c>
       <c r="D422" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E422">
         <v>19.4092308665707</v>
@@ -22764,7 +22761,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22778,7 +22775,7 @@
         <v>32.21080893028861</v>
       </c>
       <c r="D423" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E423">
         <v>19.55443143707868</v>
@@ -22814,7 +22811,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22828,7 +22825,7 @@
         <v>32.44198272920474</v>
       </c>
       <c r="D424" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E424">
         <v>19.76308830752896</v>
@@ -22864,7 +22861,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22878,7 +22875,7 @@
         <v>32.60849165225912</v>
       </c>
       <c r="D425" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E425">
         <v>19.91337882898712</v>
@@ -22914,7 +22911,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22928,7 +22925,7 @@
         <v>32.78872551361854</v>
       </c>
       <c r="D426" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E426">
         <v>20.07605744411025</v>
@@ -22964,7 +22961,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22978,7 +22975,7 @@
         <v>32.88633633076009</v>
       </c>
       <c r="D427" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E427">
         <v>20.16416071412761</v>
@@ -23014,7 +23011,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23028,7 +23025,7 @@
         <v>32.92087256937922</v>
       </c>
       <c r="D428" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E428">
         <v>20.19533303340073</v>
@@ -23064,7 +23061,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23078,7 +23075,7 @@
         <v>33.06269553801688</v>
       </c>
       <c r="D429" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E429">
         <v>20.32334207652173</v>
@@ -23114,7 +23111,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23128,7 +23125,7 @@
         <v>33.22705411164569</v>
       </c>
       <c r="D430" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E430">
         <v>20.4716916981737</v>
@@ -23164,7 +23161,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23178,7 +23175,7 @@
         <v>33.43325315348858</v>
       </c>
       <c r="D431" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E431">
         <v>20.65780641775917</v>
@@ -23214,7 +23211,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23228,7 +23225,7 @@
         <v>33.53120523654898</v>
       </c>
       <c r="D432" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E432">
         <v>20.7462177135085</v>
@@ -23264,7 +23261,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23314,7 +23311,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23328,7 +23325,7 @@
         <v>33.46421187526697</v>
       </c>
       <c r="D434" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E434">
         <v>21.58554463904314</v>
@@ -23364,7 +23361,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23414,7 +23411,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23428,7 +23425,7 @@
         <v>33.20896438389043</v>
       </c>
       <c r="D436" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E436">
         <v>21.35184401382175</v>
@@ -23464,7 +23461,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23478,7 +23475,7 @@
         <v>33.24525244457716</v>
       </c>
       <c r="D437" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E437">
         <v>21.38506879665831</v>
@@ -23528,7 +23525,7 @@
         <v>33.30754061736793</v>
       </c>
       <c r="D438" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E438">
         <v>21.44209887694077</v>
@@ -23564,7 +23561,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23614,7 +23611,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23664,7 +23661,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23714,7 +23711,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23728,7 +23725,7 @@
         <v>33.37808699058778</v>
       </c>
       <c r="D442" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E442">
         <v>21.50669003683685</v>
@@ -23764,7 +23761,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23814,7 +23811,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23864,7 +23861,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23914,7 +23911,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23928,7 +23925,7 @@
         <v>33.3491605949092</v>
       </c>
       <c r="D446" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E446">
         <v>21.48020547975453</v>
@@ -23964,7 +23961,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24014,7 +24011,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24064,7 +24061,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24114,7 +24111,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24128,7 +24125,7 @@
         <v>33.21868761846164</v>
       </c>
       <c r="D450" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E450">
         <v>21.36074645586423</v>
@@ -24164,7 +24161,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24214,7 +24211,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24264,7 +24261,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24314,7 +24311,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24364,7 +24361,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24378,7 +24375,7 @@
         <v>33.10860895395319</v>
       </c>
       <c r="D455" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E455">
         <v>21.25996014615194</v>
@@ -24414,7 +24411,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24464,7 +24461,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24514,7 +24511,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24564,7 +24561,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24578,7 +24575,7 @@
         <v>32.82858702883275</v>
       </c>
       <c r="D459" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E459">
         <v>21.00357643548973</v>
@@ -24614,7 +24611,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24728,7 +24725,7 @@
         <v>32.43391527499527</v>
       </c>
       <c r="D462" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E462">
         <v>20.64222112840476</v>
@@ -24814,7 +24811,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24828,7 +24825,7 @@
         <v>32.1976037826028</v>
       </c>
       <c r="D464" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E464">
         <v>20.42585800874672</v>
@@ -24864,7 +24861,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24878,7 +24875,7 @@
         <v>31.9359757436375</v>
       </c>
       <c r="D465" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E465">
         <v>20.18631545359018</v>
@@ -24914,7 +24911,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24928,7 +24925,7 @@
         <v>31.6928085141255</v>
       </c>
       <c r="D466" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E466">
         <v>19.96367532786815</v>
@@ -24978,7 +24975,7 @@
         <v>31.38607212722557</v>
       </c>
       <c r="D467" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E467">
         <v>19.96017071526525</v>
@@ -25014,7 +25011,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25028,7 +25025,7 @@
         <v>31.09488527318194</v>
       </c>
       <c r="D468" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E468">
         <v>19.69041319680059</v>
@@ -25078,7 +25075,7 @@
         <v>28.76090315089132</v>
       </c>
       <c r="D469" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E469">
         <v>19.57543646755398</v>
@@ -25114,7 +25111,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25128,7 +25125,7 @@
         <v>30.97077487852789</v>
       </c>
       <c r="D470" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E470">
         <v>19.57543646755398</v>
@@ -25164,7 +25161,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25178,7 +25175,7 @@
         <v>28.60148803846228</v>
       </c>
       <c r="D471" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E471">
         <v>19.42949065339434</v>
@@ -25214,7 +25211,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25228,7 +25225,7 @@
         <v>30.81323523800978</v>
       </c>
       <c r="D472" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E472">
         <v>19.42949065339434</v>
@@ -25264,7 +25261,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25278,7 +25275,7 @@
         <v>28.31621253771513</v>
       </c>
       <c r="D473" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E473">
         <v>19.16831864415417</v>
@@ -25314,7 +25311,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25328,7 +25325,7 @@
         <v>30.53131591962436</v>
       </c>
       <c r="D474" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E474">
         <v>19.16831864415417</v>
@@ -25364,7 +25361,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25378,7 +25375,7 @@
         <v>28.17117124931562</v>
       </c>
       <c r="D475" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E475">
         <v>19.16188388044775</v>
@@ -25428,7 +25425,7 @@
         <v>30.52436998310014</v>
       </c>
       <c r="D476" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E476">
         <v>19.16188388044775</v>
@@ -25478,7 +25475,7 @@
         <v>28.43299823269307</v>
       </c>
       <c r="D477" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E477">
         <v>19.40417998614624</v>
@@ -25514,7 +25511,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25528,7 +25525,7 @@
         <v>28.68381801752044</v>
       </c>
       <c r="D478" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E478">
         <v>19.6362899708081</v>
@@ -25578,7 +25575,7 @@
         <v>28.80289710513282</v>
       </c>
       <c r="D479" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E479">
         <v>19.74648640215534</v>
@@ -25614,7 +25611,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25628,7 +25625,7 @@
         <v>28.66069705648685</v>
       </c>
       <c r="D480" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E480">
         <v>19.74648640215534</v>
@@ -25664,7 +25661,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25678,7 +25675,7 @@
         <v>28.92716526228032</v>
       </c>
       <c r="D481" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E481">
         <v>19.86148482649941</v>
@@ -25714,7 +25711,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25728,7 +25725,7 @@
         <v>28.78241267851456</v>
       </c>
       <c r="D482" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E482">
         <v>19.86148482649941</v>
@@ -25764,7 +25761,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25778,7 +25775,7 @@
         <v>28.69210673371983</v>
       </c>
       <c r="D483" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E483">
         <v>19.64396039358289</v>
@@ -25814,7 +25811,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25828,7 +25825,7 @@
         <v>28.55218237918936</v>
       </c>
       <c r="D484" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E484">
         <v>19.64396039358289</v>
@@ -25864,7 +25861,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25878,7 +25875,7 @@
         <v>24.1238374281487</v>
       </c>
       <c r="D485" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E485">
         <v>15.41645928485977</v>
@@ -25914,7 +25911,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25928,7 +25925,7 @@
         <v>23.88230241564499</v>
       </c>
       <c r="D486" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E486">
         <v>15.41645928485977</v>
@@ -25964,7 +25961,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25978,7 +25975,7 @@
         <v>16.53295008901819</v>
       </c>
       <c r="D487" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E487">
         <v>8.24961705438853</v>
@@ -26028,7 +26025,7 @@
         <v>16.39809781749685</v>
       </c>
       <c r="D488" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E488">
         <v>8.24961705438853</v>
@@ -26078,7 +26075,7 @@
         <v>8.646669450447945</v>
       </c>
       <c r="D489" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E489">
         <v>0.5067815058065008</v>
@@ -26114,7 +26111,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26128,7 +26125,7 @@
         <v>11.10765720787195</v>
       </c>
       <c r="D490" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E490">
         <v>0.5067815058065008</v>
@@ -26164,7 +26161,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26178,7 +26175,7 @@
         <v>8.708207114263224</v>
       </c>
       <c r="D491" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E491">
         <v>0.5067815058065008</v>
@@ -26214,7 +26211,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26228,7 +26225,7 @@
         <v>7.091043911098566</v>
       </c>
       <c r="D492" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E492">
         <v>-0.9493259013959516</v>
@@ -26278,7 +26275,7 @@
         <v>9.494415907805923</v>
       </c>
       <c r="D493" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E493">
         <v>-0.9493259013959516</v>
@@ -26328,7 +26325,7 @@
         <v>7.115916999912343</v>
       </c>
       <c r="D494" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E494">
         <v>-0.9493259013959516</v>
@@ -26378,7 +26375,7 @@
         <v>5.65581229233937</v>
       </c>
       <c r="D495" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E495">
         <v>-2.292741355992099</v>
@@ -26414,7 +26411,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26428,7 +26425,7 @@
         <v>8.006027562426013</v>
       </c>
       <c r="D496" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E496">
         <v>-2.292741355992099</v>
@@ -26464,7 +26461,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26478,7 +26475,7 @@
         <v>5.646858373303601</v>
       </c>
       <c r="D497" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E497">
         <v>-2.292741355992099</v>
@@ -26514,7 +26511,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26528,7 +26525,7 @@
         <v>4.107061890942596</v>
       </c>
       <c r="D498" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E498">
         <v>-3.742413448882012</v>
@@ -26564,7 +26561,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26578,7 +26575,7 @@
         <v>6.399916035051582</v>
       </c>
       <c r="D499" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E499">
         <v>-3.742413448882012</v>
@@ -26614,7 +26611,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26628,7 +26625,7 @@
         <v>4.061605437193776</v>
       </c>
       <c r="D500" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E500">
         <v>-3.742413448882012</v>
@@ -26664,7 +26661,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26678,7 +26675,7 @@
         <v>3.994587595705951</v>
       </c>
       <c r="D501" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E501">
         <v>-3.847692418834157</v>
@@ -26714,7 +26711,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26728,7 +26725,7 @@
         <v>6.283276025176541</v>
       </c>
       <c r="D502" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E502">
         <v>-3.847692418834157</v>
@@ -26764,7 +26761,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26778,7 +26775,7 @@
         <v>3.94648023264179</v>
       </c>
       <c r="D503" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E503">
         <v>-3.847692418834157</v>
@@ -26814,7 +26811,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26828,7 +26825,7 @@
         <v>3.810208807303631</v>
       </c>
       <c r="D504" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E504">
         <v>-4.02027593121074</v>
@@ -26878,7 +26875,7 @@
         <v>6.092068392759323</v>
       </c>
       <c r="D505" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E505">
         <v>-4.02027593121074</v>
@@ -26928,7 +26925,7 @@
         <v>3.757755816229981</v>
       </c>
       <c r="D506" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E506">
         <v>-4.02027593121074</v>
@@ -26978,7 +26975,7 @@
         <v>3.242943955180543</v>
       </c>
       <c r="D507" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E507">
         <v>-4.551251112659287</v>
@@ -27028,7 +27025,7 @@
         <v>5.503793731298337</v>
       </c>
       <c r="D508" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E508">
         <v>-4.551251112659287</v>
@@ -27078,7 +27075,7 @@
         <v>3.177121085437328</v>
       </c>
       <c r="D509" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E509">
         <v>-4.551251112659287</v>
@@ -27128,7 +27125,7 @@
         <v>0.5276020656298783</v>
       </c>
       <c r="D510" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E510">
         <v>-7.276209063074127</v>
@@ -27164,7 +27161,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27178,7 +27175,7 @@
         <v>2.687883623616173</v>
       </c>
       <c r="D511" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E511">
         <v>-7.276209063074127</v>
@@ -27214,7 +27211,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27228,7 +27225,7 @@
         <v>0.3977812388938915</v>
       </c>
       <c r="D512" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E512">
         <v>-7.276209063074127</v>
@@ -27264,7 +27261,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27278,7 +27275,7 @@
         <v>-0.0005009764291159513</v>
       </c>
       <c r="D513" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E513">
         <v>-7.771120443679365</v>
@@ -27314,7 +27311,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27328,7 +27325,7 @@
         <v>2.140221209629061</v>
       </c>
       <c r="D514" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E514">
         <v>-7.771120443679365</v>
@@ -27364,7 +27361,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27378,7 +27375,7 @@
         <v>-0.1427686762102667</v>
       </c>
       <c r="D515" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E515">
         <v>-7.771120443679365</v>
@@ -27414,7 +27411,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27428,7 +27425,7 @@
         <v>-0.6951028983788206</v>
       </c>
       <c r="D516" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E516">
         <v>-8.422066128110345</v>
@@ -27464,7 +27461,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27478,7 +27475,7 @@
         <v>1.419893290570108</v>
       </c>
       <c r="D517" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E517">
         <v>-8.422066128110345</v>
@@ -27514,7 +27511,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27528,7 +27525,7 @@
         <v>-0.8537416872294941</v>
       </c>
       <c r="D518" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E518">
         <v>-8.422066128110345</v>
@@ -27564,7 +27561,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27578,7 +27575,7 @@
         <v>-1.098623802898558</v>
       </c>
       <c r="D519" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E519">
         <v>-8.615075478807405</v>
@@ -27614,7 +27611,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27628,7 +27625,7 @@
         <v>1.001427167364454</v>
       </c>
       <c r="D520" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E520">
         <v>-8.615075478807405</v>
@@ -27664,7 +27661,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27678,7 +27675,7 @@
         <v>-1.266773185458455</v>
       </c>
       <c r="D521" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E521">
         <v>-8.615075478807405</v>
@@ -27714,7 +27711,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27728,7 +27725,7 @@
         <v>-1.400997181997106</v>
       </c>
       <c r="D522" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E522">
         <v>-8.898105106381124</v>
@@ -27764,7 +27761,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27778,7 +27775,7 @@
         <v>0.6878547742252223</v>
       </c>
       <c r="D523" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E523">
         <v>-8.898105106381124</v>
@@ -27814,7 +27811,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27828,7 +27825,7 @@
         <v>-1.576273209855614</v>
       </c>
       <c r="D524" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E524">
         <v>-8.898105106381124</v>
@@ -27864,7 +27861,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27878,7 +27875,7 @@
         <v>-1.724593447066837</v>
       </c>
       <c r="D525" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E525">
         <v>-9.200999926884109</v>
@@ -27914,7 +27911,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27928,7 +27925,7 @@
         <v>0.3522734623010564</v>
       </c>
       <c r="D526" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E526">
         <v>-9.200999926884109</v>
@@ -27964,7 +27961,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27978,7 +27975,7 @@
         <v>-1.907496322923627</v>
       </c>
       <c r="D527" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E527">
         <v>-9.200999926884109</v>
@@ -28014,7 +28011,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28028,7 +28025,7 @@
         <v>44.86204822710516</v>
       </c>
       <c r="D528" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E528">
         <v>35.52043652295812</v>
@@ -28064,7 +28061,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28078,7 +28075,7 @@
         <v>46.13402290259216</v>
       </c>
       <c r="D529" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E529">
         <v>36.69877772856216</v>
@@ -28114,7 +28111,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28128,7 +28125,7 @@
         <v>46.08362925847739</v>
       </c>
       <c r="D530" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E530">
         <v>36.69877772856216</v>
@@ -28164,7 +28161,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28178,7 +28175,7 @@
         <v>45.05397872766954</v>
       </c>
       <c r="D531" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E531">
         <v>35.69823850422841</v>
@@ -28214,7 +28211,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28228,7 +28225,7 @@
         <v>44.98156832800709</v>
       </c>
       <c r="D532" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E532">
         <v>35.69823850422841</v>
@@ -28264,7 +28261,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28278,7 +28275,7 @@
         <v>42.5821201676108</v>
       </c>
       <c r="D533" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E533">
         <v>33.77379366345071</v>
@@ -28314,7 +28311,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28328,7 +28325,7 @@
         <v>42.55551239448888</v>
       </c>
       <c r="D534" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E534">
         <v>33.77379366345071</v>
@@ -28364,7 +28361,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28378,7 +28375,7 @@
         <v>42.86185585668593</v>
       </c>
       <c r="D535" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E535">
         <v>33.77379366345071</v>
@@ -28414,7 +28411,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28428,7 +28425,7 @@
         <v>9.729438161046986</v>
       </c>
       <c r="D536" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E536">
         <v>4.60825443961048</v>
@@ -28464,7 +28461,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28478,7 +28475,7 @@
         <v>7.54859977610915</v>
       </c>
       <c r="D537" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E537">
         <v>2.585662830903956</v>
@@ -28514,57 +28511,57 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B538" t="s">
         <v>93</v>
       </c>
       <c r="C538">
-        <v>-18.42145712811057</v>
+        <v>-0.1707707281713766</v>
       </c>
       <c r="D538" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E538">
-        <v>-19.30431939193691</v>
+        <v>4.928669866220837</v>
       </c>
       <c r="F538">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G538">
-        <v>0.07542145712811058</v>
+        <v>0.06233077072817137</v>
       </c>
       <c r="H538">
-        <v>0.07660431939193692</v>
+        <v>0.06597133013377916</v>
       </c>
       <c r="I538">
-        <v>0.8828622638263326</v>
+        <v>5.099440594392213</v>
       </c>
       <c r="J538">
-        <v>3.688793799379762</v>
+        <v>1.919580511558438</v>
       </c>
       <c r="K538">
-        <v>12.72</v>
+        <v>16.28</v>
       </c>
       <c r="L538">
-        <v>28.5</v>
+        <v>31.08</v>
       </c>
       <c r="M538">
-        <v>13</v>
+        <v>15.9</v>
       </c>
       <c r="N538">
-        <v>28.65</v>
+        <v>35.45</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28572,31 +28569,31 @@
         <v>0</v>
       </c>
       <c r="B539" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C539">
-        <v>-20.96449736029645</v>
+        <v>-18.42145712811057</v>
       </c>
       <c r="D539" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E539">
-        <v>-21.90333849715832</v>
+        <v>-19.01718165576324</v>
       </c>
       <c r="F539">
         <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.07796449736029645</v>
+        <v>0.07542145712811058</v>
       </c>
       <c r="H539">
-        <v>0.07920333849715831</v>
+        <v>0.07895718165576324</v>
       </c>
       <c r="I539">
-        <v>0.9388411368618677</v>
+        <v>0.5957245276526635</v>
       </c>
       <c r="J539">
-        <v>3.888718345935255</v>
+        <v>3.688793799379762</v>
       </c>
       <c r="K539">
         <v>12.72</v>
@@ -28605,16 +28602,16 @@
         <v>28.5</v>
       </c>
       <c r="M539">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N539">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28622,31 +28619,31 @@
         <v>0</v>
       </c>
       <c r="B540" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C540">
-        <v>-22.26553261458488</v>
+        <v>-20.96449736029645</v>
       </c>
       <c r="D540" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E540">
-        <v>-23.23301289226442</v>
+        <v>-21.67217963402018</v>
       </c>
       <c r="F540">
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.07926553261458488</v>
+        <v>0.07796449736029645</v>
       </c>
       <c r="H540">
-        <v>0.08053301289226443</v>
+        <v>0.08161217963402018</v>
       </c>
       <c r="I540">
-        <v>0.9674802776795417</v>
+        <v>0.7076822737237336</v>
       </c>
       <c r="J540">
-        <v>3.991000991712648</v>
+        <v>3.888718345935255</v>
       </c>
       <c r="K540">
         <v>12.72</v>
@@ -28655,16 +28652,16 @@
         <v>28.5</v>
       </c>
       <c r="M540">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N540">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O540">
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28672,31 +28669,31 @@
         <v>0</v>
       </c>
       <c r="B541" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C541">
-        <v>-23.39064064612373</v>
+        <v>-22.26553261458488</v>
       </c>
       <c r="D541" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E541">
-        <v>-24.38288745279941</v>
+        <v>-23.03049316994396</v>
       </c>
       <c r="F541">
         <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.08039064064612372</v>
+        <v>0.07926553261458488</v>
       </c>
       <c r="H541">
-        <v>0.0816828874527994</v>
+        <v>0.08297049316994395</v>
       </c>
       <c r="I541">
-        <v>0.9922468066756807</v>
+        <v>0.7649605553590817</v>
       </c>
       <c r="J541">
-        <v>4.07945288098457</v>
+        <v>3.991000991712648</v>
       </c>
       <c r="K541">
         <v>12.72</v>
@@ -28705,16 +28702,16 @@
         <v>28.5</v>
       </c>
       <c r="M541">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N541">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28722,31 +28719,31 @@
         <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C542">
-        <v>-24.9776650997016</v>
+        <v>-23.39064064612373</v>
       </c>
       <c r="D542" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E542">
-        <v>-26.00484640692774</v>
+        <v>-24.20513425947508</v>
       </c>
       <c r="F542">
         <v>-1</v>
       </c>
       <c r="G542">
-        <v>0.0819776650997016</v>
+        <v>0.08039064064612372</v>
       </c>
       <c r="H542">
-        <v>0.08330484640692774</v>
+        <v>0.08414513425947508</v>
       </c>
       <c r="I542">
-        <v>1.027181307226137</v>
+        <v>0.8144936133513525</v>
       </c>
       <c r="J542">
-        <v>4.204218954379057</v>
+        <v>4.07945288098457</v>
       </c>
       <c r="K542">
         <v>12.72</v>
@@ -28755,16 +28752,16 @@
         <v>28.5</v>
       </c>
       <c r="M542">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N542">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28772,31 +28769,31 @@
         <v>0</v>
       </c>
       <c r="B543" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C543">
-        <v>-27.00589345076202</v>
+        <v>-24.9776650997016</v>
       </c>
       <c r="D543" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E543">
-        <v>-28.07772129401778</v>
+        <v>-25.86202771415387</v>
       </c>
       <c r="F543">
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.08400589345076202</v>
+        <v>0.0819776650997016</v>
       </c>
       <c r="H543">
-        <v>0.08537772129401779</v>
+        <v>0.08580202771415386</v>
       </c>
       <c r="I543">
-        <v>1.071827843255768</v>
+        <v>0.8843626144522645</v>
       </c>
       <c r="J543">
-        <v>4.363670868770599</v>
+        <v>4.204218954379057</v>
       </c>
       <c r="K543">
         <v>12.72</v>
@@ -28805,16 +28802,16 @@
         <v>28.5</v>
       </c>
       <c r="M543">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N543">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28822,31 +28819,31 @@
         <v>0</v>
       </c>
       <c r="B544" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C544">
-        <v>-29.1656717820026</v>
+        <v>-27.00589345076202</v>
       </c>
       <c r="D544" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E544">
-        <v>-30.2850419155687</v>
+        <v>-27.97954913727354</v>
       </c>
       <c r="F544">
         <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.0861656717820026</v>
+        <v>0.08400589345076202</v>
       </c>
       <c r="H544">
-        <v>0.08758504191556869</v>
+        <v>0.08791954913727355</v>
       </c>
       <c r="I544">
-        <v>1.119370133566093</v>
+        <v>0.9736556865115276</v>
       </c>
       <c r="J544">
-        <v>4.533464762736053</v>
+        <v>4.363670868770599</v>
       </c>
       <c r="K544">
         <v>12.72</v>
@@ -28855,16 +28852,16 @@
         <v>28.5</v>
       </c>
       <c r="M544">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N544">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28872,31 +28869,31 @@
         <v>0</v>
       </c>
       <c r="B545" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C545">
-        <v>-29.94151334120067</v>
+        <v>-29.1656717820026</v>
       </c>
       <c r="D545" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E545">
-        <v>-31.07796174808244</v>
+        <v>-30.23441204913479</v>
       </c>
       <c r="F545">
         <v>-1</v>
       </c>
       <c r="G545">
-        <v>0.08694151334120068</v>
+        <v>0.0861656717820026</v>
       </c>
       <c r="H545">
-        <v>0.08837796174808245</v>
+        <v>0.09017441204913479</v>
       </c>
       <c r="I545">
-        <v>1.136448406881776</v>
+        <v>1.068740267132185</v>
       </c>
       <c r="J545">
-        <v>4.594458596006342</v>
+        <v>4.533464762736053</v>
       </c>
       <c r="K545">
         <v>12.72</v>
@@ -28905,16 +28902,16 @@
         <v>28.5</v>
       </c>
       <c r="M545">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N545">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28922,31 +28919,31 @@
         <v>0</v>
       </c>
       <c r="B546" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C546">
-        <v>-30.43493588680277</v>
+        <v>-29.94151334120067</v>
       </c>
       <c r="D546" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E546">
-        <v>-31.58224579626069</v>
+        <v>-31.04441015496421</v>
       </c>
       <c r="F546">
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.08743493588680278</v>
+        <v>0.08694151334120068</v>
       </c>
       <c r="H546">
-        <v>0.08888224579626069</v>
+        <v>0.09098441015496421</v>
       </c>
       <c r="I546">
-        <v>1.147309909457924</v>
+        <v>1.102896813763543</v>
       </c>
       <c r="J546">
-        <v>4.633249676635438</v>
+        <v>4.594458596006342</v>
       </c>
       <c r="K546">
         <v>12.72</v>
@@ -28955,16 +28952,16 @@
         <v>28.5</v>
       </c>
       <c r="M546">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N546">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>92</v>
+        <v>416</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28972,31 +28969,31 @@
         <v>0</v>
       </c>
       <c r="B547" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C547">
-        <v>-30.74429722076099</v>
+        <v>-30.43493588680277</v>
       </c>
       <c r="D547" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E547">
-        <v>-31.89841697090353</v>
+        <v>-31.55955570571861</v>
       </c>
       <c r="F547">
         <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.08774429722076099</v>
+        <v>0.08743493588680278</v>
       </c>
       <c r="H547">
-        <v>0.08919841697090353</v>
+        <v>0.0914995557057186</v>
       </c>
       <c r="I547">
-        <v>1.154119750142534</v>
+        <v>1.124619818915839</v>
       </c>
       <c r="J547">
-        <v>4.657570536223348</v>
+        <v>4.633249676635438</v>
       </c>
       <c r="K547">
         <v>12.72</v>
@@ -29005,16 +29002,16 @@
         <v>28.5</v>
       </c>
       <c r="M547">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N547">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>415</v>
+        <v>92</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29022,31 +29019,31 @@
         <v>0</v>
       </c>
       <c r="B548" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C548">
-        <v>-31.20320959343522</v>
+        <v>-30.74429722076099</v>
       </c>
       <c r="D548" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E548">
-        <v>-32.36743118825926</v>
+        <v>-31.88253672104606</v>
       </c>
       <c r="F548">
         <v>-1</v>
       </c>
       <c r="G548">
-        <v>0.08820320959343522</v>
+        <v>0.08774429722076099</v>
       </c>
       <c r="H548">
-        <v>0.08966743118825926</v>
+        <v>0.09182253672104605</v>
       </c>
       <c r="I548">
-        <v>1.164221594824042</v>
+        <v>1.138239500285067</v>
       </c>
       <c r="J548">
-        <v>4.69364855294302</v>
+        <v>4.657570536223348</v>
       </c>
       <c r="K548">
         <v>12.72</v>
@@ -29055,16 +29052,16 @@
         <v>28.5</v>
       </c>
       <c r="M548">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N548">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29072,31 +29069,31 @@
         <v>0</v>
       </c>
       <c r="B549" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C549">
-        <v>-31.07605732463613</v>
+        <v>-31.20320959343522</v>
       </c>
       <c r="D549" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E549">
-        <v>-32.23747997014699</v>
+        <v>-32.3616527830833</v>
       </c>
       <c r="F549">
         <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.08807605732463614</v>
+        <v>0.08820320959343522</v>
       </c>
       <c r="H549">
-        <v>0.08953747997014699</v>
+        <v>0.0923016527830833</v>
       </c>
       <c r="I549">
-        <v>1.161422645510861</v>
+        <v>1.158443189648082</v>
       </c>
       <c r="J549">
-        <v>4.683652305395922</v>
+        <v>4.69364855294302</v>
       </c>
       <c r="K549">
         <v>12.72</v>
@@ -29105,16 +29102,16 @@
         <v>28.5</v>
       </c>
       <c r="M549">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N549">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O549">
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29122,31 +29119,31 @@
         <v>0</v>
       </c>
       <c r="B550" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C550">
-        <v>-30.25066173781194</v>
+        <v>-31.07605732463613</v>
       </c>
       <c r="D550" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E550">
-        <v>-31.39391529807823</v>
+        <v>-32.22890261565784</v>
       </c>
       <c r="F550">
         <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.08725066173781194</v>
+        <v>0.08807605732463614</v>
       </c>
       <c r="H550">
-        <v>0.08869391529807823</v>
+        <v>0.09216890261565784</v>
       </c>
       <c r="I550">
-        <v>1.143253560266295</v>
+        <v>1.152845291021713</v>
       </c>
       <c r="J550">
-        <v>4.618762715236787</v>
+        <v>4.683652305395922</v>
       </c>
       <c r="K550">
         <v>12.72</v>
@@ -29155,16 +29152,16 @@
         <v>28.5</v>
       </c>
       <c r="M550">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N550">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29172,31 +29169,31 @@
         <v>0</v>
       </c>
       <c r="B551" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C551">
-        <v>-28.48555321698337</v>
+        <v>-30.25066173781194</v>
       </c>
       <c r="D551" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E551">
-        <v>-29.58995218716854</v>
+        <v>-31.36716885834453</v>
       </c>
       <c r="F551">
         <v>-1</v>
       </c>
       <c r="G551">
-        <v>0.08548555321698337</v>
+        <v>0.08725066173781194</v>
       </c>
       <c r="H551">
-        <v>0.08688995218716854</v>
+        <v>0.09130716885834454</v>
       </c>
       <c r="I551">
-        <v>1.104398970185166</v>
+        <v>1.116507120532596</v>
       </c>
       <c r="J551">
-        <v>4.479996322089887</v>
+        <v>4.618762715236787</v>
       </c>
       <c r="K551">
         <v>12.72</v>
@@ -29205,16 +29202,16 @@
         <v>28.5</v>
       </c>
       <c r="M551">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N551">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29222,31 +29219,31 @@
         <v>0</v>
       </c>
       <c r="B552" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C552">
-        <v>-28.69349087972021</v>
+        <v>-28.48555321698337</v>
       </c>
       <c r="D552" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E552">
-        <v>-29.80246709405367</v>
+        <v>-29.5243511573537</v>
       </c>
       <c r="F552">
         <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.0856934908797202</v>
+        <v>0.08548555321698337</v>
       </c>
       <c r="H552">
-        <v>0.08710246709405367</v>
+        <v>0.0894643511573537</v>
       </c>
       <c r="I552">
-        <v>1.10897621433346</v>
+        <v>1.03879794037033</v>
       </c>
       <c r="J552">
-        <v>4.496343622619513</v>
+        <v>4.479996322089887</v>
       </c>
       <c r="K552">
         <v>12.72</v>
@@ -29255,16 +29252,16 @@
         <v>28.5</v>
       </c>
       <c r="M552">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N552">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O552">
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29272,31 +29269,31 @@
         <v>0</v>
       </c>
       <c r="B553" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C553">
-        <v>-28.72399400585454</v>
+        <v>-28.69349087972021</v>
       </c>
       <c r="D553" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E553">
-        <v>-29.83364167265007</v>
+        <v>-29.74144330838713</v>
       </c>
       <c r="F553">
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.08572399400585454</v>
+        <v>0.0856934908797202</v>
       </c>
       <c r="H553">
-        <v>0.08713364167265007</v>
+        <v>0.08968144330838712</v>
       </c>
       <c r="I553">
-        <v>1.109647666795539</v>
+        <v>1.047952428666918</v>
       </c>
       <c r="J553">
-        <v>4.498741667126929</v>
+        <v>4.496343622619513</v>
       </c>
       <c r="K553">
         <v>12.72</v>
@@ -29305,16 +29302,16 @@
         <v>28.5</v>
       </c>
       <c r="M553">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N553">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O553">
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29322,31 +29319,31 @@
         <v>0</v>
       </c>
       <c r="B554" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C554">
-        <v>-29.04997068031175</v>
+        <v>-28.72399400585454</v>
       </c>
       <c r="D554" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E554">
-        <v>-30.16679393428088</v>
+        <v>-29.77328933944561</v>
       </c>
       <c r="F554">
         <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.08604997068031175</v>
+        <v>0.08572399400585454</v>
       </c>
       <c r="H554">
-        <v>0.08746679393428088</v>
+        <v>0.08971328933944561</v>
       </c>
       <c r="I554">
-        <v>1.116823253969123</v>
+        <v>1.049295333591076</v>
       </c>
       <c r="J554">
-        <v>4.524368764175452</v>
+        <v>4.498741667126929</v>
       </c>
       <c r="K554">
         <v>12.72</v>
@@ -29355,16 +29352,16 @@
         <v>28.5</v>
       </c>
       <c r="M554">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N554">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O554">
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29372,31 +29369,31 @@
         <v>0</v>
       </c>
       <c r="B555" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C555">
-        <v>-29.43168959025828</v>
+        <v>-29.04997068031175</v>
       </c>
       <c r="D555" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E555">
-        <v>-30.55691546174195</v>
+        <v>-30.11361718825</v>
       </c>
       <c r="F555">
         <v>-1</v>
       </c>
       <c r="G555">
-        <v>0.08643168959025829</v>
+        <v>0.08604997068031175</v>
       </c>
       <c r="H555">
-        <v>0.08785691546174194</v>
+        <v>0.09005361718825</v>
       </c>
       <c r="I555">
-        <v>1.125225871483671</v>
+        <v>1.063646507938245</v>
       </c>
       <c r="J555">
-        <v>4.554378112441689</v>
+        <v>4.524368764175452</v>
       </c>
       <c r="K555">
         <v>12.72</v>
@@ -29405,16 +29402,16 @@
         <v>28.5</v>
       </c>
       <c r="M555">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N555">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O555">
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29422,31 +29419,31 @@
         <v>0</v>
       </c>
       <c r="B556" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C556">
-        <v>-30.72131869184545</v>
+        <v>-29.43168959025828</v>
       </c>
       <c r="D556" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E556">
-        <v>-31.87493262531374</v>
+        <v>-30.51214133322562</v>
       </c>
       <c r="F556">
         <v>-1</v>
       </c>
       <c r="G556">
-        <v>0.08772131869184546</v>
+        <v>0.08643168959025829</v>
       </c>
       <c r="H556">
-        <v>0.08917493262531374</v>
+        <v>0.09045214133322563</v>
       </c>
       <c r="I556">
-        <v>1.153613933468293</v>
+        <v>1.080451742967341</v>
       </c>
       <c r="J556">
-        <v>4.655764048101057</v>
+        <v>4.554378112441689</v>
       </c>
       <c r="K556">
         <v>12.72</v>
@@ -29455,16 +29452,16 @@
         <v>28.5</v>
       </c>
       <c r="M556">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N556">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O556">
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -29472,31 +29469,31 @@
         <v>0</v>
       </c>
       <c r="B557" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C557">
-        <v>-32.3547496665294</v>
+        <v>-30.72131869184545</v>
       </c>
       <c r="D557" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E557">
-        <v>-33.54431962774231</v>
+        <v>-31.85854655878203</v>
       </c>
       <c r="F557">
         <v>-1</v>
       </c>
       <c r="G557">
-        <v>0.0893547496665294</v>
+        <v>0.08772131869184546</v>
       </c>
       <c r="H557">
-        <v>0.09084431962774231</v>
+        <v>0.09179854655878203</v>
       </c>
       <c r="I557">
-        <v>1.189569961212911</v>
+        <v>1.137227866936584</v>
       </c>
       <c r="J557">
-        <v>4.784178432903254</v>
+        <v>4.655764048101057</v>
       </c>
       <c r="K557">
         <v>12.72</v>
@@ -29505,16 +29502,16 @@
         <v>28.5</v>
       </c>
       <c r="M557">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N557">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O557">
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -29522,31 +29519,31 @@
         <v>0</v>
       </c>
       <c r="B558" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C558">
-        <v>-33.15849324376438</v>
+        <v>-32.3547496665294</v>
       </c>
       <c r="D558" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E558">
-        <v>-34.36575567365856</v>
+        <v>-33.56388958895521</v>
       </c>
       <c r="F558">
         <v>-1</v>
       </c>
       <c r="G558">
-        <v>0.09015849324376439</v>
+        <v>0.0893547496665294</v>
       </c>
       <c r="H558">
-        <v>0.09166575567365857</v>
+        <v>0.09350388958895522</v>
       </c>
       <c r="I558">
-        <v>1.207262429894186</v>
+        <v>1.209139922425813</v>
       </c>
       <c r="J558">
-        <v>4.847365821050658</v>
+        <v>4.784178432903254</v>
       </c>
       <c r="K558">
         <v>12.72</v>
@@ -29555,16 +29552,16 @@
         <v>28.5</v>
       </c>
       <c r="M558">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N558">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O558">
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -29572,31 +29569,31 @@
         <v>0</v>
       </c>
       <c r="B559" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C559">
-        <v>-34.25698087216963</v>
+        <v>-33.15849324376438</v>
       </c>
       <c r="D559" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E559">
-        <v>-35.48842384734316</v>
+        <v>-34.40301810355274</v>
       </c>
       <c r="F559">
         <v>-1</v>
       </c>
       <c r="G559">
-        <v>0.09125698087216964</v>
+        <v>0.09015849324376439</v>
       </c>
       <c r="H559">
-        <v>0.09278842384734315</v>
+        <v>0.09434301810355274</v>
       </c>
       <c r="I559">
-        <v>1.231442975173536</v>
+        <v>1.244524859788363</v>
       </c>
       <c r="J559">
-        <v>4.93372491133409</v>
+        <v>4.847365821050658</v>
       </c>
       <c r="K559">
         <v>12.72</v>
@@ -29605,16 +29602,16 @@
         <v>28.5</v>
       </c>
       <c r="M559">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N559">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O559">
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -29622,31 +29619,31 @@
         <v>0</v>
       </c>
       <c r="B560" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C560">
-        <v>-35.16617096130667</v>
+        <v>-34.25698087216963</v>
       </c>
       <c r="D560" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E560">
-        <v>-36.41762755479454</v>
+        <v>-35.54986682251671</v>
       </c>
       <c r="F560">
         <v>-1</v>
       </c>
       <c r="G560">
-        <v>0.09216617096130668</v>
+        <v>0.09125698087216964</v>
       </c>
       <c r="H560">
-        <v>0.09371762755479456</v>
+        <v>0.0954898668225167</v>
       </c>
       <c r="I560">
-        <v>1.251456593487873</v>
+        <v>1.292885950347078</v>
       </c>
       <c r="J560">
-        <v>5.005202119599581</v>
+        <v>4.93372491133409</v>
       </c>
       <c r="K560">
         <v>12.72</v>
@@ -29655,16 +29652,16 @@
         <v>28.5</v>
       </c>
       <c r="M560">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N560">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O560">
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>203</v>
+        <v>429</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -29672,31 +29669,31 @@
         <v>0</v>
       </c>
       <c r="B561" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C561">
-        <v>-35.90561619919141</v>
+        <v>-35.16617096130667</v>
       </c>
       <c r="D561" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E561">
-        <v>-37.17334988911072</v>
+        <v>-36.49908414828244</v>
       </c>
       <c r="F561">
         <v>-1</v>
       </c>
       <c r="G561">
-        <v>0.09290561619919141</v>
+        <v>0.09216617096130668</v>
       </c>
       <c r="H561">
-        <v>0.09447334988911073</v>
+        <v>0.09643908414828244</v>
       </c>
       <c r="I561">
-        <v>1.267733689919304</v>
+        <v>1.332913186975766</v>
       </c>
       <c r="J561">
-        <v>5.063334606854671</v>
+        <v>5.005202119599581</v>
       </c>
       <c r="K561">
         <v>12.72</v>
@@ -29705,16 +29702,16 @@
         <v>28.5</v>
       </c>
       <c r="M561">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N561">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O561">
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>428</v>
+        <v>204</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -29722,31 +29719,31 @@
         <v>0</v>
       </c>
       <c r="B562" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C562">
-        <v>-36.18997893562975</v>
+        <v>-35.90561619919141</v>
       </c>
       <c r="D562" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E562">
-        <v>-37.46397218264047</v>
+        <v>-37.27108357903002</v>
       </c>
       <c r="F562">
         <v>-1</v>
       </c>
       <c r="G562">
-        <v>0.09318997893562976</v>
+        <v>0.09290561619919141</v>
       </c>
       <c r="H562">
-        <v>0.09476397218264046</v>
+        <v>0.09721108357903002</v>
       </c>
       <c r="I562">
-        <v>1.273993247010715</v>
+        <v>1.365467379838606</v>
       </c>
       <c r="J562">
-        <v>5.085690167895421</v>
+        <v>5.063334606854671</v>
       </c>
       <c r="K562">
         <v>12.72</v>
@@ -29755,116 +29752,16 @@
         <v>28.5</v>
       </c>
       <c r="M562">
-        <v>13</v>
+        <v>13.28</v>
       </c>
       <c r="N562">
-        <v>28.65</v>
+        <v>29.97</v>
       </c>
       <c r="O562">
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="563" spans="1:16">
-      <c r="A563" s="1">
-        <v>0</v>
-      </c>
-      <c r="B563" t="s">
-        <v>93</v>
-      </c>
-      <c r="C563">
-        <v>-36.79440237149454</v>
-      </c>
-      <c r="D563" t="s">
-        <v>204</v>
-      </c>
-      <c r="E563">
-        <v>-38.0817005369048</v>
-      </c>
-      <c r="F563">
-        <v>-1</v>
-      </c>
-      <c r="G563">
-        <v>0.09379440237149454</v>
-      </c>
-      <c r="H563">
-        <v>0.09538170053690478</v>
-      </c>
-      <c r="I563">
-        <v>1.287298165410256</v>
-      </c>
-      <c r="J563">
-        <v>5.133207733608061</v>
-      </c>
-      <c r="K563">
-        <v>12.72</v>
-      </c>
-      <c r="L563">
-        <v>28.5</v>
-      </c>
-      <c r="M563">
-        <v>13</v>
-      </c>
-      <c r="N563">
-        <v>28.65</v>
-      </c>
-      <c r="O563">
-        <v>1</v>
-      </c>
-      <c r="P563" t="s">
         <v>430</v>
-      </c>
-    </row>
-    <row r="564" spans="1:16">
-      <c r="A564" s="1">
-        <v>0</v>
-      </c>
-      <c r="B564" t="s">
-        <v>93</v>
-      </c>
-      <c r="C564">
-        <v>-36.55608045442354</v>
-      </c>
-      <c r="D564" t="s">
-        <v>204</v>
-      </c>
-      <c r="E564">
-        <v>-37.83813253989826</v>
-      </c>
-      <c r="F564">
-        <v>-1</v>
-      </c>
-      <c r="G564">
-        <v>0.09355608045442354</v>
-      </c>
-      <c r="H564">
-        <v>0.09513813253989827</v>
-      </c>
-      <c r="I564">
-        <v>1.282052085474724</v>
-      </c>
-      <c r="J564">
-        <v>5.114471733838328</v>
-      </c>
-      <c r="K564">
-        <v>12.72</v>
-      </c>
-      <c r="L564">
-        <v>28.5</v>
-      </c>
-      <c r="M564">
-        <v>13</v>
-      </c>
-      <c r="N564">
-        <v>28.65</v>
-      </c>
-      <c r="O564">
-        <v>1</v>
-      </c>
-      <c r="P564" t="s">
-        <v>431</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="422">
   <si>
     <t>trade_time</t>
   </si>
@@ -634,7 +634,7 @@
     <t>2021-05-14</t>
   </si>
   <si>
-    <t>2021-08-18</t>
+    <t>2021-08-19</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1243,9 +1243,6 @@
     <t>2020-12-18</t>
   </si>
   <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
     <t>2021-01-06</t>
   </si>
   <si>
@@ -1283,30 +1280,6 @@
   </si>
   <si>
     <t>2021-01-25</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
   </si>
 </sst>
 </file>
@@ -1664,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P562"/>
+  <dimension ref="A1:P552"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28572,28 +28545,28 @@
         <v>94</v>
       </c>
       <c r="C539">
-        <v>-18.42145712811057</v>
+        <v>-20.96449736029645</v>
       </c>
       <c r="D539" t="s">
         <v>206</v>
       </c>
       <c r="E539">
-        <v>-19.01718165576324</v>
+        <v>-21.0922410294835</v>
       </c>
       <c r="F539">
         <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.07542145712811058</v>
+        <v>0.07796449736029645</v>
       </c>
       <c r="H539">
-        <v>0.07895718165576324</v>
+        <v>0.0793922410294835</v>
       </c>
       <c r="I539">
-        <v>0.5957245276526635</v>
+        <v>0.1277436691870477</v>
       </c>
       <c r="J539">
-        <v>3.688793799379762</v>
+        <v>3.888718345935255</v>
       </c>
       <c r="K539">
         <v>12.72</v>
@@ -28602,10 +28575,10 @@
         <v>28.5</v>
       </c>
       <c r="M539">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N539">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28622,28 +28595,28 @@
         <v>94</v>
       </c>
       <c r="C540">
-        <v>-20.96449736029645</v>
+        <v>-22.26553261458488</v>
       </c>
       <c r="D540" t="s">
         <v>206</v>
       </c>
       <c r="E540">
-        <v>-21.67217963402018</v>
+        <v>-22.41373281292741</v>
       </c>
       <c r="F540">
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.07796449736029645</v>
+        <v>0.07926553261458488</v>
       </c>
       <c r="H540">
-        <v>0.08161217963402018</v>
+        <v>0.0807137328129274</v>
       </c>
       <c r="I540">
-        <v>0.7076822737237336</v>
+        <v>0.1482001983425292</v>
       </c>
       <c r="J540">
-        <v>3.888718345935255</v>
+        <v>3.991000991712648</v>
       </c>
       <c r="K540">
         <v>12.72</v>
@@ -28652,10 +28625,10 @@
         <v>28.5</v>
       </c>
       <c r="M540">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N540">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28672,28 +28645,28 @@
         <v>94</v>
       </c>
       <c r="C541">
-        <v>-22.26553261458488</v>
+        <v>-23.39064064612373</v>
       </c>
       <c r="D541" t="s">
         <v>206</v>
       </c>
       <c r="E541">
-        <v>-23.03049316994396</v>
+        <v>-23.55653122232064</v>
       </c>
       <c r="F541">
         <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.07926553261458488</v>
+        <v>0.08039064064612372</v>
       </c>
       <c r="H541">
-        <v>0.08297049316994395</v>
+        <v>0.08185653122232064</v>
       </c>
       <c r="I541">
-        <v>0.7649605553590817</v>
+        <v>0.1658905761969152</v>
       </c>
       <c r="J541">
-        <v>3.991000991712648</v>
+        <v>4.07945288098457</v>
       </c>
       <c r="K541">
         <v>12.72</v>
@@ -28702,10 +28675,10 @@
         <v>28.5</v>
       </c>
       <c r="M541">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N541">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28722,28 +28695,28 @@
         <v>94</v>
       </c>
       <c r="C542">
-        <v>-23.39064064612373</v>
+        <v>-24.9776650997016</v>
       </c>
       <c r="D542" t="s">
         <v>206</v>
       </c>
       <c r="E542">
-        <v>-24.20513425947508</v>
+        <v>-25.16850889057741</v>
       </c>
       <c r="F542">
         <v>-1</v>
       </c>
       <c r="G542">
-        <v>0.08039064064612372</v>
+        <v>0.0819776650997016</v>
       </c>
       <c r="H542">
-        <v>0.08414513425947508</v>
+        <v>0.08346850889057741</v>
       </c>
       <c r="I542">
-        <v>0.8144936133513525</v>
+        <v>0.1908437908758103</v>
       </c>
       <c r="J542">
-        <v>4.07945288098457</v>
+        <v>4.204218954379057</v>
       </c>
       <c r="K542">
         <v>12.72</v>
@@ -28752,10 +28725,10 @@
         <v>28.5</v>
       </c>
       <c r="M542">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N542">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28772,28 +28745,28 @@
         <v>94</v>
       </c>
       <c r="C543">
-        <v>-24.9776650997016</v>
+        <v>-27.00589345076202</v>
       </c>
       <c r="D543" t="s">
         <v>206</v>
       </c>
       <c r="E543">
-        <v>-25.86202771415387</v>
+        <v>-27.22862762451614</v>
       </c>
       <c r="F543">
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.0819776650997016</v>
+        <v>0.08400589345076202</v>
       </c>
       <c r="H543">
-        <v>0.08580202771415386</v>
+        <v>0.08552862762451613</v>
       </c>
       <c r="I543">
-        <v>0.8843626144522645</v>
+        <v>0.2227341737541195</v>
       </c>
       <c r="J543">
-        <v>4.204218954379057</v>
+        <v>4.363670868770599</v>
       </c>
       <c r="K543">
         <v>12.72</v>
@@ -28802,10 +28775,10 @@
         <v>28.5</v>
       </c>
       <c r="M543">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N543">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28822,28 +28795,28 @@
         <v>94</v>
       </c>
       <c r="C544">
-        <v>-27.00589345076202</v>
+        <v>-29.1656717820026</v>
       </c>
       <c r="D544" t="s">
         <v>206</v>
       </c>
       <c r="E544">
-        <v>-27.97954913727354</v>
+        <v>-29.42236473454981</v>
       </c>
       <c r="F544">
         <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.08400589345076202</v>
+        <v>0.0861656717820026</v>
       </c>
       <c r="H544">
-        <v>0.08791954913727355</v>
+        <v>0.08772236473454982</v>
       </c>
       <c r="I544">
-        <v>0.9736556865115276</v>
+        <v>0.2566929525472048</v>
       </c>
       <c r="J544">
-        <v>4.363670868770599</v>
+        <v>4.533464762736053</v>
       </c>
       <c r="K544">
         <v>12.72</v>
@@ -28852,10 +28825,10 @@
         <v>28.5</v>
       </c>
       <c r="M544">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N544">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28872,28 +28845,28 @@
         <v>94</v>
       </c>
       <c r="C545">
-        <v>-29.1656717820026</v>
+        <v>-29.94151334120067</v>
       </c>
       <c r="D545" t="s">
         <v>206</v>
       </c>
       <c r="E545">
-        <v>-30.23441204913479</v>
+        <v>-30.21040506040193</v>
       </c>
       <c r="F545">
         <v>-1</v>
       </c>
       <c r="G545">
-        <v>0.0861656717820026</v>
+        <v>0.08694151334120068</v>
       </c>
       <c r="H545">
-        <v>0.09017441204913479</v>
+        <v>0.08851040506040192</v>
       </c>
       <c r="I545">
-        <v>1.068740267132185</v>
+        <v>0.2688917192012639</v>
       </c>
       <c r="J545">
-        <v>4.533464762736053</v>
+        <v>4.594458596006342</v>
       </c>
       <c r="K545">
         <v>12.72</v>
@@ -28902,10 +28875,10 @@
         <v>28.5</v>
       </c>
       <c r="M545">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N545">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28922,28 +28895,28 @@
         <v>94</v>
       </c>
       <c r="C546">
-        <v>-29.94151334120067</v>
+        <v>-30.43493588680277</v>
       </c>
       <c r="D546" t="s">
         <v>206</v>
       </c>
       <c r="E546">
-        <v>-31.04441015496421</v>
+        <v>-30.71158582212986</v>
       </c>
       <c r="F546">
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.08694151334120068</v>
+        <v>0.08743493588680278</v>
       </c>
       <c r="H546">
-        <v>0.09098441015496421</v>
+        <v>0.08901158582212985</v>
       </c>
       <c r="I546">
-        <v>1.102896813763543</v>
+        <v>0.2766499353270859</v>
       </c>
       <c r="J546">
-        <v>4.594458596006342</v>
+        <v>4.633249676635438</v>
       </c>
       <c r="K546">
         <v>12.72</v>
@@ -28952,16 +28925,16 @@
         <v>28.5</v>
       </c>
       <c r="M546">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N546">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>416</v>
+        <v>92</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28972,28 +28945,28 @@
         <v>94</v>
       </c>
       <c r="C547">
-        <v>-30.43493588680277</v>
+        <v>-30.74429722076099</v>
       </c>
       <c r="D547" t="s">
         <v>206</v>
       </c>
       <c r="E547">
-        <v>-31.55955570571861</v>
+        <v>-31.02581132800566</v>
       </c>
       <c r="F547">
         <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.08743493588680278</v>
+        <v>0.08774429722076099</v>
       </c>
       <c r="H547">
-        <v>0.0914995557057186</v>
+        <v>0.08932581132800566</v>
       </c>
       <c r="I547">
-        <v>1.124619818915839</v>
+        <v>0.2815141072446679</v>
       </c>
       <c r="J547">
-        <v>4.633249676635438</v>
+        <v>4.657570536223348</v>
       </c>
       <c r="K547">
         <v>12.72</v>
@@ -29002,16 +28975,16 @@
         <v>28.5</v>
       </c>
       <c r="M547">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N547">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>92</v>
+        <v>416</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29022,28 +28995,28 @@
         <v>94</v>
       </c>
       <c r="C548">
-        <v>-30.74429722076099</v>
+        <v>-31.20320959343522</v>
       </c>
       <c r="D548" t="s">
         <v>206</v>
       </c>
       <c r="E548">
-        <v>-31.88253672104606</v>
+        <v>-31.49193930402382</v>
       </c>
       <c r="F548">
         <v>-1</v>
       </c>
       <c r="G548">
-        <v>0.08774429722076099</v>
+        <v>0.08820320959343522</v>
       </c>
       <c r="H548">
-        <v>0.09182253672104605</v>
+        <v>0.08979193930402382</v>
       </c>
       <c r="I548">
-        <v>1.138239500285067</v>
+        <v>0.2887297105885978</v>
       </c>
       <c r="J548">
-        <v>4.657570536223348</v>
+        <v>4.69364855294302</v>
       </c>
       <c r="K548">
         <v>12.72</v>
@@ -29052,10 +29025,10 @@
         <v>28.5</v>
       </c>
       <c r="M548">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N548">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O548">
         <v>1</v>
@@ -29072,28 +29045,28 @@
         <v>94</v>
       </c>
       <c r="C549">
-        <v>-31.20320959343522</v>
+        <v>-31.07605732463613</v>
       </c>
       <c r="D549" t="s">
         <v>206</v>
       </c>
       <c r="E549">
-        <v>-32.3616527830833</v>
+        <v>-31.36278778571532</v>
       </c>
       <c r="F549">
         <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.08820320959343522</v>
+        <v>0.08807605732463614</v>
       </c>
       <c r="H549">
-        <v>0.0923016527830833</v>
+        <v>0.08966278778571532</v>
       </c>
       <c r="I549">
-        <v>1.158443189648082</v>
+        <v>0.2867304610791876</v>
       </c>
       <c r="J549">
-        <v>4.69364855294302</v>
+        <v>4.683652305395922</v>
       </c>
       <c r="K549">
         <v>12.72</v>
@@ -29102,10 +29075,10 @@
         <v>28.5</v>
       </c>
       <c r="M549">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N549">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O549">
         <v>1</v>
@@ -29122,28 +29095,28 @@
         <v>94</v>
       </c>
       <c r="C550">
-        <v>-31.07605732463613</v>
+        <v>-30.25066173781194</v>
       </c>
       <c r="D550" t="s">
         <v>206</v>
       </c>
       <c r="E550">
-        <v>-32.22890261565784</v>
+        <v>-30.5244142808593</v>
       </c>
       <c r="F550">
         <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.08807605732463614</v>
+        <v>0.08725066173781194</v>
       </c>
       <c r="H550">
-        <v>0.09216890261565784</v>
+        <v>0.08882441428085928</v>
       </c>
       <c r="I550">
-        <v>1.152845291021713</v>
+        <v>0.2737525430473582</v>
       </c>
       <c r="J550">
-        <v>4.683652305395922</v>
+        <v>4.618762715236787</v>
       </c>
       <c r="K550">
         <v>12.72</v>
@@ -29152,10 +29125,10 @@
         <v>28.5</v>
       </c>
       <c r="M550">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N550">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O550">
         <v>1</v>
@@ -29172,28 +29145,28 @@
         <v>94</v>
       </c>
       <c r="C551">
-        <v>-30.25066173781194</v>
+        <v>-28.48555321698337</v>
       </c>
       <c r="D551" t="s">
         <v>206</v>
       </c>
       <c r="E551">
-        <v>-31.36716885834453</v>
+        <v>-28.73155248140134</v>
       </c>
       <c r="F551">
         <v>-1</v>
       </c>
       <c r="G551">
-        <v>0.08725066173781194</v>
+        <v>0.08548555321698337</v>
       </c>
       <c r="H551">
-        <v>0.09130716885834454</v>
+        <v>0.08703155248140135</v>
       </c>
       <c r="I551">
-        <v>1.116507120532596</v>
+        <v>0.2459992644179749</v>
       </c>
       <c r="J551">
-        <v>4.618762715236787</v>
+        <v>4.479996322089887</v>
       </c>
       <c r="K551">
         <v>12.72</v>
@@ -29202,10 +29175,10 @@
         <v>28.5</v>
       </c>
       <c r="M551">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N551">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O551">
         <v>1</v>
@@ -29222,28 +29195,28 @@
         <v>94</v>
       </c>
       <c r="C552">
-        <v>-28.48555321698337</v>
+        <v>-28.69349087972021</v>
       </c>
       <c r="D552" t="s">
         <v>206</v>
       </c>
       <c r="E552">
-        <v>-29.5243511573537</v>
+        <v>-28.94275960424411</v>
       </c>
       <c r="F552">
         <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.08548555321698337</v>
+        <v>0.0856934908797202</v>
       </c>
       <c r="H552">
-        <v>0.0894643511573537</v>
+        <v>0.0872427596042441</v>
       </c>
       <c r="I552">
-        <v>1.03879794037033</v>
+        <v>0.2492687245239011</v>
       </c>
       <c r="J552">
-        <v>4.479996322089887</v>
+        <v>4.496343622619513</v>
       </c>
       <c r="K552">
         <v>12.72</v>
@@ -29252,516 +29225,16 @@
         <v>28.5</v>
       </c>
       <c r="M552">
-        <v>13.28</v>
+        <v>12.92</v>
       </c>
       <c r="N552">
-        <v>29.97</v>
+        <v>29.15</v>
       </c>
       <c r="O552">
         <v>1</v>
       </c>
       <c r="P552" t="s">
         <v>421</v>
-      </c>
-    </row>
-    <row r="553" spans="1:16">
-      <c r="A553" s="1">
-        <v>0</v>
-      </c>
-      <c r="B553" t="s">
-        <v>94</v>
-      </c>
-      <c r="C553">
-        <v>-28.69349087972021</v>
-      </c>
-      <c r="D553" t="s">
-        <v>206</v>
-      </c>
-      <c r="E553">
-        <v>-29.74144330838713</v>
-      </c>
-      <c r="F553">
-        <v>-1</v>
-      </c>
-      <c r="G553">
-        <v>0.0856934908797202</v>
-      </c>
-      <c r="H553">
-        <v>0.08968144330838712</v>
-      </c>
-      <c r="I553">
-        <v>1.047952428666918</v>
-      </c>
-      <c r="J553">
-        <v>4.496343622619513</v>
-      </c>
-      <c r="K553">
-        <v>12.72</v>
-      </c>
-      <c r="L553">
-        <v>28.5</v>
-      </c>
-      <c r="M553">
-        <v>13.28</v>
-      </c>
-      <c r="N553">
-        <v>29.97</v>
-      </c>
-      <c r="O553">
-        <v>1</v>
-      </c>
-      <c r="P553" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="554" spans="1:16">
-      <c r="A554" s="1">
-        <v>0</v>
-      </c>
-      <c r="B554" t="s">
-        <v>94</v>
-      </c>
-      <c r="C554">
-        <v>-28.72399400585454</v>
-      </c>
-      <c r="D554" t="s">
-        <v>206</v>
-      </c>
-      <c r="E554">
-        <v>-29.77328933944561</v>
-      </c>
-      <c r="F554">
-        <v>-1</v>
-      </c>
-      <c r="G554">
-        <v>0.08572399400585454</v>
-      </c>
-      <c r="H554">
-        <v>0.08971328933944561</v>
-      </c>
-      <c r="I554">
-        <v>1.049295333591076</v>
-      </c>
-      <c r="J554">
-        <v>4.498741667126929</v>
-      </c>
-      <c r="K554">
-        <v>12.72</v>
-      </c>
-      <c r="L554">
-        <v>28.5</v>
-      </c>
-      <c r="M554">
-        <v>13.28</v>
-      </c>
-      <c r="N554">
-        <v>29.97</v>
-      </c>
-      <c r="O554">
-        <v>1</v>
-      </c>
-      <c r="P554" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="555" spans="1:16">
-      <c r="A555" s="1">
-        <v>0</v>
-      </c>
-      <c r="B555" t="s">
-        <v>94</v>
-      </c>
-      <c r="C555">
-        <v>-29.04997068031175</v>
-      </c>
-      <c r="D555" t="s">
-        <v>206</v>
-      </c>
-      <c r="E555">
-        <v>-30.11361718825</v>
-      </c>
-      <c r="F555">
-        <v>-1</v>
-      </c>
-      <c r="G555">
-        <v>0.08604997068031175</v>
-      </c>
-      <c r="H555">
-        <v>0.09005361718825</v>
-      </c>
-      <c r="I555">
-        <v>1.063646507938245</v>
-      </c>
-      <c r="J555">
-        <v>4.524368764175452</v>
-      </c>
-      <c r="K555">
-        <v>12.72</v>
-      </c>
-      <c r="L555">
-        <v>28.5</v>
-      </c>
-      <c r="M555">
-        <v>13.28</v>
-      </c>
-      <c r="N555">
-        <v>29.97</v>
-      </c>
-      <c r="O555">
-        <v>1</v>
-      </c>
-      <c r="P555" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="556" spans="1:16">
-      <c r="A556" s="1">
-        <v>0</v>
-      </c>
-      <c r="B556" t="s">
-        <v>94</v>
-      </c>
-      <c r="C556">
-        <v>-29.43168959025828</v>
-      </c>
-      <c r="D556" t="s">
-        <v>206</v>
-      </c>
-      <c r="E556">
-        <v>-30.51214133322562</v>
-      </c>
-      <c r="F556">
-        <v>-1</v>
-      </c>
-      <c r="G556">
-        <v>0.08643168959025829</v>
-      </c>
-      <c r="H556">
-        <v>0.09045214133322563</v>
-      </c>
-      <c r="I556">
-        <v>1.080451742967341</v>
-      </c>
-      <c r="J556">
-        <v>4.554378112441689</v>
-      </c>
-      <c r="K556">
-        <v>12.72</v>
-      </c>
-      <c r="L556">
-        <v>28.5</v>
-      </c>
-      <c r="M556">
-        <v>13.28</v>
-      </c>
-      <c r="N556">
-        <v>29.97</v>
-      </c>
-      <c r="O556">
-        <v>1</v>
-      </c>
-      <c r="P556" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="557" spans="1:16">
-      <c r="A557" s="1">
-        <v>0</v>
-      </c>
-      <c r="B557" t="s">
-        <v>94</v>
-      </c>
-      <c r="C557">
-        <v>-30.72131869184545</v>
-      </c>
-      <c r="D557" t="s">
-        <v>206</v>
-      </c>
-      <c r="E557">
-        <v>-31.85854655878203</v>
-      </c>
-      <c r="F557">
-        <v>-1</v>
-      </c>
-      <c r="G557">
-        <v>0.08772131869184546</v>
-      </c>
-      <c r="H557">
-        <v>0.09179854655878203</v>
-      </c>
-      <c r="I557">
-        <v>1.137227866936584</v>
-      </c>
-      <c r="J557">
-        <v>4.655764048101057</v>
-      </c>
-      <c r="K557">
-        <v>12.72</v>
-      </c>
-      <c r="L557">
-        <v>28.5</v>
-      </c>
-      <c r="M557">
-        <v>13.28</v>
-      </c>
-      <c r="N557">
-        <v>29.97</v>
-      </c>
-      <c r="O557">
-        <v>1</v>
-      </c>
-      <c r="P557" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="558" spans="1:16">
-      <c r="A558" s="1">
-        <v>0</v>
-      </c>
-      <c r="B558" t="s">
-        <v>94</v>
-      </c>
-      <c r="C558">
-        <v>-32.3547496665294</v>
-      </c>
-      <c r="D558" t="s">
-        <v>206</v>
-      </c>
-      <c r="E558">
-        <v>-33.56388958895521</v>
-      </c>
-      <c r="F558">
-        <v>-1</v>
-      </c>
-      <c r="G558">
-        <v>0.0893547496665294</v>
-      </c>
-      <c r="H558">
-        <v>0.09350388958895522</v>
-      </c>
-      <c r="I558">
-        <v>1.209139922425813</v>
-      </c>
-      <c r="J558">
-        <v>4.784178432903254</v>
-      </c>
-      <c r="K558">
-        <v>12.72</v>
-      </c>
-      <c r="L558">
-        <v>28.5</v>
-      </c>
-      <c r="M558">
-        <v>13.28</v>
-      </c>
-      <c r="N558">
-        <v>29.97</v>
-      </c>
-      <c r="O558">
-        <v>1</v>
-      </c>
-      <c r="P558" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="559" spans="1:16">
-      <c r="A559" s="1">
-        <v>0</v>
-      </c>
-      <c r="B559" t="s">
-        <v>94</v>
-      </c>
-      <c r="C559">
-        <v>-33.15849324376438</v>
-      </c>
-      <c r="D559" t="s">
-        <v>206</v>
-      </c>
-      <c r="E559">
-        <v>-34.40301810355274</v>
-      </c>
-      <c r="F559">
-        <v>-1</v>
-      </c>
-      <c r="G559">
-        <v>0.09015849324376439</v>
-      </c>
-      <c r="H559">
-        <v>0.09434301810355274</v>
-      </c>
-      <c r="I559">
-        <v>1.244524859788363</v>
-      </c>
-      <c r="J559">
-        <v>4.847365821050658</v>
-      </c>
-      <c r="K559">
-        <v>12.72</v>
-      </c>
-      <c r="L559">
-        <v>28.5</v>
-      </c>
-      <c r="M559">
-        <v>13.28</v>
-      </c>
-      <c r="N559">
-        <v>29.97</v>
-      </c>
-      <c r="O559">
-        <v>1</v>
-      </c>
-      <c r="P559" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="560" spans="1:16">
-      <c r="A560" s="1">
-        <v>0</v>
-      </c>
-      <c r="B560" t="s">
-        <v>94</v>
-      </c>
-      <c r="C560">
-        <v>-34.25698087216963</v>
-      </c>
-      <c r="D560" t="s">
-        <v>206</v>
-      </c>
-      <c r="E560">
-        <v>-35.54986682251671</v>
-      </c>
-      <c r="F560">
-        <v>-1</v>
-      </c>
-      <c r="G560">
-        <v>0.09125698087216964</v>
-      </c>
-      <c r="H560">
-        <v>0.0954898668225167</v>
-      </c>
-      <c r="I560">
-        <v>1.292885950347078</v>
-      </c>
-      <c r="J560">
-        <v>4.93372491133409</v>
-      </c>
-      <c r="K560">
-        <v>12.72</v>
-      </c>
-      <c r="L560">
-        <v>28.5</v>
-      </c>
-      <c r="M560">
-        <v>13.28</v>
-      </c>
-      <c r="N560">
-        <v>29.97</v>
-      </c>
-      <c r="O560">
-        <v>1</v>
-      </c>
-      <c r="P560" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="561" spans="1:16">
-      <c r="A561" s="1">
-        <v>0</v>
-      </c>
-      <c r="B561" t="s">
-        <v>94</v>
-      </c>
-      <c r="C561">
-        <v>-35.16617096130667</v>
-      </c>
-      <c r="D561" t="s">
-        <v>206</v>
-      </c>
-      <c r="E561">
-        <v>-36.49908414828244</v>
-      </c>
-      <c r="F561">
-        <v>-1</v>
-      </c>
-      <c r="G561">
-        <v>0.09216617096130668</v>
-      </c>
-      <c r="H561">
-        <v>0.09643908414828244</v>
-      </c>
-      <c r="I561">
-        <v>1.332913186975766</v>
-      </c>
-      <c r="J561">
-        <v>5.005202119599581</v>
-      </c>
-      <c r="K561">
-        <v>12.72</v>
-      </c>
-      <c r="L561">
-        <v>28.5</v>
-      </c>
-      <c r="M561">
-        <v>13.28</v>
-      </c>
-      <c r="N561">
-        <v>29.97</v>
-      </c>
-      <c r="O561">
-        <v>1</v>
-      </c>
-      <c r="P561" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="562" spans="1:16">
-      <c r="A562" s="1">
-        <v>0</v>
-      </c>
-      <c r="B562" t="s">
-        <v>94</v>
-      </c>
-      <c r="C562">
-        <v>-35.90561619919141</v>
-      </c>
-      <c r="D562" t="s">
-        <v>206</v>
-      </c>
-      <c r="E562">
-        <v>-37.27108357903002</v>
-      </c>
-      <c r="F562">
-        <v>-1</v>
-      </c>
-      <c r="G562">
-        <v>0.09290561619919141</v>
-      </c>
-      <c r="H562">
-        <v>0.09721108357903002</v>
-      </c>
-      <c r="I562">
-        <v>1.365467379838606</v>
-      </c>
-      <c r="J562">
-        <v>5.063334606854671</v>
-      </c>
-      <c r="K562">
-        <v>12.72</v>
-      </c>
-      <c r="L562">
-        <v>28.5</v>
-      </c>
-      <c r="M562">
-        <v>13.28</v>
-      </c>
-      <c r="N562">
-        <v>29.97</v>
-      </c>
-      <c r="O562">
-        <v>1</v>
-      </c>
-      <c r="P562" t="s">
-        <v>430</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="433">
   <si>
     <t>trade_time</t>
   </si>
@@ -298,7 +298,7 @@
     <t>2021-03-19</t>
   </si>
   <si>
-    <t>2021-07-27</t>
+    <t>2021-08-20</t>
   </si>
   <si>
     <t>2016-05-10</t>
@@ -634,7 +634,7 @@
     <t>2021-05-14</t>
   </si>
   <si>
-    <t>2021-08-19</t>
+    <t>2021-08-23</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1243,6 +1243,15 @@
     <t>2020-12-18</t>
   </si>
   <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>2021-01-05</t>
+  </si>
+  <si>
     <t>2021-01-06</t>
   </si>
   <si>
@@ -1280,6 +1289,30 @@
   </si>
   <si>
     <t>2021-01-25</t>
+  </si>
+  <si>
+    <t>2021-01-26</t>
+  </si>
+  <si>
+    <t>2021-01-27</t>
+  </si>
+  <si>
+    <t>2021-01-28</t>
+  </si>
+  <si>
+    <t>2021-01-29</t>
+  </si>
+  <si>
+    <t>2021-02-01</t>
+  </si>
+  <si>
+    <t>2021-02-02</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>2021-02-05</t>
   </si>
 </sst>
 </file>
@@ -1637,7 +1670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P552"/>
+  <dimension ref="A1:P565"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28545,46 +28578,46 @@
         <v>94</v>
       </c>
       <c r="C539">
-        <v>-20.96449736029645</v>
+        <v>-10.28452075330963</v>
       </c>
       <c r="D539" t="s">
         <v>206</v>
       </c>
       <c r="E539">
-        <v>-21.0922410294835</v>
+        <v>-10.62673963298769</v>
       </c>
       <c r="F539">
         <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.07796449736029645</v>
+        <v>0.06960452075330963</v>
       </c>
       <c r="H539">
-        <v>0.0793922410294835</v>
+        <v>0.06938673963298768</v>
       </c>
       <c r="I539">
-        <v>0.1277436691870477</v>
+        <v>0.3422188796780574</v>
       </c>
       <c r="J539">
-        <v>3.888718345935255</v>
+        <v>3.11094398390262</v>
       </c>
       <c r="K539">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L539">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M539">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N539">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>409</v>
+        <v>199</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28595,46 +28628,46 @@
         <v>94</v>
       </c>
       <c r="C540">
-        <v>-22.26553261458488</v>
+        <v>-12.90519447650706</v>
       </c>
       <c r="D540" t="s">
         <v>206</v>
       </c>
       <c r="E540">
-        <v>-22.41373281292741</v>
+        <v>-13.25149540248293</v>
       </c>
       <c r="F540">
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.07926553261458488</v>
+        <v>0.07222519447650706</v>
       </c>
       <c r="H540">
-        <v>0.0807137328129274</v>
+        <v>0.07201149540248292</v>
       </c>
       <c r="I540">
-        <v>0.1482001983425292</v>
+        <v>0.3463009259758678</v>
       </c>
       <c r="J540">
-        <v>3.991000991712648</v>
+        <v>3.315046298793385</v>
       </c>
       <c r="K540">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L540">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M540">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N540">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O540">
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28645,46 +28678,46 @@
         <v>94</v>
       </c>
       <c r="C541">
-        <v>-23.39064064612373</v>
+        <v>-14.93671190899163</v>
       </c>
       <c r="D541" t="s">
         <v>206</v>
       </c>
       <c r="E541">
-        <v>-23.55653122232064</v>
+        <v>-15.28617719233897</v>
       </c>
       <c r="F541">
         <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.08039064064612372</v>
+        <v>0.07425671190899163</v>
       </c>
       <c r="H541">
-        <v>0.08185653122232064</v>
+        <v>0.07404617719233897</v>
       </c>
       <c r="I541">
-        <v>0.1658905761969152</v>
+        <v>0.3494652833473424</v>
       </c>
       <c r="J541">
-        <v>4.07945288098457</v>
+        <v>3.47326416736695</v>
       </c>
       <c r="K541">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L541">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M541">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N541">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28695,46 +28728,46 @@
         <v>94</v>
       </c>
       <c r="C542">
-        <v>-24.9776650997016</v>
+        <v>-17.70411238403614</v>
       </c>
       <c r="D542" t="s">
         <v>206</v>
       </c>
       <c r="E542">
-        <v>-25.16850889057741</v>
+        <v>-18.05788826002373</v>
       </c>
       <c r="F542">
         <v>-1</v>
       </c>
       <c r="G542">
-        <v>0.0819776650997016</v>
+        <v>0.07702411238403614</v>
       </c>
       <c r="H542">
-        <v>0.08346850889057741</v>
+        <v>0.07681788826002374</v>
       </c>
       <c r="I542">
-        <v>0.1908437908758103</v>
+        <v>0.3537758759875942</v>
       </c>
       <c r="J542">
-        <v>4.204218954379057</v>
+        <v>3.688793799379762</v>
       </c>
       <c r="K542">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L542">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M542">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N542">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28745,46 +28778,46 @@
         <v>94</v>
       </c>
       <c r="C543">
-        <v>-27.00589345076202</v>
+        <v>-20.27114356180867</v>
       </c>
       <c r="D543" t="s">
         <v>206</v>
       </c>
       <c r="E543">
-        <v>-27.22862762451614</v>
+        <v>-20.62891792872738</v>
       </c>
       <c r="F543">
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.08400589345076202</v>
+        <v>0.07959114356180869</v>
       </c>
       <c r="H543">
-        <v>0.08552862762451613</v>
+        <v>0.07938891792872738</v>
       </c>
       <c r="I543">
-        <v>0.2227341737541195</v>
+        <v>0.3577743669187043</v>
       </c>
       <c r="J543">
-        <v>4.363670868770599</v>
+        <v>3.888718345935255</v>
       </c>
       <c r="K543">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L543">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M543">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N543">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28795,46 +28828,46 @@
         <v>94</v>
       </c>
       <c r="C544">
-        <v>-29.1656717820026</v>
+        <v>-21.58445273359039</v>
       </c>
       <c r="D544" t="s">
         <v>206</v>
       </c>
       <c r="E544">
-        <v>-29.42236473454981</v>
+        <v>-21.94427275342465</v>
       </c>
       <c r="F544">
         <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.0861656717820026</v>
+        <v>0.08090445273359038</v>
       </c>
       <c r="H544">
-        <v>0.08772236473454982</v>
+        <v>0.08070427275342465</v>
       </c>
       <c r="I544">
-        <v>0.2566929525472048</v>
+        <v>0.3598200198342525</v>
       </c>
       <c r="J544">
-        <v>4.533464762736053</v>
+        <v>3.991000991712648</v>
       </c>
       <c r="K544">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L544">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M544">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N544">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28845,46 +28878,46 @@
         <v>94</v>
       </c>
       <c r="C545">
-        <v>-29.94151334120067</v>
+        <v>-22.72017499184188</v>
       </c>
       <c r="D545" t="s">
         <v>206</v>
       </c>
       <c r="E545">
-        <v>-30.21040506040193</v>
+        <v>-23.08176404946157</v>
       </c>
       <c r="F545">
         <v>-1</v>
       </c>
       <c r="G545">
-        <v>0.08694151334120068</v>
+        <v>0.08204017499184188</v>
       </c>
       <c r="H545">
-        <v>0.08851040506040192</v>
+        <v>0.08184176404946156</v>
       </c>
       <c r="I545">
-        <v>0.2688917192012639</v>
+        <v>0.361589057619689</v>
       </c>
       <c r="J545">
-        <v>4.594458596006342</v>
+        <v>4.07945288098457</v>
       </c>
       <c r="K545">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L545">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M545">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N545">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28895,46 +28928,46 @@
         <v>94</v>
       </c>
       <c r="C546">
-        <v>-30.43493588680277</v>
+        <v>-24.32217137422709</v>
       </c>
       <c r="D546" t="s">
         <v>206</v>
       </c>
       <c r="E546">
-        <v>-30.71158582212986</v>
+        <v>-24.68625575331466</v>
       </c>
       <c r="F546">
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.08743493588680278</v>
+        <v>0.0836421713742271</v>
       </c>
       <c r="H546">
-        <v>0.08901158582212985</v>
+        <v>0.08344625575331466</v>
       </c>
       <c r="I546">
-        <v>0.2766499353270859</v>
+        <v>0.3640843790875792</v>
       </c>
       <c r="J546">
-        <v>4.633249676635438</v>
+        <v>4.204218954379057</v>
       </c>
       <c r="K546">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L546">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M546">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N546">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>92</v>
+        <v>415</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28945,40 +28978,40 @@
         <v>94</v>
       </c>
       <c r="C547">
-        <v>-30.74429722076099</v>
+        <v>-26.36953395501449</v>
       </c>
       <c r="D547" t="s">
         <v>206</v>
       </c>
       <c r="E547">
-        <v>-31.02581132800566</v>
+        <v>-26.73680737238989</v>
       </c>
       <c r="F547">
         <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.08774429722076099</v>
+        <v>0.08568953395501448</v>
       </c>
       <c r="H547">
-        <v>0.08932581132800566</v>
+        <v>0.08549680737238989</v>
       </c>
       <c r="I547">
-        <v>0.2815141072446679</v>
+        <v>0.367273417375408</v>
       </c>
       <c r="J547">
-        <v>4.657570536223348</v>
+        <v>4.363670868770599</v>
       </c>
       <c r="K547">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L547">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M547">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N547">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O547">
         <v>1</v>
@@ -28995,40 +29028,40 @@
         <v>94</v>
       </c>
       <c r="C548">
-        <v>-31.20320959343522</v>
+        <v>-28.54968755353093</v>
       </c>
       <c r="D548" t="s">
         <v>206</v>
       </c>
       <c r="E548">
-        <v>-31.49193930402382</v>
+        <v>-28.92035684878565</v>
       </c>
       <c r="F548">
         <v>-1</v>
       </c>
       <c r="G548">
-        <v>0.08820320959343522</v>
+        <v>0.08786968755353093</v>
       </c>
       <c r="H548">
-        <v>0.08979193930402382</v>
+        <v>0.08768035684878565</v>
       </c>
       <c r="I548">
-        <v>0.2887297105885978</v>
+        <v>0.3706692952547215</v>
       </c>
       <c r="J548">
-        <v>4.69364855294302</v>
+        <v>4.533464762736053</v>
       </c>
       <c r="K548">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L548">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M548">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N548">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O548">
         <v>1</v>
@@ -29045,40 +29078,40 @@
         <v>94</v>
       </c>
       <c r="C549">
-        <v>-31.07605732463613</v>
+        <v>-29.33284837272143</v>
       </c>
       <c r="D549" t="s">
         <v>206</v>
       </c>
       <c r="E549">
-        <v>-31.36278778571532</v>
+        <v>-29.70473754464155</v>
       </c>
       <c r="F549">
         <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.08807605732463614</v>
+        <v>0.08865284837272143</v>
       </c>
       <c r="H549">
-        <v>0.08966278778571532</v>
+        <v>0.08846473754464156</v>
       </c>
       <c r="I549">
-        <v>0.2867304610791876</v>
+        <v>0.3718891719201238</v>
       </c>
       <c r="J549">
-        <v>4.683652305395922</v>
+        <v>4.594458596006342</v>
       </c>
       <c r="K549">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L549">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M549">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N549">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O549">
         <v>1</v>
@@ -29095,46 +29128,46 @@
         <v>94</v>
       </c>
       <c r="C550">
-        <v>-30.25066173781194</v>
+        <v>-29.83092584799902</v>
       </c>
       <c r="D550" t="s">
         <v>206</v>
       </c>
       <c r="E550">
-        <v>-30.5244142808593</v>
+        <v>-30.20359084153172</v>
       </c>
       <c r="F550">
         <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.08725066173781194</v>
+        <v>0.08915092584799902</v>
       </c>
       <c r="H550">
-        <v>0.08882441428085928</v>
+        <v>0.08896359084153173</v>
       </c>
       <c r="I550">
-        <v>0.2737525430473582</v>
+        <v>0.3726649935327089</v>
       </c>
       <c r="J550">
-        <v>4.618762715236787</v>
+        <v>4.633249676635438</v>
       </c>
       <c r="K550">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L550">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M550">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N550">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>419</v>
+        <v>92</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29145,46 +29178,46 @@
         <v>94</v>
       </c>
       <c r="C551">
-        <v>-28.48555321698337</v>
+        <v>-30.14320568510779</v>
       </c>
       <c r="D551" t="s">
         <v>206</v>
       </c>
       <c r="E551">
-        <v>-28.73155248140134</v>
+        <v>-30.51635709583226</v>
       </c>
       <c r="F551">
         <v>-1</v>
       </c>
       <c r="G551">
-        <v>0.08548555321698337</v>
+        <v>0.08946320568510779</v>
       </c>
       <c r="H551">
-        <v>0.08703155248140135</v>
+        <v>0.08927635709583226</v>
       </c>
       <c r="I551">
-        <v>0.2459992644179749</v>
+        <v>0.3731514107244678</v>
       </c>
       <c r="J551">
-        <v>4.479996322089887</v>
+        <v>4.657570536223348</v>
       </c>
       <c r="K551">
-        <v>12.72</v>
+        <v>12.84</v>
       </c>
       <c r="L551">
-        <v>28.5</v>
+        <v>29.66</v>
       </c>
       <c r="M551">
-        <v>12.92</v>
+        <v>12.86</v>
       </c>
       <c r="N551">
-        <v>29.15</v>
+        <v>29.38</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29195,46 +29228,696 @@
         <v>94</v>
       </c>
       <c r="C552">
-        <v>-28.69349087972021</v>
+        <v>-30.60644741978838</v>
       </c>
       <c r="D552" t="s">
         <v>206</v>
       </c>
       <c r="E552">
-        <v>-28.94275960424411</v>
+        <v>-30.98032039084724</v>
       </c>
       <c r="F552">
         <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.0856934908797202</v>
+        <v>0.08992644741978838</v>
       </c>
       <c r="H552">
-        <v>0.0872427596042441</v>
+        <v>0.08974032039084723</v>
       </c>
       <c r="I552">
-        <v>0.2492687245239011</v>
+        <v>0.3738729710588586</v>
       </c>
       <c r="J552">
+        <v>4.69364855294302</v>
+      </c>
+      <c r="K552">
+        <v>12.84</v>
+      </c>
+      <c r="L552">
+        <v>29.66</v>
+      </c>
+      <c r="M552">
+        <v>12.86</v>
+      </c>
+      <c r="N552">
+        <v>29.38</v>
+      </c>
+      <c r="O552">
+        <v>1</v>
+      </c>
+      <c r="P552" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="553" spans="1:16">
+      <c r="A553" s="1">
+        <v>0</v>
+      </c>
+      <c r="B553" t="s">
+        <v>94</v>
+      </c>
+      <c r="C553">
+        <v>-30.47809560128364</v>
+      </c>
+      <c r="D553" t="s">
+        <v>206</v>
+      </c>
+      <c r="E553">
+        <v>-30.85176864739156</v>
+      </c>
+      <c r="F553">
+        <v>-1</v>
+      </c>
+      <c r="G553">
+        <v>0.08979809560128364</v>
+      </c>
+      <c r="H553">
+        <v>0.08961176864739157</v>
+      </c>
+      <c r="I553">
+        <v>0.3736730461079176</v>
+      </c>
+      <c r="J553">
+        <v>4.683652305395922</v>
+      </c>
+      <c r="K553">
+        <v>12.84</v>
+      </c>
+      <c r="L553">
+        <v>29.66</v>
+      </c>
+      <c r="M553">
+        <v>12.86</v>
+      </c>
+      <c r="N553">
+        <v>29.38</v>
+      </c>
+      <c r="O553">
+        <v>1</v>
+      </c>
+      <c r="P553" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="554" spans="1:16">
+      <c r="A554" s="1">
+        <v>0</v>
+      </c>
+      <c r="B554" t="s">
+        <v>94</v>
+      </c>
+      <c r="C554">
+        <v>-29.64491326364035</v>
+      </c>
+      <c r="D554" t="s">
+        <v>206</v>
+      </c>
+      <c r="E554">
+        <v>-30.01728851794509</v>
+      </c>
+      <c r="F554">
+        <v>-1</v>
+      </c>
+      <c r="G554">
+        <v>0.08896491326364035</v>
+      </c>
+      <c r="H554">
+        <v>0.08877728851794509</v>
+      </c>
+      <c r="I554">
+        <v>0.3723752543047354</v>
+      </c>
+      <c r="J554">
+        <v>4.618762715236787</v>
+      </c>
+      <c r="K554">
+        <v>12.84</v>
+      </c>
+      <c r="L554">
+        <v>29.66</v>
+      </c>
+      <c r="M554">
+        <v>12.86</v>
+      </c>
+      <c r="N554">
+        <v>29.38</v>
+      </c>
+      <c r="O554">
+        <v>1</v>
+      </c>
+      <c r="P554" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="555" spans="1:16">
+      <c r="A555" s="1">
+        <v>0</v>
+      </c>
+      <c r="B555" t="s">
+        <v>94</v>
+      </c>
+      <c r="C555">
+        <v>-27.86315277563415</v>
+      </c>
+      <c r="D555" t="s">
+        <v>206</v>
+      </c>
+      <c r="E555">
+        <v>-28.23275270207595</v>
+      </c>
+      <c r="F555">
+        <v>-1</v>
+      </c>
+      <c r="G555">
+        <v>0.08718315277563415</v>
+      </c>
+      <c r="H555">
+        <v>0.08699275270207595</v>
+      </c>
+      <c r="I555">
+        <v>0.3695999264417935</v>
+      </c>
+      <c r="J555">
+        <v>4.479996322089887</v>
+      </c>
+      <c r="K555">
+        <v>12.84</v>
+      </c>
+      <c r="L555">
+        <v>29.66</v>
+      </c>
+      <c r="M555">
+        <v>12.86</v>
+      </c>
+      <c r="N555">
+        <v>29.38</v>
+      </c>
+      <c r="O555">
+        <v>1</v>
+      </c>
+      <c r="P555" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="556" spans="1:16">
+      <c r="A556" s="1">
+        <v>0</v>
+      </c>
+      <c r="B556" t="s">
+        <v>94</v>
+      </c>
+      <c r="C556">
+        <v>-28.07305211443454</v>
+      </c>
+      <c r="D556" t="s">
+        <v>206</v>
+      </c>
+      <c r="E556">
+        <v>-28.44297898688693</v>
+      </c>
+      <c r="F556">
+        <v>-1</v>
+      </c>
+      <c r="G556">
+        <v>0.08739305211443454</v>
+      </c>
+      <c r="H556">
+        <v>0.08720297898688693</v>
+      </c>
+      <c r="I556">
+        <v>0.369926872452389</v>
+      </c>
+      <c r="J556">
         <v>4.496343622619513</v>
       </c>
-      <c r="K552">
-        <v>12.72</v>
-      </c>
-      <c r="L552">
-        <v>28.5</v>
-      </c>
-      <c r="M552">
-        <v>12.92</v>
-      </c>
-      <c r="N552">
-        <v>29.15</v>
-      </c>
-      <c r="O552">
-        <v>1</v>
-      </c>
-      <c r="P552" t="s">
-        <v>421</v>
+      <c r="K556">
+        <v>12.84</v>
+      </c>
+      <c r="L556">
+        <v>29.66</v>
+      </c>
+      <c r="M556">
+        <v>12.86</v>
+      </c>
+      <c r="N556">
+        <v>29.38</v>
+      </c>
+      <c r="O556">
+        <v>1</v>
+      </c>
+      <c r="P556" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="557" spans="1:16">
+      <c r="A557" s="1">
+        <v>0</v>
+      </c>
+      <c r="B557" t="s">
+        <v>94</v>
+      </c>
+      <c r="C557">
+        <v>-28.10384300590976</v>
+      </c>
+      <c r="D557" t="s">
+        <v>206</v>
+      </c>
+      <c r="E557">
+        <v>-28.4738178392523</v>
+      </c>
+      <c r="F557">
+        <v>-1</v>
+      </c>
+      <c r="G557">
+        <v>0.08742384300590976</v>
+      </c>
+      <c r="H557">
+        <v>0.0872338178392523</v>
+      </c>
+      <c r="I557">
+        <v>0.369974833342539</v>
+      </c>
+      <c r="J557">
+        <v>4.498741667126929</v>
+      </c>
+      <c r="K557">
+        <v>12.84</v>
+      </c>
+      <c r="L557">
+        <v>29.66</v>
+      </c>
+      <c r="M557">
+        <v>12.86</v>
+      </c>
+      <c r="N557">
+        <v>29.38</v>
+      </c>
+      <c r="O557">
+        <v>1</v>
+      </c>
+      <c r="P557" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="558" spans="1:16">
+      <c r="A558" s="1">
+        <v>0</v>
+      </c>
+      <c r="B558" t="s">
+        <v>94</v>
+      </c>
+      <c r="C558">
+        <v>-28.4328949320128</v>
+      </c>
+      <c r="D558" t="s">
+        <v>206</v>
+      </c>
+      <c r="E558">
+        <v>-28.80338230729631</v>
+      </c>
+      <c r="F558">
+        <v>-1</v>
+      </c>
+      <c r="G558">
+        <v>0.0877528949320128</v>
+      </c>
+      <c r="H558">
+        <v>0.08756338230729631</v>
+      </c>
+      <c r="I558">
+        <v>0.3704873752835098</v>
+      </c>
+      <c r="J558">
+        <v>4.524368764175452</v>
+      </c>
+      <c r="K558">
+        <v>12.84</v>
+      </c>
+      <c r="L558">
+        <v>29.66</v>
+      </c>
+      <c r="M558">
+        <v>12.86</v>
+      </c>
+      <c r="N558">
+        <v>29.38</v>
+      </c>
+      <c r="O558">
+        <v>1</v>
+      </c>
+      <c r="P558" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="559" spans="1:16">
+      <c r="A559" s="1">
+        <v>0</v>
+      </c>
+      <c r="B559" t="s">
+        <v>94</v>
+      </c>
+      <c r="C559">
+        <v>-28.81821496375128</v>
+      </c>
+      <c r="D559" t="s">
+        <v>206</v>
+      </c>
+      <c r="E559">
+        <v>-29.18930252600012</v>
+      </c>
+      <c r="F559">
+        <v>-1</v>
+      </c>
+      <c r="G559">
+        <v>0.08813821496375128</v>
+      </c>
+      <c r="H559">
+        <v>0.08794930252600011</v>
+      </c>
+      <c r="I559">
+        <v>0.3710875622488317</v>
+      </c>
+      <c r="J559">
+        <v>4.554378112441689</v>
+      </c>
+      <c r="K559">
+        <v>12.84</v>
+      </c>
+      <c r="L559">
+        <v>29.66</v>
+      </c>
+      <c r="M559">
+        <v>12.86</v>
+      </c>
+      <c r="N559">
+        <v>29.38</v>
+      </c>
+      <c r="O559">
+        <v>1</v>
+      </c>
+      <c r="P559" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="560" spans="1:16">
+      <c r="A560" s="1">
+        <v>0</v>
+      </c>
+      <c r="B560" t="s">
+        <v>94</v>
+      </c>
+      <c r="C560">
+        <v>-30.12001037761757</v>
+      </c>
+      <c r="D560" t="s">
+        <v>206</v>
+      </c>
+      <c r="E560">
+        <v>-30.49312565857959</v>
+      </c>
+      <c r="F560">
+        <v>-1</v>
+      </c>
+      <c r="G560">
+        <v>0.08944001037761758</v>
+      </c>
+      <c r="H560">
+        <v>0.0892531256585796</v>
+      </c>
+      <c r="I560">
+        <v>0.3731152809620184</v>
+      </c>
+      <c r="J560">
+        <v>4.655764048101057</v>
+      </c>
+      <c r="K560">
+        <v>12.84</v>
+      </c>
+      <c r="L560">
+        <v>29.66</v>
+      </c>
+      <c r="M560">
+        <v>12.86</v>
+      </c>
+      <c r="N560">
+        <v>29.38</v>
+      </c>
+      <c r="O560">
+        <v>1</v>
+      </c>
+      <c r="P560" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="561" spans="1:16">
+      <c r="A561" s="1">
+        <v>0</v>
+      </c>
+      <c r="B561" t="s">
+        <v>94</v>
+      </c>
+      <c r="C561">
+        <v>-31.76885107847778</v>
+      </c>
+      <c r="D561" t="s">
+        <v>206</v>
+      </c>
+      <c r="E561">
+        <v>-32.14453464713586</v>
+      </c>
+      <c r="F561">
+        <v>-1</v>
+      </c>
+      <c r="G561">
+        <v>0.09108885107847779</v>
+      </c>
+      <c r="H561">
+        <v>0.09090453464713585</v>
+      </c>
+      <c r="I561">
+        <v>0.3756835686580722</v>
+      </c>
+      <c r="J561">
+        <v>4.784178432903254</v>
+      </c>
+      <c r="K561">
+        <v>12.84</v>
+      </c>
+      <c r="L561">
+        <v>29.66</v>
+      </c>
+      <c r="M561">
+        <v>12.86</v>
+      </c>
+      <c r="N561">
+        <v>29.38</v>
+      </c>
+      <c r="O561">
+        <v>1</v>
+      </c>
+      <c r="P561" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="562" spans="1:16">
+      <c r="A562" s="1">
+        <v>0</v>
+      </c>
+      <c r="B562" t="s">
+        <v>94</v>
+      </c>
+      <c r="C562">
+        <v>-32.58017714229045</v>
+      </c>
+      <c r="D562" t="s">
+        <v>206</v>
+      </c>
+      <c r="E562">
+        <v>-32.95712445871146</v>
+      </c>
+      <c r="F562">
+        <v>-1</v>
+      </c>
+      <c r="G562">
+        <v>0.09190017714229046</v>
+      </c>
+      <c r="H562">
+        <v>0.09171712445871147</v>
+      </c>
+      <c r="I562">
+        <v>0.3769473164210098</v>
+      </c>
+      <c r="J562">
+        <v>4.847365821050658</v>
+      </c>
+      <c r="K562">
+        <v>12.84</v>
+      </c>
+      <c r="L562">
+        <v>29.66</v>
+      </c>
+      <c r="M562">
+        <v>12.86</v>
+      </c>
+      <c r="N562">
+        <v>29.38</v>
+      </c>
+      <c r="O562">
+        <v>1</v>
+      </c>
+      <c r="P562" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="563" spans="1:16">
+      <c r="A563" s="1">
+        <v>0</v>
+      </c>
+      <c r="B563" t="s">
+        <v>94</v>
+      </c>
+      <c r="C563">
+        <v>-33.68902786152971</v>
+      </c>
+      <c r="D563" t="s">
+        <v>206</v>
+      </c>
+      <c r="E563">
+        <v>-34.0677023597564</v>
+      </c>
+      <c r="F563">
+        <v>-1</v>
+      </c>
+      <c r="G563">
+        <v>0.09300902786152972</v>
+      </c>
+      <c r="H563">
+        <v>0.09282770235975639</v>
+      </c>
+      <c r="I563">
+        <v>0.3786744982266868</v>
+      </c>
+      <c r="J563">
+        <v>4.93372491133409</v>
+      </c>
+      <c r="K563">
+        <v>12.84</v>
+      </c>
+      <c r="L563">
+        <v>29.66</v>
+      </c>
+      <c r="M563">
+        <v>12.86</v>
+      </c>
+      <c r="N563">
+        <v>29.38</v>
+      </c>
+      <c r="O563">
+        <v>1</v>
+      </c>
+      <c r="P563" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="564" spans="1:16">
+      <c r="A564" s="1">
+        <v>0</v>
+      </c>
+      <c r="B564" t="s">
+        <v>94</v>
+      </c>
+      <c r="C564">
+        <v>-34.60679521565862</v>
+      </c>
+      <c r="D564" t="s">
+        <v>206</v>
+      </c>
+      <c r="E564">
+        <v>-34.98689925805061</v>
+      </c>
+      <c r="F564">
+        <v>-1</v>
+      </c>
+      <c r="G564">
+        <v>0.09392679521565862</v>
+      </c>
+      <c r="H564">
+        <v>0.0937468992580506</v>
+      </c>
+      <c r="I564">
+        <v>0.3801040423919915</v>
+      </c>
+      <c r="J564">
+        <v>5.005202119599581</v>
+      </c>
+      <c r="K564">
+        <v>12.84</v>
+      </c>
+      <c r="L564">
+        <v>29.66</v>
+      </c>
+      <c r="M564">
+        <v>12.86</v>
+      </c>
+      <c r="N564">
+        <v>29.38</v>
+      </c>
+      <c r="O564">
+        <v>1</v>
+      </c>
+      <c r="P564" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="565" spans="1:16">
+      <c r="A565" s="1">
+        <v>0</v>
+      </c>
+      <c r="B565" t="s">
+        <v>94</v>
+      </c>
+      <c r="C565">
+        <v>-35.35321635201397</v>
+      </c>
+      <c r="D565" t="s">
+        <v>206</v>
+      </c>
+      <c r="E565">
+        <v>-35.73448304415106</v>
+      </c>
+      <c r="F565">
+        <v>-1</v>
+      </c>
+      <c r="G565">
+        <v>0.09467321635201396</v>
+      </c>
+      <c r="H565">
+        <v>0.09449448304415106</v>
+      </c>
+      <c r="I565">
+        <v>0.3812666921370891</v>
+      </c>
+      <c r="J565">
+        <v>5.063334606854671</v>
+      </c>
+      <c r="K565">
+        <v>12.84</v>
+      </c>
+      <c r="L565">
+        <v>29.66</v>
+      </c>
+      <c r="M565">
+        <v>12.86</v>
+      </c>
+      <c r="N565">
+        <v>29.38</v>
+      </c>
+      <c r="O565">
+        <v>1</v>
+      </c>
+      <c r="P565" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="430">
   <si>
     <t>trade_time</t>
   </si>
@@ -634,7 +634,7 @@
     <t>2021-05-14</t>
   </si>
   <si>
-    <t>2021-08-23</t>
+    <t>2021-08-24</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1304,15 +1304,6 @@
   </si>
   <si>
     <t>2021-02-01</t>
-  </si>
-  <si>
-    <t>2021-02-02</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-02-05</t>
   </si>
 </sst>
 </file>
@@ -1670,7 +1661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P565"/>
+  <dimension ref="A1:P561"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28584,7 +28575,7 @@
         <v>206</v>
       </c>
       <c r="E539">
-        <v>-10.62673963298769</v>
+        <v>-10.82005291105601</v>
       </c>
       <c r="F539">
         <v>-1</v>
@@ -28593,10 +28584,10 @@
         <v>0.06960452075330963</v>
       </c>
       <c r="H539">
-        <v>0.06938673963298768</v>
+        <v>0.069940052911056</v>
       </c>
       <c r="I539">
-        <v>0.3422188796780574</v>
+        <v>0.5355321577463741</v>
       </c>
       <c r="J539">
         <v>3.11094398390262</v>
@@ -28608,10 +28599,10 @@
         <v>29.66</v>
       </c>
       <c r="M539">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N539">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28634,7 +28625,7 @@
         <v>206</v>
       </c>
       <c r="E540">
-        <v>-13.25149540248293</v>
+        <v>-13.46930095833813</v>
       </c>
       <c r="F540">
         <v>-1</v>
@@ -28643,10 +28634,10 @@
         <v>0.07222519447650706</v>
       </c>
       <c r="H540">
-        <v>0.07201149540248292</v>
+        <v>0.07258930095833813</v>
       </c>
       <c r="I540">
-        <v>0.3463009259758678</v>
+        <v>0.5641064818310753</v>
       </c>
       <c r="J540">
         <v>3.315046298793385</v>
@@ -28658,10 +28649,10 @@
         <v>29.66</v>
       </c>
       <c r="M540">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N540">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28684,7 +28675,7 @@
         <v>206</v>
       </c>
       <c r="E541">
-        <v>-15.28617719233897</v>
+        <v>-15.52296889242301</v>
       </c>
       <c r="F541">
         <v>-1</v>
@@ -28693,10 +28684,10 @@
         <v>0.07425671190899163</v>
       </c>
       <c r="H541">
-        <v>0.07404617719233897</v>
+        <v>0.074642968892423</v>
       </c>
       <c r="I541">
-        <v>0.3494652833473424</v>
+        <v>0.586256983431376</v>
       </c>
       <c r="J541">
         <v>3.47326416736695</v>
@@ -28708,10 +28699,10 @@
         <v>29.66</v>
       </c>
       <c r="M541">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N541">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28734,7 +28725,7 @@
         <v>206</v>
       </c>
       <c r="E542">
-        <v>-18.05788826002373</v>
+        <v>-18.32054351594931</v>
       </c>
       <c r="F542">
         <v>-1</v>
@@ -28743,10 +28734,10 @@
         <v>0.07702411238403614</v>
       </c>
       <c r="H542">
-        <v>0.07681788826002374</v>
+        <v>0.07744054351594931</v>
       </c>
       <c r="I542">
-        <v>0.3537758759875942</v>
+        <v>0.6164311319131741</v>
       </c>
       <c r="J542">
         <v>3.688793799379762</v>
@@ -28758,10 +28749,10 @@
         <v>29.66</v>
       </c>
       <c r="M542">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N542">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28784,7 +28775,7 @@
         <v>206</v>
       </c>
       <c r="E543">
-        <v>-20.62891792872738</v>
+        <v>-20.91556413023961</v>
       </c>
       <c r="F543">
         <v>-1</v>
@@ -28793,10 +28784,10 @@
         <v>0.07959114356180869</v>
       </c>
       <c r="H543">
-        <v>0.07938891792872738</v>
+        <v>0.08003556413023961</v>
       </c>
       <c r="I543">
-        <v>0.3577743669187043</v>
+        <v>0.6444205684309381</v>
       </c>
       <c r="J543">
         <v>3.888718345935255</v>
@@ -28808,10 +28799,10 @@
         <v>29.66</v>
       </c>
       <c r="M543">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N543">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28834,7 +28825,7 @@
         <v>206</v>
       </c>
       <c r="E544">
-        <v>-21.94427275342465</v>
+        <v>-22.24319287243017</v>
       </c>
       <c r="F544">
         <v>-1</v>
@@ -28843,10 +28834,10 @@
         <v>0.08090445273359038</v>
       </c>
       <c r="H544">
-        <v>0.08070427275342465</v>
+        <v>0.08136319287243016</v>
       </c>
       <c r="I544">
-        <v>0.3598200198342525</v>
+        <v>0.6587401388397751</v>
       </c>
       <c r="J544">
         <v>3.991000991712648</v>
@@ -28858,10 +28849,10 @@
         <v>29.66</v>
       </c>
       <c r="M544">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N544">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28884,7 +28875,7 @@
         <v>206</v>
       </c>
       <c r="E545">
-        <v>-23.08176404946157</v>
+        <v>-23.39129839517971</v>
       </c>
       <c r="F545">
         <v>-1</v>
@@ -28893,10 +28884,10 @@
         <v>0.08204017499184188</v>
       </c>
       <c r="H545">
-        <v>0.08184176404946156</v>
+        <v>0.08251129839517971</v>
       </c>
       <c r="I545">
-        <v>0.361589057619689</v>
+        <v>0.6711234033378375</v>
       </c>
       <c r="J545">
         <v>4.07945288098457</v>
@@ -28908,10 +28899,10 @@
         <v>29.66</v>
       </c>
       <c r="M545">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N545">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28934,7 +28925,7 @@
         <v>206</v>
       </c>
       <c r="E546">
-        <v>-24.68625575331466</v>
+        <v>-25.01076202784016</v>
       </c>
       <c r="F546">
         <v>-1</v>
@@ -28943,10 +28934,10 @@
         <v>0.0836421713742271</v>
       </c>
       <c r="H546">
-        <v>0.08344625575331466</v>
+        <v>0.08413076202784016</v>
       </c>
       <c r="I546">
-        <v>0.3640843790875792</v>
+        <v>0.6885906536130761</v>
       </c>
       <c r="J546">
         <v>4.204218954379057</v>
@@ -28958,10 +28949,10 @@
         <v>29.66</v>
       </c>
       <c r="M546">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N546">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28984,7 +28975,7 @@
         <v>206</v>
       </c>
       <c r="E547">
-        <v>-26.73680737238989</v>
+        <v>-27.08044787664237</v>
       </c>
       <c r="F547">
         <v>-1</v>
@@ -28993,10 +28984,10 @@
         <v>0.08568953395501448</v>
       </c>
       <c r="H547">
-        <v>0.08549680737238989</v>
+        <v>0.08620044787664237</v>
       </c>
       <c r="I547">
-        <v>0.367273417375408</v>
+        <v>0.7109139216278848</v>
       </c>
       <c r="J547">
         <v>4.363670868770599</v>
@@ -29008,10 +28999,10 @@
         <v>29.66</v>
       </c>
       <c r="M547">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N547">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O547">
         <v>1</v>
@@ -29034,7 +29025,7 @@
         <v>206</v>
       </c>
       <c r="E548">
-        <v>-28.92035684878565</v>
+        <v>-29.28437262031398</v>
       </c>
       <c r="F548">
         <v>-1</v>
@@ -29043,10 +29034,10 @@
         <v>0.08786968755353093</v>
       </c>
       <c r="H548">
-        <v>0.08768035684878565</v>
+        <v>0.08840437262031398</v>
       </c>
       <c r="I548">
-        <v>0.3706692952547215</v>
+        <v>0.7346850667830509</v>
       </c>
       <c r="J548">
         <v>4.533464762736053</v>
@@ -29058,10 +29049,10 @@
         <v>29.66</v>
       </c>
       <c r="M548">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N548">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O548">
         <v>1</v>
@@ -29084,7 +29075,7 @@
         <v>206</v>
       </c>
       <c r="E549">
-        <v>-29.70473754464155</v>
+        <v>-30.07607257616231</v>
       </c>
       <c r="F549">
         <v>-1</v>
@@ -29093,10 +29084,10 @@
         <v>0.08865284837272143</v>
       </c>
       <c r="H549">
-        <v>0.08846473754464156</v>
+        <v>0.08919607257616231</v>
       </c>
       <c r="I549">
-        <v>0.3718891719201238</v>
+        <v>0.7432242034408887</v>
       </c>
       <c r="J549">
         <v>4.594458596006342</v>
@@ -29108,10 +29099,10 @@
         <v>29.66</v>
       </c>
       <c r="M549">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N549">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O549">
         <v>1</v>
@@ -29134,7 +29125,7 @@
         <v>206</v>
       </c>
       <c r="E550">
-        <v>-30.20359084153172</v>
+        <v>-30.57958080272799</v>
       </c>
       <c r="F550">
         <v>-1</v>
@@ -29143,10 +29134,10 @@
         <v>0.08915092584799902</v>
       </c>
       <c r="H550">
-        <v>0.08896359084153173</v>
+        <v>0.08969958080272798</v>
       </c>
       <c r="I550">
-        <v>0.3726649935327089</v>
+        <v>0.7486549547289698</v>
       </c>
       <c r="J550">
         <v>4.633249676635438</v>
@@ -29158,10 +29149,10 @@
         <v>29.66</v>
       </c>
       <c r="M550">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N550">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O550">
         <v>1</v>
@@ -29184,7 +29175,7 @@
         <v>206</v>
       </c>
       <c r="E551">
-        <v>-30.51635709583226</v>
+        <v>-30.89526556017906</v>
       </c>
       <c r="F551">
         <v>-1</v>
@@ -29193,10 +29184,10 @@
         <v>0.08946320568510779</v>
       </c>
       <c r="H551">
-        <v>0.08927635709583226</v>
+        <v>0.09001526556017907</v>
       </c>
       <c r="I551">
-        <v>0.3731514107244678</v>
+        <v>0.7520598750712679</v>
       </c>
       <c r="J551">
         <v>4.657570536223348</v>
@@ -29208,10 +29199,10 @@
         <v>29.66</v>
       </c>
       <c r="M551">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N551">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O551">
         <v>1</v>
@@ -29234,7 +29225,7 @@
         <v>206</v>
       </c>
       <c r="E552">
-        <v>-30.98032039084724</v>
+        <v>-31.3635582172004</v>
       </c>
       <c r="F552">
         <v>-1</v>
@@ -29243,10 +29234,10 @@
         <v>0.08992644741978838</v>
       </c>
       <c r="H552">
-        <v>0.08974032039084723</v>
+        <v>0.0904835582172004</v>
       </c>
       <c r="I552">
-        <v>0.3738729710588586</v>
+        <v>0.7571107974120252</v>
       </c>
       <c r="J552">
         <v>4.69364855294302</v>
@@ -29258,10 +29249,10 @@
         <v>29.66</v>
       </c>
       <c r="M552">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N552">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O552">
         <v>1</v>
@@ -29284,7 +29275,7 @@
         <v>206</v>
       </c>
       <c r="E553">
-        <v>-30.85176864739156</v>
+        <v>-31.23380692403908</v>
       </c>
       <c r="F553">
         <v>-1</v>
@@ -29293,10 +29284,10 @@
         <v>0.08979809560128364</v>
       </c>
       <c r="H553">
-        <v>0.08961176864739157</v>
+        <v>0.09035380692403908</v>
       </c>
       <c r="I553">
-        <v>0.3736730461079176</v>
+        <v>0.7557113227554382</v>
       </c>
       <c r="J553">
         <v>4.683652305395922</v>
@@ -29308,10 +29299,10 @@
         <v>29.66</v>
       </c>
       <c r="M553">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N553">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O553">
         <v>1</v>
@@ -29334,7 +29325,7 @@
         <v>206</v>
       </c>
       <c r="E554">
-        <v>-30.01728851794509</v>
+        <v>-30.39154004377351</v>
       </c>
       <c r="F554">
         <v>-1</v>
@@ -29343,10 +29334,10 @@
         <v>0.08896491326364035</v>
       </c>
       <c r="H554">
-        <v>0.08877728851794509</v>
+        <v>0.08951154004377351</v>
       </c>
       <c r="I554">
-        <v>0.3723752543047354</v>
+        <v>0.7466267801331554</v>
       </c>
       <c r="J554">
         <v>4.618762715236787</v>
@@ -29358,10 +29349,10 @@
         <v>29.66</v>
       </c>
       <c r="M554">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N554">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O554">
         <v>1</v>
@@ -29384,7 +29375,7 @@
         <v>206</v>
       </c>
       <c r="E555">
-        <v>-28.23275270207595</v>
+        <v>-28.59035226072674</v>
       </c>
       <c r="F555">
         <v>-1</v>
@@ -29393,10 +29384,10 @@
         <v>0.08718315277563415</v>
       </c>
       <c r="H555">
-        <v>0.08699275270207595</v>
+        <v>0.08771035226072674</v>
       </c>
       <c r="I555">
-        <v>0.3695999264417935</v>
+        <v>0.7271994850925836</v>
       </c>
       <c r="J555">
         <v>4.479996322089887</v>
@@ -29408,10 +29399,10 @@
         <v>29.66</v>
       </c>
       <c r="M555">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N555">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O555">
         <v>1</v>
@@ -29434,7 +29425,7 @@
         <v>206</v>
       </c>
       <c r="E556">
-        <v>-28.44297898688693</v>
+        <v>-28.80254022160128</v>
       </c>
       <c r="F556">
         <v>-1</v>
@@ -29443,10 +29434,10 @@
         <v>0.08739305211443454</v>
       </c>
       <c r="H556">
-        <v>0.08720297898688693</v>
+        <v>0.08792254022160129</v>
       </c>
       <c r="I556">
-        <v>0.369926872452389</v>
+        <v>0.7294881071667376</v>
       </c>
       <c r="J556">
         <v>4.496343622619513</v>
@@ -29458,10 +29449,10 @@
         <v>29.66</v>
       </c>
       <c r="M556">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N556">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O556">
         <v>1</v>
@@ -29484,7 +29475,7 @@
         <v>206</v>
       </c>
       <c r="E557">
-        <v>-28.4738178392523</v>
+        <v>-28.83366683930754</v>
       </c>
       <c r="F557">
         <v>-1</v>
@@ -29493,10 +29484,10 @@
         <v>0.08742384300590976</v>
       </c>
       <c r="H557">
-        <v>0.0872338178392523</v>
+        <v>0.08795366683930753</v>
       </c>
       <c r="I557">
-        <v>0.369974833342539</v>
+        <v>0.7298238333977736</v>
       </c>
       <c r="J557">
         <v>4.498741667126929</v>
@@ -29508,10 +29499,10 @@
         <v>29.66</v>
       </c>
       <c r="M557">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N557">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O557">
         <v>1</v>
@@ -29534,7 +29525,7 @@
         <v>206</v>
       </c>
       <c r="E558">
-        <v>-28.80338230729631</v>
+        <v>-29.16630655899737</v>
       </c>
       <c r="F558">
         <v>-1</v>
@@ -29543,10 +29534,10 @@
         <v>0.0877528949320128</v>
       </c>
       <c r="H558">
-        <v>0.08756338230729631</v>
+        <v>0.08828630655899737</v>
       </c>
       <c r="I558">
-        <v>0.3704873752835098</v>
+        <v>0.7334116269845694</v>
       </c>
       <c r="J558">
         <v>4.524368764175452</v>
@@ -29558,10 +29549,10 @@
         <v>29.66</v>
       </c>
       <c r="M558">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N558">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O558">
         <v>1</v>
@@ -29584,7 +29575,7 @@
         <v>206</v>
       </c>
       <c r="E559">
-        <v>-29.18930252600012</v>
+        <v>-29.55582789949312</v>
       </c>
       <c r="F559">
         <v>-1</v>
@@ -29593,10 +29584,10 @@
         <v>0.08813821496375128</v>
       </c>
       <c r="H559">
-        <v>0.08794930252600011</v>
+        <v>0.08867582789949312</v>
       </c>
       <c r="I559">
-        <v>0.3710875622488317</v>
+        <v>0.7376129357418364</v>
       </c>
       <c r="J559">
         <v>4.554378112441689</v>
@@ -29608,10 +29599,10 @@
         <v>29.66</v>
       </c>
       <c r="M559">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N559">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O559">
         <v>1</v>
@@ -29634,7 +29625,7 @@
         <v>206</v>
       </c>
       <c r="E560">
-        <v>-30.49312565857959</v>
+        <v>-30.87181734435172</v>
       </c>
       <c r="F560">
         <v>-1</v>
@@ -29643,10 +29634,10 @@
         <v>0.08944001037761758</v>
       </c>
       <c r="H560">
-        <v>0.0892531256585796</v>
+        <v>0.08999181734435172</v>
       </c>
       <c r="I560">
-        <v>0.3731152809620184</v>
+        <v>0.7518069667341507</v>
       </c>
       <c r="J560">
         <v>4.655764048101057</v>
@@ -29658,10 +29649,10 @@
         <v>29.66</v>
       </c>
       <c r="M560">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N560">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O560">
         <v>1</v>
@@ -29684,7 +29675,7 @@
         <v>206</v>
       </c>
       <c r="E561">
-        <v>-32.14453464713586</v>
+        <v>-32.53863605908424</v>
       </c>
       <c r="F561">
         <v>-1</v>
@@ -29693,10 +29684,10 @@
         <v>0.09108885107847779</v>
       </c>
       <c r="H561">
-        <v>0.09090453464713585</v>
+        <v>0.09165863605908425</v>
       </c>
       <c r="I561">
-        <v>0.3756835686580722</v>
+        <v>0.7697849806064561</v>
       </c>
       <c r="J561">
         <v>4.784178432903254</v>
@@ -29708,216 +29699,16 @@
         <v>29.66</v>
       </c>
       <c r="M561">
-        <v>12.86</v>
+        <v>12.98</v>
       </c>
       <c r="N561">
-        <v>29.38</v>
+        <v>29.56</v>
       </c>
       <c r="O561">
         <v>1</v>
       </c>
       <c r="P561" t="s">
         <v>429</v>
-      </c>
-    </row>
-    <row r="562" spans="1:16">
-      <c r="A562" s="1">
-        <v>0</v>
-      </c>
-      <c r="B562" t="s">
-        <v>94</v>
-      </c>
-      <c r="C562">
-        <v>-32.58017714229045</v>
-      </c>
-      <c r="D562" t="s">
-        <v>206</v>
-      </c>
-      <c r="E562">
-        <v>-32.95712445871146</v>
-      </c>
-      <c r="F562">
-        <v>-1</v>
-      </c>
-      <c r="G562">
-        <v>0.09190017714229046</v>
-      </c>
-      <c r="H562">
-        <v>0.09171712445871147</v>
-      </c>
-      <c r="I562">
-        <v>0.3769473164210098</v>
-      </c>
-      <c r="J562">
-        <v>4.847365821050658</v>
-      </c>
-      <c r="K562">
-        <v>12.84</v>
-      </c>
-      <c r="L562">
-        <v>29.66</v>
-      </c>
-      <c r="M562">
-        <v>12.86</v>
-      </c>
-      <c r="N562">
-        <v>29.38</v>
-      </c>
-      <c r="O562">
-        <v>1</v>
-      </c>
-      <c r="P562" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="563" spans="1:16">
-      <c r="A563" s="1">
-        <v>0</v>
-      </c>
-      <c r="B563" t="s">
-        <v>94</v>
-      </c>
-      <c r="C563">
-        <v>-33.68902786152971</v>
-      </c>
-      <c r="D563" t="s">
-        <v>206</v>
-      </c>
-      <c r="E563">
-        <v>-34.0677023597564</v>
-      </c>
-      <c r="F563">
-        <v>-1</v>
-      </c>
-      <c r="G563">
-        <v>0.09300902786152972</v>
-      </c>
-      <c r="H563">
-        <v>0.09282770235975639</v>
-      </c>
-      <c r="I563">
-        <v>0.3786744982266868</v>
-      </c>
-      <c r="J563">
-        <v>4.93372491133409</v>
-      </c>
-      <c r="K563">
-        <v>12.84</v>
-      </c>
-      <c r="L563">
-        <v>29.66</v>
-      </c>
-      <c r="M563">
-        <v>12.86</v>
-      </c>
-      <c r="N563">
-        <v>29.38</v>
-      </c>
-      <c r="O563">
-        <v>1</v>
-      </c>
-      <c r="P563" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="564" spans="1:16">
-      <c r="A564" s="1">
-        <v>0</v>
-      </c>
-      <c r="B564" t="s">
-        <v>94</v>
-      </c>
-      <c r="C564">
-        <v>-34.60679521565862</v>
-      </c>
-      <c r="D564" t="s">
-        <v>206</v>
-      </c>
-      <c r="E564">
-        <v>-34.98689925805061</v>
-      </c>
-      <c r="F564">
-        <v>-1</v>
-      </c>
-      <c r="G564">
-        <v>0.09392679521565862</v>
-      </c>
-      <c r="H564">
-        <v>0.0937468992580506</v>
-      </c>
-      <c r="I564">
-        <v>0.3801040423919915</v>
-      </c>
-      <c r="J564">
-        <v>5.005202119599581</v>
-      </c>
-      <c r="K564">
-        <v>12.84</v>
-      </c>
-      <c r="L564">
-        <v>29.66</v>
-      </c>
-      <c r="M564">
-        <v>12.86</v>
-      </c>
-      <c r="N564">
-        <v>29.38</v>
-      </c>
-      <c r="O564">
-        <v>1</v>
-      </c>
-      <c r="P564" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="565" spans="1:16">
-      <c r="A565" s="1">
-        <v>0</v>
-      </c>
-      <c r="B565" t="s">
-        <v>94</v>
-      </c>
-      <c r="C565">
-        <v>-35.35321635201397</v>
-      </c>
-      <c r="D565" t="s">
-        <v>206</v>
-      </c>
-      <c r="E565">
-        <v>-35.73448304415106</v>
-      </c>
-      <c r="F565">
-        <v>-1</v>
-      </c>
-      <c r="G565">
-        <v>0.09467321635201396</v>
-      </c>
-      <c r="H565">
-        <v>0.09449448304415106</v>
-      </c>
-      <c r="I565">
-        <v>0.3812666921370891</v>
-      </c>
-      <c r="J565">
-        <v>5.063334606854671</v>
-      </c>
-      <c r="K565">
-        <v>12.84</v>
-      </c>
-      <c r="L565">
-        <v>29.66</v>
-      </c>
-      <c r="M565">
-        <v>12.86</v>
-      </c>
-      <c r="N565">
-        <v>29.38</v>
-      </c>
-      <c r="O565">
-        <v>1</v>
-      </c>
-      <c r="P565" t="s">
-        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="426">
   <si>
     <t>trade_time</t>
   </si>
@@ -634,7 +634,7 @@
     <t>2021-05-14</t>
   </si>
   <si>
-    <t>2021-08-24</t>
+    <t>2021-08-25</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1292,18 +1292,6 @@
   </si>
   <si>
     <t>2021-01-26</t>
-  </si>
-  <si>
-    <t>2021-01-27</t>
-  </si>
-  <si>
-    <t>2021-01-28</t>
-  </si>
-  <si>
-    <t>2021-01-29</t>
-  </si>
-  <si>
-    <t>2021-02-01</t>
   </si>
 </sst>
 </file>
@@ -1661,7 +1649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P561"/>
+  <dimension ref="A1:P556"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28569,28 +28557,28 @@
         <v>94</v>
       </c>
       <c r="C539">
-        <v>-10.28452075330963</v>
+        <v>-12.90519447650706</v>
       </c>
       <c r="D539" t="s">
         <v>206</v>
       </c>
       <c r="E539">
-        <v>-10.82005291105601</v>
+        <v>-13.55930095833813</v>
       </c>
       <c r="F539">
         <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.06960452075330963</v>
+        <v>0.07222519447650706</v>
       </c>
       <c r="H539">
-        <v>0.069940052911056</v>
+        <v>0.07249930095833812</v>
       </c>
       <c r="I539">
-        <v>0.5355321577463741</v>
+        <v>0.6541064818310751</v>
       </c>
       <c r="J539">
-        <v>3.11094398390262</v>
+        <v>3.315046298793385</v>
       </c>
       <c r="K539">
         <v>12.84</v>
@@ -28602,13 +28590,13 @@
         <v>12.98</v>
       </c>
       <c r="N539">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O539">
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>199</v>
+        <v>409</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28619,28 +28607,28 @@
         <v>94</v>
       </c>
       <c r="C540">
-        <v>-12.90519447650706</v>
+        <v>-14.93671190899163</v>
       </c>
       <c r="D540" t="s">
         <v>206</v>
       </c>
       <c r="E540">
-        <v>-13.46930095833813</v>
+        <v>-15.61296889242301</v>
       </c>
       <c r="F540">
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.07222519447650706</v>
+        <v>0.07425671190899163</v>
       </c>
       <c r="H540">
-        <v>0.07258930095833813</v>
+        <v>0.07455296889242299</v>
       </c>
       <c r="I540">
-        <v>0.5641064818310753</v>
+        <v>0.6762569834313759</v>
       </c>
       <c r="J540">
-        <v>3.315046298793385</v>
+        <v>3.47326416736695</v>
       </c>
       <c r="K540">
         <v>12.84</v>
@@ -28652,13 +28640,13 @@
         <v>12.98</v>
       </c>
       <c r="N540">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O540">
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28669,28 +28657,28 @@
         <v>94</v>
       </c>
       <c r="C541">
-        <v>-14.93671190899163</v>
+        <v>-17.70411238403614</v>
       </c>
       <c r="D541" t="s">
         <v>206</v>
       </c>
       <c r="E541">
-        <v>-15.52296889242301</v>
+        <v>-18.41054351594931</v>
       </c>
       <c r="F541">
         <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.07425671190899163</v>
+        <v>0.07702411238403614</v>
       </c>
       <c r="H541">
-        <v>0.074642968892423</v>
+        <v>0.07735054351594932</v>
       </c>
       <c r="I541">
-        <v>0.586256983431376</v>
+        <v>0.706431131913174</v>
       </c>
       <c r="J541">
-        <v>3.47326416736695</v>
+        <v>3.688793799379762</v>
       </c>
       <c r="K541">
         <v>12.84</v>
@@ -28702,13 +28690,13 @@
         <v>12.98</v>
       </c>
       <c r="N541">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28719,28 +28707,28 @@
         <v>94</v>
       </c>
       <c r="C542">
-        <v>-17.70411238403614</v>
+        <v>-20.27114356180867</v>
       </c>
       <c r="D542" t="s">
         <v>206</v>
       </c>
       <c r="E542">
-        <v>-18.32054351594931</v>
+        <v>-21.00556413023961</v>
       </c>
       <c r="F542">
         <v>-1</v>
       </c>
       <c r="G542">
-        <v>0.07702411238403614</v>
+        <v>0.07959114356180869</v>
       </c>
       <c r="H542">
-        <v>0.07744054351594931</v>
+        <v>0.07994556413023961</v>
       </c>
       <c r="I542">
-        <v>0.6164311319131741</v>
+        <v>0.7344205684309379</v>
       </c>
       <c r="J542">
-        <v>3.688793799379762</v>
+        <v>3.888718345935255</v>
       </c>
       <c r="K542">
         <v>12.84</v>
@@ -28752,13 +28740,13 @@
         <v>12.98</v>
       </c>
       <c r="N542">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28769,28 +28757,28 @@
         <v>94</v>
       </c>
       <c r="C543">
-        <v>-20.27114356180867</v>
+        <v>-21.58445273359039</v>
       </c>
       <c r="D543" t="s">
         <v>206</v>
       </c>
       <c r="E543">
-        <v>-20.91556413023961</v>
+        <v>-22.33319287243017</v>
       </c>
       <c r="F543">
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.07959114356180869</v>
+        <v>0.08090445273359038</v>
       </c>
       <c r="H543">
-        <v>0.08003556413023961</v>
+        <v>0.08127319287243018</v>
       </c>
       <c r="I543">
-        <v>0.6444205684309381</v>
+        <v>0.748740138839775</v>
       </c>
       <c r="J543">
-        <v>3.888718345935255</v>
+        <v>3.991000991712648</v>
       </c>
       <c r="K543">
         <v>12.84</v>
@@ -28802,13 +28790,13 @@
         <v>12.98</v>
       </c>
       <c r="N543">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28819,28 +28807,28 @@
         <v>94</v>
       </c>
       <c r="C544">
-        <v>-21.58445273359039</v>
+        <v>-22.72017499184188</v>
       </c>
       <c r="D544" t="s">
         <v>206</v>
       </c>
       <c r="E544">
-        <v>-22.24319287243017</v>
+        <v>-23.48129839517971</v>
       </c>
       <c r="F544">
         <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.08090445273359038</v>
+        <v>0.08204017499184188</v>
       </c>
       <c r="H544">
-        <v>0.08136319287243016</v>
+        <v>0.08242129839517973</v>
       </c>
       <c r="I544">
-        <v>0.6587401388397751</v>
+        <v>0.7611234033378373</v>
       </c>
       <c r="J544">
-        <v>3.991000991712648</v>
+        <v>4.07945288098457</v>
       </c>
       <c r="K544">
         <v>12.84</v>
@@ -28852,13 +28840,13 @@
         <v>12.98</v>
       </c>
       <c r="N544">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O544">
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -28869,28 +28857,28 @@
         <v>94</v>
       </c>
       <c r="C545">
-        <v>-22.72017499184188</v>
+        <v>-24.32217137422709</v>
       </c>
       <c r="D545" t="s">
         <v>206</v>
       </c>
       <c r="E545">
-        <v>-23.39129839517971</v>
+        <v>-25.10076202784016</v>
       </c>
       <c r="F545">
         <v>-1</v>
       </c>
       <c r="G545">
-        <v>0.08204017499184188</v>
+        <v>0.0836421713742271</v>
       </c>
       <c r="H545">
-        <v>0.08251129839517971</v>
+        <v>0.08404076202784017</v>
       </c>
       <c r="I545">
-        <v>0.6711234033378375</v>
+        <v>0.778590653613076</v>
       </c>
       <c r="J545">
-        <v>4.07945288098457</v>
+        <v>4.204218954379057</v>
       </c>
       <c r="K545">
         <v>12.84</v>
@@ -28902,13 +28890,13 @@
         <v>12.98</v>
       </c>
       <c r="N545">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O545">
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -28919,28 +28907,28 @@
         <v>94</v>
       </c>
       <c r="C546">
-        <v>-24.32217137422709</v>
+        <v>-26.36953395501449</v>
       </c>
       <c r="D546" t="s">
         <v>206</v>
       </c>
       <c r="E546">
-        <v>-25.01076202784016</v>
+        <v>-27.17044787664237</v>
       </c>
       <c r="F546">
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.0836421713742271</v>
+        <v>0.08568953395501448</v>
       </c>
       <c r="H546">
-        <v>0.08413076202784016</v>
+        <v>0.08611044787664238</v>
       </c>
       <c r="I546">
-        <v>0.6885906536130761</v>
+        <v>0.8009139216278847</v>
       </c>
       <c r="J546">
-        <v>4.204218954379057</v>
+        <v>4.363670868770599</v>
       </c>
       <c r="K546">
         <v>12.84</v>
@@ -28952,13 +28940,13 @@
         <v>12.98</v>
       </c>
       <c r="N546">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -28969,28 +28957,28 @@
         <v>94</v>
       </c>
       <c r="C547">
-        <v>-26.36953395501449</v>
+        <v>-28.54968755353093</v>
       </c>
       <c r="D547" t="s">
         <v>206</v>
       </c>
       <c r="E547">
-        <v>-27.08044787664237</v>
+        <v>-29.37437262031398</v>
       </c>
       <c r="F547">
         <v>-1</v>
       </c>
       <c r="G547">
-        <v>0.08568953395501448</v>
+        <v>0.08786968755353093</v>
       </c>
       <c r="H547">
-        <v>0.08620044787664237</v>
+        <v>0.08831437262031398</v>
       </c>
       <c r="I547">
-        <v>0.7109139216278848</v>
+        <v>0.8246850667830508</v>
       </c>
       <c r="J547">
-        <v>4.363670868770599</v>
+        <v>4.533464762736053</v>
       </c>
       <c r="K547">
         <v>12.84</v>
@@ -29002,13 +28990,13 @@
         <v>12.98</v>
       </c>
       <c r="N547">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O547">
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29019,28 +29007,28 @@
         <v>94</v>
       </c>
       <c r="C548">
-        <v>-28.54968755353093</v>
+        <v>-29.33284837272143</v>
       </c>
       <c r="D548" t="s">
         <v>206</v>
       </c>
       <c r="E548">
-        <v>-29.28437262031398</v>
+        <v>-30.16607257616231</v>
       </c>
       <c r="F548">
         <v>-1</v>
       </c>
       <c r="G548">
-        <v>0.08786968755353093</v>
+        <v>0.08865284837272143</v>
       </c>
       <c r="H548">
-        <v>0.08840437262031398</v>
+        <v>0.08910607257616232</v>
       </c>
       <c r="I548">
-        <v>0.7346850667830509</v>
+        <v>0.8332242034408885</v>
       </c>
       <c r="J548">
-        <v>4.533464762736053</v>
+        <v>4.594458596006342</v>
       </c>
       <c r="K548">
         <v>12.84</v>
@@ -29052,13 +29040,13 @@
         <v>12.98</v>
       </c>
       <c r="N548">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O548">
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29069,28 +29057,28 @@
         <v>94</v>
       </c>
       <c r="C549">
-        <v>-29.33284837272143</v>
+        <v>-29.83092584799902</v>
       </c>
       <c r="D549" t="s">
         <v>206</v>
       </c>
       <c r="E549">
-        <v>-30.07607257616231</v>
+        <v>-30.66958080272799</v>
       </c>
       <c r="F549">
         <v>-1</v>
       </c>
       <c r="G549">
-        <v>0.08865284837272143</v>
+        <v>0.08915092584799902</v>
       </c>
       <c r="H549">
-        <v>0.08919607257616231</v>
+        <v>0.08960958080272798</v>
       </c>
       <c r="I549">
-        <v>0.7432242034408887</v>
+        <v>0.8386549547289697</v>
       </c>
       <c r="J549">
-        <v>4.594458596006342</v>
+        <v>4.633249676635438</v>
       </c>
       <c r="K549">
         <v>12.84</v>
@@ -29102,13 +29090,13 @@
         <v>12.98</v>
       </c>
       <c r="N549">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O549">
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>418</v>
+        <v>92</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29119,28 +29107,28 @@
         <v>94</v>
       </c>
       <c r="C550">
-        <v>-29.83092584799902</v>
+        <v>-30.14320568510779</v>
       </c>
       <c r="D550" t="s">
         <v>206</v>
       </c>
       <c r="E550">
-        <v>-30.57958080272799</v>
+        <v>-30.98526556017906</v>
       </c>
       <c r="F550">
         <v>-1</v>
       </c>
       <c r="G550">
-        <v>0.08915092584799902</v>
+        <v>0.08946320568510779</v>
       </c>
       <c r="H550">
-        <v>0.08969958080272798</v>
+        <v>0.08992526556017906</v>
       </c>
       <c r="I550">
-        <v>0.7486549547289698</v>
+        <v>0.8420598750712678</v>
       </c>
       <c r="J550">
-        <v>4.633249676635438</v>
+        <v>4.657570536223348</v>
       </c>
       <c r="K550">
         <v>12.84</v>
@@ -29152,13 +29140,13 @@
         <v>12.98</v>
       </c>
       <c r="N550">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O550">
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>92</v>
+        <v>419</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29169,28 +29157,28 @@
         <v>94</v>
       </c>
       <c r="C551">
-        <v>-30.14320568510779</v>
+        <v>-30.60644741978838</v>
       </c>
       <c r="D551" t="s">
         <v>206</v>
       </c>
       <c r="E551">
-        <v>-30.89526556017906</v>
+        <v>-31.4535582172004</v>
       </c>
       <c r="F551">
         <v>-1</v>
       </c>
       <c r="G551">
-        <v>0.08946320568510779</v>
+        <v>0.08992644741978838</v>
       </c>
       <c r="H551">
-        <v>0.09001526556017907</v>
+        <v>0.0903935582172004</v>
       </c>
       <c r="I551">
-        <v>0.7520598750712679</v>
+        <v>0.8471107974120251</v>
       </c>
       <c r="J551">
-        <v>4.657570536223348</v>
+        <v>4.69364855294302</v>
       </c>
       <c r="K551">
         <v>12.84</v>
@@ -29202,13 +29190,13 @@
         <v>12.98</v>
       </c>
       <c r="N551">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O551">
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29219,28 +29207,28 @@
         <v>94</v>
       </c>
       <c r="C552">
-        <v>-30.60644741978838</v>
+        <v>-30.47809560128364</v>
       </c>
       <c r="D552" t="s">
         <v>206</v>
       </c>
       <c r="E552">
-        <v>-31.3635582172004</v>
+        <v>-31.32380692403908</v>
       </c>
       <c r="F552">
         <v>-1</v>
       </c>
       <c r="G552">
-        <v>0.08992644741978838</v>
+        <v>0.08979809560128364</v>
       </c>
       <c r="H552">
-        <v>0.0904835582172004</v>
+        <v>0.09026380692403907</v>
       </c>
       <c r="I552">
-        <v>0.7571107974120252</v>
+        <v>0.845711322755438</v>
       </c>
       <c r="J552">
-        <v>4.69364855294302</v>
+        <v>4.683652305395922</v>
       </c>
       <c r="K552">
         <v>12.84</v>
@@ -29252,13 +29240,13 @@
         <v>12.98</v>
       </c>
       <c r="N552">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O552">
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29269,28 +29257,28 @@
         <v>94</v>
       </c>
       <c r="C553">
-        <v>-30.47809560128364</v>
+        <v>-29.64491326364035</v>
       </c>
       <c r="D553" t="s">
         <v>206</v>
       </c>
       <c r="E553">
-        <v>-31.23380692403908</v>
+        <v>-30.48154004377351</v>
       </c>
       <c r="F553">
         <v>-1</v>
       </c>
       <c r="G553">
-        <v>0.08979809560128364</v>
+        <v>0.08896491326364035</v>
       </c>
       <c r="H553">
-        <v>0.09035380692403908</v>
+        <v>0.08942154004377351</v>
       </c>
       <c r="I553">
-        <v>0.7557113227554382</v>
+        <v>0.8366267801331553</v>
       </c>
       <c r="J553">
-        <v>4.683652305395922</v>
+        <v>4.618762715236787</v>
       </c>
       <c r="K553">
         <v>12.84</v>
@@ -29302,13 +29290,13 @@
         <v>12.98</v>
       </c>
       <c r="N553">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O553">
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29319,28 +29307,28 @@
         <v>94</v>
       </c>
       <c r="C554">
-        <v>-29.64491326364035</v>
+        <v>-27.86315277563415</v>
       </c>
       <c r="D554" t="s">
         <v>206</v>
       </c>
       <c r="E554">
-        <v>-30.39154004377351</v>
+        <v>-28.68035226072674</v>
       </c>
       <c r="F554">
         <v>-1</v>
       </c>
       <c r="G554">
-        <v>0.08896491326364035</v>
+        <v>0.08718315277563415</v>
       </c>
       <c r="H554">
-        <v>0.08951154004377351</v>
+        <v>0.08762035226072673</v>
       </c>
       <c r="I554">
-        <v>0.7466267801331554</v>
+        <v>0.8171994850925834</v>
       </c>
       <c r="J554">
-        <v>4.618762715236787</v>
+        <v>4.479996322089887</v>
       </c>
       <c r="K554">
         <v>12.84</v>
@@ -29352,13 +29340,13 @@
         <v>12.98</v>
       </c>
       <c r="N554">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O554">
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29369,28 +29357,28 @@
         <v>94</v>
       </c>
       <c r="C555">
-        <v>-27.86315277563415</v>
+        <v>-28.07305211443454</v>
       </c>
       <c r="D555" t="s">
         <v>206</v>
       </c>
       <c r="E555">
-        <v>-28.59035226072674</v>
+        <v>-28.89254022160128</v>
       </c>
       <c r="F555">
         <v>-1</v>
       </c>
       <c r="G555">
-        <v>0.08718315277563415</v>
+        <v>0.08739305211443454</v>
       </c>
       <c r="H555">
-        <v>0.08771035226072674</v>
+        <v>0.08783254022160128</v>
       </c>
       <c r="I555">
-        <v>0.7271994850925836</v>
+        <v>0.8194881071667375</v>
       </c>
       <c r="J555">
-        <v>4.479996322089887</v>
+        <v>4.496343622619513</v>
       </c>
       <c r="K555">
         <v>12.84</v>
@@ -29402,13 +29390,13 @@
         <v>12.98</v>
       </c>
       <c r="N555">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O555">
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29419,28 +29407,28 @@
         <v>94</v>
       </c>
       <c r="C556">
-        <v>-28.07305211443454</v>
+        <v>-28.10384300590976</v>
       </c>
       <c r="D556" t="s">
         <v>206</v>
       </c>
       <c r="E556">
-        <v>-28.80254022160128</v>
+        <v>-28.92366683930754</v>
       </c>
       <c r="F556">
         <v>-1</v>
       </c>
       <c r="G556">
-        <v>0.08739305211443454</v>
+        <v>0.08742384300590976</v>
       </c>
       <c r="H556">
-        <v>0.08792254022160129</v>
+        <v>0.08786366683930755</v>
       </c>
       <c r="I556">
-        <v>0.7294881071667376</v>
+        <v>0.8198238333977734</v>
       </c>
       <c r="J556">
-        <v>4.496343622619513</v>
+        <v>4.498741667126929</v>
       </c>
       <c r="K556">
         <v>12.84</v>
@@ -29452,263 +29440,13 @@
         <v>12.98</v>
       </c>
       <c r="N556">
-        <v>29.56</v>
+        <v>29.47</v>
       </c>
       <c r="O556">
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="557" spans="1:16">
-      <c r="A557" s="1">
-        <v>0</v>
-      </c>
-      <c r="B557" t="s">
-        <v>94</v>
-      </c>
-      <c r="C557">
-        <v>-28.10384300590976</v>
-      </c>
-      <c r="D557" t="s">
-        <v>206</v>
-      </c>
-      <c r="E557">
-        <v>-28.83366683930754</v>
-      </c>
-      <c r="F557">
-        <v>-1</v>
-      </c>
-      <c r="G557">
-        <v>0.08742384300590976</v>
-      </c>
-      <c r="H557">
-        <v>0.08795366683930753</v>
-      </c>
-      <c r="I557">
-        <v>0.7298238333977736</v>
-      </c>
-      <c r="J557">
-        <v>4.498741667126929</v>
-      </c>
-      <c r="K557">
-        <v>12.84</v>
-      </c>
-      <c r="L557">
-        <v>29.66</v>
-      </c>
-      <c r="M557">
-        <v>12.98</v>
-      </c>
-      <c r="N557">
-        <v>29.56</v>
-      </c>
-      <c r="O557">
-        <v>1</v>
-      </c>
-      <c r="P557" t="s">
         <v>425</v>
-      </c>
-    </row>
-    <row r="558" spans="1:16">
-      <c r="A558" s="1">
-        <v>0</v>
-      </c>
-      <c r="B558" t="s">
-        <v>94</v>
-      </c>
-      <c r="C558">
-        <v>-28.4328949320128</v>
-      </c>
-      <c r="D558" t="s">
-        <v>206</v>
-      </c>
-      <c r="E558">
-        <v>-29.16630655899737</v>
-      </c>
-      <c r="F558">
-        <v>-1</v>
-      </c>
-      <c r="G558">
-        <v>0.0877528949320128</v>
-      </c>
-      <c r="H558">
-        <v>0.08828630655899737</v>
-      </c>
-      <c r="I558">
-        <v>0.7334116269845694</v>
-      </c>
-      <c r="J558">
-        <v>4.524368764175452</v>
-      </c>
-      <c r="K558">
-        <v>12.84</v>
-      </c>
-      <c r="L558">
-        <v>29.66</v>
-      </c>
-      <c r="M558">
-        <v>12.98</v>
-      </c>
-      <c r="N558">
-        <v>29.56</v>
-      </c>
-      <c r="O558">
-        <v>1</v>
-      </c>
-      <c r="P558" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="559" spans="1:16">
-      <c r="A559" s="1">
-        <v>0</v>
-      </c>
-      <c r="B559" t="s">
-        <v>94</v>
-      </c>
-      <c r="C559">
-        <v>-28.81821496375128</v>
-      </c>
-      <c r="D559" t="s">
-        <v>206</v>
-      </c>
-      <c r="E559">
-        <v>-29.55582789949312</v>
-      </c>
-      <c r="F559">
-        <v>-1</v>
-      </c>
-      <c r="G559">
-        <v>0.08813821496375128</v>
-      </c>
-      <c r="H559">
-        <v>0.08867582789949312</v>
-      </c>
-      <c r="I559">
-        <v>0.7376129357418364</v>
-      </c>
-      <c r="J559">
-        <v>4.554378112441689</v>
-      </c>
-      <c r="K559">
-        <v>12.84</v>
-      </c>
-      <c r="L559">
-        <v>29.66</v>
-      </c>
-      <c r="M559">
-        <v>12.98</v>
-      </c>
-      <c r="N559">
-        <v>29.56</v>
-      </c>
-      <c r="O559">
-        <v>1</v>
-      </c>
-      <c r="P559" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="560" spans="1:16">
-      <c r="A560" s="1">
-        <v>0</v>
-      </c>
-      <c r="B560" t="s">
-        <v>94</v>
-      </c>
-      <c r="C560">
-        <v>-30.12001037761757</v>
-      </c>
-      <c r="D560" t="s">
-        <v>206</v>
-      </c>
-      <c r="E560">
-        <v>-30.87181734435172</v>
-      </c>
-      <c r="F560">
-        <v>-1</v>
-      </c>
-      <c r="G560">
-        <v>0.08944001037761758</v>
-      </c>
-      <c r="H560">
-        <v>0.08999181734435172</v>
-      </c>
-      <c r="I560">
-        <v>0.7518069667341507</v>
-      </c>
-      <c r="J560">
-        <v>4.655764048101057</v>
-      </c>
-      <c r="K560">
-        <v>12.84</v>
-      </c>
-      <c r="L560">
-        <v>29.66</v>
-      </c>
-      <c r="M560">
-        <v>12.98</v>
-      </c>
-      <c r="N560">
-        <v>29.56</v>
-      </c>
-      <c r="O560">
-        <v>1</v>
-      </c>
-      <c r="P560" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="561" spans="1:16">
-      <c r="A561" s="1">
-        <v>0</v>
-      </c>
-      <c r="B561" t="s">
-        <v>94</v>
-      </c>
-      <c r="C561">
-        <v>-31.76885107847778</v>
-      </c>
-      <c r="D561" t="s">
-        <v>206</v>
-      </c>
-      <c r="E561">
-        <v>-32.53863605908424</v>
-      </c>
-      <c r="F561">
-        <v>-1</v>
-      </c>
-      <c r="G561">
-        <v>0.09108885107847779</v>
-      </c>
-      <c r="H561">
-        <v>0.09165863605908425</v>
-      </c>
-      <c r="I561">
-        <v>0.7697849806064561</v>
-      </c>
-      <c r="J561">
-        <v>4.784178432903254</v>
-      </c>
-      <c r="K561">
-        <v>12.84</v>
-      </c>
-      <c r="L561">
-        <v>29.66</v>
-      </c>
-      <c r="M561">
-        <v>12.98</v>
-      </c>
-      <c r="N561">
-        <v>29.56</v>
-      </c>
-      <c r="O561">
-        <v>1</v>
-      </c>
-      <c r="P561" t="s">
-        <v>429</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="423">
   <si>
     <t>trade_time</t>
   </si>
@@ -634,7 +634,7 @@
     <t>2021-05-14</t>
   </si>
   <si>
-    <t>2021-08-25</t>
+    <t>2021-08-26</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1283,15 +1283,6 @@
   </si>
   <si>
     <t>2021-01-21</t>
-  </si>
-  <si>
-    <t>2021-01-22</t>
-  </si>
-  <si>
-    <t>2021-01-25</t>
-  </si>
-  <si>
-    <t>2021-01-26</t>
   </si>
 </sst>
 </file>
@@ -1649,7 +1640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P556"/>
+  <dimension ref="A1:P553"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28563,7 +28554,7 @@
         <v>206</v>
       </c>
       <c r="E539">
-        <v>-13.55930095833813</v>
+        <v>-13.9966991063864</v>
       </c>
       <c r="F539">
         <v>-1</v>
@@ -28572,10 +28563,10 @@
         <v>0.07222519447650706</v>
       </c>
       <c r="H539">
-        <v>0.07249930095833812</v>
+        <v>0.07179669910638641</v>
       </c>
       <c r="I539">
-        <v>0.6541064818310751</v>
+        <v>1.091504629879342</v>
       </c>
       <c r="J539">
         <v>3.315046298793385</v>
@@ -28587,10 +28578,10 @@
         <v>29.66</v>
       </c>
       <c r="M539">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N539">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28613,7 +28604,7 @@
         <v>206</v>
       </c>
       <c r="E540">
-        <v>-15.61296889242301</v>
+        <v>-16.04403832572833</v>
       </c>
       <c r="F540">
         <v>-1</v>
@@ -28622,10 +28613,10 @@
         <v>0.07425671190899163</v>
       </c>
       <c r="H540">
-        <v>0.07455296889242299</v>
+        <v>0.07384403832572832</v>
       </c>
       <c r="I540">
-        <v>0.6762569834313759</v>
+        <v>1.107326416736701</v>
       </c>
       <c r="J540">
         <v>3.47326416736695</v>
@@ -28637,10 +28628,10 @@
         <v>29.66</v>
       </c>
       <c r="M540">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N540">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28663,7 +28654,7 @@
         <v>206</v>
       </c>
       <c r="E541">
-        <v>-18.41054351594931</v>
+        <v>-18.83299176397412</v>
       </c>
       <c r="F541">
         <v>-1</v>
@@ -28672,10 +28663,10 @@
         <v>0.07702411238403614</v>
       </c>
       <c r="H541">
-        <v>0.07735054351594932</v>
+        <v>0.07663299176397412</v>
       </c>
       <c r="I541">
-        <v>0.706431131913174</v>
+        <v>1.128879379937981</v>
       </c>
       <c r="J541">
         <v>3.688793799379762</v>
@@ -28687,10 +28678,10 @@
         <v>29.66</v>
       </c>
       <c r="M541">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N541">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28713,7 +28704,7 @@
         <v>206</v>
       </c>
       <c r="E542">
-        <v>-21.00556413023961</v>
+        <v>-21.4200153964022</v>
       </c>
       <c r="F542">
         <v>-1</v>
@@ -28722,10 +28713,10 @@
         <v>0.07959114356180869</v>
       </c>
       <c r="H542">
-        <v>0.07994556413023961</v>
+        <v>0.07922001539640221</v>
       </c>
       <c r="I542">
-        <v>0.7344205684309379</v>
+        <v>1.148871834593525</v>
       </c>
       <c r="J542">
         <v>3.888718345935255</v>
@@ -28737,10 +28728,10 @@
         <v>29.66</v>
       </c>
       <c r="M542">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N542">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28763,7 +28754,7 @@
         <v>206</v>
       </c>
       <c r="E543">
-        <v>-22.33319287243017</v>
+        <v>-22.74355283276166</v>
       </c>
       <c r="F543">
         <v>-1</v>
@@ -28772,10 +28763,10 @@
         <v>0.08090445273359038</v>
       </c>
       <c r="H543">
-        <v>0.08127319287243018</v>
+        <v>0.08054355283276167</v>
       </c>
       <c r="I543">
-        <v>0.748740138839775</v>
+        <v>1.159100099171265</v>
       </c>
       <c r="J543">
         <v>3.991000991712648</v>
@@ -28787,10 +28778,10 @@
         <v>29.66</v>
       </c>
       <c r="M543">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N543">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28813,7 +28804,7 @@
         <v>206</v>
       </c>
       <c r="E544">
-        <v>-23.48129839517971</v>
+        <v>-23.88812027994033</v>
       </c>
       <c r="F544">
         <v>-1</v>
@@ -28822,10 +28813,10 @@
         <v>0.08204017499184188</v>
       </c>
       <c r="H544">
-        <v>0.08242129839517973</v>
+        <v>0.08168812027994034</v>
       </c>
       <c r="I544">
-        <v>0.7611234033378373</v>
+        <v>1.167945288098455</v>
       </c>
       <c r="J544">
         <v>4.07945288098457</v>
@@ -28837,10 +28828,10 @@
         <v>29.66</v>
       </c>
       <c r="M544">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N544">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28863,7 +28854,7 @@
         <v>206</v>
       </c>
       <c r="E545">
-        <v>-25.10076202784016</v>
+        <v>-25.50259326966499</v>
       </c>
       <c r="F545">
         <v>-1</v>
@@ -28872,10 +28863,10 @@
         <v>0.0836421713742271</v>
       </c>
       <c r="H545">
-        <v>0.08404076202784017</v>
+        <v>0.08330259326966498</v>
       </c>
       <c r="I545">
-        <v>0.778590653613076</v>
+        <v>1.180421895437906</v>
       </c>
       <c r="J545">
         <v>4.204218954379057</v>
@@ -28887,10 +28878,10 @@
         <v>29.66</v>
       </c>
       <c r="M545">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N545">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28913,7 +28904,7 @@
         <v>206</v>
       </c>
       <c r="E546">
-        <v>-27.17044787664237</v>
+        <v>-27.56590104189154</v>
       </c>
       <c r="F546">
         <v>-1</v>
@@ -28922,10 +28913,10 @@
         <v>0.08568953395501448</v>
       </c>
       <c r="H546">
-        <v>0.08611044787664238</v>
+        <v>0.08536590104189154</v>
       </c>
       <c r="I546">
-        <v>0.8009139216278847</v>
+        <v>1.196367086877057</v>
       </c>
       <c r="J546">
         <v>4.363670868770599</v>
@@ -28937,10 +28928,10 @@
         <v>29.66</v>
       </c>
       <c r="M546">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N546">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O546">
         <v>1</v>
@@ -28963,7 +28954,7 @@
         <v>206</v>
       </c>
       <c r="E547">
-        <v>-29.37437262031398</v>
+        <v>-29.76303402980453</v>
       </c>
       <c r="F547">
         <v>-1</v>
@@ -28972,10 +28963,10 @@
         <v>0.08786968755353093</v>
       </c>
       <c r="H547">
-        <v>0.08831437262031398</v>
+        <v>0.08756303402980453</v>
       </c>
       <c r="I547">
-        <v>0.8246850667830508</v>
+        <v>1.213346476273603</v>
       </c>
       <c r="J547">
         <v>4.533464762736053</v>
@@ -28987,10 +28978,10 @@
         <v>29.66</v>
       </c>
       <c r="M547">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N547">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O547">
         <v>1</v>
@@ -29013,7 +29004,7 @@
         <v>206</v>
       </c>
       <c r="E548">
-        <v>-30.16607257616231</v>
+        <v>-30.55229423232206</v>
       </c>
       <c r="F548">
         <v>-1</v>
@@ -29022,10 +29013,10 @@
         <v>0.08865284837272143</v>
       </c>
       <c r="H548">
-        <v>0.08910607257616232</v>
+        <v>0.08835229423232206</v>
       </c>
       <c r="I548">
-        <v>0.8332242034408885</v>
+        <v>1.219445859600636</v>
       </c>
       <c r="J548">
         <v>4.594458596006342</v>
@@ -29037,10 +29028,10 @@
         <v>29.66</v>
       </c>
       <c r="M548">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N548">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O548">
         <v>1</v>
@@ -29063,7 +29054,7 @@
         <v>206</v>
       </c>
       <c r="E549">
-        <v>-30.66958080272799</v>
+        <v>-31.05425081566256</v>
       </c>
       <c r="F549">
         <v>-1</v>
@@ -29072,10 +29063,10 @@
         <v>0.08915092584799902</v>
       </c>
       <c r="H549">
-        <v>0.08960958080272798</v>
+        <v>0.08885425081566257</v>
       </c>
       <c r="I549">
-        <v>0.8386549547289697</v>
+        <v>1.223324967663547</v>
       </c>
       <c r="J549">
         <v>4.633249676635438</v>
@@ -29087,10 +29078,10 @@
         <v>29.66</v>
       </c>
       <c r="M549">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N549">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O549">
         <v>1</v>
@@ -29113,7 +29104,7 @@
         <v>206</v>
       </c>
       <c r="E550">
-        <v>-30.98526556017906</v>
+        <v>-31.36896273873013</v>
       </c>
       <c r="F550">
         <v>-1</v>
@@ -29122,10 +29113,10 @@
         <v>0.08946320568510779</v>
       </c>
       <c r="H550">
-        <v>0.08992526556017906</v>
+        <v>0.08916896273873014</v>
       </c>
       <c r="I550">
-        <v>0.8420598750712678</v>
+        <v>1.225757053622335</v>
       </c>
       <c r="J550">
         <v>4.657570536223348</v>
@@ -29137,10 +29128,10 @@
         <v>29.66</v>
       </c>
       <c r="M550">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N550">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O550">
         <v>1</v>
@@ -29163,7 +29154,7 @@
         <v>206</v>
       </c>
       <c r="E551">
-        <v>-31.4535582172004</v>
+        <v>-31.83581227508267</v>
       </c>
       <c r="F551">
         <v>-1</v>
@@ -29172,10 +29163,10 @@
         <v>0.08992644741978838</v>
       </c>
       <c r="H551">
-        <v>0.0903935582172004</v>
+        <v>0.08963581227508267</v>
       </c>
       <c r="I551">
-        <v>0.8471107974120251</v>
+        <v>1.229364855294296</v>
       </c>
       <c r="J551">
         <v>4.69364855294302</v>
@@ -29187,10 +29178,10 @@
         <v>29.66</v>
       </c>
       <c r="M551">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N551">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O551">
         <v>1</v>
@@ -29213,7 +29204,7 @@
         <v>206</v>
       </c>
       <c r="E552">
-        <v>-31.32380692403908</v>
+        <v>-31.70646083182324</v>
       </c>
       <c r="F552">
         <v>-1</v>
@@ -29222,10 +29213,10 @@
         <v>0.08979809560128364</v>
       </c>
       <c r="H552">
-        <v>0.09026380692403907</v>
+        <v>0.08950646083182323</v>
       </c>
       <c r="I552">
-        <v>0.845711322755438</v>
+        <v>1.228365230539598</v>
       </c>
       <c r="J552">
         <v>4.683652305395922</v>
@@ -29237,10 +29228,10 @@
         <v>29.66</v>
       </c>
       <c r="M552">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N552">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O552">
         <v>1</v>
@@ -29263,7 +29254,7 @@
         <v>206</v>
       </c>
       <c r="E553">
-        <v>-30.48154004377351</v>
+        <v>-30.86678953516403</v>
       </c>
       <c r="F553">
         <v>-1</v>
@@ -29272,10 +29263,10 @@
         <v>0.08896491326364035</v>
       </c>
       <c r="H553">
-        <v>0.08942154004377351</v>
+        <v>0.08866678953516403</v>
       </c>
       <c r="I553">
-        <v>0.8366267801331553</v>
+        <v>1.22187627152368</v>
       </c>
       <c r="J553">
         <v>4.618762715236787</v>
@@ -29287,166 +29278,16 @@
         <v>29.66</v>
       </c>
       <c r="M553">
-        <v>12.98</v>
+        <v>12.94</v>
       </c>
       <c r="N553">
-        <v>29.47</v>
+        <v>28.9</v>
       </c>
       <c r="O553">
         <v>1</v>
       </c>
       <c r="P553" t="s">
         <v>422</v>
-      </c>
-    </row>
-    <row r="554" spans="1:16">
-      <c r="A554" s="1">
-        <v>0</v>
-      </c>
-      <c r="B554" t="s">
-        <v>94</v>
-      </c>
-      <c r="C554">
-        <v>-27.86315277563415</v>
-      </c>
-      <c r="D554" t="s">
-        <v>206</v>
-      </c>
-      <c r="E554">
-        <v>-28.68035226072674</v>
-      </c>
-      <c r="F554">
-        <v>-1</v>
-      </c>
-      <c r="G554">
-        <v>0.08718315277563415</v>
-      </c>
-      <c r="H554">
-        <v>0.08762035226072673</v>
-      </c>
-      <c r="I554">
-        <v>0.8171994850925834</v>
-      </c>
-      <c r="J554">
-        <v>4.479996322089887</v>
-      </c>
-      <c r="K554">
-        <v>12.84</v>
-      </c>
-      <c r="L554">
-        <v>29.66</v>
-      </c>
-      <c r="M554">
-        <v>12.98</v>
-      </c>
-      <c r="N554">
-        <v>29.47</v>
-      </c>
-      <c r="O554">
-        <v>1</v>
-      </c>
-      <c r="P554" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="555" spans="1:16">
-      <c r="A555" s="1">
-        <v>0</v>
-      </c>
-      <c r="B555" t="s">
-        <v>94</v>
-      </c>
-      <c r="C555">
-        <v>-28.07305211443454</v>
-      </c>
-      <c r="D555" t="s">
-        <v>206</v>
-      </c>
-      <c r="E555">
-        <v>-28.89254022160128</v>
-      </c>
-      <c r="F555">
-        <v>-1</v>
-      </c>
-      <c r="G555">
-        <v>0.08739305211443454</v>
-      </c>
-      <c r="H555">
-        <v>0.08783254022160128</v>
-      </c>
-      <c r="I555">
-        <v>0.8194881071667375</v>
-      </c>
-      <c r="J555">
-        <v>4.496343622619513</v>
-      </c>
-      <c r="K555">
-        <v>12.84</v>
-      </c>
-      <c r="L555">
-        <v>29.66</v>
-      </c>
-      <c r="M555">
-        <v>12.98</v>
-      </c>
-      <c r="N555">
-        <v>29.47</v>
-      </c>
-      <c r="O555">
-        <v>1</v>
-      </c>
-      <c r="P555" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="556" spans="1:16">
-      <c r="A556" s="1">
-        <v>0</v>
-      </c>
-      <c r="B556" t="s">
-        <v>94</v>
-      </c>
-      <c r="C556">
-        <v>-28.10384300590976</v>
-      </c>
-      <c r="D556" t="s">
-        <v>206</v>
-      </c>
-      <c r="E556">
-        <v>-28.92366683930754</v>
-      </c>
-      <c r="F556">
-        <v>-1</v>
-      </c>
-      <c r="G556">
-        <v>0.08742384300590976</v>
-      </c>
-      <c r="H556">
-        <v>0.08786366683930755</v>
-      </c>
-      <c r="I556">
-        <v>0.8198238333977734</v>
-      </c>
-      <c r="J556">
-        <v>4.498741667126929</v>
-      </c>
-      <c r="K556">
-        <v>12.84</v>
-      </c>
-      <c r="L556">
-        <v>29.66</v>
-      </c>
-      <c r="M556">
-        <v>12.98</v>
-      </c>
-      <c r="N556">
-        <v>29.47</v>
-      </c>
-      <c r="O556">
-        <v>1</v>
-      </c>
-      <c r="P556" t="s">
-        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="417">
   <si>
     <t>trade_time</t>
   </si>
@@ -295,6 +295,9 @@
     <t>2021-01-15</t>
   </si>
   <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
     <t>2021-03-19</t>
   </si>
   <si>
@@ -634,7 +637,7 @@
     <t>2021-05-14</t>
   </si>
   <si>
-    <t>2021-08-26</t>
+    <t>2021-08-30</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1243,12 +1246,6 @@
     <t>2020-12-18</t>
   </si>
   <si>
-    <t>2020-12-31</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
     <t>2021-01-05</t>
   </si>
   <si>
@@ -1268,21 +1265,6 @@
   </si>
   <si>
     <t>2021-01-13</t>
-  </si>
-  <si>
-    <t>2021-01-14</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-01-19</t>
-  </si>
-  <si>
-    <t>2021-01-20</t>
-  </si>
-  <si>
-    <t>2021-01-21</t>
   </si>
 </sst>
 </file>
@@ -1640,7 +1622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P553"/>
+  <dimension ref="A1:P546"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1701,7 +1683,7 @@
         <v>7.937839468679289</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2">
         <v>5.219520382832306</v>
@@ -1737,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1751,7 +1733,7 @@
         <v>3.136690364271253</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3">
         <v>5.635410691649231</v>
@@ -1787,7 +1769,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1801,7 +1783,7 @@
         <v>2.638216954758501</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4">
         <v>5.635410691649231</v>
@@ -1837,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1851,7 +1833,7 @@
         <v>3.237530821347761</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5">
         <v>5.635410691649231</v>
@@ -1887,7 +1869,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1901,7 +1883,7 @@
         <v>3.230584002322257</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E6">
         <v>5.635410691649231</v>
@@ -1937,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1951,7 +1933,7 @@
         <v>3.256004230860512</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7">
         <v>5.635410691649231</v>
@@ -1987,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2001,7 +1983,7 @@
         <v>3.286004230860513</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E8">
         <v>5.635410691649231</v>
@@ -2037,7 +2019,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2051,7 +2033,7 @@
         <v>7.640037484949179</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E9">
         <v>4.941353694732751</v>
@@ -2087,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2101,7 +2083,7 @@
         <v>2.786527592192993</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10">
         <v>5.320918706633144</v>
@@ -2137,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2151,7 +2133,7 @@
         <v>2.28641790804436</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>5.320918706633144</v>
@@ -2187,7 +2169,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2201,7 +2183,7 @@
         <v>2.897185697084776</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E12">
         <v>5.320918706633144</v>
@@ -2237,7 +2219,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2251,7 +2233,7 @@
         <v>2.886966328787512</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E13">
         <v>5.320918706633144</v>
@@ -2287,7 +2269,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2301,7 +2283,7 @@
         <v>2.917295381233409</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E14">
         <v>5.320918706633144</v>
@@ -2337,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2351,7 +2333,7 @@
         <v>2.94729538123341</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15">
         <v>5.320918706633144</v>
@@ -2387,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2401,7 +2383,7 @@
         <v>7.265164792922025</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E16">
         <v>4.591197883498596</v>
@@ -2437,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2451,7 +2433,7 @@
         <v>2.345743218051176</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E17">
         <v>4.925036665931941</v>
@@ -2487,7 +2469,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2501,7 +2483,7 @@
         <v>1.843573793836459</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18">
         <v>4.925036665931941</v>
@@ -2537,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2551,7 +2533,7 @@
         <v>2.468759763339456</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E19">
         <v>4.925036665931941</v>
@@ -2587,7 +2569,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2601,7 +2583,7 @@
         <v>2.454420914910028</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E20">
         <v>4.925036665931941</v>
@@ -2637,7 +2619,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2651,7 +2633,7 @@
         <v>2.490929187554173</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E21">
         <v>4.925036665931941</v>
@@ -2687,7 +2669,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2701,7 +2683,7 @@
         <v>2.520929187554174</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E22">
         <v>4.925036665931941</v>
@@ -2737,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2751,7 +2733,7 @@
         <v>1.980046625394046</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E23">
         <v>4.596593277573533</v>
@@ -2801,7 +2783,7 @@
         <v>1.476168338596821</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E24">
         <v>4.596593277573533</v>
@@ -2851,7 +2833,7 @@
         <v>2.113316346177388</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E25">
         <v>4.596593277573533</v>
@@ -2901,7 +2883,7 @@
         <v>2.095559772582941</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E26">
         <v>4.596593277573533</v>
@@ -2951,7 +2933,7 @@
         <v>2.137194632974616</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E27">
         <v>4.596593277573533</v>
@@ -3001,7 +2983,7 @@
         <v>2.167194632974617</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E28">
         <v>4.596593277573533</v>
@@ -3051,7 +3033,7 @@
         <v>2.844772647031224</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E29">
         <v>5.373230386726174</v>
@@ -3087,7 +3069,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3101,7 +3083,7 @@
         <v>2.344935136036042</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E30">
         <v>5.373230386726174</v>
@@ -3137,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3151,7 +3133,7 @@
         <v>2.953797713002309</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E31">
         <v>5.373230386726174</v>
@@ -3187,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3201,7 +3183,7 @@
         <v>2.944122691011945</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E32">
         <v>5.373230386726174</v>
@@ -3237,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3251,7 +3233,7 @@
         <v>2.973635223997491</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E33">
         <v>5.373230386726174</v>
@@ -3287,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3301,7 +3283,7 @@
         <v>3.003635223997492</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E34">
         <v>5.373230386726174</v>
@@ -3337,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3351,7 +3333,7 @@
         <v>7.289203935514355</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E35">
         <v>5.128184916132415</v>
@@ -3387,7 +3369,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3401,7 +3383,7 @@
         <v>-2.117497474419014</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E36">
         <v>0.8991929718719938</v>
@@ -3437,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3451,7 +3433,7 @@
         <v>-2.80975033090947</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E37">
         <v>0.2758434229577951</v>
@@ -3487,7 +3469,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3501,7 +3483,7 @@
         <v>-2.902998496046035</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E38">
         <v>0.1918767030952893</v>
@@ -3537,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3551,7 +3533,7 @@
         <v>-2.830339867902396</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E39">
         <v>0.2573032631353307</v>
@@ -3587,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3601,7 +3583,7 @@
         <v>-2.537341046304341</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E40">
         <v>0.5211384810952531</v>
@@ -3637,7 +3619,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3651,7 +3633,7 @@
         <v>-2.336644974997025</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E41">
         <v>0.7018582922817487</v>
@@ -3687,7 +3669,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3701,7 +3683,7 @@
         <v>-2.249226521683095</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E42">
         <v>0.7018582922817487</v>
@@ -3737,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3751,7 +3733,7 @@
         <v>-1.845740644766149</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E43">
         <v>1.143900517084994</v>
@@ -3787,7 +3769,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3801,7 +3783,7 @@
         <v>-1.76174710538406</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E44">
         <v>1.143900517084994</v>
@@ -3837,7 +3819,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3887,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3901,7 +3883,7 @@
         <v>-1.483754394543759</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E46">
         <v>1.469856507982922</v>
@@ -3937,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3951,7 +3933,7 @@
         <v>-1.402286340628343</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E47">
         <v>1.469856507982922</v>
@@ -3987,7 +3969,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4037,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4051,7 +4033,7 @@
         <v>-1.119201343261796</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E49">
         <v>1.798123813695423</v>
@@ -4087,7 +4069,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4101,7 +4083,7 @@
         <v>-1.040276682727416</v>
       </c>
       <c r="D50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E50">
         <v>1.798123813695423</v>
@@ -4137,7 +4119,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4151,7 +4133,7 @@
         <v>-0.970418309242234</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E51">
         <v>-1.315795006570312</v>
@@ -4187,7 +4169,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4201,7 +4183,7 @@
         <v>-1.094604783790125</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E52">
         <v>1.627274602785022</v>
@@ -4237,7 +4219,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4251,7 +4233,7 @@
         <v>-1.015851727159035</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E53">
         <v>1.627274602785022</v>
@@ -4287,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4301,7 +4283,7 @@
         <v>-1.190513514023774</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E54">
         <v>-1.147995174237213</v>
@@ -4337,7 +4319,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4351,7 +4333,7 @@
         <v>-1.15006863091817</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E55">
         <v>1.577640908889972</v>
@@ -4387,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4401,7 +4383,7 @@
         <v>-1.255522302285485</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E56">
         <v>-0.5624021926528435</v>
@@ -4437,7 +4419,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4451,7 +4433,7 @@
         <v>-1.320960230949986</v>
       </c>
       <c r="D57" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E57">
         <v>1.424712797977779</v>
@@ -4487,7 +4469,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4501,7 +4483,7 @@
         <v>-1.455823154415796</v>
       </c>
       <c r="D58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E58">
         <v>-0.3493885347260317</v>
@@ -4537,7 +4519,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4551,7 +4533,7 @@
         <v>-1.605480846937454</v>
       </c>
       <c r="D59" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E59">
         <v>-0.7894370781288025</v>
@@ -4587,7 +4569,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4601,7 +4583,7 @@
         <v>-1.761773123733541</v>
       </c>
       <c r="D60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E60">
         <v>-1.128596969277446</v>
@@ -4637,7 +4619,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4651,7 +4633,7 @@
         <v>-1.457944364792599</v>
       </c>
       <c r="D61" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E61">
         <v>-0.8017368070151889</v>
@@ -4687,7 +4669,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4701,7 +4683,7 @@
         <v>-1.234076514305805</v>
       </c>
       <c r="D62" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E62">
         <v>0.01703472753200685</v>
@@ -4737,7 +4719,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4751,7 +4733,7 @@
         <v>-0.7963224235233177</v>
       </c>
       <c r="D63" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E63">
         <v>0.2870665855800212</v>
@@ -4787,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4801,7 +4783,7 @@
         <v>-0.8942517780380754</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E64">
         <v>0.59890656545236</v>
@@ -4837,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4851,7 +4833,7 @@
         <v>-0.899307304101125</v>
       </c>
       <c r="D65" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E65">
         <v>0.6876116265245429</v>
@@ -4887,7 +4869,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4901,7 +4883,7 @@
         <v>-0.8589383918075626</v>
       </c>
       <c r="D66" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E66">
         <v>0.8335609313842731</v>
@@ -4937,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4951,7 +4933,7 @@
         <v>-0.6533981903373771</v>
       </c>
       <c r="D67" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E67">
         <v>1.169788560028703</v>
@@ -4987,7 +4969,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5001,7 +4983,7 @@
         <v>4.835153534210221</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E68">
         <v>2.04429947322755</v>
@@ -5037,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5051,7 +5033,7 @@
         <v>-0.406918334342155</v>
       </c>
       <c r="D69" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E69">
         <v>1.312995819177061</v>
@@ -5087,7 +5069,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5101,7 +5083,7 @@
         <v>0.04130730968482865</v>
       </c>
       <c r="D70" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E70">
         <v>2.64378384364354</v>
@@ -5137,7 +5119,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5151,7 +5133,7 @@
         <v>5.033791575296075</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E71">
         <v>2.275021568455536</v>
@@ -5187,7 +5169,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5201,7 +5183,7 @@
         <v>-0.1691188742298735</v>
       </c>
       <c r="D72" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E72">
         <v>1.79275039480164</v>
@@ -5237,7 +5219,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5251,7 +5233,7 @@
         <v>0.2293541709380591</v>
       </c>
       <c r="D73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E73">
         <v>2.812063918551083</v>
@@ -5287,7 +5269,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5301,7 +5283,7 @@
         <v>5.217902572011447</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E74">
         <v>2.488870208345837</v>
@@ -5337,7 +5319,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5351,7 +5333,7 @@
         <v>0.0512895398901918</v>
       </c>
       <c r="D75" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E75">
         <v>1.57274123510015</v>
@@ -5387,7 +5369,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5401,7 +5383,7 @@
         <v>0.3237189931323456</v>
       </c>
       <c r="D76" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E76">
         <v>2.896509461761223</v>
@@ -5437,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5451,7 +5433,7 @@
         <v>5.3102923165319</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E77">
         <v>2.596182761957483</v>
@@ -5487,7 +5469,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5501,7 +5483,7 @@
         <v>0.161893889624892</v>
       </c>
       <c r="D78" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E78">
         <v>1.501333830022219</v>
@@ -5537,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5551,7 +5533,7 @@
         <v>5.33023415169577</v>
       </c>
       <c r="D79" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E79">
         <v>2.619345606126444</v>
@@ -5587,7 +5569,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5601,7 +5583,7 @@
         <v>0.1857672504861512</v>
       </c>
       <c r="D80" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E80">
         <v>1.155646098159064</v>
@@ -5637,7 +5619,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5651,7 +5633,7 @@
         <v>5.37850629613547</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E81">
         <v>2.675414676508897</v>
@@ -5687,7 +5669,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5701,7 +5683,7 @@
         <v>0.243556231003037</v>
       </c>
       <c r="D82" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E82">
         <v>1.799674337820232</v>
@@ -5737,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5751,7 +5733,7 @@
         <v>5.505970450595548</v>
       </c>
       <c r="D83" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E83">
         <v>2.823466865418581</v>
@@ -5787,7 +5769,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5801,7 +5783,7 @@
         <v>0.3961498981001377</v>
       </c>
       <c r="D84" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E84">
         <v>1.846556155176511</v>
@@ -5837,7 +5819,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5851,7 +5833,7 @@
         <v>5.552898822755296</v>
       </c>
       <c r="D85" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E85">
         <v>2.877975117167079</v>
@@ -5887,7 +5869,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5901,7 +5883,7 @@
         <v>0.4523301821108561</v>
       </c>
       <c r="D86" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E86">
         <v>2.714577056552891</v>
@@ -5937,7 +5919,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5951,7 +5933,7 @@
         <v>0.844003460842476</v>
       </c>
       <c r="D87" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E87">
         <v>3.182739844457025</v>
@@ -5987,7 +5969,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6001,7 +5983,7 @@
         <v>5.819687109336471</v>
       </c>
       <c r="D88" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E88">
         <v>2.897855098492958</v>
@@ -6037,7 +6019,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6051,7 +6033,7 @@
         <v>0.7717156843363</v>
       </c>
       <c r="D89" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E89">
         <v>3.232403806926722</v>
@@ -6087,7 +6069,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6101,7 +6083,7 @@
         <v>2.174557955758587</v>
       </c>
       <c r="D90" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E90">
         <v>4.552795119478848</v>
@@ -6137,7 +6119,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6151,7 +6133,7 @@
         <v>2.230502900253292</v>
       </c>
       <c r="D91" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E91">
         <v>4.552795119478848</v>
@@ -6187,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6201,7 +6183,7 @@
         <v>7.122392789242706</v>
       </c>
       <c r="D92" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E92">
         <v>4.410974047362672</v>
@@ -6237,7 +6219,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6251,7 +6233,7 @@
         <v>3.377229031968387</v>
       </c>
       <c r="D93" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E93">
         <v>5.847002514367812</v>
@@ -6287,7 +6269,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6301,7 +6283,7 @@
         <v>3.424783248024418</v>
       </c>
       <c r="D94" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E94">
         <v>5.847002514367812</v>
@@ -6337,7 +6319,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6351,7 +6333,7 @@
         <v>8.29989168013649</v>
       </c>
       <c r="D95" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E95">
         <v>5.631180854885052</v>
@@ -6387,7 +6369,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6401,7 +6383,7 @@
         <v>4.683694888843547</v>
       </c>
       <c r="D96" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E96">
         <v>7.023429444093537</v>
@@ -6437,7 +6419,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6451,7 +6433,7 @@
         <v>4.722134226828356</v>
       </c>
       <c r="D97" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E97">
         <v>7.023429444093537</v>
@@ -6487,7 +6469,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6501,7 +6483,7 @@
         <v>9.579012902797984</v>
       </c>
       <c r="D98" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E98">
         <v>6.893347467132109</v>
@@ -6537,7 +6519,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6551,7 +6533,7 @@
         <v>3.961474621504259</v>
       </c>
       <c r="D99" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E99">
         <v>6.476706188649629</v>
@@ -6587,7 +6569,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6601,7 +6583,7 @@
         <v>8.320444610292363</v>
       </c>
       <c r="D100" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E100">
         <v>7.021567248362409</v>
@@ -6637,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6651,7 +6633,7 @@
         <v>8.530866989040167</v>
       </c>
       <c r="D101" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E101">
         <v>7.021567248362409</v>
@@ -6687,7 +6669,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6701,7 +6683,7 @@
         <v>3.2890165208482</v>
       </c>
       <c r="D102" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E102">
         <v>5.857937357507026</v>
@@ -6737,7 +6719,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6751,7 +6733,7 @@
         <v>7.698991315674085</v>
       </c>
       <c r="D103" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E103">
         <v>6.277165792762322</v>
@@ -6787,7 +6769,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6801,7 +6783,7 @@
         <v>7.862435583597616</v>
       </c>
       <c r="D104" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E104">
         <v>6.277165792762322</v>
@@ -6837,7 +6819,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6851,7 +6833,7 @@
         <v>2.706415003086228</v>
       </c>
       <c r="D105" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E105">
         <v>5.321850930983533</v>
@@ -6887,7 +6869,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6901,7 +6883,7 @@
         <v>7.160579134588669</v>
       </c>
       <c r="D106" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E106">
         <v>5.783497068837448</v>
@@ -6937,7 +6919,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6951,7 +6933,7 @@
         <v>7.283322697678528</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E107">
         <v>5.783497068837448</v>
@@ -6987,7 +6969,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7001,7 +6983,7 @@
         <v>2.25250194719996</v>
       </c>
       <c r="D108" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E108">
         <v>4.90417843844148</v>
@@ -7037,7 +7019,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7051,7 +7033,7 @@
         <v>6.741094613879405</v>
       </c>
       <c r="D109" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E109">
         <v>5.766049754225914</v>
@@ -7087,7 +7069,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7101,7 +7083,7 @@
         <v>6.83212768404308</v>
       </c>
       <c r="D110" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E110">
         <v>5.766049754225914</v>
@@ -7137,7 +7119,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7151,7 +7133,7 @@
         <v>1.648635956687475</v>
       </c>
       <c r="D111" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E111">
         <v>4.348525301462924</v>
@@ -7187,7 +7169,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7201,7 +7183,7 @@
         <v>6.183030834224155</v>
       </c>
       <c r="D112" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E112">
         <v>5.350064030791522</v>
@@ -7237,7 +7219,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7251,7 +7233,7 @@
         <v>6.231877657545638</v>
       </c>
       <c r="D113" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E113">
         <v>5.350064030791522</v>
@@ -7287,7 +7269,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7301,7 +7283,7 @@
         <v>1.432518806234409</v>
       </c>
       <c r="D114" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E114">
         <v>4.149663013321483</v>
@@ -7337,7 +7319,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7351,7 +7333,7 @@
         <v>5.983305802967131</v>
       </c>
       <c r="D115" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E115">
         <v>4.577912304600769</v>
@@ -7387,7 +7369,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7401,7 +7383,7 @@
         <v>6.017054621765944</v>
       </c>
       <c r="D116" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E116">
         <v>4.577912304600769</v>
@@ -7437,7 +7419,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7451,7 +7433,7 @@
         <v>1.226728012835469</v>
       </c>
       <c r="D117" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E117">
         <v>3.960302622589126</v>
@@ -7487,7 +7469,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7501,7 +7483,7 @@
         <v>5.793123892101445</v>
       </c>
       <c r="D118" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E118">
         <v>4.612872778687663</v>
@@ -7537,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7551,7 +7533,7 @@
         <v>5.812496108566997</v>
       </c>
       <c r="D119" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E119">
         <v>4.612872778687663</v>
@@ -7587,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7601,7 +7583,7 @@
         <v>1.216947853386511</v>
       </c>
       <c r="D120" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E120">
         <v>3.951303314193975</v>
@@ -7637,7 +7619,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7651,7 +7633,7 @@
         <v>5.802774512947074</v>
       </c>
       <c r="D121" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E121">
         <v>4.403561129870987</v>
@@ -7687,7 +7669,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7701,7 +7683,7 @@
         <v>1.177523163430447</v>
       </c>
       <c r="D122" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E122">
         <v>3.915026304074722</v>
@@ -7737,7 +7719,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7751,7 +7733,7 @@
         <v>5.763585898978771</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E123">
         <v>4.466025047817013</v>
@@ -7787,7 +7769,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7801,7 +7783,7 @@
         <v>0.9680478903759173</v>
       </c>
       <c r="D124" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E124">
         <v>3.722275603719158</v>
@@ -7837,7 +7819,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7851,7 +7833,7 @@
         <v>0.8515262832029507</v>
       </c>
       <c r="D125" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E125">
         <v>3.61505711887537</v>
@@ -7887,7 +7869,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7901,7 +7883,7 @@
         <v>0.6675490824101864</v>
       </c>
       <c r="D126" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E126">
         <v>3.445768716549093</v>
@@ -7937,7 +7919,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7951,7 +7933,7 @@
         <v>0.2453647773980379</v>
       </c>
       <c r="D127" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E127">
         <v>3.057291741278434</v>
@@ -7987,7 +7969,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8001,7 +7983,7 @@
         <v>-0.1442597189068877</v>
       </c>
       <c r="D128" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E128">
         <v>2.69877498918947</v>
@@ -8037,7 +8019,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8051,7 +8033,7 @@
         <v>3.671796227407118</v>
       </c>
       <c r="D129" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E129">
         <v>1.089748757437874</v>
@@ -8087,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8101,7 +8083,7 @@
         <v>-1.239097601114093</v>
       </c>
       <c r="D130" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E130">
         <v>1.261882831716061</v>
@@ -8137,7 +8119,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8151,7 +8133,7 @@
         <v>3.066548753992304</v>
       </c>
       <c r="D131" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E131">
         <v>0.4140568037443764</v>
@@ -8187,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8201,7 +8183,7 @@
         <v>-1.959356470902271</v>
       </c>
       <c r="D132" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E132">
         <v>0.6034425874785647</v>
@@ -8237,7 +8219,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8251,7 +8233,7 @@
         <v>2.434653904799742</v>
       </c>
       <c r="D133" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E133">
         <v>-0.2913840017675113</v>
@@ -8287,7 +8269,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8301,7 +8283,7 @@
         <v>-2.711326350820261</v>
       </c>
       <c r="D134" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E134">
         <v>-0.08398696342450762</v>
@@ -8337,7 +8319,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8351,7 +8333,7 @@
         <v>2.046949385277987</v>
       </c>
       <c r="D135" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E135">
         <v>-0.7242132753428656</v>
@@ -8387,7 +8369,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8401,7 +8383,7 @@
         <v>-3.172703938184629</v>
       </c>
       <c r="D136" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E136">
         <v>-0.5057652768234711</v>
@@ -8437,7 +8419,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8451,7 +8433,7 @@
         <v>1.727381390460117</v>
       </c>
       <c r="D137" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E137">
         <v>0.5925973930511788</v>
@@ -8487,7 +8469,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8501,7 +8483,7 @@
         <v>1.685047495782005</v>
       </c>
       <c r="D138" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E138">
         <v>-1.128236762428639</v>
@@ -8537,7 +8519,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8551,7 +8533,7 @@
         <v>-3.603375782929252</v>
       </c>
       <c r="D139" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E139">
         <v>-0.8994732706219501</v>
@@ -8587,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8601,7 +8583,7 @@
         <v>1.329375274458599</v>
       </c>
       <c r="D140" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E140">
         <v>-0.02169112718700106</v>
@@ -8637,7 +8619,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8651,7 +8633,7 @@
         <v>1.370767088004978</v>
       </c>
       <c r="D141" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E141">
         <v>-1.479096125030072</v>
@@ -8687,7 +8669,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8701,7 +8683,7 @@
         <v>-3.977376933276734</v>
       </c>
       <c r="D142" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E142">
         <v>-1.241374521837809</v>
@@ -8737,7 +8719,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8751,7 +8733,7 @@
         <v>0.9837414768320834</v>
       </c>
       <c r="D143" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E143">
         <v>-0.5624929319466254</v>
@@ -8787,7 +8769,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8801,7 +8783,7 @@
         <v>-4.274892307557078</v>
       </c>
       <c r="D144" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E144">
         <v>-1.513354644433413</v>
@@ -8851,7 +8833,7 @@
         <v>0.7087921389242986</v>
       </c>
       <c r="D145" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E145">
         <v>-0.01219137097330147</v>
@@ -8901,7 +8883,7 @@
         <v>-6.600419867221269</v>
       </c>
       <c r="D146" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E146">
         <v>-3.935750603200287</v>
@@ -8937,7 +8919,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8951,7 +8933,7 @@
         <v>-1.740049190571469</v>
       </c>
       <c r="D147" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E147">
         <v>-3.803035064283293</v>
@@ -8987,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9001,7 +8983,7 @@
         <v>-7.356943655480499</v>
       </c>
       <c r="D148" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E148">
         <v>-4.634314907681588</v>
@@ -9037,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9051,7 +9033,7 @@
         <v>-2.446239742918287</v>
       </c>
       <c r="D149" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E149">
         <v>-3.284642996427294</v>
@@ -9087,7 +9069,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9101,7 +9083,7 @@
         <v>-2.764549545202325</v>
       </c>
       <c r="D150" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E150">
         <v>-3.284642996427294</v>
@@ -9137,7 +9119,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9151,7 +9133,7 @@
         <v>-8.273062059554213</v>
       </c>
       <c r="D151" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E151">
         <v>-5.480246821120623</v>
@@ -9187,7 +9169,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9201,7 +9183,7 @@
         <v>-3.301406720914517</v>
       </c>
       <c r="D152" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E152">
         <v>-3.80770165872979</v>
@@ -9237,7 +9219,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9251,7 +9233,7 @@
         <v>-3.640798600667189</v>
       </c>
       <c r="D153" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E153">
         <v>-3.80770165872979</v>
@@ -9287,7 +9269,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9301,7 +9283,7 @@
         <v>-9.028638086965721</v>
       </c>
       <c r="D154" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E154">
         <v>-6.177935975464312</v>
@@ -9337,7 +9319,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9351,7 +9333,7 @@
         <v>-4.006712569082914</v>
       </c>
       <c r="D155" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E155">
         <v>-5.764446572941544</v>
@@ -9387,7 +9369,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9401,7 +9383,7 @@
         <v>-4.355244481425245</v>
       </c>
       <c r="D156" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E156">
         <v>-5.764446572941544</v>
@@ -9437,7 +9419,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9451,7 +9433,7 @@
         <v>-9.288472736223071</v>
       </c>
       <c r="D157" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E157">
         <v>-6.4178639378834</v>
@@ -9487,7 +9469,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9501,7 +9483,7 @@
         <v>-4.249259832401776</v>
       </c>
       <c r="D158" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E158">
         <v>-5.572990039214197</v>
@@ -9537,7 +9519,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9551,7 +9533,7 @@
         <v>-4.600934905823827</v>
       </c>
       <c r="D159" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E159">
         <v>-5.572990039214197</v>
@@ -9587,7 +9569,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9601,7 +9583,7 @@
         <v>-8.391360480599353</v>
       </c>
       <c r="D160" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E160">
         <v>-5.589482056682467</v>
@@ -9637,7 +9619,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9651,7 +9633,7 @@
         <v>-3.41183448088206</v>
       </c>
       <c r="D161" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E161">
         <v>-4.236414237755341</v>
@@ -9687,7 +9669,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9701,7 +9683,7 @@
         <v>-3.752657389921566</v>
       </c>
       <c r="D162" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E162">
         <v>-4.236414237755341</v>
@@ -9737,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9751,7 +9733,7 @@
         <v>-7.284701623181299</v>
       </c>
       <c r="D163" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E163">
         <v>-4.567607547211761</v>
@@ -9787,7 +9769,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9801,7 +9783,7 @@
         <v>-2.378804136155122</v>
       </c>
       <c r="D164" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E164">
         <v>-3.182992288094191</v>
@@ -9837,7 +9819,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9887,7 +9869,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9937,7 +9919,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9951,7 +9933,7 @@
         <v>15.30025538505301</v>
       </c>
       <c r="D167" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E167">
         <v>12.2194473505381</v>
@@ -9987,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10001,7 +9983,7 @@
         <v>16.08154605938966</v>
       </c>
       <c r="D168" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E168">
         <v>12.2194473505381</v>
@@ -10037,7 +10019,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10087,7 +10069,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10137,7 +10119,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10187,7 +10169,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10237,7 +10219,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10287,7 +10269,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10337,7 +10319,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10387,7 +10369,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10437,7 +10419,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10487,7 +10469,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10537,7 +10519,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10551,7 +10533,7 @@
         <v>-2.965774048910724</v>
       </c>
       <c r="D179" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E179">
         <v>-6.323583762599906</v>
@@ -10587,7 +10569,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10601,7 +10583,7 @@
         <v>-3.841273412039687</v>
       </c>
       <c r="D180" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E180">
         <v>-6.323583762599906</v>
@@ -10637,7 +10619,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10687,7 +10669,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10701,7 +10683,7 @@
         <v>-4.596644143057084</v>
       </c>
       <c r="D182" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E182">
         <v>-7.87451662725034</v>
@@ -10737,7 +10719,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10751,7 +10733,7 @@
         <v>-5.499155847289916</v>
       </c>
       <c r="D183" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E183">
         <v>-7.87451662725034</v>
@@ -10787,7 +10769,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10837,7 +10819,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10851,7 +10833,7 @@
         <v>-6.176260919928573</v>
       </c>
       <c r="D185" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E185">
         <v>-9.588220956609884</v>
@@ -10887,7 +10869,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10901,7 +10883,7 @@
         <v>-7.104936049037125</v>
       </c>
       <c r="D186" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E186">
         <v>-9.588220956609884</v>
@@ -10937,7 +10919,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10987,7 +10969,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11037,7 +11019,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11051,7 +11033,7 @@
         <v>-5.957065888688689</v>
       </c>
       <c r="D189" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E189">
         <v>-9.35041930781134</v>
@@ -11087,7 +11069,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11101,7 +11083,7 @@
         <v>-6.882110458273605</v>
       </c>
       <c r="D190" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E190">
         <v>-9.35041930781134</v>
@@ -11137,7 +11119,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11151,7 +11133,7 @@
         <v>-5.75373473480284</v>
       </c>
       <c r="D191" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E191">
         <v>-9.129828159496252</v>
@@ -11201,7 +11183,7 @@
         <v>-6.675411500596677</v>
       </c>
       <c r="D192" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E192">
         <v>-9.129828159496252</v>
@@ -11251,7 +11233,7 @@
         <v>4.036863233290944</v>
       </c>
       <c r="D193" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E193">
         <v>1.091137151603181</v>
@@ -11301,7 +11283,7 @@
         <v>4.353212181898559</v>
       </c>
       <c r="D194" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E194">
         <v>1.091137151603181</v>
@@ -11351,7 +11333,7 @@
         <v>4.092859462531468</v>
       </c>
       <c r="D195" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E195">
         <v>1.091137151603181</v>
@@ -11437,7 +11419,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11487,7 +11469,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11637,7 +11619,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11687,7 +11669,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11737,7 +11719,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11787,7 +11769,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11837,7 +11819,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11887,7 +11869,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11937,7 +11919,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11987,7 +11969,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12037,7 +12019,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12087,7 +12069,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12137,7 +12119,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12187,7 +12169,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12237,7 +12219,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12287,7 +12269,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12337,7 +12319,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12351,7 +12333,7 @@
         <v>2.797016608461103</v>
       </c>
       <c r="D215" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E215">
         <v>-0.1302387600075896</v>
@@ -12387,7 +12369,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12401,7 +12383,7 @@
         <v>3.23804287129742</v>
       </c>
       <c r="D216" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E216">
         <v>-0.1302387600075896</v>
@@ -12437,7 +12419,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12451,7 +12433,7 @@
         <v>2.97076363447318</v>
       </c>
       <c r="D217" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E217">
         <v>-0.1302387600075896</v>
@@ -12487,7 +12469,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12501,7 +12483,7 @@
         <v>-2.735537076225839</v>
       </c>
       <c r="D218" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E218">
         <v>-0.06446785034954416</v>
@@ -12537,7 +12519,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12551,7 +12533,7 @@
         <v>2.142297248198716</v>
       </c>
       <c r="D219" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E219">
         <v>-0.7752043867837592</v>
@@ -12587,7 +12569,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12601,7 +12583,7 @@
         <v>2.649161212067007</v>
       </c>
       <c r="D220" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E220">
         <v>-0.7752043867837592</v>
@@ -12637,7 +12619,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12651,7 +12633,7 @@
         <v>1.866662847049479</v>
       </c>
       <c r="D221" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E221">
         <v>-0.7752043867837592</v>
@@ -12687,7 +12669,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12701,7 +12683,7 @@
         <v>-3.292719101626048</v>
       </c>
       <c r="D222" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E222">
         <v>-0.5316716843393898</v>
@@ -12737,7 +12719,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12751,7 +12733,7 @@
         <v>0.7343076746441</v>
       </c>
       <c r="D223" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E223">
         <v>-2.162218324233283</v>
@@ -12801,7 +12783,7 @@
         <v>1.382757182221791</v>
       </c>
       <c r="D224" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E224">
         <v>-2.162218324233283</v>
@@ -12851,7 +12833,7 @@
         <v>0.5792831810991643</v>
       </c>
       <c r="D225" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E225">
         <v>-2.162218324233283</v>
@@ -12901,7 +12883,7 @@
         <v>-4.4909523141297</v>
       </c>
       <c r="D226" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E226">
         <v>-1.797099453998044</v>
@@ -12951,7 +12933,7 @@
         <v>-0.5271433345479153</v>
       </c>
       <c r="D227" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E227">
         <v>-3.404876767180344</v>
@@ -13001,7 +12983,7 @@
         <v>0.2481559951831649</v>
       </c>
       <c r="D228" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E228">
         <v>-3.404876767180344</v>
@@ -13051,7 +13033,7 @@
         <v>-0.5741105721844058</v>
       </c>
       <c r="D229" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E229">
         <v>-3.404876767180344</v>
@@ -13101,7 +13083,7 @@
         <v>-5.289194339951301</v>
       </c>
       <c r="D230" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E230">
         <v>-2.93597803324387</v>
@@ -13151,7 +13133,7 @@
         <v>-1.521590007004434</v>
       </c>
       <c r="D231" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E231">
         <v>-4.774748703164175</v>
@@ -13187,7 +13169,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13201,7 +13183,7 @@
         <v>-2.373169137555241</v>
       </c>
       <c r="D232" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E232">
         <v>-4.774748703164175</v>
@@ -13237,7 +13219,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13251,7 +13233,7 @@
         <v>-6.960010441395497</v>
       </c>
       <c r="D233" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E233">
         <v>-4.500536093148853</v>
@@ -13287,7 +13269,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13301,7 +13283,7 @@
         <v>-2.452340392521911</v>
       </c>
       <c r="D234" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E234">
         <v>-5.548191233294997</v>
@@ -13351,7 +13333,7 @@
         <v>-2.754963624773605</v>
       </c>
       <c r="D235" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E235">
         <v>-5.548191233294997</v>
@@ -13401,7 +13383,7 @@
         <v>-7.838731302256715</v>
       </c>
       <c r="D236" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E236">
         <v>-5.323373390490392</v>
@@ -13451,7 +13433,7 @@
         <v>-4.58678078170076</v>
       </c>
       <c r="D237" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E237">
         <v>-7.667945163513835</v>
@@ -13487,7 +13469,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13501,7 +13483,7 @@
         <v>-5.270890369576151</v>
       </c>
       <c r="D238" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E238">
         <v>-7.667945163513835</v>
@@ -13537,7 +13519,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13551,7 +13533,7 @@
         <v>-4.902661407674056</v>
       </c>
       <c r="D239" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E239">
         <v>-7.667945163513835</v>
@@ -13587,7 +13569,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13601,7 +13583,7 @@
         <v>-9.853855147941093</v>
       </c>
       <c r="D240" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E240">
         <v>-7.21034243019923</v>
@@ -13637,7 +13619,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13651,7 +13633,7 @@
         <v>-5.59817458645032</v>
       </c>
       <c r="D241" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E241">
         <v>-8.513312611948162</v>
@@ -13687,7 +13669,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13701,7 +13683,7 @@
         <v>-5.920337161521442</v>
       </c>
       <c r="D242" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E242">
         <v>-8.513312611948162</v>
@@ -13737,7 +13719,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13751,7 +13733,7 @@
         <v>-10.78187598777789</v>
       </c>
       <c r="D243" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E243">
         <v>-7.189437361711093</v>
@@ -13787,7 +13769,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13801,7 +13783,7 @@
         <v>-10.80871141081024</v>
       </c>
       <c r="D244" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E244">
         <v>-8.104473185122753</v>
@@ -13837,7 +13819,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13851,7 +13833,7 @@
         <v>-5.98278744209609</v>
       </c>
       <c r="D245" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E245">
         <v>-8.914647765665489</v>
@@ -13887,7 +13869,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13901,7 +13883,7 @@
         <v>-6.30733891689172</v>
       </c>
       <c r="D246" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E246">
         <v>-8.914647765665489</v>
@@ -13937,7 +13919,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13951,7 +13933,7 @@
         <v>-11.21108163828114</v>
       </c>
       <c r="D247" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E247">
         <v>-7.582809516346728</v>
@@ -13987,7 +13969,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14001,7 +13983,7 @@
         <v>-11.09924338896238</v>
       </c>
       <c r="D248" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E248">
         <v>-7.582809516346728</v>
@@ -14037,7 +14019,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14051,7 +14033,7 @@
         <v>-11.17182416893544</v>
       </c>
       <c r="D249" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E249">
         <v>-8.444493245911037</v>
@@ -14087,7 +14069,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14101,7 +14083,7 @@
         <v>-6.197743032286496</v>
       </c>
       <c r="D250" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E250">
         <v>-9.138949251081566</v>
@@ -14137,7 +14119,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14151,7 +14133,7 @@
         <v>-6.52362963497151</v>
       </c>
       <c r="D251" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E251">
         <v>-9.138949251081566</v>
@@ -14187,7 +14169,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14201,7 +14183,7 @@
         <v>-11.45095961574</v>
       </c>
       <c r="D252" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E252">
         <v>-7.802660575464863</v>
@@ -14237,7 +14219,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14251,7 +14233,7 @@
         <v>-11.33467094012331</v>
       </c>
       <c r="D253" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E253">
         <v>-7.802660575464863</v>
@@ -14287,7 +14269,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14301,7 +14283,7 @@
         <v>-11.37476360812142</v>
       </c>
       <c r="D254" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E254">
         <v>-8.63452644883299</v>
@@ -14337,7 +14319,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14351,7 +14333,7 @@
         <v>-6.365423262694474</v>
       </c>
       <c r="D255" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E255">
         <v>-6.712841826990488</v>
@@ -14387,7 +14369,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14401,7 +14383,7 @@
         <v>-6.180679040630039</v>
       </c>
       <c r="D256" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E256">
         <v>-9.121143346744393</v>
@@ -14437,7 +14419,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14451,7 +14433,7 @@
         <v>-6.506459655789232</v>
       </c>
       <c r="D257" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E257">
         <v>-9.121143346744393</v>
@@ -14487,7 +14469,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14501,7 +14483,7 @@
         <v>-11.43191719026831</v>
       </c>
       <c r="D258" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E258">
         <v>-7.785207962880413</v>
@@ -14537,7 +14519,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14551,7 +14533,7 @@
         <v>-11.31598180640433</v>
       </c>
       <c r="D259" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E259">
         <v>-7.785207962880413</v>
@@ -14587,7 +14569,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14601,7 +14583,7 @@
         <v>-11.3586535041973</v>
       </c>
       <c r="D260" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E260">
         <v>-8.619440890991779</v>
@@ -14637,7 +14619,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14651,7 +14633,7 @@
         <v>-6.352422126194313</v>
       </c>
       <c r="D261" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E261">
         <v>-7.002545941158143</v>
@@ -14687,7 +14669,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14701,7 +14683,7 @@
         <v>-6.259072586714403</v>
       </c>
       <c r="D262" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E262">
         <v>-9.202945307875904</v>
@@ -14737,7 +14719,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14751,7 +14733,7 @@
         <v>-6.58534011830891</v>
       </c>
       <c r="D263" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E263">
         <v>-9.202945307875904</v>
@@ -14787,7 +14769,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14801,7 +14783,7 @@
         <v>-11.51939984314506</v>
       </c>
       <c r="D264" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E264">
         <v>-7.865386869227571</v>
@@ -14837,7 +14819,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14851,7 +14833,7 @@
         <v>-11.40184140449673</v>
       </c>
       <c r="D265" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E265">
         <v>-7.865386869227571</v>
@@ -14887,7 +14869,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14901,7 +14883,7 @@
         <v>-11.43266480236391</v>
       </c>
       <c r="D266" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E266">
         <v>-8.688745330283755</v>
@@ -14937,7 +14919,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14951,7 +14933,7 @@
         <v>-6.412150542258594</v>
       </c>
       <c r="D267" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E267">
         <v>-6.792666905080129</v>
@@ -14987,7 +14969,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15001,7 +14983,7 @@
         <v>-6.321920167701883</v>
       </c>
       <c r="D268" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E268">
         <v>-9.268525392384579</v>
@@ -15037,7 +15019,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15051,7 +15033,7 @@
         <v>-11.58953410018906</v>
       </c>
       <c r="D269" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E269">
         <v>-7.929665761583294</v>
@@ -15087,7 +15069,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15101,7 +15083,7 @@
         <v>-11.47067446938778</v>
       </c>
       <c r="D270" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E270">
         <v>-7.929665761583294</v>
@@ -15137,7 +15119,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15151,7 +15133,7 @@
         <v>-11.49199916453843</v>
       </c>
       <c r="D271" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E271">
         <v>-8.744306235214712</v>
@@ -15187,7 +15169,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15201,7 +15183,7 @@
         <v>-6.460034413487151</v>
       </c>
       <c r="D272" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E272">
         <v>-6.681381790702538</v>
@@ -15237,7 +15219,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15251,7 +15233,7 @@
         <v>-6.550476318984671</v>
       </c>
       <c r="D273" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E273">
         <v>-9.507018767636186</v>
@@ -15287,7 +15269,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15301,7 +15283,7 @@
         <v>-11.8445895153887</v>
       </c>
       <c r="D274" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E274">
         <v>-8.16342712542118</v>
@@ -15337,7 +15319,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15351,7 +15333,7 @@
         <v>-11.72099787317369</v>
       </c>
       <c r="D275" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E275">
         <v>-8.16342712542118</v>
@@ -15387,7 +15369,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15401,7 +15383,7 @@
         <v>-11.70777888500417</v>
       </c>
       <c r="D276" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E276">
         <v>-8.94636312258066</v>
@@ -15437,7 +15419,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15487,7 +15469,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15501,7 +15483,7 @@
         <v>-6.704638136207883</v>
       </c>
       <c r="D278" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E278">
         <v>-9.667883272564755</v>
@@ -15537,7 +15519,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15551,7 +15533,7 @@
         <v>-12.01662516649286</v>
       </c>
       <c r="D279" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E279">
         <v>-8.321099874299577</v>
@@ -15587,7 +15569,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15601,7 +15583,7 @@
         <v>-11.88984176822768</v>
       </c>
       <c r="D280" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E280">
         <v>-8.321099874299577</v>
@@ -15637,7 +15619,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15651,7 +15633,7 @@
         <v>-12.14300130071843</v>
       </c>
       <c r="D281" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E281">
         <v>-9.082651105922917</v>
@@ -15687,7 +15669,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15701,7 +15683,7 @@
         <v>-6.751629056158386</v>
       </c>
       <c r="D282" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E282">
         <v>-6.181746306378969</v>
@@ -15737,7 +15719,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15751,7 +15733,7 @@
         <v>-6.169874970448358</v>
       </c>
       <c r="D283" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E283">
         <v>-6.181746306378969</v>
@@ -15787,7 +15769,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15801,7 +15783,7 @@
         <v>-6.791555990766213</v>
       </c>
       <c r="D284" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E284">
         <v>-9.758580164277792</v>
@@ -15837,7 +15819,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15851,7 +15833,7 @@
         <v>-12.11362045346375</v>
       </c>
       <c r="D285" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E285">
         <v>-8.40999722451037</v>
@@ -15887,7 +15869,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15901,7 +15883,7 @@
         <v>-12.22524034737093</v>
       </c>
       <c r="D286" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E286">
         <v>-9.159491528068681</v>
@@ -15937,7 +15919,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15951,7 +15933,7 @@
         <v>-6.817852183440923</v>
       </c>
       <c r="D287" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E287">
         <v>-6.265382608492114</v>
@@ -15987,7 +15969,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16001,7 +15983,7 @@
         <v>-6.233722702947933</v>
       </c>
       <c r="D288" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E288">
         <v>-6.265382608492114</v>
@@ -16037,7 +16019,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16051,7 +16033,7 @@
         <v>-12.15514825489226</v>
       </c>
       <c r="D289" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E289">
         <v>-8.448057955318696</v>
@@ -16087,7 +16069,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16101,7 +16083,7 @@
         <v>-12.26045037566933</v>
       </c>
       <c r="D290" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E290">
         <v>-9.192390175953609</v>
@@ -16137,7 +16119,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16151,7 +16133,7 @@
         <v>-6.261058628637798</v>
       </c>
       <c r="D291" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E291">
         <v>-6.075524180706029</v>
@@ -16187,7 +16169,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16201,7 +16183,7 @@
         <v>-12.2145658985059</v>
       </c>
       <c r="D292" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E292">
         <v>-8.502514942229901</v>
@@ -16251,7 +16233,7 @@
         <v>-12.31082860040297</v>
       </c>
       <c r="D293" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E293">
         <v>-9.239461296218966</v>
@@ -16301,7 +16283,7 @@
         <v>-6.300170650816128</v>
       </c>
       <c r="D294" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E294">
         <v>-5.649532575530262</v>
@@ -16351,7 +16333,7 @@
         <v>-11.84108439837907</v>
       </c>
       <c r="D295" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E295">
         <v>-8.80055369389029</v>
@@ -16387,7 +16369,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16401,7 +16383,7 @@
         <v>-5.935476465087291</v>
       </c>
       <c r="D296" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E296">
         <v>-5.137979270573577</v>
@@ -16437,7 +16419,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16487,7 +16469,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16537,7 +16519,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16587,7 +16569,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16637,7 +16619,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16687,7 +16669,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16737,7 +16719,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16787,7 +16769,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16801,7 +16783,7 @@
         <v>-0.3501812538917548</v>
       </c>
       <c r="D304" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E304">
         <v>-4.299167540216818</v>
@@ -16837,7 +16819,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16887,7 +16869,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16901,7 +16883,7 @@
         <v>-0.2510998261771533</v>
       </c>
       <c r="D306" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E306">
         <v>-4.192512218904984</v>
@@ -16937,7 +16919,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16987,7 +16969,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17001,7 +16983,7 @@
         <v>-0.1528009024453745</v>
       </c>
       <c r="D308" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E308">
         <v>-4.086699217043329</v>
@@ -17037,7 +17019,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17087,7 +17069,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17101,7 +17083,7 @@
         <v>0.06625268284449959</v>
       </c>
       <c r="D310" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E310">
         <v>-3.850900934131047</v>
@@ -17137,7 +17119,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17187,7 +17169,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17237,7 +17219,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17287,7 +17269,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17337,7 +17319,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17387,7 +17369,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17401,7 +17383,7 @@
         <v>1.82693717047681</v>
       </c>
       <c r="D316" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E316">
         <v>0.6963720300954037</v>
@@ -17437,7 +17419,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17487,7 +17469,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17501,7 +17483,7 @@
         <v>2.198341117699623</v>
       </c>
       <c r="D318" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E318">
         <v>0.5276096580294123</v>
@@ -17537,7 +17519,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17551,7 +17533,7 @@
         <v>12.7271211800604</v>
       </c>
       <c r="D319" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E319">
         <v>10.466793520675</v>
@@ -17587,7 +17569,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17601,7 +17583,7 @@
         <v>13.26860393649666</v>
       </c>
       <c r="D320" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E320">
         <v>10.466793520675</v>
@@ -17637,7 +17619,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17651,7 +17633,7 @@
         <v>12.90082807115104</v>
       </c>
       <c r="D321" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E321">
         <v>10.466793520675</v>
@@ -17687,7 +17669,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17701,7 +17683,7 @@
         <v>12.60281108867061</v>
       </c>
       <c r="D322" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E322">
         <v>10.00917894691048</v>
@@ -17737,7 +17719,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17751,7 +17733,7 @@
         <v>13.14484756489033</v>
       </c>
       <c r="D323" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E323">
         <v>10.00917894691048</v>
@@ -17787,7 +17769,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17801,7 +17783,7 @@
         <v>12.77790227921993</v>
       </c>
       <c r="D324" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E324">
         <v>10.00917894691048</v>
@@ -17837,7 +17819,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17851,7 +17833,7 @@
         <v>12.94031582834918</v>
       </c>
       <c r="D325" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E325">
         <v>10.4990798111086</v>
@@ -17887,7 +17869,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17901,7 +17883,7 @@
         <v>13.48084894269951</v>
       </c>
       <c r="D326" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E326">
         <v>10.4990798111086</v>
@@ -17937,7 +17919,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17951,7 +17933,7 @@
         <v>13.11164861422502</v>
       </c>
       <c r="D327" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E327">
         <v>10.4990798111086</v>
@@ -17987,7 +17969,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18001,7 +17983,7 @@
         <v>12.89880385150152</v>
       </c>
       <c r="D328" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E328">
         <v>10.62546343074822</v>
@@ -18037,7 +18019,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18051,7 +18033,7 @@
         <v>13.4395218744347</v>
       </c>
       <c r="D329" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E329">
         <v>10.62546343074822</v>
@@ -18087,7 +18069,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18101,7 +18083,7 @@
         <v>13.07059890883446</v>
       </c>
       <c r="D330" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E330">
         <v>10.62546343074822</v>
@@ -18137,7 +18119,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18151,7 +18133,7 @@
         <v>12.9234363080082</v>
       </c>
       <c r="D331" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E331">
         <v>11.0537757639692</v>
@@ -18187,7 +18169,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18201,7 +18183,7 @@
         <v>13.46404460953155</v>
       </c>
       <c r="D332" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E332">
         <v>11.0537757639692</v>
@@ -18237,7 +18219,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18251,7 +18233,7 @@
         <v>13.09495706181657</v>
       </c>
       <c r="D333" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E333">
         <v>11.0537757639692</v>
@@ -18287,7 +18269,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18301,7 +18283,7 @@
         <v>13.44227382778946</v>
       </c>
       <c r="D334" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E334">
         <v>11.03770193240324</v>
@@ -18337,7 +18319,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18351,7 +18333,7 @@
         <v>13.07333239270363</v>
       </c>
       <c r="D335" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E335">
         <v>11.03770193240324</v>
@@ -18387,7 +18369,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18401,7 +18383,7 @@
         <v>13.47049330154028</v>
       </c>
       <c r="D336" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E336">
         <v>12.2200768479712</v>
@@ -18437,7 +18419,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18451,7 +18433,7 @@
         <v>13.10136247401317</v>
       </c>
       <c r="D337" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E337">
         <v>12.2200768479712</v>
@@ -18487,7 +18469,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18501,7 +18483,7 @@
         <v>13.41024108188445</v>
       </c>
       <c r="D338" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E338">
         <v>11.606966539383</v>
@@ -18537,7 +18519,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18551,7 +18533,7 @@
         <v>13.04151463167046</v>
       </c>
       <c r="D339" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E339">
         <v>11.606966539383</v>
@@ -18587,7 +18569,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18601,7 +18583,7 @@
         <v>15.99098556432473</v>
       </c>
       <c r="D340" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E340">
         <v>12.49688805745362</v>
@@ -18637,7 +18619,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18651,7 +18633,7 @@
         <v>15.82125527263218</v>
       </c>
       <c r="D341" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E341">
         <v>12.49688805745362</v>
@@ -18687,7 +18669,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18701,7 +18683,7 @@
         <v>16.12796689068343</v>
       </c>
       <c r="D342" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E342">
         <v>12.49688805745362</v>
@@ -18737,7 +18719,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18751,7 +18733,7 @@
         <v>16.05759498721028</v>
       </c>
       <c r="D343" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E343">
         <v>12.56617445478137</v>
@@ -18787,7 +18769,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18801,7 +18783,7 @@
         <v>15.8869198810087</v>
       </c>
       <c r="D344" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E344">
         <v>12.56617445478137</v>
@@ -18837,7 +18819,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18851,7 +18833,7 @@
         <v>16.19347402997512</v>
       </c>
       <c r="D345" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E345">
         <v>12.56617445478137</v>
@@ -18887,7 +18869,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18901,7 +18883,7 @@
         <v>16.08852224791477</v>
       </c>
       <c r="D346" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E346">
         <v>12.59834465504137</v>
@@ -18937,7 +18919,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18951,7 +18933,7 @@
         <v>15.9174084571642</v>
       </c>
       <c r="D347" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E347">
         <v>12.59834465504137</v>
@@ -18987,7 +18969,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19001,7 +18983,7 @@
         <v>16.22388949203912</v>
       </c>
       <c r="D348" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E348">
         <v>12.59834465504137</v>
@@ -19037,7 +19019,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19051,7 +19033,7 @@
         <v>15.99827269225045</v>
       </c>
       <c r="D349" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E349">
         <v>12.50446804867659</v>
@@ -19087,7 +19069,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19101,7 +19083,7 @@
         <v>15.82843903704122</v>
       </c>
       <c r="D350" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E350">
         <v>12.50446804867659</v>
@@ -19137,7 +19119,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19151,7 +19133,7 @@
         <v>16.13513342783969</v>
       </c>
       <c r="D351" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E351">
         <v>12.50446804867659</v>
@@ -19187,7 +19169,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19201,7 +19183,7 @@
         <v>10.5571576031199</v>
       </c>
       <c r="D352" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E352">
         <v>11.2357781978979</v>
@@ -19251,7 +19233,7 @@
         <v>10.4146275818384</v>
       </c>
       <c r="D353" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E353">
         <v>11.2357781978979</v>
@@ -19301,7 +19283,7 @@
         <v>11.02395259544049</v>
       </c>
       <c r="D354" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E354">
         <v>11.2357781978979</v>
@@ -19387,7 +19369,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19437,7 +19419,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19487,7 +19469,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19537,7 +19519,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19587,7 +19569,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19637,7 +19619,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19687,7 +19669,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19737,7 +19719,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19751,7 +19733,7 @@
         <v>7.109582508392513</v>
       </c>
       <c r="D363" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E363">
         <v>10.1191386498793</v>
@@ -19801,7 +19783,7 @@
         <v>8.320739177217412</v>
       </c>
       <c r="D364" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E364">
         <v>10.1191386498793</v>
@@ -19887,7 +19869,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19937,7 +19919,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19951,7 +19933,7 @@
         <v>5.429328338517664</v>
       </c>
       <c r="D367" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E367">
         <v>6.453570540990412</v>
@@ -19987,7 +19969,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20001,7 +19983,7 @@
         <v>4.28114123100805</v>
       </c>
       <c r="D368" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E368">
         <v>5.201857907737669</v>
@@ -20037,7 +20019,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20051,7 +20033,7 @@
         <v>3.478556159579213</v>
       </c>
       <c r="D369" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E369">
         <v>4.355782779043444</v>
@@ -20087,7 +20069,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20101,7 +20083,7 @@
         <v>2.542133382528917</v>
       </c>
       <c r="D370" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E370">
         <v>3.611162052395251</v>
@@ -20137,7 +20119,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20187,7 +20169,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20201,7 +20183,7 @@
         <v>3.166397470697689</v>
       </c>
       <c r="D372" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E372">
         <v>2.50604388321451</v>
@@ -20237,7 +20219,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20287,7 +20269,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20337,7 +20319,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20387,7 +20369,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20401,7 +20383,7 @@
         <v>0.5258114362592394</v>
       </c>
       <c r="D376" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E376">
         <v>0.9640594525915418</v>
@@ -20437,7 +20419,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20451,7 +20433,7 @@
         <v>1.029412028487577</v>
       </c>
       <c r="D377" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E377">
         <v>0.9640594525915418</v>
@@ -20487,7 +20469,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20501,7 +20483,7 @@
         <v>0.5230738845135647</v>
       </c>
       <c r="D378" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E378">
         <v>0.9640594525915418</v>
@@ -20537,7 +20519,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20551,7 +20533,7 @@
         <v>0.2932995584235911</v>
       </c>
       <c r="D379" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E379">
         <v>-0.2507339019854058</v>
@@ -20587,7 +20569,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20601,7 +20583,7 @@
         <v>0.8110931833932682</v>
       </c>
       <c r="D380" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E380">
         <v>-0.2507339019854058</v>
@@ -20637,7 +20619,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20651,7 +20633,7 @@
         <v>0.3063705065605404</v>
       </c>
       <c r="D381" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E381">
         <v>-0.2507339019854058</v>
@@ -20687,7 +20669,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20701,7 +20683,7 @@
         <v>0.25081902425989</v>
       </c>
       <c r="D382" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E382">
         <v>-1.810462939778127</v>
@@ -20737,7 +20719,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20751,7 +20733,7 @@
         <v>0.7712057537963801</v>
       </c>
       <c r="D383" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E383">
         <v>-1.810462939778127</v>
@@ -20787,7 +20769,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20801,7 +20783,7 @@
         <v>0.266778227076955</v>
       </c>
       <c r="D384" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E384">
         <v>-1.810462939778127</v>
@@ -20837,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20851,7 +20833,7 @@
         <v>0.2555858995649842</v>
       </c>
       <c r="D385" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E385">
         <v>-0.5322733758888774</v>
@@ -20887,7 +20869,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20901,7 +20883,7 @@
         <v>0.7756816486237952</v>
       </c>
       <c r="D386" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E386">
         <v>-0.5322733758888774</v>
@@ -20937,7 +20919,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20951,7 +20933,7 @@
         <v>0.2712210021752028</v>
       </c>
       <c r="D387" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E387">
         <v>-0.5322733758888774</v>
@@ -20987,7 +20969,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21037,7 +21019,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21087,7 +21069,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21137,7 +21119,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21187,7 +21169,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21201,7 +21183,7 @@
         <v>2.068109497945251</v>
       </c>
       <c r="D392" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E392">
         <v>1.103589803610085</v>
@@ -21237,7 +21219,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21251,7 +21233,7 @@
         <v>1.130775764308638</v>
       </c>
       <c r="D393" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E393">
         <v>1.103589803610085</v>
@@ -21287,7 +21269,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21301,7 +21283,7 @@
         <v>1.848060841515313</v>
       </c>
       <c r="D394" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E394">
         <v>0.99412281255767</v>
@@ -21337,7 +21319,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21351,7 +21333,7 @@
         <v>0.9315277271432265</v>
       </c>
       <c r="D395" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E395">
         <v>0.99412281255767</v>
@@ -21387,7 +21369,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21401,7 +21383,7 @@
         <v>1.694201531226533</v>
       </c>
       <c r="D396" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E396">
         <v>0.6700023738905614</v>
@@ -21437,7 +21419,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21451,7 +21433,7 @@
         <v>0.7922123317573622</v>
       </c>
       <c r="D397" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E397">
         <v>0.6700023738905614</v>
@@ -21487,7 +21469,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21501,7 +21483,7 @@
         <v>1.513646695334067</v>
       </c>
       <c r="D398" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E398">
         <v>0.5589534979668187</v>
@@ -21537,7 +21519,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21551,7 +21533,7 @@
         <v>0.6287248684119433</v>
       </c>
       <c r="D399" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E399">
         <v>0.5589534979668187</v>
@@ -21587,7 +21569,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21637,7 +21619,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21687,7 +21669,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21701,7 +21683,7 @@
         <v>1.430312383569088</v>
       </c>
       <c r="D402" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E402">
         <v>2.785832606944602</v>
@@ -21737,7 +21719,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21751,7 +21733,7 @@
         <v>1.015447344707901</v>
       </c>
       <c r="D403" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E403">
         <v>2.785832606944602</v>
@@ -21787,7 +21769,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21801,7 +21783,7 @@
         <v>2.872497404927479</v>
       </c>
       <c r="D404" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E404">
         <v>2.785832606944602</v>
@@ -21837,7 +21819,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21851,7 +21833,7 @@
         <v>1.657667083906176</v>
       </c>
       <c r="D405" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E405">
         <v>3.010263722734074</v>
@@ -21887,7 +21869,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21901,7 +21883,7 @@
         <v>3.082432889417845</v>
       </c>
       <c r="D406" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E406">
         <v>3.010263722734074</v>
@@ -21937,7 +21919,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21951,7 +21933,7 @@
         <v>1.760495757853356</v>
       </c>
       <c r="D407" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E407">
         <v>2.967064908431617</v>
@@ -21987,7 +21969,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22001,7 +21983,7 @@
         <v>3.177383147550167</v>
       </c>
       <c r="D408" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E408">
         <v>2.967064908431617</v>
@@ -22037,7 +22019,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22051,7 +22033,7 @@
         <v>3.419213206004784</v>
       </c>
       <c r="D409" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E409">
         <v>4.96095189349581</v>
@@ -22087,7 +22069,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22101,7 +22083,7 @@
         <v>30.71910142906406</v>
       </c>
       <c r="D410" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E410">
         <v>17.77124839717711</v>
@@ -22137,7 +22119,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22151,7 +22133,7 @@
         <v>30.74457906406285</v>
       </c>
       <c r="D411" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E411">
         <v>18.07805575594424</v>
@@ -22187,7 +22169,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22201,7 +22183,7 @@
         <v>30.94531632533681</v>
       </c>
       <c r="D412" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E412">
         <v>18.41220109884297</v>
@@ -22237,7 +22219,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22251,7 +22233,7 @@
         <v>31.10162189647678</v>
       </c>
       <c r="D413" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E413">
         <v>18.55328210136541</v>
@@ -22287,7 +22269,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22301,7 +22283,7 @@
         <v>31.28406714947664</v>
       </c>
       <c r="D414" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E414">
         <v>18.71795671283931</v>
@@ -22337,7 +22319,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22351,7 +22333,7 @@
         <v>31.41016164358475</v>
       </c>
       <c r="D415" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E415">
         <v>18.83176927570312</v>
@@ -22387,7 +22369,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22401,7 +22383,7 @@
         <v>31.50687459786862</v>
       </c>
       <c r="D416" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E416">
         <v>18.91906213703726</v>
@@ -22437,7 +22419,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22451,7 +22433,7 @@
         <v>31.56465330836859</v>
       </c>
       <c r="D417" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E417">
         <v>18.97121305105996</v>
@@ -22487,7 +22469,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22501,7 +22483,7 @@
         <v>31.59842308925229</v>
       </c>
       <c r="D418" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E418">
         <v>19.00169356757187</v>
@@ -22537,7 +22519,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22551,7 +22533,7 @@
         <v>31.66012131009328</v>
       </c>
       <c r="D419" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E419">
         <v>19.05738222144783</v>
@@ -22587,7 +22569,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22601,7 +22583,7 @@
         <v>31.70713316886447</v>
       </c>
       <c r="D420" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E420">
         <v>19.09981500306598</v>
@@ -22637,7 +22619,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22651,7 +22633,7 @@
         <v>31.87762108191551</v>
       </c>
       <c r="D421" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E421">
         <v>19.25369695056011</v>
@@ -22687,7 +22669,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22701,7 +22683,7 @@
         <v>32.04993923346682</v>
       </c>
       <c r="D422" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E422">
         <v>19.4092308665707</v>
@@ -22737,7 +22719,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22751,7 +22733,7 @@
         <v>32.21080893028861</v>
       </c>
       <c r="D423" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E423">
         <v>19.55443143707868</v>
@@ -22787,7 +22769,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22801,7 +22783,7 @@
         <v>32.44198272920474</v>
       </c>
       <c r="D424" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E424">
         <v>19.76308830752896</v>
@@ -22837,7 +22819,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22851,7 +22833,7 @@
         <v>32.60849165225912</v>
       </c>
       <c r="D425" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E425">
         <v>19.91337882898712</v>
@@ -22887,7 +22869,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22901,7 +22883,7 @@
         <v>32.78872551361854</v>
       </c>
       <c r="D426" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E426">
         <v>20.07605744411025</v>
@@ -22937,7 +22919,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22951,7 +22933,7 @@
         <v>32.88633633076009</v>
       </c>
       <c r="D427" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E427">
         <v>20.16416071412761</v>
@@ -22987,7 +22969,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23001,7 +22983,7 @@
         <v>32.92087256937922</v>
       </c>
       <c r="D428" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E428">
         <v>20.19533303340073</v>
@@ -23037,7 +23019,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23051,7 +23033,7 @@
         <v>33.06269553801688</v>
       </c>
       <c r="D429" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E429">
         <v>20.32334207652173</v>
@@ -23087,7 +23069,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23101,7 +23083,7 @@
         <v>33.22705411164569</v>
       </c>
       <c r="D430" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E430">
         <v>20.4716916981737</v>
@@ -23137,7 +23119,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23151,7 +23133,7 @@
         <v>33.43325315348858</v>
       </c>
       <c r="D431" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E431">
         <v>20.65780641775917</v>
@@ -23187,7 +23169,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23201,7 +23183,7 @@
         <v>33.53120523654898</v>
       </c>
       <c r="D432" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E432">
         <v>20.7462177135085</v>
@@ -23237,7 +23219,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23287,7 +23269,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23301,7 +23283,7 @@
         <v>33.46421187526697</v>
       </c>
       <c r="D434" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E434">
         <v>21.58554463904314</v>
@@ -23337,7 +23319,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23387,7 +23369,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23401,7 +23383,7 @@
         <v>33.20896438389043</v>
       </c>
       <c r="D436" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E436">
         <v>21.35184401382175</v>
@@ -23437,7 +23419,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23451,7 +23433,7 @@
         <v>33.24525244457716</v>
       </c>
       <c r="D437" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E437">
         <v>21.38506879665831</v>
@@ -23501,7 +23483,7 @@
         <v>33.30754061736793</v>
       </c>
       <c r="D438" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E438">
         <v>21.44209887694077</v>
@@ -23537,7 +23519,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23587,7 +23569,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23637,7 +23619,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23687,7 +23669,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23701,7 +23683,7 @@
         <v>33.37808699058778</v>
       </c>
       <c r="D442" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E442">
         <v>21.50669003683685</v>
@@ -23737,7 +23719,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23787,7 +23769,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23837,7 +23819,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23887,7 +23869,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23901,7 +23883,7 @@
         <v>33.3491605949092</v>
       </c>
       <c r="D446" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E446">
         <v>21.48020547975453</v>
@@ -23937,7 +23919,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23987,7 +23969,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24037,7 +24019,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24087,7 +24069,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24101,7 +24083,7 @@
         <v>33.21868761846164</v>
       </c>
       <c r="D450" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E450">
         <v>21.36074645586423</v>
@@ -24137,7 +24119,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24187,7 +24169,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24237,7 +24219,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24287,7 +24269,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24337,7 +24319,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24351,7 +24333,7 @@
         <v>33.10860895395319</v>
       </c>
       <c r="D455" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E455">
         <v>21.25996014615194</v>
@@ -24387,7 +24369,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24437,7 +24419,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24487,7 +24469,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24537,7 +24519,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24551,7 +24533,7 @@
         <v>32.82858702883275</v>
       </c>
       <c r="D459" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E459">
         <v>21.00357643548973</v>
@@ -24587,7 +24569,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24701,7 +24683,7 @@
         <v>32.43391527499527</v>
       </c>
       <c r="D462" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E462">
         <v>20.64222112840476</v>
@@ -24787,7 +24769,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24801,7 +24783,7 @@
         <v>32.1976037826028</v>
       </c>
       <c r="D464" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E464">
         <v>20.42585800874672</v>
@@ -24837,7 +24819,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24851,7 +24833,7 @@
         <v>31.9359757436375</v>
       </c>
       <c r="D465" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E465">
         <v>20.18631545359018</v>
@@ -24887,7 +24869,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24901,7 +24883,7 @@
         <v>31.6928085141255</v>
       </c>
       <c r="D466" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E466">
         <v>19.96367532786815</v>
@@ -24951,7 +24933,7 @@
         <v>31.38607212722557</v>
       </c>
       <c r="D467" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E467">
         <v>19.96017071526525</v>
@@ -24987,7 +24969,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25001,7 +24983,7 @@
         <v>31.09488527318194</v>
       </c>
       <c r="D468" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E468">
         <v>19.69041319680059</v>
@@ -25051,7 +25033,7 @@
         <v>28.76090315089132</v>
       </c>
       <c r="D469" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E469">
         <v>19.57543646755398</v>
@@ -25087,7 +25069,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25101,7 +25083,7 @@
         <v>30.97077487852789</v>
       </c>
       <c r="D470" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E470">
         <v>19.57543646755398</v>
@@ -25137,7 +25119,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25151,7 +25133,7 @@
         <v>28.60148803846228</v>
       </c>
       <c r="D471" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E471">
         <v>19.42949065339434</v>
@@ -25187,7 +25169,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25201,7 +25183,7 @@
         <v>30.81323523800978</v>
       </c>
       <c r="D472" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E472">
         <v>19.42949065339434</v>
@@ -25237,7 +25219,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25251,7 +25233,7 @@
         <v>28.31621253771513</v>
       </c>
       <c r="D473" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E473">
         <v>19.16831864415417</v>
@@ -25287,7 +25269,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25301,7 +25283,7 @@
         <v>30.53131591962436</v>
       </c>
       <c r="D474" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E474">
         <v>19.16831864415417</v>
@@ -25337,7 +25319,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25351,7 +25333,7 @@
         <v>28.17117124931562</v>
       </c>
       <c r="D475" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E475">
         <v>19.16188388044775</v>
@@ -25401,7 +25383,7 @@
         <v>30.52436998310014</v>
       </c>
       <c r="D476" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E476">
         <v>19.16188388044775</v>
@@ -25451,7 +25433,7 @@
         <v>28.43299823269307</v>
       </c>
       <c r="D477" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E477">
         <v>19.40417998614624</v>
@@ -25487,7 +25469,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25501,7 +25483,7 @@
         <v>28.68381801752044</v>
       </c>
       <c r="D478" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E478">
         <v>19.6362899708081</v>
@@ -25551,7 +25533,7 @@
         <v>28.80289710513282</v>
       </c>
       <c r="D479" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E479">
         <v>19.74648640215534</v>
@@ -25587,7 +25569,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25601,7 +25583,7 @@
         <v>28.66069705648685</v>
       </c>
       <c r="D480" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E480">
         <v>19.74648640215534</v>
@@ -25637,7 +25619,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25651,7 +25633,7 @@
         <v>28.92716526228032</v>
       </c>
       <c r="D481" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E481">
         <v>19.86148482649941</v>
@@ -25687,7 +25669,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25701,7 +25683,7 @@
         <v>28.78241267851456</v>
       </c>
       <c r="D482" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E482">
         <v>19.86148482649941</v>
@@ -25737,7 +25719,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25751,7 +25733,7 @@
         <v>28.69210673371983</v>
       </c>
       <c r="D483" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E483">
         <v>19.64396039358289</v>
@@ -25787,7 +25769,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25801,7 +25783,7 @@
         <v>28.55218237918936</v>
       </c>
       <c r="D484" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E484">
         <v>19.64396039358289</v>
@@ -25837,7 +25819,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25851,7 +25833,7 @@
         <v>24.1238374281487</v>
       </c>
       <c r="D485" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E485">
         <v>15.41645928485977</v>
@@ -25887,7 +25869,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25901,7 +25883,7 @@
         <v>23.88230241564499</v>
       </c>
       <c r="D486" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E486">
         <v>15.41645928485977</v>
@@ -25937,7 +25919,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25951,7 +25933,7 @@
         <v>16.53295008901819</v>
       </c>
       <c r="D487" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E487">
         <v>8.24961705438853</v>
@@ -26001,7 +25983,7 @@
         <v>16.39809781749685</v>
       </c>
       <c r="D488" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E488">
         <v>8.24961705438853</v>
@@ -26051,7 +26033,7 @@
         <v>8.646669450447945</v>
       </c>
       <c r="D489" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E489">
         <v>0.5067815058065008</v>
@@ -26087,7 +26069,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26101,7 +26083,7 @@
         <v>11.10765720787195</v>
       </c>
       <c r="D490" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E490">
         <v>0.5067815058065008</v>
@@ -26137,7 +26119,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26151,7 +26133,7 @@
         <v>8.708207114263224</v>
       </c>
       <c r="D491" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E491">
         <v>0.5067815058065008</v>
@@ -26187,7 +26169,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26201,7 +26183,7 @@
         <v>7.091043911098566</v>
       </c>
       <c r="D492" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E492">
         <v>-0.9493259013959516</v>
@@ -26251,7 +26233,7 @@
         <v>9.494415907805923</v>
       </c>
       <c r="D493" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E493">
         <v>-0.9493259013959516</v>
@@ -26301,7 +26283,7 @@
         <v>7.115916999912343</v>
       </c>
       <c r="D494" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E494">
         <v>-0.9493259013959516</v>
@@ -26351,7 +26333,7 @@
         <v>5.65581229233937</v>
       </c>
       <c r="D495" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E495">
         <v>-2.292741355992099</v>
@@ -26387,7 +26369,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26401,7 +26383,7 @@
         <v>8.006027562426013</v>
       </c>
       <c r="D496" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E496">
         <v>-2.292741355992099</v>
@@ -26437,7 +26419,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26451,7 +26433,7 @@
         <v>5.646858373303601</v>
       </c>
       <c r="D497" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E497">
         <v>-2.292741355992099</v>
@@ -26487,7 +26469,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26501,7 +26483,7 @@
         <v>4.107061890942596</v>
       </c>
       <c r="D498" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E498">
         <v>-3.742413448882012</v>
@@ -26537,7 +26519,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26551,7 +26533,7 @@
         <v>6.399916035051582</v>
       </c>
       <c r="D499" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E499">
         <v>-3.742413448882012</v>
@@ -26587,7 +26569,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26601,7 +26583,7 @@
         <v>4.061605437193776</v>
       </c>
       <c r="D500" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E500">
         <v>-3.742413448882012</v>
@@ -26637,7 +26619,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26651,7 +26633,7 @@
         <v>3.994587595705951</v>
       </c>
       <c r="D501" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E501">
         <v>-3.847692418834157</v>
@@ -26687,7 +26669,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26701,7 +26683,7 @@
         <v>6.283276025176541</v>
       </c>
       <c r="D502" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E502">
         <v>-3.847692418834157</v>
@@ -26737,7 +26719,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26751,7 +26733,7 @@
         <v>3.94648023264179</v>
       </c>
       <c r="D503" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E503">
         <v>-3.847692418834157</v>
@@ -26787,7 +26769,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26801,7 +26783,7 @@
         <v>3.810208807303631</v>
       </c>
       <c r="D504" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E504">
         <v>-4.02027593121074</v>
@@ -26851,7 +26833,7 @@
         <v>6.092068392759323</v>
       </c>
       <c r="D505" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E505">
         <v>-4.02027593121074</v>
@@ -26901,7 +26883,7 @@
         <v>3.757755816229981</v>
       </c>
       <c r="D506" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E506">
         <v>-4.02027593121074</v>
@@ -26951,7 +26933,7 @@
         <v>3.242943955180543</v>
       </c>
       <c r="D507" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E507">
         <v>-4.551251112659287</v>
@@ -27001,7 +26983,7 @@
         <v>5.503793731298337</v>
       </c>
       <c r="D508" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E508">
         <v>-4.551251112659287</v>
@@ -27051,7 +27033,7 @@
         <v>3.177121085437328</v>
       </c>
       <c r="D509" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E509">
         <v>-4.551251112659287</v>
@@ -27101,7 +27083,7 @@
         <v>0.5276020656298783</v>
       </c>
       <c r="D510" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E510">
         <v>-7.276209063074127</v>
@@ -27137,7 +27119,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27151,7 +27133,7 @@
         <v>2.687883623616173</v>
       </c>
       <c r="D511" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E511">
         <v>-7.276209063074127</v>
@@ -27187,7 +27169,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27201,7 +27183,7 @@
         <v>0.3977812388938915</v>
       </c>
       <c r="D512" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E512">
         <v>-7.276209063074127</v>
@@ -27237,7 +27219,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27251,7 +27233,7 @@
         <v>-0.0005009764291159513</v>
       </c>
       <c r="D513" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E513">
         <v>-7.771120443679365</v>
@@ -27287,7 +27269,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27301,7 +27283,7 @@
         <v>2.140221209629061</v>
       </c>
       <c r="D514" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E514">
         <v>-7.771120443679365</v>
@@ -27337,7 +27319,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27351,7 +27333,7 @@
         <v>-0.1427686762102667</v>
       </c>
       <c r="D515" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E515">
         <v>-7.771120443679365</v>
@@ -27387,7 +27369,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27401,7 +27383,7 @@
         <v>-0.6951028983788206</v>
       </c>
       <c r="D516" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E516">
         <v>-8.422066128110345</v>
@@ -27437,7 +27419,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27451,7 +27433,7 @@
         <v>1.419893290570108</v>
       </c>
       <c r="D517" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E517">
         <v>-8.422066128110345</v>
@@ -27487,7 +27469,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27501,7 +27483,7 @@
         <v>-0.8537416872294941</v>
       </c>
       <c r="D518" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E518">
         <v>-8.422066128110345</v>
@@ -27537,7 +27519,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27551,7 +27533,7 @@
         <v>-1.098623802898558</v>
       </c>
       <c r="D519" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E519">
         <v>-8.615075478807405</v>
@@ -27587,7 +27569,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27601,7 +27583,7 @@
         <v>1.001427167364454</v>
       </c>
       <c r="D520" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E520">
         <v>-8.615075478807405</v>
@@ -27637,7 +27619,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27651,7 +27633,7 @@
         <v>-1.266773185458455</v>
       </c>
       <c r="D521" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E521">
         <v>-8.615075478807405</v>
@@ -27687,7 +27669,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27701,7 +27683,7 @@
         <v>-1.400997181997106</v>
       </c>
       <c r="D522" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E522">
         <v>-8.898105106381124</v>
@@ -27737,7 +27719,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27751,7 +27733,7 @@
         <v>0.6878547742252223</v>
       </c>
       <c r="D523" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E523">
         <v>-8.898105106381124</v>
@@ -27787,7 +27769,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27801,7 +27783,7 @@
         <v>-1.576273209855614</v>
       </c>
       <c r="D524" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E524">
         <v>-8.898105106381124</v>
@@ -27837,7 +27819,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27851,7 +27833,7 @@
         <v>-1.724593447066837</v>
       </c>
       <c r="D525" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E525">
         <v>-9.200999926884109</v>
@@ -27887,7 +27869,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27901,7 +27883,7 @@
         <v>0.3522734623010564</v>
       </c>
       <c r="D526" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E526">
         <v>-9.200999926884109</v>
@@ -27937,7 +27919,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27951,7 +27933,7 @@
         <v>-1.907496322923627</v>
       </c>
       <c r="D527" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E527">
         <v>-9.200999926884109</v>
@@ -27987,7 +27969,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28001,7 +27983,7 @@
         <v>44.86204822710516</v>
       </c>
       <c r="D528" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E528">
         <v>35.52043652295812</v>
@@ -28037,7 +28019,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28051,7 +28033,7 @@
         <v>46.13402290259216</v>
       </c>
       <c r="D529" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E529">
         <v>36.69877772856216</v>
@@ -28087,7 +28069,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28101,7 +28083,7 @@
         <v>46.08362925847739</v>
       </c>
       <c r="D530" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E530">
         <v>36.69877772856216</v>
@@ -28137,7 +28119,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28151,7 +28133,7 @@
         <v>45.05397872766954</v>
       </c>
       <c r="D531" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E531">
         <v>35.69823850422841</v>
@@ -28187,7 +28169,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28201,7 +28183,7 @@
         <v>44.98156832800709</v>
       </c>
       <c r="D532" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E532">
         <v>35.69823850422841</v>
@@ -28237,7 +28219,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28251,7 +28233,7 @@
         <v>42.5821201676108</v>
       </c>
       <c r="D533" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E533">
         <v>33.77379366345071</v>
@@ -28287,7 +28269,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28301,7 +28283,7 @@
         <v>42.55551239448888</v>
       </c>
       <c r="D534" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E534">
         <v>33.77379366345071</v>
@@ -28337,7 +28319,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28351,7 +28333,7 @@
         <v>42.86185585668593</v>
       </c>
       <c r="D535" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E535">
         <v>33.77379366345071</v>
@@ -28387,7 +28369,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28401,7 +28383,7 @@
         <v>9.729438161046986</v>
       </c>
       <c r="D536" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E536">
         <v>4.60825443961048</v>
@@ -28437,7 +28419,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28451,7 +28433,7 @@
         <v>7.54859977610915</v>
       </c>
       <c r="D537" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E537">
         <v>2.585662830903956</v>
@@ -28487,7 +28469,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28498,10 +28480,10 @@
         <v>93</v>
       </c>
       <c r="C538">
-        <v>-0.1707707281713766</v>
+        <v>-0.07307844071422664</v>
       </c>
       <c r="D538" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E538">
         <v>4.928669866220837</v>
@@ -28510,22 +28492,22 @@
         <v>1</v>
       </c>
       <c r="G538">
-        <v>0.06233077072817137</v>
+        <v>0.06327307844071423</v>
       </c>
       <c r="H538">
         <v>0.06597133013377916</v>
       </c>
       <c r="I538">
-        <v>5.099440594392213</v>
+        <v>5.001748306935063</v>
       </c>
       <c r="J538">
         <v>1.919580511558438</v>
       </c>
       <c r="K538">
-        <v>16.28</v>
+        <v>16.5</v>
       </c>
       <c r="L538">
-        <v>31.08</v>
+        <v>31.6</v>
       </c>
       <c r="M538">
         <v>15.9</v>
@@ -28537,51 +28519,51 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B539" t="s">
         <v>94</v>
       </c>
       <c r="C539">
-        <v>-12.90519447650706</v>
+        <v>-0.1707707281713766</v>
       </c>
       <c r="D539" t="s">
         <v>206</v>
       </c>
       <c r="E539">
-        <v>-13.9966991063864</v>
+        <v>4.928669866220837</v>
       </c>
       <c r="F539">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G539">
-        <v>0.07222519447650706</v>
+        <v>0.06233077072817137</v>
       </c>
       <c r="H539">
-        <v>0.07179669910638641</v>
+        <v>0.06597133013377916</v>
       </c>
       <c r="I539">
-        <v>1.091504629879342</v>
+        <v>5.099440594392213</v>
       </c>
       <c r="J539">
-        <v>3.315046298793385</v>
+        <v>1.919580511558438</v>
       </c>
       <c r="K539">
-        <v>12.84</v>
+        <v>16.28</v>
       </c>
       <c r="L539">
-        <v>29.66</v>
+        <v>31.08</v>
       </c>
       <c r="M539">
-        <v>12.94</v>
+        <v>15.9</v>
       </c>
       <c r="N539">
-        <v>28.9</v>
+        <v>35.45</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28595,31 +28577,31 @@
         <v>0</v>
       </c>
       <c r="B540" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C540">
-        <v>-14.93671190899163</v>
+        <v>-17.70411238403614</v>
       </c>
       <c r="D540" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E540">
-        <v>-16.04403832572833</v>
+        <v>-19.36431939193691</v>
       </c>
       <c r="F540">
         <v>-1</v>
       </c>
       <c r="G540">
-        <v>0.07425671190899163</v>
+        <v>0.07702411238403614</v>
       </c>
       <c r="H540">
-        <v>0.07384403832572832</v>
+        <v>0.07654431939193691</v>
       </c>
       <c r="I540">
-        <v>1.107326416736701</v>
+        <v>1.660207007900766</v>
       </c>
       <c r="J540">
-        <v>3.47326416736695</v>
+        <v>3.688793799379762</v>
       </c>
       <c r="K540">
         <v>12.84</v>
@@ -28628,10 +28610,10 @@
         <v>29.66</v>
       </c>
       <c r="M540">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="N540">
-        <v>28.9</v>
+        <v>28.59</v>
       </c>
       <c r="O540">
         <v>1</v>
@@ -28645,31 +28627,31 @@
         <v>0</v>
       </c>
       <c r="B541" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C541">
-        <v>-17.70411238403614</v>
+        <v>-20.27114356180867</v>
       </c>
       <c r="D541" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E541">
-        <v>-18.83299176397412</v>
+        <v>-21.96333849715831</v>
       </c>
       <c r="F541">
         <v>-1</v>
       </c>
       <c r="G541">
-        <v>0.07702411238403614</v>
+        <v>0.07959114356180869</v>
       </c>
       <c r="H541">
-        <v>0.07663299176397412</v>
+        <v>0.07914333849715831</v>
       </c>
       <c r="I541">
-        <v>1.128879379937981</v>
+        <v>1.69219493534964</v>
       </c>
       <c r="J541">
-        <v>3.688793799379762</v>
+        <v>3.888718345935255</v>
       </c>
       <c r="K541">
         <v>12.84</v>
@@ -28678,10 +28660,10 @@
         <v>29.66</v>
       </c>
       <c r="M541">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="N541">
-        <v>28.9</v>
+        <v>28.59</v>
       </c>
       <c r="O541">
         <v>1</v>
@@ -28695,31 +28677,31 @@
         <v>0</v>
       </c>
       <c r="B542" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C542">
-        <v>-20.27114356180867</v>
+        <v>-21.58445273359039</v>
       </c>
       <c r="D542" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E542">
-        <v>-21.4200153964022</v>
+        <v>-23.29301289226442</v>
       </c>
       <c r="F542">
         <v>-1</v>
       </c>
       <c r="G542">
-        <v>0.07959114356180869</v>
+        <v>0.08090445273359038</v>
       </c>
       <c r="H542">
-        <v>0.07922001539640221</v>
+        <v>0.08047301289226443</v>
       </c>
       <c r="I542">
-        <v>1.148871834593525</v>
+        <v>1.708560158674025</v>
       </c>
       <c r="J542">
-        <v>3.888718345935255</v>
+        <v>3.991000991712648</v>
       </c>
       <c r="K542">
         <v>12.84</v>
@@ -28728,10 +28710,10 @@
         <v>29.66</v>
       </c>
       <c r="M542">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="N542">
-        <v>28.9</v>
+        <v>28.59</v>
       </c>
       <c r="O542">
         <v>1</v>
@@ -28745,31 +28727,31 @@
         <v>0</v>
       </c>
       <c r="B543" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C543">
-        <v>-21.58445273359039</v>
+        <v>-22.72017499184188</v>
       </c>
       <c r="D543" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E543">
-        <v>-22.74355283276166</v>
+        <v>-24.44288745279941</v>
       </c>
       <c r="F543">
         <v>-1</v>
       </c>
       <c r="G543">
-        <v>0.08090445273359038</v>
+        <v>0.08204017499184188</v>
       </c>
       <c r="H543">
-        <v>0.08054355283276167</v>
+        <v>0.0816228874527994</v>
       </c>
       <c r="I543">
-        <v>1.159100099171265</v>
+        <v>1.722712460957531</v>
       </c>
       <c r="J543">
-        <v>3.991000991712648</v>
+        <v>4.07945288098457</v>
       </c>
       <c r="K543">
         <v>12.84</v>
@@ -28778,10 +28760,10 @@
         <v>29.66</v>
       </c>
       <c r="M543">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="N543">
-        <v>28.9</v>
+        <v>28.59</v>
       </c>
       <c r="O543">
         <v>1</v>
@@ -28795,31 +28777,31 @@
         <v>0</v>
       </c>
       <c r="B544" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C544">
-        <v>-22.72017499184188</v>
+        <v>-24.32217137422709</v>
       </c>
       <c r="D544" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E544">
-        <v>-23.88812027994033</v>
+        <v>-26.06484640692774</v>
       </c>
       <c r="F544">
         <v>-1</v>
       </c>
       <c r="G544">
-        <v>0.08204017499184188</v>
+        <v>0.0836421713742271</v>
       </c>
       <c r="H544">
-        <v>0.08168812027994034</v>
+        <v>0.08324484640692774</v>
       </c>
       <c r="I544">
-        <v>1.167945288098455</v>
+        <v>1.742675032700653</v>
       </c>
       <c r="J544">
-        <v>4.07945288098457</v>
+        <v>4.204218954379057</v>
       </c>
       <c r="K544">
         <v>12.84</v>
@@ -28828,10 +28810,10 @@
         <v>29.66</v>
       </c>
       <c r="M544">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="N544">
-        <v>28.9</v>
+        <v>28.59</v>
       </c>
       <c r="O544">
         <v>1</v>
@@ -28845,31 +28827,31 @@
         <v>0</v>
       </c>
       <c r="B545" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C545">
-        <v>-24.32217137422709</v>
+        <v>-26.36953395501449</v>
       </c>
       <c r="D545" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E545">
-        <v>-25.50259326966499</v>
+        <v>-28.13772129401778</v>
       </c>
       <c r="F545">
         <v>-1</v>
       </c>
       <c r="G545">
-        <v>0.0836421713742271</v>
+        <v>0.08568953395501448</v>
       </c>
       <c r="H545">
-        <v>0.08330259326966498</v>
+        <v>0.0853177212940178</v>
       </c>
       <c r="I545">
-        <v>1.180421895437906</v>
+        <v>1.768187339003298</v>
       </c>
       <c r="J545">
-        <v>4.204218954379057</v>
+        <v>4.363670868770599</v>
       </c>
       <c r="K545">
         <v>12.84</v>
@@ -28878,10 +28860,10 @@
         <v>29.66</v>
       </c>
       <c r="M545">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="N545">
-        <v>28.9</v>
+        <v>28.59</v>
       </c>
       <c r="O545">
         <v>1</v>
@@ -28895,31 +28877,31 @@
         <v>0</v>
       </c>
       <c r="B546" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C546">
-        <v>-26.36953395501449</v>
+        <v>-28.54968755353093</v>
       </c>
       <c r="D546" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E546">
-        <v>-27.56590104189154</v>
+        <v>-30.3450419155687</v>
       </c>
       <c r="F546">
         <v>-1</v>
       </c>
       <c r="G546">
-        <v>0.08568953395501448</v>
+        <v>0.08786968755353093</v>
       </c>
       <c r="H546">
-        <v>0.08536590104189154</v>
+        <v>0.08752504191556869</v>
       </c>
       <c r="I546">
-        <v>1.196367086877057</v>
+        <v>1.79535436203777</v>
       </c>
       <c r="J546">
-        <v>4.363670868770599</v>
+        <v>4.533464762736053</v>
       </c>
       <c r="K546">
         <v>12.84</v>
@@ -28928,366 +28910,16 @@
         <v>29.66</v>
       </c>
       <c r="M546">
-        <v>12.94</v>
+        <v>13</v>
       </c>
       <c r="N546">
-        <v>28.9</v>
+        <v>28.59</v>
       </c>
       <c r="O546">
         <v>1</v>
       </c>
       <c r="P546" t="s">
         <v>416</v>
-      </c>
-    </row>
-    <row r="547" spans="1:16">
-      <c r="A547" s="1">
-        <v>0</v>
-      </c>
-      <c r="B547" t="s">
-        <v>94</v>
-      </c>
-      <c r="C547">
-        <v>-28.54968755353093</v>
-      </c>
-      <c r="D547" t="s">
-        <v>206</v>
-      </c>
-      <c r="E547">
-        <v>-29.76303402980453</v>
-      </c>
-      <c r="F547">
-        <v>-1</v>
-      </c>
-      <c r="G547">
-        <v>0.08786968755353093</v>
-      </c>
-      <c r="H547">
-        <v>0.08756303402980453</v>
-      </c>
-      <c r="I547">
-        <v>1.213346476273603</v>
-      </c>
-      <c r="J547">
-        <v>4.533464762736053</v>
-      </c>
-      <c r="K547">
-        <v>12.84</v>
-      </c>
-      <c r="L547">
-        <v>29.66</v>
-      </c>
-      <c r="M547">
-        <v>12.94</v>
-      </c>
-      <c r="N547">
-        <v>28.9</v>
-      </c>
-      <c r="O547">
-        <v>1</v>
-      </c>
-      <c r="P547" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="548" spans="1:16">
-      <c r="A548" s="1">
-        <v>0</v>
-      </c>
-      <c r="B548" t="s">
-        <v>94</v>
-      </c>
-      <c r="C548">
-        <v>-29.33284837272143</v>
-      </c>
-      <c r="D548" t="s">
-        <v>206</v>
-      </c>
-      <c r="E548">
-        <v>-30.55229423232206</v>
-      </c>
-      <c r="F548">
-        <v>-1</v>
-      </c>
-      <c r="G548">
-        <v>0.08865284837272143</v>
-      </c>
-      <c r="H548">
-        <v>0.08835229423232206</v>
-      </c>
-      <c r="I548">
-        <v>1.219445859600636</v>
-      </c>
-      <c r="J548">
-        <v>4.594458596006342</v>
-      </c>
-      <c r="K548">
-        <v>12.84</v>
-      </c>
-      <c r="L548">
-        <v>29.66</v>
-      </c>
-      <c r="M548">
-        <v>12.94</v>
-      </c>
-      <c r="N548">
-        <v>28.9</v>
-      </c>
-      <c r="O548">
-        <v>1</v>
-      </c>
-      <c r="P548" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="549" spans="1:16">
-      <c r="A549" s="1">
-        <v>0</v>
-      </c>
-      <c r="B549" t="s">
-        <v>94</v>
-      </c>
-      <c r="C549">
-        <v>-29.83092584799902</v>
-      </c>
-      <c r="D549" t="s">
-        <v>206</v>
-      </c>
-      <c r="E549">
-        <v>-31.05425081566256</v>
-      </c>
-      <c r="F549">
-        <v>-1</v>
-      </c>
-      <c r="G549">
-        <v>0.08915092584799902</v>
-      </c>
-      <c r="H549">
-        <v>0.08885425081566257</v>
-      </c>
-      <c r="I549">
-        <v>1.223324967663547</v>
-      </c>
-      <c r="J549">
-        <v>4.633249676635438</v>
-      </c>
-      <c r="K549">
-        <v>12.84</v>
-      </c>
-      <c r="L549">
-        <v>29.66</v>
-      </c>
-      <c r="M549">
-        <v>12.94</v>
-      </c>
-      <c r="N549">
-        <v>28.9</v>
-      </c>
-      <c r="O549">
-        <v>1</v>
-      </c>
-      <c r="P549" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="550" spans="1:16">
-      <c r="A550" s="1">
-        <v>0</v>
-      </c>
-      <c r="B550" t="s">
-        <v>94</v>
-      </c>
-      <c r="C550">
-        <v>-30.14320568510779</v>
-      </c>
-      <c r="D550" t="s">
-        <v>206</v>
-      </c>
-      <c r="E550">
-        <v>-31.36896273873013</v>
-      </c>
-      <c r="F550">
-        <v>-1</v>
-      </c>
-      <c r="G550">
-        <v>0.08946320568510779</v>
-      </c>
-      <c r="H550">
-        <v>0.08916896273873014</v>
-      </c>
-      <c r="I550">
-        <v>1.225757053622335</v>
-      </c>
-      <c r="J550">
-        <v>4.657570536223348</v>
-      </c>
-      <c r="K550">
-        <v>12.84</v>
-      </c>
-      <c r="L550">
-        <v>29.66</v>
-      </c>
-      <c r="M550">
-        <v>12.94</v>
-      </c>
-      <c r="N550">
-        <v>28.9</v>
-      </c>
-      <c r="O550">
-        <v>1</v>
-      </c>
-      <c r="P550" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="551" spans="1:16">
-      <c r="A551" s="1">
-        <v>0</v>
-      </c>
-      <c r="B551" t="s">
-        <v>94</v>
-      </c>
-      <c r="C551">
-        <v>-30.60644741978838</v>
-      </c>
-      <c r="D551" t="s">
-        <v>206</v>
-      </c>
-      <c r="E551">
-        <v>-31.83581227508267</v>
-      </c>
-      <c r="F551">
-        <v>-1</v>
-      </c>
-      <c r="G551">
-        <v>0.08992644741978838</v>
-      </c>
-      <c r="H551">
-        <v>0.08963581227508267</v>
-      </c>
-      <c r="I551">
-        <v>1.229364855294296</v>
-      </c>
-      <c r="J551">
-        <v>4.69364855294302</v>
-      </c>
-      <c r="K551">
-        <v>12.84</v>
-      </c>
-      <c r="L551">
-        <v>29.66</v>
-      </c>
-      <c r="M551">
-        <v>12.94</v>
-      </c>
-      <c r="N551">
-        <v>28.9</v>
-      </c>
-      <c r="O551">
-        <v>1</v>
-      </c>
-      <c r="P551" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="552" spans="1:16">
-      <c r="A552" s="1">
-        <v>0</v>
-      </c>
-      <c r="B552" t="s">
-        <v>94</v>
-      </c>
-      <c r="C552">
-        <v>-30.47809560128364</v>
-      </c>
-      <c r="D552" t="s">
-        <v>206</v>
-      </c>
-      <c r="E552">
-        <v>-31.70646083182324</v>
-      </c>
-      <c r="F552">
-        <v>-1</v>
-      </c>
-      <c r="G552">
-        <v>0.08979809560128364</v>
-      </c>
-      <c r="H552">
-        <v>0.08950646083182323</v>
-      </c>
-      <c r="I552">
-        <v>1.228365230539598</v>
-      </c>
-      <c r="J552">
-        <v>4.683652305395922</v>
-      </c>
-      <c r="K552">
-        <v>12.84</v>
-      </c>
-      <c r="L552">
-        <v>29.66</v>
-      </c>
-      <c r="M552">
-        <v>12.94</v>
-      </c>
-      <c r="N552">
-        <v>28.9</v>
-      </c>
-      <c r="O552">
-        <v>1</v>
-      </c>
-      <c r="P552" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="553" spans="1:16">
-      <c r="A553" s="1">
-        <v>0</v>
-      </c>
-      <c r="B553" t="s">
-        <v>94</v>
-      </c>
-      <c r="C553">
-        <v>-29.64491326364035</v>
-      </c>
-      <c r="D553" t="s">
-        <v>206</v>
-      </c>
-      <c r="E553">
-        <v>-30.86678953516403</v>
-      </c>
-      <c r="F553">
-        <v>-1</v>
-      </c>
-      <c r="G553">
-        <v>0.08896491326364035</v>
-      </c>
-      <c r="H553">
-        <v>0.08866678953516403</v>
-      </c>
-      <c r="I553">
-        <v>1.22187627152368</v>
-      </c>
-      <c r="J553">
-        <v>4.618762715236787</v>
-      </c>
-      <c r="K553">
-        <v>12.84</v>
-      </c>
-      <c r="L553">
-        <v>29.66</v>
-      </c>
-      <c r="M553">
-        <v>12.94</v>
-      </c>
-      <c r="N553">
-        <v>28.9</v>
-      </c>
-      <c r="O553">
-        <v>1</v>
-      </c>
-      <c r="P553" t="s">
-        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="412">
   <si>
     <t>trade_time</t>
   </si>
@@ -295,12 +295,12 @@
     <t>2021-01-15</t>
   </si>
   <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
     <t>2021-03-10</t>
   </si>
   <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
     <t>2021-08-20</t>
   </si>
   <si>
@@ -637,7 +637,7 @@
     <t>2021-05-14</t>
   </si>
   <si>
-    <t>2021-08-30</t>
+    <t>2021-08-31</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1246,25 +1246,10 @@
     <t>2020-12-18</t>
   </si>
   <si>
-    <t>2021-01-05</t>
-  </si>
-  <si>
     <t>2021-01-06</t>
   </si>
   <si>
     <t>2021-01-07</t>
-  </si>
-  <si>
-    <t>2021-01-08</t>
-  </si>
-  <si>
-    <t>2021-01-11</t>
-  </si>
-  <si>
-    <t>2021-01-12</t>
-  </si>
-  <si>
-    <t>2021-01-13</t>
   </si>
 </sst>
 </file>
@@ -1622,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P546"/>
+  <dimension ref="A1:P542"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28424,96 +28409,96 @@
     </row>
     <row r="537" spans="1:16">
       <c r="A537" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B537" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C537">
-        <v>7.54859977610915</v>
+        <v>1.841930457020688</v>
       </c>
       <c r="D537" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E537">
-        <v>2.585662830903956</v>
+        <v>6.89439153971923</v>
       </c>
       <c r="F537">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G537">
-        <v>0.07527140022389085</v>
+        <v>0.06031806954297931</v>
       </c>
       <c r="H537">
-        <v>0.06539433716909605</v>
+        <v>0.06400560846028076</v>
       </c>
       <c r="I537">
-        <v>4.962936945205193</v>
+        <v>5.052461082698542</v>
       </c>
       <c r="J537">
-        <v>1.919580511558438</v>
+        <v>1.795950217627722</v>
       </c>
       <c r="K537">
-        <v>17.64</v>
+        <v>16.28</v>
       </c>
       <c r="L537">
-        <v>41.41</v>
+        <v>31.08</v>
       </c>
       <c r="M537">
-        <v>16.36</v>
+        <v>15.9</v>
       </c>
       <c r="N537">
-        <v>33.99</v>
+        <v>35.45</v>
       </c>
       <c r="O537">
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B538" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C538">
-        <v>-0.07307844071422664</v>
+        <v>7.54859977610915</v>
       </c>
       <c r="D538" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E538">
-        <v>4.928669866220837</v>
+        <v>2.585662830903956</v>
       </c>
       <c r="F538">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G538">
-        <v>0.06327307844071423</v>
+        <v>0.07527140022389085</v>
       </c>
       <c r="H538">
-        <v>0.06597133013377916</v>
+        <v>0.06539433716909605</v>
       </c>
       <c r="I538">
-        <v>5.001748306935063</v>
+        <v>4.962936945205193</v>
       </c>
       <c r="J538">
         <v>1.919580511558438</v>
       </c>
       <c r="K538">
-        <v>16.5</v>
+        <v>17.64</v>
       </c>
       <c r="L538">
-        <v>31.6</v>
+        <v>41.41</v>
       </c>
       <c r="M538">
-        <v>15.9</v>
+        <v>16.36</v>
       </c>
       <c r="N538">
-        <v>35.45</v>
+        <v>33.99</v>
       </c>
       <c r="O538">
         <v>1</v>
@@ -28524,13 +28509,13 @@
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B539" t="s">
         <v>94</v>
       </c>
       <c r="C539">
-        <v>-0.1707707281713766</v>
+        <v>-0.07307844071422664</v>
       </c>
       <c r="D539" t="s">
         <v>206</v>
@@ -28542,22 +28527,22 @@
         <v>1</v>
       </c>
       <c r="G539">
-        <v>0.06233077072817137</v>
+        <v>0.06327307844071423</v>
       </c>
       <c r="H539">
         <v>0.06597133013377916</v>
       </c>
       <c r="I539">
-        <v>5.099440594392213</v>
+        <v>5.001748306935063</v>
       </c>
       <c r="J539">
         <v>1.919580511558438</v>
       </c>
       <c r="K539">
-        <v>16.28</v>
+        <v>16.5</v>
       </c>
       <c r="L539">
-        <v>31.08</v>
+        <v>31.6</v>
       </c>
       <c r="M539">
         <v>15.9</v>
@@ -28574,52 +28559,52 @@
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B540" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C540">
-        <v>-17.70411238403614</v>
+        <v>-0.1707707281713766</v>
       </c>
       <c r="D540" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E540">
-        <v>-19.36431939193691</v>
+        <v>4.928669866220837</v>
       </c>
       <c r="F540">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G540">
-        <v>0.07702411238403614</v>
+        <v>0.06233077072817137</v>
       </c>
       <c r="H540">
-        <v>0.07654431939193691</v>
+        <v>0.06597133013377916</v>
       </c>
       <c r="I540">
-        <v>1.660207007900766</v>
+        <v>5.099440594392213</v>
       </c>
       <c r="J540">
-        <v>3.688793799379762</v>
+        <v>1.919580511558438</v>
       </c>
       <c r="K540">
-        <v>12.84</v>
+        <v>16.28</v>
       </c>
       <c r="L540">
-        <v>29.66</v>
+        <v>31.08</v>
       </c>
       <c r="M540">
-        <v>13</v>
+        <v>15.9</v>
       </c>
       <c r="N540">
-        <v>28.59</v>
+        <v>35.45</v>
       </c>
       <c r="O540">
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28636,7 +28621,7 @@
         <v>207</v>
       </c>
       <c r="E541">
-        <v>-21.96333849715831</v>
+        <v>-21.79111286407702</v>
       </c>
       <c r="F541">
         <v>-1</v>
@@ -28645,10 +28630,10 @@
         <v>0.07959114356180869</v>
       </c>
       <c r="H541">
-        <v>0.07914333849715831</v>
+        <v>0.07947111286407701</v>
       </c>
       <c r="I541">
-        <v>1.69219493534964</v>
+        <v>1.519969302268343</v>
       </c>
       <c r="J541">
         <v>3.888718345935255</v>
@@ -28660,16 +28645,16 @@
         <v>29.66</v>
       </c>
       <c r="M541">
-        <v>13</v>
+        <v>13.02</v>
       </c>
       <c r="N541">
-        <v>28.59</v>
+        <v>28.84</v>
       </c>
       <c r="O541">
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28686,7 +28671,7 @@
         <v>207</v>
       </c>
       <c r="E542">
-        <v>-23.29301289226442</v>
+        <v>-23.12283291209867</v>
       </c>
       <c r="F542">
         <v>-1</v>
@@ -28695,10 +28680,10 @@
         <v>0.08090445273359038</v>
       </c>
       <c r="H542">
-        <v>0.08047301289226443</v>
+        <v>0.08080283291209867</v>
       </c>
       <c r="I542">
-        <v>1.708560158674025</v>
+        <v>1.538380178508277</v>
       </c>
       <c r="J542">
         <v>3.991000991712648</v>
@@ -28710,216 +28695,16 @@
         <v>29.66</v>
       </c>
       <c r="M542">
-        <v>13</v>
+        <v>13.02</v>
       </c>
       <c r="N542">
-        <v>28.59</v>
+        <v>28.84</v>
       </c>
       <c r="O542">
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="543" spans="1:16">
-      <c r="A543" s="1">
-        <v>0</v>
-      </c>
-      <c r="B543" t="s">
-        <v>95</v>
-      </c>
-      <c r="C543">
-        <v>-22.72017499184188</v>
-      </c>
-      <c r="D543" t="s">
-        <v>207</v>
-      </c>
-      <c r="E543">
-        <v>-24.44288745279941</v>
-      </c>
-      <c r="F543">
-        <v>-1</v>
-      </c>
-      <c r="G543">
-        <v>0.08204017499184188</v>
-      </c>
-      <c r="H543">
-        <v>0.0816228874527994</v>
-      </c>
-      <c r="I543">
-        <v>1.722712460957531</v>
-      </c>
-      <c r="J543">
-        <v>4.07945288098457</v>
-      </c>
-      <c r="K543">
-        <v>12.84</v>
-      </c>
-      <c r="L543">
-        <v>29.66</v>
-      </c>
-      <c r="M543">
-        <v>13</v>
-      </c>
-      <c r="N543">
-        <v>28.59</v>
-      </c>
-      <c r="O543">
-        <v>1</v>
-      </c>
-      <c r="P543" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="544" spans="1:16">
-      <c r="A544" s="1">
-        <v>0</v>
-      </c>
-      <c r="B544" t="s">
-        <v>95</v>
-      </c>
-      <c r="C544">
-        <v>-24.32217137422709</v>
-      </c>
-      <c r="D544" t="s">
-        <v>207</v>
-      </c>
-      <c r="E544">
-        <v>-26.06484640692774</v>
-      </c>
-      <c r="F544">
-        <v>-1</v>
-      </c>
-      <c r="G544">
-        <v>0.0836421713742271</v>
-      </c>
-      <c r="H544">
-        <v>0.08324484640692774</v>
-      </c>
-      <c r="I544">
-        <v>1.742675032700653</v>
-      </c>
-      <c r="J544">
-        <v>4.204218954379057</v>
-      </c>
-      <c r="K544">
-        <v>12.84</v>
-      </c>
-      <c r="L544">
-        <v>29.66</v>
-      </c>
-      <c r="M544">
-        <v>13</v>
-      </c>
-      <c r="N544">
-        <v>28.59</v>
-      </c>
-      <c r="O544">
-        <v>1</v>
-      </c>
-      <c r="P544" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="545" spans="1:16">
-      <c r="A545" s="1">
-        <v>0</v>
-      </c>
-      <c r="B545" t="s">
-        <v>95</v>
-      </c>
-      <c r="C545">
-        <v>-26.36953395501449</v>
-      </c>
-      <c r="D545" t="s">
-        <v>207</v>
-      </c>
-      <c r="E545">
-        <v>-28.13772129401778</v>
-      </c>
-      <c r="F545">
-        <v>-1</v>
-      </c>
-      <c r="G545">
-        <v>0.08568953395501448</v>
-      </c>
-      <c r="H545">
-        <v>0.0853177212940178</v>
-      </c>
-      <c r="I545">
-        <v>1.768187339003298</v>
-      </c>
-      <c r="J545">
-        <v>4.363670868770599</v>
-      </c>
-      <c r="K545">
-        <v>12.84</v>
-      </c>
-      <c r="L545">
-        <v>29.66</v>
-      </c>
-      <c r="M545">
-        <v>13</v>
-      </c>
-      <c r="N545">
-        <v>28.59</v>
-      </c>
-      <c r="O545">
-        <v>1</v>
-      </c>
-      <c r="P545" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="546" spans="1:16">
-      <c r="A546" s="1">
-        <v>0</v>
-      </c>
-      <c r="B546" t="s">
-        <v>95</v>
-      </c>
-      <c r="C546">
-        <v>-28.54968755353093</v>
-      </c>
-      <c r="D546" t="s">
-        <v>207</v>
-      </c>
-      <c r="E546">
-        <v>-30.3450419155687</v>
-      </c>
-      <c r="F546">
-        <v>-1</v>
-      </c>
-      <c r="G546">
-        <v>0.08786968755353093</v>
-      </c>
-      <c r="H546">
-        <v>0.08752504191556869</v>
-      </c>
-      <c r="I546">
-        <v>1.79535436203777</v>
-      </c>
-      <c r="J546">
-        <v>4.533464762736053</v>
-      </c>
-      <c r="K546">
-        <v>12.84</v>
-      </c>
-      <c r="L546">
-        <v>29.66</v>
-      </c>
-      <c r="M546">
-        <v>13</v>
-      </c>
-      <c r="N546">
-        <v>28.59</v>
-      </c>
-      <c r="O546">
-        <v>1</v>
-      </c>
-      <c r="P546" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="408">
   <si>
     <t>trade_time</t>
   </si>
@@ -301,9 +301,6 @@
     <t>2021-03-10</t>
   </si>
   <si>
-    <t>2021-08-20</t>
-  </si>
-  <si>
     <t>2016-05-10</t>
   </si>
   <si>
@@ -637,9 +634,6 @@
     <t>2021-05-14</t>
   </si>
   <si>
-    <t>2021-08-31</t>
-  </si>
-  <si>
     <t>2016-03-30</t>
   </si>
   <si>
@@ -1244,12 +1238,6 @@
   </si>
   <si>
     <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2021-01-06</t>
-  </si>
-  <si>
-    <t>2021-01-07</t>
   </si>
 </sst>
 </file>
@@ -1607,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P542"/>
+  <dimension ref="A1:P540"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1668,7 +1656,7 @@
         <v>7.937839468679289</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2">
         <v>5.219520382832306</v>
@@ -1704,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1718,7 +1706,7 @@
         <v>3.136690364271253</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E3">
         <v>5.635410691649231</v>
@@ -1754,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1768,7 +1756,7 @@
         <v>2.638216954758501</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E4">
         <v>5.635410691649231</v>
@@ -1804,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1818,7 +1806,7 @@
         <v>3.237530821347761</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5">
         <v>5.635410691649231</v>
@@ -1854,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1868,7 +1856,7 @@
         <v>3.230584002322257</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E6">
         <v>5.635410691649231</v>
@@ -1904,7 +1892,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1918,7 +1906,7 @@
         <v>3.256004230860512</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E7">
         <v>5.635410691649231</v>
@@ -1954,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1968,7 +1956,7 @@
         <v>3.286004230860513</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E8">
         <v>5.635410691649231</v>
@@ -2004,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2018,7 +2006,7 @@
         <v>7.640037484949179</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>4.941353694732751</v>
@@ -2054,7 +2042,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2068,7 +2056,7 @@
         <v>2.786527592192993</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>5.320918706633144</v>
@@ -2104,7 +2092,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2118,7 +2106,7 @@
         <v>2.28641790804436</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E11">
         <v>5.320918706633144</v>
@@ -2154,7 +2142,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2168,7 +2156,7 @@
         <v>2.897185697084776</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E12">
         <v>5.320918706633144</v>
@@ -2204,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2218,7 +2206,7 @@
         <v>2.886966328787512</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E13">
         <v>5.320918706633144</v>
@@ -2254,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2268,7 +2256,7 @@
         <v>2.917295381233409</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E14">
         <v>5.320918706633144</v>
@@ -2304,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2318,7 +2306,7 @@
         <v>2.94729538123341</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15">
         <v>5.320918706633144</v>
@@ -2354,7 +2342,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2368,7 +2356,7 @@
         <v>7.265164792922025</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E16">
         <v>4.591197883498596</v>
@@ -2404,7 +2392,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2418,7 +2406,7 @@
         <v>2.345743218051176</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E17">
         <v>4.925036665931941</v>
@@ -2454,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2468,7 +2456,7 @@
         <v>1.843573793836459</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E18">
         <v>4.925036665931941</v>
@@ -2504,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2518,7 +2506,7 @@
         <v>2.468759763339456</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E19">
         <v>4.925036665931941</v>
@@ -2554,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2568,7 +2556,7 @@
         <v>2.454420914910028</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E20">
         <v>4.925036665931941</v>
@@ -2604,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2618,7 +2606,7 @@
         <v>2.490929187554173</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E21">
         <v>4.925036665931941</v>
@@ -2654,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2668,7 +2656,7 @@
         <v>2.520929187554174</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E22">
         <v>4.925036665931941</v>
@@ -2704,7 +2692,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2718,7 +2706,7 @@
         <v>1.980046625394046</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E23">
         <v>4.596593277573533</v>
@@ -2768,7 +2756,7 @@
         <v>1.476168338596821</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E24">
         <v>4.596593277573533</v>
@@ -2818,7 +2806,7 @@
         <v>2.113316346177388</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E25">
         <v>4.596593277573533</v>
@@ -2868,7 +2856,7 @@
         <v>2.095559772582941</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E26">
         <v>4.596593277573533</v>
@@ -2918,7 +2906,7 @@
         <v>2.137194632974616</v>
       </c>
       <c r="D27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E27">
         <v>4.596593277573533</v>
@@ -2968,7 +2956,7 @@
         <v>2.167194632974617</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E28">
         <v>4.596593277573533</v>
@@ -3018,7 +3006,7 @@
         <v>2.844772647031224</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E29">
         <v>5.373230386726174</v>
@@ -3054,7 +3042,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3068,7 +3056,7 @@
         <v>2.344935136036042</v>
       </c>
       <c r="D30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E30">
         <v>5.373230386726174</v>
@@ -3104,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3118,7 +3106,7 @@
         <v>2.953797713002309</v>
       </c>
       <c r="D31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E31">
         <v>5.373230386726174</v>
@@ -3154,7 +3142,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3168,7 +3156,7 @@
         <v>2.944122691011945</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E32">
         <v>5.373230386726174</v>
@@ -3204,7 +3192,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3218,7 +3206,7 @@
         <v>2.973635223997491</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E33">
         <v>5.373230386726174</v>
@@ -3254,7 +3242,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3268,7 +3256,7 @@
         <v>3.003635223997492</v>
       </c>
       <c r="D34" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E34">
         <v>5.373230386726174</v>
@@ -3304,7 +3292,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3318,7 +3306,7 @@
         <v>7.289203935514355</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E35">
         <v>5.128184916132415</v>
@@ -3354,7 +3342,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3368,7 +3356,7 @@
         <v>-2.117497474419014</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E36">
         <v>0.8991929718719938</v>
@@ -3404,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3418,7 +3406,7 @@
         <v>-2.80975033090947</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E37">
         <v>0.2758434229577951</v>
@@ -3454,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3468,7 +3456,7 @@
         <v>-2.902998496046035</v>
       </c>
       <c r="D38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E38">
         <v>0.1918767030952893</v>
@@ -3504,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3518,7 +3506,7 @@
         <v>-2.830339867902396</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E39">
         <v>0.2573032631353307</v>
@@ -3554,7 +3542,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3568,7 +3556,7 @@
         <v>-2.537341046304341</v>
       </c>
       <c r="D40" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E40">
         <v>0.5211384810952531</v>
@@ -3604,7 +3592,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3618,7 +3606,7 @@
         <v>-2.336644974997025</v>
       </c>
       <c r="D41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E41">
         <v>0.7018582922817487</v>
@@ -3654,7 +3642,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3668,7 +3656,7 @@
         <v>-2.249226521683095</v>
       </c>
       <c r="D42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E42">
         <v>0.7018582922817487</v>
@@ -3704,7 +3692,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3718,7 +3706,7 @@
         <v>-1.845740644766149</v>
       </c>
       <c r="D43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E43">
         <v>1.143900517084994</v>
@@ -3754,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3768,7 +3756,7 @@
         <v>-1.76174710538406</v>
       </c>
       <c r="D44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E44">
         <v>1.143900517084994</v>
@@ -3804,7 +3792,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3854,7 +3842,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3868,7 +3856,7 @@
         <v>-1.483754394543759</v>
       </c>
       <c r="D46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E46">
         <v>1.469856507982922</v>
@@ -3904,7 +3892,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3918,7 +3906,7 @@
         <v>-1.402286340628343</v>
       </c>
       <c r="D47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E47">
         <v>1.469856507982922</v>
@@ -3954,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4004,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4018,7 +4006,7 @@
         <v>-1.119201343261796</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E49">
         <v>1.798123813695423</v>
@@ -4054,7 +4042,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4068,7 +4056,7 @@
         <v>-1.040276682727416</v>
       </c>
       <c r="D50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E50">
         <v>1.798123813695423</v>
@@ -4104,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4118,7 +4106,7 @@
         <v>-0.970418309242234</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E51">
         <v>-1.315795006570312</v>
@@ -4154,7 +4142,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4168,7 +4156,7 @@
         <v>-1.094604783790125</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E52">
         <v>1.627274602785022</v>
@@ -4204,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4218,7 +4206,7 @@
         <v>-1.015851727159035</v>
       </c>
       <c r="D53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E53">
         <v>1.627274602785022</v>
@@ -4254,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4268,7 +4256,7 @@
         <v>-1.190513514023774</v>
       </c>
       <c r="D54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E54">
         <v>-1.147995174237213</v>
@@ -4304,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4318,7 +4306,7 @@
         <v>-1.15006863091817</v>
       </c>
       <c r="D55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E55">
         <v>1.577640908889972</v>
@@ -4354,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4368,7 +4356,7 @@
         <v>-1.255522302285485</v>
       </c>
       <c r="D56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E56">
         <v>-0.5624021926528435</v>
@@ -4404,7 +4392,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4418,7 +4406,7 @@
         <v>-1.320960230949986</v>
       </c>
       <c r="D57" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E57">
         <v>1.424712797977779</v>
@@ -4454,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4468,7 +4456,7 @@
         <v>-1.455823154415796</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E58">
         <v>-0.3493885347260317</v>
@@ -4504,7 +4492,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4518,7 +4506,7 @@
         <v>-1.605480846937454</v>
       </c>
       <c r="D59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E59">
         <v>-0.7894370781288025</v>
@@ -4554,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4568,7 +4556,7 @@
         <v>-1.761773123733541</v>
       </c>
       <c r="D60" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E60">
         <v>-1.128596969277446</v>
@@ -4604,7 +4592,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4618,7 +4606,7 @@
         <v>-1.457944364792599</v>
       </c>
       <c r="D61" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E61">
         <v>-0.8017368070151889</v>
@@ -4654,7 +4642,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4668,7 +4656,7 @@
         <v>-1.234076514305805</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E62">
         <v>0.01703472753200685</v>
@@ -4704,7 +4692,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4718,7 +4706,7 @@
         <v>-0.7963224235233177</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E63">
         <v>0.2870665855800212</v>
@@ -4754,7 +4742,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4768,7 +4756,7 @@
         <v>-0.8942517780380754</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E64">
         <v>0.59890656545236</v>
@@ -4804,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4818,7 +4806,7 @@
         <v>-0.899307304101125</v>
       </c>
       <c r="D65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E65">
         <v>0.6876116265245429</v>
@@ -4854,7 +4842,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4868,7 +4856,7 @@
         <v>-0.8589383918075626</v>
       </c>
       <c r="D66" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E66">
         <v>0.8335609313842731</v>
@@ -4904,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4918,7 +4906,7 @@
         <v>-0.6533981903373771</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E67">
         <v>1.169788560028703</v>
@@ -4954,7 +4942,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4968,7 +4956,7 @@
         <v>4.835153534210221</v>
       </c>
       <c r="D68" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E68">
         <v>2.04429947322755</v>
@@ -5004,7 +4992,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5018,7 +5006,7 @@
         <v>-0.406918334342155</v>
       </c>
       <c r="D69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E69">
         <v>1.312995819177061</v>
@@ -5054,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5068,7 +5056,7 @@
         <v>0.04130730968482865</v>
       </c>
       <c r="D70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E70">
         <v>2.64378384364354</v>
@@ -5104,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5118,7 +5106,7 @@
         <v>5.033791575296075</v>
       </c>
       <c r="D71" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E71">
         <v>2.275021568455536</v>
@@ -5154,7 +5142,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5168,7 +5156,7 @@
         <v>-0.1691188742298735</v>
       </c>
       <c r="D72" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E72">
         <v>1.79275039480164</v>
@@ -5204,7 +5192,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5218,7 +5206,7 @@
         <v>0.2293541709380591</v>
       </c>
       <c r="D73" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E73">
         <v>2.812063918551083</v>
@@ -5254,7 +5242,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5268,7 +5256,7 @@
         <v>5.217902572011447</v>
       </c>
       <c r="D74" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E74">
         <v>2.488870208345837</v>
@@ -5304,7 +5292,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5318,7 +5306,7 @@
         <v>0.0512895398901918</v>
       </c>
       <c r="D75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E75">
         <v>1.57274123510015</v>
@@ -5354,7 +5342,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5368,7 +5356,7 @@
         <v>0.3237189931323456</v>
       </c>
       <c r="D76" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E76">
         <v>2.896509461761223</v>
@@ -5404,7 +5392,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5418,7 +5406,7 @@
         <v>5.3102923165319</v>
       </c>
       <c r="D77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E77">
         <v>2.596182761957483</v>
@@ -5454,7 +5442,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5468,7 +5456,7 @@
         <v>0.161893889624892</v>
       </c>
       <c r="D78" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E78">
         <v>1.501333830022219</v>
@@ -5504,7 +5492,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5518,7 +5506,7 @@
         <v>5.33023415169577</v>
       </c>
       <c r="D79" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E79">
         <v>2.619345606126444</v>
@@ -5554,7 +5542,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5568,7 +5556,7 @@
         <v>0.1857672504861512</v>
       </c>
       <c r="D80" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E80">
         <v>1.155646098159064</v>
@@ -5604,7 +5592,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5618,7 +5606,7 @@
         <v>5.37850629613547</v>
       </c>
       <c r="D81" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E81">
         <v>2.675414676508897</v>
@@ -5654,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5668,7 +5656,7 @@
         <v>0.243556231003037</v>
       </c>
       <c r="D82" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E82">
         <v>1.799674337820232</v>
@@ -5704,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5718,7 +5706,7 @@
         <v>5.505970450595548</v>
       </c>
       <c r="D83" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E83">
         <v>2.823466865418581</v>
@@ -5754,7 +5742,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5768,7 +5756,7 @@
         <v>0.3961498981001377</v>
       </c>
       <c r="D84" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E84">
         <v>1.846556155176511</v>
@@ -5804,7 +5792,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5818,7 +5806,7 @@
         <v>5.552898822755296</v>
       </c>
       <c r="D85" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E85">
         <v>2.877975117167079</v>
@@ -5854,7 +5842,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5868,7 +5856,7 @@
         <v>0.4523301821108561</v>
       </c>
       <c r="D86" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E86">
         <v>2.714577056552891</v>
@@ -5904,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5918,7 +5906,7 @@
         <v>0.844003460842476</v>
       </c>
       <c r="D87" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E87">
         <v>3.182739844457025</v>
@@ -5954,7 +5942,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5968,7 +5956,7 @@
         <v>5.819687109336471</v>
       </c>
       <c r="D88" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E88">
         <v>2.897855098492958</v>
@@ -6004,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6018,7 +6006,7 @@
         <v>0.7717156843363</v>
       </c>
       <c r="D89" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E89">
         <v>3.232403806926722</v>
@@ -6054,7 +6042,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6068,7 +6056,7 @@
         <v>2.174557955758587</v>
       </c>
       <c r="D90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E90">
         <v>4.552795119478848</v>
@@ -6104,7 +6092,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6118,7 +6106,7 @@
         <v>2.230502900253292</v>
       </c>
       <c r="D91" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E91">
         <v>4.552795119478848</v>
@@ -6154,7 +6142,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6168,7 +6156,7 @@
         <v>7.122392789242706</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E92">
         <v>4.410974047362672</v>
@@ -6204,7 +6192,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6218,7 +6206,7 @@
         <v>3.377229031968387</v>
       </c>
       <c r="D93" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E93">
         <v>5.847002514367812</v>
@@ -6254,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6268,7 +6256,7 @@
         <v>3.424783248024418</v>
       </c>
       <c r="D94" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E94">
         <v>5.847002514367812</v>
@@ -6304,7 +6292,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6318,7 +6306,7 @@
         <v>8.29989168013649</v>
       </c>
       <c r="D95" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E95">
         <v>5.631180854885052</v>
@@ -6354,7 +6342,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6368,7 +6356,7 @@
         <v>4.683694888843547</v>
       </c>
       <c r="D96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E96">
         <v>7.023429444093537</v>
@@ -6404,7 +6392,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6418,7 +6406,7 @@
         <v>4.722134226828356</v>
       </c>
       <c r="D97" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E97">
         <v>7.023429444093537</v>
@@ -6454,7 +6442,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6468,7 +6456,7 @@
         <v>9.579012902797984</v>
       </c>
       <c r="D98" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E98">
         <v>6.893347467132109</v>
@@ -6504,7 +6492,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6518,7 +6506,7 @@
         <v>3.961474621504259</v>
       </c>
       <c r="D99" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E99">
         <v>6.476706188649629</v>
@@ -6554,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6568,7 +6556,7 @@
         <v>8.320444610292363</v>
       </c>
       <c r="D100" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E100">
         <v>7.021567248362409</v>
@@ -6604,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6618,7 +6606,7 @@
         <v>8.530866989040167</v>
       </c>
       <c r="D101" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E101">
         <v>7.021567248362409</v>
@@ -6654,7 +6642,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6668,7 +6656,7 @@
         <v>3.2890165208482</v>
       </c>
       <c r="D102" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E102">
         <v>5.857937357507026</v>
@@ -6704,7 +6692,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6718,7 +6706,7 @@
         <v>7.698991315674085</v>
       </c>
       <c r="D103" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E103">
         <v>6.277165792762322</v>
@@ -6754,7 +6742,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6768,7 +6756,7 @@
         <v>7.862435583597616</v>
       </c>
       <c r="D104" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E104">
         <v>6.277165792762322</v>
@@ -6804,7 +6792,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6818,7 +6806,7 @@
         <v>2.706415003086228</v>
       </c>
       <c r="D105" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E105">
         <v>5.321850930983533</v>
@@ -6854,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6868,7 +6856,7 @@
         <v>7.160579134588669</v>
       </c>
       <c r="D106" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E106">
         <v>5.783497068837448</v>
@@ -6904,7 +6892,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6918,7 +6906,7 @@
         <v>7.283322697678528</v>
       </c>
       <c r="D107" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E107">
         <v>5.783497068837448</v>
@@ -6954,7 +6942,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6968,7 +6956,7 @@
         <v>2.25250194719996</v>
       </c>
       <c r="D108" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E108">
         <v>4.90417843844148</v>
@@ -7004,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7018,7 +7006,7 @@
         <v>6.741094613879405</v>
       </c>
       <c r="D109" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E109">
         <v>5.766049754225914</v>
@@ -7054,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7068,7 +7056,7 @@
         <v>6.83212768404308</v>
       </c>
       <c r="D110" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E110">
         <v>5.766049754225914</v>
@@ -7104,7 +7092,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7118,7 +7106,7 @@
         <v>1.648635956687475</v>
       </c>
       <c r="D111" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E111">
         <v>4.348525301462924</v>
@@ -7154,7 +7142,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7168,7 +7156,7 @@
         <v>6.183030834224155</v>
       </c>
       <c r="D112" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E112">
         <v>5.350064030791522</v>
@@ -7204,7 +7192,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7218,7 +7206,7 @@
         <v>6.231877657545638</v>
       </c>
       <c r="D113" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E113">
         <v>5.350064030791522</v>
@@ -7254,7 +7242,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7268,7 +7256,7 @@
         <v>1.432518806234409</v>
       </c>
       <c r="D114" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E114">
         <v>4.149663013321483</v>
@@ -7304,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7318,7 +7306,7 @@
         <v>5.983305802967131</v>
       </c>
       <c r="D115" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E115">
         <v>4.577912304600769</v>
@@ -7354,7 +7342,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7368,7 +7356,7 @@
         <v>6.017054621765944</v>
       </c>
       <c r="D116" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E116">
         <v>4.577912304600769</v>
@@ -7404,7 +7392,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7418,7 +7406,7 @@
         <v>1.226728012835469</v>
       </c>
       <c r="D117" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E117">
         <v>3.960302622589126</v>
@@ -7454,7 +7442,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7468,7 +7456,7 @@
         <v>5.793123892101445</v>
       </c>
       <c r="D118" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E118">
         <v>4.612872778687663</v>
@@ -7504,7 +7492,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7518,7 +7506,7 @@
         <v>5.812496108566997</v>
       </c>
       <c r="D119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E119">
         <v>4.612872778687663</v>
@@ -7554,7 +7542,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7568,7 +7556,7 @@
         <v>1.216947853386511</v>
       </c>
       <c r="D120" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E120">
         <v>3.951303314193975</v>
@@ -7604,7 +7592,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7618,7 +7606,7 @@
         <v>5.802774512947074</v>
       </c>
       <c r="D121" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E121">
         <v>4.403561129870987</v>
@@ -7654,7 +7642,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7668,7 +7656,7 @@
         <v>1.177523163430447</v>
       </c>
       <c r="D122" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E122">
         <v>3.915026304074722</v>
@@ -7704,7 +7692,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7718,7 +7706,7 @@
         <v>5.763585898978771</v>
       </c>
       <c r="D123" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E123">
         <v>4.466025047817013</v>
@@ -7754,7 +7742,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7768,7 +7756,7 @@
         <v>0.9680478903759173</v>
       </c>
       <c r="D124" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E124">
         <v>3.722275603719158</v>
@@ -7804,7 +7792,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7818,7 +7806,7 @@
         <v>0.8515262832029507</v>
       </c>
       <c r="D125" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E125">
         <v>3.61505711887537</v>
@@ -7854,7 +7842,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7868,7 +7856,7 @@
         <v>0.6675490824101864</v>
       </c>
       <c r="D126" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E126">
         <v>3.445768716549093</v>
@@ -7904,7 +7892,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7918,7 +7906,7 @@
         <v>0.2453647773980379</v>
       </c>
       <c r="D127" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E127">
         <v>3.057291741278434</v>
@@ -7954,7 +7942,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7968,7 +7956,7 @@
         <v>-0.1442597189068877</v>
       </c>
       <c r="D128" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E128">
         <v>2.69877498918947</v>
@@ -8004,7 +7992,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8018,7 +8006,7 @@
         <v>3.671796227407118</v>
       </c>
       <c r="D129" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E129">
         <v>1.089748757437874</v>
@@ -8054,7 +8042,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8068,7 +8056,7 @@
         <v>-1.239097601114093</v>
       </c>
       <c r="D130" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E130">
         <v>1.261882831716061</v>
@@ -8104,7 +8092,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8118,7 +8106,7 @@
         <v>3.066548753992304</v>
       </c>
       <c r="D131" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E131">
         <v>0.4140568037443764</v>
@@ -8154,7 +8142,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8168,7 +8156,7 @@
         <v>-1.959356470902271</v>
       </c>
       <c r="D132" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E132">
         <v>0.6034425874785647</v>
@@ -8204,7 +8192,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8218,7 +8206,7 @@
         <v>2.434653904799742</v>
       </c>
       <c r="D133" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E133">
         <v>-0.2913840017675113</v>
@@ -8254,7 +8242,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8268,7 +8256,7 @@
         <v>-2.711326350820261</v>
       </c>
       <c r="D134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E134">
         <v>-0.08398696342450762</v>
@@ -8304,7 +8292,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8318,7 +8306,7 @@
         <v>2.046949385277987</v>
       </c>
       <c r="D135" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E135">
         <v>-0.7242132753428656</v>
@@ -8354,7 +8342,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8368,7 +8356,7 @@
         <v>-3.172703938184629</v>
       </c>
       <c r="D136" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E136">
         <v>-0.5057652768234711</v>
@@ -8404,7 +8392,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8418,7 +8406,7 @@
         <v>1.727381390460117</v>
       </c>
       <c r="D137" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E137">
         <v>0.5925973930511788</v>
@@ -8454,7 +8442,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8468,7 +8456,7 @@
         <v>1.685047495782005</v>
       </c>
       <c r="D138" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E138">
         <v>-1.128236762428639</v>
@@ -8504,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8518,7 +8506,7 @@
         <v>-3.603375782929252</v>
       </c>
       <c r="D139" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E139">
         <v>-0.8994732706219501</v>
@@ -8554,7 +8542,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8568,7 +8556,7 @@
         <v>1.329375274458599</v>
       </c>
       <c r="D140" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E140">
         <v>-0.02169112718700106</v>
@@ -8604,7 +8592,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8618,7 +8606,7 @@
         <v>1.370767088004978</v>
       </c>
       <c r="D141" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E141">
         <v>-1.479096125030072</v>
@@ -8654,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8668,7 +8656,7 @@
         <v>-3.977376933276734</v>
       </c>
       <c r="D142" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E142">
         <v>-1.241374521837809</v>
@@ -8704,7 +8692,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8718,7 +8706,7 @@
         <v>0.9837414768320834</v>
       </c>
       <c r="D143" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E143">
         <v>-0.5624929319466254</v>
@@ -8754,7 +8742,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8768,7 +8756,7 @@
         <v>-4.274892307557078</v>
       </c>
       <c r="D144" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E144">
         <v>-1.513354644433413</v>
@@ -8818,7 +8806,7 @@
         <v>0.7087921389242986</v>
       </c>
       <c r="D145" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E145">
         <v>-0.01219137097330147</v>
@@ -8868,7 +8856,7 @@
         <v>-6.600419867221269</v>
       </c>
       <c r="D146" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E146">
         <v>-3.935750603200287</v>
@@ -8904,7 +8892,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8918,7 +8906,7 @@
         <v>-1.740049190571469</v>
       </c>
       <c r="D147" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E147">
         <v>-3.803035064283293</v>
@@ -8954,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8968,7 +8956,7 @@
         <v>-7.356943655480499</v>
       </c>
       <c r="D148" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E148">
         <v>-4.634314907681588</v>
@@ -9004,7 +8992,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9018,7 +9006,7 @@
         <v>-2.446239742918287</v>
       </c>
       <c r="D149" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E149">
         <v>-3.284642996427294</v>
@@ -9054,7 +9042,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9068,7 +9056,7 @@
         <v>-2.764549545202325</v>
       </c>
       <c r="D150" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E150">
         <v>-3.284642996427294</v>
@@ -9104,7 +9092,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9118,7 +9106,7 @@
         <v>-8.273062059554213</v>
       </c>
       <c r="D151" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E151">
         <v>-5.480246821120623</v>
@@ -9154,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9168,7 +9156,7 @@
         <v>-3.301406720914517</v>
       </c>
       <c r="D152" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E152">
         <v>-3.80770165872979</v>
@@ -9204,7 +9192,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9218,7 +9206,7 @@
         <v>-3.640798600667189</v>
       </c>
       <c r="D153" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E153">
         <v>-3.80770165872979</v>
@@ -9254,7 +9242,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9268,7 +9256,7 @@
         <v>-9.028638086965721</v>
       </c>
       <c r="D154" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E154">
         <v>-6.177935975464312</v>
@@ -9304,7 +9292,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9318,7 +9306,7 @@
         <v>-4.006712569082914</v>
       </c>
       <c r="D155" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E155">
         <v>-5.764446572941544</v>
@@ -9354,7 +9342,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9368,7 +9356,7 @@
         <v>-4.355244481425245</v>
       </c>
       <c r="D156" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E156">
         <v>-5.764446572941544</v>
@@ -9404,7 +9392,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9418,7 +9406,7 @@
         <v>-9.288472736223071</v>
       </c>
       <c r="D157" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E157">
         <v>-6.4178639378834</v>
@@ -9454,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9468,7 +9456,7 @@
         <v>-4.249259832401776</v>
       </c>
       <c r="D158" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E158">
         <v>-5.572990039214197</v>
@@ -9504,7 +9492,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9518,7 +9506,7 @@
         <v>-4.600934905823827</v>
       </c>
       <c r="D159" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E159">
         <v>-5.572990039214197</v>
@@ -9554,7 +9542,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9568,7 +9556,7 @@
         <v>-8.391360480599353</v>
       </c>
       <c r="D160" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E160">
         <v>-5.589482056682467</v>
@@ -9604,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9618,7 +9606,7 @@
         <v>-3.41183448088206</v>
       </c>
       <c r="D161" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E161">
         <v>-4.236414237755341</v>
@@ -9654,7 +9642,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9668,7 +9656,7 @@
         <v>-3.752657389921566</v>
       </c>
       <c r="D162" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E162">
         <v>-4.236414237755341</v>
@@ -9704,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9718,7 +9706,7 @@
         <v>-7.284701623181299</v>
       </c>
       <c r="D163" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E163">
         <v>-4.567607547211761</v>
@@ -9754,7 +9742,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9768,7 +9756,7 @@
         <v>-2.378804136155122</v>
       </c>
       <c r="D164" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E164">
         <v>-3.182992288094191</v>
@@ -9804,7 +9792,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9854,7 +9842,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9904,7 +9892,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9918,7 +9906,7 @@
         <v>15.30025538505301</v>
       </c>
       <c r="D167" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E167">
         <v>12.2194473505381</v>
@@ -9954,7 +9942,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9968,7 +9956,7 @@
         <v>16.08154605938966</v>
       </c>
       <c r="D168" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E168">
         <v>12.2194473505381</v>
@@ -10004,7 +9992,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10054,7 +10042,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10104,7 +10092,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10154,7 +10142,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10204,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10254,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10304,7 +10292,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10354,7 +10342,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10404,7 +10392,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10454,7 +10442,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10504,7 +10492,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10518,7 +10506,7 @@
         <v>-2.965774048910724</v>
       </c>
       <c r="D179" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E179">
         <v>-6.323583762599906</v>
@@ -10554,7 +10542,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10568,7 +10556,7 @@
         <v>-3.841273412039687</v>
       </c>
       <c r="D180" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E180">
         <v>-6.323583762599906</v>
@@ -10604,7 +10592,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10654,7 +10642,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10668,7 +10656,7 @@
         <v>-4.596644143057084</v>
       </c>
       <c r="D182" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E182">
         <v>-7.87451662725034</v>
@@ -10704,7 +10692,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10718,7 +10706,7 @@
         <v>-5.499155847289916</v>
       </c>
       <c r="D183" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E183">
         <v>-7.87451662725034</v>
@@ -10754,7 +10742,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10804,7 +10792,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10818,7 +10806,7 @@
         <v>-6.176260919928573</v>
       </c>
       <c r="D185" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E185">
         <v>-9.588220956609884</v>
@@ -10854,7 +10842,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10868,7 +10856,7 @@
         <v>-7.104936049037125</v>
       </c>
       <c r="D186" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E186">
         <v>-9.588220956609884</v>
@@ -10904,7 +10892,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10954,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11004,7 +10992,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11018,7 +11006,7 @@
         <v>-5.957065888688689</v>
       </c>
       <c r="D189" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E189">
         <v>-9.35041930781134</v>
@@ -11054,7 +11042,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11068,7 +11056,7 @@
         <v>-6.882110458273605</v>
       </c>
       <c r="D190" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E190">
         <v>-9.35041930781134</v>
@@ -11104,7 +11092,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11118,7 +11106,7 @@
         <v>-5.75373473480284</v>
       </c>
       <c r="D191" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E191">
         <v>-9.129828159496252</v>
@@ -11168,7 +11156,7 @@
         <v>-6.675411500596677</v>
       </c>
       <c r="D192" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E192">
         <v>-9.129828159496252</v>
@@ -11218,7 +11206,7 @@
         <v>4.036863233290944</v>
       </c>
       <c r="D193" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E193">
         <v>1.091137151603181</v>
@@ -11268,7 +11256,7 @@
         <v>4.353212181898559</v>
       </c>
       <c r="D194" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E194">
         <v>1.091137151603181</v>
@@ -11318,7 +11306,7 @@
         <v>4.092859462531468</v>
       </c>
       <c r="D195" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E195">
         <v>1.091137151603181</v>
@@ -11404,7 +11392,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11454,7 +11442,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11604,7 +11592,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11654,7 +11642,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11704,7 +11692,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11754,7 +11742,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11804,7 +11792,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11854,7 +11842,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11904,7 +11892,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11954,7 +11942,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12004,7 +11992,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12054,7 +12042,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12104,7 +12092,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12154,7 +12142,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12204,7 +12192,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12254,7 +12242,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12304,7 +12292,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12318,7 +12306,7 @@
         <v>2.797016608461103</v>
       </c>
       <c r="D215" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E215">
         <v>-0.1302387600075896</v>
@@ -12354,7 +12342,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12368,7 +12356,7 @@
         <v>3.23804287129742</v>
       </c>
       <c r="D216" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E216">
         <v>-0.1302387600075896</v>
@@ -12404,7 +12392,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12418,7 +12406,7 @@
         <v>2.97076363447318</v>
       </c>
       <c r="D217" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E217">
         <v>-0.1302387600075896</v>
@@ -12454,7 +12442,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12468,7 +12456,7 @@
         <v>-2.735537076225839</v>
       </c>
       <c r="D218" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E218">
         <v>-0.06446785034954416</v>
@@ -12504,7 +12492,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12518,7 +12506,7 @@
         <v>2.142297248198716</v>
       </c>
       <c r="D219" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E219">
         <v>-0.7752043867837592</v>
@@ -12554,7 +12542,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12568,7 +12556,7 @@
         <v>2.649161212067007</v>
       </c>
       <c r="D220" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E220">
         <v>-0.7752043867837592</v>
@@ -12604,7 +12592,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12618,7 +12606,7 @@
         <v>1.866662847049479</v>
       </c>
       <c r="D221" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E221">
         <v>-0.7752043867837592</v>
@@ -12654,7 +12642,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12668,7 +12656,7 @@
         <v>-3.292719101626048</v>
       </c>
       <c r="D222" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E222">
         <v>-0.5316716843393898</v>
@@ -12704,7 +12692,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12718,7 +12706,7 @@
         <v>0.7343076746441</v>
       </c>
       <c r="D223" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E223">
         <v>-2.162218324233283</v>
@@ -12768,7 +12756,7 @@
         <v>1.382757182221791</v>
       </c>
       <c r="D224" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E224">
         <v>-2.162218324233283</v>
@@ -12818,7 +12806,7 @@
         <v>0.5792831810991643</v>
       </c>
       <c r="D225" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E225">
         <v>-2.162218324233283</v>
@@ -12868,7 +12856,7 @@
         <v>-4.4909523141297</v>
       </c>
       <c r="D226" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E226">
         <v>-1.797099453998044</v>
@@ -12918,7 +12906,7 @@
         <v>-0.5271433345479153</v>
       </c>
       <c r="D227" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E227">
         <v>-3.404876767180344</v>
@@ -12968,7 +12956,7 @@
         <v>0.2481559951831649</v>
       </c>
       <c r="D228" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E228">
         <v>-3.404876767180344</v>
@@ -13018,7 +13006,7 @@
         <v>-0.5741105721844058</v>
       </c>
       <c r="D229" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E229">
         <v>-3.404876767180344</v>
@@ -13068,7 +13056,7 @@
         <v>-5.289194339951301</v>
       </c>
       <c r="D230" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E230">
         <v>-2.93597803324387</v>
@@ -13118,7 +13106,7 @@
         <v>-1.521590007004434</v>
       </c>
       <c r="D231" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E231">
         <v>-4.774748703164175</v>
@@ -13154,7 +13142,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13168,7 +13156,7 @@
         <v>-2.373169137555241</v>
       </c>
       <c r="D232" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E232">
         <v>-4.774748703164175</v>
@@ -13204,7 +13192,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13218,7 +13206,7 @@
         <v>-6.960010441395497</v>
       </c>
       <c r="D233" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E233">
         <v>-4.500536093148853</v>
@@ -13254,7 +13242,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13268,7 +13256,7 @@
         <v>-2.452340392521911</v>
       </c>
       <c r="D234" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E234">
         <v>-5.548191233294997</v>
@@ -13318,7 +13306,7 @@
         <v>-2.754963624773605</v>
       </c>
       <c r="D235" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E235">
         <v>-5.548191233294997</v>
@@ -13368,7 +13356,7 @@
         <v>-7.838731302256715</v>
       </c>
       <c r="D236" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E236">
         <v>-5.323373390490392</v>
@@ -13418,7 +13406,7 @@
         <v>-4.58678078170076</v>
       </c>
       <c r="D237" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E237">
         <v>-7.667945163513835</v>
@@ -13454,7 +13442,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13468,7 +13456,7 @@
         <v>-5.270890369576151</v>
       </c>
       <c r="D238" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E238">
         <v>-7.667945163513835</v>
@@ -13504,7 +13492,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13518,7 +13506,7 @@
         <v>-4.902661407674056</v>
       </c>
       <c r="D239" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E239">
         <v>-7.667945163513835</v>
@@ -13554,7 +13542,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13568,7 +13556,7 @@
         <v>-9.853855147941093</v>
       </c>
       <c r="D240" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E240">
         <v>-7.21034243019923</v>
@@ -13604,7 +13592,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13618,7 +13606,7 @@
         <v>-5.59817458645032</v>
       </c>
       <c r="D241" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E241">
         <v>-8.513312611948162</v>
@@ -13654,7 +13642,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13668,7 +13656,7 @@
         <v>-5.920337161521442</v>
       </c>
       <c r="D242" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E242">
         <v>-8.513312611948162</v>
@@ -13704,7 +13692,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13718,7 +13706,7 @@
         <v>-10.78187598777789</v>
       </c>
       <c r="D243" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E243">
         <v>-7.189437361711093</v>
@@ -13754,7 +13742,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13768,7 +13756,7 @@
         <v>-10.80871141081024</v>
       </c>
       <c r="D244" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E244">
         <v>-8.104473185122753</v>
@@ -13804,7 +13792,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13818,7 +13806,7 @@
         <v>-5.98278744209609</v>
       </c>
       <c r="D245" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E245">
         <v>-8.914647765665489</v>
@@ -13854,7 +13842,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13868,7 +13856,7 @@
         <v>-6.30733891689172</v>
       </c>
       <c r="D246" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E246">
         <v>-8.914647765665489</v>
@@ -13904,7 +13892,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13918,7 +13906,7 @@
         <v>-11.21108163828114</v>
       </c>
       <c r="D247" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E247">
         <v>-7.582809516346728</v>
@@ -13954,7 +13942,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13968,7 +13956,7 @@
         <v>-11.09924338896238</v>
       </c>
       <c r="D248" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E248">
         <v>-7.582809516346728</v>
@@ -14004,7 +13992,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14018,7 +14006,7 @@
         <v>-11.17182416893544</v>
       </c>
       <c r="D249" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E249">
         <v>-8.444493245911037</v>
@@ -14054,7 +14042,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14068,7 +14056,7 @@
         <v>-6.197743032286496</v>
       </c>
       <c r="D250" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E250">
         <v>-9.138949251081566</v>
@@ -14104,7 +14092,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14118,7 +14106,7 @@
         <v>-6.52362963497151</v>
       </c>
       <c r="D251" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E251">
         <v>-9.138949251081566</v>
@@ -14154,7 +14142,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14168,7 +14156,7 @@
         <v>-11.45095961574</v>
       </c>
       <c r="D252" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E252">
         <v>-7.802660575464863</v>
@@ -14204,7 +14192,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14218,7 +14206,7 @@
         <v>-11.33467094012331</v>
       </c>
       <c r="D253" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E253">
         <v>-7.802660575464863</v>
@@ -14254,7 +14242,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14268,7 +14256,7 @@
         <v>-11.37476360812142</v>
       </c>
       <c r="D254" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E254">
         <v>-8.63452644883299</v>
@@ -14304,7 +14292,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14318,7 +14306,7 @@
         <v>-6.365423262694474</v>
       </c>
       <c r="D255" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E255">
         <v>-6.712841826990488</v>
@@ -14354,7 +14342,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14368,7 +14356,7 @@
         <v>-6.180679040630039</v>
       </c>
       <c r="D256" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E256">
         <v>-9.121143346744393</v>
@@ -14404,7 +14392,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14418,7 +14406,7 @@
         <v>-6.506459655789232</v>
       </c>
       <c r="D257" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E257">
         <v>-9.121143346744393</v>
@@ -14454,7 +14442,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14468,7 +14456,7 @@
         <v>-11.43191719026831</v>
       </c>
       <c r="D258" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E258">
         <v>-7.785207962880413</v>
@@ -14504,7 +14492,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14518,7 +14506,7 @@
         <v>-11.31598180640433</v>
       </c>
       <c r="D259" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E259">
         <v>-7.785207962880413</v>
@@ -14554,7 +14542,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14568,7 +14556,7 @@
         <v>-11.3586535041973</v>
       </c>
       <c r="D260" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E260">
         <v>-8.619440890991779</v>
@@ -14604,7 +14592,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14618,7 +14606,7 @@
         <v>-6.352422126194313</v>
       </c>
       <c r="D261" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E261">
         <v>-7.002545941158143</v>
@@ -14654,7 +14642,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14668,7 +14656,7 @@
         <v>-6.259072586714403</v>
       </c>
       <c r="D262" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E262">
         <v>-9.202945307875904</v>
@@ -14704,7 +14692,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14718,7 +14706,7 @@
         <v>-6.58534011830891</v>
       </c>
       <c r="D263" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E263">
         <v>-9.202945307875904</v>
@@ -14754,7 +14742,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14768,7 +14756,7 @@
         <v>-11.51939984314506</v>
       </c>
       <c r="D264" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E264">
         <v>-7.865386869227571</v>
@@ -14804,7 +14792,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14818,7 +14806,7 @@
         <v>-11.40184140449673</v>
       </c>
       <c r="D265" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E265">
         <v>-7.865386869227571</v>
@@ -14854,7 +14842,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14868,7 +14856,7 @@
         <v>-11.43266480236391</v>
       </c>
       <c r="D266" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E266">
         <v>-8.688745330283755</v>
@@ -14904,7 +14892,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14918,7 +14906,7 @@
         <v>-6.412150542258594</v>
       </c>
       <c r="D267" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E267">
         <v>-6.792666905080129</v>
@@ -14954,7 +14942,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14968,7 +14956,7 @@
         <v>-6.321920167701883</v>
       </c>
       <c r="D268" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E268">
         <v>-9.268525392384579</v>
@@ -15004,7 +14992,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15018,7 +15006,7 @@
         <v>-11.58953410018906</v>
       </c>
       <c r="D269" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E269">
         <v>-7.929665761583294</v>
@@ -15054,7 +15042,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15068,7 +15056,7 @@
         <v>-11.47067446938778</v>
       </c>
       <c r="D270" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E270">
         <v>-7.929665761583294</v>
@@ -15104,7 +15092,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15118,7 +15106,7 @@
         <v>-11.49199916453843</v>
       </c>
       <c r="D271" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E271">
         <v>-8.744306235214712</v>
@@ -15154,7 +15142,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15168,7 +15156,7 @@
         <v>-6.460034413487151</v>
       </c>
       <c r="D272" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E272">
         <v>-6.681381790702538</v>
@@ -15204,7 +15192,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15218,7 +15206,7 @@
         <v>-6.550476318984671</v>
       </c>
       <c r="D273" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E273">
         <v>-9.507018767636186</v>
@@ -15254,7 +15242,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15268,7 +15256,7 @@
         <v>-11.8445895153887</v>
       </c>
       <c r="D274" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E274">
         <v>-8.16342712542118</v>
@@ -15304,7 +15292,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15318,7 +15306,7 @@
         <v>-11.72099787317369</v>
       </c>
       <c r="D275" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E275">
         <v>-8.16342712542118</v>
@@ -15354,7 +15342,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15368,7 +15356,7 @@
         <v>-11.70777888500417</v>
       </c>
       <c r="D276" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E276">
         <v>-8.94636312258066</v>
@@ -15404,7 +15392,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15454,7 +15442,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15468,7 +15456,7 @@
         <v>-6.704638136207883</v>
       </c>
       <c r="D278" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E278">
         <v>-9.667883272564755</v>
@@ -15504,7 +15492,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15518,7 +15506,7 @@
         <v>-12.01662516649286</v>
       </c>
       <c r="D279" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E279">
         <v>-8.321099874299577</v>
@@ -15554,7 +15542,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15568,7 +15556,7 @@
         <v>-11.88984176822768</v>
       </c>
       <c r="D280" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E280">
         <v>-8.321099874299577</v>
@@ -15604,7 +15592,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15618,7 +15606,7 @@
         <v>-12.14300130071843</v>
       </c>
       <c r="D281" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E281">
         <v>-9.082651105922917</v>
@@ -15654,7 +15642,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15668,7 +15656,7 @@
         <v>-6.751629056158386</v>
       </c>
       <c r="D282" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E282">
         <v>-6.181746306378969</v>
@@ -15704,7 +15692,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15718,7 +15706,7 @@
         <v>-6.169874970448358</v>
       </c>
       <c r="D283" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E283">
         <v>-6.181746306378969</v>
@@ -15754,7 +15742,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15768,7 +15756,7 @@
         <v>-6.791555990766213</v>
       </c>
       <c r="D284" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E284">
         <v>-9.758580164277792</v>
@@ -15804,7 +15792,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15818,7 +15806,7 @@
         <v>-12.11362045346375</v>
       </c>
       <c r="D285" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E285">
         <v>-8.40999722451037</v>
@@ -15854,7 +15842,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15868,7 +15856,7 @@
         <v>-12.22524034737093</v>
       </c>
       <c r="D286" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E286">
         <v>-9.159491528068681</v>
@@ -15904,7 +15892,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15918,7 +15906,7 @@
         <v>-6.817852183440923</v>
       </c>
       <c r="D287" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E287">
         <v>-6.265382608492114</v>
@@ -15954,7 +15942,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15968,7 +15956,7 @@
         <v>-6.233722702947933</v>
       </c>
       <c r="D288" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E288">
         <v>-6.265382608492114</v>
@@ -16004,7 +15992,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16018,7 +16006,7 @@
         <v>-12.15514825489226</v>
       </c>
       <c r="D289" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E289">
         <v>-8.448057955318696</v>
@@ -16054,7 +16042,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16068,7 +16056,7 @@
         <v>-12.26045037566933</v>
       </c>
       <c r="D290" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E290">
         <v>-9.192390175953609</v>
@@ -16104,7 +16092,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16118,7 +16106,7 @@
         <v>-6.261058628637798</v>
       </c>
       <c r="D291" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E291">
         <v>-6.075524180706029</v>
@@ -16154,7 +16142,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16168,7 +16156,7 @@
         <v>-12.2145658985059</v>
       </c>
       <c r="D292" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E292">
         <v>-8.502514942229901</v>
@@ -16218,7 +16206,7 @@
         <v>-12.31082860040297</v>
       </c>
       <c r="D293" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E293">
         <v>-9.239461296218966</v>
@@ -16268,7 +16256,7 @@
         <v>-6.300170650816128</v>
       </c>
       <c r="D294" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E294">
         <v>-5.649532575530262</v>
@@ -16318,7 +16306,7 @@
         <v>-11.84108439837907</v>
       </c>
       <c r="D295" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E295">
         <v>-8.80055369389029</v>
@@ -16354,7 +16342,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16368,7 +16356,7 @@
         <v>-5.935476465087291</v>
       </c>
       <c r="D296" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E296">
         <v>-5.137979270573577</v>
@@ -16404,7 +16392,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16454,7 +16442,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16504,7 +16492,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16554,7 +16542,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16604,7 +16592,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16654,7 +16642,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16704,7 +16692,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16754,7 +16742,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16768,7 +16756,7 @@
         <v>-0.3501812538917548</v>
       </c>
       <c r="D304" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E304">
         <v>-4.299167540216818</v>
@@ -16804,7 +16792,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16854,7 +16842,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16868,7 +16856,7 @@
         <v>-0.2510998261771533</v>
       </c>
       <c r="D306" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E306">
         <v>-4.192512218904984</v>
@@ -16904,7 +16892,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16954,7 +16942,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16968,7 +16956,7 @@
         <v>-0.1528009024453745</v>
       </c>
       <c r="D308" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E308">
         <v>-4.086699217043329</v>
@@ -17004,7 +16992,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17054,7 +17042,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17068,7 +17056,7 @@
         <v>0.06625268284449959</v>
       </c>
       <c r="D310" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E310">
         <v>-3.850900934131047</v>
@@ -17104,7 +17092,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17154,7 +17142,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17204,7 +17192,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17254,7 +17242,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17304,7 +17292,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17354,7 +17342,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17368,7 +17356,7 @@
         <v>1.82693717047681</v>
       </c>
       <c r="D316" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E316">
         <v>0.6963720300954037</v>
@@ -17404,7 +17392,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17454,7 +17442,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17468,7 +17456,7 @@
         <v>2.198341117699623</v>
       </c>
       <c r="D318" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E318">
         <v>0.5276096580294123</v>
@@ -17504,7 +17492,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17518,7 +17506,7 @@
         <v>12.7271211800604</v>
       </c>
       <c r="D319" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E319">
         <v>10.466793520675</v>
@@ -17554,7 +17542,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17568,7 +17556,7 @@
         <v>13.26860393649666</v>
       </c>
       <c r="D320" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E320">
         <v>10.466793520675</v>
@@ -17604,7 +17592,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17618,7 +17606,7 @@
         <v>12.90082807115104</v>
       </c>
       <c r="D321" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E321">
         <v>10.466793520675</v>
@@ -17654,7 +17642,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17668,7 +17656,7 @@
         <v>12.60281108867061</v>
       </c>
       <c r="D322" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E322">
         <v>10.00917894691048</v>
@@ -17704,7 +17692,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17718,7 +17706,7 @@
         <v>13.14484756489033</v>
       </c>
       <c r="D323" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E323">
         <v>10.00917894691048</v>
@@ -17754,7 +17742,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17768,7 +17756,7 @@
         <v>12.77790227921993</v>
       </c>
       <c r="D324" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E324">
         <v>10.00917894691048</v>
@@ -17804,7 +17792,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17818,7 +17806,7 @@
         <v>12.94031582834918</v>
       </c>
       <c r="D325" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E325">
         <v>10.4990798111086</v>
@@ -17854,7 +17842,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17868,7 +17856,7 @@
         <v>13.48084894269951</v>
       </c>
       <c r="D326" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E326">
         <v>10.4990798111086</v>
@@ -17904,7 +17892,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17918,7 +17906,7 @@
         <v>13.11164861422502</v>
       </c>
       <c r="D327" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E327">
         <v>10.4990798111086</v>
@@ -17954,7 +17942,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17968,7 +17956,7 @@
         <v>12.89880385150152</v>
       </c>
       <c r="D328" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E328">
         <v>10.62546343074822</v>
@@ -18004,7 +17992,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18018,7 +18006,7 @@
         <v>13.4395218744347</v>
       </c>
       <c r="D329" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E329">
         <v>10.62546343074822</v>
@@ -18054,7 +18042,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18068,7 +18056,7 @@
         <v>13.07059890883446</v>
       </c>
       <c r="D330" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E330">
         <v>10.62546343074822</v>
@@ -18104,7 +18092,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18118,7 +18106,7 @@
         <v>12.9234363080082</v>
       </c>
       <c r="D331" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E331">
         <v>11.0537757639692</v>
@@ -18154,7 +18142,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18168,7 +18156,7 @@
         <v>13.46404460953155</v>
       </c>
       <c r="D332" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E332">
         <v>11.0537757639692</v>
@@ -18204,7 +18192,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18218,7 +18206,7 @@
         <v>13.09495706181657</v>
       </c>
       <c r="D333" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E333">
         <v>11.0537757639692</v>
@@ -18254,7 +18242,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18268,7 +18256,7 @@
         <v>13.44227382778946</v>
       </c>
       <c r="D334" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E334">
         <v>11.03770193240324</v>
@@ -18304,7 +18292,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18318,7 +18306,7 @@
         <v>13.07333239270363</v>
       </c>
       <c r="D335" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E335">
         <v>11.03770193240324</v>
@@ -18354,7 +18342,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18368,7 +18356,7 @@
         <v>13.47049330154028</v>
       </c>
       <c r="D336" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E336">
         <v>12.2200768479712</v>
@@ -18404,7 +18392,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18418,7 +18406,7 @@
         <v>13.10136247401317</v>
       </c>
       <c r="D337" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E337">
         <v>12.2200768479712</v>
@@ -18454,7 +18442,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18468,7 +18456,7 @@
         <v>13.41024108188445</v>
       </c>
       <c r="D338" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E338">
         <v>11.606966539383</v>
@@ -18504,7 +18492,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18518,7 +18506,7 @@
         <v>13.04151463167046</v>
       </c>
       <c r="D339" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E339">
         <v>11.606966539383</v>
@@ -18554,7 +18542,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18568,7 +18556,7 @@
         <v>15.99098556432473</v>
       </c>
       <c r="D340" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E340">
         <v>12.49688805745362</v>
@@ -18604,7 +18592,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18618,7 +18606,7 @@
         <v>15.82125527263218</v>
       </c>
       <c r="D341" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E341">
         <v>12.49688805745362</v>
@@ -18654,7 +18642,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18668,7 +18656,7 @@
         <v>16.12796689068343</v>
       </c>
       <c r="D342" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E342">
         <v>12.49688805745362</v>
@@ -18704,7 +18692,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18718,7 +18706,7 @@
         <v>16.05759498721028</v>
       </c>
       <c r="D343" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E343">
         <v>12.56617445478137</v>
@@ -18754,7 +18742,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18768,7 +18756,7 @@
         <v>15.8869198810087</v>
       </c>
       <c r="D344" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E344">
         <v>12.56617445478137</v>
@@ -18804,7 +18792,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18818,7 +18806,7 @@
         <v>16.19347402997512</v>
       </c>
       <c r="D345" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E345">
         <v>12.56617445478137</v>
@@ -18854,7 +18842,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18868,7 +18856,7 @@
         <v>16.08852224791477</v>
       </c>
       <c r="D346" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E346">
         <v>12.59834465504137</v>
@@ -18904,7 +18892,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18918,7 +18906,7 @@
         <v>15.9174084571642</v>
       </c>
       <c r="D347" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E347">
         <v>12.59834465504137</v>
@@ -18954,7 +18942,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18968,7 +18956,7 @@
         <v>16.22388949203912</v>
       </c>
       <c r="D348" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E348">
         <v>12.59834465504137</v>
@@ -19004,7 +18992,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19018,7 +19006,7 @@
         <v>15.99827269225045</v>
       </c>
       <c r="D349" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E349">
         <v>12.50446804867659</v>
@@ -19054,7 +19042,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19068,7 +19056,7 @@
         <v>15.82843903704122</v>
       </c>
       <c r="D350" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E350">
         <v>12.50446804867659</v>
@@ -19104,7 +19092,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19118,7 +19106,7 @@
         <v>16.13513342783969</v>
       </c>
       <c r="D351" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E351">
         <v>12.50446804867659</v>
@@ -19154,7 +19142,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19168,7 +19156,7 @@
         <v>10.5571576031199</v>
       </c>
       <c r="D352" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E352">
         <v>11.2357781978979</v>
@@ -19218,7 +19206,7 @@
         <v>10.4146275818384</v>
       </c>
       <c r="D353" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E353">
         <v>11.2357781978979</v>
@@ -19268,7 +19256,7 @@
         <v>11.02395259544049</v>
       </c>
       <c r="D354" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E354">
         <v>11.2357781978979</v>
@@ -19354,7 +19342,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19404,7 +19392,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19454,7 +19442,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19504,7 +19492,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19554,7 +19542,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19604,7 +19592,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19654,7 +19642,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19704,7 +19692,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19718,7 +19706,7 @@
         <v>7.109582508392513</v>
       </c>
       <c r="D363" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E363">
         <v>10.1191386498793</v>
@@ -19768,7 +19756,7 @@
         <v>8.320739177217412</v>
       </c>
       <c r="D364" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E364">
         <v>10.1191386498793</v>
@@ -19854,7 +19842,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19904,7 +19892,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19918,7 +19906,7 @@
         <v>5.429328338517664</v>
       </c>
       <c r="D367" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E367">
         <v>6.453570540990412</v>
@@ -19954,7 +19942,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19968,7 +19956,7 @@
         <v>4.28114123100805</v>
       </c>
       <c r="D368" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E368">
         <v>5.201857907737669</v>
@@ -20004,7 +19992,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20018,7 +20006,7 @@
         <v>3.478556159579213</v>
       </c>
       <c r="D369" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E369">
         <v>4.355782779043444</v>
@@ -20054,7 +20042,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20068,7 +20056,7 @@
         <v>2.542133382528917</v>
       </c>
       <c r="D370" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E370">
         <v>3.611162052395251</v>
@@ -20104,7 +20092,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20154,7 +20142,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20168,7 +20156,7 @@
         <v>3.166397470697689</v>
       </c>
       <c r="D372" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E372">
         <v>2.50604388321451</v>
@@ -20204,7 +20192,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20254,7 +20242,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20304,7 +20292,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20354,7 +20342,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20368,7 +20356,7 @@
         <v>0.5258114362592394</v>
       </c>
       <c r="D376" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E376">
         <v>0.9640594525915418</v>
@@ -20404,7 +20392,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20418,7 +20406,7 @@
         <v>1.029412028487577</v>
       </c>
       <c r="D377" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E377">
         <v>0.9640594525915418</v>
@@ -20454,7 +20442,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20468,7 +20456,7 @@
         <v>0.5230738845135647</v>
       </c>
       <c r="D378" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E378">
         <v>0.9640594525915418</v>
@@ -20504,7 +20492,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20518,7 +20506,7 @@
         <v>0.2932995584235911</v>
       </c>
       <c r="D379" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E379">
         <v>-0.2507339019854058</v>
@@ -20554,7 +20542,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20568,7 +20556,7 @@
         <v>0.8110931833932682</v>
       </c>
       <c r="D380" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E380">
         <v>-0.2507339019854058</v>
@@ -20604,7 +20592,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20618,7 +20606,7 @@
         <v>0.3063705065605404</v>
       </c>
       <c r="D381" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E381">
         <v>-0.2507339019854058</v>
@@ -20654,7 +20642,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20668,7 +20656,7 @@
         <v>0.25081902425989</v>
       </c>
       <c r="D382" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E382">
         <v>-1.810462939778127</v>
@@ -20704,7 +20692,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20718,7 +20706,7 @@
         <v>0.7712057537963801</v>
       </c>
       <c r="D383" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E383">
         <v>-1.810462939778127</v>
@@ -20754,7 +20742,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20768,7 +20756,7 @@
         <v>0.266778227076955</v>
       </c>
       <c r="D384" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E384">
         <v>-1.810462939778127</v>
@@ -20804,7 +20792,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20818,7 +20806,7 @@
         <v>0.2555858995649842</v>
       </c>
       <c r="D385" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E385">
         <v>-0.5322733758888774</v>
@@ -20854,7 +20842,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20868,7 +20856,7 @@
         <v>0.7756816486237952</v>
       </c>
       <c r="D386" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E386">
         <v>-0.5322733758888774</v>
@@ -20904,7 +20892,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20918,7 +20906,7 @@
         <v>0.2712210021752028</v>
       </c>
       <c r="D387" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E387">
         <v>-0.5322733758888774</v>
@@ -20954,7 +20942,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21004,7 +20992,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21054,7 +21042,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21104,7 +21092,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21154,7 +21142,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21168,7 +21156,7 @@
         <v>2.068109497945251</v>
       </c>
       <c r="D392" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E392">
         <v>1.103589803610085</v>
@@ -21204,7 +21192,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21218,7 +21206,7 @@
         <v>1.130775764308638</v>
       </c>
       <c r="D393" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E393">
         <v>1.103589803610085</v>
@@ -21254,7 +21242,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21268,7 +21256,7 @@
         <v>1.848060841515313</v>
       </c>
       <c r="D394" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E394">
         <v>0.99412281255767</v>
@@ -21304,7 +21292,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21318,7 +21306,7 @@
         <v>0.9315277271432265</v>
       </c>
       <c r="D395" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E395">
         <v>0.99412281255767</v>
@@ -21354,7 +21342,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21368,7 +21356,7 @@
         <v>1.694201531226533</v>
       </c>
       <c r="D396" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E396">
         <v>0.6700023738905614</v>
@@ -21404,7 +21392,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21418,7 +21406,7 @@
         <v>0.7922123317573622</v>
       </c>
       <c r="D397" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E397">
         <v>0.6700023738905614</v>
@@ -21454,7 +21442,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21468,7 +21456,7 @@
         <v>1.513646695334067</v>
       </c>
       <c r="D398" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E398">
         <v>0.5589534979668187</v>
@@ -21504,7 +21492,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21518,7 +21506,7 @@
         <v>0.6287248684119433</v>
       </c>
       <c r="D399" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E399">
         <v>0.5589534979668187</v>
@@ -21554,7 +21542,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21604,7 +21592,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21654,7 +21642,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21668,7 +21656,7 @@
         <v>1.430312383569088</v>
       </c>
       <c r="D402" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E402">
         <v>2.785832606944602</v>
@@ -21704,7 +21692,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21718,7 +21706,7 @@
         <v>1.015447344707901</v>
       </c>
       <c r="D403" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E403">
         <v>2.785832606944602</v>
@@ -21754,7 +21742,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21768,7 +21756,7 @@
         <v>2.872497404927479</v>
       </c>
       <c r="D404" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E404">
         <v>2.785832606944602</v>
@@ -21804,7 +21792,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21818,7 +21806,7 @@
         <v>1.657667083906176</v>
       </c>
       <c r="D405" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E405">
         <v>3.010263722734074</v>
@@ -21854,7 +21842,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21868,7 +21856,7 @@
         <v>3.082432889417845</v>
       </c>
       <c r="D406" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E406">
         <v>3.010263722734074</v>
@@ -21904,7 +21892,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21918,7 +21906,7 @@
         <v>1.760495757853356</v>
       </c>
       <c r="D407" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E407">
         <v>2.967064908431617</v>
@@ -21954,7 +21942,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21968,7 +21956,7 @@
         <v>3.177383147550167</v>
       </c>
       <c r="D408" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E408">
         <v>2.967064908431617</v>
@@ -22004,7 +21992,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22018,7 +22006,7 @@
         <v>3.419213206004784</v>
       </c>
       <c r="D409" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E409">
         <v>4.96095189349581</v>
@@ -22054,7 +22042,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22068,7 +22056,7 @@
         <v>30.71910142906406</v>
       </c>
       <c r="D410" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E410">
         <v>17.77124839717711</v>
@@ -22104,7 +22092,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22118,7 +22106,7 @@
         <v>30.74457906406285</v>
       </c>
       <c r="D411" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E411">
         <v>18.07805575594424</v>
@@ -22154,7 +22142,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22168,7 +22156,7 @@
         <v>30.94531632533681</v>
       </c>
       <c r="D412" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E412">
         <v>18.41220109884297</v>
@@ -22204,7 +22192,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22218,7 +22206,7 @@
         <v>31.10162189647678</v>
       </c>
       <c r="D413" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E413">
         <v>18.55328210136541</v>
@@ -22254,7 +22242,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22268,7 +22256,7 @@
         <v>31.28406714947664</v>
       </c>
       <c r="D414" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E414">
         <v>18.71795671283931</v>
@@ -22304,7 +22292,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22318,7 +22306,7 @@
         <v>31.41016164358475</v>
       </c>
       <c r="D415" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E415">
         <v>18.83176927570312</v>
@@ -22354,7 +22342,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22368,7 +22356,7 @@
         <v>31.50687459786862</v>
       </c>
       <c r="D416" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E416">
         <v>18.91906213703726</v>
@@ -22404,7 +22392,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22418,7 +22406,7 @@
         <v>31.56465330836859</v>
       </c>
       <c r="D417" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E417">
         <v>18.97121305105996</v>
@@ -22454,7 +22442,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22468,7 +22456,7 @@
         <v>31.59842308925229</v>
       </c>
       <c r="D418" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E418">
         <v>19.00169356757187</v>
@@ -22504,7 +22492,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22518,7 +22506,7 @@
         <v>31.66012131009328</v>
       </c>
       <c r="D419" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E419">
         <v>19.05738222144783</v>
@@ -22554,7 +22542,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22568,7 +22556,7 @@
         <v>31.70713316886447</v>
       </c>
       <c r="D420" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E420">
         <v>19.09981500306598</v>
@@ -22604,7 +22592,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22618,7 +22606,7 @@
         <v>31.87762108191551</v>
       </c>
       <c r="D421" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E421">
         <v>19.25369695056011</v>
@@ -22654,7 +22642,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22668,7 +22656,7 @@
         <v>32.04993923346682</v>
       </c>
       <c r="D422" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E422">
         <v>19.4092308665707</v>
@@ -22704,7 +22692,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22718,7 +22706,7 @@
         <v>32.21080893028861</v>
       </c>
       <c r="D423" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E423">
         <v>19.55443143707868</v>
@@ -22754,7 +22742,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22768,7 +22756,7 @@
         <v>32.44198272920474</v>
       </c>
       <c r="D424" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E424">
         <v>19.76308830752896</v>
@@ -22804,7 +22792,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22818,7 +22806,7 @@
         <v>32.60849165225912</v>
       </c>
       <c r="D425" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E425">
         <v>19.91337882898712</v>
@@ -22854,7 +22842,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22868,7 +22856,7 @@
         <v>32.78872551361854</v>
       </c>
       <c r="D426" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E426">
         <v>20.07605744411025</v>
@@ -22904,7 +22892,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22918,7 +22906,7 @@
         <v>32.88633633076009</v>
       </c>
       <c r="D427" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E427">
         <v>20.16416071412761</v>
@@ -22954,7 +22942,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22968,7 +22956,7 @@
         <v>32.92087256937922</v>
       </c>
       <c r="D428" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E428">
         <v>20.19533303340073</v>
@@ -23004,7 +22992,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23018,7 +23006,7 @@
         <v>33.06269553801688</v>
       </c>
       <c r="D429" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E429">
         <v>20.32334207652173</v>
@@ -23054,7 +23042,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23068,7 +23056,7 @@
         <v>33.22705411164569</v>
       </c>
       <c r="D430" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E430">
         <v>20.4716916981737</v>
@@ -23104,7 +23092,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23118,7 +23106,7 @@
         <v>33.43325315348858</v>
       </c>
       <c r="D431" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E431">
         <v>20.65780641775917</v>
@@ -23154,7 +23142,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23168,7 +23156,7 @@
         <v>33.53120523654898</v>
       </c>
       <c r="D432" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E432">
         <v>20.7462177135085</v>
@@ -23204,7 +23192,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23254,7 +23242,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23268,7 +23256,7 @@
         <v>33.46421187526697</v>
       </c>
       <c r="D434" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E434">
         <v>21.58554463904314</v>
@@ -23304,7 +23292,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23354,7 +23342,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23368,7 +23356,7 @@
         <v>33.20896438389043</v>
       </c>
       <c r="D436" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E436">
         <v>21.35184401382175</v>
@@ -23404,7 +23392,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23418,7 +23406,7 @@
         <v>33.24525244457716</v>
       </c>
       <c r="D437" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E437">
         <v>21.38506879665831</v>
@@ -23468,7 +23456,7 @@
         <v>33.30754061736793</v>
       </c>
       <c r="D438" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E438">
         <v>21.44209887694077</v>
@@ -23504,7 +23492,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23554,7 +23542,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23604,7 +23592,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23654,7 +23642,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23668,7 +23656,7 @@
         <v>33.37808699058778</v>
       </c>
       <c r="D442" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E442">
         <v>21.50669003683685</v>
@@ -23704,7 +23692,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23754,7 +23742,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23804,7 +23792,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23854,7 +23842,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23868,7 +23856,7 @@
         <v>33.3491605949092</v>
       </c>
       <c r="D446" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E446">
         <v>21.48020547975453</v>
@@ -23904,7 +23892,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23954,7 +23942,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24004,7 +23992,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24054,7 +24042,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24068,7 +24056,7 @@
         <v>33.21868761846164</v>
       </c>
       <c r="D450" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E450">
         <v>21.36074645586423</v>
@@ -24104,7 +24092,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24154,7 +24142,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24204,7 +24192,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24254,7 +24242,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24304,7 +24292,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24318,7 +24306,7 @@
         <v>33.10860895395319</v>
       </c>
       <c r="D455" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E455">
         <v>21.25996014615194</v>
@@ -24354,7 +24342,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24404,7 +24392,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24454,7 +24442,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24504,7 +24492,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24518,7 +24506,7 @@
         <v>32.82858702883275</v>
       </c>
       <c r="D459" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E459">
         <v>21.00357643548973</v>
@@ -24554,7 +24542,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24668,7 +24656,7 @@
         <v>32.43391527499527</v>
       </c>
       <c r="D462" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E462">
         <v>20.64222112840476</v>
@@ -24754,7 +24742,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24768,7 +24756,7 @@
         <v>32.1976037826028</v>
       </c>
       <c r="D464" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E464">
         <v>20.42585800874672</v>
@@ -24804,7 +24792,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24818,7 +24806,7 @@
         <v>31.9359757436375</v>
       </c>
       <c r="D465" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E465">
         <v>20.18631545359018</v>
@@ -24854,7 +24842,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24868,7 +24856,7 @@
         <v>31.6928085141255</v>
       </c>
       <c r="D466" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E466">
         <v>19.96367532786815</v>
@@ -24918,7 +24906,7 @@
         <v>31.38607212722557</v>
       </c>
       <c r="D467" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E467">
         <v>19.96017071526525</v>
@@ -24954,7 +24942,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24968,7 +24956,7 @@
         <v>31.09488527318194</v>
       </c>
       <c r="D468" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E468">
         <v>19.69041319680059</v>
@@ -25018,7 +25006,7 @@
         <v>28.76090315089132</v>
       </c>
       <c r="D469" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E469">
         <v>19.57543646755398</v>
@@ -25054,7 +25042,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25068,7 +25056,7 @@
         <v>30.97077487852789</v>
       </c>
       <c r="D470" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E470">
         <v>19.57543646755398</v>
@@ -25104,7 +25092,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25118,7 +25106,7 @@
         <v>28.60148803846228</v>
       </c>
       <c r="D471" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E471">
         <v>19.42949065339434</v>
@@ -25154,7 +25142,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25168,7 +25156,7 @@
         <v>30.81323523800978</v>
       </c>
       <c r="D472" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E472">
         <v>19.42949065339434</v>
@@ -25204,7 +25192,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25218,7 +25206,7 @@
         <v>28.31621253771513</v>
       </c>
       <c r="D473" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E473">
         <v>19.16831864415417</v>
@@ -25254,7 +25242,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25268,7 +25256,7 @@
         <v>30.53131591962436</v>
       </c>
       <c r="D474" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E474">
         <v>19.16831864415417</v>
@@ -25304,7 +25292,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25318,7 +25306,7 @@
         <v>28.17117124931562</v>
       </c>
       <c r="D475" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E475">
         <v>19.16188388044775</v>
@@ -25368,7 +25356,7 @@
         <v>30.52436998310014</v>
       </c>
       <c r="D476" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E476">
         <v>19.16188388044775</v>
@@ -25418,7 +25406,7 @@
         <v>28.43299823269307</v>
       </c>
       <c r="D477" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E477">
         <v>19.40417998614624</v>
@@ -25454,7 +25442,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25468,7 +25456,7 @@
         <v>28.68381801752044</v>
       </c>
       <c r="D478" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E478">
         <v>19.6362899708081</v>
@@ -25518,7 +25506,7 @@
         <v>28.80289710513282</v>
       </c>
       <c r="D479" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E479">
         <v>19.74648640215534</v>
@@ -25554,7 +25542,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25568,7 +25556,7 @@
         <v>28.66069705648685</v>
       </c>
       <c r="D480" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E480">
         <v>19.74648640215534</v>
@@ -25604,7 +25592,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25618,7 +25606,7 @@
         <v>28.92716526228032</v>
       </c>
       <c r="D481" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E481">
         <v>19.86148482649941</v>
@@ -25654,7 +25642,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25668,7 +25656,7 @@
         <v>28.78241267851456</v>
       </c>
       <c r="D482" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E482">
         <v>19.86148482649941</v>
@@ -25704,7 +25692,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25718,7 +25706,7 @@
         <v>28.69210673371983</v>
       </c>
       <c r="D483" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E483">
         <v>19.64396039358289</v>
@@ -25754,7 +25742,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25768,7 +25756,7 @@
         <v>28.55218237918936</v>
       </c>
       <c r="D484" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E484">
         <v>19.64396039358289</v>
@@ -25804,7 +25792,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25818,7 +25806,7 @@
         <v>24.1238374281487</v>
       </c>
       <c r="D485" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E485">
         <v>15.41645928485977</v>
@@ -25854,7 +25842,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25868,7 +25856,7 @@
         <v>23.88230241564499</v>
       </c>
       <c r="D486" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E486">
         <v>15.41645928485977</v>
@@ -25904,7 +25892,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25918,7 +25906,7 @@
         <v>16.53295008901819</v>
       </c>
       <c r="D487" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E487">
         <v>8.24961705438853</v>
@@ -25968,7 +25956,7 @@
         <v>16.39809781749685</v>
       </c>
       <c r="D488" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E488">
         <v>8.24961705438853</v>
@@ -26018,7 +26006,7 @@
         <v>8.646669450447945</v>
       </c>
       <c r="D489" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E489">
         <v>0.5067815058065008</v>
@@ -26054,7 +26042,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26068,7 +26056,7 @@
         <v>11.10765720787195</v>
       </c>
       <c r="D490" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E490">
         <v>0.5067815058065008</v>
@@ -26104,7 +26092,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26118,7 +26106,7 @@
         <v>8.708207114263224</v>
       </c>
       <c r="D491" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E491">
         <v>0.5067815058065008</v>
@@ -26154,7 +26142,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26168,7 +26156,7 @@
         <v>7.091043911098566</v>
       </c>
       <c r="D492" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E492">
         <v>-0.9493259013959516</v>
@@ -26218,7 +26206,7 @@
         <v>9.494415907805923</v>
       </c>
       <c r="D493" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E493">
         <v>-0.9493259013959516</v>
@@ -26268,7 +26256,7 @@
         <v>7.115916999912343</v>
       </c>
       <c r="D494" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E494">
         <v>-0.9493259013959516</v>
@@ -26318,7 +26306,7 @@
         <v>5.65581229233937</v>
       </c>
       <c r="D495" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E495">
         <v>-2.292741355992099</v>
@@ -26354,7 +26342,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26368,7 +26356,7 @@
         <v>8.006027562426013</v>
       </c>
       <c r="D496" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E496">
         <v>-2.292741355992099</v>
@@ -26404,7 +26392,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26418,7 +26406,7 @@
         <v>5.646858373303601</v>
       </c>
       <c r="D497" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E497">
         <v>-2.292741355992099</v>
@@ -26454,7 +26442,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26468,7 +26456,7 @@
         <v>4.107061890942596</v>
       </c>
       <c r="D498" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E498">
         <v>-3.742413448882012</v>
@@ -26504,7 +26492,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26518,7 +26506,7 @@
         <v>6.399916035051582</v>
       </c>
       <c r="D499" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E499">
         <v>-3.742413448882012</v>
@@ -26554,7 +26542,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26568,7 +26556,7 @@
         <v>4.061605437193776</v>
       </c>
       <c r="D500" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E500">
         <v>-3.742413448882012</v>
@@ -26604,7 +26592,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26618,7 +26606,7 @@
         <v>3.994587595705951</v>
       </c>
       <c r="D501" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E501">
         <v>-3.847692418834157</v>
@@ -26654,7 +26642,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26668,7 +26656,7 @@
         <v>6.283276025176541</v>
       </c>
       <c r="D502" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E502">
         <v>-3.847692418834157</v>
@@ -26704,7 +26692,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26718,7 +26706,7 @@
         <v>3.94648023264179</v>
       </c>
       <c r="D503" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E503">
         <v>-3.847692418834157</v>
@@ -26754,7 +26742,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26768,7 +26756,7 @@
         <v>3.810208807303631</v>
       </c>
       <c r="D504" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E504">
         <v>-4.02027593121074</v>
@@ -26818,7 +26806,7 @@
         <v>6.092068392759323</v>
       </c>
       <c r="D505" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E505">
         <v>-4.02027593121074</v>
@@ -26868,7 +26856,7 @@
         <v>3.757755816229981</v>
       </c>
       <c r="D506" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E506">
         <v>-4.02027593121074</v>
@@ -26918,7 +26906,7 @@
         <v>3.242943955180543</v>
       </c>
       <c r="D507" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E507">
         <v>-4.551251112659287</v>
@@ -26968,7 +26956,7 @@
         <v>5.503793731298337</v>
       </c>
       <c r="D508" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E508">
         <v>-4.551251112659287</v>
@@ -27018,7 +27006,7 @@
         <v>3.177121085437328</v>
       </c>
       <c r="D509" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E509">
         <v>-4.551251112659287</v>
@@ -27068,7 +27056,7 @@
         <v>0.5276020656298783</v>
       </c>
       <c r="D510" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E510">
         <v>-7.276209063074127</v>
@@ -27104,7 +27092,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27118,7 +27106,7 @@
         <v>2.687883623616173</v>
       </c>
       <c r="D511" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E511">
         <v>-7.276209063074127</v>
@@ -27154,7 +27142,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27168,7 +27156,7 @@
         <v>0.3977812388938915</v>
       </c>
       <c r="D512" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E512">
         <v>-7.276209063074127</v>
@@ -27204,7 +27192,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27218,7 +27206,7 @@
         <v>-0.0005009764291159513</v>
       </c>
       <c r="D513" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E513">
         <v>-7.771120443679365</v>
@@ -27254,7 +27242,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27268,7 +27256,7 @@
         <v>2.140221209629061</v>
       </c>
       <c r="D514" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E514">
         <v>-7.771120443679365</v>
@@ -27304,7 +27292,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27318,7 +27306,7 @@
         <v>-0.1427686762102667</v>
       </c>
       <c r="D515" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E515">
         <v>-7.771120443679365</v>
@@ -27354,7 +27342,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27368,7 +27356,7 @@
         <v>-0.6951028983788206</v>
       </c>
       <c r="D516" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E516">
         <v>-8.422066128110345</v>
@@ -27404,7 +27392,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27418,7 +27406,7 @@
         <v>1.419893290570108</v>
       </c>
       <c r="D517" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E517">
         <v>-8.422066128110345</v>
@@ -27454,7 +27442,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27468,7 +27456,7 @@
         <v>-0.8537416872294941</v>
       </c>
       <c r="D518" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E518">
         <v>-8.422066128110345</v>
@@ -27504,7 +27492,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27518,7 +27506,7 @@
         <v>-1.098623802898558</v>
       </c>
       <c r="D519" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E519">
         <v>-8.615075478807405</v>
@@ -27554,7 +27542,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27568,7 +27556,7 @@
         <v>1.001427167364454</v>
       </c>
       <c r="D520" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E520">
         <v>-8.615075478807405</v>
@@ -27604,7 +27592,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27618,7 +27606,7 @@
         <v>-1.266773185458455</v>
       </c>
       <c r="D521" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E521">
         <v>-8.615075478807405</v>
@@ -27654,7 +27642,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27668,7 +27656,7 @@
         <v>-1.400997181997106</v>
       </c>
       <c r="D522" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E522">
         <v>-8.898105106381124</v>
@@ -27704,7 +27692,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27718,7 +27706,7 @@
         <v>0.6878547742252223</v>
       </c>
       <c r="D523" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E523">
         <v>-8.898105106381124</v>
@@ -27754,7 +27742,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27768,7 +27756,7 @@
         <v>-1.576273209855614</v>
       </c>
       <c r="D524" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E524">
         <v>-8.898105106381124</v>
@@ -27804,7 +27792,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27818,7 +27806,7 @@
         <v>-1.724593447066837</v>
       </c>
       <c r="D525" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E525">
         <v>-9.200999926884109</v>
@@ -27854,7 +27842,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27868,7 +27856,7 @@
         <v>0.3522734623010564</v>
       </c>
       <c r="D526" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E526">
         <v>-9.200999926884109</v>
@@ -27904,7 +27892,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27918,7 +27906,7 @@
         <v>-1.907496322923627</v>
       </c>
       <c r="D527" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E527">
         <v>-9.200999926884109</v>
@@ -27954,7 +27942,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27968,7 +27956,7 @@
         <v>44.86204822710516</v>
       </c>
       <c r="D528" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E528">
         <v>35.52043652295812</v>
@@ -28004,7 +27992,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28018,7 +28006,7 @@
         <v>46.13402290259216</v>
       </c>
       <c r="D529" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E529">
         <v>36.69877772856216</v>
@@ -28054,7 +28042,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28068,7 +28056,7 @@
         <v>46.08362925847739</v>
       </c>
       <c r="D530" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E530">
         <v>36.69877772856216</v>
@@ -28104,7 +28092,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28118,7 +28106,7 @@
         <v>45.05397872766954</v>
       </c>
       <c r="D531" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E531">
         <v>35.69823850422841</v>
@@ -28154,7 +28142,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28168,7 +28156,7 @@
         <v>44.98156832800709</v>
       </c>
       <c r="D532" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E532">
         <v>35.69823850422841</v>
@@ -28204,7 +28192,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28218,7 +28206,7 @@
         <v>42.5821201676108</v>
       </c>
       <c r="D533" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E533">
         <v>33.77379366345071</v>
@@ -28254,7 +28242,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28268,7 +28256,7 @@
         <v>42.55551239448888</v>
       </c>
       <c r="D534" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E534">
         <v>33.77379366345071</v>
@@ -28304,7 +28292,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28318,7 +28306,7 @@
         <v>42.86185585668593</v>
       </c>
       <c r="D535" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E535">
         <v>33.77379366345071</v>
@@ -28354,7 +28342,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28368,7 +28356,7 @@
         <v>9.729438161046986</v>
       </c>
       <c r="D536" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E536">
         <v>4.60825443961048</v>
@@ -28404,7 +28392,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28418,7 +28406,7 @@
         <v>1.841930457020688</v>
       </c>
       <c r="D537" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E537">
         <v>6.89439153971923</v>
@@ -28454,7 +28442,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28468,7 +28456,7 @@
         <v>7.54859977610915</v>
       </c>
       <c r="D538" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E538">
         <v>2.585662830903956</v>
@@ -28504,7 +28492,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28518,7 +28506,7 @@
         <v>-0.07307844071422664</v>
       </c>
       <c r="D539" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E539">
         <v>4.928669866220837</v>
@@ -28554,7 +28542,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28568,7 +28556,7 @@
         <v>-0.1707707281713766</v>
       </c>
       <c r="D540" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E540">
         <v>4.928669866220837</v>
@@ -28604,107 +28592,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="541" spans="1:16">
-      <c r="A541" s="1">
-        <v>0</v>
-      </c>
-      <c r="B541" t="s">
-        <v>95</v>
-      </c>
-      <c r="C541">
-        <v>-20.27114356180867</v>
-      </c>
-      <c r="D541" t="s">
-        <v>207</v>
-      </c>
-      <c r="E541">
-        <v>-21.79111286407702</v>
-      </c>
-      <c r="F541">
-        <v>-1</v>
-      </c>
-      <c r="G541">
-        <v>0.07959114356180869</v>
-      </c>
-      <c r="H541">
-        <v>0.07947111286407701</v>
-      </c>
-      <c r="I541">
-        <v>1.519969302268343</v>
-      </c>
-      <c r="J541">
-        <v>3.888718345935255</v>
-      </c>
-      <c r="K541">
-        <v>12.84</v>
-      </c>
-      <c r="L541">
-        <v>29.66</v>
-      </c>
-      <c r="M541">
-        <v>13.02</v>
-      </c>
-      <c r="N541">
-        <v>28.84</v>
-      </c>
-      <c r="O541">
-        <v>1</v>
-      </c>
-      <c r="P541" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="542" spans="1:16">
-      <c r="A542" s="1">
-        <v>0</v>
-      </c>
-      <c r="B542" t="s">
-        <v>95</v>
-      </c>
-      <c r="C542">
-        <v>-21.58445273359039</v>
-      </c>
-      <c r="D542" t="s">
-        <v>207</v>
-      </c>
-      <c r="E542">
-        <v>-23.12283291209867</v>
-      </c>
-      <c r="F542">
-        <v>-1</v>
-      </c>
-      <c r="G542">
-        <v>0.08090445273359038</v>
-      </c>
-      <c r="H542">
-        <v>0.08080283291209867</v>
-      </c>
-      <c r="I542">
-        <v>1.538380178508277</v>
-      </c>
-      <c r="J542">
-        <v>3.991000991712648</v>
-      </c>
-      <c r="K542">
-        <v>12.84</v>
-      </c>
-      <c r="L542">
-        <v>29.66</v>
-      </c>
-      <c r="M542">
-        <v>13.02</v>
-      </c>
-      <c r="N542">
-        <v>28.84</v>
-      </c>
-      <c r="O542">
-        <v>1</v>
-      </c>
-      <c r="P542" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="409">
   <si>
     <t>trade_time</t>
   </si>
@@ -632,6 +632,9 @@
   </si>
   <si>
     <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1692,7 +1695,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1742,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1792,7 +1795,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1842,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1892,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1942,7 +1945,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1992,7 +1995,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2042,7 +2045,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2092,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2142,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2192,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2242,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2292,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2342,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2392,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2442,7 +2445,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2492,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2542,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2592,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2642,7 +2645,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2692,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3042,7 +3045,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3092,7 +3095,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3142,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3192,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3242,7 +3245,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3292,7 +3295,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3342,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3392,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3442,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3492,7 +3495,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3542,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3592,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3642,7 +3645,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3692,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3742,7 +3745,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3792,7 +3795,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3842,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3892,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3942,7 +3945,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3992,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4042,7 +4045,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4092,7 +4095,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4142,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4192,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4242,7 +4245,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4292,7 +4295,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4342,7 +4345,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4392,7 +4395,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4442,7 +4445,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4492,7 +4495,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4542,7 +4545,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4592,7 +4595,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4642,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4692,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4742,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4792,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4842,7 +4845,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4892,7 +4895,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4942,7 +4945,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4992,7 +4995,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5042,7 +5045,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5092,7 +5095,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5142,7 +5145,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5192,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5242,7 +5245,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5292,7 +5295,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5342,7 +5345,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5392,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5442,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5492,7 +5495,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5542,7 +5545,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5592,7 +5595,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5642,7 +5645,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5692,7 +5695,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5742,7 +5745,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5792,7 +5795,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5842,7 +5845,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5892,7 +5895,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5942,7 +5945,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5992,7 +5995,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6042,7 +6045,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6092,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6142,7 +6145,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6192,7 +6195,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6242,7 +6245,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6292,7 +6295,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6342,7 +6345,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6392,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6442,7 +6445,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6492,7 +6495,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6542,7 +6545,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6592,7 +6595,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6642,7 +6645,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6692,7 +6695,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6742,7 +6745,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6792,7 +6795,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6842,7 +6845,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6892,7 +6895,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6942,7 +6945,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6992,7 +6995,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7042,7 +7045,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7092,7 +7095,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7142,7 +7145,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7192,7 +7195,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7242,7 +7245,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7292,7 +7295,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7342,7 +7345,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7392,7 +7395,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7442,7 +7445,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7492,7 +7495,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7542,7 +7545,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7592,7 +7595,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7642,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7692,7 +7695,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7742,7 +7745,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7792,7 +7795,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7842,7 +7845,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7892,7 +7895,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7942,7 +7945,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7992,7 +7995,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8042,7 +8045,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8092,7 +8095,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8142,7 +8145,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8192,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8242,7 +8245,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8292,7 +8295,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8342,7 +8345,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8392,7 +8395,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8442,7 +8445,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8492,7 +8495,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8542,7 +8545,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8592,7 +8595,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8642,7 +8645,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8692,7 +8695,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8742,7 +8745,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8892,7 +8895,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8942,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8992,7 +8995,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9042,7 +9045,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9092,7 +9095,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9142,7 +9145,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9192,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9242,7 +9245,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9292,7 +9295,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9342,7 +9345,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9392,7 +9395,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9442,7 +9445,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9492,7 +9495,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9542,7 +9545,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9742,7 +9745,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9792,7 +9795,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9842,7 +9845,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9892,7 +9895,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9942,7 +9945,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9992,7 +9995,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10042,7 +10045,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10092,7 +10095,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10142,7 +10145,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10192,7 +10195,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10242,7 +10245,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10292,7 +10295,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10342,7 +10345,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10392,7 +10395,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10442,7 +10445,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10492,7 +10495,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10542,7 +10545,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10592,7 +10595,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10642,7 +10645,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10692,7 +10695,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10742,7 +10745,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10792,7 +10795,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10842,7 +10845,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10892,7 +10895,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10942,7 +10945,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10992,7 +10995,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11042,7 +11045,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11092,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11392,7 +11395,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11442,7 +11445,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11592,7 +11595,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11642,7 +11645,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -12042,7 +12045,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12092,7 +12095,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12142,7 +12145,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12192,7 +12195,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12242,7 +12245,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12292,7 +12295,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12342,7 +12345,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12392,7 +12395,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12442,7 +12445,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12492,7 +12495,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12542,7 +12545,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12592,7 +12595,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12642,7 +12645,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12692,7 +12695,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -13142,7 +13145,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13192,7 +13195,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13242,7 +13245,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13442,7 +13445,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13492,7 +13495,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13542,7 +13545,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13592,7 +13595,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13642,7 +13645,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13692,7 +13695,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13742,7 +13745,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13792,7 +13795,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13842,7 +13845,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13892,7 +13895,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13942,7 +13945,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13992,7 +13995,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14042,7 +14045,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14092,7 +14095,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14142,7 +14145,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14192,7 +14195,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14242,7 +14245,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14292,7 +14295,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14342,7 +14345,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14392,7 +14395,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14442,7 +14445,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14492,7 +14495,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14542,7 +14545,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14592,7 +14595,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14642,7 +14645,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14692,7 +14695,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14742,7 +14745,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14792,7 +14795,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14842,7 +14845,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14892,7 +14895,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14942,7 +14945,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14992,7 +14995,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15042,7 +15045,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15092,7 +15095,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15142,7 +15145,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15192,7 +15195,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15242,7 +15245,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15292,7 +15295,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15342,7 +15345,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15392,7 +15395,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15442,7 +15445,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15492,7 +15495,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15542,7 +15545,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15592,7 +15595,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15642,7 +15645,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15692,7 +15695,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15742,7 +15745,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15792,7 +15795,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15842,7 +15845,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15892,7 +15895,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15942,7 +15945,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15992,7 +15995,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16042,7 +16045,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16092,7 +16095,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16142,7 +16145,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16342,7 +16345,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16392,7 +16395,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16442,7 +16445,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16492,7 +16495,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16542,7 +16545,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16592,7 +16595,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16642,7 +16645,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16692,7 +16695,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16742,7 +16745,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16792,7 +16795,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16842,7 +16845,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16892,7 +16895,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16942,7 +16945,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16992,7 +16995,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17042,7 +17045,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17092,7 +17095,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17142,7 +17145,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17192,7 +17195,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17242,7 +17245,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17292,7 +17295,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17342,7 +17345,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17392,7 +17395,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17442,7 +17445,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17492,7 +17495,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17542,7 +17545,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17592,7 +17595,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17642,7 +17645,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17692,7 +17695,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17742,7 +17745,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17792,7 +17795,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17842,7 +17845,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17892,7 +17895,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17942,7 +17945,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17992,7 +17995,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18042,7 +18045,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18092,7 +18095,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18142,7 +18145,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18192,7 +18195,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18242,7 +18245,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18292,7 +18295,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18342,7 +18345,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18392,7 +18395,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18442,7 +18445,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18492,7 +18495,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18542,7 +18545,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18592,7 +18595,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18642,7 +18645,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18692,7 +18695,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18742,7 +18745,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18792,7 +18795,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18842,7 +18845,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18892,7 +18895,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18942,7 +18945,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18992,7 +18995,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19042,7 +19045,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19092,7 +19095,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19142,7 +19145,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19342,7 +19345,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19392,7 +19395,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19442,7 +19445,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19492,7 +19495,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19542,7 +19545,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19592,7 +19595,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19642,7 +19645,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19692,7 +19695,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19842,7 +19845,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19892,7 +19895,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19942,7 +19945,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19992,7 +19995,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20042,7 +20045,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20092,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20142,7 +20145,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20192,7 +20195,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20242,7 +20245,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20292,7 +20295,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20342,7 +20345,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20392,7 +20395,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20442,7 +20445,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20492,7 +20495,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20542,7 +20545,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20592,7 +20595,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20642,7 +20645,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20692,7 +20695,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20742,7 +20745,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20792,7 +20795,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20842,7 +20845,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20892,7 +20895,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20942,7 +20945,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20992,7 +20995,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21042,7 +21045,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21092,7 +21095,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21142,7 +21145,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21192,7 +21195,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21242,7 +21245,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21292,7 +21295,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21342,7 +21345,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21392,7 +21395,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21442,7 +21445,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21492,7 +21495,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21542,7 +21545,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21592,7 +21595,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21642,7 +21645,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21692,7 +21695,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21742,7 +21745,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21792,7 +21795,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21842,7 +21845,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21892,7 +21895,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21942,7 +21945,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21992,7 +21995,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22042,7 +22045,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22092,7 +22095,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22142,7 +22145,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22192,7 +22195,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22242,7 +22245,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22292,7 +22295,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22342,7 +22345,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22392,7 +22395,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22442,7 +22445,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22492,7 +22495,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22542,7 +22545,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22592,7 +22595,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22642,7 +22645,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22692,7 +22695,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22742,7 +22745,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22792,7 +22795,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22842,7 +22845,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22892,7 +22895,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22942,7 +22945,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22992,7 +22995,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23042,7 +23045,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23092,7 +23095,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23142,7 +23145,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23192,7 +23195,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23242,7 +23245,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23292,7 +23295,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23342,7 +23345,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23392,7 +23395,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23492,7 +23495,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23542,7 +23545,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23592,7 +23595,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23642,7 +23645,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23692,7 +23695,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23742,7 +23745,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23792,7 +23795,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23842,7 +23845,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23892,7 +23895,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23942,7 +23945,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23992,7 +23995,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24042,7 +24045,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24092,7 +24095,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24142,7 +24145,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24192,7 +24195,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24242,7 +24245,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24292,7 +24295,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24342,7 +24345,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24392,7 +24395,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24442,7 +24445,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24492,7 +24495,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24542,7 +24545,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24742,7 +24745,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24792,7 +24795,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24842,7 +24845,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24942,7 +24945,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25042,7 +25045,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25092,7 +25095,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25142,7 +25145,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25192,7 +25195,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25242,7 +25245,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25292,7 +25295,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25442,7 +25445,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25542,7 +25545,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25592,7 +25595,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25642,7 +25645,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25692,7 +25695,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25742,7 +25745,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25792,7 +25795,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25842,7 +25845,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25892,7 +25895,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26042,7 +26045,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26092,7 +26095,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26142,7 +26145,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26342,7 +26345,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26392,7 +26395,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26442,7 +26445,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26492,7 +26495,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26542,7 +26545,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26592,7 +26595,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26642,7 +26645,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26692,7 +26695,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26742,7 +26745,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27092,7 +27095,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27142,7 +27145,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27192,7 +27195,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27242,7 +27245,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27292,7 +27295,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27342,7 +27345,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27392,7 +27395,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27442,7 +27445,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27492,7 +27495,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27542,7 +27545,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27592,7 +27595,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27642,7 +27645,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27692,7 +27695,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27742,7 +27745,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27792,7 +27795,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27842,7 +27845,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27892,7 +27895,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27942,7 +27945,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27992,7 +27995,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28042,7 +28045,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28092,7 +28095,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28142,7 +28145,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28192,7 +28195,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28242,7 +28245,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28292,7 +28295,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28342,7 +28345,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28392,7 +28395,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28442,7 +28445,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28456,10 +28459,10 @@
         <v>7.54859977610915</v>
       </c>
       <c r="D538" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E538">
-        <v>2.585662830903956</v>
+        <v>3.585313169516937</v>
       </c>
       <c r="F538">
         <v>-1</v>
@@ -28468,10 +28471,10 @@
         <v>0.07527140022389085</v>
       </c>
       <c r="H538">
-        <v>0.06539433716909605</v>
+        <v>0.06685468683048307</v>
       </c>
       <c r="I538">
-        <v>4.962936945205193</v>
+        <v>3.963286606592213</v>
       </c>
       <c r="J538">
         <v>1.919580511558438</v>
@@ -28483,16 +28486,16 @@
         <v>41.41</v>
       </c>
       <c r="M538">
-        <v>16.36</v>
+        <v>16.48</v>
       </c>
       <c r="N538">
-        <v>33.99</v>
+        <v>35.22</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28542,7 +28545,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28592,7 +28595,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="412">
   <si>
     <t>trade_time</t>
   </si>
@@ -301,6 +301,9 @@
     <t>2021-03-10</t>
   </si>
   <si>
+    <t>2021-08-30</t>
+  </si>
+  <si>
     <t>2016-05-10</t>
   </si>
   <si>
@@ -637,6 +640,9 @@
     <t>2021-02-03</t>
   </si>
   <si>
+    <t>2021-09-02</t>
+  </si>
+  <si>
     <t>2016-03-30</t>
   </si>
   <si>
@@ -1241,6 +1247,9 @@
   </si>
   <si>
     <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2021-08-27</t>
   </si>
 </sst>
 </file>
@@ -1598,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P540"/>
+  <dimension ref="A1:P541"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1659,7 +1668,7 @@
         <v>7.937839468679289</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2">
         <v>5.219520382832306</v>
@@ -1695,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1709,7 +1718,7 @@
         <v>3.136690364271253</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3">
         <v>5.635410691649231</v>
@@ -1745,7 +1754,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1759,7 +1768,7 @@
         <v>2.638216954758501</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4">
         <v>5.635410691649231</v>
@@ -1795,7 +1804,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1809,7 +1818,7 @@
         <v>3.237530821347761</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5">
         <v>5.635410691649231</v>
@@ -1845,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1859,7 +1868,7 @@
         <v>3.230584002322257</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E6">
         <v>5.635410691649231</v>
@@ -1895,7 +1904,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1909,7 +1918,7 @@
         <v>3.256004230860512</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7">
         <v>5.635410691649231</v>
@@ -1945,7 +1954,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1959,7 +1968,7 @@
         <v>3.286004230860513</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E8">
         <v>5.635410691649231</v>
@@ -1995,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2009,7 +2018,7 @@
         <v>7.640037484949179</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E9">
         <v>4.941353694732751</v>
@@ -2045,7 +2054,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2059,7 +2068,7 @@
         <v>2.786527592192993</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10">
         <v>5.320918706633144</v>
@@ -2095,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2109,7 +2118,7 @@
         <v>2.28641790804436</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>5.320918706633144</v>
@@ -2145,7 +2154,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2159,7 +2168,7 @@
         <v>2.897185697084776</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E12">
         <v>5.320918706633144</v>
@@ -2195,7 +2204,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2209,7 +2218,7 @@
         <v>2.886966328787512</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E13">
         <v>5.320918706633144</v>
@@ -2245,7 +2254,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2259,7 +2268,7 @@
         <v>2.917295381233409</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E14">
         <v>5.320918706633144</v>
@@ -2295,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2309,7 +2318,7 @@
         <v>2.94729538123341</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15">
         <v>5.320918706633144</v>
@@ -2345,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2359,7 +2368,7 @@
         <v>7.265164792922025</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E16">
         <v>4.591197883498596</v>
@@ -2395,7 +2404,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2409,7 +2418,7 @@
         <v>2.345743218051176</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E17">
         <v>4.925036665931941</v>
@@ -2445,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2459,7 +2468,7 @@
         <v>1.843573793836459</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18">
         <v>4.925036665931941</v>
@@ -2495,7 +2504,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2509,7 +2518,7 @@
         <v>2.468759763339456</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E19">
         <v>4.925036665931941</v>
@@ -2545,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2559,7 +2568,7 @@
         <v>2.454420914910028</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E20">
         <v>4.925036665931941</v>
@@ -2595,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2609,7 +2618,7 @@
         <v>2.490929187554173</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E21">
         <v>4.925036665931941</v>
@@ -2645,7 +2654,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2659,7 +2668,7 @@
         <v>2.520929187554174</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E22">
         <v>4.925036665931941</v>
@@ -2695,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2709,7 +2718,7 @@
         <v>1.980046625394046</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E23">
         <v>4.596593277573533</v>
@@ -2759,7 +2768,7 @@
         <v>1.476168338596821</v>
       </c>
       <c r="D24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E24">
         <v>4.596593277573533</v>
@@ -2809,7 +2818,7 @@
         <v>2.113316346177388</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E25">
         <v>4.596593277573533</v>
@@ -2859,7 +2868,7 @@
         <v>2.095559772582941</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E26">
         <v>4.596593277573533</v>
@@ -2909,7 +2918,7 @@
         <v>2.137194632974616</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E27">
         <v>4.596593277573533</v>
@@ -2959,7 +2968,7 @@
         <v>2.167194632974617</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E28">
         <v>4.596593277573533</v>
@@ -3009,7 +3018,7 @@
         <v>2.844772647031224</v>
       </c>
       <c r="D29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E29">
         <v>5.373230386726174</v>
@@ -3045,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3059,7 +3068,7 @@
         <v>2.344935136036042</v>
       </c>
       <c r="D30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E30">
         <v>5.373230386726174</v>
@@ -3095,7 +3104,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3109,7 +3118,7 @@
         <v>2.953797713002309</v>
       </c>
       <c r="D31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E31">
         <v>5.373230386726174</v>
@@ -3145,7 +3154,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3159,7 +3168,7 @@
         <v>2.944122691011945</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E32">
         <v>5.373230386726174</v>
@@ -3195,7 +3204,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3209,7 +3218,7 @@
         <v>2.973635223997491</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E33">
         <v>5.373230386726174</v>
@@ -3245,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3259,7 +3268,7 @@
         <v>3.003635223997492</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E34">
         <v>5.373230386726174</v>
@@ -3295,7 +3304,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3309,7 +3318,7 @@
         <v>7.289203935514355</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E35">
         <v>5.128184916132415</v>
@@ -3345,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3359,7 +3368,7 @@
         <v>-2.117497474419014</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E36">
         <v>0.8991929718719938</v>
@@ -3395,7 +3404,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3409,7 +3418,7 @@
         <v>-2.80975033090947</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E37">
         <v>0.2758434229577951</v>
@@ -3445,7 +3454,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3459,7 +3468,7 @@
         <v>-2.902998496046035</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E38">
         <v>0.1918767030952893</v>
@@ -3495,7 +3504,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3509,7 +3518,7 @@
         <v>-2.830339867902396</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E39">
         <v>0.2573032631353307</v>
@@ -3545,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3559,7 +3568,7 @@
         <v>-2.537341046304341</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E40">
         <v>0.5211384810952531</v>
@@ -3595,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3609,7 +3618,7 @@
         <v>-2.336644974997025</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E41">
         <v>0.7018582922817487</v>
@@ -3645,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3659,7 +3668,7 @@
         <v>-2.249226521683095</v>
       </c>
       <c r="D42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E42">
         <v>0.7018582922817487</v>
@@ -3695,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3709,7 +3718,7 @@
         <v>-1.845740644766149</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E43">
         <v>1.143900517084994</v>
@@ -3745,7 +3754,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3759,7 +3768,7 @@
         <v>-1.76174710538406</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E44">
         <v>1.143900517084994</v>
@@ -3795,7 +3804,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3845,7 +3854,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3859,7 +3868,7 @@
         <v>-1.483754394543759</v>
       </c>
       <c r="D46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E46">
         <v>1.469856507982922</v>
@@ -3895,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3909,7 +3918,7 @@
         <v>-1.402286340628343</v>
       </c>
       <c r="D47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E47">
         <v>1.469856507982922</v>
@@ -3945,7 +3954,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3995,7 +4004,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4009,7 +4018,7 @@
         <v>-1.119201343261796</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E49">
         <v>1.798123813695423</v>
@@ -4045,7 +4054,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4059,7 +4068,7 @@
         <v>-1.040276682727416</v>
       </c>
       <c r="D50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E50">
         <v>1.798123813695423</v>
@@ -4095,7 +4104,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4109,7 +4118,7 @@
         <v>-0.970418309242234</v>
       </c>
       <c r="D51" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E51">
         <v>-1.315795006570312</v>
@@ -4145,7 +4154,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4159,7 +4168,7 @@
         <v>-1.094604783790125</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E52">
         <v>1.627274602785022</v>
@@ -4195,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4209,7 +4218,7 @@
         <v>-1.015851727159035</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E53">
         <v>1.627274602785022</v>
@@ -4245,7 +4254,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4259,7 +4268,7 @@
         <v>-1.190513514023774</v>
       </c>
       <c r="D54" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E54">
         <v>-1.147995174237213</v>
@@ -4295,7 +4304,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4309,7 +4318,7 @@
         <v>-1.15006863091817</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E55">
         <v>1.577640908889972</v>
@@ -4345,7 +4354,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4359,7 +4368,7 @@
         <v>-1.255522302285485</v>
       </c>
       <c r="D56" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E56">
         <v>-0.5624021926528435</v>
@@ -4395,7 +4404,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4409,7 +4418,7 @@
         <v>-1.320960230949986</v>
       </c>
       <c r="D57" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E57">
         <v>1.424712797977779</v>
@@ -4445,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4459,7 +4468,7 @@
         <v>-1.455823154415796</v>
       </c>
       <c r="D58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E58">
         <v>-0.3493885347260317</v>
@@ -4495,7 +4504,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4509,7 +4518,7 @@
         <v>-1.605480846937454</v>
       </c>
       <c r="D59" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E59">
         <v>-0.7894370781288025</v>
@@ -4545,7 +4554,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4559,7 +4568,7 @@
         <v>-1.761773123733541</v>
       </c>
       <c r="D60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E60">
         <v>-1.128596969277446</v>
@@ -4595,7 +4604,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4609,7 +4618,7 @@
         <v>-1.457944364792599</v>
       </c>
       <c r="D61" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E61">
         <v>-0.8017368070151889</v>
@@ -4645,7 +4654,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4659,7 +4668,7 @@
         <v>-1.234076514305805</v>
       </c>
       <c r="D62" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E62">
         <v>0.01703472753200685</v>
@@ -4695,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4709,7 +4718,7 @@
         <v>-0.7963224235233177</v>
       </c>
       <c r="D63" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E63">
         <v>0.2870665855800212</v>
@@ -4745,7 +4754,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4759,7 +4768,7 @@
         <v>-0.8942517780380754</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E64">
         <v>0.59890656545236</v>
@@ -4795,7 +4804,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4809,7 +4818,7 @@
         <v>-0.899307304101125</v>
       </c>
       <c r="D65" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E65">
         <v>0.6876116265245429</v>
@@ -4845,7 +4854,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4859,7 +4868,7 @@
         <v>-0.8589383918075626</v>
       </c>
       <c r="D66" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E66">
         <v>0.8335609313842731</v>
@@ -4895,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4909,7 +4918,7 @@
         <v>-0.6533981903373771</v>
       </c>
       <c r="D67" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E67">
         <v>1.169788560028703</v>
@@ -4945,7 +4954,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4959,7 +4968,7 @@
         <v>4.835153534210221</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E68">
         <v>2.04429947322755</v>
@@ -4995,7 +5004,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5009,7 +5018,7 @@
         <v>-0.406918334342155</v>
       </c>
       <c r="D69" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E69">
         <v>1.312995819177061</v>
@@ -5045,7 +5054,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5059,7 +5068,7 @@
         <v>0.04130730968482865</v>
       </c>
       <c r="D70" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E70">
         <v>2.64378384364354</v>
@@ -5095,7 +5104,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5109,7 +5118,7 @@
         <v>5.033791575296075</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E71">
         <v>2.275021568455536</v>
@@ -5145,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5159,7 +5168,7 @@
         <v>-0.1691188742298735</v>
       </c>
       <c r="D72" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E72">
         <v>1.79275039480164</v>
@@ -5195,7 +5204,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5209,7 +5218,7 @@
         <v>0.2293541709380591</v>
       </c>
       <c r="D73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E73">
         <v>2.812063918551083</v>
@@ -5245,7 +5254,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5259,7 +5268,7 @@
         <v>5.217902572011447</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E74">
         <v>2.488870208345837</v>
@@ -5295,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5309,7 +5318,7 @@
         <v>0.0512895398901918</v>
       </c>
       <c r="D75" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E75">
         <v>1.57274123510015</v>
@@ -5345,7 +5354,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5359,7 +5368,7 @@
         <v>0.3237189931323456</v>
       </c>
       <c r="D76" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E76">
         <v>2.896509461761223</v>
@@ -5395,7 +5404,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5409,7 +5418,7 @@
         <v>5.3102923165319</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E77">
         <v>2.596182761957483</v>
@@ -5445,7 +5454,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5459,7 +5468,7 @@
         <v>0.161893889624892</v>
       </c>
       <c r="D78" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E78">
         <v>1.501333830022219</v>
@@ -5495,7 +5504,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5509,7 +5518,7 @@
         <v>5.33023415169577</v>
       </c>
       <c r="D79" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E79">
         <v>2.619345606126444</v>
@@ -5545,7 +5554,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5559,7 +5568,7 @@
         <v>0.1857672504861512</v>
       </c>
       <c r="D80" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E80">
         <v>1.155646098159064</v>
@@ -5595,7 +5604,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5609,7 +5618,7 @@
         <v>5.37850629613547</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E81">
         <v>2.675414676508897</v>
@@ -5645,7 +5654,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5659,7 +5668,7 @@
         <v>0.243556231003037</v>
       </c>
       <c r="D82" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E82">
         <v>1.799674337820232</v>
@@ -5695,7 +5704,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5709,7 +5718,7 @@
         <v>5.505970450595548</v>
       </c>
       <c r="D83" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E83">
         <v>2.823466865418581</v>
@@ -5745,7 +5754,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5759,7 +5768,7 @@
         <v>0.3961498981001377</v>
       </c>
       <c r="D84" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E84">
         <v>1.846556155176511</v>
@@ -5795,7 +5804,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5809,7 +5818,7 @@
         <v>5.552898822755296</v>
       </c>
       <c r="D85" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E85">
         <v>2.877975117167079</v>
@@ -5845,7 +5854,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5859,7 +5868,7 @@
         <v>0.4523301821108561</v>
       </c>
       <c r="D86" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E86">
         <v>2.714577056552891</v>
@@ -5895,7 +5904,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5909,7 +5918,7 @@
         <v>0.844003460842476</v>
       </c>
       <c r="D87" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E87">
         <v>3.182739844457025</v>
@@ -5945,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5959,7 +5968,7 @@
         <v>5.819687109336471</v>
       </c>
       <c r="D88" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E88">
         <v>2.897855098492958</v>
@@ -5995,7 +6004,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6009,7 +6018,7 @@
         <v>0.7717156843363</v>
       </c>
       <c r="D89" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E89">
         <v>3.232403806926722</v>
@@ -6045,7 +6054,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6059,7 +6068,7 @@
         <v>2.174557955758587</v>
       </c>
       <c r="D90" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E90">
         <v>4.552795119478848</v>
@@ -6095,7 +6104,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6109,7 +6118,7 @@
         <v>2.230502900253292</v>
       </c>
       <c r="D91" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E91">
         <v>4.552795119478848</v>
@@ -6145,7 +6154,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6159,7 +6168,7 @@
         <v>7.122392789242706</v>
       </c>
       <c r="D92" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E92">
         <v>4.410974047362672</v>
@@ -6195,7 +6204,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6209,7 +6218,7 @@
         <v>3.377229031968387</v>
       </c>
       <c r="D93" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E93">
         <v>5.847002514367812</v>
@@ -6245,7 +6254,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6259,7 +6268,7 @@
         <v>3.424783248024418</v>
       </c>
       <c r="D94" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E94">
         <v>5.847002514367812</v>
@@ -6295,7 +6304,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6309,7 +6318,7 @@
         <v>8.29989168013649</v>
       </c>
       <c r="D95" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E95">
         <v>5.631180854885052</v>
@@ -6345,7 +6354,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6359,7 +6368,7 @@
         <v>4.683694888843547</v>
       </c>
       <c r="D96" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E96">
         <v>7.023429444093537</v>
@@ -6395,7 +6404,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6409,7 +6418,7 @@
         <v>4.722134226828356</v>
       </c>
       <c r="D97" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E97">
         <v>7.023429444093537</v>
@@ -6445,7 +6454,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6459,7 +6468,7 @@
         <v>9.579012902797984</v>
       </c>
       <c r="D98" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E98">
         <v>6.893347467132109</v>
@@ -6495,7 +6504,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6509,7 +6518,7 @@
         <v>3.961474621504259</v>
       </c>
       <c r="D99" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E99">
         <v>6.476706188649629</v>
@@ -6545,7 +6554,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6559,7 +6568,7 @@
         <v>8.320444610292363</v>
       </c>
       <c r="D100" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E100">
         <v>7.021567248362409</v>
@@ -6595,7 +6604,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6609,7 +6618,7 @@
         <v>8.530866989040167</v>
       </c>
       <c r="D101" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E101">
         <v>7.021567248362409</v>
@@ -6645,7 +6654,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6659,7 +6668,7 @@
         <v>3.2890165208482</v>
       </c>
       <c r="D102" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E102">
         <v>5.857937357507026</v>
@@ -6695,7 +6704,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6709,7 +6718,7 @@
         <v>7.698991315674085</v>
       </c>
       <c r="D103" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E103">
         <v>6.277165792762322</v>
@@ -6745,7 +6754,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6759,7 +6768,7 @@
         <v>7.862435583597616</v>
       </c>
       <c r="D104" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E104">
         <v>6.277165792762322</v>
@@ -6795,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6809,7 +6818,7 @@
         <v>2.706415003086228</v>
       </c>
       <c r="D105" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E105">
         <v>5.321850930983533</v>
@@ -6845,7 +6854,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6859,7 +6868,7 @@
         <v>7.160579134588669</v>
       </c>
       <c r="D106" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E106">
         <v>5.783497068837448</v>
@@ -6895,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6909,7 +6918,7 @@
         <v>7.283322697678528</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E107">
         <v>5.783497068837448</v>
@@ -6945,7 +6954,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6959,7 +6968,7 @@
         <v>2.25250194719996</v>
       </c>
       <c r="D108" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E108">
         <v>4.90417843844148</v>
@@ -6995,7 +7004,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7009,7 +7018,7 @@
         <v>6.741094613879405</v>
       </c>
       <c r="D109" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E109">
         <v>5.766049754225914</v>
@@ -7045,7 +7054,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7059,7 +7068,7 @@
         <v>6.83212768404308</v>
       </c>
       <c r="D110" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E110">
         <v>5.766049754225914</v>
@@ -7095,7 +7104,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7109,7 +7118,7 @@
         <v>1.648635956687475</v>
       </c>
       <c r="D111" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E111">
         <v>4.348525301462924</v>
@@ -7145,7 +7154,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7159,7 +7168,7 @@
         <v>6.183030834224155</v>
       </c>
       <c r="D112" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E112">
         <v>5.350064030791522</v>
@@ -7195,7 +7204,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7209,7 +7218,7 @@
         <v>6.231877657545638</v>
       </c>
       <c r="D113" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E113">
         <v>5.350064030791522</v>
@@ -7245,7 +7254,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7259,7 +7268,7 @@
         <v>1.432518806234409</v>
       </c>
       <c r="D114" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E114">
         <v>4.149663013321483</v>
@@ -7295,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7309,7 +7318,7 @@
         <v>5.983305802967131</v>
       </c>
       <c r="D115" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E115">
         <v>4.577912304600769</v>
@@ -7345,7 +7354,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7359,7 +7368,7 @@
         <v>6.017054621765944</v>
       </c>
       <c r="D116" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E116">
         <v>4.577912304600769</v>
@@ -7395,7 +7404,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7409,7 +7418,7 @@
         <v>1.226728012835469</v>
       </c>
       <c r="D117" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E117">
         <v>3.960302622589126</v>
@@ -7445,7 +7454,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7459,7 +7468,7 @@
         <v>5.793123892101445</v>
       </c>
       <c r="D118" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E118">
         <v>4.612872778687663</v>
@@ -7495,7 +7504,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7509,7 +7518,7 @@
         <v>5.812496108566997</v>
       </c>
       <c r="D119" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E119">
         <v>4.612872778687663</v>
@@ -7545,7 +7554,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7559,7 +7568,7 @@
         <v>1.216947853386511</v>
       </c>
       <c r="D120" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E120">
         <v>3.951303314193975</v>
@@ -7595,7 +7604,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7609,7 +7618,7 @@
         <v>5.802774512947074</v>
       </c>
       <c r="D121" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E121">
         <v>4.403561129870987</v>
@@ -7645,7 +7654,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7659,7 +7668,7 @@
         <v>1.177523163430447</v>
       </c>
       <c r="D122" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E122">
         <v>3.915026304074722</v>
@@ -7695,7 +7704,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7709,7 +7718,7 @@
         <v>5.763585898978771</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E123">
         <v>4.466025047817013</v>
@@ -7745,7 +7754,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7759,7 +7768,7 @@
         <v>0.9680478903759173</v>
       </c>
       <c r="D124" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E124">
         <v>3.722275603719158</v>
@@ -7795,7 +7804,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7809,7 +7818,7 @@
         <v>0.8515262832029507</v>
       </c>
       <c r="D125" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E125">
         <v>3.61505711887537</v>
@@ -7845,7 +7854,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7859,7 +7868,7 @@
         <v>0.6675490824101864</v>
       </c>
       <c r="D126" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E126">
         <v>3.445768716549093</v>
@@ -7895,7 +7904,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7909,7 +7918,7 @@
         <v>0.2453647773980379</v>
       </c>
       <c r="D127" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E127">
         <v>3.057291741278434</v>
@@ -7945,7 +7954,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7959,7 +7968,7 @@
         <v>-0.1442597189068877</v>
       </c>
       <c r="D128" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E128">
         <v>2.69877498918947</v>
@@ -7995,7 +8004,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8009,7 +8018,7 @@
         <v>3.671796227407118</v>
       </c>
       <c r="D129" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E129">
         <v>1.089748757437874</v>
@@ -8045,7 +8054,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8059,7 +8068,7 @@
         <v>-1.239097601114093</v>
       </c>
       <c r="D130" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E130">
         <v>1.261882831716061</v>
@@ -8095,7 +8104,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8109,7 +8118,7 @@
         <v>3.066548753992304</v>
       </c>
       <c r="D131" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E131">
         <v>0.4140568037443764</v>
@@ -8145,7 +8154,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8159,7 +8168,7 @@
         <v>-1.959356470902271</v>
       </c>
       <c r="D132" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E132">
         <v>0.6034425874785647</v>
@@ -8195,7 +8204,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8209,7 +8218,7 @@
         <v>2.434653904799742</v>
       </c>
       <c r="D133" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E133">
         <v>-0.2913840017675113</v>
@@ -8245,7 +8254,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8259,7 +8268,7 @@
         <v>-2.711326350820261</v>
       </c>
       <c r="D134" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E134">
         <v>-0.08398696342450762</v>
@@ -8295,7 +8304,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8309,7 +8318,7 @@
         <v>2.046949385277987</v>
       </c>
       <c r="D135" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E135">
         <v>-0.7242132753428656</v>
@@ -8345,7 +8354,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8359,7 +8368,7 @@
         <v>-3.172703938184629</v>
       </c>
       <c r="D136" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E136">
         <v>-0.5057652768234711</v>
@@ -8395,7 +8404,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8409,7 +8418,7 @@
         <v>1.727381390460117</v>
       </c>
       <c r="D137" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E137">
         <v>0.5925973930511788</v>
@@ -8445,7 +8454,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8459,7 +8468,7 @@
         <v>1.685047495782005</v>
       </c>
       <c r="D138" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E138">
         <v>-1.128236762428639</v>
@@ -8495,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8509,7 +8518,7 @@
         <v>-3.603375782929252</v>
       </c>
       <c r="D139" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E139">
         <v>-0.8994732706219501</v>
@@ -8545,7 +8554,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8559,7 +8568,7 @@
         <v>1.329375274458599</v>
       </c>
       <c r="D140" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E140">
         <v>-0.02169112718700106</v>
@@ -8595,7 +8604,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8609,7 +8618,7 @@
         <v>1.370767088004978</v>
       </c>
       <c r="D141" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E141">
         <v>-1.479096125030072</v>
@@ -8645,7 +8654,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8659,7 +8668,7 @@
         <v>-3.977376933276734</v>
       </c>
       <c r="D142" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E142">
         <v>-1.241374521837809</v>
@@ -8695,7 +8704,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8709,7 +8718,7 @@
         <v>0.9837414768320834</v>
       </c>
       <c r="D143" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E143">
         <v>-0.5624929319466254</v>
@@ -8745,7 +8754,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8759,7 +8768,7 @@
         <v>-4.274892307557078</v>
       </c>
       <c r="D144" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E144">
         <v>-1.513354644433413</v>
@@ -8809,7 +8818,7 @@
         <v>0.7087921389242986</v>
       </c>
       <c r="D145" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E145">
         <v>-0.01219137097330147</v>
@@ -8859,7 +8868,7 @@
         <v>-6.600419867221269</v>
       </c>
       <c r="D146" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E146">
         <v>-3.935750603200287</v>
@@ -8895,7 +8904,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8909,7 +8918,7 @@
         <v>-1.740049190571469</v>
       </c>
       <c r="D147" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E147">
         <v>-3.803035064283293</v>
@@ -8945,7 +8954,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -8959,7 +8968,7 @@
         <v>-7.356943655480499</v>
       </c>
       <c r="D148" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E148">
         <v>-4.634314907681588</v>
@@ -8995,7 +9004,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9009,7 +9018,7 @@
         <v>-2.446239742918287</v>
       </c>
       <c r="D149" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E149">
         <v>-3.284642996427294</v>
@@ -9045,7 +9054,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9059,7 +9068,7 @@
         <v>-2.764549545202325</v>
       </c>
       <c r="D150" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E150">
         <v>-3.284642996427294</v>
@@ -9095,7 +9104,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9109,7 +9118,7 @@
         <v>-8.273062059554213</v>
       </c>
       <c r="D151" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E151">
         <v>-5.480246821120623</v>
@@ -9145,7 +9154,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9159,7 +9168,7 @@
         <v>-3.301406720914517</v>
       </c>
       <c r="D152" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E152">
         <v>-3.80770165872979</v>
@@ -9195,7 +9204,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9209,7 +9218,7 @@
         <v>-3.640798600667189</v>
       </c>
       <c r="D153" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E153">
         <v>-3.80770165872979</v>
@@ -9245,7 +9254,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9259,7 +9268,7 @@
         <v>-9.028638086965721</v>
       </c>
       <c r="D154" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E154">
         <v>-6.177935975464312</v>
@@ -9295,7 +9304,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9309,7 +9318,7 @@
         <v>-4.006712569082914</v>
       </c>
       <c r="D155" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E155">
         <v>-5.764446572941544</v>
@@ -9345,7 +9354,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9359,7 +9368,7 @@
         <v>-4.355244481425245</v>
       </c>
       <c r="D156" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E156">
         <v>-5.764446572941544</v>
@@ -9395,7 +9404,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9409,7 +9418,7 @@
         <v>-9.288472736223071</v>
       </c>
       <c r="D157" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E157">
         <v>-6.4178639378834</v>
@@ -9445,7 +9454,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9459,7 +9468,7 @@
         <v>-4.249259832401776</v>
       </c>
       <c r="D158" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E158">
         <v>-5.572990039214197</v>
@@ -9495,7 +9504,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9509,7 +9518,7 @@
         <v>-4.600934905823827</v>
       </c>
       <c r="D159" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E159">
         <v>-5.572990039214197</v>
@@ -9545,7 +9554,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9559,7 +9568,7 @@
         <v>-8.391360480599353</v>
       </c>
       <c r="D160" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E160">
         <v>-5.589482056682467</v>
@@ -9595,7 +9604,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9609,7 +9618,7 @@
         <v>-3.41183448088206</v>
       </c>
       <c r="D161" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E161">
         <v>-4.236414237755341</v>
@@ -9645,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9659,7 +9668,7 @@
         <v>-3.752657389921566</v>
       </c>
       <c r="D162" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E162">
         <v>-4.236414237755341</v>
@@ -9695,7 +9704,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9709,7 +9718,7 @@
         <v>-7.284701623181299</v>
       </c>
       <c r="D163" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E163">
         <v>-4.567607547211761</v>
@@ -9745,7 +9754,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9759,7 +9768,7 @@
         <v>-2.378804136155122</v>
       </c>
       <c r="D164" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E164">
         <v>-3.182992288094191</v>
@@ -9795,7 +9804,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9845,7 +9854,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9895,7 +9904,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9909,7 +9918,7 @@
         <v>15.30025538505301</v>
       </c>
       <c r="D167" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E167">
         <v>12.2194473505381</v>
@@ -9945,7 +9954,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9959,7 +9968,7 @@
         <v>16.08154605938966</v>
       </c>
       <c r="D168" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E168">
         <v>12.2194473505381</v>
@@ -9995,7 +10004,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10045,7 +10054,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10095,7 +10104,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10145,7 +10154,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10195,7 +10204,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10245,7 +10254,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10295,7 +10304,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10345,7 +10354,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10395,7 +10404,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10445,7 +10454,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10495,7 +10504,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10509,7 +10518,7 @@
         <v>-2.965774048910724</v>
       </c>
       <c r="D179" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E179">
         <v>-6.323583762599906</v>
@@ -10545,7 +10554,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10559,7 +10568,7 @@
         <v>-3.841273412039687</v>
       </c>
       <c r="D180" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E180">
         <v>-6.323583762599906</v>
@@ -10595,7 +10604,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10645,7 +10654,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10659,7 +10668,7 @@
         <v>-4.596644143057084</v>
       </c>
       <c r="D182" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E182">
         <v>-7.87451662725034</v>
@@ -10695,7 +10704,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10709,7 +10718,7 @@
         <v>-5.499155847289916</v>
       </c>
       <c r="D183" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E183">
         <v>-7.87451662725034</v>
@@ -10745,7 +10754,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10795,7 +10804,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10809,7 +10818,7 @@
         <v>-6.176260919928573</v>
       </c>
       <c r="D185" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E185">
         <v>-9.588220956609884</v>
@@ -10845,7 +10854,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10859,7 +10868,7 @@
         <v>-7.104936049037125</v>
       </c>
       <c r="D186" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E186">
         <v>-9.588220956609884</v>
@@ -10895,7 +10904,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10945,7 +10954,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10995,7 +11004,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11009,7 +11018,7 @@
         <v>-5.957065888688689</v>
       </c>
       <c r="D189" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E189">
         <v>-9.35041930781134</v>
@@ -11045,7 +11054,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11059,7 +11068,7 @@
         <v>-6.882110458273605</v>
       </c>
       <c r="D190" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E190">
         <v>-9.35041930781134</v>
@@ -11095,7 +11104,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11109,7 +11118,7 @@
         <v>-5.75373473480284</v>
       </c>
       <c r="D191" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E191">
         <v>-9.129828159496252</v>
@@ -11159,7 +11168,7 @@
         <v>-6.675411500596677</v>
       </c>
       <c r="D192" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E192">
         <v>-9.129828159496252</v>
@@ -11209,7 +11218,7 @@
         <v>4.036863233290944</v>
       </c>
       <c r="D193" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E193">
         <v>1.091137151603181</v>
@@ -11259,7 +11268,7 @@
         <v>4.353212181898559</v>
       </c>
       <c r="D194" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E194">
         <v>1.091137151603181</v>
@@ -11309,7 +11318,7 @@
         <v>4.092859462531468</v>
       </c>
       <c r="D195" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E195">
         <v>1.091137151603181</v>
@@ -11395,7 +11404,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11445,7 +11454,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11595,7 +11604,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11645,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11695,7 +11704,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11745,7 +11754,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11795,7 +11804,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11845,7 +11854,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11895,7 +11904,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11945,7 +11954,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -11995,7 +12004,7 @@
         <v>1</v>
       </c>
       <c r="P208" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -12045,7 +12054,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12095,7 +12104,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12145,7 +12154,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12195,7 +12204,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12245,7 +12254,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12295,7 +12304,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12309,7 +12318,7 @@
         <v>2.797016608461103</v>
       </c>
       <c r="D215" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E215">
         <v>-0.1302387600075896</v>
@@ -12345,7 +12354,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12359,7 +12368,7 @@
         <v>3.23804287129742</v>
       </c>
       <c r="D216" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E216">
         <v>-0.1302387600075896</v>
@@ -12395,7 +12404,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12409,7 +12418,7 @@
         <v>2.97076363447318</v>
       </c>
       <c r="D217" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E217">
         <v>-0.1302387600075896</v>
@@ -12445,7 +12454,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12459,7 +12468,7 @@
         <v>-2.735537076225839</v>
       </c>
       <c r="D218" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E218">
         <v>-0.06446785034954416</v>
@@ -12495,7 +12504,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12509,7 +12518,7 @@
         <v>2.142297248198716</v>
       </c>
       <c r="D219" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E219">
         <v>-0.7752043867837592</v>
@@ -12545,7 +12554,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12559,7 +12568,7 @@
         <v>2.649161212067007</v>
       </c>
       <c r="D220" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E220">
         <v>-0.7752043867837592</v>
@@ -12595,7 +12604,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12609,7 +12618,7 @@
         <v>1.866662847049479</v>
       </c>
       <c r="D221" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E221">
         <v>-0.7752043867837592</v>
@@ -12645,7 +12654,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12659,7 +12668,7 @@
         <v>-3.292719101626048</v>
       </c>
       <c r="D222" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E222">
         <v>-0.5316716843393898</v>
@@ -12695,7 +12704,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12709,7 +12718,7 @@
         <v>0.7343076746441</v>
       </c>
       <c r="D223" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E223">
         <v>-2.162218324233283</v>
@@ -12759,7 +12768,7 @@
         <v>1.382757182221791</v>
       </c>
       <c r="D224" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E224">
         <v>-2.162218324233283</v>
@@ -12809,7 +12818,7 @@
         <v>0.5792831810991643</v>
       </c>
       <c r="D225" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E225">
         <v>-2.162218324233283</v>
@@ -12859,7 +12868,7 @@
         <v>-4.4909523141297</v>
       </c>
       <c r="D226" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E226">
         <v>-1.797099453998044</v>
@@ -12909,7 +12918,7 @@
         <v>-0.5271433345479153</v>
       </c>
       <c r="D227" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E227">
         <v>-3.404876767180344</v>
@@ -12959,7 +12968,7 @@
         <v>0.2481559951831649</v>
       </c>
       <c r="D228" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E228">
         <v>-3.404876767180344</v>
@@ -13009,7 +13018,7 @@
         <v>-0.5741105721844058</v>
       </c>
       <c r="D229" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E229">
         <v>-3.404876767180344</v>
@@ -13059,7 +13068,7 @@
         <v>-5.289194339951301</v>
       </c>
       <c r="D230" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E230">
         <v>-2.93597803324387</v>
@@ -13109,7 +13118,7 @@
         <v>-1.521590007004434</v>
       </c>
       <c r="D231" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E231">
         <v>-4.774748703164175</v>
@@ -13145,7 +13154,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13159,7 +13168,7 @@
         <v>-2.373169137555241</v>
       </c>
       <c r="D232" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E232">
         <v>-4.774748703164175</v>
@@ -13195,7 +13204,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13209,7 +13218,7 @@
         <v>-6.960010441395497</v>
       </c>
       <c r="D233" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E233">
         <v>-4.500536093148853</v>
@@ -13245,7 +13254,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13259,7 +13268,7 @@
         <v>-2.452340392521911</v>
       </c>
       <c r="D234" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E234">
         <v>-5.548191233294997</v>
@@ -13309,7 +13318,7 @@
         <v>-2.754963624773605</v>
       </c>
       <c r="D235" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E235">
         <v>-5.548191233294997</v>
@@ -13359,7 +13368,7 @@
         <v>-7.838731302256715</v>
       </c>
       <c r="D236" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E236">
         <v>-5.323373390490392</v>
@@ -13409,7 +13418,7 @@
         <v>-4.58678078170076</v>
       </c>
       <c r="D237" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E237">
         <v>-7.667945163513835</v>
@@ -13445,7 +13454,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13459,7 +13468,7 @@
         <v>-5.270890369576151</v>
       </c>
       <c r="D238" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E238">
         <v>-7.667945163513835</v>
@@ -13495,7 +13504,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13509,7 +13518,7 @@
         <v>-4.902661407674056</v>
       </c>
       <c r="D239" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E239">
         <v>-7.667945163513835</v>
@@ -13545,7 +13554,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13559,7 +13568,7 @@
         <v>-9.853855147941093</v>
       </c>
       <c r="D240" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E240">
         <v>-7.21034243019923</v>
@@ -13595,7 +13604,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13609,7 +13618,7 @@
         <v>-5.59817458645032</v>
       </c>
       <c r="D241" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E241">
         <v>-8.513312611948162</v>
@@ -13645,7 +13654,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13659,7 +13668,7 @@
         <v>-5.920337161521442</v>
       </c>
       <c r="D242" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E242">
         <v>-8.513312611948162</v>
@@ -13695,7 +13704,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13709,7 +13718,7 @@
         <v>-10.78187598777789</v>
       </c>
       <c r="D243" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E243">
         <v>-7.189437361711093</v>
@@ -13745,7 +13754,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13759,7 +13768,7 @@
         <v>-10.80871141081024</v>
       </c>
       <c r="D244" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E244">
         <v>-8.104473185122753</v>
@@ -13795,7 +13804,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13809,7 +13818,7 @@
         <v>-5.98278744209609</v>
       </c>
       <c r="D245" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E245">
         <v>-8.914647765665489</v>
@@ -13845,7 +13854,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13859,7 +13868,7 @@
         <v>-6.30733891689172</v>
       </c>
       <c r="D246" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E246">
         <v>-8.914647765665489</v>
@@ -13895,7 +13904,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13909,7 +13918,7 @@
         <v>-11.21108163828114</v>
       </c>
       <c r="D247" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E247">
         <v>-7.582809516346728</v>
@@ -13945,7 +13954,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13959,7 +13968,7 @@
         <v>-11.09924338896238</v>
       </c>
       <c r="D248" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E248">
         <v>-7.582809516346728</v>
@@ -13995,7 +14004,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14009,7 +14018,7 @@
         <v>-11.17182416893544</v>
       </c>
       <c r="D249" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E249">
         <v>-8.444493245911037</v>
@@ -14045,7 +14054,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14059,7 +14068,7 @@
         <v>-6.197743032286496</v>
       </c>
       <c r="D250" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E250">
         <v>-9.138949251081566</v>
@@ -14095,7 +14104,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14109,7 +14118,7 @@
         <v>-6.52362963497151</v>
       </c>
       <c r="D251" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E251">
         <v>-9.138949251081566</v>
@@ -14145,7 +14154,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14159,7 +14168,7 @@
         <v>-11.45095961574</v>
       </c>
       <c r="D252" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E252">
         <v>-7.802660575464863</v>
@@ -14195,7 +14204,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14209,7 +14218,7 @@
         <v>-11.33467094012331</v>
       </c>
       <c r="D253" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E253">
         <v>-7.802660575464863</v>
@@ -14245,7 +14254,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14259,7 +14268,7 @@
         <v>-11.37476360812142</v>
       </c>
       <c r="D254" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E254">
         <v>-8.63452644883299</v>
@@ -14295,7 +14304,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14309,7 +14318,7 @@
         <v>-6.365423262694474</v>
       </c>
       <c r="D255" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E255">
         <v>-6.712841826990488</v>
@@ -14345,7 +14354,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14359,7 +14368,7 @@
         <v>-6.180679040630039</v>
       </c>
       <c r="D256" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E256">
         <v>-9.121143346744393</v>
@@ -14395,7 +14404,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14409,7 +14418,7 @@
         <v>-6.506459655789232</v>
       </c>
       <c r="D257" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E257">
         <v>-9.121143346744393</v>
@@ -14445,7 +14454,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14459,7 +14468,7 @@
         <v>-11.43191719026831</v>
       </c>
       <c r="D258" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E258">
         <v>-7.785207962880413</v>
@@ -14495,7 +14504,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14509,7 +14518,7 @@
         <v>-11.31598180640433</v>
       </c>
       <c r="D259" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E259">
         <v>-7.785207962880413</v>
@@ -14545,7 +14554,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14559,7 +14568,7 @@
         <v>-11.3586535041973</v>
       </c>
       <c r="D260" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E260">
         <v>-8.619440890991779</v>
@@ -14595,7 +14604,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14609,7 +14618,7 @@
         <v>-6.352422126194313</v>
       </c>
       <c r="D261" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E261">
         <v>-7.002545941158143</v>
@@ -14645,7 +14654,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14659,7 +14668,7 @@
         <v>-6.259072586714403</v>
       </c>
       <c r="D262" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E262">
         <v>-9.202945307875904</v>
@@ -14695,7 +14704,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14709,7 +14718,7 @@
         <v>-6.58534011830891</v>
       </c>
       <c r="D263" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E263">
         <v>-9.202945307875904</v>
@@ -14745,7 +14754,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14759,7 +14768,7 @@
         <v>-11.51939984314506</v>
       </c>
       <c r="D264" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E264">
         <v>-7.865386869227571</v>
@@ -14795,7 +14804,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14809,7 +14818,7 @@
         <v>-11.40184140449673</v>
       </c>
       <c r="D265" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E265">
         <v>-7.865386869227571</v>
@@ -14845,7 +14854,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14859,7 +14868,7 @@
         <v>-11.43266480236391</v>
       </c>
       <c r="D266" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E266">
         <v>-8.688745330283755</v>
@@ -14895,7 +14904,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14909,7 +14918,7 @@
         <v>-6.412150542258594</v>
       </c>
       <c r="D267" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E267">
         <v>-6.792666905080129</v>
@@ -14945,7 +14954,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14959,7 +14968,7 @@
         <v>-6.321920167701883</v>
       </c>
       <c r="D268" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E268">
         <v>-9.268525392384579</v>
@@ -14995,7 +15004,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15009,7 +15018,7 @@
         <v>-11.58953410018906</v>
       </c>
       <c r="D269" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E269">
         <v>-7.929665761583294</v>
@@ -15045,7 +15054,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15059,7 +15068,7 @@
         <v>-11.47067446938778</v>
       </c>
       <c r="D270" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E270">
         <v>-7.929665761583294</v>
@@ -15095,7 +15104,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15109,7 +15118,7 @@
         <v>-11.49199916453843</v>
       </c>
       <c r="D271" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E271">
         <v>-8.744306235214712</v>
@@ -15145,7 +15154,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15159,7 +15168,7 @@
         <v>-6.460034413487151</v>
       </c>
       <c r="D272" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E272">
         <v>-6.681381790702538</v>
@@ -15195,7 +15204,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15209,7 +15218,7 @@
         <v>-6.550476318984671</v>
       </c>
       <c r="D273" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E273">
         <v>-9.507018767636186</v>
@@ -15245,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15259,7 +15268,7 @@
         <v>-11.8445895153887</v>
       </c>
       <c r="D274" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E274">
         <v>-8.16342712542118</v>
@@ -15295,7 +15304,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15309,7 +15318,7 @@
         <v>-11.72099787317369</v>
       </c>
       <c r="D275" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E275">
         <v>-8.16342712542118</v>
@@ -15345,7 +15354,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15359,7 +15368,7 @@
         <v>-11.70777888500417</v>
       </c>
       <c r="D276" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E276">
         <v>-8.94636312258066</v>
@@ -15395,7 +15404,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15445,7 +15454,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15459,7 +15468,7 @@
         <v>-6.704638136207883</v>
       </c>
       <c r="D278" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E278">
         <v>-9.667883272564755</v>
@@ -15495,7 +15504,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15509,7 +15518,7 @@
         <v>-12.01662516649286</v>
       </c>
       <c r="D279" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E279">
         <v>-8.321099874299577</v>
@@ -15545,7 +15554,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15559,7 +15568,7 @@
         <v>-11.88984176822768</v>
       </c>
       <c r="D280" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E280">
         <v>-8.321099874299577</v>
@@ -15595,7 +15604,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15609,7 +15618,7 @@
         <v>-12.14300130071843</v>
       </c>
       <c r="D281" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E281">
         <v>-9.082651105922917</v>
@@ -15645,7 +15654,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15659,7 +15668,7 @@
         <v>-6.751629056158386</v>
       </c>
       <c r="D282" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E282">
         <v>-6.181746306378969</v>
@@ -15695,7 +15704,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15709,7 +15718,7 @@
         <v>-6.169874970448358</v>
       </c>
       <c r="D283" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E283">
         <v>-6.181746306378969</v>
@@ -15745,7 +15754,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15759,7 +15768,7 @@
         <v>-6.791555990766213</v>
       </c>
       <c r="D284" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E284">
         <v>-9.758580164277792</v>
@@ -15795,7 +15804,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15809,7 +15818,7 @@
         <v>-12.11362045346375</v>
       </c>
       <c r="D285" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E285">
         <v>-8.40999722451037</v>
@@ -15845,7 +15854,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15859,7 +15868,7 @@
         <v>-12.22524034737093</v>
       </c>
       <c r="D286" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E286">
         <v>-9.159491528068681</v>
@@ -15895,7 +15904,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15909,7 +15918,7 @@
         <v>-6.817852183440923</v>
       </c>
       <c r="D287" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E287">
         <v>-6.265382608492114</v>
@@ -15945,7 +15954,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -15959,7 +15968,7 @@
         <v>-6.233722702947933</v>
       </c>
       <c r="D288" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E288">
         <v>-6.265382608492114</v>
@@ -15995,7 +16004,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16009,7 +16018,7 @@
         <v>-12.15514825489226</v>
       </c>
       <c r="D289" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E289">
         <v>-8.448057955318696</v>
@@ -16045,7 +16054,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16059,7 +16068,7 @@
         <v>-12.26045037566933</v>
       </c>
       <c r="D290" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E290">
         <v>-9.192390175953609</v>
@@ -16095,7 +16104,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16109,7 +16118,7 @@
         <v>-6.261058628637798</v>
       </c>
       <c r="D291" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E291">
         <v>-6.075524180706029</v>
@@ -16145,7 +16154,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16159,7 +16168,7 @@
         <v>-12.2145658985059</v>
       </c>
       <c r="D292" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E292">
         <v>-8.502514942229901</v>
@@ -16209,7 +16218,7 @@
         <v>-12.31082860040297</v>
       </c>
       <c r="D293" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E293">
         <v>-9.239461296218966</v>
@@ -16259,7 +16268,7 @@
         <v>-6.300170650816128</v>
       </c>
       <c r="D294" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E294">
         <v>-5.649532575530262</v>
@@ -16309,7 +16318,7 @@
         <v>-11.84108439837907</v>
       </c>
       <c r="D295" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E295">
         <v>-8.80055369389029</v>
@@ -16345,7 +16354,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16359,7 +16368,7 @@
         <v>-5.935476465087291</v>
       </c>
       <c r="D296" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E296">
         <v>-5.137979270573577</v>
@@ -16395,7 +16404,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16445,7 +16454,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16495,7 +16504,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16545,7 +16554,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16595,7 +16604,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16645,7 +16654,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16695,7 +16704,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16745,7 +16754,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16759,7 +16768,7 @@
         <v>-0.3501812538917548</v>
       </c>
       <c r="D304" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E304">
         <v>-4.299167540216818</v>
@@ -16795,7 +16804,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16845,7 +16854,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16859,7 +16868,7 @@
         <v>-0.2510998261771533</v>
       </c>
       <c r="D306" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E306">
         <v>-4.192512218904984</v>
@@ -16895,7 +16904,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16945,7 +16954,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16959,7 +16968,7 @@
         <v>-0.1528009024453745</v>
       </c>
       <c r="D308" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E308">
         <v>-4.086699217043329</v>
@@ -16995,7 +17004,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17045,7 +17054,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17059,7 +17068,7 @@
         <v>0.06625268284449959</v>
       </c>
       <c r="D310" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E310">
         <v>-3.850900934131047</v>
@@ -17095,7 +17104,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17145,7 +17154,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17195,7 +17204,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17245,7 +17254,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17295,7 +17304,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17345,7 +17354,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17359,7 +17368,7 @@
         <v>1.82693717047681</v>
       </c>
       <c r="D316" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E316">
         <v>0.6963720300954037</v>
@@ -17395,7 +17404,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17445,7 +17454,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17459,7 +17468,7 @@
         <v>2.198341117699623</v>
       </c>
       <c r="D318" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E318">
         <v>0.5276096580294123</v>
@@ -17495,7 +17504,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17509,7 +17518,7 @@
         <v>12.7271211800604</v>
       </c>
       <c r="D319" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E319">
         <v>10.466793520675</v>
@@ -17545,7 +17554,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17559,7 +17568,7 @@
         <v>13.26860393649666</v>
       </c>
       <c r="D320" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E320">
         <v>10.466793520675</v>
@@ -17595,7 +17604,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17609,7 +17618,7 @@
         <v>12.90082807115104</v>
       </c>
       <c r="D321" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E321">
         <v>10.466793520675</v>
@@ -17645,7 +17654,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17659,7 +17668,7 @@
         <v>12.60281108867061</v>
       </c>
       <c r="D322" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E322">
         <v>10.00917894691048</v>
@@ -17695,7 +17704,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17709,7 +17718,7 @@
         <v>13.14484756489033</v>
       </c>
       <c r="D323" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E323">
         <v>10.00917894691048</v>
@@ -17745,7 +17754,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17759,7 +17768,7 @@
         <v>12.77790227921993</v>
       </c>
       <c r="D324" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E324">
         <v>10.00917894691048</v>
@@ -17795,7 +17804,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17809,7 +17818,7 @@
         <v>12.94031582834918</v>
       </c>
       <c r="D325" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E325">
         <v>10.4990798111086</v>
@@ -17845,7 +17854,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17859,7 +17868,7 @@
         <v>13.48084894269951</v>
       </c>
       <c r="D326" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E326">
         <v>10.4990798111086</v>
@@ -17895,7 +17904,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17909,7 +17918,7 @@
         <v>13.11164861422502</v>
       </c>
       <c r="D327" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E327">
         <v>10.4990798111086</v>
@@ -17945,7 +17954,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17959,7 +17968,7 @@
         <v>12.89880385150152</v>
       </c>
       <c r="D328" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E328">
         <v>10.62546343074822</v>
@@ -17995,7 +18004,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18009,7 +18018,7 @@
         <v>13.4395218744347</v>
       </c>
       <c r="D329" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E329">
         <v>10.62546343074822</v>
@@ -18045,7 +18054,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18059,7 +18068,7 @@
         <v>13.07059890883446</v>
       </c>
       <c r="D330" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E330">
         <v>10.62546343074822</v>
@@ -18095,7 +18104,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18109,7 +18118,7 @@
         <v>12.9234363080082</v>
       </c>
       <c r="D331" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E331">
         <v>11.0537757639692</v>
@@ -18145,7 +18154,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18159,7 +18168,7 @@
         <v>13.46404460953155</v>
       </c>
       <c r="D332" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E332">
         <v>11.0537757639692</v>
@@ -18195,7 +18204,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18209,7 +18218,7 @@
         <v>13.09495706181657</v>
       </c>
       <c r="D333" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E333">
         <v>11.0537757639692</v>
@@ -18245,7 +18254,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18259,7 +18268,7 @@
         <v>13.44227382778946</v>
       </c>
       <c r="D334" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E334">
         <v>11.03770193240324</v>
@@ -18295,7 +18304,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18309,7 +18318,7 @@
         <v>13.07333239270363</v>
       </c>
       <c r="D335" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E335">
         <v>11.03770193240324</v>
@@ -18345,7 +18354,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18359,7 +18368,7 @@
         <v>13.47049330154028</v>
       </c>
       <c r="D336" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E336">
         <v>12.2200768479712</v>
@@ -18395,7 +18404,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18409,7 +18418,7 @@
         <v>13.10136247401317</v>
       </c>
       <c r="D337" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E337">
         <v>12.2200768479712</v>
@@ -18445,7 +18454,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18459,7 +18468,7 @@
         <v>13.41024108188445</v>
       </c>
       <c r="D338" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E338">
         <v>11.606966539383</v>
@@ -18495,7 +18504,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18509,7 +18518,7 @@
         <v>13.04151463167046</v>
       </c>
       <c r="D339" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E339">
         <v>11.606966539383</v>
@@ -18545,7 +18554,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18559,7 +18568,7 @@
         <v>15.99098556432473</v>
       </c>
       <c r="D340" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E340">
         <v>12.49688805745362</v>
@@ -18595,7 +18604,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18609,7 +18618,7 @@
         <v>15.82125527263218</v>
       </c>
       <c r="D341" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E341">
         <v>12.49688805745362</v>
@@ -18645,7 +18654,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18659,7 +18668,7 @@
         <v>16.12796689068343</v>
       </c>
       <c r="D342" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E342">
         <v>12.49688805745362</v>
@@ -18695,7 +18704,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18709,7 +18718,7 @@
         <v>16.05759498721028</v>
       </c>
       <c r="D343" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E343">
         <v>12.56617445478137</v>
@@ -18745,7 +18754,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18759,7 +18768,7 @@
         <v>15.8869198810087</v>
       </c>
       <c r="D344" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E344">
         <v>12.56617445478137</v>
@@ -18795,7 +18804,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18809,7 +18818,7 @@
         <v>16.19347402997512</v>
       </c>
       <c r="D345" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E345">
         <v>12.56617445478137</v>
@@ -18845,7 +18854,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18859,7 +18868,7 @@
         <v>16.08852224791477</v>
       </c>
       <c r="D346" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E346">
         <v>12.59834465504137</v>
@@ -18895,7 +18904,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18909,7 +18918,7 @@
         <v>15.9174084571642</v>
       </c>
       <c r="D347" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E347">
         <v>12.59834465504137</v>
@@ -18945,7 +18954,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18959,7 +18968,7 @@
         <v>16.22388949203912</v>
       </c>
       <c r="D348" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E348">
         <v>12.59834465504137</v>
@@ -18995,7 +19004,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19009,7 +19018,7 @@
         <v>15.99827269225045</v>
       </c>
       <c r="D349" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E349">
         <v>12.50446804867659</v>
@@ -19045,7 +19054,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19059,7 +19068,7 @@
         <v>15.82843903704122</v>
       </c>
       <c r="D350" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E350">
         <v>12.50446804867659</v>
@@ -19095,7 +19104,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19109,7 +19118,7 @@
         <v>16.13513342783969</v>
       </c>
       <c r="D351" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E351">
         <v>12.50446804867659</v>
@@ -19145,7 +19154,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19159,7 +19168,7 @@
         <v>10.5571576031199</v>
       </c>
       <c r="D352" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E352">
         <v>11.2357781978979</v>
@@ -19209,7 +19218,7 @@
         <v>10.4146275818384</v>
       </c>
       <c r="D353" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E353">
         <v>11.2357781978979</v>
@@ -19259,7 +19268,7 @@
         <v>11.02395259544049</v>
       </c>
       <c r="D354" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E354">
         <v>11.2357781978979</v>
@@ -19345,7 +19354,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19395,7 +19404,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19445,7 +19454,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19495,7 +19504,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19545,7 +19554,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19595,7 +19604,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19645,7 +19654,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19695,7 +19704,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19709,7 +19718,7 @@
         <v>7.109582508392513</v>
       </c>
       <c r="D363" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E363">
         <v>10.1191386498793</v>
@@ -19759,7 +19768,7 @@
         <v>8.320739177217412</v>
       </c>
       <c r="D364" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E364">
         <v>10.1191386498793</v>
@@ -19845,7 +19854,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19895,7 +19904,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19909,7 +19918,7 @@
         <v>5.429328338517664</v>
       </c>
       <c r="D367" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E367">
         <v>6.453570540990412</v>
@@ -19945,7 +19954,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19959,7 +19968,7 @@
         <v>4.28114123100805</v>
       </c>
       <c r="D368" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E368">
         <v>5.201857907737669</v>
@@ -19995,7 +20004,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20009,7 +20018,7 @@
         <v>3.478556159579213</v>
       </c>
       <c r="D369" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E369">
         <v>4.355782779043444</v>
@@ -20045,7 +20054,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20059,7 +20068,7 @@
         <v>2.542133382528917</v>
       </c>
       <c r="D370" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E370">
         <v>3.611162052395251</v>
@@ -20095,7 +20104,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20145,7 +20154,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20159,7 +20168,7 @@
         <v>3.166397470697689</v>
       </c>
       <c r="D372" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E372">
         <v>2.50604388321451</v>
@@ -20195,7 +20204,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20245,7 +20254,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20295,7 +20304,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20345,7 +20354,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20359,7 +20368,7 @@
         <v>0.5258114362592394</v>
       </c>
       <c r="D376" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E376">
         <v>0.9640594525915418</v>
@@ -20395,7 +20404,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20409,7 +20418,7 @@
         <v>1.029412028487577</v>
       </c>
       <c r="D377" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E377">
         <v>0.9640594525915418</v>
@@ -20445,7 +20454,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20459,7 +20468,7 @@
         <v>0.5230738845135647</v>
       </c>
       <c r="D378" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E378">
         <v>0.9640594525915418</v>
@@ -20495,7 +20504,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20509,7 +20518,7 @@
         <v>0.2932995584235911</v>
       </c>
       <c r="D379" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E379">
         <v>-0.2507339019854058</v>
@@ -20545,7 +20554,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20559,7 +20568,7 @@
         <v>0.8110931833932682</v>
       </c>
       <c r="D380" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E380">
         <v>-0.2507339019854058</v>
@@ -20595,7 +20604,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20609,7 +20618,7 @@
         <v>0.3063705065605404</v>
       </c>
       <c r="D381" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E381">
         <v>-0.2507339019854058</v>
@@ -20645,7 +20654,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20659,7 +20668,7 @@
         <v>0.25081902425989</v>
       </c>
       <c r="D382" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E382">
         <v>-1.810462939778127</v>
@@ -20695,7 +20704,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20709,7 +20718,7 @@
         <v>0.7712057537963801</v>
       </c>
       <c r="D383" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E383">
         <v>-1.810462939778127</v>
@@ -20745,7 +20754,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20759,7 +20768,7 @@
         <v>0.266778227076955</v>
       </c>
       <c r="D384" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E384">
         <v>-1.810462939778127</v>
@@ -20795,7 +20804,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20809,7 +20818,7 @@
         <v>0.2555858995649842</v>
       </c>
       <c r="D385" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E385">
         <v>-0.5322733758888774</v>
@@ -20845,7 +20854,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20859,7 +20868,7 @@
         <v>0.7756816486237952</v>
       </c>
       <c r="D386" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E386">
         <v>-0.5322733758888774</v>
@@ -20895,7 +20904,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20909,7 +20918,7 @@
         <v>0.2712210021752028</v>
       </c>
       <c r="D387" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E387">
         <v>-0.5322733758888774</v>
@@ -20945,7 +20954,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20995,7 +21004,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21045,7 +21054,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21095,7 +21104,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21145,7 +21154,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21159,7 +21168,7 @@
         <v>2.068109497945251</v>
       </c>
       <c r="D392" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E392">
         <v>1.103589803610085</v>
@@ -21195,7 +21204,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21209,7 +21218,7 @@
         <v>1.130775764308638</v>
       </c>
       <c r="D393" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E393">
         <v>1.103589803610085</v>
@@ -21245,7 +21254,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21259,7 +21268,7 @@
         <v>1.848060841515313</v>
       </c>
       <c r="D394" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E394">
         <v>0.99412281255767</v>
@@ -21295,7 +21304,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21309,7 +21318,7 @@
         <v>0.9315277271432265</v>
       </c>
       <c r="D395" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E395">
         <v>0.99412281255767</v>
@@ -21345,7 +21354,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21359,7 +21368,7 @@
         <v>1.694201531226533</v>
       </c>
       <c r="D396" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E396">
         <v>0.6700023738905614</v>
@@ -21395,7 +21404,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21409,7 +21418,7 @@
         <v>0.7922123317573622</v>
       </c>
       <c r="D397" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E397">
         <v>0.6700023738905614</v>
@@ -21445,7 +21454,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21459,7 +21468,7 @@
         <v>1.513646695334067</v>
       </c>
       <c r="D398" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E398">
         <v>0.5589534979668187</v>
@@ -21495,7 +21504,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21509,7 +21518,7 @@
         <v>0.6287248684119433</v>
       </c>
       <c r="D399" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E399">
         <v>0.5589534979668187</v>
@@ -21545,7 +21554,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21595,7 +21604,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21645,7 +21654,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21659,7 +21668,7 @@
         <v>1.430312383569088</v>
       </c>
       <c r="D402" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E402">
         <v>2.785832606944602</v>
@@ -21695,7 +21704,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21709,7 +21718,7 @@
         <v>1.015447344707901</v>
       </c>
       <c r="D403" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E403">
         <v>2.785832606944602</v>
@@ -21745,7 +21754,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21759,7 +21768,7 @@
         <v>2.872497404927479</v>
       </c>
       <c r="D404" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E404">
         <v>2.785832606944602</v>
@@ -21795,7 +21804,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21809,7 +21818,7 @@
         <v>1.657667083906176</v>
       </c>
       <c r="D405" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E405">
         <v>3.010263722734074</v>
@@ -21845,7 +21854,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21859,7 +21868,7 @@
         <v>3.082432889417845</v>
       </c>
       <c r="D406" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E406">
         <v>3.010263722734074</v>
@@ -21895,7 +21904,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21909,7 +21918,7 @@
         <v>1.760495757853356</v>
       </c>
       <c r="D407" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E407">
         <v>2.967064908431617</v>
@@ -21945,7 +21954,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21959,7 +21968,7 @@
         <v>3.177383147550167</v>
       </c>
       <c r="D408" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E408">
         <v>2.967064908431617</v>
@@ -21995,7 +22004,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22009,7 +22018,7 @@
         <v>3.419213206004784</v>
       </c>
       <c r="D409" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E409">
         <v>4.96095189349581</v>
@@ -22045,7 +22054,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22059,7 +22068,7 @@
         <v>30.71910142906406</v>
       </c>
       <c r="D410" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E410">
         <v>17.77124839717711</v>
@@ -22095,7 +22104,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22109,7 +22118,7 @@
         <v>30.74457906406285</v>
       </c>
       <c r="D411" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E411">
         <v>18.07805575594424</v>
@@ -22145,7 +22154,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22159,7 +22168,7 @@
         <v>30.94531632533681</v>
       </c>
       <c r="D412" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E412">
         <v>18.41220109884297</v>
@@ -22195,7 +22204,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22209,7 +22218,7 @@
         <v>31.10162189647678</v>
       </c>
       <c r="D413" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E413">
         <v>18.55328210136541</v>
@@ -22245,7 +22254,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22259,7 +22268,7 @@
         <v>31.28406714947664</v>
       </c>
       <c r="D414" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E414">
         <v>18.71795671283931</v>
@@ -22295,7 +22304,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22309,7 +22318,7 @@
         <v>31.41016164358475</v>
       </c>
       <c r="D415" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E415">
         <v>18.83176927570312</v>
@@ -22345,7 +22354,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22359,7 +22368,7 @@
         <v>31.50687459786862</v>
       </c>
       <c r="D416" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E416">
         <v>18.91906213703726</v>
@@ -22395,7 +22404,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22409,7 +22418,7 @@
         <v>31.56465330836859</v>
       </c>
       <c r="D417" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E417">
         <v>18.97121305105996</v>
@@ -22445,7 +22454,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22459,7 +22468,7 @@
         <v>31.59842308925229</v>
       </c>
       <c r="D418" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E418">
         <v>19.00169356757187</v>
@@ -22495,7 +22504,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22509,7 +22518,7 @@
         <v>31.66012131009328</v>
       </c>
       <c r="D419" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E419">
         <v>19.05738222144783</v>
@@ -22545,7 +22554,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22559,7 +22568,7 @@
         <v>31.70713316886447</v>
       </c>
       <c r="D420" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E420">
         <v>19.09981500306598</v>
@@ -22595,7 +22604,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22609,7 +22618,7 @@
         <v>31.87762108191551</v>
       </c>
       <c r="D421" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E421">
         <v>19.25369695056011</v>
@@ -22645,7 +22654,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22659,7 +22668,7 @@
         <v>32.04993923346682</v>
       </c>
       <c r="D422" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E422">
         <v>19.4092308665707</v>
@@ -22695,7 +22704,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22709,7 +22718,7 @@
         <v>32.21080893028861</v>
       </c>
       <c r="D423" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E423">
         <v>19.55443143707868</v>
@@ -22745,7 +22754,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22759,7 +22768,7 @@
         <v>32.44198272920474</v>
       </c>
       <c r="D424" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E424">
         <v>19.76308830752896</v>
@@ -22795,7 +22804,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22809,7 +22818,7 @@
         <v>32.60849165225912</v>
       </c>
       <c r="D425" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E425">
         <v>19.91337882898712</v>
@@ -22845,7 +22854,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22859,7 +22868,7 @@
         <v>32.78872551361854</v>
       </c>
       <c r="D426" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E426">
         <v>20.07605744411025</v>
@@ -22895,7 +22904,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22909,7 +22918,7 @@
         <v>32.88633633076009</v>
       </c>
       <c r="D427" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E427">
         <v>20.16416071412761</v>
@@ -22945,7 +22954,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22959,7 +22968,7 @@
         <v>32.92087256937922</v>
       </c>
       <c r="D428" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E428">
         <v>20.19533303340073</v>
@@ -22995,7 +23004,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23009,7 +23018,7 @@
         <v>33.06269553801688</v>
       </c>
       <c r="D429" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E429">
         <v>20.32334207652173</v>
@@ -23045,7 +23054,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23059,7 +23068,7 @@
         <v>33.22705411164569</v>
       </c>
       <c r="D430" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E430">
         <v>20.4716916981737</v>
@@ -23095,7 +23104,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23109,7 +23118,7 @@
         <v>33.43325315348858</v>
       </c>
       <c r="D431" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E431">
         <v>20.65780641775917</v>
@@ -23145,7 +23154,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23159,7 +23168,7 @@
         <v>33.53120523654898</v>
       </c>
       <c r="D432" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E432">
         <v>20.7462177135085</v>
@@ -23195,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23245,7 +23254,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23259,7 +23268,7 @@
         <v>33.46421187526697</v>
       </c>
       <c r="D434" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E434">
         <v>21.58554463904314</v>
@@ -23295,7 +23304,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23345,7 +23354,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23359,7 +23368,7 @@
         <v>33.20896438389043</v>
       </c>
       <c r="D436" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E436">
         <v>21.35184401382175</v>
@@ -23395,7 +23404,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23409,7 +23418,7 @@
         <v>33.24525244457716</v>
       </c>
       <c r="D437" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E437">
         <v>21.38506879665831</v>
@@ -23459,7 +23468,7 @@
         <v>33.30754061736793</v>
       </c>
       <c r="D438" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E438">
         <v>21.44209887694077</v>
@@ -23495,7 +23504,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23545,7 +23554,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23595,7 +23604,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23645,7 +23654,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23659,7 +23668,7 @@
         <v>33.37808699058778</v>
       </c>
       <c r="D442" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E442">
         <v>21.50669003683685</v>
@@ -23695,7 +23704,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23745,7 +23754,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23795,7 +23804,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23845,7 +23854,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23859,7 +23868,7 @@
         <v>33.3491605949092</v>
       </c>
       <c r="D446" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E446">
         <v>21.48020547975453</v>
@@ -23895,7 +23904,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23945,7 +23954,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -23995,7 +24004,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24045,7 +24054,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24059,7 +24068,7 @@
         <v>33.21868761846164</v>
       </c>
       <c r="D450" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E450">
         <v>21.36074645586423</v>
@@ -24095,7 +24104,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24145,7 +24154,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24195,7 +24204,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24245,7 +24254,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24295,7 +24304,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24309,7 +24318,7 @@
         <v>33.10860895395319</v>
       </c>
       <c r="D455" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E455">
         <v>21.25996014615194</v>
@@ -24345,7 +24354,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24395,7 +24404,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24445,7 +24454,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24495,7 +24504,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24509,7 +24518,7 @@
         <v>32.82858702883275</v>
       </c>
       <c r="D459" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E459">
         <v>21.00357643548973</v>
@@ -24545,7 +24554,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24659,7 +24668,7 @@
         <v>32.43391527499527</v>
       </c>
       <c r="D462" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E462">
         <v>20.64222112840476</v>
@@ -24745,7 +24754,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24759,7 +24768,7 @@
         <v>32.1976037826028</v>
       </c>
       <c r="D464" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E464">
         <v>20.42585800874672</v>
@@ -24795,7 +24804,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24809,7 +24818,7 @@
         <v>31.9359757436375</v>
       </c>
       <c r="D465" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E465">
         <v>20.18631545359018</v>
@@ -24845,7 +24854,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24859,7 +24868,7 @@
         <v>31.6928085141255</v>
       </c>
       <c r="D466" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E466">
         <v>19.96367532786815</v>
@@ -24909,7 +24918,7 @@
         <v>31.38607212722557</v>
       </c>
       <c r="D467" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E467">
         <v>19.96017071526525</v>
@@ -24945,7 +24954,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24959,7 +24968,7 @@
         <v>31.09488527318194</v>
       </c>
       <c r="D468" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E468">
         <v>19.69041319680059</v>
@@ -25009,7 +25018,7 @@
         <v>28.76090315089132</v>
       </c>
       <c r="D469" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E469">
         <v>19.57543646755398</v>
@@ -25045,7 +25054,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25059,7 +25068,7 @@
         <v>30.97077487852789</v>
       </c>
       <c r="D470" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E470">
         <v>19.57543646755398</v>
@@ -25095,7 +25104,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25109,7 +25118,7 @@
         <v>28.60148803846228</v>
       </c>
       <c r="D471" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E471">
         <v>19.42949065339434</v>
@@ -25145,7 +25154,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25159,7 +25168,7 @@
         <v>30.81323523800978</v>
       </c>
       <c r="D472" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E472">
         <v>19.42949065339434</v>
@@ -25195,7 +25204,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25209,7 +25218,7 @@
         <v>28.31621253771513</v>
       </c>
       <c r="D473" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E473">
         <v>19.16831864415417</v>
@@ -25245,7 +25254,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25259,7 +25268,7 @@
         <v>30.53131591962436</v>
       </c>
       <c r="D474" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E474">
         <v>19.16831864415417</v>
@@ -25295,7 +25304,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25309,7 +25318,7 @@
         <v>28.17117124931562</v>
       </c>
       <c r="D475" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E475">
         <v>19.16188388044775</v>
@@ -25359,7 +25368,7 @@
         <v>30.52436998310014</v>
       </c>
       <c r="D476" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E476">
         <v>19.16188388044775</v>
@@ -25409,7 +25418,7 @@
         <v>28.43299823269307</v>
       </c>
       <c r="D477" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E477">
         <v>19.40417998614624</v>
@@ -25445,7 +25454,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25459,7 +25468,7 @@
         <v>28.68381801752044</v>
       </c>
       <c r="D478" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E478">
         <v>19.6362899708081</v>
@@ -25509,7 +25518,7 @@
         <v>28.80289710513282</v>
       </c>
       <c r="D479" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E479">
         <v>19.74648640215534</v>
@@ -25545,7 +25554,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25559,7 +25568,7 @@
         <v>28.66069705648685</v>
       </c>
       <c r="D480" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E480">
         <v>19.74648640215534</v>
@@ -25595,7 +25604,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25609,7 +25618,7 @@
         <v>28.92716526228032</v>
       </c>
       <c r="D481" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E481">
         <v>19.86148482649941</v>
@@ -25645,7 +25654,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25659,7 +25668,7 @@
         <v>28.78241267851456</v>
       </c>
       <c r="D482" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E482">
         <v>19.86148482649941</v>
@@ -25695,7 +25704,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25709,7 +25718,7 @@
         <v>28.69210673371983</v>
       </c>
       <c r="D483" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E483">
         <v>19.64396039358289</v>
@@ -25745,7 +25754,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25759,7 +25768,7 @@
         <v>28.55218237918936</v>
       </c>
       <c r="D484" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E484">
         <v>19.64396039358289</v>
@@ -25795,7 +25804,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25809,7 +25818,7 @@
         <v>24.1238374281487</v>
       </c>
       <c r="D485" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E485">
         <v>15.41645928485977</v>
@@ -25845,7 +25854,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25859,7 +25868,7 @@
         <v>23.88230241564499</v>
       </c>
       <c r="D486" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E486">
         <v>15.41645928485977</v>
@@ -25895,7 +25904,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25909,7 +25918,7 @@
         <v>16.53295008901819</v>
       </c>
       <c r="D487" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E487">
         <v>8.24961705438853</v>
@@ -25959,7 +25968,7 @@
         <v>16.39809781749685</v>
       </c>
       <c r="D488" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E488">
         <v>8.24961705438853</v>
@@ -26009,7 +26018,7 @@
         <v>8.646669450447945</v>
       </c>
       <c r="D489" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E489">
         <v>0.5067815058065008</v>
@@ -26045,7 +26054,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26059,7 +26068,7 @@
         <v>11.10765720787195</v>
       </c>
       <c r="D490" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E490">
         <v>0.5067815058065008</v>
@@ -26095,7 +26104,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26109,7 +26118,7 @@
         <v>8.708207114263224</v>
       </c>
       <c r="D491" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E491">
         <v>0.5067815058065008</v>
@@ -26145,7 +26154,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26159,7 +26168,7 @@
         <v>7.091043911098566</v>
       </c>
       <c r="D492" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E492">
         <v>-0.9493259013959516</v>
@@ -26209,7 +26218,7 @@
         <v>9.494415907805923</v>
       </c>
       <c r="D493" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E493">
         <v>-0.9493259013959516</v>
@@ -26259,7 +26268,7 @@
         <v>7.115916999912343</v>
       </c>
       <c r="D494" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E494">
         <v>-0.9493259013959516</v>
@@ -26309,7 +26318,7 @@
         <v>5.65581229233937</v>
       </c>
       <c r="D495" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E495">
         <v>-2.292741355992099</v>
@@ -26345,7 +26354,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26359,7 +26368,7 @@
         <v>8.006027562426013</v>
       </c>
       <c r="D496" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E496">
         <v>-2.292741355992099</v>
@@ -26395,7 +26404,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26409,7 +26418,7 @@
         <v>5.646858373303601</v>
       </c>
       <c r="D497" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E497">
         <v>-2.292741355992099</v>
@@ -26445,7 +26454,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26459,7 +26468,7 @@
         <v>4.107061890942596</v>
       </c>
       <c r="D498" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E498">
         <v>-3.742413448882012</v>
@@ -26495,7 +26504,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26509,7 +26518,7 @@
         <v>6.399916035051582</v>
       </c>
       <c r="D499" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E499">
         <v>-3.742413448882012</v>
@@ -26545,7 +26554,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26559,7 +26568,7 @@
         <v>4.061605437193776</v>
       </c>
       <c r="D500" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E500">
         <v>-3.742413448882012</v>
@@ -26595,7 +26604,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26609,7 +26618,7 @@
         <v>3.994587595705951</v>
       </c>
       <c r="D501" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E501">
         <v>-3.847692418834157</v>
@@ -26645,7 +26654,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26659,7 +26668,7 @@
         <v>6.283276025176541</v>
       </c>
       <c r="D502" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E502">
         <v>-3.847692418834157</v>
@@ -26695,7 +26704,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26709,7 +26718,7 @@
         <v>3.94648023264179</v>
       </c>
       <c r="D503" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E503">
         <v>-3.847692418834157</v>
@@ -26745,7 +26754,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26759,7 +26768,7 @@
         <v>3.810208807303631</v>
       </c>
       <c r="D504" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E504">
         <v>-4.02027593121074</v>
@@ -26809,7 +26818,7 @@
         <v>6.092068392759323</v>
       </c>
       <c r="D505" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E505">
         <v>-4.02027593121074</v>
@@ -26859,7 +26868,7 @@
         <v>3.757755816229981</v>
       </c>
       <c r="D506" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E506">
         <v>-4.02027593121074</v>
@@ -26909,7 +26918,7 @@
         <v>3.242943955180543</v>
       </c>
       <c r="D507" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E507">
         <v>-4.551251112659287</v>
@@ -26959,7 +26968,7 @@
         <v>5.503793731298337</v>
       </c>
       <c r="D508" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E508">
         <v>-4.551251112659287</v>
@@ -27009,7 +27018,7 @@
         <v>3.177121085437328</v>
       </c>
       <c r="D509" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E509">
         <v>-4.551251112659287</v>
@@ -27059,7 +27068,7 @@
         <v>0.5276020656298783</v>
       </c>
       <c r="D510" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E510">
         <v>-7.276209063074127</v>
@@ -27095,7 +27104,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27109,7 +27118,7 @@
         <v>2.687883623616173</v>
       </c>
       <c r="D511" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E511">
         <v>-7.276209063074127</v>
@@ -27145,7 +27154,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27159,7 +27168,7 @@
         <v>0.3977812388938915</v>
       </c>
       <c r="D512" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E512">
         <v>-7.276209063074127</v>
@@ -27195,7 +27204,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27209,7 +27218,7 @@
         <v>-0.0005009764291159513</v>
       </c>
       <c r="D513" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E513">
         <v>-7.771120443679365</v>
@@ -27245,7 +27254,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27259,7 +27268,7 @@
         <v>2.140221209629061</v>
       </c>
       <c r="D514" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E514">
         <v>-7.771120443679365</v>
@@ -27295,7 +27304,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27309,7 +27318,7 @@
         <v>-0.1427686762102667</v>
       </c>
       <c r="D515" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E515">
         <v>-7.771120443679365</v>
@@ -27345,7 +27354,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27359,7 +27368,7 @@
         <v>-0.6951028983788206</v>
       </c>
       <c r="D516" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E516">
         <v>-8.422066128110345</v>
@@ -27395,7 +27404,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27409,7 +27418,7 @@
         <v>1.419893290570108</v>
       </c>
       <c r="D517" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E517">
         <v>-8.422066128110345</v>
@@ -27445,7 +27454,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27459,7 +27468,7 @@
         <v>-0.8537416872294941</v>
       </c>
       <c r="D518" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E518">
         <v>-8.422066128110345</v>
@@ -27495,7 +27504,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27509,7 +27518,7 @@
         <v>-1.098623802898558</v>
       </c>
       <c r="D519" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E519">
         <v>-8.615075478807405</v>
@@ -27545,7 +27554,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27559,7 +27568,7 @@
         <v>1.001427167364454</v>
       </c>
       <c r="D520" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E520">
         <v>-8.615075478807405</v>
@@ -27595,7 +27604,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27609,7 +27618,7 @@
         <v>-1.266773185458455</v>
       </c>
       <c r="D521" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E521">
         <v>-8.615075478807405</v>
@@ -27645,7 +27654,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27659,7 +27668,7 @@
         <v>-1.400997181997106</v>
       </c>
       <c r="D522" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E522">
         <v>-8.898105106381124</v>
@@ -27695,7 +27704,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27709,7 +27718,7 @@
         <v>0.6878547742252223</v>
       </c>
       <c r="D523" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E523">
         <v>-8.898105106381124</v>
@@ -27745,7 +27754,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27759,7 +27768,7 @@
         <v>-1.576273209855614</v>
       </c>
       <c r="D524" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E524">
         <v>-8.898105106381124</v>
@@ -27795,7 +27804,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27809,7 +27818,7 @@
         <v>-1.724593447066837</v>
       </c>
       <c r="D525" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E525">
         <v>-9.200999926884109</v>
@@ -27845,7 +27854,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27859,7 +27868,7 @@
         <v>0.3522734623010564</v>
       </c>
       <c r="D526" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E526">
         <v>-9.200999926884109</v>
@@ -27895,7 +27904,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27909,7 +27918,7 @@
         <v>-1.907496322923627</v>
       </c>
       <c r="D527" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E527">
         <v>-9.200999926884109</v>
@@ -27945,7 +27954,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27959,7 +27968,7 @@
         <v>44.86204822710516</v>
       </c>
       <c r="D528" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E528">
         <v>35.52043652295812</v>
@@ -27995,7 +28004,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28009,7 +28018,7 @@
         <v>46.13402290259216</v>
       </c>
       <c r="D529" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E529">
         <v>36.69877772856216</v>
@@ -28045,7 +28054,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28059,7 +28068,7 @@
         <v>46.08362925847739</v>
       </c>
       <c r="D530" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E530">
         <v>36.69877772856216</v>
@@ -28095,7 +28104,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28109,7 +28118,7 @@
         <v>45.05397872766954</v>
       </c>
       <c r="D531" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E531">
         <v>35.69823850422841</v>
@@ -28145,7 +28154,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28159,7 +28168,7 @@
         <v>44.98156832800709</v>
       </c>
       <c r="D532" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E532">
         <v>35.69823850422841</v>
@@ -28195,7 +28204,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28209,7 +28218,7 @@
         <v>42.5821201676108</v>
       </c>
       <c r="D533" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E533">
         <v>33.77379366345071</v>
@@ -28245,7 +28254,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28259,7 +28268,7 @@
         <v>42.55551239448888</v>
       </c>
       <c r="D534" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E534">
         <v>33.77379366345071</v>
@@ -28295,7 +28304,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28309,7 +28318,7 @@
         <v>42.86185585668593</v>
       </c>
       <c r="D535" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E535">
         <v>33.77379366345071</v>
@@ -28345,7 +28354,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28359,7 +28368,7 @@
         <v>9.729438161046986</v>
       </c>
       <c r="D536" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E536">
         <v>4.60825443961048</v>
@@ -28395,7 +28404,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28409,7 +28418,7 @@
         <v>1.841930457020688</v>
       </c>
       <c r="D537" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E537">
         <v>6.89439153971923</v>
@@ -28445,7 +28454,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28459,7 +28468,7 @@
         <v>7.54859977610915</v>
       </c>
       <c r="D538" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E538">
         <v>3.585313169516937</v>
@@ -28495,7 +28504,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28509,7 +28518,7 @@
         <v>-0.07307844071422664</v>
       </c>
       <c r="D539" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E539">
         <v>4.928669866220837</v>
@@ -28545,7 +28554,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28559,7 +28568,7 @@
         <v>-0.1707707281713766</v>
       </c>
       <c r="D540" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E540">
         <v>4.928669866220837</v>
@@ -28595,7 +28604,57 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>408</v>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="541" spans="1:16">
+      <c r="A541" s="1">
+        <v>0</v>
+      </c>
+      <c r="B541" t="s">
+        <v>95</v>
+      </c>
+      <c r="C541">
+        <v>3.699818204723471</v>
+      </c>
+      <c r="D541" t="s">
+        <v>208</v>
+      </c>
+      <c r="E541">
+        <v>5.312259044553848</v>
+      </c>
+      <c r="F541">
+        <v>1</v>
+      </c>
+      <c r="G541">
+        <v>0.05348018179527653</v>
+      </c>
+      <c r="H541">
+        <v>0.05654774095544615</v>
+      </c>
+      <c r="I541">
+        <v>1.612440839830377</v>
+      </c>
+      <c r="J541">
+        <v>1.914629368867425</v>
+      </c>
+      <c r="K541">
+        <v>13</v>
+      </c>
+      <c r="L541">
+        <v>28.59</v>
+      </c>
+      <c r="M541">
+        <v>13.38</v>
+      </c>
+      <c r="N541">
+        <v>30.93</v>
+      </c>
+      <c r="O541">
+        <v>1</v>
+      </c>
+      <c r="P541" t="s">
+        <v>411</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="412">
   <si>
     <t>trade_time</t>
   </si>
@@ -295,12 +295,12 @@
     <t>2021-01-15</t>
   </si>
   <si>
+    <t>2021-03-10</t>
+  </si>
+  <si>
     <t>2021-03-19</t>
   </si>
   <si>
-    <t>2021-03-10</t>
-  </si>
-  <si>
     <t>2021-08-30</t>
   </si>
   <si>
@@ -640,7 +640,7 @@
     <t>2021-02-03</t>
   </si>
   <si>
-    <t>2021-09-02</t>
+    <t>2021-09-07</t>
   </si>
   <si>
     <t>2016-03-30</t>
@@ -1607,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P541"/>
+  <dimension ref="A1:P542"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28415,7 +28415,7 @@
         <v>93</v>
       </c>
       <c r="C537">
-        <v>1.841930457020688</v>
+        <v>1.966821409142597</v>
       </c>
       <c r="D537" t="s">
         <v>206</v>
@@ -28427,22 +28427,22 @@
         <v>1</v>
       </c>
       <c r="G537">
-        <v>0.06031806954297931</v>
+        <v>0.06123317859085741</v>
       </c>
       <c r="H537">
         <v>0.06400560846028076</v>
       </c>
       <c r="I537">
-        <v>5.052461082698542</v>
+        <v>4.927570130576633</v>
       </c>
       <c r="J537">
         <v>1.795950217627722</v>
       </c>
       <c r="K537">
-        <v>16.28</v>
+        <v>16.5</v>
       </c>
       <c r="L537">
-        <v>31.08</v>
+        <v>31.6</v>
       </c>
       <c r="M537">
         <v>15.9</v>
@@ -28459,96 +28459,96 @@
     </row>
     <row r="538" spans="1:16">
       <c r="A538" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B538" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C538">
-        <v>7.54859977610915</v>
+        <v>1.841930457020688</v>
       </c>
       <c r="D538" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E538">
-        <v>3.585313169516937</v>
+        <v>6.89439153971923</v>
       </c>
       <c r="F538">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G538">
-        <v>0.07527140022389085</v>
+        <v>0.06031806954297931</v>
       </c>
       <c r="H538">
-        <v>0.06685468683048307</v>
+        <v>0.06400560846028076</v>
       </c>
       <c r="I538">
-        <v>3.963286606592213</v>
+        <v>5.052461082698542</v>
       </c>
       <c r="J538">
-        <v>1.919580511558438</v>
+        <v>1.795950217627722</v>
       </c>
       <c r="K538">
-        <v>17.64</v>
+        <v>16.28</v>
       </c>
       <c r="L538">
-        <v>41.41</v>
+        <v>31.08</v>
       </c>
       <c r="M538">
-        <v>16.48</v>
+        <v>15.9</v>
       </c>
       <c r="N538">
-        <v>35.22</v>
+        <v>35.45</v>
       </c>
       <c r="O538">
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="539" spans="1:16">
       <c r="A539" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B539" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C539">
-        <v>-0.07307844071422664</v>
+        <v>7.54859977610915</v>
       </c>
       <c r="D539" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E539">
-        <v>4.928669866220837</v>
+        <v>3.585313169516937</v>
       </c>
       <c r="F539">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G539">
-        <v>0.06327307844071423</v>
+        <v>0.07527140022389085</v>
       </c>
       <c r="H539">
-        <v>0.06597133013377916</v>
+        <v>0.06685468683048307</v>
       </c>
       <c r="I539">
-        <v>5.001748306935063</v>
+        <v>3.963286606592213</v>
       </c>
       <c r="J539">
         <v>1.919580511558438</v>
       </c>
       <c r="K539">
-        <v>16.5</v>
+        <v>17.64</v>
       </c>
       <c r="L539">
-        <v>31.6</v>
+        <v>41.41</v>
       </c>
       <c r="M539">
-        <v>15.9</v>
+        <v>16.48</v>
       </c>
       <c r="N539">
-        <v>35.45</v>
+        <v>35.22</v>
       </c>
       <c r="O539">
         <v>1</v>
@@ -28559,13 +28559,13 @@
     </row>
     <row r="540" spans="1:16">
       <c r="A540" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B540" t="s">
         <v>93</v>
       </c>
       <c r="C540">
-        <v>-0.1707707281713766</v>
+        <v>-0.07307844071422664</v>
       </c>
       <c r="D540" t="s">
         <v>206</v>
@@ -28577,22 +28577,22 @@
         <v>1</v>
       </c>
       <c r="G540">
-        <v>0.06233077072817137</v>
+        <v>0.06327307844071423</v>
       </c>
       <c r="H540">
         <v>0.06597133013377916</v>
       </c>
       <c r="I540">
-        <v>5.099440594392213</v>
+        <v>5.001748306935063</v>
       </c>
       <c r="J540">
         <v>1.919580511558438</v>
       </c>
       <c r="K540">
-        <v>16.28</v>
+        <v>16.5</v>
       </c>
       <c r="L540">
-        <v>31.08</v>
+        <v>31.6</v>
       </c>
       <c r="M540">
         <v>15.9</v>
@@ -28609,51 +28609,101 @@
     </row>
     <row r="541" spans="1:16">
       <c r="A541" s="1">
+        <v>2</v>
+      </c>
+      <c r="B541" t="s">
+        <v>94</v>
+      </c>
+      <c r="C541">
+        <v>-0.1707707281713766</v>
+      </c>
+      <c r="D541" t="s">
+        <v>206</v>
+      </c>
+      <c r="E541">
+        <v>4.928669866220837</v>
+      </c>
+      <c r="F541">
+        <v>1</v>
+      </c>
+      <c r="G541">
+        <v>0.06233077072817137</v>
+      </c>
+      <c r="H541">
+        <v>0.06597133013377916</v>
+      </c>
+      <c r="I541">
+        <v>5.099440594392213</v>
+      </c>
+      <c r="J541">
+        <v>1.919580511558438</v>
+      </c>
+      <c r="K541">
+        <v>16.28</v>
+      </c>
+      <c r="L541">
+        <v>31.08</v>
+      </c>
+      <c r="M541">
+        <v>15.9</v>
+      </c>
+      <c r="N541">
+        <v>35.45</v>
+      </c>
+      <c r="O541">
+        <v>1</v>
+      </c>
+      <c r="P541" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="542" spans="1:16">
+      <c r="A542" s="1">
         <v>0</v>
       </c>
-      <c r="B541" t="s">
+      <c r="B542" t="s">
         <v>95</v>
       </c>
-      <c r="C541">
+      <c r="C542">
         <v>3.699818204723471</v>
       </c>
-      <c r="D541" t="s">
+      <c r="D542" t="s">
         <v>208</v>
       </c>
-      <c r="E541">
-        <v>5.312259044553848</v>
-      </c>
-      <c r="F541">
-        <v>1</v>
-      </c>
-      <c r="G541">
+      <c r="E542">
+        <v>5.615918345535061</v>
+      </c>
+      <c r="F542">
+        <v>1</v>
+      </c>
+      <c r="G542">
         <v>0.05348018179527653</v>
       </c>
-      <c r="H541">
-        <v>0.05654774095544615</v>
-      </c>
-      <c r="I541">
-        <v>1.612440839830377</v>
-      </c>
-      <c r="J541">
+      <c r="H542">
+        <v>0.05746408165446493</v>
+      </c>
+      <c r="I542">
+        <v>1.91610014081159</v>
+      </c>
+      <c r="J542">
         <v>1.914629368867425</v>
       </c>
-      <c r="K541">
+      <c r="K542">
         <v>13</v>
       </c>
-      <c r="L541">
+      <c r="L542">
         <v>28.59</v>
       </c>
-      <c r="M541">
-        <v>13.38</v>
-      </c>
-      <c r="N541">
-        <v>30.93</v>
-      </c>
-      <c r="O541">
-        <v>1</v>
-      </c>
-      <c r="P541" t="s">
+      <c r="M542">
+        <v>13.54</v>
+      </c>
+      <c r="N542">
+        <v>31.54</v>
+      </c>
+      <c r="O542">
+        <v>1</v>
+      </c>
+      <c r="P542" t="s">
         <v>411</v>
       </c>
     </row>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="414">
   <si>
     <t>trade_time</t>
   </si>
@@ -640,6 +640,9 @@
     <t>2021-02-03</t>
   </si>
   <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
     <t>2021-09-07</t>
   </si>
   <si>
@@ -1247,6 +1250,9 @@
   </si>
   <si>
     <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2021-08-20</t>
   </si>
   <si>
     <t>2021-08-27</t>
@@ -1607,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P542"/>
+  <dimension ref="A1:P543"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1704,7 +1710,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1754,7 +1760,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1804,7 +1810,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1854,7 +1860,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1904,7 +1910,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1954,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2004,7 +2010,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2054,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2104,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2154,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2204,7 +2210,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2254,7 +2260,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2304,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2354,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2404,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2454,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2504,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2554,7 +2560,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2604,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2654,7 +2660,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2704,7 +2710,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3054,7 +3060,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3104,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3154,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3204,7 +3210,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3254,7 +3260,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3304,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3354,7 +3360,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3404,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3454,7 +3460,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3504,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3554,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3604,7 +3610,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3654,7 +3660,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3704,7 +3710,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3754,7 +3760,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3804,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3854,7 +3860,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3904,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3954,7 +3960,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4004,7 +4010,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4054,7 +4060,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4104,7 +4110,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4154,7 +4160,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4204,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4254,7 +4260,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4304,7 +4310,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4354,7 +4360,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4404,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4454,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4504,7 +4510,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4554,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4604,7 +4610,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4654,7 +4660,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4704,7 +4710,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4754,7 +4760,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4804,7 +4810,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4854,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4904,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4954,7 +4960,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5004,7 +5010,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5054,7 +5060,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5104,7 +5110,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5154,7 +5160,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5204,7 +5210,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5254,7 +5260,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5304,7 +5310,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5354,7 +5360,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5404,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5454,7 +5460,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5504,7 +5510,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5554,7 +5560,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5604,7 +5610,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5654,7 +5660,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5704,7 +5710,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5754,7 +5760,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5804,7 +5810,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5854,7 +5860,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5904,7 +5910,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5954,7 +5960,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6004,7 +6010,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6054,7 +6060,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6104,7 +6110,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6154,7 +6160,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6204,7 +6210,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6254,7 +6260,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6304,7 +6310,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6354,7 +6360,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6404,7 +6410,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6454,7 +6460,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6504,7 +6510,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6554,7 +6560,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6604,7 +6610,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6654,7 +6660,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6704,7 +6710,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6754,7 +6760,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6804,7 +6810,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6854,7 +6860,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6904,7 +6910,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6954,7 +6960,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7004,7 +7010,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7054,7 +7060,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7104,7 +7110,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7154,7 +7160,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7204,7 +7210,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7254,7 +7260,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7304,7 +7310,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7354,7 +7360,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7404,7 +7410,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7454,7 +7460,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7504,7 +7510,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7554,7 +7560,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7604,7 +7610,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7654,7 +7660,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7704,7 +7710,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7754,7 +7760,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7804,7 +7810,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7854,7 +7860,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7904,7 +7910,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7954,7 +7960,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8004,7 +8010,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8054,7 +8060,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8104,7 +8110,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8154,7 +8160,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8204,7 +8210,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8254,7 +8260,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8304,7 +8310,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8354,7 +8360,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8404,7 +8410,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8454,7 +8460,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8504,7 +8510,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8554,7 +8560,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8604,7 +8610,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8654,7 +8660,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8704,7 +8710,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8754,7 +8760,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8904,7 +8910,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8954,7 +8960,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9004,7 +9010,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9054,7 +9060,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9104,7 +9110,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9154,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9204,7 +9210,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9254,7 +9260,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9304,7 +9310,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9354,7 +9360,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9404,7 +9410,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9454,7 +9460,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9504,7 +9510,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9554,7 +9560,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9754,7 +9760,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9804,7 +9810,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9854,7 +9860,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9904,7 +9910,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9954,7 +9960,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10004,7 +10010,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10054,7 +10060,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10104,7 +10110,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10154,7 +10160,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10204,7 +10210,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10254,7 +10260,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10304,7 +10310,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10354,7 +10360,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10404,7 +10410,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10454,7 +10460,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10504,7 +10510,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10554,7 +10560,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10604,7 +10610,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10654,7 +10660,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10704,7 +10710,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10754,7 +10760,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10804,7 +10810,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10854,7 +10860,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10904,7 +10910,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10954,7 +10960,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11004,7 +11010,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11054,7 +11060,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11104,7 +11110,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11404,7 +11410,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11454,7 +11460,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11604,7 +11610,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11654,7 +11660,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -12054,7 +12060,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12104,7 +12110,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12154,7 +12160,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12204,7 +12210,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12254,7 +12260,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12304,7 +12310,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12354,7 +12360,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12404,7 +12410,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12454,7 +12460,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12504,7 +12510,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12554,7 +12560,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12604,7 +12610,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12654,7 +12660,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12704,7 +12710,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -13154,7 +13160,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13204,7 +13210,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13254,7 +13260,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13454,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13504,7 +13510,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13554,7 +13560,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13604,7 +13610,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13654,7 +13660,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13704,7 +13710,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13754,7 +13760,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13804,7 +13810,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13854,7 +13860,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13904,7 +13910,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13954,7 +13960,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14004,7 +14010,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14054,7 +14060,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14104,7 +14110,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14154,7 +14160,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14204,7 +14210,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14254,7 +14260,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14304,7 +14310,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14354,7 +14360,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14404,7 +14410,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14454,7 +14460,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14504,7 +14510,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14554,7 +14560,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14604,7 +14610,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14654,7 +14660,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14704,7 +14710,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14754,7 +14760,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14804,7 +14810,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14854,7 +14860,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14904,7 +14910,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14954,7 +14960,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15004,7 +15010,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15054,7 +15060,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15104,7 +15110,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15154,7 +15160,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15204,7 +15210,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15254,7 +15260,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15304,7 +15310,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15354,7 +15360,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15404,7 +15410,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15454,7 +15460,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15504,7 +15510,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15554,7 +15560,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15604,7 +15610,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15654,7 +15660,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15704,7 +15710,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15754,7 +15760,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15804,7 +15810,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15854,7 +15860,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15904,7 +15910,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15954,7 +15960,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16004,7 +16010,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16054,7 +16060,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16104,7 +16110,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16154,7 +16160,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16354,7 +16360,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16404,7 +16410,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16454,7 +16460,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16504,7 +16510,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16554,7 +16560,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16604,7 +16610,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16654,7 +16660,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16704,7 +16710,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16754,7 +16760,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16804,7 +16810,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16854,7 +16860,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16904,7 +16910,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16954,7 +16960,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17004,7 +17010,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17054,7 +17060,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17104,7 +17110,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17154,7 +17160,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17204,7 +17210,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17254,7 +17260,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17304,7 +17310,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17354,7 +17360,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17404,7 +17410,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17454,7 +17460,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17504,7 +17510,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17554,7 +17560,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17604,7 +17610,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17654,7 +17660,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17704,7 +17710,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17754,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17804,7 +17810,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17854,7 +17860,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17904,7 +17910,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17954,7 +17960,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18004,7 +18010,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18054,7 +18060,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18104,7 +18110,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18154,7 +18160,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18204,7 +18210,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18254,7 +18260,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18304,7 +18310,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18354,7 +18360,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18404,7 +18410,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18454,7 +18460,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18504,7 +18510,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18554,7 +18560,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18604,7 +18610,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18654,7 +18660,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18704,7 +18710,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18754,7 +18760,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18804,7 +18810,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18854,7 +18860,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18904,7 +18910,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18954,7 +18960,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19004,7 +19010,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19054,7 +19060,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19104,7 +19110,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19154,7 +19160,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19354,7 +19360,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19404,7 +19410,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19454,7 +19460,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19504,7 +19510,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19554,7 +19560,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19604,7 +19610,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19654,7 +19660,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19704,7 +19710,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19854,7 +19860,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19904,7 +19910,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19954,7 +19960,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20004,7 +20010,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20054,7 +20060,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20104,7 +20110,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20154,7 +20160,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20204,7 +20210,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20254,7 +20260,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20304,7 +20310,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20354,7 +20360,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20404,7 +20410,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20454,7 +20460,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20504,7 +20510,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20554,7 +20560,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20604,7 +20610,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20654,7 +20660,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20704,7 +20710,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20754,7 +20760,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20804,7 +20810,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20854,7 +20860,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20904,7 +20910,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20954,7 +20960,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21004,7 +21010,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21054,7 +21060,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21104,7 +21110,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21154,7 +21160,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21204,7 +21210,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21254,7 +21260,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21304,7 +21310,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21354,7 +21360,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21404,7 +21410,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21454,7 +21460,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21504,7 +21510,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21554,7 +21560,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21604,7 +21610,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21654,7 +21660,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21704,7 +21710,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21754,7 +21760,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21804,7 +21810,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21854,7 +21860,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21904,7 +21910,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21954,7 +21960,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22004,7 +22010,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22054,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22104,7 +22110,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22154,7 +22160,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22204,7 +22210,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22254,7 +22260,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22304,7 +22310,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22354,7 +22360,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22404,7 +22410,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22454,7 +22460,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22504,7 +22510,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22554,7 +22560,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22604,7 +22610,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22654,7 +22660,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22704,7 +22710,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22754,7 +22760,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22804,7 +22810,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22854,7 +22860,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22904,7 +22910,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22954,7 +22960,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23004,7 +23010,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23054,7 +23060,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23104,7 +23110,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23154,7 +23160,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23204,7 +23210,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23254,7 +23260,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23304,7 +23310,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23354,7 +23360,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23404,7 +23410,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23504,7 +23510,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23554,7 +23560,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23604,7 +23610,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23654,7 +23660,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23704,7 +23710,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23754,7 +23760,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23804,7 +23810,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23854,7 +23860,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23904,7 +23910,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23954,7 +23960,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24004,7 +24010,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24054,7 +24060,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24104,7 +24110,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24154,7 +24160,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24204,7 +24210,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24254,7 +24260,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24304,7 +24310,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24354,7 +24360,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24404,7 +24410,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24454,7 +24460,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24504,7 +24510,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24554,7 +24560,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24754,7 +24760,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24804,7 +24810,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24854,7 +24860,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24954,7 +24960,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25054,7 +25060,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25104,7 +25110,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25154,7 +25160,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25204,7 +25210,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25254,7 +25260,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25304,7 +25310,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25454,7 +25460,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25554,7 +25560,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25604,7 +25610,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25654,7 +25660,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25704,7 +25710,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25754,7 +25760,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25804,7 +25810,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25854,7 +25860,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25904,7 +25910,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26054,7 +26060,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26104,7 +26110,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26154,7 +26160,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26354,7 +26360,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26404,7 +26410,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26454,7 +26460,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26504,7 +26510,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26554,7 +26560,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26604,7 +26610,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26654,7 +26660,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26704,7 +26710,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26754,7 +26760,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27104,7 +27110,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27154,7 +27160,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27204,7 +27210,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27254,7 +27260,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27304,7 +27310,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27354,7 +27360,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27404,7 +27410,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27454,7 +27460,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27504,7 +27510,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27554,7 +27560,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27604,7 +27610,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27654,7 +27660,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27704,7 +27710,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27754,7 +27760,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27804,7 +27810,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27854,7 +27860,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27904,7 +27910,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27954,7 +27960,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28004,7 +28010,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28054,7 +28060,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28104,7 +28110,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28154,7 +28160,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28204,7 +28210,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28254,7 +28260,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28304,7 +28310,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28354,7 +28360,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28404,7 +28410,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28454,7 +28460,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28504,7 +28510,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28554,7 +28560,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28604,7 +28610,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28654,7 +28660,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28665,28 +28671,28 @@
         <v>95</v>
       </c>
       <c r="C542">
-        <v>3.699818204723471</v>
+        <v>4.212040637078079</v>
       </c>
       <c r="D542" t="s">
         <v>208</v>
       </c>
       <c r="E542">
-        <v>5.615918345535061</v>
+        <v>5.766958685489474</v>
       </c>
       <c r="F542">
         <v>1</v>
       </c>
       <c r="G542">
-        <v>0.05348018179527653</v>
+        <v>0.05296795936292192</v>
       </c>
       <c r="H542">
-        <v>0.05746408165446493</v>
+        <v>0.05587304131451053</v>
       </c>
       <c r="I542">
-        <v>1.91610014081159</v>
+        <v>1.554918048411395</v>
       </c>
       <c r="J542">
-        <v>1.914629368867425</v>
+        <v>1.875227643301686</v>
       </c>
       <c r="K542">
         <v>13</v>
@@ -28695,16 +28701,66 @@
         <v>28.59</v>
       </c>
       <c r="M542">
+        <v>13.36</v>
+      </c>
+      <c r="N542">
+        <v>30.82</v>
+      </c>
+      <c r="O542">
+        <v>1</v>
+      </c>
+      <c r="P542" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="543" spans="1:16">
+      <c r="A543" s="1">
+        <v>0</v>
+      </c>
+      <c r="B543" t="s">
+        <v>95</v>
+      </c>
+      <c r="C543">
+        <v>3.699818204723471</v>
+      </c>
+      <c r="D543" t="s">
+        <v>209</v>
+      </c>
+      <c r="E543">
+        <v>5.615918345535061</v>
+      </c>
+      <c r="F543">
+        <v>1</v>
+      </c>
+      <c r="G543">
+        <v>0.05348018179527653</v>
+      </c>
+      <c r="H543">
+        <v>0.05746408165446493</v>
+      </c>
+      <c r="I543">
+        <v>1.91610014081159</v>
+      </c>
+      <c r="J543">
+        <v>1.914629368867425</v>
+      </c>
+      <c r="K543">
+        <v>13</v>
+      </c>
+      <c r="L543">
+        <v>28.59</v>
+      </c>
+      <c r="M543">
         <v>13.54</v>
       </c>
-      <c r="N542">
+      <c r="N543">
         <v>31.54</v>
       </c>
-      <c r="O542">
-        <v>1</v>
-      </c>
-      <c r="P542" t="s">
-        <v>411</v>
+      <c r="O543">
+        <v>1</v>
+      </c>
+      <c r="P543" t="s">
+        <v>413</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="415">
   <si>
     <t>trade_time</t>
   </si>
@@ -1250,6 +1250,9 @@
   </si>
   <si>
     <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2021-08-18</t>
   </si>
   <si>
     <t>2021-08-20</t>
@@ -1613,7 +1616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P543"/>
+  <dimension ref="A1:P544"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -28671,28 +28674,28 @@
         <v>95</v>
       </c>
       <c r="C542">
-        <v>4.212040637078079</v>
+        <v>4.58724487239736</v>
       </c>
       <c r="D542" t="s">
         <v>208</v>
       </c>
       <c r="E542">
-        <v>5.766958685489474</v>
+        <v>6.152553191940676</v>
       </c>
       <c r="F542">
         <v>1</v>
       </c>
       <c r="G542">
-        <v>0.05296795936292192</v>
+        <v>0.05259275512760264</v>
       </c>
       <c r="H542">
-        <v>0.05587304131451053</v>
+        <v>0.05548744680805932</v>
       </c>
       <c r="I542">
-        <v>1.554918048411395</v>
+        <v>1.565308319543316</v>
       </c>
       <c r="J542">
-        <v>1.875227643301686</v>
+        <v>1.846365779046357</v>
       </c>
       <c r="K542">
         <v>13</v>
@@ -28721,28 +28724,28 @@
         <v>95</v>
       </c>
       <c r="C543">
-        <v>3.699818204723471</v>
+        <v>4.212040637078079</v>
       </c>
       <c r="D543" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E543">
-        <v>5.615918345535061</v>
+        <v>5.766958685489474</v>
       </c>
       <c r="F543">
         <v>1</v>
       </c>
       <c r="G543">
-        <v>0.05348018179527653</v>
+        <v>0.05296795936292192</v>
       </c>
       <c r="H543">
-        <v>0.05746408165446493</v>
+        <v>0.05587304131451053</v>
       </c>
       <c r="I543">
-        <v>1.91610014081159</v>
+        <v>1.554918048411395</v>
       </c>
       <c r="J543">
-        <v>1.914629368867425</v>
+        <v>1.875227643301686</v>
       </c>
       <c r="K543">
         <v>13</v>
@@ -28751,16 +28754,66 @@
         <v>28.59</v>
       </c>
       <c r="M543">
-        <v>13.54</v>
+        <v>13.36</v>
       </c>
       <c r="N543">
-        <v>31.54</v>
+        <v>30.82</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
         <v>413</v>
+      </c>
+    </row>
+    <row r="544" spans="1:16">
+      <c r="A544" s="1">
+        <v>0</v>
+      </c>
+      <c r="B544" t="s">
+        <v>95</v>
+      </c>
+      <c r="C544">
+        <v>3.699818204723471</v>
+      </c>
+      <c r="D544" t="s">
+        <v>209</v>
+      </c>
+      <c r="E544">
+        <v>5.615918345535061</v>
+      </c>
+      <c r="F544">
+        <v>1</v>
+      </c>
+      <c r="G544">
+        <v>0.05348018179527653</v>
+      </c>
+      <c r="H544">
+        <v>0.05746408165446493</v>
+      </c>
+      <c r="I544">
+        <v>1.91610014081159</v>
+      </c>
+      <c r="J544">
+        <v>1.914629368867425</v>
+      </c>
+      <c r="K544">
+        <v>13</v>
+      </c>
+      <c r="L544">
+        <v>28.59</v>
+      </c>
+      <c r="M544">
+        <v>13.54</v>
+      </c>
+      <c r="N544">
+        <v>31.54</v>
+      </c>
+      <c r="O544">
+        <v>1</v>
+      </c>
+      <c r="P544" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="416">
   <si>
     <t>trade_time</t>
   </si>
@@ -641,6 +641,9 @@
   </si>
   <si>
     <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-02</t>
   </si>
   <si>
     <t>2021-09-07</t>
@@ -1713,7 +1716,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1763,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1813,7 +1816,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1863,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1913,7 +1916,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1963,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2013,7 +2016,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2063,7 +2066,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2113,7 +2116,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2163,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2213,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2263,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2313,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2363,7 +2366,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2413,7 +2416,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2463,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2513,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2563,7 +2566,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2613,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2663,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2713,7 +2716,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3063,7 +3066,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3113,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3163,7 +3166,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3213,7 +3216,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3263,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3313,7 +3316,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3363,7 +3366,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3413,7 +3416,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3463,7 +3466,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3513,7 +3516,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3563,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3613,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3663,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3713,7 +3716,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3763,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3813,7 +3816,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3863,7 +3866,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3913,7 +3916,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3963,7 +3966,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4013,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4063,7 +4066,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4113,7 +4116,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4163,7 +4166,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4213,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4263,7 +4266,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4313,7 +4316,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4363,7 +4366,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4413,7 +4416,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4463,7 +4466,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4513,7 +4516,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4563,7 +4566,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4613,7 +4616,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4663,7 +4666,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4713,7 +4716,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4763,7 +4766,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4813,7 +4816,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4863,7 +4866,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4913,7 +4916,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4963,7 +4966,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5013,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5063,7 +5066,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5113,7 +5116,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5163,7 +5166,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5213,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5263,7 +5266,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5313,7 +5316,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5363,7 +5366,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5413,7 +5416,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5463,7 +5466,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5513,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5563,7 +5566,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5613,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5663,7 +5666,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5713,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5763,7 +5766,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5813,7 +5816,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5863,7 +5866,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5913,7 +5916,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5963,7 +5966,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6013,7 +6016,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6063,7 +6066,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6113,7 +6116,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6163,7 +6166,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6213,7 +6216,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6263,7 +6266,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6313,7 +6316,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6363,7 +6366,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6413,7 +6416,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6463,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6513,7 +6516,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6563,7 +6566,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6613,7 +6616,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6663,7 +6666,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6713,7 +6716,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6763,7 +6766,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6813,7 +6816,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6863,7 +6866,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6913,7 +6916,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6963,7 +6966,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7013,7 +7016,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7063,7 +7066,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7113,7 +7116,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7163,7 +7166,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7213,7 +7216,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7263,7 +7266,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7313,7 +7316,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7363,7 +7366,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7413,7 +7416,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7463,7 +7466,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7513,7 +7516,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7563,7 +7566,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7613,7 +7616,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7663,7 +7666,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7713,7 +7716,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7763,7 +7766,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7813,7 +7816,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7863,7 +7866,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7913,7 +7916,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7963,7 +7966,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8013,7 +8016,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8063,7 +8066,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8113,7 +8116,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8163,7 +8166,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8213,7 +8216,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8263,7 +8266,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8313,7 +8316,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8363,7 +8366,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8413,7 +8416,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8463,7 +8466,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8513,7 +8516,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8563,7 +8566,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8613,7 +8616,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8663,7 +8666,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8713,7 +8716,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8763,7 +8766,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8913,7 +8916,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8963,7 +8966,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9013,7 +9016,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9063,7 +9066,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9113,7 +9116,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9163,7 +9166,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9213,7 +9216,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9263,7 +9266,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9313,7 +9316,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9363,7 +9366,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9413,7 +9416,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9463,7 +9466,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9513,7 +9516,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9563,7 +9566,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9763,7 +9766,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9813,7 +9816,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9863,7 +9866,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9913,7 +9916,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9963,7 +9966,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10013,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10063,7 +10066,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10113,7 +10116,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10163,7 +10166,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10213,7 +10216,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10263,7 +10266,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10313,7 +10316,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10363,7 +10366,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10413,7 +10416,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10463,7 +10466,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10513,7 +10516,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10563,7 +10566,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10613,7 +10616,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10663,7 +10666,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10713,7 +10716,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10763,7 +10766,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10813,7 +10816,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10863,7 +10866,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10913,7 +10916,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10963,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11013,7 +11016,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11063,7 +11066,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11113,7 +11116,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11413,7 +11416,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11463,7 +11466,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11613,7 +11616,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11663,7 +11666,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -12063,7 +12066,7 @@
         <v>1</v>
       </c>
       <c r="P209" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -12113,7 +12116,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12163,7 +12166,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12213,7 +12216,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12263,7 +12266,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12313,7 +12316,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12363,7 +12366,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12413,7 +12416,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12463,7 +12466,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12513,7 +12516,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12563,7 +12566,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12613,7 +12616,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12663,7 +12666,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12713,7 +12716,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -13163,7 +13166,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13213,7 +13216,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13263,7 +13266,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13463,7 +13466,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13513,7 +13516,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13563,7 +13566,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13613,7 +13616,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13663,7 +13666,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13713,7 +13716,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13763,7 +13766,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13813,7 +13816,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13863,7 +13866,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13913,7 +13916,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13963,7 +13966,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14013,7 +14016,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14063,7 +14066,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14113,7 +14116,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14163,7 +14166,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14213,7 +14216,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14263,7 +14266,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14313,7 +14316,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14363,7 +14366,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14413,7 +14416,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14463,7 +14466,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14513,7 +14516,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14563,7 +14566,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14613,7 +14616,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14663,7 +14666,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14713,7 +14716,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14763,7 +14766,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14813,7 +14816,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14863,7 +14866,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14913,7 +14916,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14963,7 +14966,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15013,7 +15016,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15063,7 +15066,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15113,7 +15116,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15163,7 +15166,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15213,7 +15216,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15263,7 +15266,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15313,7 +15316,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15363,7 +15366,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15413,7 +15416,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15463,7 +15466,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15513,7 +15516,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15563,7 +15566,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15613,7 +15616,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15663,7 +15666,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15713,7 +15716,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15763,7 +15766,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15813,7 +15816,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15863,7 +15866,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15913,7 +15916,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15963,7 +15966,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16013,7 +16016,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16063,7 +16066,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16113,7 +16116,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16163,7 +16166,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16363,7 +16366,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16413,7 +16416,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16463,7 +16466,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16513,7 +16516,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16563,7 +16566,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16613,7 +16616,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16663,7 +16666,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16713,7 +16716,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16763,7 +16766,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16813,7 +16816,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16863,7 +16866,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16913,7 +16916,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16963,7 +16966,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17013,7 +17016,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17063,7 +17066,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17113,7 +17116,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17163,7 +17166,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17213,7 +17216,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17263,7 +17266,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17313,7 +17316,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17363,7 +17366,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17413,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17463,7 +17466,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17513,7 +17516,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17563,7 +17566,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17613,7 +17616,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17663,7 +17666,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17713,7 +17716,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17763,7 +17766,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17813,7 +17816,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17863,7 +17866,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17913,7 +17916,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17963,7 +17966,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18013,7 +18016,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18063,7 +18066,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18113,7 +18116,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18163,7 +18166,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18213,7 +18216,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18263,7 +18266,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18313,7 +18316,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18363,7 +18366,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18413,7 +18416,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18463,7 +18466,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18513,7 +18516,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18563,7 +18566,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18613,7 +18616,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18663,7 +18666,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18713,7 +18716,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18763,7 +18766,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18813,7 +18816,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18863,7 +18866,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18913,7 +18916,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18963,7 +18966,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19013,7 +19016,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19063,7 +19066,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19113,7 +19116,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19163,7 +19166,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19363,7 +19366,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19413,7 +19416,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19463,7 +19466,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19513,7 +19516,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19563,7 +19566,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19613,7 +19616,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19663,7 +19666,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19713,7 +19716,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19863,7 +19866,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19913,7 +19916,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19963,7 +19966,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20013,7 +20016,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20063,7 +20066,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20113,7 +20116,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20163,7 +20166,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20213,7 +20216,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20263,7 +20266,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20313,7 +20316,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20363,7 +20366,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20413,7 +20416,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20463,7 +20466,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20513,7 +20516,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20563,7 +20566,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20613,7 +20616,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20663,7 +20666,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20713,7 +20716,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20763,7 +20766,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20813,7 +20816,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20863,7 +20866,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20913,7 +20916,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20963,7 +20966,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21013,7 +21016,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21063,7 +21066,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21113,7 +21116,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21163,7 +21166,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21213,7 +21216,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21263,7 +21266,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21313,7 +21316,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21363,7 +21366,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21413,7 +21416,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21463,7 +21466,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21513,7 +21516,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21563,7 +21566,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21613,7 +21616,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21663,7 +21666,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21713,7 +21716,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21763,7 +21766,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21813,7 +21816,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21863,7 +21866,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21913,7 +21916,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21963,7 +21966,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22013,7 +22016,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22063,7 +22066,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22113,7 +22116,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22163,7 +22166,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22213,7 +22216,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22263,7 +22266,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22313,7 +22316,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22363,7 +22366,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22413,7 +22416,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22463,7 +22466,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22513,7 +22516,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22563,7 +22566,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22613,7 +22616,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22663,7 +22666,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22713,7 +22716,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22763,7 +22766,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22813,7 +22816,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22863,7 +22866,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22913,7 +22916,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22963,7 +22966,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23013,7 +23016,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23063,7 +23066,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23113,7 +23116,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23163,7 +23166,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23213,7 +23216,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23263,7 +23266,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23313,7 +23316,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23363,7 +23366,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23413,7 +23416,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23513,7 +23516,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23563,7 +23566,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -23613,7 +23616,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23663,7 +23666,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -23713,7 +23716,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23763,7 +23766,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23813,7 +23816,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23863,7 +23866,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23913,7 +23916,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23963,7 +23966,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24013,7 +24016,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24063,7 +24066,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24113,7 +24116,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24163,7 +24166,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24213,7 +24216,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24263,7 +24266,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24313,7 +24316,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24363,7 +24366,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24413,7 +24416,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24463,7 +24466,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24513,7 +24516,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24563,7 +24566,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24763,7 +24766,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24813,7 +24816,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24863,7 +24866,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24963,7 +24966,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25063,7 +25066,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25113,7 +25116,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25163,7 +25166,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25213,7 +25216,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25263,7 +25266,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25313,7 +25316,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25463,7 +25466,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25563,7 +25566,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25613,7 +25616,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25663,7 +25666,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25713,7 +25716,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25763,7 +25766,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25813,7 +25816,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25863,7 +25866,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25913,7 +25916,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26063,7 +26066,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26113,7 +26116,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26163,7 +26166,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26363,7 +26366,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26413,7 +26416,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26463,7 +26466,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26513,7 +26516,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26563,7 +26566,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26613,7 +26616,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26663,7 +26666,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26713,7 +26716,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26763,7 +26766,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27113,7 +27116,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27163,7 +27166,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27213,7 +27216,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27263,7 +27266,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27313,7 +27316,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27363,7 +27366,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27413,7 +27416,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27463,7 +27466,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27513,7 +27516,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27563,7 +27566,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27613,7 +27616,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27663,7 +27666,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27713,7 +27716,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27763,7 +27766,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27813,7 +27816,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27863,7 +27866,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27913,7 +27916,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27963,7 +27966,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28013,7 +28016,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28063,7 +28066,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28113,7 +28116,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28163,7 +28166,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28213,7 +28216,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28263,7 +28266,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28313,7 +28316,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28363,7 +28366,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28413,7 +28416,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -28463,7 +28466,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -28513,7 +28516,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -28563,7 +28566,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -28613,7 +28616,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -28663,7 +28666,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -28713,7 +28716,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -28727,10 +28730,10 @@
         <v>4.212040637078079</v>
       </c>
       <c r="D543" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E543">
-        <v>5.766958685489474</v>
+        <v>5.839454132623437</v>
       </c>
       <c r="F543">
         <v>1</v>
@@ -28739,10 +28742,10 @@
         <v>0.05296795936292192</v>
       </c>
       <c r="H543">
-        <v>0.05587304131451053</v>
+        <v>0.05602054586737656</v>
       </c>
       <c r="I543">
-        <v>1.554918048411395</v>
+        <v>1.627413495545358</v>
       </c>
       <c r="J543">
         <v>1.875227643301686</v>
@@ -28754,16 +28757,16 @@
         <v>28.59</v>
       </c>
       <c r="M543">
-        <v>13.36</v>
+        <v>13.38</v>
       </c>
       <c r="N543">
-        <v>30.82</v>
+        <v>30.93</v>
       </c>
       <c r="O543">
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -28777,7 +28780,7 @@
         <v>3.699818204723471</v>
       </c>
       <c r="D544" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E544">
         <v>5.615918345535061</v>
@@ -28813,7 +28816,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="418">
   <si>
     <t>trade_time</t>
   </si>
@@ -301,6 +301,9 @@
     <t>2021-08-30</t>
   </si>
   <si>
+    <t>2021-10-18</t>
+  </si>
+  <si>
     <t>2016-11-11</t>
   </si>
   <si>
@@ -643,6 +646,9 @@
     <t>2021-09-07</t>
   </si>
   <si>
+    <t>2021-10-19</t>
+  </si>
+  <si>
     <t>2016-04-05</t>
   </si>
   <si>
@@ -1250,6 +1256,18 @@
   </si>
   <si>
     <t>2021-08-27</t>
+  </si>
+  <si>
+    <t>2021-08-31</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>2021-09-06</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
   </si>
 </sst>
 </file>
@@ -1607,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P523"/>
+  <dimension ref="A1:P530"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1668,7 +1686,7 @@
         <v>1.980046625394046</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2">
         <v>4.596593277573533</v>
@@ -1704,7 +1722,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1718,7 +1736,7 @@
         <v>1.476168338596821</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E3">
         <v>4.596593277573533</v>
@@ -1754,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1768,7 +1786,7 @@
         <v>2.113316346177388</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E4">
         <v>4.596593277573533</v>
@@ -1804,7 +1822,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1818,7 +1836,7 @@
         <v>2.095559772582941</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E5">
         <v>4.596593277573533</v>
@@ -1854,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1868,7 +1886,7 @@
         <v>2.137194632974616</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E6">
         <v>4.596593277573533</v>
@@ -1904,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1918,7 +1936,7 @@
         <v>2.167194632974617</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E7">
         <v>4.596593277573533</v>
@@ -1954,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1968,7 +1986,7 @@
         <v>2.844772647031224</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E8">
         <v>5.373230386726174</v>
@@ -2004,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2018,7 +2036,7 @@
         <v>2.344935136036042</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E9">
         <v>5.373230386726174</v>
@@ -2054,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2068,7 +2086,7 @@
         <v>2.953797713002309</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>5.373230386726174</v>
@@ -2104,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2118,7 +2136,7 @@
         <v>2.944122691011945</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E11">
         <v>5.373230386726174</v>
@@ -2154,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2168,7 +2186,7 @@
         <v>2.973635223997491</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12">
         <v>5.373230386726174</v>
@@ -2204,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2218,7 +2236,7 @@
         <v>3.003635223997492</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E13">
         <v>5.373230386726174</v>
@@ -2254,7 +2272,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2268,7 +2286,7 @@
         <v>7.289203935514355</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E14">
         <v>5.128184916132415</v>
@@ -2304,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2318,7 +2336,7 @@
         <v>-2.117497474419014</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E15">
         <v>0.8991929718719938</v>
@@ -2354,7 +2372,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2368,7 +2386,7 @@
         <v>-2.80975033090947</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16">
         <v>0.2758434229577951</v>
@@ -2404,7 +2422,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2418,7 +2436,7 @@
         <v>-2.902998496046035</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E17">
         <v>0.1918767030952893</v>
@@ -2454,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2468,7 +2486,7 @@
         <v>-2.830339867902396</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E18">
         <v>0.2573032631353307</v>
@@ -2504,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2518,7 +2536,7 @@
         <v>-2.537341046304341</v>
       </c>
       <c r="D19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E19">
         <v>0.5211384810952531</v>
@@ -2554,7 +2572,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2568,7 +2586,7 @@
         <v>-2.336644974997025</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E20">
         <v>0.7018582922817487</v>
@@ -2604,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2618,7 +2636,7 @@
         <v>-2.249226521683095</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E21">
         <v>0.7018582922817487</v>
@@ -2654,7 +2672,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2668,7 +2686,7 @@
         <v>-1.845740644766149</v>
       </c>
       <c r="D22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E22">
         <v>1.143900517084994</v>
@@ -2704,7 +2722,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2718,7 +2736,7 @@
         <v>-1.76174710538406</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E23">
         <v>1.143900517084994</v>
@@ -2754,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2804,7 +2822,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2818,7 +2836,7 @@
         <v>-1.483754394543759</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E25">
         <v>1.469856507982922</v>
@@ -2854,7 +2872,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2868,7 +2886,7 @@
         <v>-1.402286340628343</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E26">
         <v>1.469856507982922</v>
@@ -2904,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2954,7 +2972,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2968,7 +2986,7 @@
         <v>-1.119201343261796</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E28">
         <v>1.798123813695423</v>
@@ -3004,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3018,7 +3036,7 @@
         <v>-1.040276682727416</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E29">
         <v>1.798123813695423</v>
@@ -3054,7 +3072,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3068,7 +3086,7 @@
         <v>-0.970418309242234</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E30">
         <v>-1.315795006570312</v>
@@ -3104,7 +3122,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3118,7 +3136,7 @@
         <v>-1.094604783790125</v>
       </c>
       <c r="D31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>1.627274602785022</v>
@@ -3154,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3168,7 +3186,7 @@
         <v>-1.015851727159035</v>
       </c>
       <c r="D32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>1.627274602785022</v>
@@ -3204,7 +3222,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3218,7 +3236,7 @@
         <v>-1.190513514023774</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E33">
         <v>-1.147995174237213</v>
@@ -3254,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3268,7 +3286,7 @@
         <v>-1.15006863091817</v>
       </c>
       <c r="D34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>1.577640908889972</v>
@@ -3304,7 +3322,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3318,7 +3336,7 @@
         <v>-1.255522302285485</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E35">
         <v>-0.5624021926528435</v>
@@ -3354,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3368,7 +3386,7 @@
         <v>-1.320960230949986</v>
       </c>
       <c r="D36" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>1.424712797977779</v>
@@ -3404,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3418,7 +3436,7 @@
         <v>-1.455823154415796</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E37">
         <v>-0.3493885347260317</v>
@@ -3454,7 +3472,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3468,7 +3486,7 @@
         <v>-1.605480846937454</v>
       </c>
       <c r="D38" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E38">
         <v>-0.7894370781288025</v>
@@ -3504,7 +3522,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3518,7 +3536,7 @@
         <v>-1.761773123733541</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E39">
         <v>-1.128596969277446</v>
@@ -3554,7 +3572,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3568,7 +3586,7 @@
         <v>-1.457944364792599</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E40">
         <v>-0.8017368070151889</v>
@@ -3604,7 +3622,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3618,7 +3636,7 @@
         <v>-1.234076514305805</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E41">
         <v>0.01703472753200685</v>
@@ -3654,7 +3672,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3668,7 +3686,7 @@
         <v>-0.7963224235233177</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E42">
         <v>0.2870665855800212</v>
@@ -3704,7 +3722,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3718,7 +3736,7 @@
         <v>-0.8942517780380754</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E43">
         <v>0.59890656545236</v>
@@ -3754,7 +3772,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3768,7 +3786,7 @@
         <v>-0.899307304101125</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E44">
         <v>0.6876116265245429</v>
@@ -3804,7 +3822,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3818,7 +3836,7 @@
         <v>-0.8589383918075626</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E45">
         <v>0.8335609313842731</v>
@@ -3854,7 +3872,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3868,7 +3886,7 @@
         <v>-0.6533981903373771</v>
       </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E46">
         <v>1.169788560028703</v>
@@ -3904,7 +3922,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3918,7 +3936,7 @@
         <v>4.835153534210221</v>
       </c>
       <c r="D47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E47">
         <v>2.04429947322755</v>
@@ -3954,7 +3972,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3968,7 +3986,7 @@
         <v>-0.406918334342155</v>
       </c>
       <c r="D48" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E48">
         <v>1.312995819177061</v>
@@ -4004,7 +4022,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4018,7 +4036,7 @@
         <v>0.04130730968482865</v>
       </c>
       <c r="D49" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E49">
         <v>2.64378384364354</v>
@@ -4054,7 +4072,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4068,7 +4086,7 @@
         <v>5.033791575296075</v>
       </c>
       <c r="D50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E50">
         <v>2.275021568455536</v>
@@ -4104,7 +4122,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4118,7 +4136,7 @@
         <v>-0.1691188742298735</v>
       </c>
       <c r="D51" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E51">
         <v>1.79275039480164</v>
@@ -4154,7 +4172,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4168,7 +4186,7 @@
         <v>0.2293541709380591</v>
       </c>
       <c r="D52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E52">
         <v>2.812063918551083</v>
@@ -4204,7 +4222,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4218,7 +4236,7 @@
         <v>5.217902572011447</v>
       </c>
       <c r="D53" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E53">
         <v>2.488870208345837</v>
@@ -4254,7 +4272,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4268,7 +4286,7 @@
         <v>0.0512895398901918</v>
       </c>
       <c r="D54" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E54">
         <v>1.57274123510015</v>
@@ -4304,7 +4322,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4318,7 +4336,7 @@
         <v>0.3237189931323456</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E55">
         <v>2.896509461761223</v>
@@ -4354,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4368,7 +4386,7 @@
         <v>5.3102923165319</v>
       </c>
       <c r="D56" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E56">
         <v>2.596182761957483</v>
@@ -4404,7 +4422,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4418,7 +4436,7 @@
         <v>0.161893889624892</v>
       </c>
       <c r="D57" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E57">
         <v>1.501333830022219</v>
@@ -4454,7 +4472,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4468,7 +4486,7 @@
         <v>5.33023415169577</v>
       </c>
       <c r="D58" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E58">
         <v>2.619345606126444</v>
@@ -4504,7 +4522,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4518,7 +4536,7 @@
         <v>0.1857672504861512</v>
       </c>
       <c r="D59" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E59">
         <v>1.155646098159064</v>
@@ -4554,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4568,7 +4586,7 @@
         <v>5.37850629613547</v>
       </c>
       <c r="D60" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E60">
         <v>2.675414676508897</v>
@@ -4604,7 +4622,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4618,7 +4636,7 @@
         <v>0.243556231003037</v>
       </c>
       <c r="D61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E61">
         <v>1.799674337820232</v>
@@ -4654,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4668,7 +4686,7 @@
         <v>5.505970450595548</v>
       </c>
       <c r="D62" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E62">
         <v>2.823466865418581</v>
@@ -4704,7 +4722,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4718,7 +4736,7 @@
         <v>0.3961498981001377</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E63">
         <v>1.846556155176511</v>
@@ -4754,7 +4772,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4768,7 +4786,7 @@
         <v>5.552898822755296</v>
       </c>
       <c r="D64" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E64">
         <v>2.877975117167079</v>
@@ -4804,7 +4822,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4818,7 +4836,7 @@
         <v>0.4523301821108561</v>
       </c>
       <c r="D65" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E65">
         <v>2.714577056552891</v>
@@ -4854,7 +4872,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4868,7 +4886,7 @@
         <v>0.844003460842476</v>
       </c>
       <c r="D66" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E66">
         <v>3.182739844457025</v>
@@ -4904,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4918,7 +4936,7 @@
         <v>5.819687109336471</v>
       </c>
       <c r="D67" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E67">
         <v>2.897855098492958</v>
@@ -4954,7 +4972,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4968,7 +4986,7 @@
         <v>0.7717156843363</v>
       </c>
       <c r="D68" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E68">
         <v>3.232403806926722</v>
@@ -5004,7 +5022,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5018,7 +5036,7 @@
         <v>2.174557955758587</v>
       </c>
       <c r="D69" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E69">
         <v>4.552795119478848</v>
@@ -5054,7 +5072,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5068,7 +5086,7 @@
         <v>2.230502900253292</v>
       </c>
       <c r="D70" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E70">
         <v>4.552795119478848</v>
@@ -5104,7 +5122,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5118,7 +5136,7 @@
         <v>7.122392789242706</v>
       </c>
       <c r="D71" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E71">
         <v>4.410974047362672</v>
@@ -5154,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5168,7 +5186,7 @@
         <v>3.377229031968387</v>
       </c>
       <c r="D72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E72">
         <v>5.847002514367812</v>
@@ -5204,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5218,7 +5236,7 @@
         <v>3.424783248024418</v>
       </c>
       <c r="D73" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E73">
         <v>5.847002514367812</v>
@@ -5254,7 +5272,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5268,7 +5286,7 @@
         <v>8.29989168013649</v>
       </c>
       <c r="D74" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E74">
         <v>5.631180854885052</v>
@@ -5304,7 +5322,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5318,7 +5336,7 @@
         <v>4.683694888843547</v>
       </c>
       <c r="D75" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E75">
         <v>7.023429444093537</v>
@@ -5354,7 +5372,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5368,7 +5386,7 @@
         <v>4.722134226828356</v>
       </c>
       <c r="D76" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E76">
         <v>7.023429444093537</v>
@@ -5404,7 +5422,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5418,7 +5436,7 @@
         <v>9.579012902797984</v>
       </c>
       <c r="D77" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E77">
         <v>6.893347467132109</v>
@@ -5454,7 +5472,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5468,7 +5486,7 @@
         <v>3.961474621504259</v>
       </c>
       <c r="D78" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E78">
         <v>6.476706188649629</v>
@@ -5504,7 +5522,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5518,7 +5536,7 @@
         <v>8.320444610292363</v>
       </c>
       <c r="D79" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E79">
         <v>7.021567248362409</v>
@@ -5554,7 +5572,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5568,7 +5586,7 @@
         <v>8.530866989040167</v>
       </c>
       <c r="D80" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E80">
         <v>7.021567248362409</v>
@@ -5604,7 +5622,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5618,7 +5636,7 @@
         <v>3.2890165208482</v>
       </c>
       <c r="D81" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E81">
         <v>5.857937357507026</v>
@@ -5654,7 +5672,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5668,7 +5686,7 @@
         <v>7.698991315674085</v>
       </c>
       <c r="D82" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E82">
         <v>6.277165792762322</v>
@@ -5704,7 +5722,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5718,7 +5736,7 @@
         <v>7.862435583597616</v>
       </c>
       <c r="D83" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E83">
         <v>6.277165792762322</v>
@@ -5754,7 +5772,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5768,7 +5786,7 @@
         <v>2.706415003086228</v>
       </c>
       <c r="D84" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E84">
         <v>5.321850930983533</v>
@@ -5804,7 +5822,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5818,7 +5836,7 @@
         <v>7.160579134588669</v>
       </c>
       <c r="D85" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E85">
         <v>5.783497068837448</v>
@@ -5854,7 +5872,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5868,7 +5886,7 @@
         <v>7.283322697678528</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E86">
         <v>5.783497068837448</v>
@@ -5904,7 +5922,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5918,7 +5936,7 @@
         <v>2.25250194719996</v>
       </c>
       <c r="D87" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E87">
         <v>4.90417843844148</v>
@@ -5954,7 +5972,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5968,7 +5986,7 @@
         <v>6.741094613879405</v>
       </c>
       <c r="D88" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E88">
         <v>5.766049754225914</v>
@@ -6004,7 +6022,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6018,7 +6036,7 @@
         <v>6.83212768404308</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E89">
         <v>5.766049754225914</v>
@@ -6054,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6068,7 +6086,7 @@
         <v>1.648635956687475</v>
       </c>
       <c r="D90" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E90">
         <v>4.348525301462924</v>
@@ -6104,7 +6122,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6118,7 +6136,7 @@
         <v>6.183030834224155</v>
       </c>
       <c r="D91" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E91">
         <v>5.350064030791522</v>
@@ -6154,7 +6172,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6168,7 +6186,7 @@
         <v>6.231877657545638</v>
       </c>
       <c r="D92" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E92">
         <v>5.350064030791522</v>
@@ -6204,7 +6222,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6218,7 +6236,7 @@
         <v>1.432518806234409</v>
       </c>
       <c r="D93" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E93">
         <v>4.149663013321483</v>
@@ -6254,7 +6272,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6268,7 +6286,7 @@
         <v>5.983305802967131</v>
       </c>
       <c r="D94" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E94">
         <v>4.577912304600769</v>
@@ -6304,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6318,7 +6336,7 @@
         <v>6.017054621765944</v>
       </c>
       <c r="D95" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E95">
         <v>4.577912304600769</v>
@@ -6354,7 +6372,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6368,7 +6386,7 @@
         <v>1.226728012835469</v>
       </c>
       <c r="D96" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E96">
         <v>3.960302622589126</v>
@@ -6404,7 +6422,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6418,7 +6436,7 @@
         <v>5.793123892101445</v>
       </c>
       <c r="D97" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E97">
         <v>4.612872778687663</v>
@@ -6454,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6468,7 +6486,7 @@
         <v>5.812496108566997</v>
       </c>
       <c r="D98" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E98">
         <v>4.612872778687663</v>
@@ -6504,7 +6522,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6518,7 +6536,7 @@
         <v>1.216947853386511</v>
       </c>
       <c r="D99" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E99">
         <v>3.951303314193975</v>
@@ -6554,7 +6572,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6568,7 +6586,7 @@
         <v>5.802774512947074</v>
       </c>
       <c r="D100" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E100">
         <v>4.403561129870987</v>
@@ -6604,7 +6622,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6618,7 +6636,7 @@
         <v>1.177523163430447</v>
       </c>
       <c r="D101" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E101">
         <v>3.915026304074722</v>
@@ -6654,7 +6672,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6668,7 +6686,7 @@
         <v>5.763585898978771</v>
       </c>
       <c r="D102" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E102">
         <v>4.466025047817013</v>
@@ -6704,7 +6722,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6718,7 +6736,7 @@
         <v>0.9680478903759173</v>
       </c>
       <c r="D103" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E103">
         <v>3.722275603719158</v>
@@ -6754,7 +6772,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6768,7 +6786,7 @@
         <v>0.8515262832029507</v>
       </c>
       <c r="D104" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E104">
         <v>3.61505711887537</v>
@@ -6804,7 +6822,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6818,7 +6836,7 @@
         <v>0.6675490824101864</v>
       </c>
       <c r="D105" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E105">
         <v>3.445768716549093</v>
@@ -6854,7 +6872,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6868,7 +6886,7 @@
         <v>0.2453647773980379</v>
       </c>
       <c r="D106" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E106">
         <v>3.057291741278434</v>
@@ -6904,7 +6922,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6918,7 +6936,7 @@
         <v>-0.1442597189068877</v>
       </c>
       <c r="D107" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E107">
         <v>2.69877498918947</v>
@@ -6954,7 +6972,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6968,7 +6986,7 @@
         <v>3.671796227407118</v>
       </c>
       <c r="D108" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E108">
         <v>1.089748757437874</v>
@@ -7004,7 +7022,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7018,7 +7036,7 @@
         <v>-1.239097601114093</v>
       </c>
       <c r="D109" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E109">
         <v>1.261882831716061</v>
@@ -7054,7 +7072,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7068,7 +7086,7 @@
         <v>3.066548753992304</v>
       </c>
       <c r="D110" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E110">
         <v>0.4140568037443764</v>
@@ -7104,7 +7122,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7118,7 +7136,7 @@
         <v>-1.959356470902271</v>
       </c>
       <c r="D111" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E111">
         <v>0.6034425874785647</v>
@@ -7154,7 +7172,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7168,7 +7186,7 @@
         <v>2.434653904799742</v>
       </c>
       <c r="D112" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E112">
         <v>-0.2913840017675113</v>
@@ -7204,7 +7222,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7218,7 +7236,7 @@
         <v>-2.711326350820261</v>
       </c>
       <c r="D113" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E113">
         <v>-0.08398696342450762</v>
@@ -7254,7 +7272,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7268,7 +7286,7 @@
         <v>2.046949385277987</v>
       </c>
       <c r="D114" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E114">
         <v>-0.7242132753428656</v>
@@ -7304,7 +7322,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7318,7 +7336,7 @@
         <v>-3.172703938184629</v>
       </c>
       <c r="D115" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E115">
         <v>-0.5057652768234711</v>
@@ -7354,7 +7372,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7368,7 +7386,7 @@
         <v>1.727381390460117</v>
       </c>
       <c r="D116" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E116">
         <v>0.5925973930511788</v>
@@ -7404,7 +7422,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7418,7 +7436,7 @@
         <v>1.685047495782005</v>
       </c>
       <c r="D117" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E117">
         <v>-1.128236762428639</v>
@@ -7454,7 +7472,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7468,7 +7486,7 @@
         <v>-3.603375782929252</v>
       </c>
       <c r="D118" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E118">
         <v>-0.8994732706219501</v>
@@ -7504,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7518,7 +7536,7 @@
         <v>1.329375274458599</v>
       </c>
       <c r="D119" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E119">
         <v>-0.02169112718700106</v>
@@ -7554,7 +7572,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7568,7 +7586,7 @@
         <v>1.370767088004978</v>
       </c>
       <c r="D120" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E120">
         <v>-1.479096125030072</v>
@@ -7604,7 +7622,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7618,7 +7636,7 @@
         <v>-3.977376933276734</v>
       </c>
       <c r="D121" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E121">
         <v>-1.241374521837809</v>
@@ -7654,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7668,7 +7686,7 @@
         <v>0.9837414768320834</v>
       </c>
       <c r="D122" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E122">
         <v>-0.5624929319466254</v>
@@ -7704,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7718,7 +7736,7 @@
         <v>-4.274892307557078</v>
       </c>
       <c r="D123" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E123">
         <v>-1.513354644433413</v>
@@ -7768,7 +7786,7 @@
         <v>0.7087921389242986</v>
       </c>
       <c r="D124" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E124">
         <v>-0.01219137097330147</v>
@@ -7818,7 +7836,7 @@
         <v>-6.600419867221269</v>
       </c>
       <c r="D125" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E125">
         <v>-3.935750603200287</v>
@@ -7854,7 +7872,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7868,7 +7886,7 @@
         <v>-1.740049190571469</v>
       </c>
       <c r="D126" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E126">
         <v>-3.803035064283293</v>
@@ -7904,7 +7922,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7918,7 +7936,7 @@
         <v>-7.356943655480499</v>
       </c>
       <c r="D127" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E127">
         <v>-4.634314907681588</v>
@@ -7954,7 +7972,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7968,7 +7986,7 @@
         <v>-2.446239742918287</v>
       </c>
       <c r="D128" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E128">
         <v>-3.284642996427294</v>
@@ -8004,7 +8022,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8018,7 +8036,7 @@
         <v>-2.764549545202325</v>
       </c>
       <c r="D129" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E129">
         <v>-3.284642996427294</v>
@@ -8054,7 +8072,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8068,7 +8086,7 @@
         <v>-8.273062059554213</v>
       </c>
       <c r="D130" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E130">
         <v>-5.480246821120623</v>
@@ -8104,7 +8122,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8118,7 +8136,7 @@
         <v>-3.301406720914517</v>
       </c>
       <c r="D131" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E131">
         <v>-3.80770165872979</v>
@@ -8154,7 +8172,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8168,7 +8186,7 @@
         <v>-3.640798600667189</v>
       </c>
       <c r="D132" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E132">
         <v>-3.80770165872979</v>
@@ -8204,7 +8222,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8218,7 +8236,7 @@
         <v>-9.028638086965721</v>
       </c>
       <c r="D133" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E133">
         <v>-6.177935975464312</v>
@@ -8254,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8268,7 +8286,7 @@
         <v>-4.006712569082914</v>
       </c>
       <c r="D134" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E134">
         <v>-5.764446572941544</v>
@@ -8304,7 +8322,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8318,7 +8336,7 @@
         <v>-4.355244481425245</v>
       </c>
       <c r="D135" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E135">
         <v>-5.764446572941544</v>
@@ -8354,7 +8372,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8368,7 +8386,7 @@
         <v>-9.288472736223071</v>
       </c>
       <c r="D136" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E136">
         <v>-6.4178639378834</v>
@@ -8404,7 +8422,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8418,7 +8436,7 @@
         <v>-4.249259832401776</v>
       </c>
       <c r="D137" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E137">
         <v>-5.572990039214197</v>
@@ -8454,7 +8472,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8468,7 +8486,7 @@
         <v>-4.600934905823827</v>
       </c>
       <c r="D138" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E138">
         <v>-5.572990039214197</v>
@@ -8504,7 +8522,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8518,7 +8536,7 @@
         <v>-8.391360480599353</v>
       </c>
       <c r="D139" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E139">
         <v>-5.589482056682467</v>
@@ -8554,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8568,7 +8586,7 @@
         <v>-3.41183448088206</v>
       </c>
       <c r="D140" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E140">
         <v>-4.236414237755341</v>
@@ -8604,7 +8622,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8618,7 +8636,7 @@
         <v>-3.752657389921566</v>
       </c>
       <c r="D141" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E141">
         <v>-4.236414237755341</v>
@@ -8654,7 +8672,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8668,7 +8686,7 @@
         <v>-7.284701623181299</v>
       </c>
       <c r="D142" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E142">
         <v>-4.567607547211761</v>
@@ -8704,7 +8722,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8718,7 +8736,7 @@
         <v>-2.378804136155122</v>
       </c>
       <c r="D143" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E143">
         <v>-3.182992288094191</v>
@@ -8754,7 +8772,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8804,7 +8822,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8854,7 +8872,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8868,7 +8886,7 @@
         <v>15.30025538505301</v>
       </c>
       <c r="D146" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E146">
         <v>12.2194473505381</v>
@@ -8904,7 +8922,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8918,7 +8936,7 @@
         <v>16.08154605938966</v>
       </c>
       <c r="D147" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E147">
         <v>12.2194473505381</v>
@@ -8954,7 +8972,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9004,7 +9022,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9054,7 +9072,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9104,7 +9122,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9154,7 +9172,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9204,7 +9222,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9254,7 +9272,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9304,7 +9322,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9354,7 +9372,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9404,7 +9422,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9454,7 +9472,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9468,7 +9486,7 @@
         <v>-2.965774048910724</v>
       </c>
       <c r="D158" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E158">
         <v>-6.323583762599906</v>
@@ -9504,7 +9522,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9518,7 +9536,7 @@
         <v>-3.841273412039687</v>
       </c>
       <c r="D159" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E159">
         <v>-6.323583762599906</v>
@@ -9554,7 +9572,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9604,7 +9622,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9618,7 +9636,7 @@
         <v>-4.596644143057084</v>
       </c>
       <c r="D161" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E161">
         <v>-7.87451662725034</v>
@@ -9654,7 +9672,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9668,7 +9686,7 @@
         <v>-5.499155847289916</v>
       </c>
       <c r="D162" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E162">
         <v>-7.87451662725034</v>
@@ -9704,7 +9722,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9754,7 +9772,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9768,7 +9786,7 @@
         <v>-6.176260919928573</v>
       </c>
       <c r="D164" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E164">
         <v>-9.588220956609884</v>
@@ -9804,7 +9822,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9818,7 +9836,7 @@
         <v>-7.104936049037125</v>
       </c>
       <c r="D165" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E165">
         <v>-9.588220956609884</v>
@@ -9854,7 +9872,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9904,7 +9922,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9954,7 +9972,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9968,7 +9986,7 @@
         <v>-5.957065888688689</v>
       </c>
       <c r="D168" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E168">
         <v>-9.35041930781134</v>
@@ -10004,7 +10022,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10018,7 +10036,7 @@
         <v>-6.882110458273605</v>
       </c>
       <c r="D169" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E169">
         <v>-9.35041930781134</v>
@@ -10054,7 +10072,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10068,7 +10086,7 @@
         <v>-5.75373473480284</v>
       </c>
       <c r="D170" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E170">
         <v>-9.129828159496252</v>
@@ -10118,7 +10136,7 @@
         <v>-6.675411500596677</v>
       </c>
       <c r="D171" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E171">
         <v>-9.129828159496252</v>
@@ -10168,7 +10186,7 @@
         <v>4.036863233290944</v>
       </c>
       <c r="D172" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E172">
         <v>1.091137151603181</v>
@@ -10218,7 +10236,7 @@
         <v>4.353212181898559</v>
       </c>
       <c r="D173" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E173">
         <v>1.091137151603181</v>
@@ -10268,7 +10286,7 @@
         <v>4.092859462531468</v>
       </c>
       <c r="D174" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E174">
         <v>1.091137151603181</v>
@@ -10354,7 +10372,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10404,7 +10422,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10554,7 +10572,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10604,7 +10622,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10654,7 +10672,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10704,7 +10722,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10754,7 +10772,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10804,7 +10822,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10854,7 +10872,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10904,7 +10922,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10954,7 +10972,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11004,7 +11022,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11054,7 +11072,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11104,7 +11122,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11154,7 +11172,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11204,7 +11222,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11254,7 +11272,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11268,7 +11286,7 @@
         <v>2.797016608461103</v>
       </c>
       <c r="D194" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E194">
         <v>-0.1302387600075896</v>
@@ -11304,7 +11322,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11318,7 +11336,7 @@
         <v>3.23804287129742</v>
       </c>
       <c r="D195" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E195">
         <v>-0.1302387600075896</v>
@@ -11354,7 +11372,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11368,7 +11386,7 @@
         <v>2.97076363447318</v>
       </c>
       <c r="D196" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E196">
         <v>-0.1302387600075896</v>
@@ -11404,7 +11422,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11418,7 +11436,7 @@
         <v>-2.735537076225839</v>
       </c>
       <c r="D197" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E197">
         <v>-0.06446785034954416</v>
@@ -11454,7 +11472,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11468,7 +11486,7 @@
         <v>2.142297248198716</v>
       </c>
       <c r="D198" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E198">
         <v>-0.7752043867837592</v>
@@ -11504,7 +11522,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11518,7 +11536,7 @@
         <v>2.649161212067007</v>
       </c>
       <c r="D199" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E199">
         <v>-0.7752043867837592</v>
@@ -11554,7 +11572,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11568,7 +11586,7 @@
         <v>1.866662847049479</v>
       </c>
       <c r="D200" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E200">
         <v>-0.7752043867837592</v>
@@ -11604,7 +11622,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11618,7 +11636,7 @@
         <v>-3.292719101626048</v>
       </c>
       <c r="D201" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E201">
         <v>-0.5316716843393898</v>
@@ -11654,7 +11672,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11668,7 +11686,7 @@
         <v>0.7343076746441</v>
       </c>
       <c r="D202" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E202">
         <v>-2.162218324233283</v>
@@ -11718,7 +11736,7 @@
         <v>1.382757182221791</v>
       </c>
       <c r="D203" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E203">
         <v>-2.162218324233283</v>
@@ -11768,7 +11786,7 @@
         <v>0.5792831810991643</v>
       </c>
       <c r="D204" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E204">
         <v>-2.162218324233283</v>
@@ -11818,7 +11836,7 @@
         <v>-4.4909523141297</v>
       </c>
       <c r="D205" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E205">
         <v>-1.797099453998044</v>
@@ -11868,7 +11886,7 @@
         <v>-0.5271433345479153</v>
       </c>
       <c r="D206" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E206">
         <v>-3.404876767180344</v>
@@ -11918,7 +11936,7 @@
         <v>0.2481559951831649</v>
       </c>
       <c r="D207" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E207">
         <v>-3.404876767180344</v>
@@ -11968,7 +11986,7 @@
         <v>-0.5741105721844058</v>
       </c>
       <c r="D208" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E208">
         <v>-3.404876767180344</v>
@@ -12018,7 +12036,7 @@
         <v>-5.289194339951301</v>
       </c>
       <c r="D209" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E209">
         <v>-2.93597803324387</v>
@@ -12068,7 +12086,7 @@
         <v>-1.521590007004434</v>
       </c>
       <c r="D210" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E210">
         <v>-4.774748703164175</v>
@@ -12104,7 +12122,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12118,7 +12136,7 @@
         <v>-2.373169137555241</v>
       </c>
       <c r="D211" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E211">
         <v>-4.774748703164175</v>
@@ -12154,7 +12172,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12168,7 +12186,7 @@
         <v>-6.960010441395497</v>
       </c>
       <c r="D212" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E212">
         <v>-4.500536093148853</v>
@@ -12204,7 +12222,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12218,7 +12236,7 @@
         <v>-2.452340392521911</v>
       </c>
       <c r="D213" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E213">
         <v>-5.548191233294997</v>
@@ -12268,7 +12286,7 @@
         <v>-2.754963624773605</v>
       </c>
       <c r="D214" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E214">
         <v>-5.548191233294997</v>
@@ -12318,7 +12336,7 @@
         <v>-7.838731302256715</v>
       </c>
       <c r="D215" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E215">
         <v>-5.323373390490392</v>
@@ -12368,7 +12386,7 @@
         <v>-4.58678078170076</v>
       </c>
       <c r="D216" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E216">
         <v>-7.667945163513835</v>
@@ -12404,7 +12422,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12418,7 +12436,7 @@
         <v>-5.270890369576151</v>
       </c>
       <c r="D217" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E217">
         <v>-7.667945163513835</v>
@@ -12454,7 +12472,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12468,7 +12486,7 @@
         <v>-4.902661407674056</v>
       </c>
       <c r="D218" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E218">
         <v>-7.667945163513835</v>
@@ -12504,7 +12522,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12518,7 +12536,7 @@
         <v>-9.853855147941093</v>
       </c>
       <c r="D219" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E219">
         <v>-7.21034243019923</v>
@@ -12554,7 +12572,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12568,7 +12586,7 @@
         <v>-5.59817458645032</v>
       </c>
       <c r="D220" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E220">
         <v>-8.513312611948162</v>
@@ -12604,7 +12622,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12618,7 +12636,7 @@
         <v>-5.920337161521442</v>
       </c>
       <c r="D221" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E221">
         <v>-8.513312611948162</v>
@@ -12654,7 +12672,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12668,7 +12686,7 @@
         <v>-10.78187598777789</v>
       </c>
       <c r="D222" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E222">
         <v>-7.189437361711093</v>
@@ -12704,7 +12722,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12718,7 +12736,7 @@
         <v>-10.80871141081024</v>
       </c>
       <c r="D223" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E223">
         <v>-8.104473185122753</v>
@@ -12754,7 +12772,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12768,7 +12786,7 @@
         <v>-5.98278744209609</v>
       </c>
       <c r="D224" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E224">
         <v>-8.914647765665489</v>
@@ -12804,7 +12822,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12818,7 +12836,7 @@
         <v>-6.30733891689172</v>
       </c>
       <c r="D225" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E225">
         <v>-8.914647765665489</v>
@@ -12854,7 +12872,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12868,7 +12886,7 @@
         <v>-11.21108163828114</v>
       </c>
       <c r="D226" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E226">
         <v>-7.582809516346728</v>
@@ -12904,7 +12922,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12918,7 +12936,7 @@
         <v>-11.09924338896238</v>
       </c>
       <c r="D227" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E227">
         <v>-7.582809516346728</v>
@@ -12954,7 +12972,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12968,7 +12986,7 @@
         <v>-11.17182416893544</v>
       </c>
       <c r="D228" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E228">
         <v>-8.444493245911037</v>
@@ -13004,7 +13022,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13018,7 +13036,7 @@
         <v>-6.197743032286496</v>
       </c>
       <c r="D229" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E229">
         <v>-9.138949251081566</v>
@@ -13054,7 +13072,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13068,7 +13086,7 @@
         <v>-6.52362963497151</v>
       </c>
       <c r="D230" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E230">
         <v>-9.138949251081566</v>
@@ -13104,7 +13122,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13118,7 +13136,7 @@
         <v>-11.45095961574</v>
       </c>
       <c r="D231" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E231">
         <v>-7.802660575464863</v>
@@ -13154,7 +13172,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13168,7 +13186,7 @@
         <v>-11.33467094012331</v>
       </c>
       <c r="D232" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E232">
         <v>-7.802660575464863</v>
@@ -13204,7 +13222,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13218,7 +13236,7 @@
         <v>-11.37476360812142</v>
       </c>
       <c r="D233" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E233">
         <v>-8.63452644883299</v>
@@ -13254,7 +13272,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13268,7 +13286,7 @@
         <v>-6.365423262694474</v>
       </c>
       <c r="D234" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E234">
         <v>-6.712841826990488</v>
@@ -13304,7 +13322,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13318,7 +13336,7 @@
         <v>-6.180679040630039</v>
       </c>
       <c r="D235" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E235">
         <v>-9.121143346744393</v>
@@ -13354,7 +13372,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13368,7 +13386,7 @@
         <v>-6.506459655789232</v>
       </c>
       <c r="D236" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E236">
         <v>-9.121143346744393</v>
@@ -13404,7 +13422,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13418,7 +13436,7 @@
         <v>-11.43191719026831</v>
       </c>
       <c r="D237" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E237">
         <v>-7.785207962880413</v>
@@ -13454,7 +13472,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13468,7 +13486,7 @@
         <v>-11.31598180640433</v>
       </c>
       <c r="D238" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E238">
         <v>-7.785207962880413</v>
@@ -13504,7 +13522,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13518,7 +13536,7 @@
         <v>-11.3586535041973</v>
       </c>
       <c r="D239" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E239">
         <v>-8.619440890991779</v>
@@ -13554,7 +13572,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13568,7 +13586,7 @@
         <v>-6.352422126194313</v>
       </c>
       <c r="D240" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E240">
         <v>-7.002545941158143</v>
@@ -13604,7 +13622,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13618,7 +13636,7 @@
         <v>-6.259072586714403</v>
       </c>
       <c r="D241" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E241">
         <v>-9.202945307875904</v>
@@ -13654,7 +13672,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13668,7 +13686,7 @@
         <v>-6.58534011830891</v>
       </c>
       <c r="D242" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E242">
         <v>-9.202945307875904</v>
@@ -13704,7 +13722,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13718,7 +13736,7 @@
         <v>-11.51939984314506</v>
       </c>
       <c r="D243" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E243">
         <v>-7.865386869227571</v>
@@ -13754,7 +13772,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13768,7 +13786,7 @@
         <v>-11.40184140449673</v>
       </c>
       <c r="D244" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E244">
         <v>-7.865386869227571</v>
@@ -13804,7 +13822,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13818,7 +13836,7 @@
         <v>-11.43266480236391</v>
       </c>
       <c r="D245" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E245">
         <v>-8.688745330283755</v>
@@ -13854,7 +13872,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13868,7 +13886,7 @@
         <v>-6.412150542258594</v>
       </c>
       <c r="D246" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E246">
         <v>-6.792666905080129</v>
@@ -13904,7 +13922,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13918,7 +13936,7 @@
         <v>-6.321920167701883</v>
       </c>
       <c r="D247" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E247">
         <v>-9.268525392384579</v>
@@ -13954,7 +13972,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13968,7 +13986,7 @@
         <v>-11.58953410018906</v>
       </c>
       <c r="D248" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E248">
         <v>-7.929665761583294</v>
@@ -14004,7 +14022,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14018,7 +14036,7 @@
         <v>-11.47067446938778</v>
       </c>
       <c r="D249" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E249">
         <v>-7.929665761583294</v>
@@ -14054,7 +14072,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14068,7 +14086,7 @@
         <v>-11.49199916453843</v>
       </c>
       <c r="D250" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E250">
         <v>-8.744306235214712</v>
@@ -14104,7 +14122,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14118,7 +14136,7 @@
         <v>-6.460034413487151</v>
       </c>
       <c r="D251" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E251">
         <v>-6.681381790702538</v>
@@ -14154,7 +14172,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14168,7 +14186,7 @@
         <v>-6.550476318984671</v>
       </c>
       <c r="D252" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E252">
         <v>-9.507018767636186</v>
@@ -14204,7 +14222,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14218,7 +14236,7 @@
         <v>-11.8445895153887</v>
       </c>
       <c r="D253" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E253">
         <v>-8.16342712542118</v>
@@ -14254,7 +14272,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14268,7 +14286,7 @@
         <v>-11.72099787317369</v>
       </c>
       <c r="D254" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E254">
         <v>-8.16342712542118</v>
@@ -14304,7 +14322,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14318,7 +14336,7 @@
         <v>-11.70777888500417</v>
       </c>
       <c r="D255" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E255">
         <v>-8.94636312258066</v>
@@ -14354,7 +14372,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14404,7 +14422,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14418,7 +14436,7 @@
         <v>-6.704638136207883</v>
       </c>
       <c r="D257" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E257">
         <v>-9.667883272564755</v>
@@ -14454,7 +14472,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14468,7 +14486,7 @@
         <v>-12.01662516649286</v>
       </c>
       <c r="D258" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E258">
         <v>-8.321099874299577</v>
@@ -14504,7 +14522,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14518,7 +14536,7 @@
         <v>-11.88984176822768</v>
       </c>
       <c r="D259" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E259">
         <v>-8.321099874299577</v>
@@ -14554,7 +14572,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14568,7 +14586,7 @@
         <v>-12.14300130071843</v>
       </c>
       <c r="D260" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E260">
         <v>-9.082651105922917</v>
@@ -14604,7 +14622,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14618,7 +14636,7 @@
         <v>-6.751629056158386</v>
       </c>
       <c r="D261" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E261">
         <v>-6.181746306378969</v>
@@ -14654,7 +14672,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14668,7 +14686,7 @@
         <v>-6.169874970448358</v>
       </c>
       <c r="D262" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E262">
         <v>-6.181746306378969</v>
@@ -14704,7 +14722,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14718,7 +14736,7 @@
         <v>-6.791555990766213</v>
       </c>
       <c r="D263" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E263">
         <v>-9.758580164277792</v>
@@ -14754,7 +14772,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14768,7 +14786,7 @@
         <v>-12.11362045346375</v>
       </c>
       <c r="D264" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E264">
         <v>-8.40999722451037</v>
@@ -14804,7 +14822,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14818,7 +14836,7 @@
         <v>-12.22524034737093</v>
       </c>
       <c r="D265" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E265">
         <v>-9.159491528068681</v>
@@ -14854,7 +14872,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14868,7 +14886,7 @@
         <v>-6.817852183440923</v>
       </c>
       <c r="D266" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E266">
         <v>-6.265382608492114</v>
@@ -14904,7 +14922,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14918,7 +14936,7 @@
         <v>-6.233722702947933</v>
       </c>
       <c r="D267" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E267">
         <v>-6.265382608492114</v>
@@ -14954,7 +14972,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14968,7 +14986,7 @@
         <v>-12.15514825489226</v>
       </c>
       <c r="D268" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E268">
         <v>-8.448057955318696</v>
@@ -15004,7 +15022,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15018,7 +15036,7 @@
         <v>-12.26045037566933</v>
       </c>
       <c r="D269" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E269">
         <v>-9.192390175953609</v>
@@ -15054,7 +15072,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15068,7 +15086,7 @@
         <v>-6.261058628637798</v>
       </c>
       <c r="D270" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E270">
         <v>-6.075524180706029</v>
@@ -15104,7 +15122,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15118,7 +15136,7 @@
         <v>-12.2145658985059</v>
       </c>
       <c r="D271" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E271">
         <v>-8.502514942229901</v>
@@ -15168,7 +15186,7 @@
         <v>-12.31082860040297</v>
       </c>
       <c r="D272" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E272">
         <v>-9.239461296218966</v>
@@ -15218,7 +15236,7 @@
         <v>-6.300170650816128</v>
       </c>
       <c r="D273" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E273">
         <v>-5.649532575530262</v>
@@ -15268,7 +15286,7 @@
         <v>-11.84108439837907</v>
       </c>
       <c r="D274" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E274">
         <v>-8.80055369389029</v>
@@ -15304,7 +15322,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15318,7 +15336,7 @@
         <v>-5.935476465087291</v>
       </c>
       <c r="D275" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E275">
         <v>-5.137979270573577</v>
@@ -15354,7 +15372,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15404,7 +15422,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15454,7 +15472,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15504,7 +15522,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15554,7 +15572,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15604,7 +15622,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15654,7 +15672,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15704,7 +15722,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15718,7 +15736,7 @@
         <v>-0.3501812538917548</v>
       </c>
       <c r="D283" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E283">
         <v>-4.299167540216818</v>
@@ -15754,7 +15772,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15804,7 +15822,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15818,7 +15836,7 @@
         <v>-0.2510998261771533</v>
       </c>
       <c r="D285" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E285">
         <v>-4.192512218904984</v>
@@ -15854,7 +15872,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15904,7 +15922,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15918,7 +15936,7 @@
         <v>-0.1528009024453745</v>
       </c>
       <c r="D287" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E287">
         <v>-4.086699217043329</v>
@@ -15954,7 +15972,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16004,7 +16022,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16018,7 +16036,7 @@
         <v>0.06625268284449959</v>
       </c>
       <c r="D289" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E289">
         <v>-3.850900934131047</v>
@@ -16054,7 +16072,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16104,7 +16122,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16154,7 +16172,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16204,7 +16222,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16254,7 +16272,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16304,7 +16322,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16318,7 +16336,7 @@
         <v>1.82693717047681</v>
       </c>
       <c r="D295" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E295">
         <v>0.6963720300954037</v>
@@ -16354,7 +16372,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16404,7 +16422,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16418,7 +16436,7 @@
         <v>2.198341117699623</v>
       </c>
       <c r="D297" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E297">
         <v>0.5276096580294123</v>
@@ -16454,7 +16472,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16468,7 +16486,7 @@
         <v>12.7271211800604</v>
       </c>
       <c r="D298" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E298">
         <v>10.466793520675</v>
@@ -16504,7 +16522,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16518,7 +16536,7 @@
         <v>13.26860393649666</v>
       </c>
       <c r="D299" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E299">
         <v>10.466793520675</v>
@@ -16554,7 +16572,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16568,7 +16586,7 @@
         <v>12.90082807115104</v>
       </c>
       <c r="D300" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E300">
         <v>10.466793520675</v>
@@ -16604,7 +16622,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16618,7 +16636,7 @@
         <v>12.60281108867061</v>
       </c>
       <c r="D301" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E301">
         <v>10.00917894691048</v>
@@ -16654,7 +16672,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16668,7 +16686,7 @@
         <v>13.14484756489033</v>
       </c>
       <c r="D302" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E302">
         <v>10.00917894691048</v>
@@ -16704,7 +16722,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16718,7 +16736,7 @@
         <v>12.77790227921993</v>
       </c>
       <c r="D303" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E303">
         <v>10.00917894691048</v>
@@ -16754,7 +16772,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16768,7 +16786,7 @@
         <v>12.94031582834918</v>
       </c>
       <c r="D304" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E304">
         <v>10.4990798111086</v>
@@ -16804,7 +16822,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16818,7 +16836,7 @@
         <v>13.48084894269951</v>
       </c>
       <c r="D305" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E305">
         <v>10.4990798111086</v>
@@ -16854,7 +16872,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16868,7 +16886,7 @@
         <v>13.11164861422502</v>
       </c>
       <c r="D306" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E306">
         <v>10.4990798111086</v>
@@ -16904,7 +16922,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16918,7 +16936,7 @@
         <v>12.89880385150152</v>
       </c>
       <c r="D307" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E307">
         <v>10.62546343074822</v>
@@ -16954,7 +16972,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16968,7 +16986,7 @@
         <v>13.4395218744347</v>
       </c>
       <c r="D308" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E308">
         <v>10.62546343074822</v>
@@ -17004,7 +17022,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17018,7 +17036,7 @@
         <v>13.07059890883446</v>
       </c>
       <c r="D309" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E309">
         <v>10.62546343074822</v>
@@ -17054,7 +17072,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17068,7 +17086,7 @@
         <v>12.9234363080082</v>
       </c>
       <c r="D310" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E310">
         <v>11.0537757639692</v>
@@ -17104,7 +17122,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17118,7 +17136,7 @@
         <v>13.46404460953155</v>
       </c>
       <c r="D311" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E311">
         <v>11.0537757639692</v>
@@ -17154,7 +17172,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17168,7 +17186,7 @@
         <v>13.09495706181657</v>
       </c>
       <c r="D312" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E312">
         <v>11.0537757639692</v>
@@ -17204,7 +17222,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17218,7 +17236,7 @@
         <v>13.44227382778946</v>
       </c>
       <c r="D313" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E313">
         <v>11.03770193240324</v>
@@ -17254,7 +17272,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17268,7 +17286,7 @@
         <v>13.07333239270363</v>
       </c>
       <c r="D314" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E314">
         <v>11.03770193240324</v>
@@ -17304,7 +17322,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17318,7 +17336,7 @@
         <v>13.47049330154028</v>
       </c>
       <c r="D315" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E315">
         <v>12.2200768479712</v>
@@ -17354,7 +17372,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17368,7 +17386,7 @@
         <v>13.10136247401317</v>
       </c>
       <c r="D316" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E316">
         <v>12.2200768479712</v>
@@ -17404,7 +17422,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17418,7 +17436,7 @@
         <v>13.41024108188445</v>
       </c>
       <c r="D317" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E317">
         <v>11.606966539383</v>
@@ -17454,7 +17472,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17468,7 +17486,7 @@
         <v>13.04151463167046</v>
       </c>
       <c r="D318" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E318">
         <v>11.606966539383</v>
@@ -17504,7 +17522,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17518,7 +17536,7 @@
         <v>15.99098556432473</v>
       </c>
       <c r="D319" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E319">
         <v>12.49688805745362</v>
@@ -17554,7 +17572,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17568,7 +17586,7 @@
         <v>15.82125527263218</v>
       </c>
       <c r="D320" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E320">
         <v>12.49688805745362</v>
@@ -17604,7 +17622,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17618,7 +17636,7 @@
         <v>16.12796689068343</v>
       </c>
       <c r="D321" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E321">
         <v>12.49688805745362</v>
@@ -17654,7 +17672,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17668,7 +17686,7 @@
         <v>16.05759498721028</v>
       </c>
       <c r="D322" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E322">
         <v>12.56617445478137</v>
@@ -17704,7 +17722,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17718,7 +17736,7 @@
         <v>15.8869198810087</v>
       </c>
       <c r="D323" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E323">
         <v>12.56617445478137</v>
@@ -17754,7 +17772,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17768,7 +17786,7 @@
         <v>16.19347402997512</v>
       </c>
       <c r="D324" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E324">
         <v>12.56617445478137</v>
@@ -17804,7 +17822,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17818,7 +17836,7 @@
         <v>16.08852224791477</v>
       </c>
       <c r="D325" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E325">
         <v>12.59834465504137</v>
@@ -17854,7 +17872,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17868,7 +17886,7 @@
         <v>15.9174084571642</v>
       </c>
       <c r="D326" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E326">
         <v>12.59834465504137</v>
@@ -17904,7 +17922,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17918,7 +17936,7 @@
         <v>16.22388949203912</v>
       </c>
       <c r="D327" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E327">
         <v>12.59834465504137</v>
@@ -17954,7 +17972,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17968,7 +17986,7 @@
         <v>15.99827269225045</v>
       </c>
       <c r="D328" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E328">
         <v>12.50446804867659</v>
@@ -18004,7 +18022,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18018,7 +18036,7 @@
         <v>15.82843903704122</v>
       </c>
       <c r="D329" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E329">
         <v>12.50446804867659</v>
@@ -18054,7 +18072,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18068,7 +18086,7 @@
         <v>16.13513342783969</v>
       </c>
       <c r="D330" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E330">
         <v>12.50446804867659</v>
@@ -18104,7 +18122,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18118,7 +18136,7 @@
         <v>10.5571576031199</v>
       </c>
       <c r="D331" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E331">
         <v>11.2357781978979</v>
@@ -18168,7 +18186,7 @@
         <v>10.4146275818384</v>
       </c>
       <c r="D332" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E332">
         <v>11.2357781978979</v>
@@ -18218,7 +18236,7 @@
         <v>11.02395259544049</v>
       </c>
       <c r="D333" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E333">
         <v>11.2357781978979</v>
@@ -18304,7 +18322,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18354,7 +18372,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18404,7 +18422,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18454,7 +18472,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18504,7 +18522,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18554,7 +18572,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18604,7 +18622,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18654,7 +18672,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18668,7 +18686,7 @@
         <v>7.109582508392513</v>
       </c>
       <c r="D342" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E342">
         <v>10.1191386498793</v>
@@ -18718,7 +18736,7 @@
         <v>8.320739177217412</v>
       </c>
       <c r="D343" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E343">
         <v>10.1191386498793</v>
@@ -18804,7 +18822,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18854,7 +18872,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18868,7 +18886,7 @@
         <v>5.429328338517664</v>
       </c>
       <c r="D346" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E346">
         <v>6.453570540990412</v>
@@ -18904,7 +18922,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18918,7 +18936,7 @@
         <v>4.28114123100805</v>
       </c>
       <c r="D347" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E347">
         <v>5.201857907737669</v>
@@ -18954,7 +18972,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18968,7 +18986,7 @@
         <v>3.478556159579213</v>
       </c>
       <c r="D348" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E348">
         <v>4.355782779043444</v>
@@ -19004,7 +19022,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19018,7 +19036,7 @@
         <v>2.542133382528917</v>
       </c>
       <c r="D349" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E349">
         <v>3.611162052395251</v>
@@ -19054,7 +19072,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19104,7 +19122,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19118,7 +19136,7 @@
         <v>3.166397470697689</v>
       </c>
       <c r="D351" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E351">
         <v>2.50604388321451</v>
@@ -19154,7 +19172,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19204,7 +19222,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19254,7 +19272,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19304,7 +19322,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19318,7 +19336,7 @@
         <v>0.5258114362592394</v>
       </c>
       <c r="D355" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E355">
         <v>0.9640594525915418</v>
@@ -19354,7 +19372,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19368,7 +19386,7 @@
         <v>1.029412028487577</v>
       </c>
       <c r="D356" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E356">
         <v>0.9640594525915418</v>
@@ -19404,7 +19422,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19418,7 +19436,7 @@
         <v>0.5230738845135647</v>
       </c>
       <c r="D357" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E357">
         <v>0.9640594525915418</v>
@@ -19454,7 +19472,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19468,7 +19486,7 @@
         <v>0.2932995584235911</v>
       </c>
       <c r="D358" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E358">
         <v>-0.2507339019854058</v>
@@ -19504,7 +19522,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19518,7 +19536,7 @@
         <v>0.8110931833932682</v>
       </c>
       <c r="D359" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E359">
         <v>-0.2507339019854058</v>
@@ -19554,7 +19572,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19568,7 +19586,7 @@
         <v>0.3063705065605404</v>
       </c>
       <c r="D360" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E360">
         <v>-0.2507339019854058</v>
@@ -19604,7 +19622,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19618,7 +19636,7 @@
         <v>0.25081902425989</v>
       </c>
       <c r="D361" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E361">
         <v>-1.810462939778127</v>
@@ -19654,7 +19672,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19668,7 +19686,7 @@
         <v>0.7712057537963801</v>
       </c>
       <c r="D362" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E362">
         <v>-1.810462939778127</v>
@@ -19704,7 +19722,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19718,7 +19736,7 @@
         <v>0.266778227076955</v>
       </c>
       <c r="D363" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E363">
         <v>-1.810462939778127</v>
@@ -19754,7 +19772,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19768,7 +19786,7 @@
         <v>0.2555858995649842</v>
       </c>
       <c r="D364" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E364">
         <v>-0.5322733758888774</v>
@@ -19804,7 +19822,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19818,7 +19836,7 @@
         <v>0.7756816486237952</v>
       </c>
       <c r="D365" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E365">
         <v>-0.5322733758888774</v>
@@ -19854,7 +19872,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19868,7 +19886,7 @@
         <v>0.2712210021752028</v>
       </c>
       <c r="D366" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E366">
         <v>-0.5322733758888774</v>
@@ -19904,7 +19922,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19954,7 +19972,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20004,7 +20022,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20054,7 +20072,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20104,7 +20122,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20118,7 +20136,7 @@
         <v>2.068109497945251</v>
       </c>
       <c r="D371" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E371">
         <v>1.103589803610085</v>
@@ -20154,7 +20172,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20168,7 +20186,7 @@
         <v>1.130775764308638</v>
       </c>
       <c r="D372" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E372">
         <v>1.103589803610085</v>
@@ -20204,7 +20222,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20218,7 +20236,7 @@
         <v>1.848060841515313</v>
       </c>
       <c r="D373" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E373">
         <v>0.99412281255767</v>
@@ -20254,7 +20272,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20268,7 +20286,7 @@
         <v>0.9315277271432265</v>
       </c>
       <c r="D374" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E374">
         <v>0.99412281255767</v>
@@ -20304,7 +20322,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20318,7 +20336,7 @@
         <v>1.694201531226533</v>
       </c>
       <c r="D375" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E375">
         <v>0.6700023738905614</v>
@@ -20354,7 +20372,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20368,7 +20386,7 @@
         <v>0.7922123317573622</v>
       </c>
       <c r="D376" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E376">
         <v>0.6700023738905614</v>
@@ -20404,7 +20422,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20418,7 +20436,7 @@
         <v>1.513646695334067</v>
       </c>
       <c r="D377" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E377">
         <v>0.5589534979668187</v>
@@ -20454,7 +20472,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20468,7 +20486,7 @@
         <v>0.6287248684119433</v>
       </c>
       <c r="D378" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E378">
         <v>0.5589534979668187</v>
@@ -20504,7 +20522,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20554,7 +20572,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20604,7 +20622,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20618,7 +20636,7 @@
         <v>1.430312383569088</v>
       </c>
       <c r="D381" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E381">
         <v>2.785832606944602</v>
@@ -20654,7 +20672,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20668,7 +20686,7 @@
         <v>1.015447344707901</v>
       </c>
       <c r="D382" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E382">
         <v>2.785832606944602</v>
@@ -20704,7 +20722,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20718,7 +20736,7 @@
         <v>2.872497404927479</v>
       </c>
       <c r="D383" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E383">
         <v>2.785832606944602</v>
@@ -20754,7 +20772,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20768,7 +20786,7 @@
         <v>1.657667083906176</v>
       </c>
       <c r="D384" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E384">
         <v>3.010263722734074</v>
@@ -20804,7 +20822,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20818,7 +20836,7 @@
         <v>3.082432889417845</v>
       </c>
       <c r="D385" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E385">
         <v>3.010263722734074</v>
@@ -20854,7 +20872,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20868,7 +20886,7 @@
         <v>1.760495757853356</v>
       </c>
       <c r="D386" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E386">
         <v>2.967064908431617</v>
@@ -20904,7 +20922,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20918,7 +20936,7 @@
         <v>3.177383147550167</v>
       </c>
       <c r="D387" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E387">
         <v>2.967064908431617</v>
@@ -20954,7 +20972,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20968,7 +20986,7 @@
         <v>3.419213206004784</v>
       </c>
       <c r="D388" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E388">
         <v>4.96095189349581</v>
@@ -21004,7 +21022,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21018,7 +21036,7 @@
         <v>30.71910142906406</v>
       </c>
       <c r="D389" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E389">
         <v>17.77124839717711</v>
@@ -21054,7 +21072,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21068,7 +21086,7 @@
         <v>30.74457906406285</v>
       </c>
       <c r="D390" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E390">
         <v>18.07805575594424</v>
@@ -21104,7 +21122,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21118,7 +21136,7 @@
         <v>30.94531632533681</v>
       </c>
       <c r="D391" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E391">
         <v>18.41220109884297</v>
@@ -21154,7 +21172,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21168,7 +21186,7 @@
         <v>31.10162189647678</v>
       </c>
       <c r="D392" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E392">
         <v>18.55328210136541</v>
@@ -21204,7 +21222,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21218,7 +21236,7 @@
         <v>31.28406714947664</v>
       </c>
       <c r="D393" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E393">
         <v>18.71795671283931</v>
@@ -21254,7 +21272,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21268,7 +21286,7 @@
         <v>31.41016164358475</v>
       </c>
       <c r="D394" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E394">
         <v>18.83176927570312</v>
@@ -21304,7 +21322,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21318,7 +21336,7 @@
         <v>31.50687459786862</v>
       </c>
       <c r="D395" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E395">
         <v>18.91906213703726</v>
@@ -21354,7 +21372,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21368,7 +21386,7 @@
         <v>31.56465330836859</v>
       </c>
       <c r="D396" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E396">
         <v>18.97121305105996</v>
@@ -21404,7 +21422,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21418,7 +21436,7 @@
         <v>31.59842308925229</v>
       </c>
       <c r="D397" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E397">
         <v>19.00169356757187</v>
@@ -21454,7 +21472,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21468,7 +21486,7 @@
         <v>31.66012131009328</v>
       </c>
       <c r="D398" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E398">
         <v>19.05738222144783</v>
@@ -21504,7 +21522,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21518,7 +21536,7 @@
         <v>31.70713316886447</v>
       </c>
       <c r="D399" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E399">
         <v>19.09981500306598</v>
@@ -21554,7 +21572,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21568,7 +21586,7 @@
         <v>31.87762108191551</v>
       </c>
       <c r="D400" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E400">
         <v>19.25369695056011</v>
@@ -21604,7 +21622,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21618,7 +21636,7 @@
         <v>32.04993923346682</v>
       </c>
       <c r="D401" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E401">
         <v>19.4092308665707</v>
@@ -21654,7 +21672,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21668,7 +21686,7 @@
         <v>32.21080893028861</v>
       </c>
       <c r="D402" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E402">
         <v>19.55443143707868</v>
@@ -21704,7 +21722,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21718,7 +21736,7 @@
         <v>32.44198272920474</v>
       </c>
       <c r="D403" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E403">
         <v>19.76308830752896</v>
@@ -21754,7 +21772,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21768,7 +21786,7 @@
         <v>32.60849165225912</v>
       </c>
       <c r="D404" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E404">
         <v>19.91337882898712</v>
@@ -21804,7 +21822,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21818,7 +21836,7 @@
         <v>32.78872551361854</v>
       </c>
       <c r="D405" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E405">
         <v>20.07605744411025</v>
@@ -21854,7 +21872,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21868,7 +21886,7 @@
         <v>32.88633633076009</v>
       </c>
       <c r="D406" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E406">
         <v>20.16416071412761</v>
@@ -21904,7 +21922,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21918,7 +21936,7 @@
         <v>32.92087256937922</v>
       </c>
       <c r="D407" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E407">
         <v>20.19533303340073</v>
@@ -21954,7 +21972,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21968,7 +21986,7 @@
         <v>33.06269553801688</v>
       </c>
       <c r="D408" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E408">
         <v>20.32334207652173</v>
@@ -22004,7 +22022,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22018,7 +22036,7 @@
         <v>33.22705411164569</v>
       </c>
       <c r="D409" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E409">
         <v>20.4716916981737</v>
@@ -22054,7 +22072,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22068,7 +22086,7 @@
         <v>33.43325315348858</v>
       </c>
       <c r="D410" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E410">
         <v>20.65780641775917</v>
@@ -22104,7 +22122,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22118,7 +22136,7 @@
         <v>33.53120523654898</v>
       </c>
       <c r="D411" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E411">
         <v>20.7462177135085</v>
@@ -22154,7 +22172,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22204,7 +22222,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22218,7 +22236,7 @@
         <v>33.46421187526697</v>
       </c>
       <c r="D413" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E413">
         <v>21.58554463904314</v>
@@ -22254,7 +22272,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22304,7 +22322,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22318,7 +22336,7 @@
         <v>33.20896438389043</v>
       </c>
       <c r="D415" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E415">
         <v>21.35184401382175</v>
@@ -22354,7 +22372,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22368,7 +22386,7 @@
         <v>33.24525244457716</v>
       </c>
       <c r="D416" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E416">
         <v>21.38506879665831</v>
@@ -22418,7 +22436,7 @@
         <v>33.30754061736793</v>
       </c>
       <c r="D417" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E417">
         <v>21.44209887694077</v>
@@ -22454,7 +22472,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22504,7 +22522,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22554,7 +22572,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22604,7 +22622,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22618,7 +22636,7 @@
         <v>33.37808699058778</v>
       </c>
       <c r="D421" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E421">
         <v>21.50669003683685</v>
@@ -22654,7 +22672,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22704,7 +22722,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22754,7 +22772,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22804,7 +22822,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22818,7 +22836,7 @@
         <v>33.3491605949092</v>
       </c>
       <c r="D425" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E425">
         <v>21.48020547975453</v>
@@ -22854,7 +22872,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22904,7 +22922,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22954,7 +22972,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23004,7 +23022,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23018,7 +23036,7 @@
         <v>33.21868761846164</v>
       </c>
       <c r="D429" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E429">
         <v>21.36074645586423</v>
@@ -23054,7 +23072,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23104,7 +23122,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23154,7 +23172,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23204,7 +23222,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23254,7 +23272,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23268,7 +23286,7 @@
         <v>33.10860895395319</v>
       </c>
       <c r="D434" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E434">
         <v>21.25996014615194</v>
@@ -23304,7 +23322,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23354,7 +23372,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23404,7 +23422,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23454,7 +23472,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23468,7 +23486,7 @@
         <v>32.82858702883275</v>
       </c>
       <c r="D438" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E438">
         <v>21.00357643548973</v>
@@ -23504,7 +23522,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23618,7 +23636,7 @@
         <v>32.43391527499527</v>
       </c>
       <c r="D441" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E441">
         <v>20.64222112840476</v>
@@ -23704,7 +23722,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23718,7 +23736,7 @@
         <v>32.1976037826028</v>
       </c>
       <c r="D443" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E443">
         <v>20.42585800874672</v>
@@ -23754,7 +23772,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23768,7 +23786,7 @@
         <v>31.9359757436375</v>
       </c>
       <c r="D444" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E444">
         <v>20.18631545359018</v>
@@ -23804,7 +23822,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23818,7 +23836,7 @@
         <v>31.6928085141255</v>
       </c>
       <c r="D445" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E445">
         <v>19.96367532786815</v>
@@ -23868,7 +23886,7 @@
         <v>31.38607212722557</v>
       </c>
       <c r="D446" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E446">
         <v>19.96017071526525</v>
@@ -23904,7 +23922,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23918,7 +23936,7 @@
         <v>31.09488527318194</v>
       </c>
       <c r="D447" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E447">
         <v>19.69041319680059</v>
@@ -23968,7 +23986,7 @@
         <v>28.76090315089132</v>
       </c>
       <c r="D448" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E448">
         <v>19.57543646755398</v>
@@ -24004,7 +24022,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24018,7 +24036,7 @@
         <v>30.97077487852789</v>
       </c>
       <c r="D449" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E449">
         <v>19.57543646755398</v>
@@ -24054,7 +24072,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24068,7 +24086,7 @@
         <v>28.60148803846228</v>
       </c>
       <c r="D450" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E450">
         <v>19.42949065339434</v>
@@ -24104,7 +24122,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24118,7 +24136,7 @@
         <v>30.81323523800978</v>
       </c>
       <c r="D451" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E451">
         <v>19.42949065339434</v>
@@ -24154,7 +24172,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24168,7 +24186,7 @@
         <v>28.31621253771513</v>
       </c>
       <c r="D452" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E452">
         <v>19.16831864415417</v>
@@ -24204,7 +24222,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24218,7 +24236,7 @@
         <v>30.53131591962436</v>
       </c>
       <c r="D453" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E453">
         <v>19.16831864415417</v>
@@ -24254,7 +24272,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24268,7 +24286,7 @@
         <v>28.17117124931562</v>
       </c>
       <c r="D454" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E454">
         <v>19.16188388044775</v>
@@ -24318,7 +24336,7 @@
         <v>30.52436998310014</v>
       </c>
       <c r="D455" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E455">
         <v>19.16188388044775</v>
@@ -24368,7 +24386,7 @@
         <v>28.43299823269307</v>
       </c>
       <c r="D456" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E456">
         <v>19.40417998614624</v>
@@ -24404,7 +24422,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24418,7 +24436,7 @@
         <v>28.68381801752044</v>
       </c>
       <c r="D457" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E457">
         <v>19.6362899708081</v>
@@ -24468,7 +24486,7 @@
         <v>28.80289710513282</v>
       </c>
       <c r="D458" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E458">
         <v>19.74648640215534</v>
@@ -24504,7 +24522,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24518,7 +24536,7 @@
         <v>28.66069705648685</v>
       </c>
       <c r="D459" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E459">
         <v>19.74648640215534</v>
@@ -24554,7 +24572,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24568,7 +24586,7 @@
         <v>28.92716526228032</v>
       </c>
       <c r="D460" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E460">
         <v>19.86148482649941</v>
@@ -24604,7 +24622,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24618,7 +24636,7 @@
         <v>28.78241267851456</v>
       </c>
       <c r="D461" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E461">
         <v>19.86148482649941</v>
@@ -24654,7 +24672,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24668,7 +24686,7 @@
         <v>28.69210673371983</v>
       </c>
       <c r="D462" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E462">
         <v>19.64396039358289</v>
@@ -24704,7 +24722,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24718,7 +24736,7 @@
         <v>28.55218237918936</v>
       </c>
       <c r="D463" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E463">
         <v>19.64396039358289</v>
@@ -24754,7 +24772,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24768,7 +24786,7 @@
         <v>24.1238374281487</v>
       </c>
       <c r="D464" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E464">
         <v>15.41645928485977</v>
@@ -24804,7 +24822,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24818,7 +24836,7 @@
         <v>23.88230241564499</v>
       </c>
       <c r="D465" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E465">
         <v>15.41645928485977</v>
@@ -24854,7 +24872,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24868,7 +24886,7 @@
         <v>16.53295008901819</v>
       </c>
       <c r="D466" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E466">
         <v>8.24961705438853</v>
@@ -24918,7 +24936,7 @@
         <v>16.39809781749685</v>
       </c>
       <c r="D467" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E467">
         <v>8.24961705438853</v>
@@ -24968,7 +24986,7 @@
         <v>8.646669450447945</v>
       </c>
       <c r="D468" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E468">
         <v>0.5067815058065008</v>
@@ -25004,7 +25022,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25018,7 +25036,7 @@
         <v>11.10765720787195</v>
       </c>
       <c r="D469" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E469">
         <v>0.5067815058065008</v>
@@ -25054,7 +25072,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25068,7 +25086,7 @@
         <v>8.708207114263224</v>
       </c>
       <c r="D470" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E470">
         <v>0.5067815058065008</v>
@@ -25104,7 +25122,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25118,7 +25136,7 @@
         <v>7.091043911098566</v>
       </c>
       <c r="D471" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E471">
         <v>-0.9493259013959516</v>
@@ -25168,7 +25186,7 @@
         <v>9.494415907805923</v>
       </c>
       <c r="D472" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E472">
         <v>-0.9493259013959516</v>
@@ -25218,7 +25236,7 @@
         <v>7.115916999912343</v>
       </c>
       <c r="D473" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E473">
         <v>-0.9493259013959516</v>
@@ -25268,7 +25286,7 @@
         <v>5.65581229233937</v>
       </c>
       <c r="D474" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E474">
         <v>-2.292741355992099</v>
@@ -25304,7 +25322,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25318,7 +25336,7 @@
         <v>8.006027562426013</v>
       </c>
       <c r="D475" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E475">
         <v>-2.292741355992099</v>
@@ -25354,7 +25372,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25368,7 +25386,7 @@
         <v>5.646858373303601</v>
       </c>
       <c r="D476" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E476">
         <v>-2.292741355992099</v>
@@ -25404,7 +25422,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25418,7 +25436,7 @@
         <v>4.107061890942596</v>
       </c>
       <c r="D477" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E477">
         <v>-3.742413448882012</v>
@@ -25454,7 +25472,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25468,7 +25486,7 @@
         <v>6.399916035051582</v>
       </c>
       <c r="D478" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E478">
         <v>-3.742413448882012</v>
@@ -25504,7 +25522,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25518,7 +25536,7 @@
         <v>4.061605437193776</v>
       </c>
       <c r="D479" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E479">
         <v>-3.742413448882012</v>
@@ -25554,7 +25572,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25568,7 +25586,7 @@
         <v>3.994587595705951</v>
       </c>
       <c r="D480" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E480">
         <v>-3.847692418834157</v>
@@ -25604,7 +25622,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25618,7 +25636,7 @@
         <v>6.283276025176541</v>
       </c>
       <c r="D481" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E481">
         <v>-3.847692418834157</v>
@@ -25654,7 +25672,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25668,7 +25686,7 @@
         <v>3.94648023264179</v>
       </c>
       <c r="D482" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E482">
         <v>-3.847692418834157</v>
@@ -25704,7 +25722,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25718,7 +25736,7 @@
         <v>3.810208807303631</v>
       </c>
       <c r="D483" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E483">
         <v>-4.02027593121074</v>
@@ -25768,7 +25786,7 @@
         <v>6.092068392759323</v>
       </c>
       <c r="D484" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E484">
         <v>-4.02027593121074</v>
@@ -25818,7 +25836,7 @@
         <v>3.757755816229981</v>
       </c>
       <c r="D485" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E485">
         <v>-4.02027593121074</v>
@@ -25868,7 +25886,7 @@
         <v>3.242943955180543</v>
       </c>
       <c r="D486" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E486">
         <v>-4.551251112659287</v>
@@ -25918,7 +25936,7 @@
         <v>5.503793731298337</v>
       </c>
       <c r="D487" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E487">
         <v>-4.551251112659287</v>
@@ -25968,7 +25986,7 @@
         <v>3.177121085437328</v>
       </c>
       <c r="D488" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E488">
         <v>-4.551251112659287</v>
@@ -26018,7 +26036,7 @@
         <v>0.5276020656298783</v>
       </c>
       <c r="D489" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E489">
         <v>-7.276209063074127</v>
@@ -26054,7 +26072,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26068,7 +26086,7 @@
         <v>2.687883623616173</v>
       </c>
       <c r="D490" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E490">
         <v>-7.276209063074127</v>
@@ -26104,7 +26122,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26118,7 +26136,7 @@
         <v>0.3977812388938915</v>
       </c>
       <c r="D491" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E491">
         <v>-7.276209063074127</v>
@@ -26154,7 +26172,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26168,7 +26186,7 @@
         <v>-0.0005009764291159513</v>
       </c>
       <c r="D492" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E492">
         <v>-7.771120443679365</v>
@@ -26204,7 +26222,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26218,7 +26236,7 @@
         <v>2.140221209629061</v>
       </c>
       <c r="D493" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E493">
         <v>-7.771120443679365</v>
@@ -26254,7 +26272,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26268,7 +26286,7 @@
         <v>-0.1427686762102667</v>
       </c>
       <c r="D494" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E494">
         <v>-7.771120443679365</v>
@@ -26304,7 +26322,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26318,7 +26336,7 @@
         <v>-0.6951028983788206</v>
       </c>
       <c r="D495" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E495">
         <v>-8.422066128110345</v>
@@ -26354,7 +26372,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26368,7 +26386,7 @@
         <v>1.419893290570108</v>
       </c>
       <c r="D496" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E496">
         <v>-8.422066128110345</v>
@@ -26404,7 +26422,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26418,7 +26436,7 @@
         <v>-0.8537416872294941</v>
       </c>
       <c r="D497" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E497">
         <v>-8.422066128110345</v>
@@ -26454,7 +26472,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26468,7 +26486,7 @@
         <v>-1.098623802898558</v>
       </c>
       <c r="D498" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E498">
         <v>-8.615075478807405</v>
@@ -26504,7 +26522,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26518,7 +26536,7 @@
         <v>1.001427167364454</v>
       </c>
       <c r="D499" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E499">
         <v>-8.615075478807405</v>
@@ -26554,7 +26572,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26568,7 +26586,7 @@
         <v>-1.266773185458455</v>
       </c>
       <c r="D500" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E500">
         <v>-8.615075478807405</v>
@@ -26604,7 +26622,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26618,7 +26636,7 @@
         <v>-1.400997181997106</v>
       </c>
       <c r="D501" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E501">
         <v>-8.898105106381124</v>
@@ -26654,7 +26672,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26668,7 +26686,7 @@
         <v>0.6878547742252223</v>
       </c>
       <c r="D502" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E502">
         <v>-8.898105106381124</v>
@@ -26704,7 +26722,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26718,7 +26736,7 @@
         <v>-1.576273209855614</v>
       </c>
       <c r="D503" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E503">
         <v>-8.898105106381124</v>
@@ -26754,7 +26772,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26768,7 +26786,7 @@
         <v>-1.724593447066837</v>
       </c>
       <c r="D504" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E504">
         <v>-9.200999926884109</v>
@@ -26804,7 +26822,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26818,7 +26836,7 @@
         <v>0.3522734623010564</v>
       </c>
       <c r="D505" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E505">
         <v>-9.200999926884109</v>
@@ -26854,7 +26872,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26868,7 +26886,7 @@
         <v>-1.907496322923627</v>
       </c>
       <c r="D506" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E506">
         <v>-9.200999926884109</v>
@@ -26904,7 +26922,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26918,7 +26936,7 @@
         <v>44.86204822710516</v>
       </c>
       <c r="D507" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E507">
         <v>35.52043652295812</v>
@@ -26954,7 +26972,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26968,7 +26986,7 @@
         <v>46.13402290259216</v>
       </c>
       <c r="D508" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E508">
         <v>36.69877772856216</v>
@@ -27004,7 +27022,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27018,7 +27036,7 @@
         <v>46.08362925847739</v>
       </c>
       <c r="D509" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E509">
         <v>36.69877772856216</v>
@@ -27054,7 +27072,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27068,7 +27086,7 @@
         <v>45.05397872766954</v>
       </c>
       <c r="D510" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E510">
         <v>35.69823850422841</v>
@@ -27104,7 +27122,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27118,7 +27136,7 @@
         <v>44.98156832800709</v>
       </c>
       <c r="D511" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E511">
         <v>35.69823850422841</v>
@@ -27154,7 +27172,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27168,7 +27186,7 @@
         <v>42.5821201676108</v>
       </c>
       <c r="D512" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E512">
         <v>33.77379366345071</v>
@@ -27204,7 +27222,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27218,7 +27236,7 @@
         <v>42.55551239448888</v>
       </c>
       <c r="D513" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E513">
         <v>33.77379366345071</v>
@@ -27254,7 +27272,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27268,7 +27286,7 @@
         <v>42.86185585668593</v>
       </c>
       <c r="D514" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E514">
         <v>33.77379366345071</v>
@@ -27304,7 +27322,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27318,7 +27336,7 @@
         <v>9.729438161046986</v>
       </c>
       <c r="D515" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E515">
         <v>4.60825443961048</v>
@@ -27354,7 +27372,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27368,7 +27386,7 @@
         <v>1.966821409142597</v>
       </c>
       <c r="D516" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E516">
         <v>6.89439153971923</v>
@@ -27404,7 +27422,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27418,7 +27436,7 @@
         <v>1.841930457020688</v>
       </c>
       <c r="D517" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E517">
         <v>6.89439153971923</v>
@@ -27454,7 +27472,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27468,7 +27486,7 @@
         <v>7.54859977610915</v>
       </c>
       <c r="D518" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E518">
         <v>3.585313169516937</v>
@@ -27504,7 +27522,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27518,7 +27536,7 @@
         <v>-0.07307844071422664</v>
       </c>
       <c r="D519" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E519">
         <v>4.928669866220837</v>
@@ -27554,7 +27572,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27568,7 +27586,7 @@
         <v>-0.1707707281713766</v>
       </c>
       <c r="D520" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E520">
         <v>4.928669866220837</v>
@@ -27604,7 +27622,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27618,7 +27636,7 @@
         <v>4.58724487239736</v>
       </c>
       <c r="D521" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E521">
         <v>6.152553191940676</v>
@@ -27654,7 +27672,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27668,7 +27686,7 @@
         <v>4.212040637078079</v>
       </c>
       <c r="D522" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E522">
         <v>5.839454132623437</v>
@@ -27704,7 +27722,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27718,7 +27736,7 @@
         <v>3.699818204723471</v>
       </c>
       <c r="D523" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E523">
         <v>5.615918345535061</v>
@@ -27754,7 +27772,357 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>411</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="524" spans="1:16">
+      <c r="A524" s="1">
+        <v>0</v>
+      </c>
+      <c r="B524" t="s">
+        <v>95</v>
+      </c>
+      <c r="C524">
+        <v>4.002895527219746</v>
+      </c>
+      <c r="D524" t="s">
+        <v>210</v>
+      </c>
+      <c r="E524">
+        <v>4.187640055392684</v>
+      </c>
+      <c r="F524">
+        <v>1</v>
+      </c>
+      <c r="G524">
+        <v>0.05719710447278026</v>
+      </c>
+      <c r="H524">
+        <v>0.05831235994460732</v>
+      </c>
+      <c r="I524">
+        <v>0.1847445281729385</v>
+      </c>
+      <c r="J524">
+        <v>1.938564465946083</v>
+      </c>
+      <c r="K524">
+        <v>13.72</v>
+      </c>
+      <c r="L524">
+        <v>30.6</v>
+      </c>
+      <c r="M524">
+        <v>13.96</v>
+      </c>
+      <c r="N524">
+        <v>31.25</v>
+      </c>
+      <c r="O524">
+        <v>1</v>
+      </c>
+      <c r="P524" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="525" spans="1:16">
+      <c r="A525" s="1">
+        <v>0</v>
+      </c>
+      <c r="B525" t="s">
+        <v>95</v>
+      </c>
+      <c r="C525">
+        <v>3.732407742902605</v>
+      </c>
+      <c r="D525" t="s">
+        <v>210</v>
+      </c>
+      <c r="E525">
+        <v>3.9124207063353</v>
+      </c>
+      <c r="F525">
+        <v>1</v>
+      </c>
+      <c r="G525">
+        <v>0.0574675922570974</v>
+      </c>
+      <c r="H525">
+        <v>0.0585875792936647</v>
+      </c>
+      <c r="I525">
+        <v>0.180012963432695</v>
+      </c>
+      <c r="J525">
+        <v>1.958279319030422</v>
+      </c>
+      <c r="K525">
+        <v>13.72</v>
+      </c>
+      <c r="L525">
+        <v>30.6</v>
+      </c>
+      <c r="M525">
+        <v>13.96</v>
+      </c>
+      <c r="N525">
+        <v>31.25</v>
+      </c>
+      <c r="O525">
+        <v>1</v>
+      </c>
+      <c r="P525" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="526" spans="1:16">
+      <c r="A526" s="1">
+        <v>0</v>
+      </c>
+      <c r="B526" t="s">
+        <v>95</v>
+      </c>
+      <c r="C526">
+        <v>3.563836789836007</v>
+      </c>
+      <c r="D526" t="s">
+        <v>210</v>
+      </c>
+      <c r="E526">
+        <v>3.7409009902413</v>
+      </c>
+      <c r="F526">
+        <v>1</v>
+      </c>
+      <c r="G526">
+        <v>0.057636163210164</v>
+      </c>
+      <c r="H526">
+        <v>0.0587590990097587</v>
+      </c>
+      <c r="I526">
+        <v>0.1770642004052938</v>
+      </c>
+      <c r="J526">
+        <v>1.970565831644606</v>
+      </c>
+      <c r="K526">
+        <v>13.72</v>
+      </c>
+      <c r="L526">
+        <v>30.6</v>
+      </c>
+      <c r="M526">
+        <v>13.96</v>
+      </c>
+      <c r="N526">
+        <v>31.25</v>
+      </c>
+      <c r="O526">
+        <v>1</v>
+      </c>
+      <c r="P526" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="527" spans="1:16">
+      <c r="A527" s="1">
+        <v>0</v>
+      </c>
+      <c r="B527" t="s">
+        <v>95</v>
+      </c>
+      <c r="C527">
+        <v>3.292630819264101</v>
+      </c>
+      <c r="D527" t="s">
+        <v>210</v>
+      </c>
+      <c r="E527">
+        <v>3.464950891904291</v>
+      </c>
+      <c r="F527">
+        <v>1</v>
+      </c>
+      <c r="G527">
+        <v>0.0579073691807359</v>
+      </c>
+      <c r="H527">
+        <v>0.05903504910809571</v>
+      </c>
+      <c r="I527">
+        <v>0.1723200726401899</v>
+      </c>
+      <c r="J527">
+        <v>1.990333030665882</v>
+      </c>
+      <c r="K527">
+        <v>13.72</v>
+      </c>
+      <c r="L527">
+        <v>30.6</v>
+      </c>
+      <c r="M527">
+        <v>13.96</v>
+      </c>
+      <c r="N527">
+        <v>31.25</v>
+      </c>
+      <c r="O527">
+        <v>1</v>
+      </c>
+      <c r="P527" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="528" spans="1:16">
+      <c r="A528" s="1">
+        <v>0</v>
+      </c>
+      <c r="B528" t="s">
+        <v>95</v>
+      </c>
+      <c r="C528">
+        <v>3.187918659013199</v>
+      </c>
+      <c r="D528" t="s">
+        <v>210</v>
+      </c>
+      <c r="E528">
+        <v>3.358407032057158</v>
+      </c>
+      <c r="F528">
+        <v>1</v>
+      </c>
+      <c r="G528">
+        <v>0.0580120813409868</v>
+      </c>
+      <c r="H528">
+        <v>0.05914159296794284</v>
+      </c>
+      <c r="I528">
+        <v>0.170488373043959</v>
+      </c>
+      <c r="J528">
+        <v>1.997965112316822</v>
+      </c>
+      <c r="K528">
+        <v>13.72</v>
+      </c>
+      <c r="L528">
+        <v>30.6</v>
+      </c>
+      <c r="M528">
+        <v>13.96</v>
+      </c>
+      <c r="N528">
+        <v>31.25</v>
+      </c>
+      <c r="O528">
+        <v>1</v>
+      </c>
+      <c r="P528" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="529" spans="1:16">
+      <c r="A529" s="1">
+        <v>0</v>
+      </c>
+      <c r="B529" t="s">
+        <v>95</v>
+      </c>
+      <c r="C529">
+        <v>3.095210370074518</v>
+      </c>
+      <c r="D529" t="s">
+        <v>210</v>
+      </c>
+      <c r="E529">
+        <v>3.264077023778444</v>
+      </c>
+      <c r="F529">
+        <v>1</v>
+      </c>
+      <c r="G529">
+        <v>0.05810478962992548</v>
+      </c>
+      <c r="H529">
+        <v>0.05923592297622156</v>
+      </c>
+      <c r="I529">
+        <v>0.1688666537039261</v>
+      </c>
+      <c r="J529">
+        <v>2.004722276233636</v>
+      </c>
+      <c r="K529">
+        <v>13.72</v>
+      </c>
+      <c r="L529">
+        <v>30.6</v>
+      </c>
+      <c r="M529">
+        <v>13.96</v>
+      </c>
+      <c r="N529">
+        <v>31.25</v>
+      </c>
+      <c r="O529">
+        <v>1</v>
+      </c>
+      <c r="P529" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="530" spans="1:16">
+      <c r="A530" s="1">
+        <v>0</v>
+      </c>
+      <c r="B530" t="s">
+        <v>95</v>
+      </c>
+      <c r="C530">
+        <v>3.067560158467881</v>
+      </c>
+      <c r="D530" t="s">
+        <v>210</v>
+      </c>
+      <c r="E530">
+        <v>3.235943135000845</v>
+      </c>
+      <c r="F530">
+        <v>1</v>
+      </c>
+      <c r="G530">
+        <v>0.05813243984153212</v>
+      </c>
+      <c r="H530">
+        <v>0.05926405686499916</v>
+      </c>
+      <c r="I530">
+        <v>0.1683829765329641</v>
+      </c>
+      <c r="J530">
+        <v>2.006737597779309</v>
+      </c>
+      <c r="K530">
+        <v>13.72</v>
+      </c>
+      <c r="L530">
+        <v>30.6</v>
+      </c>
+      <c r="M530">
+        <v>13.96</v>
+      </c>
+      <c r="N530">
+        <v>31.25</v>
+      </c>
+      <c r="O530">
+        <v>1</v>
+      </c>
+      <c r="P530" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="420">
   <si>
     <t>trade_time</t>
   </si>
@@ -298,6 +298,9 @@
     <t>2021-03-19</t>
   </si>
   <si>
+    <t>2021-06-11</t>
+  </si>
+  <si>
     <t>2021-08-30</t>
   </si>
   <si>
@@ -637,6 +640,9 @@
     <t>2021-02-03</t>
   </si>
   <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
     <t>2021-09-01</t>
   </si>
   <si>
@@ -646,7 +652,7 @@
     <t>2021-09-07</t>
   </si>
   <si>
-    <t>2021-10-19</t>
+    <t>2021-10-20</t>
   </si>
   <si>
     <t>2016-04-05</t>
@@ -1249,6 +1255,9 @@
     <t>2020-12-18</t>
   </si>
   <si>
+    <t>2021-05-31</t>
+  </si>
+  <si>
     <t>2021-08-18</t>
   </si>
   <si>
@@ -1256,9 +1265,6 @@
   </si>
   <si>
     <t>2021-08-27</t>
-  </si>
-  <si>
-    <t>2021-08-31</t>
   </si>
   <si>
     <t>2021-09-03</t>
@@ -1686,7 +1692,7 @@
         <v>1.980046625394046</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E2">
         <v>4.596593277573533</v>
@@ -1722,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1736,7 +1742,7 @@
         <v>1.476168338596821</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3">
         <v>4.596593277573533</v>
@@ -1772,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1786,7 +1792,7 @@
         <v>2.113316346177388</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E4">
         <v>4.596593277573533</v>
@@ -1822,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1836,7 +1842,7 @@
         <v>2.095559772582941</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E5">
         <v>4.596593277573533</v>
@@ -1872,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1886,7 +1892,7 @@
         <v>2.137194632974616</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E6">
         <v>4.596593277573533</v>
@@ -1922,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1936,7 +1942,7 @@
         <v>2.167194632974617</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7">
         <v>4.596593277573533</v>
@@ -1972,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1986,7 +1992,7 @@
         <v>2.844772647031224</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E8">
         <v>5.373230386726174</v>
@@ -2022,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2036,7 +2042,7 @@
         <v>2.344935136036042</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9">
         <v>5.373230386726174</v>
@@ -2072,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2086,7 +2092,7 @@
         <v>2.953797713002309</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E10">
         <v>5.373230386726174</v>
@@ -2122,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2136,7 +2142,7 @@
         <v>2.944122691011945</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>5.373230386726174</v>
@@ -2172,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2186,7 +2192,7 @@
         <v>2.973635223997491</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E12">
         <v>5.373230386726174</v>
@@ -2222,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2236,7 +2242,7 @@
         <v>3.003635223997492</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E13">
         <v>5.373230386726174</v>
@@ -2272,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2286,7 +2292,7 @@
         <v>7.289203935514355</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E14">
         <v>5.128184916132415</v>
@@ -2322,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2336,7 +2342,7 @@
         <v>-2.117497474419014</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E15">
         <v>0.8991929718719938</v>
@@ -2372,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2386,7 +2392,7 @@
         <v>-2.80975033090947</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E16">
         <v>0.2758434229577951</v>
@@ -2422,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2436,7 +2442,7 @@
         <v>-2.902998496046035</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E17">
         <v>0.1918767030952893</v>
@@ -2472,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2486,7 +2492,7 @@
         <v>-2.830339867902396</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E18">
         <v>0.2573032631353307</v>
@@ -2522,7 +2528,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2536,7 +2542,7 @@
         <v>-2.537341046304341</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E19">
         <v>0.5211384810952531</v>
@@ -2572,7 +2578,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2586,7 +2592,7 @@
         <v>-2.336644974997025</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E20">
         <v>0.7018582922817487</v>
@@ -2622,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2636,7 +2642,7 @@
         <v>-2.249226521683095</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21">
         <v>0.7018582922817487</v>
@@ -2672,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2686,7 +2692,7 @@
         <v>-1.845740644766149</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E22">
         <v>1.143900517084994</v>
@@ -2722,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2736,7 +2742,7 @@
         <v>-1.76174710538406</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23">
         <v>1.143900517084994</v>
@@ -2772,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2822,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2836,7 +2842,7 @@
         <v>-1.483754394543759</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E25">
         <v>1.469856507982922</v>
@@ -2872,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2886,7 +2892,7 @@
         <v>-1.402286340628343</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E26">
         <v>1.469856507982922</v>
@@ -2922,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2972,7 +2978,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2986,7 +2992,7 @@
         <v>-1.119201343261796</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E28">
         <v>1.798123813695423</v>
@@ -3022,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3036,7 +3042,7 @@
         <v>-1.040276682727416</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E29">
         <v>1.798123813695423</v>
@@ -3072,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3086,7 +3092,7 @@
         <v>-0.970418309242234</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>-1.315795006570312</v>
@@ -3122,7 +3128,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3136,7 +3142,7 @@
         <v>-1.094604783790125</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E31">
         <v>1.627274602785022</v>
@@ -3172,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3186,7 +3192,7 @@
         <v>-1.015851727159035</v>
       </c>
       <c r="D32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E32">
         <v>1.627274602785022</v>
@@ -3222,7 +3228,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3236,7 +3242,7 @@
         <v>-1.190513514023774</v>
       </c>
       <c r="D33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E33">
         <v>-1.147995174237213</v>
@@ -3272,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3286,7 +3292,7 @@
         <v>-1.15006863091817</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E34">
         <v>1.577640908889972</v>
@@ -3322,7 +3328,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3336,7 +3342,7 @@
         <v>-1.255522302285485</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E35">
         <v>-0.5624021926528435</v>
@@ -3372,7 +3378,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3386,7 +3392,7 @@
         <v>-1.320960230949986</v>
       </c>
       <c r="D36" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E36">
         <v>1.424712797977779</v>
@@ -3422,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3436,7 +3442,7 @@
         <v>-1.455823154415796</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E37">
         <v>-0.3493885347260317</v>
@@ -3472,7 +3478,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3486,7 +3492,7 @@
         <v>-1.605480846937454</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E38">
         <v>-0.7894370781288025</v>
@@ -3522,7 +3528,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3536,7 +3542,7 @@
         <v>-1.761773123733541</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E39">
         <v>-1.128596969277446</v>
@@ -3572,7 +3578,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3586,7 +3592,7 @@
         <v>-1.457944364792599</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E40">
         <v>-0.8017368070151889</v>
@@ -3622,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3636,7 +3642,7 @@
         <v>-1.234076514305805</v>
       </c>
       <c r="D41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E41">
         <v>0.01703472753200685</v>
@@ -3672,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3686,7 +3692,7 @@
         <v>-0.7963224235233177</v>
       </c>
       <c r="D42" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E42">
         <v>0.2870665855800212</v>
@@ -3722,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3736,7 +3742,7 @@
         <v>-0.8942517780380754</v>
       </c>
       <c r="D43" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E43">
         <v>0.59890656545236</v>
@@ -3772,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3786,7 +3792,7 @@
         <v>-0.899307304101125</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E44">
         <v>0.6876116265245429</v>
@@ -3822,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3836,7 +3842,7 @@
         <v>-0.8589383918075626</v>
       </c>
       <c r="D45" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E45">
         <v>0.8335609313842731</v>
@@ -3872,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3886,7 +3892,7 @@
         <v>-0.6533981903373771</v>
       </c>
       <c r="D46" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E46">
         <v>1.169788560028703</v>
@@ -3922,7 +3928,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3936,7 +3942,7 @@
         <v>4.835153534210221</v>
       </c>
       <c r="D47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E47">
         <v>2.04429947322755</v>
@@ -3972,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3986,7 +3992,7 @@
         <v>-0.406918334342155</v>
       </c>
       <c r="D48" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E48">
         <v>1.312995819177061</v>
@@ -4022,7 +4028,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4036,7 +4042,7 @@
         <v>0.04130730968482865</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E49">
         <v>2.64378384364354</v>
@@ -4072,7 +4078,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4086,7 +4092,7 @@
         <v>5.033791575296075</v>
       </c>
       <c r="D50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E50">
         <v>2.275021568455536</v>
@@ -4122,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4136,7 +4142,7 @@
         <v>-0.1691188742298735</v>
       </c>
       <c r="D51" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E51">
         <v>1.79275039480164</v>
@@ -4172,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4186,7 +4192,7 @@
         <v>0.2293541709380591</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E52">
         <v>2.812063918551083</v>
@@ -4222,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4236,7 +4242,7 @@
         <v>5.217902572011447</v>
       </c>
       <c r="D53" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E53">
         <v>2.488870208345837</v>
@@ -4272,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4286,7 +4292,7 @@
         <v>0.0512895398901918</v>
       </c>
       <c r="D54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E54">
         <v>1.57274123510015</v>
@@ -4322,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4336,7 +4342,7 @@
         <v>0.3237189931323456</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E55">
         <v>2.896509461761223</v>
@@ -4372,7 +4378,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4386,7 +4392,7 @@
         <v>5.3102923165319</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E56">
         <v>2.596182761957483</v>
@@ -4422,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4436,7 +4442,7 @@
         <v>0.161893889624892</v>
       </c>
       <c r="D57" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E57">
         <v>1.501333830022219</v>
@@ -4472,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4486,7 +4492,7 @@
         <v>5.33023415169577</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E58">
         <v>2.619345606126444</v>
@@ -4522,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4536,7 +4542,7 @@
         <v>0.1857672504861512</v>
       </c>
       <c r="D59" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E59">
         <v>1.155646098159064</v>
@@ -4572,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4586,7 +4592,7 @@
         <v>5.37850629613547</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E60">
         <v>2.675414676508897</v>
@@ -4622,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4636,7 +4642,7 @@
         <v>0.243556231003037</v>
       </c>
       <c r="D61" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E61">
         <v>1.799674337820232</v>
@@ -4672,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4686,7 +4692,7 @@
         <v>5.505970450595548</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E62">
         <v>2.823466865418581</v>
@@ -4722,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4736,7 +4742,7 @@
         <v>0.3961498981001377</v>
       </c>
       <c r="D63" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E63">
         <v>1.846556155176511</v>
@@ -4772,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4786,7 +4792,7 @@
         <v>5.552898822755296</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E64">
         <v>2.877975117167079</v>
@@ -4822,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4836,7 +4842,7 @@
         <v>0.4523301821108561</v>
       </c>
       <c r="D65" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E65">
         <v>2.714577056552891</v>
@@ -4872,7 +4878,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4886,7 +4892,7 @@
         <v>0.844003460842476</v>
       </c>
       <c r="D66" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E66">
         <v>3.182739844457025</v>
@@ -4922,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4936,7 +4942,7 @@
         <v>5.819687109336471</v>
       </c>
       <c r="D67" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E67">
         <v>2.897855098492958</v>
@@ -4972,7 +4978,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4986,7 +4992,7 @@
         <v>0.7717156843363</v>
       </c>
       <c r="D68" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E68">
         <v>3.232403806926722</v>
@@ -5022,7 +5028,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5036,7 +5042,7 @@
         <v>2.174557955758587</v>
       </c>
       <c r="D69" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E69">
         <v>4.552795119478848</v>
@@ -5072,7 +5078,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5086,7 +5092,7 @@
         <v>2.230502900253292</v>
       </c>
       <c r="D70" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E70">
         <v>4.552795119478848</v>
@@ -5122,7 +5128,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5136,7 +5142,7 @@
         <v>7.122392789242706</v>
       </c>
       <c r="D71" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E71">
         <v>4.410974047362672</v>
@@ -5172,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5186,7 +5192,7 @@
         <v>3.377229031968387</v>
       </c>
       <c r="D72" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E72">
         <v>5.847002514367812</v>
@@ -5222,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5236,7 +5242,7 @@
         <v>3.424783248024418</v>
       </c>
       <c r="D73" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E73">
         <v>5.847002514367812</v>
@@ -5272,7 +5278,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5286,7 +5292,7 @@
         <v>8.29989168013649</v>
       </c>
       <c r="D74" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E74">
         <v>5.631180854885052</v>
@@ -5322,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5336,7 +5342,7 @@
         <v>4.683694888843547</v>
       </c>
       <c r="D75" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E75">
         <v>7.023429444093537</v>
@@ -5372,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5386,7 +5392,7 @@
         <v>4.722134226828356</v>
       </c>
       <c r="D76" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E76">
         <v>7.023429444093537</v>
@@ -5422,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5436,7 +5442,7 @@
         <v>9.579012902797984</v>
       </c>
       <c r="D77" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E77">
         <v>6.893347467132109</v>
@@ -5472,7 +5478,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5486,7 +5492,7 @@
         <v>3.961474621504259</v>
       </c>
       <c r="D78" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E78">
         <v>6.476706188649629</v>
@@ -5522,7 +5528,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5536,7 +5542,7 @@
         <v>8.320444610292363</v>
       </c>
       <c r="D79" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E79">
         <v>7.021567248362409</v>
@@ -5572,7 +5578,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5586,7 +5592,7 @@
         <v>8.530866989040167</v>
       </c>
       <c r="D80" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E80">
         <v>7.021567248362409</v>
@@ -5622,7 +5628,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5636,7 +5642,7 @@
         <v>3.2890165208482</v>
       </c>
       <c r="D81" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E81">
         <v>5.857937357507026</v>
@@ -5672,7 +5678,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5686,7 +5692,7 @@
         <v>7.698991315674085</v>
       </c>
       <c r="D82" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E82">
         <v>6.277165792762322</v>
@@ -5722,7 +5728,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5736,7 +5742,7 @@
         <v>7.862435583597616</v>
       </c>
       <c r="D83" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E83">
         <v>6.277165792762322</v>
@@ -5772,7 +5778,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5786,7 +5792,7 @@
         <v>2.706415003086228</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E84">
         <v>5.321850930983533</v>
@@ -5822,7 +5828,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5836,7 +5842,7 @@
         <v>7.160579134588669</v>
       </c>
       <c r="D85" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E85">
         <v>5.783497068837448</v>
@@ -5872,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5886,7 +5892,7 @@
         <v>7.283322697678528</v>
       </c>
       <c r="D86" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E86">
         <v>5.783497068837448</v>
@@ -5922,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5936,7 +5942,7 @@
         <v>2.25250194719996</v>
       </c>
       <c r="D87" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E87">
         <v>4.90417843844148</v>
@@ -5972,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5986,7 +5992,7 @@
         <v>6.741094613879405</v>
       </c>
       <c r="D88" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E88">
         <v>5.766049754225914</v>
@@ -6022,7 +6028,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6036,7 +6042,7 @@
         <v>6.83212768404308</v>
       </c>
       <c r="D89" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E89">
         <v>5.766049754225914</v>
@@ -6072,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6086,7 +6092,7 @@
         <v>1.648635956687475</v>
       </c>
       <c r="D90" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E90">
         <v>4.348525301462924</v>
@@ -6122,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6136,7 +6142,7 @@
         <v>6.183030834224155</v>
       </c>
       <c r="D91" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E91">
         <v>5.350064030791522</v>
@@ -6172,7 +6178,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6186,7 +6192,7 @@
         <v>6.231877657545638</v>
       </c>
       <c r="D92" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E92">
         <v>5.350064030791522</v>
@@ -6222,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6236,7 +6242,7 @@
         <v>1.432518806234409</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E93">
         <v>4.149663013321483</v>
@@ -6272,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6286,7 +6292,7 @@
         <v>5.983305802967131</v>
       </c>
       <c r="D94" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E94">
         <v>4.577912304600769</v>
@@ -6322,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6336,7 +6342,7 @@
         <v>6.017054621765944</v>
       </c>
       <c r="D95" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E95">
         <v>4.577912304600769</v>
@@ -6372,7 +6378,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6386,7 +6392,7 @@
         <v>1.226728012835469</v>
       </c>
       <c r="D96" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E96">
         <v>3.960302622589126</v>
@@ -6422,7 +6428,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6436,7 +6442,7 @@
         <v>5.793123892101445</v>
       </c>
       <c r="D97" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E97">
         <v>4.612872778687663</v>
@@ -6472,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6486,7 +6492,7 @@
         <v>5.812496108566997</v>
       </c>
       <c r="D98" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E98">
         <v>4.612872778687663</v>
@@ -6522,7 +6528,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6536,7 +6542,7 @@
         <v>1.216947853386511</v>
       </c>
       <c r="D99" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E99">
         <v>3.951303314193975</v>
@@ -6572,7 +6578,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6586,7 +6592,7 @@
         <v>5.802774512947074</v>
       </c>
       <c r="D100" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E100">
         <v>4.403561129870987</v>
@@ -6622,7 +6628,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6636,7 +6642,7 @@
         <v>1.177523163430447</v>
       </c>
       <c r="D101" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E101">
         <v>3.915026304074722</v>
@@ -6672,7 +6678,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6686,7 +6692,7 @@
         <v>5.763585898978771</v>
       </c>
       <c r="D102" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E102">
         <v>4.466025047817013</v>
@@ -6722,7 +6728,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6736,7 +6742,7 @@
         <v>0.9680478903759173</v>
       </c>
       <c r="D103" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E103">
         <v>3.722275603719158</v>
@@ -6772,7 +6778,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6786,7 +6792,7 @@
         <v>0.8515262832029507</v>
       </c>
       <c r="D104" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E104">
         <v>3.61505711887537</v>
@@ -6822,7 +6828,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6836,7 +6842,7 @@
         <v>0.6675490824101864</v>
       </c>
       <c r="D105" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E105">
         <v>3.445768716549093</v>
@@ -6872,7 +6878,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6886,7 +6892,7 @@
         <v>0.2453647773980379</v>
       </c>
       <c r="D106" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E106">
         <v>3.057291741278434</v>
@@ -6922,7 +6928,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6936,7 +6942,7 @@
         <v>-0.1442597189068877</v>
       </c>
       <c r="D107" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E107">
         <v>2.69877498918947</v>
@@ -6972,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6986,7 +6992,7 @@
         <v>3.671796227407118</v>
       </c>
       <c r="D108" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E108">
         <v>1.089748757437874</v>
@@ -7022,7 +7028,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7036,7 +7042,7 @@
         <v>-1.239097601114093</v>
       </c>
       <c r="D109" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E109">
         <v>1.261882831716061</v>
@@ -7072,7 +7078,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7086,7 +7092,7 @@
         <v>3.066548753992304</v>
       </c>
       <c r="D110" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E110">
         <v>0.4140568037443764</v>
@@ -7122,7 +7128,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7136,7 +7142,7 @@
         <v>-1.959356470902271</v>
       </c>
       <c r="D111" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E111">
         <v>0.6034425874785647</v>
@@ -7172,7 +7178,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7186,7 +7192,7 @@
         <v>2.434653904799742</v>
       </c>
       <c r="D112" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E112">
         <v>-0.2913840017675113</v>
@@ -7222,7 +7228,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7236,7 +7242,7 @@
         <v>-2.711326350820261</v>
       </c>
       <c r="D113" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E113">
         <v>-0.08398696342450762</v>
@@ -7272,7 +7278,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7286,7 +7292,7 @@
         <v>2.046949385277987</v>
       </c>
       <c r="D114" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E114">
         <v>-0.7242132753428656</v>
@@ -7322,7 +7328,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7336,7 +7342,7 @@
         <v>-3.172703938184629</v>
       </c>
       <c r="D115" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E115">
         <v>-0.5057652768234711</v>
@@ -7372,7 +7378,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7386,7 +7392,7 @@
         <v>1.727381390460117</v>
       </c>
       <c r="D116" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E116">
         <v>0.5925973930511788</v>
@@ -7422,7 +7428,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7436,7 +7442,7 @@
         <v>1.685047495782005</v>
       </c>
       <c r="D117" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E117">
         <v>-1.128236762428639</v>
@@ -7472,7 +7478,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7486,7 +7492,7 @@
         <v>-3.603375782929252</v>
       </c>
       <c r="D118" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E118">
         <v>-0.8994732706219501</v>
@@ -7522,7 +7528,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7536,7 +7542,7 @@
         <v>1.329375274458599</v>
       </c>
       <c r="D119" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E119">
         <v>-0.02169112718700106</v>
@@ -7572,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7586,7 +7592,7 @@
         <v>1.370767088004978</v>
       </c>
       <c r="D120" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E120">
         <v>-1.479096125030072</v>
@@ -7622,7 +7628,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7636,7 +7642,7 @@
         <v>-3.977376933276734</v>
       </c>
       <c r="D121" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E121">
         <v>-1.241374521837809</v>
@@ -7672,7 +7678,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7686,7 +7692,7 @@
         <v>0.9837414768320834</v>
       </c>
       <c r="D122" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E122">
         <v>-0.5624929319466254</v>
@@ -7722,7 +7728,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7736,7 +7742,7 @@
         <v>-4.274892307557078</v>
       </c>
       <c r="D123" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E123">
         <v>-1.513354644433413</v>
@@ -7786,7 +7792,7 @@
         <v>0.7087921389242986</v>
       </c>
       <c r="D124" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E124">
         <v>-0.01219137097330147</v>
@@ -7836,7 +7842,7 @@
         <v>-6.600419867221269</v>
       </c>
       <c r="D125" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E125">
         <v>-3.935750603200287</v>
@@ -7872,7 +7878,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7886,7 +7892,7 @@
         <v>-1.740049190571469</v>
       </c>
       <c r="D126" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E126">
         <v>-3.803035064283293</v>
@@ -7922,7 +7928,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7936,7 +7942,7 @@
         <v>-7.356943655480499</v>
       </c>
       <c r="D127" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E127">
         <v>-4.634314907681588</v>
@@ -7972,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7986,7 +7992,7 @@
         <v>-2.446239742918287</v>
       </c>
       <c r="D128" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E128">
         <v>-3.284642996427294</v>
@@ -8022,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8036,7 +8042,7 @@
         <v>-2.764549545202325</v>
       </c>
       <c r="D129" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E129">
         <v>-3.284642996427294</v>
@@ -8072,7 +8078,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8086,7 +8092,7 @@
         <v>-8.273062059554213</v>
       </c>
       <c r="D130" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E130">
         <v>-5.480246821120623</v>
@@ -8122,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8136,7 +8142,7 @@
         <v>-3.301406720914517</v>
       </c>
       <c r="D131" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E131">
         <v>-3.80770165872979</v>
@@ -8172,7 +8178,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8186,7 +8192,7 @@
         <v>-3.640798600667189</v>
       </c>
       <c r="D132" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E132">
         <v>-3.80770165872979</v>
@@ -8222,7 +8228,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8236,7 +8242,7 @@
         <v>-9.028638086965721</v>
       </c>
       <c r="D133" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E133">
         <v>-6.177935975464312</v>
@@ -8272,7 +8278,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8286,7 +8292,7 @@
         <v>-4.006712569082914</v>
       </c>
       <c r="D134" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E134">
         <v>-5.764446572941544</v>
@@ -8322,7 +8328,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8336,7 +8342,7 @@
         <v>-4.355244481425245</v>
       </c>
       <c r="D135" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E135">
         <v>-5.764446572941544</v>
@@ -8372,7 +8378,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8386,7 +8392,7 @@
         <v>-9.288472736223071</v>
       </c>
       <c r="D136" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E136">
         <v>-6.4178639378834</v>
@@ -8422,7 +8428,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8436,7 +8442,7 @@
         <v>-4.249259832401776</v>
       </c>
       <c r="D137" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E137">
         <v>-5.572990039214197</v>
@@ -8472,7 +8478,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8486,7 +8492,7 @@
         <v>-4.600934905823827</v>
       </c>
       <c r="D138" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E138">
         <v>-5.572990039214197</v>
@@ -8522,7 +8528,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8536,7 +8542,7 @@
         <v>-8.391360480599353</v>
       </c>
       <c r="D139" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E139">
         <v>-5.589482056682467</v>
@@ -8572,7 +8578,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8586,7 +8592,7 @@
         <v>-3.41183448088206</v>
       </c>
       <c r="D140" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E140">
         <v>-4.236414237755341</v>
@@ -8622,7 +8628,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8636,7 +8642,7 @@
         <v>-3.752657389921566</v>
       </c>
       <c r="D141" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E141">
         <v>-4.236414237755341</v>
@@ -8672,7 +8678,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8686,7 +8692,7 @@
         <v>-7.284701623181299</v>
       </c>
       <c r="D142" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E142">
         <v>-4.567607547211761</v>
@@ -8722,7 +8728,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8736,7 +8742,7 @@
         <v>-2.378804136155122</v>
       </c>
       <c r="D143" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E143">
         <v>-3.182992288094191</v>
@@ -8772,7 +8778,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8822,7 +8828,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8872,7 +8878,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8886,7 +8892,7 @@
         <v>15.30025538505301</v>
       </c>
       <c r="D146" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E146">
         <v>12.2194473505381</v>
@@ -8922,7 +8928,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8936,7 +8942,7 @@
         <v>16.08154605938966</v>
       </c>
       <c r="D147" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E147">
         <v>12.2194473505381</v>
@@ -8972,7 +8978,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9022,7 +9028,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9072,7 +9078,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9122,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9172,7 +9178,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9222,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9272,7 +9278,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9322,7 +9328,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9372,7 +9378,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9422,7 +9428,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9472,7 +9478,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9486,7 +9492,7 @@
         <v>-2.965774048910724</v>
       </c>
       <c r="D158" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E158">
         <v>-6.323583762599906</v>
@@ -9522,7 +9528,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9536,7 +9542,7 @@
         <v>-3.841273412039687</v>
       </c>
       <c r="D159" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E159">
         <v>-6.323583762599906</v>
@@ -9572,7 +9578,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9622,7 +9628,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9636,7 +9642,7 @@
         <v>-4.596644143057084</v>
       </c>
       <c r="D161" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E161">
         <v>-7.87451662725034</v>
@@ -9672,7 +9678,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9686,7 +9692,7 @@
         <v>-5.499155847289916</v>
       </c>
       <c r="D162" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E162">
         <v>-7.87451662725034</v>
@@ -9722,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9772,7 +9778,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9786,7 +9792,7 @@
         <v>-6.176260919928573</v>
       </c>
       <c r="D164" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E164">
         <v>-9.588220956609884</v>
@@ -9822,7 +9828,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -9836,7 +9842,7 @@
         <v>-7.104936049037125</v>
       </c>
       <c r="D165" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E165">
         <v>-9.588220956609884</v>
@@ -9872,7 +9878,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9922,7 +9928,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9972,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9986,7 +9992,7 @@
         <v>-5.957065888688689</v>
       </c>
       <c r="D168" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E168">
         <v>-9.35041930781134</v>
@@ -10022,7 +10028,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10036,7 +10042,7 @@
         <v>-6.882110458273605</v>
       </c>
       <c r="D169" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E169">
         <v>-9.35041930781134</v>
@@ -10072,7 +10078,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10086,7 +10092,7 @@
         <v>-5.75373473480284</v>
       </c>
       <c r="D170" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E170">
         <v>-9.129828159496252</v>
@@ -10136,7 +10142,7 @@
         <v>-6.675411500596677</v>
       </c>
       <c r="D171" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E171">
         <v>-9.129828159496252</v>
@@ -10186,7 +10192,7 @@
         <v>4.036863233290944</v>
       </c>
       <c r="D172" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E172">
         <v>1.091137151603181</v>
@@ -10236,7 +10242,7 @@
         <v>4.353212181898559</v>
       </c>
       <c r="D173" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E173">
         <v>1.091137151603181</v>
@@ -10286,7 +10292,7 @@
         <v>4.092859462531468</v>
       </c>
       <c r="D174" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E174">
         <v>1.091137151603181</v>
@@ -10372,7 +10378,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10422,7 +10428,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10572,7 +10578,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10622,7 +10628,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10672,7 +10678,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10722,7 +10728,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10772,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10822,7 +10828,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10872,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10922,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10972,7 +10978,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11022,7 +11028,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11072,7 +11078,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11122,7 +11128,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11172,7 +11178,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11222,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11272,7 +11278,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11286,7 +11292,7 @@
         <v>2.797016608461103</v>
       </c>
       <c r="D194" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E194">
         <v>-0.1302387600075896</v>
@@ -11322,7 +11328,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11336,7 +11342,7 @@
         <v>3.23804287129742</v>
       </c>
       <c r="D195" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E195">
         <v>-0.1302387600075896</v>
@@ -11372,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11386,7 +11392,7 @@
         <v>2.97076363447318</v>
       </c>
       <c r="D196" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E196">
         <v>-0.1302387600075896</v>
@@ -11422,7 +11428,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11436,7 +11442,7 @@
         <v>-2.735537076225839</v>
       </c>
       <c r="D197" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E197">
         <v>-0.06446785034954416</v>
@@ -11472,7 +11478,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11486,7 +11492,7 @@
         <v>2.142297248198716</v>
       </c>
       <c r="D198" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E198">
         <v>-0.7752043867837592</v>
@@ -11522,7 +11528,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11536,7 +11542,7 @@
         <v>2.649161212067007</v>
       </c>
       <c r="D199" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E199">
         <v>-0.7752043867837592</v>
@@ -11572,7 +11578,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11586,7 +11592,7 @@
         <v>1.866662847049479</v>
       </c>
       <c r="D200" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E200">
         <v>-0.7752043867837592</v>
@@ -11622,7 +11628,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11636,7 +11642,7 @@
         <v>-3.292719101626048</v>
       </c>
       <c r="D201" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E201">
         <v>-0.5316716843393898</v>
@@ -11672,7 +11678,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11686,7 +11692,7 @@
         <v>0.7343076746441</v>
       </c>
       <c r="D202" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E202">
         <v>-2.162218324233283</v>
@@ -11736,7 +11742,7 @@
         <v>1.382757182221791</v>
       </c>
       <c r="D203" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E203">
         <v>-2.162218324233283</v>
@@ -11786,7 +11792,7 @@
         <v>0.5792831810991643</v>
       </c>
       <c r="D204" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E204">
         <v>-2.162218324233283</v>
@@ -11836,7 +11842,7 @@
         <v>-4.4909523141297</v>
       </c>
       <c r="D205" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E205">
         <v>-1.797099453998044</v>
@@ -11886,7 +11892,7 @@
         <v>-0.5271433345479153</v>
       </c>
       <c r="D206" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E206">
         <v>-3.404876767180344</v>
@@ -11936,7 +11942,7 @@
         <v>0.2481559951831649</v>
       </c>
       <c r="D207" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E207">
         <v>-3.404876767180344</v>
@@ -11986,7 +11992,7 @@
         <v>-0.5741105721844058</v>
       </c>
       <c r="D208" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E208">
         <v>-3.404876767180344</v>
@@ -12036,7 +12042,7 @@
         <v>-5.289194339951301</v>
       </c>
       <c r="D209" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E209">
         <v>-2.93597803324387</v>
@@ -12086,7 +12092,7 @@
         <v>-1.521590007004434</v>
       </c>
       <c r="D210" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E210">
         <v>-4.774748703164175</v>
@@ -12122,7 +12128,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12136,7 +12142,7 @@
         <v>-2.373169137555241</v>
       </c>
       <c r="D211" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E211">
         <v>-4.774748703164175</v>
@@ -12172,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12186,7 +12192,7 @@
         <v>-6.960010441395497</v>
       </c>
       <c r="D212" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E212">
         <v>-4.500536093148853</v>
@@ -12222,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12236,7 +12242,7 @@
         <v>-2.452340392521911</v>
       </c>
       <c r="D213" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E213">
         <v>-5.548191233294997</v>
@@ -12286,7 +12292,7 @@
         <v>-2.754963624773605</v>
       </c>
       <c r="D214" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E214">
         <v>-5.548191233294997</v>
@@ -12336,7 +12342,7 @@
         <v>-7.838731302256715</v>
       </c>
       <c r="D215" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E215">
         <v>-5.323373390490392</v>
@@ -12386,7 +12392,7 @@
         <v>-4.58678078170076</v>
       </c>
       <c r="D216" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E216">
         <v>-7.667945163513835</v>
@@ -12422,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12436,7 +12442,7 @@
         <v>-5.270890369576151</v>
       </c>
       <c r="D217" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E217">
         <v>-7.667945163513835</v>
@@ -12472,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12486,7 +12492,7 @@
         <v>-4.902661407674056</v>
       </c>
       <c r="D218" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E218">
         <v>-7.667945163513835</v>
@@ -12522,7 +12528,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12536,7 +12542,7 @@
         <v>-9.853855147941093</v>
       </c>
       <c r="D219" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E219">
         <v>-7.21034243019923</v>
@@ -12572,7 +12578,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12586,7 +12592,7 @@
         <v>-5.59817458645032</v>
       </c>
       <c r="D220" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E220">
         <v>-8.513312611948162</v>
@@ -12622,7 +12628,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12636,7 +12642,7 @@
         <v>-5.920337161521442</v>
       </c>
       <c r="D221" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E221">
         <v>-8.513312611948162</v>
@@ -12672,7 +12678,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12686,7 +12692,7 @@
         <v>-10.78187598777789</v>
       </c>
       <c r="D222" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E222">
         <v>-7.189437361711093</v>
@@ -12722,7 +12728,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12736,7 +12742,7 @@
         <v>-10.80871141081024</v>
       </c>
       <c r="D223" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E223">
         <v>-8.104473185122753</v>
@@ -12772,7 +12778,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12786,7 +12792,7 @@
         <v>-5.98278744209609</v>
       </c>
       <c r="D224" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E224">
         <v>-8.914647765665489</v>
@@ -12822,7 +12828,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12836,7 +12842,7 @@
         <v>-6.30733891689172</v>
       </c>
       <c r="D225" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E225">
         <v>-8.914647765665489</v>
@@ -12872,7 +12878,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12886,7 +12892,7 @@
         <v>-11.21108163828114</v>
       </c>
       <c r="D226" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E226">
         <v>-7.582809516346728</v>
@@ -12922,7 +12928,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12936,7 +12942,7 @@
         <v>-11.09924338896238</v>
       </c>
       <c r="D227" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E227">
         <v>-7.582809516346728</v>
@@ -12972,7 +12978,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12986,7 +12992,7 @@
         <v>-11.17182416893544</v>
       </c>
       <c r="D228" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E228">
         <v>-8.444493245911037</v>
@@ -13022,7 +13028,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13036,7 +13042,7 @@
         <v>-6.197743032286496</v>
       </c>
       <c r="D229" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E229">
         <v>-9.138949251081566</v>
@@ -13072,7 +13078,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13086,7 +13092,7 @@
         <v>-6.52362963497151</v>
       </c>
       <c r="D230" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E230">
         <v>-9.138949251081566</v>
@@ -13122,7 +13128,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13136,7 +13142,7 @@
         <v>-11.45095961574</v>
       </c>
       <c r="D231" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E231">
         <v>-7.802660575464863</v>
@@ -13172,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13186,7 +13192,7 @@
         <v>-11.33467094012331</v>
       </c>
       <c r="D232" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E232">
         <v>-7.802660575464863</v>
@@ -13222,7 +13228,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13236,7 +13242,7 @@
         <v>-11.37476360812142</v>
       </c>
       <c r="D233" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E233">
         <v>-8.63452644883299</v>
@@ -13272,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13286,7 +13292,7 @@
         <v>-6.365423262694474</v>
       </c>
       <c r="D234" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E234">
         <v>-6.712841826990488</v>
@@ -13322,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13336,7 +13342,7 @@
         <v>-6.180679040630039</v>
       </c>
       <c r="D235" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E235">
         <v>-9.121143346744393</v>
@@ -13372,7 +13378,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13386,7 +13392,7 @@
         <v>-6.506459655789232</v>
       </c>
       <c r="D236" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E236">
         <v>-9.121143346744393</v>
@@ -13422,7 +13428,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13436,7 +13442,7 @@
         <v>-11.43191719026831</v>
       </c>
       <c r="D237" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E237">
         <v>-7.785207962880413</v>
@@ -13472,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13486,7 +13492,7 @@
         <v>-11.31598180640433</v>
       </c>
       <c r="D238" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E238">
         <v>-7.785207962880413</v>
@@ -13522,7 +13528,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13536,7 +13542,7 @@
         <v>-11.3586535041973</v>
       </c>
       <c r="D239" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E239">
         <v>-8.619440890991779</v>
@@ -13572,7 +13578,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13586,7 +13592,7 @@
         <v>-6.352422126194313</v>
       </c>
       <c r="D240" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E240">
         <v>-7.002545941158143</v>
@@ -13622,7 +13628,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13636,7 +13642,7 @@
         <v>-6.259072586714403</v>
       </c>
       <c r="D241" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E241">
         <v>-9.202945307875904</v>
@@ -13672,7 +13678,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13686,7 +13692,7 @@
         <v>-6.58534011830891</v>
       </c>
       <c r="D242" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E242">
         <v>-9.202945307875904</v>
@@ -13722,7 +13728,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13736,7 +13742,7 @@
         <v>-11.51939984314506</v>
       </c>
       <c r="D243" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E243">
         <v>-7.865386869227571</v>
@@ -13772,7 +13778,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13786,7 +13792,7 @@
         <v>-11.40184140449673</v>
       </c>
       <c r="D244" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E244">
         <v>-7.865386869227571</v>
@@ -13822,7 +13828,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13836,7 +13842,7 @@
         <v>-11.43266480236391</v>
       </c>
       <c r="D245" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E245">
         <v>-8.688745330283755</v>
@@ -13872,7 +13878,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13886,7 +13892,7 @@
         <v>-6.412150542258594</v>
       </c>
       <c r="D246" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E246">
         <v>-6.792666905080129</v>
@@ -13922,7 +13928,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13936,7 +13942,7 @@
         <v>-6.321920167701883</v>
       </c>
       <c r="D247" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E247">
         <v>-9.268525392384579</v>
@@ -13972,7 +13978,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13986,7 +13992,7 @@
         <v>-11.58953410018906</v>
       </c>
       <c r="D248" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E248">
         <v>-7.929665761583294</v>
@@ -14022,7 +14028,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14036,7 +14042,7 @@
         <v>-11.47067446938778</v>
       </c>
       <c r="D249" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E249">
         <v>-7.929665761583294</v>
@@ -14072,7 +14078,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14086,7 +14092,7 @@
         <v>-11.49199916453843</v>
       </c>
       <c r="D250" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E250">
         <v>-8.744306235214712</v>
@@ -14122,7 +14128,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14136,7 +14142,7 @@
         <v>-6.460034413487151</v>
       </c>
       <c r="D251" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E251">
         <v>-6.681381790702538</v>
@@ -14172,7 +14178,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14186,7 +14192,7 @@
         <v>-6.550476318984671</v>
       </c>
       <c r="D252" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E252">
         <v>-9.507018767636186</v>
@@ -14222,7 +14228,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14236,7 +14242,7 @@
         <v>-11.8445895153887</v>
       </c>
       <c r="D253" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E253">
         <v>-8.16342712542118</v>
@@ -14272,7 +14278,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14286,7 +14292,7 @@
         <v>-11.72099787317369</v>
       </c>
       <c r="D254" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E254">
         <v>-8.16342712542118</v>
@@ -14322,7 +14328,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14336,7 +14342,7 @@
         <v>-11.70777888500417</v>
       </c>
       <c r="D255" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E255">
         <v>-8.94636312258066</v>
@@ -14372,7 +14378,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14422,7 +14428,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14436,7 +14442,7 @@
         <v>-6.704638136207883</v>
       </c>
       <c r="D257" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E257">
         <v>-9.667883272564755</v>
@@ -14472,7 +14478,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14486,7 +14492,7 @@
         <v>-12.01662516649286</v>
       </c>
       <c r="D258" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E258">
         <v>-8.321099874299577</v>
@@ -14522,7 +14528,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14536,7 +14542,7 @@
         <v>-11.88984176822768</v>
       </c>
       <c r="D259" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E259">
         <v>-8.321099874299577</v>
@@ -14572,7 +14578,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14586,7 +14592,7 @@
         <v>-12.14300130071843</v>
       </c>
       <c r="D260" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E260">
         <v>-9.082651105922917</v>
@@ -14622,7 +14628,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14636,7 +14642,7 @@
         <v>-6.751629056158386</v>
       </c>
       <c r="D261" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E261">
         <v>-6.181746306378969</v>
@@ -14672,7 +14678,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14686,7 +14692,7 @@
         <v>-6.169874970448358</v>
       </c>
       <c r="D262" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E262">
         <v>-6.181746306378969</v>
@@ -14722,7 +14728,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14736,7 +14742,7 @@
         <v>-6.791555990766213</v>
       </c>
       <c r="D263" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E263">
         <v>-9.758580164277792</v>
@@ -14772,7 +14778,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14786,7 +14792,7 @@
         <v>-12.11362045346375</v>
       </c>
       <c r="D264" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E264">
         <v>-8.40999722451037</v>
@@ -14822,7 +14828,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14836,7 +14842,7 @@
         <v>-12.22524034737093</v>
       </c>
       <c r="D265" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E265">
         <v>-9.159491528068681</v>
@@ -14872,7 +14878,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14886,7 +14892,7 @@
         <v>-6.817852183440923</v>
       </c>
       <c r="D266" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E266">
         <v>-6.265382608492114</v>
@@ -14922,7 +14928,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14936,7 +14942,7 @@
         <v>-6.233722702947933</v>
       </c>
       <c r="D267" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E267">
         <v>-6.265382608492114</v>
@@ -14972,7 +14978,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -14986,7 +14992,7 @@
         <v>-12.15514825489226</v>
       </c>
       <c r="D268" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E268">
         <v>-8.448057955318696</v>
@@ -15022,7 +15028,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15036,7 +15042,7 @@
         <v>-12.26045037566933</v>
       </c>
       <c r="D269" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E269">
         <v>-9.192390175953609</v>
@@ -15072,7 +15078,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15086,7 +15092,7 @@
         <v>-6.261058628637798</v>
       </c>
       <c r="D270" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E270">
         <v>-6.075524180706029</v>
@@ -15122,7 +15128,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15136,7 +15142,7 @@
         <v>-12.2145658985059</v>
       </c>
       <c r="D271" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E271">
         <v>-8.502514942229901</v>
@@ -15186,7 +15192,7 @@
         <v>-12.31082860040297</v>
       </c>
       <c r="D272" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E272">
         <v>-9.239461296218966</v>
@@ -15236,7 +15242,7 @@
         <v>-6.300170650816128</v>
       </c>
       <c r="D273" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E273">
         <v>-5.649532575530262</v>
@@ -15286,7 +15292,7 @@
         <v>-11.84108439837907</v>
       </c>
       <c r="D274" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E274">
         <v>-8.80055369389029</v>
@@ -15322,7 +15328,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15336,7 +15342,7 @@
         <v>-5.935476465087291</v>
       </c>
       <c r="D275" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E275">
         <v>-5.137979270573577</v>
@@ -15372,7 +15378,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15422,7 +15428,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15472,7 +15478,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15522,7 +15528,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15572,7 +15578,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15622,7 +15628,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15672,7 +15678,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15722,7 +15728,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15736,7 +15742,7 @@
         <v>-0.3501812538917548</v>
       </c>
       <c r="D283" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E283">
         <v>-4.299167540216818</v>
@@ -15772,7 +15778,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15822,7 +15828,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15836,7 +15842,7 @@
         <v>-0.2510998261771533</v>
       </c>
       <c r="D285" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E285">
         <v>-4.192512218904984</v>
@@ -15872,7 +15878,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15922,7 +15928,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15936,7 +15942,7 @@
         <v>-0.1528009024453745</v>
       </c>
       <c r="D287" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E287">
         <v>-4.086699217043329</v>
@@ -15972,7 +15978,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16022,7 +16028,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16036,7 +16042,7 @@
         <v>0.06625268284449959</v>
       </c>
       <c r="D289" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E289">
         <v>-3.850900934131047</v>
@@ -16072,7 +16078,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16122,7 +16128,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16172,7 +16178,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16222,7 +16228,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16272,7 +16278,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16322,7 +16328,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16336,7 +16342,7 @@
         <v>1.82693717047681</v>
       </c>
       <c r="D295" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E295">
         <v>0.6963720300954037</v>
@@ -16372,7 +16378,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16422,7 +16428,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16436,7 +16442,7 @@
         <v>2.198341117699623</v>
       </c>
       <c r="D297" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E297">
         <v>0.5276096580294123</v>
@@ -16472,7 +16478,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16486,7 +16492,7 @@
         <v>12.7271211800604</v>
       </c>
       <c r="D298" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E298">
         <v>10.466793520675</v>
@@ -16522,7 +16528,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16536,7 +16542,7 @@
         <v>13.26860393649666</v>
       </c>
       <c r="D299" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E299">
         <v>10.466793520675</v>
@@ -16572,7 +16578,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16586,7 +16592,7 @@
         <v>12.90082807115104</v>
       </c>
       <c r="D300" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E300">
         <v>10.466793520675</v>
@@ -16622,7 +16628,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16636,7 +16642,7 @@
         <v>12.60281108867061</v>
       </c>
       <c r="D301" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E301">
         <v>10.00917894691048</v>
@@ -16672,7 +16678,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16686,7 +16692,7 @@
         <v>13.14484756489033</v>
       </c>
       <c r="D302" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E302">
         <v>10.00917894691048</v>
@@ -16722,7 +16728,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16736,7 +16742,7 @@
         <v>12.77790227921993</v>
       </c>
       <c r="D303" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E303">
         <v>10.00917894691048</v>
@@ -16772,7 +16778,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16786,7 +16792,7 @@
         <v>12.94031582834918</v>
       </c>
       <c r="D304" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E304">
         <v>10.4990798111086</v>
@@ -16822,7 +16828,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16836,7 +16842,7 @@
         <v>13.48084894269951</v>
       </c>
       <c r="D305" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E305">
         <v>10.4990798111086</v>
@@ -16872,7 +16878,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16886,7 +16892,7 @@
         <v>13.11164861422502</v>
       </c>
       <c r="D306" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E306">
         <v>10.4990798111086</v>
@@ -16922,7 +16928,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16936,7 +16942,7 @@
         <v>12.89880385150152</v>
       </c>
       <c r="D307" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E307">
         <v>10.62546343074822</v>
@@ -16972,7 +16978,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16986,7 +16992,7 @@
         <v>13.4395218744347</v>
       </c>
       <c r="D308" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E308">
         <v>10.62546343074822</v>
@@ -17022,7 +17028,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17036,7 +17042,7 @@
         <v>13.07059890883446</v>
       </c>
       <c r="D309" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E309">
         <v>10.62546343074822</v>
@@ -17072,7 +17078,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17086,7 +17092,7 @@
         <v>12.9234363080082</v>
       </c>
       <c r="D310" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E310">
         <v>11.0537757639692</v>
@@ -17122,7 +17128,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17136,7 +17142,7 @@
         <v>13.46404460953155</v>
       </c>
       <c r="D311" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E311">
         <v>11.0537757639692</v>
@@ -17172,7 +17178,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17186,7 +17192,7 @@
         <v>13.09495706181657</v>
       </c>
       <c r="D312" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E312">
         <v>11.0537757639692</v>
@@ -17222,7 +17228,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17236,7 +17242,7 @@
         <v>13.44227382778946</v>
       </c>
       <c r="D313" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E313">
         <v>11.03770193240324</v>
@@ -17272,7 +17278,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17286,7 +17292,7 @@
         <v>13.07333239270363</v>
       </c>
       <c r="D314" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E314">
         <v>11.03770193240324</v>
@@ -17322,7 +17328,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17336,7 +17342,7 @@
         <v>13.47049330154028</v>
       </c>
       <c r="D315" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E315">
         <v>12.2200768479712</v>
@@ -17372,7 +17378,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17386,7 +17392,7 @@
         <v>13.10136247401317</v>
       </c>
       <c r="D316" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E316">
         <v>12.2200768479712</v>
@@ -17422,7 +17428,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17436,7 +17442,7 @@
         <v>13.41024108188445</v>
       </c>
       <c r="D317" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E317">
         <v>11.606966539383</v>
@@ -17472,7 +17478,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17486,7 +17492,7 @@
         <v>13.04151463167046</v>
       </c>
       <c r="D318" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E318">
         <v>11.606966539383</v>
@@ -17522,7 +17528,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17536,7 +17542,7 @@
         <v>15.99098556432473</v>
       </c>
       <c r="D319" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E319">
         <v>12.49688805745362</v>
@@ -17572,7 +17578,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17586,7 +17592,7 @@
         <v>15.82125527263218</v>
       </c>
       <c r="D320" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E320">
         <v>12.49688805745362</v>
@@ -17622,7 +17628,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17636,7 +17642,7 @@
         <v>16.12796689068343</v>
       </c>
       <c r="D321" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E321">
         <v>12.49688805745362</v>
@@ -17672,7 +17678,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17686,7 +17692,7 @@
         <v>16.05759498721028</v>
       </c>
       <c r="D322" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E322">
         <v>12.56617445478137</v>
@@ -17722,7 +17728,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17736,7 +17742,7 @@
         <v>15.8869198810087</v>
       </c>
       <c r="D323" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E323">
         <v>12.56617445478137</v>
@@ -17772,7 +17778,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17786,7 +17792,7 @@
         <v>16.19347402997512</v>
       </c>
       <c r="D324" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E324">
         <v>12.56617445478137</v>
@@ -17822,7 +17828,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -17836,7 +17842,7 @@
         <v>16.08852224791477</v>
       </c>
       <c r="D325" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E325">
         <v>12.59834465504137</v>
@@ -17872,7 +17878,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -17886,7 +17892,7 @@
         <v>15.9174084571642</v>
       </c>
       <c r="D326" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E326">
         <v>12.59834465504137</v>
@@ -17922,7 +17928,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -17936,7 +17942,7 @@
         <v>16.22388949203912</v>
       </c>
       <c r="D327" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E327">
         <v>12.59834465504137</v>
@@ -17972,7 +17978,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17986,7 +17992,7 @@
         <v>15.99827269225045</v>
       </c>
       <c r="D328" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E328">
         <v>12.50446804867659</v>
@@ -18022,7 +18028,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18036,7 +18042,7 @@
         <v>15.82843903704122</v>
       </c>
       <c r="D329" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E329">
         <v>12.50446804867659</v>
@@ -18072,7 +18078,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18086,7 +18092,7 @@
         <v>16.13513342783969</v>
       </c>
       <c r="D330" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E330">
         <v>12.50446804867659</v>
@@ -18122,7 +18128,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18136,7 +18142,7 @@
         <v>10.5571576031199</v>
       </c>
       <c r="D331" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E331">
         <v>11.2357781978979</v>
@@ -18186,7 +18192,7 @@
         <v>10.4146275818384</v>
       </c>
       <c r="D332" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E332">
         <v>11.2357781978979</v>
@@ -18236,7 +18242,7 @@
         <v>11.02395259544049</v>
       </c>
       <c r="D333" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E333">
         <v>11.2357781978979</v>
@@ -18322,7 +18328,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18372,7 +18378,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18422,7 +18428,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -18472,7 +18478,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18522,7 +18528,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18572,7 +18578,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18622,7 +18628,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18672,7 +18678,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18686,7 +18692,7 @@
         <v>7.109582508392513</v>
       </c>
       <c r="D342" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E342">
         <v>10.1191386498793</v>
@@ -18736,7 +18742,7 @@
         <v>8.320739177217412</v>
       </c>
       <c r="D343" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E343">
         <v>10.1191386498793</v>
@@ -18822,7 +18828,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18872,7 +18878,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18886,7 +18892,7 @@
         <v>5.429328338517664</v>
       </c>
       <c r="D346" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E346">
         <v>6.453570540990412</v>
@@ -18922,7 +18928,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18936,7 +18942,7 @@
         <v>4.28114123100805</v>
       </c>
       <c r="D347" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E347">
         <v>5.201857907737669</v>
@@ -18972,7 +18978,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -18986,7 +18992,7 @@
         <v>3.478556159579213</v>
       </c>
       <c r="D348" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E348">
         <v>4.355782779043444</v>
@@ -19022,7 +19028,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19036,7 +19042,7 @@
         <v>2.542133382528917</v>
       </c>
       <c r="D349" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E349">
         <v>3.611162052395251</v>
@@ -19072,7 +19078,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19122,7 +19128,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19136,7 +19142,7 @@
         <v>3.166397470697689</v>
       </c>
       <c r="D351" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E351">
         <v>2.50604388321451</v>
@@ -19172,7 +19178,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19222,7 +19228,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19272,7 +19278,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19322,7 +19328,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19336,7 +19342,7 @@
         <v>0.5258114362592394</v>
       </c>
       <c r="D355" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E355">
         <v>0.9640594525915418</v>
@@ -19372,7 +19378,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19386,7 +19392,7 @@
         <v>1.029412028487577</v>
       </c>
       <c r="D356" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E356">
         <v>0.9640594525915418</v>
@@ -19422,7 +19428,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19436,7 +19442,7 @@
         <v>0.5230738845135647</v>
       </c>
       <c r="D357" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E357">
         <v>0.9640594525915418</v>
@@ -19472,7 +19478,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19486,7 +19492,7 @@
         <v>0.2932995584235911</v>
       </c>
       <c r="D358" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E358">
         <v>-0.2507339019854058</v>
@@ -19522,7 +19528,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19536,7 +19542,7 @@
         <v>0.8110931833932682</v>
       </c>
       <c r="D359" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E359">
         <v>-0.2507339019854058</v>
@@ -19572,7 +19578,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19586,7 +19592,7 @@
         <v>0.3063705065605404</v>
       </c>
       <c r="D360" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E360">
         <v>-0.2507339019854058</v>
@@ -19622,7 +19628,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19636,7 +19642,7 @@
         <v>0.25081902425989</v>
       </c>
       <c r="D361" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E361">
         <v>-1.810462939778127</v>
@@ -19672,7 +19678,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19686,7 +19692,7 @@
         <v>0.7712057537963801</v>
       </c>
       <c r="D362" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E362">
         <v>-1.810462939778127</v>
@@ -19722,7 +19728,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19736,7 +19742,7 @@
         <v>0.266778227076955</v>
       </c>
       <c r="D363" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E363">
         <v>-1.810462939778127</v>
@@ -19772,7 +19778,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19786,7 +19792,7 @@
         <v>0.2555858995649842</v>
       </c>
       <c r="D364" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E364">
         <v>-0.5322733758888774</v>
@@ -19822,7 +19828,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19836,7 +19842,7 @@
         <v>0.7756816486237952</v>
       </c>
       <c r="D365" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E365">
         <v>-0.5322733758888774</v>
@@ -19872,7 +19878,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19886,7 +19892,7 @@
         <v>0.2712210021752028</v>
       </c>
       <c r="D366" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E366">
         <v>-0.5322733758888774</v>
@@ -19922,7 +19928,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19972,7 +19978,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20022,7 +20028,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20072,7 +20078,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20122,7 +20128,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20136,7 +20142,7 @@
         <v>2.068109497945251</v>
       </c>
       <c r="D371" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E371">
         <v>1.103589803610085</v>
@@ -20172,7 +20178,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20186,7 +20192,7 @@
         <v>1.130775764308638</v>
       </c>
       <c r="D372" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E372">
         <v>1.103589803610085</v>
@@ -20222,7 +20228,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20236,7 +20242,7 @@
         <v>1.848060841515313</v>
       </c>
       <c r="D373" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E373">
         <v>0.99412281255767</v>
@@ -20272,7 +20278,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20286,7 +20292,7 @@
         <v>0.9315277271432265</v>
       </c>
       <c r="D374" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E374">
         <v>0.99412281255767</v>
@@ -20322,7 +20328,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20336,7 +20342,7 @@
         <v>1.694201531226533</v>
       </c>
       <c r="D375" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E375">
         <v>0.6700023738905614</v>
@@ -20372,7 +20378,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20386,7 +20392,7 @@
         <v>0.7922123317573622</v>
       </c>
       <c r="D376" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E376">
         <v>0.6700023738905614</v>
@@ -20422,7 +20428,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20436,7 +20442,7 @@
         <v>1.513646695334067</v>
       </c>
       <c r="D377" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E377">
         <v>0.5589534979668187</v>
@@ -20472,7 +20478,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20486,7 +20492,7 @@
         <v>0.6287248684119433</v>
       </c>
       <c r="D378" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E378">
         <v>0.5589534979668187</v>
@@ -20522,7 +20528,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20572,7 +20578,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20622,7 +20628,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20636,7 +20642,7 @@
         <v>1.430312383569088</v>
       </c>
       <c r="D381" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E381">
         <v>2.785832606944602</v>
@@ -20672,7 +20678,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20686,7 +20692,7 @@
         <v>1.015447344707901</v>
       </c>
       <c r="D382" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E382">
         <v>2.785832606944602</v>
@@ -20722,7 +20728,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20736,7 +20742,7 @@
         <v>2.872497404927479</v>
       </c>
       <c r="D383" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E383">
         <v>2.785832606944602</v>
@@ -20772,7 +20778,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20786,7 +20792,7 @@
         <v>1.657667083906176</v>
       </c>
       <c r="D384" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E384">
         <v>3.010263722734074</v>
@@ -20822,7 +20828,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20836,7 +20842,7 @@
         <v>3.082432889417845</v>
       </c>
       <c r="D385" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E385">
         <v>3.010263722734074</v>
@@ -20872,7 +20878,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20886,7 +20892,7 @@
         <v>1.760495757853356</v>
       </c>
       <c r="D386" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E386">
         <v>2.967064908431617</v>
@@ -20922,7 +20928,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20936,7 +20942,7 @@
         <v>3.177383147550167</v>
       </c>
       <c r="D387" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E387">
         <v>2.967064908431617</v>
@@ -20972,7 +20978,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20986,7 +20992,7 @@
         <v>3.419213206004784</v>
       </c>
       <c r="D388" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E388">
         <v>4.96095189349581</v>
@@ -21022,7 +21028,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21036,7 +21042,7 @@
         <v>30.71910142906406</v>
       </c>
       <c r="D389" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E389">
         <v>17.77124839717711</v>
@@ -21072,7 +21078,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21086,7 +21092,7 @@
         <v>30.74457906406285</v>
       </c>
       <c r="D390" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E390">
         <v>18.07805575594424</v>
@@ -21122,7 +21128,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21136,7 +21142,7 @@
         <v>30.94531632533681</v>
       </c>
       <c r="D391" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E391">
         <v>18.41220109884297</v>
@@ -21172,7 +21178,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21186,7 +21192,7 @@
         <v>31.10162189647678</v>
       </c>
       <c r="D392" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E392">
         <v>18.55328210136541</v>
@@ -21222,7 +21228,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21236,7 +21242,7 @@
         <v>31.28406714947664</v>
       </c>
       <c r="D393" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E393">
         <v>18.71795671283931</v>
@@ -21272,7 +21278,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21286,7 +21292,7 @@
         <v>31.41016164358475</v>
       </c>
       <c r="D394" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E394">
         <v>18.83176927570312</v>
@@ -21322,7 +21328,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21336,7 +21342,7 @@
         <v>31.50687459786862</v>
       </c>
       <c r="D395" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E395">
         <v>18.91906213703726</v>
@@ -21372,7 +21378,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21386,7 +21392,7 @@
         <v>31.56465330836859</v>
       </c>
       <c r="D396" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E396">
         <v>18.97121305105996</v>
@@ -21422,7 +21428,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21436,7 +21442,7 @@
         <v>31.59842308925229</v>
       </c>
       <c r="D397" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E397">
         <v>19.00169356757187</v>
@@ -21472,7 +21478,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21486,7 +21492,7 @@
         <v>31.66012131009328</v>
       </c>
       <c r="D398" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E398">
         <v>19.05738222144783</v>
@@ -21522,7 +21528,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21536,7 +21542,7 @@
         <v>31.70713316886447</v>
       </c>
       <c r="D399" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E399">
         <v>19.09981500306598</v>
@@ -21572,7 +21578,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21586,7 +21592,7 @@
         <v>31.87762108191551</v>
       </c>
       <c r="D400" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E400">
         <v>19.25369695056011</v>
@@ -21622,7 +21628,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21636,7 +21642,7 @@
         <v>32.04993923346682</v>
       </c>
       <c r="D401" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E401">
         <v>19.4092308665707</v>
@@ -21672,7 +21678,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21686,7 +21692,7 @@
         <v>32.21080893028861</v>
       </c>
       <c r="D402" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E402">
         <v>19.55443143707868</v>
@@ -21722,7 +21728,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21736,7 +21742,7 @@
         <v>32.44198272920474</v>
       </c>
       <c r="D403" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E403">
         <v>19.76308830752896</v>
@@ -21772,7 +21778,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21786,7 +21792,7 @@
         <v>32.60849165225912</v>
       </c>
       <c r="D404" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E404">
         <v>19.91337882898712</v>
@@ -21822,7 +21828,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21836,7 +21842,7 @@
         <v>32.78872551361854</v>
       </c>
       <c r="D405" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E405">
         <v>20.07605744411025</v>
@@ -21872,7 +21878,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21886,7 +21892,7 @@
         <v>32.88633633076009</v>
       </c>
       <c r="D406" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E406">
         <v>20.16416071412761</v>
@@ -21922,7 +21928,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21936,7 +21942,7 @@
         <v>32.92087256937922</v>
       </c>
       <c r="D407" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E407">
         <v>20.19533303340073</v>
@@ -21972,7 +21978,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21986,7 +21992,7 @@
         <v>33.06269553801688</v>
       </c>
       <c r="D408" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E408">
         <v>20.32334207652173</v>
@@ -22022,7 +22028,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22036,7 +22042,7 @@
         <v>33.22705411164569</v>
       </c>
       <c r="D409" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E409">
         <v>20.4716916981737</v>
@@ -22072,7 +22078,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22086,7 +22092,7 @@
         <v>33.43325315348858</v>
       </c>
       <c r="D410" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E410">
         <v>20.65780641775917</v>
@@ -22122,7 +22128,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22136,7 +22142,7 @@
         <v>33.53120523654898</v>
       </c>
       <c r="D411" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E411">
         <v>20.7462177135085</v>
@@ -22172,7 +22178,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22222,7 +22228,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22236,7 +22242,7 @@
         <v>33.46421187526697</v>
       </c>
       <c r="D413" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E413">
         <v>21.58554463904314</v>
@@ -22272,7 +22278,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22322,7 +22328,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22336,7 +22342,7 @@
         <v>33.20896438389043</v>
       </c>
       <c r="D415" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E415">
         <v>21.35184401382175</v>
@@ -22372,7 +22378,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22386,7 +22392,7 @@
         <v>33.24525244457716</v>
       </c>
       <c r="D416" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E416">
         <v>21.38506879665831</v>
@@ -22436,7 +22442,7 @@
         <v>33.30754061736793</v>
       </c>
       <c r="D417" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E417">
         <v>21.44209887694077</v>
@@ -22472,7 +22478,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22522,7 +22528,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22572,7 +22578,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22622,7 +22628,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22636,7 +22642,7 @@
         <v>33.37808699058778</v>
       </c>
       <c r="D421" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E421">
         <v>21.50669003683685</v>
@@ -22672,7 +22678,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22722,7 +22728,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22772,7 +22778,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22822,7 +22828,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22836,7 +22842,7 @@
         <v>33.3491605949092</v>
       </c>
       <c r="D425" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E425">
         <v>21.48020547975453</v>
@@ -22872,7 +22878,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22922,7 +22928,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22972,7 +22978,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23022,7 +23028,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23036,7 +23042,7 @@
         <v>33.21868761846164</v>
       </c>
       <c r="D429" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E429">
         <v>21.36074645586423</v>
@@ -23072,7 +23078,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23122,7 +23128,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23172,7 +23178,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23222,7 +23228,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23272,7 +23278,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23286,7 +23292,7 @@
         <v>33.10860895395319</v>
       </c>
       <c r="D434" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E434">
         <v>21.25996014615194</v>
@@ -23322,7 +23328,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23372,7 +23378,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23422,7 +23428,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23472,7 +23478,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23486,7 +23492,7 @@
         <v>32.82858702883275</v>
       </c>
       <c r="D438" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E438">
         <v>21.00357643548973</v>
@@ -23522,7 +23528,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23636,7 +23642,7 @@
         <v>32.43391527499527</v>
       </c>
       <c r="D441" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E441">
         <v>20.64222112840476</v>
@@ -23722,7 +23728,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23736,7 +23742,7 @@
         <v>32.1976037826028</v>
       </c>
       <c r="D443" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E443">
         <v>20.42585800874672</v>
@@ -23772,7 +23778,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23786,7 +23792,7 @@
         <v>31.9359757436375</v>
       </c>
       <c r="D444" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E444">
         <v>20.18631545359018</v>
@@ -23822,7 +23828,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23836,7 +23842,7 @@
         <v>31.6928085141255</v>
       </c>
       <c r="D445" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E445">
         <v>19.96367532786815</v>
@@ -23886,7 +23892,7 @@
         <v>31.38607212722557</v>
       </c>
       <c r="D446" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E446">
         <v>19.96017071526525</v>
@@ -23922,7 +23928,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23936,7 +23942,7 @@
         <v>31.09488527318194</v>
       </c>
       <c r="D447" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E447">
         <v>19.69041319680059</v>
@@ -23986,7 +23992,7 @@
         <v>28.76090315089132</v>
       </c>
       <c r="D448" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E448">
         <v>19.57543646755398</v>
@@ -24022,7 +24028,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24036,7 +24042,7 @@
         <v>30.97077487852789</v>
       </c>
       <c r="D449" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E449">
         <v>19.57543646755398</v>
@@ -24072,7 +24078,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24086,7 +24092,7 @@
         <v>28.60148803846228</v>
       </c>
       <c r="D450" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E450">
         <v>19.42949065339434</v>
@@ -24122,7 +24128,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24136,7 +24142,7 @@
         <v>30.81323523800978</v>
       </c>
       <c r="D451" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E451">
         <v>19.42949065339434</v>
@@ -24172,7 +24178,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24186,7 +24192,7 @@
         <v>28.31621253771513</v>
       </c>
       <c r="D452" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E452">
         <v>19.16831864415417</v>
@@ -24222,7 +24228,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24236,7 +24242,7 @@
         <v>30.53131591962436</v>
       </c>
       <c r="D453" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E453">
         <v>19.16831864415417</v>
@@ -24272,7 +24278,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24286,7 +24292,7 @@
         <v>28.17117124931562</v>
       </c>
       <c r="D454" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E454">
         <v>19.16188388044775</v>
@@ -24336,7 +24342,7 @@
         <v>30.52436998310014</v>
       </c>
       <c r="D455" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E455">
         <v>19.16188388044775</v>
@@ -24386,7 +24392,7 @@
         <v>28.43299823269307</v>
       </c>
       <c r="D456" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E456">
         <v>19.40417998614624</v>
@@ -24422,7 +24428,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24436,7 +24442,7 @@
         <v>28.68381801752044</v>
       </c>
       <c r="D457" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E457">
         <v>19.6362899708081</v>
@@ -24486,7 +24492,7 @@
         <v>28.80289710513282</v>
       </c>
       <c r="D458" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E458">
         <v>19.74648640215534</v>
@@ -24522,7 +24528,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24536,7 +24542,7 @@
         <v>28.66069705648685</v>
       </c>
       <c r="D459" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E459">
         <v>19.74648640215534</v>
@@ -24572,7 +24578,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24586,7 +24592,7 @@
         <v>28.92716526228032</v>
       </c>
       <c r="D460" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E460">
         <v>19.86148482649941</v>
@@ -24622,7 +24628,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -24636,7 +24642,7 @@
         <v>28.78241267851456</v>
       </c>
       <c r="D461" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E461">
         <v>19.86148482649941</v>
@@ -24672,7 +24678,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24686,7 +24692,7 @@
         <v>28.69210673371983</v>
       </c>
       <c r="D462" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E462">
         <v>19.64396039358289</v>
@@ -24722,7 +24728,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24736,7 +24742,7 @@
         <v>28.55218237918936</v>
       </c>
       <c r="D463" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E463">
         <v>19.64396039358289</v>
@@ -24772,7 +24778,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24786,7 +24792,7 @@
         <v>24.1238374281487</v>
       </c>
       <c r="D464" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E464">
         <v>15.41645928485977</v>
@@ -24822,7 +24828,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24836,7 +24842,7 @@
         <v>23.88230241564499</v>
       </c>
       <c r="D465" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E465">
         <v>15.41645928485977</v>
@@ -24872,7 +24878,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24886,7 +24892,7 @@
         <v>16.53295008901819</v>
       </c>
       <c r="D466" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E466">
         <v>8.24961705438853</v>
@@ -24936,7 +24942,7 @@
         <v>16.39809781749685</v>
       </c>
       <c r="D467" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E467">
         <v>8.24961705438853</v>
@@ -24986,7 +24992,7 @@
         <v>8.646669450447945</v>
       </c>
       <c r="D468" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E468">
         <v>0.5067815058065008</v>
@@ -25022,7 +25028,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25036,7 +25042,7 @@
         <v>11.10765720787195</v>
       </c>
       <c r="D469" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E469">
         <v>0.5067815058065008</v>
@@ -25072,7 +25078,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25086,7 +25092,7 @@
         <v>8.708207114263224</v>
       </c>
       <c r="D470" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E470">
         <v>0.5067815058065008</v>
@@ -25122,7 +25128,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25136,7 +25142,7 @@
         <v>7.091043911098566</v>
       </c>
       <c r="D471" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E471">
         <v>-0.9493259013959516</v>
@@ -25186,7 +25192,7 @@
         <v>9.494415907805923</v>
       </c>
       <c r="D472" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E472">
         <v>-0.9493259013959516</v>
@@ -25236,7 +25242,7 @@
         <v>7.115916999912343</v>
       </c>
       <c r="D473" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E473">
         <v>-0.9493259013959516</v>
@@ -25286,7 +25292,7 @@
         <v>5.65581229233937</v>
       </c>
       <c r="D474" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E474">
         <v>-2.292741355992099</v>
@@ -25322,7 +25328,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25336,7 +25342,7 @@
         <v>8.006027562426013</v>
       </c>
       <c r="D475" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E475">
         <v>-2.292741355992099</v>
@@ -25372,7 +25378,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25386,7 +25392,7 @@
         <v>5.646858373303601</v>
       </c>
       <c r="D476" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E476">
         <v>-2.292741355992099</v>
@@ -25422,7 +25428,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25436,7 +25442,7 @@
         <v>4.107061890942596</v>
       </c>
       <c r="D477" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E477">
         <v>-3.742413448882012</v>
@@ -25472,7 +25478,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25486,7 +25492,7 @@
         <v>6.399916035051582</v>
       </c>
       <c r="D478" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E478">
         <v>-3.742413448882012</v>
@@ -25522,7 +25528,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -25536,7 +25542,7 @@
         <v>4.061605437193776</v>
       </c>
       <c r="D479" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E479">
         <v>-3.742413448882012</v>
@@ -25572,7 +25578,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -25586,7 +25592,7 @@
         <v>3.994587595705951</v>
       </c>
       <c r="D480" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E480">
         <v>-3.847692418834157</v>
@@ -25622,7 +25628,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -25636,7 +25642,7 @@
         <v>6.283276025176541</v>
       </c>
       <c r="D481" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E481">
         <v>-3.847692418834157</v>
@@ -25672,7 +25678,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -25686,7 +25692,7 @@
         <v>3.94648023264179</v>
       </c>
       <c r="D482" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E482">
         <v>-3.847692418834157</v>
@@ -25722,7 +25728,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -25736,7 +25742,7 @@
         <v>3.810208807303631</v>
       </c>
       <c r="D483" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E483">
         <v>-4.02027593121074</v>
@@ -25786,7 +25792,7 @@
         <v>6.092068392759323</v>
       </c>
       <c r="D484" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E484">
         <v>-4.02027593121074</v>
@@ -25836,7 +25842,7 @@
         <v>3.757755816229981</v>
       </c>
       <c r="D485" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E485">
         <v>-4.02027593121074</v>
@@ -25886,7 +25892,7 @@
         <v>3.242943955180543</v>
       </c>
       <c r="D486" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E486">
         <v>-4.551251112659287</v>
@@ -25936,7 +25942,7 @@
         <v>5.503793731298337</v>
       </c>
       <c r="D487" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E487">
         <v>-4.551251112659287</v>
@@ -25986,7 +25992,7 @@
         <v>3.177121085437328</v>
       </c>
       <c r="D488" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E488">
         <v>-4.551251112659287</v>
@@ -26036,7 +26042,7 @@
         <v>0.5276020656298783</v>
       </c>
       <c r="D489" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E489">
         <v>-7.276209063074127</v>
@@ -26072,7 +26078,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26086,7 +26092,7 @@
         <v>2.687883623616173</v>
       </c>
       <c r="D490" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E490">
         <v>-7.276209063074127</v>
@@ -26122,7 +26128,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26136,7 +26142,7 @@
         <v>0.3977812388938915</v>
       </c>
       <c r="D491" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E491">
         <v>-7.276209063074127</v>
@@ -26172,7 +26178,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26186,7 +26192,7 @@
         <v>-0.0005009764291159513</v>
       </c>
       <c r="D492" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E492">
         <v>-7.771120443679365</v>
@@ -26222,7 +26228,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26236,7 +26242,7 @@
         <v>2.140221209629061</v>
       </c>
       <c r="D493" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E493">
         <v>-7.771120443679365</v>
@@ -26272,7 +26278,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26286,7 +26292,7 @@
         <v>-0.1427686762102667</v>
       </c>
       <c r="D494" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E494">
         <v>-7.771120443679365</v>
@@ -26322,7 +26328,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26336,7 +26342,7 @@
         <v>-0.6951028983788206</v>
       </c>
       <c r="D495" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E495">
         <v>-8.422066128110345</v>
@@ -26372,7 +26378,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26386,7 +26392,7 @@
         <v>1.419893290570108</v>
       </c>
       <c r="D496" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E496">
         <v>-8.422066128110345</v>
@@ -26422,7 +26428,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26436,7 +26442,7 @@
         <v>-0.8537416872294941</v>
       </c>
       <c r="D497" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E497">
         <v>-8.422066128110345</v>
@@ -26472,7 +26478,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26486,7 +26492,7 @@
         <v>-1.098623802898558</v>
       </c>
       <c r="D498" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E498">
         <v>-8.615075478807405</v>
@@ -26522,7 +26528,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26536,7 +26542,7 @@
         <v>1.001427167364454</v>
       </c>
       <c r="D499" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E499">
         <v>-8.615075478807405</v>
@@ -26572,7 +26578,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26586,7 +26592,7 @@
         <v>-1.266773185458455</v>
       </c>
       <c r="D500" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E500">
         <v>-8.615075478807405</v>
@@ -26622,7 +26628,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26636,7 +26642,7 @@
         <v>-1.400997181997106</v>
       </c>
       <c r="D501" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E501">
         <v>-8.898105106381124</v>
@@ -26672,7 +26678,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26686,7 +26692,7 @@
         <v>0.6878547742252223</v>
       </c>
       <c r="D502" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E502">
         <v>-8.898105106381124</v>
@@ -26722,7 +26728,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26736,7 +26742,7 @@
         <v>-1.576273209855614</v>
       </c>
       <c r="D503" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E503">
         <v>-8.898105106381124</v>
@@ -26772,7 +26778,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26786,7 +26792,7 @@
         <v>-1.724593447066837</v>
       </c>
       <c r="D504" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E504">
         <v>-9.200999926884109</v>
@@ -26822,7 +26828,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26836,7 +26842,7 @@
         <v>0.3522734623010564</v>
       </c>
       <c r="D505" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E505">
         <v>-9.200999926884109</v>
@@ -26872,7 +26878,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26886,7 +26892,7 @@
         <v>-1.907496322923627</v>
       </c>
       <c r="D506" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E506">
         <v>-9.200999926884109</v>
@@ -26922,7 +26928,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26936,7 +26942,7 @@
         <v>44.86204822710516</v>
       </c>
       <c r="D507" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E507">
         <v>35.52043652295812</v>
@@ -26972,7 +26978,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26986,7 +26992,7 @@
         <v>46.13402290259216</v>
       </c>
       <c r="D508" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E508">
         <v>36.69877772856216</v>
@@ -27022,7 +27028,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27036,7 +27042,7 @@
         <v>46.08362925847739</v>
       </c>
       <c r="D509" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E509">
         <v>36.69877772856216</v>
@@ -27072,7 +27078,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27086,7 +27092,7 @@
         <v>45.05397872766954</v>
       </c>
       <c r="D510" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E510">
         <v>35.69823850422841</v>
@@ -27122,7 +27128,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27136,7 +27142,7 @@
         <v>44.98156832800709</v>
       </c>
       <c r="D511" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E511">
         <v>35.69823850422841</v>
@@ -27172,7 +27178,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27186,7 +27192,7 @@
         <v>42.5821201676108</v>
       </c>
       <c r="D512" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E512">
         <v>33.77379366345071</v>
@@ -27222,7 +27228,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27236,7 +27242,7 @@
         <v>42.55551239448888</v>
       </c>
       <c r="D513" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E513">
         <v>33.77379366345071</v>
@@ -27272,7 +27278,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27286,7 +27292,7 @@
         <v>42.86185585668593</v>
       </c>
       <c r="D514" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E514">
         <v>33.77379366345071</v>
@@ -27322,7 +27328,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27336,7 +27342,7 @@
         <v>9.729438161046986</v>
       </c>
       <c r="D515" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E515">
         <v>4.60825443961048</v>
@@ -27372,7 +27378,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27386,7 +27392,7 @@
         <v>1.966821409142597</v>
       </c>
       <c r="D516" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E516">
         <v>6.89439153971923</v>
@@ -27422,7 +27428,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27436,7 +27442,7 @@
         <v>1.841930457020688</v>
       </c>
       <c r="D517" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E517">
         <v>6.89439153971923</v>
@@ -27472,7 +27478,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27486,7 +27492,7 @@
         <v>7.54859977610915</v>
       </c>
       <c r="D518" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E518">
         <v>3.585313169516937</v>
@@ -27522,7 +27528,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27536,7 +27542,7 @@
         <v>-0.07307844071422664</v>
       </c>
       <c r="D519" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E519">
         <v>4.928669866220837</v>
@@ -27572,7 +27578,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27586,7 +27592,7 @@
         <v>-0.1707707281713766</v>
       </c>
       <c r="D520" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E520">
         <v>4.928669866220837</v>
@@ -27622,7 +27628,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27633,46 +27639,46 @@
         <v>94</v>
       </c>
       <c r="C521">
-        <v>4.58724487239736</v>
+        <v>-19.34223351080617</v>
       </c>
       <c r="D521" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E521">
-        <v>6.152553191940676</v>
+        <v>-14.93886814413644</v>
       </c>
       <c r="F521">
         <v>1</v>
       </c>
       <c r="G521">
-        <v>0.05259275512760264</v>
+        <v>0.08594223351080617</v>
       </c>
       <c r="H521">
-        <v>0.05548744680805932</v>
+        <v>0.08163886814413644</v>
       </c>
       <c r="I521">
-        <v>1.565308319543316</v>
+        <v>4.403365366669732</v>
       </c>
       <c r="J521">
-        <v>1.846365779046357</v>
+        <v>3.348742589745939</v>
       </c>
       <c r="K521">
-        <v>13</v>
+        <v>15.72</v>
       </c>
       <c r="L521">
-        <v>28.59</v>
+        <v>33.3</v>
       </c>
       <c r="M521">
-        <v>13.36</v>
+        <v>14.42</v>
       </c>
       <c r="N521">
-        <v>30.82</v>
+        <v>33.35</v>
       </c>
       <c r="O521">
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27680,31 +27686,31 @@
         <v>0</v>
       </c>
       <c r="B522" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C522">
-        <v>4.212040637078079</v>
+        <v>4.58724487239736</v>
       </c>
       <c r="D522" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E522">
-        <v>5.839454132623437</v>
+        <v>6.152553191940676</v>
       </c>
       <c r="F522">
         <v>1</v>
       </c>
       <c r="G522">
-        <v>0.05296795936292192</v>
+        <v>0.05259275512760264</v>
       </c>
       <c r="H522">
-        <v>0.05602054586737656</v>
+        <v>0.05548744680805932</v>
       </c>
       <c r="I522">
-        <v>1.627413495545358</v>
+        <v>1.565308319543316</v>
       </c>
       <c r="J522">
-        <v>1.875227643301686</v>
+        <v>1.846365779046357</v>
       </c>
       <c r="K522">
         <v>13</v>
@@ -27713,16 +27719,16 @@
         <v>28.59</v>
       </c>
       <c r="M522">
-        <v>13.38</v>
+        <v>13.36</v>
       </c>
       <c r="N522">
-        <v>30.93</v>
+        <v>30.82</v>
       </c>
       <c r="O522">
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27730,31 +27736,31 @@
         <v>0</v>
       </c>
       <c r="B523" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C523">
-        <v>3.699818204723471</v>
+        <v>4.212040637078079</v>
       </c>
       <c r="D523" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E523">
-        <v>5.615918345535061</v>
+        <v>5.839454132623437</v>
       </c>
       <c r="F523">
         <v>1</v>
       </c>
       <c r="G523">
-        <v>0.05348018179527653</v>
+        <v>0.05296795936292192</v>
       </c>
       <c r="H523">
-        <v>0.05746408165446493</v>
+        <v>0.05602054586737656</v>
       </c>
       <c r="I523">
-        <v>1.91610014081159</v>
+        <v>1.627413495545358</v>
       </c>
       <c r="J523">
-        <v>1.914629368867425</v>
+        <v>1.875227643301686</v>
       </c>
       <c r="K523">
         <v>13</v>
@@ -27763,16 +27769,16 @@
         <v>28.59</v>
       </c>
       <c r="M523">
-        <v>13.54</v>
+        <v>13.38</v>
       </c>
       <c r="N523">
-        <v>31.54</v>
+        <v>30.93</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27783,46 +27789,46 @@
         <v>95</v>
       </c>
       <c r="C524">
-        <v>4.002895527219746</v>
+        <v>3.699818204723471</v>
       </c>
       <c r="D524" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E524">
-        <v>4.187640055392684</v>
+        <v>5.615918345535061</v>
       </c>
       <c r="F524">
         <v>1</v>
       </c>
       <c r="G524">
-        <v>0.05719710447278026</v>
+        <v>0.05348018179527653</v>
       </c>
       <c r="H524">
-        <v>0.05831235994460732</v>
+        <v>0.05746408165446493</v>
       </c>
       <c r="I524">
-        <v>0.1847445281729385</v>
+        <v>1.91610014081159</v>
       </c>
       <c r="J524">
-        <v>1.938564465946083</v>
+        <v>1.914629368867425</v>
       </c>
       <c r="K524">
-        <v>13.72</v>
+        <v>13</v>
       </c>
       <c r="L524">
-        <v>30.6</v>
+        <v>28.59</v>
       </c>
       <c r="M524">
-        <v>13.96</v>
+        <v>13.54</v>
       </c>
       <c r="N524">
-        <v>31.25</v>
+        <v>31.54</v>
       </c>
       <c r="O524">
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27830,16 +27836,16 @@
         <v>0</v>
       </c>
       <c r="B525" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C525">
         <v>3.732407742902605</v>
       </c>
       <c r="D525" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E525">
-        <v>3.9124207063353</v>
+        <v>3.703255119954694</v>
       </c>
       <c r="F525">
         <v>1</v>
@@ -27848,10 +27854,10 @@
         <v>0.0574675922570974</v>
       </c>
       <c r="H525">
-        <v>0.0585875792936647</v>
+        <v>0.05845674488004531</v>
       </c>
       <c r="I525">
-        <v>0.180012963432695</v>
+        <v>-0.02915262294791177</v>
       </c>
       <c r="J525">
         <v>1.958279319030422</v>
@@ -27863,16 +27869,16 @@
         <v>30.6</v>
       </c>
       <c r="M525">
-        <v>13.96</v>
+        <v>13.98</v>
       </c>
       <c r="N525">
-        <v>31.25</v>
+        <v>31.08</v>
       </c>
       <c r="O525">
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -27880,16 +27886,16 @@
         <v>0</v>
       </c>
       <c r="B526" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C526">
         <v>3.563836789836007</v>
       </c>
       <c r="D526" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E526">
-        <v>3.7409009902413</v>
+        <v>3.531489673608405</v>
       </c>
       <c r="F526">
         <v>1</v>
@@ -27898,10 +27904,10 @@
         <v>0.057636163210164</v>
       </c>
       <c r="H526">
-        <v>0.0587590990097587</v>
+        <v>0.0586285103263916</v>
       </c>
       <c r="I526">
-        <v>0.1770642004052938</v>
+        <v>-0.03234711622760145</v>
       </c>
       <c r="J526">
         <v>1.970565831644606</v>
@@ -27913,16 +27919,16 @@
         <v>30.6</v>
       </c>
       <c r="M526">
-        <v>13.96</v>
+        <v>13.98</v>
       </c>
       <c r="N526">
-        <v>31.25</v>
+        <v>31.08</v>
       </c>
       <c r="O526">
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -27930,16 +27936,16 @@
         <v>0</v>
       </c>
       <c r="B527" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C527">
         <v>3.292630819264101</v>
       </c>
       <c r="D527" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E527">
-        <v>3.464950891904291</v>
+        <v>3.25514423129097</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27948,10 +27954,10 @@
         <v>0.0579073691807359</v>
       </c>
       <c r="H527">
-        <v>0.05903504910809571</v>
+        <v>0.05890485576870903</v>
       </c>
       <c r="I527">
-        <v>0.1723200726401899</v>
+        <v>-0.03748658797313098</v>
       </c>
       <c r="J527">
         <v>1.990333030665882</v>
@@ -27963,16 +27969,16 @@
         <v>30.6</v>
       </c>
       <c r="M527">
-        <v>13.96</v>
+        <v>13.98</v>
       </c>
       <c r="N527">
-        <v>31.25</v>
+        <v>31.08</v>
       </c>
       <c r="O527">
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -27980,16 +27986,16 @@
         <v>0</v>
       </c>
       <c r="B528" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C528">
         <v>3.187918659013199</v>
       </c>
       <c r="D528" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E528">
-        <v>3.358407032057158</v>
+        <v>3.148447729810822</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -27998,10 +28004,10 @@
         <v>0.0580120813409868</v>
       </c>
       <c r="H528">
-        <v>0.05914159296794284</v>
+        <v>0.05901155227018917</v>
       </c>
       <c r="I528">
-        <v>0.170488373043959</v>
+        <v>-0.03947092920237694</v>
       </c>
       <c r="J528">
         <v>1.997965112316822</v>
@@ -28013,16 +28019,16 @@
         <v>30.6</v>
       </c>
       <c r="M528">
-        <v>13.96</v>
+        <v>13.98</v>
       </c>
       <c r="N528">
-        <v>31.25</v>
+        <v>31.08</v>
       </c>
       <c r="O528">
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28030,16 +28036,16 @@
         <v>0</v>
       </c>
       <c r="B529" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C529">
         <v>3.095210370074518</v>
       </c>
       <c r="D529" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E529">
-        <v>3.264077023778444</v>
+        <v>3.05398257825377</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -28048,10 +28054,10 @@
         <v>0.05810478962992548</v>
       </c>
       <c r="H529">
-        <v>0.05923592297622156</v>
+        <v>0.05910601742174623</v>
       </c>
       <c r="I529">
-        <v>0.1688666537039261</v>
+        <v>-0.04122779182074865</v>
       </c>
       <c r="J529">
         <v>2.004722276233636</v>
@@ -28063,16 +28069,16 @@
         <v>30.6</v>
       </c>
       <c r="M529">
-        <v>13.96</v>
+        <v>13.98</v>
       </c>
       <c r="N529">
-        <v>31.25</v>
+        <v>31.08</v>
       </c>
       <c r="O529">
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28080,16 +28086,16 @@
         <v>0</v>
       </c>
       <c r="B530" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C530">
         <v>3.067560158467881</v>
       </c>
       <c r="D530" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E530">
-        <v>3.235943135000845</v>
+        <v>3.025808383045259</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28098,10 +28104,10 @@
         <v>0.05813243984153212</v>
       </c>
       <c r="H530">
-        <v>0.05926405686499916</v>
+        <v>0.05913419161695474</v>
       </c>
       <c r="I530">
-        <v>0.1683829765329641</v>
+        <v>-0.04175177542262176</v>
       </c>
       <c r="J530">
         <v>2.006737597779309</v>
@@ -28113,16 +28119,16 @@
         <v>30.6</v>
       </c>
       <c r="M530">
-        <v>13.96</v>
+        <v>13.98</v>
       </c>
       <c r="N530">
-        <v>31.25</v>
+        <v>31.08</v>
       </c>
       <c r="O530">
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -658,7 +658,7 @@
     <t>2021-09-07</t>
   </si>
   <si>
-    <t>2021-10-21</t>
+    <t>2021-10-25</t>
   </si>
   <si>
     <t>2016-05-17</t>
@@ -27598,7 +27598,7 @@
         <v>214</v>
       </c>
       <c r="E520">
-        <v>4.575771324245569</v>
+        <v>4.922433669768001</v>
       </c>
       <c r="F520">
         <v>1</v>
@@ -27607,10 +27607,10 @@
         <v>0.0574675922570974</v>
       </c>
       <c r="H520">
-        <v>0.06050422867575443</v>
+        <v>0.060537566330232</v>
       </c>
       <c r="I520">
-        <v>0.8433635813429632</v>
+        <v>1.190025926865395</v>
       </c>
       <c r="J520">
         <v>1.958279319030422</v>
@@ -27622,10 +27622,10 @@
         <v>30.6</v>
       </c>
       <c r="M520">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N520">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O520">
         <v>1</v>
@@ -27648,7 +27648,7 @@
         <v>214</v>
       </c>
       <c r="E521">
-        <v>4.575771324245569</v>
+        <v>4.922433669768001</v>
       </c>
       <c r="F521">
         <v>1</v>
@@ -27657,10 +27657,10 @@
         <v>0.05845674488004531</v>
       </c>
       <c r="H521">
-        <v>0.06050422867575443</v>
+        <v>0.060537566330232</v>
       </c>
       <c r="I521">
-        <v>0.872516204290875</v>
+        <v>1.219178549813307</v>
       </c>
       <c r="J521">
         <v>1.958279319030422</v>
@@ -27672,10 +27672,10 @@
         <v>31.08</v>
       </c>
       <c r="M521">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N521">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O521">
         <v>1</v>
@@ -27698,7 +27698,7 @@
         <v>214</v>
       </c>
       <c r="E522">
-        <v>4.400319924115028</v>
+        <v>4.747965190646593</v>
       </c>
       <c r="F522">
         <v>1</v>
@@ -27707,10 +27707,10 @@
         <v>0.057636163210164</v>
       </c>
       <c r="H522">
-        <v>0.06067968007588498</v>
+        <v>0.0607120348093534</v>
       </c>
       <c r="I522">
-        <v>0.8364831342790211</v>
+        <v>1.184128400810586</v>
       </c>
       <c r="J522">
         <v>1.970565831644606</v>
@@ -27722,10 +27722,10 @@
         <v>30.6</v>
       </c>
       <c r="M522">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N522">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27748,7 +27748,7 @@
         <v>214</v>
       </c>
       <c r="E523">
-        <v>4.400319924115028</v>
+        <v>4.747965190646593</v>
       </c>
       <c r="F523">
         <v>1</v>
@@ -27757,10 +27757,10 @@
         <v>0.0586285103263916</v>
       </c>
       <c r="H523">
-        <v>0.06067968007588498</v>
+        <v>0.0607120348093534</v>
       </c>
       <c r="I523">
-        <v>0.8688302505066225</v>
+        <v>1.216475517038187</v>
       </c>
       <c r="J523">
         <v>1.970565831644606</v>
@@ -27772,10 +27772,10 @@
         <v>31.08</v>
       </c>
       <c r="M523">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N523">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27798,7 +27798,7 @@
         <v>214</v>
       </c>
       <c r="E524">
-        <v>4.118044322091208</v>
+        <v>4.467270964544479</v>
       </c>
       <c r="F524">
         <v>1</v>
@@ -27807,10 +27807,10 @@
         <v>0.0579073691807359</v>
       </c>
       <c r="H524">
-        <v>0.06096195567790879</v>
+        <v>0.06099272903545551</v>
       </c>
       <c r="I524">
-        <v>0.8254135028271072</v>
+        <v>1.174640145280378</v>
       </c>
       <c r="J524">
         <v>1.990333030665882</v>
@@ -27822,10 +27822,10 @@
         <v>30.6</v>
       </c>
       <c r="M524">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N524">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27848,7 +27848,7 @@
         <v>214</v>
       </c>
       <c r="E525">
-        <v>4.118044322091208</v>
+        <v>4.467270964544479</v>
       </c>
       <c r="F525">
         <v>1</v>
@@ -27857,10 +27857,10 @@
         <v>0.05890485576870903</v>
       </c>
       <c r="H525">
-        <v>0.06096195567790879</v>
+        <v>0.06099272903545551</v>
       </c>
       <c r="I525">
-        <v>0.8629000908002382</v>
+        <v>1.212126733253509</v>
       </c>
       <c r="J525">
         <v>1.990333030665882</v>
@@ -27872,10 +27872,10 @@
         <v>31.08</v>
       </c>
       <c r="M525">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N525">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27898,7 +27898,7 @@
         <v>214</v>
       </c>
       <c r="E526">
-        <v>4.009058196115777</v>
+        <v>4.358895405101123</v>
       </c>
       <c r="F526">
         <v>1</v>
@@ -27907,10 +27907,10 @@
         <v>0.0580120813409868</v>
       </c>
       <c r="H526">
-        <v>0.06107094180388423</v>
+        <v>0.06110110459489887</v>
       </c>
       <c r="I526">
-        <v>0.821139537102578</v>
+        <v>1.170976746087923</v>
       </c>
       <c r="J526">
         <v>1.997965112316822</v>
@@ -27922,10 +27922,10 @@
         <v>30.6</v>
       </c>
       <c r="M526">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N526">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27948,7 +27948,7 @@
         <v>214</v>
       </c>
       <c r="E527">
-        <v>4.009058196115777</v>
+        <v>4.358895405101123</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27957,10 +27957,10 @@
         <v>0.05901155227018917</v>
       </c>
       <c r="H527">
-        <v>0.06107094180388423</v>
+        <v>0.06110110459489887</v>
       </c>
       <c r="I527">
-        <v>0.860610466304955</v>
+        <v>1.2104476752903</v>
       </c>
       <c r="J527">
         <v>1.997965112316822</v>
@@ -27972,10 +27972,10 @@
         <v>31.08</v>
       </c>
       <c r="M527">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N527">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -27998,7 +27998,7 @@
         <v>214</v>
       </c>
       <c r="E528">
-        <v>3.912565895383683</v>
+        <v>4.262943677482372</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -28007,10 +28007,10 @@
         <v>0.05810478962992548</v>
       </c>
       <c r="H528">
-        <v>0.06116743410461632</v>
+        <v>0.06119705632251762</v>
       </c>
       <c r="I528">
-        <v>0.8173555253091642</v>
+        <v>1.167733307407854</v>
       </c>
       <c r="J528">
         <v>2.004722276233636</v>
@@ -28022,10 +28022,10 @@
         <v>30.6</v>
       </c>
       <c r="M528">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N528">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -28048,7 +28048,7 @@
         <v>214</v>
       </c>
       <c r="E529">
-        <v>3.912565895383683</v>
+        <v>4.262943677482372</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -28057,10 +28057,10 @@
         <v>0.05910601742174623</v>
       </c>
       <c r="H529">
-        <v>0.06116743410461632</v>
+        <v>0.06119705632251762</v>
       </c>
       <c r="I529">
-        <v>0.8585833171299129</v>
+        <v>1.208961099228603</v>
       </c>
       <c r="J529">
         <v>2.004722276233636</v>
@@ -28072,10 +28072,10 @@
         <v>31.08</v>
       </c>
       <c r="M529">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N529">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -28098,7 +28098,7 @@
         <v>214</v>
       </c>
       <c r="E530">
-        <v>3.88378710371147</v>
+        <v>4.234326111533811</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28107,10 +28107,10 @@
         <v>0.05813243984153212</v>
       </c>
       <c r="H530">
-        <v>0.06119621289628853</v>
+        <v>0.06122567388846618</v>
       </c>
       <c r="I530">
-        <v>0.8162269452435886</v>
+        <v>1.16676595306593</v>
       </c>
       <c r="J530">
         <v>2.006737597779309</v>
@@ -28122,10 +28122,10 @@
         <v>30.6</v>
       </c>
       <c r="M530">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N530">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28148,7 +28148,7 @@
         <v>214</v>
       </c>
       <c r="E531">
-        <v>3.88378710371147</v>
+        <v>4.234326111533811</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28157,10 +28157,10 @@
         <v>0.05913419161695474</v>
       </c>
       <c r="H531">
-        <v>0.06119621289628853</v>
+        <v>0.06122567388846618</v>
       </c>
       <c r="I531">
-        <v>0.8579787206662104</v>
+        <v>1.208517728488552</v>
       </c>
       <c r="J531">
         <v>2.006737597779309</v>
@@ -28172,10 +28172,10 @@
         <v>31.08</v>
       </c>
       <c r="M531">
-        <v>14.28</v>
+        <v>14.2</v>
       </c>
       <c r="N531">
-        <v>32.54</v>
+        <v>32.73</v>
       </c>
       <c r="O531">
         <v>1</v>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="423">
   <si>
     <t>trade_time</t>
   </si>
@@ -307,12 +307,12 @@
     <t>2021-08-30</t>
   </si>
   <si>
+    <t>2021-10-20</t>
+  </si>
+  <si>
     <t>2021-10-18</t>
   </si>
   <si>
-    <t>2021-10-20</t>
-  </si>
-  <si>
     <t>2016-11-11</t>
   </si>
   <si>
@@ -661,6 +661,9 @@
     <t>2021-10-25</t>
   </si>
   <si>
+    <t>2021-10-26</t>
+  </si>
+  <si>
     <t>2016-05-17</t>
   </si>
   <si>
@@ -1268,6 +1271,9 @@
   </si>
   <si>
     <t>2021-08-27</t>
+  </si>
+  <si>
+    <t>2021-08-31</t>
   </si>
   <si>
     <t>2021-09-03</t>
@@ -1634,7 +1640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P531"/>
+  <dimension ref="A1:P532"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1731,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1781,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1831,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1881,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1931,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1981,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2031,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2081,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2131,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2181,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2231,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2281,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2331,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2381,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2431,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2481,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2531,7 +2537,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2581,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2631,7 +2637,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2681,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2731,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2781,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2831,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2881,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2931,7 +2937,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2981,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3031,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3081,7 +3087,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3131,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3181,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3231,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3281,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3331,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3381,7 +3387,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3431,7 +3437,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3481,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3531,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3581,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3631,7 +3637,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3681,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3731,7 +3737,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3781,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3831,7 +3837,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3881,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3931,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3981,7 +3987,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4031,7 +4037,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4081,7 +4087,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4131,7 +4137,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4181,7 +4187,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4231,7 +4237,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4281,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4331,7 +4337,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4381,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4431,7 +4437,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4481,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4531,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4581,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4631,7 +4637,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4681,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4731,7 +4737,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4781,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4831,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4881,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4931,7 +4937,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4981,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5031,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5081,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5131,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5181,7 +5187,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5231,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5281,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5331,7 +5337,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5381,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5431,7 +5437,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5481,7 +5487,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5531,7 +5537,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5581,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5631,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5681,7 +5687,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5731,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5781,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5831,7 +5837,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5881,7 +5887,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5931,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5981,7 +5987,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6031,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6081,7 +6087,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6131,7 +6137,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6181,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6231,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6281,7 +6287,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6331,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6381,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6431,7 +6437,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6481,7 +6487,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6531,7 +6537,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6581,7 +6587,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6631,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6681,7 +6687,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6731,7 +6737,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6781,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6831,7 +6837,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6881,7 +6887,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6931,7 +6937,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6981,7 +6987,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7031,7 +7037,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7081,7 +7087,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7131,7 +7137,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7181,7 +7187,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7231,7 +7237,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7281,7 +7287,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7331,7 +7337,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7381,7 +7387,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7431,7 +7437,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7581,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7631,7 +7637,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7681,7 +7687,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7731,7 +7737,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7781,7 +7787,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7831,7 +7837,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7881,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7931,7 +7937,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7981,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8031,7 +8037,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8081,7 +8087,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8131,7 +8137,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8181,7 +8187,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8231,7 +8237,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8431,7 +8437,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8481,7 +8487,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8531,7 +8537,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8581,7 +8587,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8631,7 +8637,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8681,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8731,7 +8737,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8781,7 +8787,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8831,7 +8837,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8881,7 +8887,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8931,7 +8937,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8981,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9031,7 +9037,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9081,7 +9087,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9131,7 +9137,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9181,7 +9187,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9231,7 +9237,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9281,7 +9287,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9331,7 +9337,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9381,7 +9387,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9431,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9481,7 +9487,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9531,7 +9537,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9581,7 +9587,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9631,7 +9637,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9681,7 +9687,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9731,7 +9737,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9781,7 +9787,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10081,7 +10087,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10131,7 +10137,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10281,7 +10287,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10331,7 +10337,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10731,7 +10737,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10781,7 +10787,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10831,7 +10837,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10881,7 +10887,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10931,7 +10937,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10981,7 +10987,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11031,7 +11037,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11081,7 +11087,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11131,7 +11137,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11181,7 +11187,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11231,7 +11237,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11281,7 +11287,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11331,7 +11337,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11381,7 +11387,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11831,7 +11837,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11881,7 +11887,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11931,7 +11937,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12131,7 +12137,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12181,7 +12187,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12231,7 +12237,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12281,7 +12287,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12331,7 +12337,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12381,7 +12387,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12431,7 +12437,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12481,7 +12487,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12531,7 +12537,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12581,7 +12587,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12631,7 +12637,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12681,7 +12687,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12731,7 +12737,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12781,7 +12787,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12831,7 +12837,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12881,7 +12887,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12931,7 +12937,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12981,7 +12987,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13031,7 +13037,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13081,7 +13087,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13131,7 +13137,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13181,7 +13187,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13231,7 +13237,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13281,7 +13287,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13331,7 +13337,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13381,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13431,7 +13437,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13481,7 +13487,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13531,7 +13537,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13581,7 +13587,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13631,7 +13637,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13681,7 +13687,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13731,7 +13737,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13781,7 +13787,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13831,7 +13837,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13881,7 +13887,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13931,7 +13937,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13981,7 +13987,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14031,7 +14037,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14081,7 +14087,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14131,7 +14137,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14181,7 +14187,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14231,7 +14237,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14281,7 +14287,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14331,7 +14337,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14381,7 +14387,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14431,7 +14437,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14481,7 +14487,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14531,7 +14537,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14581,7 +14587,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14631,7 +14637,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14681,7 +14687,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14731,7 +14737,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14781,7 +14787,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14831,7 +14837,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15031,7 +15037,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15081,7 +15087,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15131,7 +15137,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15181,7 +15187,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15231,7 +15237,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15281,7 +15287,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15331,7 +15337,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15381,7 +15387,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15431,7 +15437,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15481,7 +15487,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15531,7 +15537,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15581,7 +15587,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15631,7 +15637,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15681,7 +15687,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15731,7 +15737,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15781,7 +15787,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15831,7 +15837,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15881,7 +15887,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15931,7 +15937,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15981,7 +15987,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16031,7 +16037,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16081,7 +16087,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16131,7 +16137,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16181,7 +16187,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16231,7 +16237,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16281,7 +16287,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16331,7 +16337,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16381,7 +16387,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16431,7 +16437,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16481,7 +16487,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16531,7 +16537,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16581,7 +16587,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16631,7 +16637,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16681,7 +16687,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16731,7 +16737,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16781,7 +16787,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16831,7 +16837,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16881,7 +16887,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16931,7 +16937,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16981,7 +16987,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17031,7 +17037,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17081,7 +17087,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17131,7 +17137,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17181,7 +17187,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17231,7 +17237,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17281,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17331,7 +17337,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17381,7 +17387,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17431,7 +17437,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17481,7 +17487,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17531,7 +17537,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17581,7 +17587,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17631,7 +17637,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17681,7 +17687,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17731,7 +17737,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17781,7 +17787,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17831,7 +17837,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18031,7 +18037,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18081,7 +18087,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18131,7 +18137,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18181,7 +18187,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18231,7 +18237,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18281,7 +18287,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18331,7 +18337,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18381,7 +18387,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18531,7 +18537,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18581,7 +18587,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18631,7 +18637,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18681,7 +18687,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18731,7 +18737,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18781,7 +18787,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18831,7 +18837,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18881,7 +18887,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18931,7 +18937,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18981,7 +18987,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19031,7 +19037,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19081,7 +19087,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19131,7 +19137,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19181,7 +19187,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19231,7 +19237,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19281,7 +19287,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19331,7 +19337,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19381,7 +19387,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19431,7 +19437,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19481,7 +19487,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19531,7 +19537,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19581,7 +19587,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19631,7 +19637,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19681,7 +19687,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19731,7 +19737,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19781,7 +19787,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19831,7 +19837,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19881,7 +19887,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19931,7 +19937,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19981,7 +19987,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20031,7 +20037,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20081,7 +20087,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20131,7 +20137,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20181,7 +20187,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20231,7 +20237,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20281,7 +20287,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20331,7 +20337,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20381,7 +20387,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20431,7 +20437,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20481,7 +20487,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20531,7 +20537,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20581,7 +20587,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20631,7 +20637,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20681,7 +20687,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20731,7 +20737,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20781,7 +20787,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20831,7 +20837,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20881,7 +20887,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20931,7 +20937,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20981,7 +20987,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21031,7 +21037,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21081,7 +21087,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21131,7 +21137,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21181,7 +21187,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21231,7 +21237,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21281,7 +21287,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21331,7 +21337,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21381,7 +21387,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21431,7 +21437,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21481,7 +21487,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21531,7 +21537,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21581,7 +21587,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21631,7 +21637,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21681,7 +21687,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21731,7 +21737,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21781,7 +21787,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21831,7 +21837,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21881,7 +21887,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21931,7 +21937,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21981,7 +21987,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22031,7 +22037,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22081,7 +22087,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22181,7 +22187,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22231,7 +22237,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22281,7 +22287,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22331,7 +22337,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22381,7 +22387,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22431,7 +22437,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22481,7 +22487,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22531,7 +22537,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22581,7 +22587,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22631,7 +22637,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22681,7 +22687,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22731,7 +22737,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22781,7 +22787,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22831,7 +22837,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22881,7 +22887,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22931,7 +22937,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22981,7 +22987,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23031,7 +23037,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23081,7 +23087,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23131,7 +23137,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23181,7 +23187,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23231,7 +23237,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23431,7 +23437,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23481,7 +23487,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23531,7 +23537,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23631,7 +23637,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23731,7 +23737,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23781,7 +23787,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23831,7 +23837,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23881,7 +23887,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23931,7 +23937,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23981,7 +23987,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24131,7 +24137,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24231,7 +24237,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24281,7 +24287,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24331,7 +24337,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24381,7 +24387,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24431,7 +24437,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24481,7 +24487,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24531,7 +24537,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24581,7 +24587,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24731,7 +24737,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24781,7 +24787,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24831,7 +24837,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25031,7 +25037,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25081,7 +25087,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25131,7 +25137,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25181,7 +25187,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25231,7 +25237,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25281,7 +25287,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25331,7 +25337,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25381,7 +25387,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25431,7 +25437,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25781,7 +25787,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25831,7 +25837,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25881,7 +25887,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25931,7 +25937,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25981,7 +25987,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26031,7 +26037,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26081,7 +26087,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26131,7 +26137,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26181,7 +26187,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26231,7 +26237,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26281,7 +26287,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26331,7 +26337,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26381,7 +26387,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26431,7 +26437,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26481,7 +26487,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26531,7 +26537,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26581,7 +26587,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26631,7 +26637,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26681,7 +26687,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26731,7 +26737,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26781,7 +26787,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26831,7 +26837,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26881,7 +26887,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26931,7 +26937,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26981,7 +26987,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27031,7 +27037,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27081,7 +27087,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27131,7 +27137,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27181,7 +27187,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27231,7 +27237,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27281,7 +27287,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27331,7 +27337,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27381,7 +27387,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27431,7 +27437,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27481,7 +27487,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27531,7 +27537,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27581,7 +27587,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27592,34 +27598,34 @@
         <v>97</v>
       </c>
       <c r="C520">
-        <v>3.732407742902605</v>
+        <v>3.978868766073763</v>
       </c>
       <c r="D520" t="s">
         <v>214</v>
       </c>
       <c r="E520">
-        <v>4.922433669768001</v>
+        <v>5.202384583565625</v>
       </c>
       <c r="F520">
         <v>1</v>
       </c>
       <c r="G520">
-        <v>0.0574675922570974</v>
+        <v>0.05818113123392624</v>
       </c>
       <c r="H520">
-        <v>0.060537566330232</v>
+        <v>0.06025761541643437</v>
       </c>
       <c r="I520">
-        <v>1.190025926865395</v>
+        <v>1.223515817491862</v>
       </c>
       <c r="J520">
-        <v>1.958279319030422</v>
+        <v>1.938564465946083</v>
       </c>
       <c r="K520">
-        <v>13.72</v>
+        <v>13.98</v>
       </c>
       <c r="L520">
-        <v>30.6</v>
+        <v>31.08</v>
       </c>
       <c r="M520">
         <v>14.2</v>
@@ -27631,18 +27637,18 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>211</v>
+        <v>419</v>
       </c>
     </row>
     <row r="521" spans="1:16">
       <c r="A521" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B521" t="s">
         <v>98</v>
       </c>
       <c r="C521">
-        <v>3.703255119954694</v>
+        <v>3.732407742902605</v>
       </c>
       <c r="D521" t="s">
         <v>214</v>
@@ -27654,22 +27660,22 @@
         <v>1</v>
       </c>
       <c r="G521">
-        <v>0.05845674488004531</v>
+        <v>0.0574675922570974</v>
       </c>
       <c r="H521">
         <v>0.060537566330232</v>
       </c>
       <c r="I521">
-        <v>1.219178549813307</v>
+        <v>1.190025926865395</v>
       </c>
       <c r="J521">
         <v>1.958279319030422</v>
       </c>
       <c r="K521">
-        <v>13.98</v>
+        <v>13.72</v>
       </c>
       <c r="L521">
-        <v>31.08</v>
+        <v>30.6</v>
       </c>
       <c r="M521">
         <v>14.2</v>
@@ -27686,40 +27692,40 @@
     </row>
     <row r="522" spans="1:16">
       <c r="A522" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B522" t="s">
         <v>97</v>
       </c>
       <c r="C522">
-        <v>3.563836789836007</v>
+        <v>3.703255119954694</v>
       </c>
       <c r="D522" t="s">
         <v>214</v>
       </c>
       <c r="E522">
-        <v>4.747965190646593</v>
+        <v>4.922433669768001</v>
       </c>
       <c r="F522">
         <v>1</v>
       </c>
       <c r="G522">
-        <v>0.057636163210164</v>
+        <v>0.05845674488004531</v>
       </c>
       <c r="H522">
-        <v>0.0607120348093534</v>
+        <v>0.060537566330232</v>
       </c>
       <c r="I522">
-        <v>1.184128400810586</v>
+        <v>1.219178549813307</v>
       </c>
       <c r="J522">
-        <v>1.970565831644606</v>
+        <v>1.958279319030422</v>
       </c>
       <c r="K522">
-        <v>13.72</v>
+        <v>13.98</v>
       </c>
       <c r="L522">
-        <v>30.6</v>
+        <v>31.08</v>
       </c>
       <c r="M522">
         <v>14.2</v>
@@ -27731,18 +27737,18 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="523" spans="1:16">
       <c r="A523" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B523" t="s">
         <v>98</v>
       </c>
       <c r="C523">
-        <v>3.531489673608405</v>
+        <v>3.563836789836007</v>
       </c>
       <c r="D523" t="s">
         <v>214</v>
@@ -27754,22 +27760,22 @@
         <v>1</v>
       </c>
       <c r="G523">
-        <v>0.0586285103263916</v>
+        <v>0.057636163210164</v>
       </c>
       <c r="H523">
         <v>0.0607120348093534</v>
       </c>
       <c r="I523">
-        <v>1.216475517038187</v>
+        <v>1.184128400810586</v>
       </c>
       <c r="J523">
         <v>1.970565831644606</v>
       </c>
       <c r="K523">
-        <v>13.98</v>
+        <v>13.72</v>
       </c>
       <c r="L523">
-        <v>31.08</v>
+        <v>30.6</v>
       </c>
       <c r="M523">
         <v>14.2</v>
@@ -27786,40 +27792,40 @@
     </row>
     <row r="524" spans="1:16">
       <c r="A524" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B524" t="s">
         <v>97</v>
       </c>
       <c r="C524">
-        <v>3.292630819264101</v>
+        <v>3.531489673608405</v>
       </c>
       <c r="D524" t="s">
         <v>214</v>
       </c>
       <c r="E524">
-        <v>4.467270964544479</v>
+        <v>4.747965190646593</v>
       </c>
       <c r="F524">
         <v>1</v>
       </c>
       <c r="G524">
-        <v>0.0579073691807359</v>
+        <v>0.0586285103263916</v>
       </c>
       <c r="H524">
-        <v>0.06099272903545551</v>
+        <v>0.0607120348093534</v>
       </c>
       <c r="I524">
-        <v>1.174640145280378</v>
+        <v>1.216475517038187</v>
       </c>
       <c r="J524">
-        <v>1.990333030665882</v>
+        <v>1.970565831644606</v>
       </c>
       <c r="K524">
-        <v>13.72</v>
+        <v>13.98</v>
       </c>
       <c r="L524">
-        <v>30.6</v>
+        <v>31.08</v>
       </c>
       <c r="M524">
         <v>14.2</v>
@@ -27831,251 +27837,251 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>418</v>
+        <v>212</v>
       </c>
     </row>
     <row r="525" spans="1:16">
       <c r="A525" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B525" t="s">
         <v>98</v>
       </c>
       <c r="C525">
-        <v>3.25514423129097</v>
+        <v>3.292630819264101</v>
       </c>
       <c r="D525" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E525">
-        <v>4.467270964544479</v>
+        <v>4.15669094638443</v>
       </c>
       <c r="F525">
         <v>1</v>
       </c>
       <c r="G525">
-        <v>0.05890485576870903</v>
+        <v>0.0579073691807359</v>
       </c>
       <c r="H525">
-        <v>0.06099272903545551</v>
+        <v>0.06044330905361556</v>
       </c>
       <c r="I525">
-        <v>1.212126733253509</v>
+        <v>0.8640601271203288</v>
       </c>
       <c r="J525">
         <v>1.990333030665882</v>
       </c>
       <c r="K525">
-        <v>13.98</v>
+        <v>13.72</v>
       </c>
       <c r="L525">
-        <v>31.08</v>
+        <v>30.6</v>
       </c>
       <c r="M525">
-        <v>14.2</v>
+        <v>14.14</v>
       </c>
       <c r="N525">
-        <v>32.73</v>
+        <v>32.3</v>
       </c>
       <c r="O525">
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="526" spans="1:16">
       <c r="A526" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B526" t="s">
         <v>97</v>
       </c>
       <c r="C526">
-        <v>3.187918659013199</v>
+        <v>3.25514423129097</v>
       </c>
       <c r="D526" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E526">
-        <v>4.358895405101123</v>
+        <v>4.15669094638443</v>
       </c>
       <c r="F526">
         <v>1</v>
       </c>
       <c r="G526">
-        <v>0.0580120813409868</v>
+        <v>0.05890485576870903</v>
       </c>
       <c r="H526">
-        <v>0.06110110459489887</v>
+        <v>0.06044330905361556</v>
       </c>
       <c r="I526">
-        <v>1.170976746087923</v>
+        <v>0.9015467150934597</v>
       </c>
       <c r="J526">
-        <v>1.997965112316822</v>
+        <v>1.990333030665882</v>
       </c>
       <c r="K526">
-        <v>13.72</v>
+        <v>13.98</v>
       </c>
       <c r="L526">
-        <v>30.6</v>
+        <v>31.08</v>
       </c>
       <c r="M526">
-        <v>14.2</v>
+        <v>14.14</v>
       </c>
       <c r="N526">
-        <v>32.73</v>
+        <v>32.3</v>
       </c>
       <c r="O526">
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="527" spans="1:16">
       <c r="A527" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B527" t="s">
         <v>98</v>
       </c>
       <c r="C527">
-        <v>3.148447729810822</v>
+        <v>3.187918659013199</v>
       </c>
       <c r="D527" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E527">
-        <v>4.358895405101123</v>
+        <v>4.048773311840129</v>
       </c>
       <c r="F527">
         <v>1</v>
       </c>
       <c r="G527">
-        <v>0.05901155227018917</v>
+        <v>0.0580120813409868</v>
       </c>
       <c r="H527">
-        <v>0.06110110459489887</v>
+        <v>0.06055122668815987</v>
       </c>
       <c r="I527">
-        <v>1.2104476752903</v>
+        <v>0.8608546528269301</v>
       </c>
       <c r="J527">
         <v>1.997965112316822</v>
       </c>
       <c r="K527">
-        <v>13.98</v>
+        <v>13.72</v>
       </c>
       <c r="L527">
-        <v>31.08</v>
+        <v>30.6</v>
       </c>
       <c r="M527">
-        <v>14.2</v>
+        <v>14.14</v>
       </c>
       <c r="N527">
-        <v>32.73</v>
+        <v>32.3</v>
       </c>
       <c r="O527">
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="528" spans="1:16">
       <c r="A528" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B528" t="s">
         <v>97</v>
       </c>
       <c r="C528">
-        <v>3.095210370074518</v>
+        <v>3.148447729810822</v>
       </c>
       <c r="D528" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E528">
-        <v>4.262943677482372</v>
+        <v>4.048773311840129</v>
       </c>
       <c r="F528">
         <v>1</v>
       </c>
       <c r="G528">
-        <v>0.05810478962992548</v>
+        <v>0.05901155227018917</v>
       </c>
       <c r="H528">
-        <v>0.06119705632251762</v>
+        <v>0.06055122668815987</v>
       </c>
       <c r="I528">
-        <v>1.167733307407854</v>
+        <v>0.900325582029307</v>
       </c>
       <c r="J528">
-        <v>2.004722276233636</v>
+        <v>1.997965112316822</v>
       </c>
       <c r="K528">
-        <v>13.72</v>
+        <v>13.98</v>
       </c>
       <c r="L528">
-        <v>30.6</v>
+        <v>31.08</v>
       </c>
       <c r="M528">
-        <v>14.2</v>
+        <v>14.14</v>
       </c>
       <c r="N528">
-        <v>32.73</v>
+        <v>32.3</v>
       </c>
       <c r="O528">
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>213</v>
+        <v>421</v>
       </c>
     </row>
     <row r="529" spans="1:16">
       <c r="A529" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B529" t="s">
         <v>98</v>
       </c>
       <c r="C529">
-        <v>3.05398257825377</v>
+        <v>3.095210370074518</v>
       </c>
       <c r="D529" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E529">
-        <v>4.262943677482372</v>
+        <v>3.953227014056388</v>
       </c>
       <c r="F529">
         <v>1</v>
       </c>
       <c r="G529">
-        <v>0.05910601742174623</v>
+        <v>0.05810478962992548</v>
       </c>
       <c r="H529">
-        <v>0.06119705632251762</v>
+        <v>0.06064677298594361</v>
       </c>
       <c r="I529">
-        <v>1.208961099228603</v>
+        <v>0.8580166439818697</v>
       </c>
       <c r="J529">
         <v>2.004722276233636</v>
       </c>
       <c r="K529">
-        <v>13.98</v>
+        <v>13.72</v>
       </c>
       <c r="L529">
-        <v>31.08</v>
+        <v>30.6</v>
       </c>
       <c r="M529">
-        <v>14.2</v>
+        <v>14.14</v>
       </c>
       <c r="N529">
-        <v>32.73</v>
+        <v>32.3</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -28086,102 +28092,152 @@
     </row>
     <row r="530" spans="1:16">
       <c r="A530" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B530" t="s">
         <v>97</v>
       </c>
       <c r="C530">
-        <v>3.067560158467881</v>
+        <v>3.05398257825377</v>
       </c>
       <c r="D530" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E530">
-        <v>4.234326111533811</v>
+        <v>3.953227014056388</v>
       </c>
       <c r="F530">
         <v>1</v>
       </c>
       <c r="G530">
-        <v>0.05813243984153212</v>
+        <v>0.05910601742174623</v>
       </c>
       <c r="H530">
-        <v>0.06122567388846618</v>
+        <v>0.06064677298594361</v>
       </c>
       <c r="I530">
-        <v>1.16676595306593</v>
+        <v>0.8992444358026184</v>
       </c>
       <c r="J530">
-        <v>2.006737597779309</v>
+        <v>2.004722276233636</v>
       </c>
       <c r="K530">
-        <v>13.72</v>
+        <v>13.98</v>
       </c>
       <c r="L530">
-        <v>30.6</v>
+        <v>31.08</v>
       </c>
       <c r="M530">
-        <v>14.2</v>
+        <v>14.14</v>
       </c>
       <c r="N530">
-        <v>32.73</v>
+        <v>32.3</v>
       </c>
       <c r="O530">
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>420</v>
+        <v>213</v>
       </c>
     </row>
     <row r="531" spans="1:16">
       <c r="A531" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B531" t="s">
         <v>98</v>
       </c>
       <c r="C531">
-        <v>3.025808383045259</v>
+        <v>3.067560158467881</v>
       </c>
       <c r="D531" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E531">
-        <v>4.234326111533811</v>
+        <v>3.924730367400567</v>
       </c>
       <c r="F531">
         <v>1</v>
       </c>
       <c r="G531">
-        <v>0.05913419161695474</v>
+        <v>0.05813243984153212</v>
       </c>
       <c r="H531">
-        <v>0.06122567388846618</v>
+        <v>0.06067526963259943</v>
       </c>
       <c r="I531">
-        <v>1.208517728488552</v>
+        <v>0.8571702089326863</v>
       </c>
       <c r="J531">
         <v>2.006737597779309</v>
       </c>
       <c r="K531">
+        <v>13.72</v>
+      </c>
+      <c r="L531">
+        <v>30.6</v>
+      </c>
+      <c r="M531">
+        <v>14.14</v>
+      </c>
+      <c r="N531">
+        <v>32.3</v>
+      </c>
+      <c r="O531">
+        <v>1</v>
+      </c>
+      <c r="P531" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="532" spans="1:16">
+      <c r="A532" s="1">
+        <v>1</v>
+      </c>
+      <c r="B532" t="s">
+        <v>97</v>
+      </c>
+      <c r="C532">
+        <v>3.025808383045259</v>
+      </c>
+      <c r="D532" t="s">
+        <v>215</v>
+      </c>
+      <c r="E532">
+        <v>3.924730367400567</v>
+      </c>
+      <c r="F532">
+        <v>1</v>
+      </c>
+      <c r="G532">
+        <v>0.05913419161695474</v>
+      </c>
+      <c r="H532">
+        <v>0.06067526963259943</v>
+      </c>
+      <c r="I532">
+        <v>0.898921984355308</v>
+      </c>
+      <c r="J532">
+        <v>2.006737597779309</v>
+      </c>
+      <c r="K532">
         <v>13.98</v>
       </c>
-      <c r="L531">
+      <c r="L532">
         <v>31.08</v>
       </c>
-      <c r="M531">
-        <v>14.2</v>
-      </c>
-      <c r="N531">
-        <v>32.73</v>
-      </c>
-      <c r="O531">
-        <v>1</v>
-      </c>
-      <c r="P531" t="s">
-        <v>420</v>
+      <c r="M532">
+        <v>14.14</v>
+      </c>
+      <c r="N532">
+        <v>32.3</v>
+      </c>
+      <c r="O532">
+        <v>1</v>
+      </c>
+      <c r="P532" t="s">
+        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -661,7 +661,7 @@
     <t>2021-10-25</t>
   </si>
   <si>
-    <t>2021-10-26</t>
+    <t>2021-10-27</t>
   </si>
   <si>
     <t>2016-05-17</t>
@@ -27851,10 +27851,10 @@
         <v>3.292630819264101</v>
       </c>
       <c r="D525" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E525">
-        <v>4.15669094638443</v>
+        <v>4.467270964544479</v>
       </c>
       <c r="F525">
         <v>1</v>
@@ -27863,10 +27863,10 @@
         <v>0.0579073691807359</v>
       </c>
       <c r="H525">
-        <v>0.06044330905361556</v>
+        <v>0.06099272903545551</v>
       </c>
       <c r="I525">
-        <v>0.8640601271203288</v>
+        <v>1.174640145280378</v>
       </c>
       <c r="J525">
         <v>1.990333030665882</v>
@@ -27878,10 +27878,10 @@
         <v>30.6</v>
       </c>
       <c r="M525">
-        <v>14.14</v>
+        <v>14.2</v>
       </c>
       <c r="N525">
-        <v>32.3</v>
+        <v>32.73</v>
       </c>
       <c r="O525">
         <v>1</v>
@@ -27901,10 +27901,10 @@
         <v>3.25514423129097</v>
       </c>
       <c r="D526" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E526">
-        <v>4.15669094638443</v>
+        <v>4.467270964544479</v>
       </c>
       <c r="F526">
         <v>1</v>
@@ -27913,10 +27913,10 @@
         <v>0.05890485576870903</v>
       </c>
       <c r="H526">
-        <v>0.06044330905361556</v>
+        <v>0.06099272903545551</v>
       </c>
       <c r="I526">
-        <v>0.9015467150934597</v>
+        <v>1.212126733253509</v>
       </c>
       <c r="J526">
         <v>1.990333030665882</v>
@@ -27928,10 +27928,10 @@
         <v>31.08</v>
       </c>
       <c r="M526">
-        <v>14.14</v>
+        <v>14.2</v>
       </c>
       <c r="N526">
-        <v>32.3</v>
+        <v>32.73</v>
       </c>
       <c r="O526">
         <v>1</v>
@@ -27954,7 +27954,7 @@
         <v>215</v>
       </c>
       <c r="E527">
-        <v>4.048773311840129</v>
+        <v>3.95869191633281</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27963,10 +27963,10 @@
         <v>0.0580120813409868</v>
       </c>
       <c r="H527">
-        <v>0.06055122668815987</v>
+        <v>0.0603013080836672</v>
       </c>
       <c r="I527">
-        <v>0.8608546528269301</v>
+        <v>0.7707732573196111</v>
       </c>
       <c r="J527">
         <v>1.997965112316822</v>
@@ -27978,10 +27978,10 @@
         <v>30.6</v>
       </c>
       <c r="M527">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="N527">
-        <v>32.3</v>
+        <v>32.13</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -28004,7 +28004,7 @@
         <v>215</v>
       </c>
       <c r="E528">
-        <v>4.048773311840129</v>
+        <v>3.95869191633281</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -28013,10 +28013,10 @@
         <v>0.05901155227018917</v>
       </c>
       <c r="H528">
-        <v>0.06055122668815987</v>
+        <v>0.0603013080836672</v>
       </c>
       <c r="I528">
-        <v>0.900325582029307</v>
+        <v>0.810244186521988</v>
       </c>
       <c r="J528">
         <v>1.997965112316822</v>
@@ -28028,10 +28028,10 @@
         <v>31.08</v>
       </c>
       <c r="M528">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="N528">
-        <v>32.3</v>
+        <v>32.13</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -28054,7 +28054,7 @@
         <v>215</v>
       </c>
       <c r="E529">
-        <v>3.953227014056388</v>
+        <v>3.86341590510574</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -28063,10 +28063,10 @@
         <v>0.05810478962992548</v>
       </c>
       <c r="H529">
-        <v>0.06064677298594361</v>
+        <v>0.06039658409489427</v>
       </c>
       <c r="I529">
-        <v>0.8580166439818697</v>
+        <v>0.7682055350312211</v>
       </c>
       <c r="J529">
         <v>2.004722276233636</v>
@@ -28078,10 +28078,10 @@
         <v>30.6</v>
       </c>
       <c r="M529">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="N529">
-        <v>32.3</v>
+        <v>32.13</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -28104,7 +28104,7 @@
         <v>215</v>
       </c>
       <c r="E530">
-        <v>3.953227014056388</v>
+        <v>3.86341590510574</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28113,10 +28113,10 @@
         <v>0.05910601742174623</v>
       </c>
       <c r="H530">
-        <v>0.06064677298594361</v>
+        <v>0.06039658409489427</v>
       </c>
       <c r="I530">
-        <v>0.8992444358026184</v>
+        <v>0.8094333268519698</v>
       </c>
       <c r="J530">
         <v>2.004722276233636</v>
@@ -28128,10 +28128,10 @@
         <v>31.08</v>
       </c>
       <c r="M530">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="N530">
-        <v>32.3</v>
+        <v>32.13</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28154,7 +28154,7 @@
         <v>215</v>
       </c>
       <c r="E531">
-        <v>3.924730367400567</v>
+        <v>3.834999871311748</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28163,10 +28163,10 @@
         <v>0.05813243984153212</v>
       </c>
       <c r="H531">
-        <v>0.06067526963259943</v>
+        <v>0.06042500012868825</v>
       </c>
       <c r="I531">
-        <v>0.8571702089326863</v>
+        <v>0.767439712843867</v>
       </c>
       <c r="J531">
         <v>2.006737597779309</v>
@@ -28178,10 +28178,10 @@
         <v>30.6</v>
       </c>
       <c r="M531">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="N531">
-        <v>32.3</v>
+        <v>32.13</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28204,7 +28204,7 @@
         <v>215</v>
       </c>
       <c r="E532">
-        <v>3.924730367400567</v>
+        <v>3.834999871311748</v>
       </c>
       <c r="F532">
         <v>1</v>
@@ -28213,10 +28213,10 @@
         <v>0.05913419161695474</v>
       </c>
       <c r="H532">
-        <v>0.06067526963259943</v>
+        <v>0.06042500012868825</v>
       </c>
       <c r="I532">
-        <v>0.898921984355308</v>
+        <v>0.8091914882664888</v>
       </c>
       <c r="J532">
         <v>2.006737597779309</v>
@@ -28228,10 +28228,10 @@
         <v>31.08</v>
       </c>
       <c r="M532">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="N532">
-        <v>32.3</v>
+        <v>32.13</v>
       </c>
       <c r="O532">
         <v>1</v>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -661,7 +661,7 @@
     <t>2021-10-25</t>
   </si>
   <si>
-    <t>2021-10-27</t>
+    <t>2021-10-28</t>
   </si>
   <si>
     <t>2016-05-17</t>
@@ -27951,10 +27951,10 @@
         <v>3.187918659013199</v>
       </c>
       <c r="D527" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E527">
-        <v>3.95869191633281</v>
+        <v>4.358895405101123</v>
       </c>
       <c r="F527">
         <v>1</v>
@@ -27963,10 +27963,10 @@
         <v>0.0580120813409868</v>
       </c>
       <c r="H527">
-        <v>0.0603013080836672</v>
+        <v>0.06110110459489887</v>
       </c>
       <c r="I527">
-        <v>0.7707732573196111</v>
+        <v>1.170976746087923</v>
       </c>
       <c r="J527">
         <v>1.997965112316822</v>
@@ -27978,10 +27978,10 @@
         <v>30.6</v>
       </c>
       <c r="M527">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="N527">
-        <v>32.13</v>
+        <v>32.73</v>
       </c>
       <c r="O527">
         <v>1</v>
@@ -28001,10 +28001,10 @@
         <v>3.148447729810822</v>
       </c>
       <c r="D528" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E528">
-        <v>3.95869191633281</v>
+        <v>4.358895405101123</v>
       </c>
       <c r="F528">
         <v>1</v>
@@ -28013,10 +28013,10 @@
         <v>0.05901155227018917</v>
       </c>
       <c r="H528">
-        <v>0.0603013080836672</v>
+        <v>0.06110110459489887</v>
       </c>
       <c r="I528">
-        <v>0.810244186521988</v>
+        <v>1.2104476752903</v>
       </c>
       <c r="J528">
         <v>1.997965112316822</v>
@@ -28028,10 +28028,10 @@
         <v>31.08</v>
       </c>
       <c r="M528">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="N528">
-        <v>32.13</v>
+        <v>32.73</v>
       </c>
       <c r="O528">
         <v>1</v>
@@ -28054,7 +28054,7 @@
         <v>215</v>
       </c>
       <c r="E529">
-        <v>3.86341590510574</v>
+        <v>3.833888132729101</v>
       </c>
       <c r="F529">
         <v>1</v>
@@ -28063,10 +28063,10 @@
         <v>0.05810478962992548</v>
       </c>
       <c r="H529">
-        <v>0.06039658409489427</v>
+        <v>0.0599661118672709</v>
       </c>
       <c r="I529">
-        <v>0.7682055350312211</v>
+        <v>0.7386777626545822</v>
       </c>
       <c r="J529">
         <v>2.004722276233636</v>
@@ -28078,10 +28078,10 @@
         <v>30.6</v>
       </c>
       <c r="M529">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="N529">
-        <v>32.13</v>
+        <v>31.9</v>
       </c>
       <c r="O529">
         <v>1</v>
@@ -28104,7 +28104,7 @@
         <v>215</v>
       </c>
       <c r="E530">
-        <v>3.86341590510574</v>
+        <v>3.833888132729101</v>
       </c>
       <c r="F530">
         <v>1</v>
@@ -28113,10 +28113,10 @@
         <v>0.05910601742174623</v>
       </c>
       <c r="H530">
-        <v>0.06039658409489427</v>
+        <v>0.0599661118672709</v>
       </c>
       <c r="I530">
-        <v>0.8094333268519698</v>
+        <v>0.7799055544753308</v>
       </c>
       <c r="J530">
         <v>2.004722276233636</v>
@@ -28128,10 +28128,10 @@
         <v>31.08</v>
       </c>
       <c r="M530">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="N530">
-        <v>32.13</v>
+        <v>31.9</v>
       </c>
       <c r="O530">
         <v>1</v>
@@ -28154,7 +28154,7 @@
         <v>215</v>
       </c>
       <c r="E531">
-        <v>3.834999871311748</v>
+        <v>3.805673631089675</v>
       </c>
       <c r="F531">
         <v>1</v>
@@ -28163,10 +28163,10 @@
         <v>0.05813243984153212</v>
       </c>
       <c r="H531">
-        <v>0.06042500012868825</v>
+        <v>0.05999432636891033</v>
       </c>
       <c r="I531">
-        <v>0.767439712843867</v>
+        <v>0.7381134726217944</v>
       </c>
       <c r="J531">
         <v>2.006737597779309</v>
@@ -28178,10 +28178,10 @@
         <v>30.6</v>
       </c>
       <c r="M531">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="N531">
-        <v>32.13</v>
+        <v>31.9</v>
       </c>
       <c r="O531">
         <v>1</v>
@@ -28204,7 +28204,7 @@
         <v>215</v>
       </c>
       <c r="E532">
-        <v>3.834999871311748</v>
+        <v>3.805673631089675</v>
       </c>
       <c r="F532">
         <v>1</v>
@@ -28213,10 +28213,10 @@
         <v>0.05913419161695474</v>
       </c>
       <c r="H532">
-        <v>0.06042500012868825</v>
+        <v>0.05999432636891033</v>
       </c>
       <c r="I532">
-        <v>0.8091914882664888</v>
+        <v>0.7798652480444161</v>
       </c>
       <c r="J532">
         <v>2.006737597779309</v>
@@ -28228,10 +28228,10 @@
         <v>31.08</v>
       </c>
       <c r="M532">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="N532">
-        <v>32.13</v>
+        <v>31.9</v>
       </c>
       <c r="O532">
         <v>1</v>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="420">
   <si>
     <t>trade_time</t>
   </si>
@@ -304,967 +304,964 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-11-01</t>
+  </si>
+  <si>
+    <t>2021-10-29</t>
+  </si>
+  <si>
+    <t>2016-11-11</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2016-11-10</t>
+  </si>
+  <si>
+    <t>2017-03-22</t>
+  </si>
+  <si>
+    <t>2016-11-03</t>
+  </si>
+  <si>
+    <t>2017-03-23</t>
+  </si>
+  <si>
+    <t>2017-03-24</t>
+  </si>
+  <si>
+    <t>2017-03-27</t>
+  </si>
+  <si>
+    <t>2017-03-28</t>
+  </si>
+  <si>
+    <t>2017-03-29</t>
+  </si>
+  <si>
+    <t>2017-03-30</t>
+  </si>
+  <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
+    <t>2017-04-05</t>
+  </si>
+  <si>
+    <t>2017-04-06</t>
+  </si>
+  <si>
+    <t>2017-04-07</t>
+  </si>
+  <si>
+    <t>2017-04-10</t>
+  </si>
+  <si>
+    <t>2017-04-11</t>
+  </si>
+  <si>
+    <t>2017-02-13</t>
+  </si>
+  <si>
+    <t>2017-04-12</t>
+  </si>
+  <si>
+    <t>2017-04-13</t>
+  </si>
+  <si>
+    <t>2017-04-18</t>
+  </si>
+  <si>
+    <t>2017-04-19</t>
+  </si>
+  <si>
+    <t>2017-04-20</t>
+  </si>
+  <si>
+    <t>2017-04-24</t>
+  </si>
+  <si>
+    <t>2017-04-25</t>
+  </si>
+  <si>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>2016-10-31</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2017-04-28</t>
+  </si>
+  <si>
+    <t>2017-02-23</t>
+  </si>
+  <si>
+    <t>2017-02-24</t>
+  </si>
+  <si>
+    <t>2017-05-08</t>
+  </si>
+  <si>
+    <t>2017-09-11</t>
+  </si>
+  <si>
+    <t>2017-09-12</t>
+  </si>
+  <si>
+    <t>2017-09-13</t>
+  </si>
+  <si>
+    <t>2017-09-14</t>
+  </si>
+  <si>
+    <t>2017-09-15</t>
+  </si>
+  <si>
+    <t>2017-09-18</t>
+  </si>
+  <si>
+    <t>2017-09-19</t>
+  </si>
+  <si>
+    <t>2017-09-20</t>
+  </si>
+  <si>
+    <t>2017-09-21</t>
+  </si>
+  <si>
+    <t>2017-05-05</t>
+  </si>
+  <si>
+    <t>2017-10-16</t>
+  </si>
+  <si>
+    <t>2017-10-17</t>
+  </si>
+  <si>
+    <t>2017-10-18</t>
+  </si>
+  <si>
+    <t>2017-10-19</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
+    <t>2017-11-01</t>
+  </si>
+  <si>
+    <t>2017-11-02</t>
+  </si>
+  <si>
+    <t>2017-11-03</t>
+  </si>
+  <si>
+    <t>2017-11-06</t>
+  </si>
+  <si>
+    <t>2018-01-25</t>
+  </si>
+  <si>
+    <t>2018-01-22</t>
+  </si>
+  <si>
+    <t>2018-01-18</t>
+  </si>
+  <si>
+    <t>2018-01-23</t>
+  </si>
+  <si>
+    <t>2018-07-06</t>
+  </si>
+  <si>
+    <t>2018-07-05</t>
+  </si>
+  <si>
+    <t>2018-06-19</t>
+  </si>
+  <si>
+    <t>2018-01-03</t>
+  </si>
+  <si>
+    <t>2018-01-02</t>
+  </si>
+  <si>
+    <t>2018-02-06</t>
+  </si>
+  <si>
+    <t>2018-08-27</t>
+  </si>
+  <si>
+    <t>2018-08-28</t>
+  </si>
+  <si>
+    <t>2018-08-29</t>
+  </si>
+  <si>
+    <t>2018-08-30</t>
+  </si>
+  <si>
+    <t>2018-09-03</t>
+  </si>
+  <si>
+    <t>2018-09-04</t>
+  </si>
+  <si>
+    <t>2018-09-05</t>
+  </si>
+  <si>
+    <t>2018-09-06</t>
+  </si>
+  <si>
+    <t>2018-09-07</t>
+  </si>
+  <si>
+    <t>2019-01-09</t>
+  </si>
+  <si>
+    <t>2019-03-22</t>
+  </si>
+  <si>
+    <t>2019-03-25</t>
+  </si>
+  <si>
+    <t>2019-05-16</t>
+  </si>
+  <si>
+    <t>2019-05-17</t>
+  </si>
+  <si>
+    <t>2019-05-23</t>
+  </si>
+  <si>
+    <t>2019-05-24</t>
+  </si>
+  <si>
+    <t>2019-05-27</t>
+  </si>
+  <si>
+    <t>2019-05-28</t>
+  </si>
+  <si>
+    <t>2019-05-29</t>
+  </si>
+  <si>
+    <t>2019-05-30</t>
+  </si>
+  <si>
+    <t>2020-01-17</t>
+  </si>
+  <si>
+    <t>2020-08-13</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>2020-08-26</t>
+  </si>
+  <si>
+    <t>2020-08-27</t>
+  </si>
+  <si>
+    <t>2020-08-31</t>
+  </si>
+  <si>
+    <t>2020-09-03</t>
+  </si>
+  <si>
+    <t>2020-09-04</t>
+  </si>
+  <si>
+    <t>2020-09-07</t>
+  </si>
+  <si>
+    <t>2020-09-08</t>
+  </si>
+  <si>
+    <t>2020-09-14</t>
+  </si>
+  <si>
+    <t>2020-09-15</t>
+  </si>
+  <si>
+    <t>2020-09-16</t>
+  </si>
+  <si>
+    <t>2020-09-17</t>
+  </si>
+  <si>
+    <t>2020-09-21</t>
+  </si>
+  <si>
+    <t>2020-09-22</t>
+  </si>
+  <si>
+    <t>2020-09-23</t>
+  </si>
+  <si>
+    <t>2020-09-24</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2020-12-24</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-15</t>
+  </si>
+  <si>
+    <t>2020-12-14</t>
+  </si>
+  <si>
+    <t>2021-02-04</t>
+  </si>
+  <si>
+    <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2021-02-03</t>
+  </si>
+  <si>
+    <t>2021-07-07</t>
+  </si>
+  <si>
+    <t>2021-11-02</t>
+  </si>
+  <si>
+    <t>2016-05-17</t>
+  </si>
+  <si>
+    <t>2016-06-02</t>
+  </si>
+  <si>
+    <t>2016-06-03</t>
+  </si>
+  <si>
+    <t>2016-06-06</t>
+  </si>
+  <si>
+    <t>2016-06-08</t>
+  </si>
+  <si>
+    <t>2016-06-13</t>
+  </si>
+  <si>
+    <t>2016-06-14</t>
+  </si>
+  <si>
+    <t>2016-06-15</t>
+  </si>
+  <si>
+    <t>2016-06-16</t>
+  </si>
+  <si>
+    <t>2016-06-17</t>
+  </si>
+  <si>
+    <t>2016-06-20</t>
+  </si>
+  <si>
+    <t>2016-06-21</t>
+  </si>
+  <si>
+    <t>2016-06-22</t>
+  </si>
+  <si>
+    <t>2016-06-23</t>
+  </si>
+  <si>
+    <t>2016-06-24</t>
+  </si>
+  <si>
+    <t>2016-06-27</t>
+  </si>
+  <si>
+    <t>2016-06-28</t>
+  </si>
+  <si>
+    <t>2016-06-29</t>
+  </si>
+  <si>
+    <t>2016-06-30</t>
+  </si>
+  <si>
+    <t>2016-07-04</t>
+  </si>
+  <si>
+    <t>2016-07-05</t>
+  </si>
+  <si>
+    <t>2016-07-06</t>
+  </si>
+  <si>
+    <t>2016-07-07</t>
+  </si>
+  <si>
+    <t>2016-07-08</t>
+  </si>
+  <si>
+    <t>2016-07-11</t>
+  </si>
+  <si>
+    <t>2016-07-12</t>
+  </si>
+  <si>
+    <t>2016-07-13</t>
+  </si>
+  <si>
+    <t>2016-07-15</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
+    <t>2016-07-21</t>
+  </si>
+  <si>
+    <t>2016-07-28</t>
+  </si>
+  <si>
+    <t>2016-08-01</t>
+  </si>
+  <si>
+    <t>2016-08-05</t>
+  </si>
+  <si>
+    <t>2016-12-09</t>
+  </si>
+  <si>
+    <t>2016-12-12</t>
+  </si>
+  <si>
+    <t>2016-12-13</t>
+  </si>
+  <si>
+    <t>2016-12-14</t>
+  </si>
+  <si>
+    <t>2016-12-15</t>
+  </si>
+  <si>
+    <t>2016-12-16</t>
+  </si>
+  <si>
+    <t>2016-12-19</t>
+  </si>
+  <si>
+    <t>2016-12-20</t>
+  </si>
+  <si>
+    <t>2016-12-21</t>
+  </si>
+  <si>
+    <t>2016-12-22</t>
+  </si>
+  <si>
+    <t>2016-12-23</t>
+  </si>
+  <si>
+    <t>2016-12-28</t>
+  </si>
+  <si>
+    <t>2016-12-29</t>
+  </si>
+  <si>
+    <t>2016-12-30</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-01-10</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-01-13</t>
+  </si>
+  <si>
+    <t>2017-01-24</t>
+  </si>
+  <si>
+    <t>2017-01-25</t>
+  </si>
+  <si>
+    <t>2017-01-26</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-02-06</t>
+  </si>
+  <si>
+    <t>2017-02-08</t>
+  </si>
+  <si>
+    <t>2017-06-01</t>
+  </si>
+  <si>
+    <t>2017-06-02</t>
+  </si>
+  <si>
+    <t>2017-06-05</t>
+  </si>
+  <si>
+    <t>2017-06-06</t>
+  </si>
+  <si>
+    <t>2017-06-07</t>
+  </si>
+  <si>
+    <t>2017-07-20</t>
+  </si>
+  <si>
+    <t>2017-07-21</t>
+  </si>
+  <si>
+    <t>2017-07-24</t>
+  </si>
+  <si>
+    <t>2017-07-31</t>
+  </si>
+  <si>
+    <t>2017-08-28</t>
+  </si>
+  <si>
+    <t>2017-08-31</t>
+  </si>
+  <si>
+    <t>2017-11-07</t>
+  </si>
+  <si>
+    <t>2017-11-08</t>
+  </si>
+  <si>
+    <t>2017-11-09</t>
+  </si>
+  <si>
+    <t>2017-11-10</t>
+  </si>
+  <si>
+    <t>2017-11-16</t>
+  </si>
+  <si>
+    <t>2017-11-21</t>
+  </si>
+  <si>
+    <t>2017-11-22</t>
+  </si>
+  <si>
+    <t>2017-11-23</t>
+  </si>
+  <si>
+    <t>2017-11-24</t>
+  </si>
+  <si>
+    <t>2017-11-27</t>
+  </si>
+  <si>
+    <t>2017-11-28</t>
+  </si>
+  <si>
+    <t>2017-11-29</t>
+  </si>
+  <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
+    <t>2017-12-01</t>
+  </si>
+  <si>
+    <t>2017-12-04</t>
+  </si>
+  <si>
+    <t>2017-12-05</t>
+  </si>
+  <si>
+    <t>2017-12-07</t>
+  </si>
+  <si>
+    <t>2018-04-27</t>
+  </si>
+  <si>
+    <t>2018-05-02</t>
+  </si>
+  <si>
+    <t>2018-05-03</t>
+  </si>
+  <si>
+    <t>2018-05-04</t>
+  </si>
+  <si>
+    <t>2018-05-07</t>
+  </si>
+  <si>
+    <t>2018-05-08</t>
+  </si>
+  <si>
+    <t>2018-05-18</t>
+  </si>
+  <si>
+    <t>2018-05-21</t>
+  </si>
+  <si>
+    <t>2018-05-23</t>
+  </si>
+  <si>
+    <t>2018-05-24</t>
+  </si>
+  <si>
+    <t>2018-05-31</t>
+  </si>
+  <si>
+    <t>2018-06-01</t>
+  </si>
+  <si>
+    <t>2018-06-04</t>
+  </si>
+  <si>
+    <t>2018-06-05</t>
+  </si>
+  <si>
+    <t>2018-06-20</t>
+  </si>
+  <si>
+    <t>2018-06-21</t>
+  </si>
+  <si>
+    <t>2018-08-06</t>
+  </si>
+  <si>
+    <t>2018-08-07</t>
+  </si>
+  <si>
+    <t>2018-08-13</t>
+  </si>
+  <si>
+    <t>2018-08-14</t>
+  </si>
+  <si>
+    <t>2018-08-15</t>
+  </si>
+  <si>
+    <t>2018-08-16</t>
+  </si>
+  <si>
+    <t>2018-08-17</t>
+  </si>
+  <si>
+    <t>2018-08-20</t>
+  </si>
+  <si>
+    <t>2019-06-24</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-06-26</t>
+  </si>
+  <si>
+    <t>2019-06-27</t>
+  </si>
+  <si>
+    <t>2019-11-13</t>
+  </si>
+  <si>
+    <t>2019-11-15</t>
+  </si>
+  <si>
+    <t>2019-11-19</t>
+  </si>
+  <si>
+    <t>2019-11-20</t>
+  </si>
+  <si>
+    <t>2019-11-21</t>
+  </si>
+  <si>
+    <t>2019-11-22</t>
+  </si>
+  <si>
+    <t>2019-11-25</t>
+  </si>
+  <si>
+    <t>2019-11-26</t>
+  </si>
+  <si>
+    <t>2019-11-27</t>
+  </si>
+  <si>
+    <t>2019-11-28</t>
+  </si>
+  <si>
+    <t>2019-11-29</t>
+  </si>
+  <si>
+    <t>2019-12-02</t>
+  </si>
+  <si>
+    <t>2019-12-03</t>
+  </si>
+  <si>
+    <t>2019-12-04</t>
+  </si>
+  <si>
+    <t>2019-12-05</t>
+  </si>
+  <si>
+    <t>2019-12-09</t>
+  </si>
+  <si>
+    <t>2019-12-11</t>
+  </si>
+  <si>
+    <t>2019-12-12</t>
+  </si>
+  <si>
+    <t>2019-12-13</t>
+  </si>
+  <si>
+    <t>2019-12-16</t>
+  </si>
+  <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>2019-12-19</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2019-12-23</t>
+  </si>
+  <si>
+    <t>2020-04-09</t>
+  </si>
+  <si>
+    <t>2020-04-21</t>
+  </si>
+  <si>
+    <t>2020-04-22</t>
+  </si>
+  <si>
+    <t>2020-04-23</t>
+  </si>
+  <si>
+    <t>2020-04-24</t>
+  </si>
+  <si>
+    <t>2020-04-27</t>
+  </si>
+  <si>
+    <t>2020-04-28</t>
+  </si>
+  <si>
+    <t>2020-04-29</t>
+  </si>
+  <si>
+    <t>2020-05-06</t>
+  </si>
+  <si>
+    <t>2020-05-07</t>
+  </si>
+  <si>
+    <t>2020-05-08</t>
+  </si>
+  <si>
+    <t>2020-05-11</t>
+  </si>
+  <si>
+    <t>2020-05-12</t>
+  </si>
+  <si>
+    <t>2020-05-13</t>
+  </si>
+  <si>
+    <t>2020-05-14</t>
+  </si>
+  <si>
+    <t>2020-05-15</t>
+  </si>
+  <si>
+    <t>2020-05-18</t>
+  </si>
+  <si>
+    <t>2020-05-19</t>
+  </si>
+  <si>
+    <t>2020-05-20</t>
+  </si>
+  <si>
+    <t>2020-05-21</t>
+  </si>
+  <si>
+    <t>2020-05-22</t>
+  </si>
+  <si>
+    <t>2020-05-25</t>
+  </si>
+  <si>
+    <t>2020-05-26</t>
+  </si>
+  <si>
+    <t>2020-05-27</t>
+  </si>
+  <si>
+    <t>2020-05-28</t>
+  </si>
+  <si>
+    <t>2020-06-01</t>
+  </si>
+  <si>
+    <t>2020-06-02</t>
+  </si>
+  <si>
+    <t>2020-06-03</t>
+  </si>
+  <si>
+    <t>2020-06-05</t>
+  </si>
+  <si>
+    <t>2020-06-08</t>
+  </si>
+  <si>
+    <t>2020-06-09</t>
+  </si>
+  <si>
+    <t>2020-06-11</t>
+  </si>
+  <si>
+    <t>2020-06-12</t>
+  </si>
+  <si>
+    <t>2020-06-16</t>
+  </si>
+  <si>
+    <t>2020-06-18</t>
+  </si>
+  <si>
+    <t>2020-06-19</t>
+  </si>
+  <si>
+    <t>2020-06-22</t>
+  </si>
+  <si>
+    <t>2020-06-24</t>
+  </si>
+  <si>
+    <t>2020-06-30</t>
+  </si>
+  <si>
+    <t>2020-07-02</t>
+  </si>
+  <si>
+    <t>2020-07-03</t>
+  </si>
+  <si>
+    <t>2020-07-07</t>
+  </si>
+  <si>
+    <t>2020-07-13</t>
+  </si>
+  <si>
+    <t>2020-07-15</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-07-20</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>2020-07-28</t>
+  </si>
+  <si>
+    <t>2020-07-29</t>
+  </si>
+  <si>
+    <t>2020-07-30</t>
+  </si>
+  <si>
+    <t>2020-07-31</t>
+  </si>
+  <si>
+    <t>2020-11-10</t>
+  </si>
+  <si>
+    <t>2020-11-11</t>
+  </si>
+  <si>
+    <t>2020-11-12</t>
+  </si>
+  <si>
+    <t>2020-11-13</t>
+  </si>
+  <si>
+    <t>2020-12-17</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2021-05-31</t>
+  </si>
+  <si>
+    <t>2021-08-27</t>
+  </si>
+  <si>
     <t>2021-08-30</t>
   </si>
   <si>
-    <t>2021-10-29</t>
-  </si>
-  <si>
-    <t>2016-11-11</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2016-11-10</t>
-  </si>
-  <si>
-    <t>2017-03-22</t>
-  </si>
-  <si>
-    <t>2016-11-03</t>
-  </si>
-  <si>
-    <t>2017-03-23</t>
-  </si>
-  <si>
-    <t>2017-03-24</t>
-  </si>
-  <si>
-    <t>2017-03-27</t>
-  </si>
-  <si>
-    <t>2017-03-28</t>
-  </si>
-  <si>
-    <t>2017-03-29</t>
-  </si>
-  <si>
-    <t>2017-03-30</t>
-  </si>
-  <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
-    <t>2017-04-05</t>
-  </si>
-  <si>
-    <t>2017-04-06</t>
-  </si>
-  <si>
-    <t>2017-04-07</t>
-  </si>
-  <si>
-    <t>2017-04-10</t>
-  </si>
-  <si>
-    <t>2017-04-11</t>
-  </si>
-  <si>
-    <t>2017-02-13</t>
-  </si>
-  <si>
-    <t>2017-04-12</t>
-  </si>
-  <si>
-    <t>2017-04-13</t>
-  </si>
-  <si>
-    <t>2017-04-18</t>
-  </si>
-  <si>
-    <t>2017-04-19</t>
-  </si>
-  <si>
-    <t>2017-04-20</t>
-  </si>
-  <si>
-    <t>2017-04-24</t>
-  </si>
-  <si>
-    <t>2017-04-25</t>
-  </si>
-  <si>
-    <t>2017-04-27</t>
-  </si>
-  <si>
-    <t>2016-10-31</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2017-04-28</t>
-  </si>
-  <si>
-    <t>2017-02-23</t>
-  </si>
-  <si>
-    <t>2017-02-24</t>
-  </si>
-  <si>
-    <t>2017-05-08</t>
-  </si>
-  <si>
-    <t>2017-09-11</t>
-  </si>
-  <si>
-    <t>2017-09-12</t>
-  </si>
-  <si>
-    <t>2017-09-13</t>
-  </si>
-  <si>
-    <t>2017-09-14</t>
-  </si>
-  <si>
-    <t>2017-09-15</t>
-  </si>
-  <si>
-    <t>2017-09-18</t>
-  </si>
-  <si>
-    <t>2017-09-19</t>
-  </si>
-  <si>
-    <t>2017-09-20</t>
-  </si>
-  <si>
-    <t>2017-09-21</t>
-  </si>
-  <si>
-    <t>2017-05-05</t>
-  </si>
-  <si>
-    <t>2017-10-16</t>
-  </si>
-  <si>
-    <t>2017-10-17</t>
-  </si>
-  <si>
-    <t>2017-10-18</t>
-  </si>
-  <si>
-    <t>2017-10-19</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
-    <t>2017-11-01</t>
-  </si>
-  <si>
-    <t>2017-11-02</t>
-  </si>
-  <si>
-    <t>2017-11-03</t>
-  </si>
-  <si>
-    <t>2017-11-06</t>
-  </si>
-  <si>
-    <t>2018-01-25</t>
-  </si>
-  <si>
-    <t>2018-01-22</t>
-  </si>
-  <si>
-    <t>2018-01-18</t>
-  </si>
-  <si>
-    <t>2018-01-23</t>
-  </si>
-  <si>
-    <t>2018-07-06</t>
-  </si>
-  <si>
-    <t>2018-07-05</t>
-  </si>
-  <si>
-    <t>2018-06-19</t>
-  </si>
-  <si>
-    <t>2018-01-03</t>
-  </si>
-  <si>
-    <t>2018-01-02</t>
-  </si>
-  <si>
-    <t>2018-02-06</t>
-  </si>
-  <si>
-    <t>2018-08-27</t>
-  </si>
-  <si>
-    <t>2018-08-28</t>
-  </si>
-  <si>
-    <t>2018-08-29</t>
-  </si>
-  <si>
-    <t>2018-08-30</t>
-  </si>
-  <si>
-    <t>2018-09-03</t>
-  </si>
-  <si>
-    <t>2018-09-04</t>
-  </si>
-  <si>
-    <t>2018-09-05</t>
-  </si>
-  <si>
-    <t>2018-09-06</t>
-  </si>
-  <si>
-    <t>2018-09-07</t>
-  </si>
-  <si>
-    <t>2019-01-09</t>
-  </si>
-  <si>
-    <t>2019-03-22</t>
-  </si>
-  <si>
-    <t>2019-03-25</t>
-  </si>
-  <si>
-    <t>2019-05-16</t>
-  </si>
-  <si>
-    <t>2019-05-17</t>
-  </si>
-  <si>
-    <t>2019-05-23</t>
-  </si>
-  <si>
-    <t>2019-05-24</t>
-  </si>
-  <si>
-    <t>2019-05-27</t>
-  </si>
-  <si>
-    <t>2019-05-28</t>
-  </si>
-  <si>
-    <t>2019-05-29</t>
-  </si>
-  <si>
-    <t>2019-05-30</t>
-  </si>
-  <si>
-    <t>2020-01-17</t>
-  </si>
-  <si>
-    <t>2020-08-13</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>2020-08-26</t>
-  </si>
-  <si>
-    <t>2020-08-27</t>
-  </si>
-  <si>
-    <t>2020-08-31</t>
-  </si>
-  <si>
-    <t>2020-09-03</t>
-  </si>
-  <si>
-    <t>2020-09-04</t>
-  </si>
-  <si>
-    <t>2020-09-07</t>
-  </si>
-  <si>
-    <t>2020-09-08</t>
-  </si>
-  <si>
-    <t>2020-09-14</t>
-  </si>
-  <si>
-    <t>2020-09-15</t>
-  </si>
-  <si>
-    <t>2020-09-16</t>
-  </si>
-  <si>
-    <t>2020-09-17</t>
-  </si>
-  <si>
-    <t>2020-09-21</t>
-  </si>
-  <si>
-    <t>2020-09-22</t>
-  </si>
-  <si>
-    <t>2020-09-23</t>
-  </si>
-  <si>
-    <t>2020-09-24</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2020-12-24</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-15</t>
-  </si>
-  <si>
-    <t>2020-12-14</t>
-  </si>
-  <si>
-    <t>2021-02-04</t>
-  </si>
-  <si>
-    <t>2021-05-14</t>
-  </si>
-  <si>
-    <t>2021-02-03</t>
-  </si>
-  <si>
-    <t>2021-07-07</t>
+    <t>2021-08-31</t>
   </si>
   <si>
     <t>2021-09-01</t>
   </si>
   <si>
     <t>2021-09-02</t>
-  </si>
-  <si>
-    <t>2021-11-01</t>
-  </si>
-  <si>
-    <t>2016-05-17</t>
-  </si>
-  <si>
-    <t>2016-06-02</t>
-  </si>
-  <si>
-    <t>2016-06-03</t>
-  </si>
-  <si>
-    <t>2016-06-06</t>
-  </si>
-  <si>
-    <t>2016-06-08</t>
-  </si>
-  <si>
-    <t>2016-06-13</t>
-  </si>
-  <si>
-    <t>2016-06-14</t>
-  </si>
-  <si>
-    <t>2016-06-15</t>
-  </si>
-  <si>
-    <t>2016-06-16</t>
-  </si>
-  <si>
-    <t>2016-06-17</t>
-  </si>
-  <si>
-    <t>2016-06-20</t>
-  </si>
-  <si>
-    <t>2016-06-21</t>
-  </si>
-  <si>
-    <t>2016-06-22</t>
-  </si>
-  <si>
-    <t>2016-06-23</t>
-  </si>
-  <si>
-    <t>2016-06-24</t>
-  </si>
-  <si>
-    <t>2016-06-27</t>
-  </si>
-  <si>
-    <t>2016-06-28</t>
-  </si>
-  <si>
-    <t>2016-06-29</t>
-  </si>
-  <si>
-    <t>2016-06-30</t>
-  </si>
-  <si>
-    <t>2016-07-04</t>
-  </si>
-  <si>
-    <t>2016-07-05</t>
-  </si>
-  <si>
-    <t>2016-07-06</t>
-  </si>
-  <si>
-    <t>2016-07-07</t>
-  </si>
-  <si>
-    <t>2016-07-08</t>
-  </si>
-  <si>
-    <t>2016-07-11</t>
-  </si>
-  <si>
-    <t>2016-07-12</t>
-  </si>
-  <si>
-    <t>2016-07-13</t>
-  </si>
-  <si>
-    <t>2016-07-15</t>
-  </si>
-  <si>
-    <t>2016-07-18</t>
-  </si>
-  <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
-    <t>2016-07-21</t>
-  </si>
-  <si>
-    <t>2016-07-28</t>
-  </si>
-  <si>
-    <t>2016-08-01</t>
-  </si>
-  <si>
-    <t>2016-08-05</t>
-  </si>
-  <si>
-    <t>2016-12-09</t>
-  </si>
-  <si>
-    <t>2016-12-12</t>
-  </si>
-  <si>
-    <t>2016-12-13</t>
-  </si>
-  <si>
-    <t>2016-12-14</t>
-  </si>
-  <si>
-    <t>2016-12-15</t>
-  </si>
-  <si>
-    <t>2016-12-16</t>
-  </si>
-  <si>
-    <t>2016-12-19</t>
-  </si>
-  <si>
-    <t>2016-12-20</t>
-  </si>
-  <si>
-    <t>2016-12-21</t>
-  </si>
-  <si>
-    <t>2016-12-22</t>
-  </si>
-  <si>
-    <t>2016-12-23</t>
-  </si>
-  <si>
-    <t>2016-12-28</t>
-  </si>
-  <si>
-    <t>2016-12-29</t>
-  </si>
-  <si>
-    <t>2016-12-30</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-01-10</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-01-13</t>
-  </si>
-  <si>
-    <t>2017-01-24</t>
-  </si>
-  <si>
-    <t>2017-01-25</t>
-  </si>
-  <si>
-    <t>2017-01-26</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-02-06</t>
-  </si>
-  <si>
-    <t>2017-02-08</t>
-  </si>
-  <si>
-    <t>2017-06-01</t>
-  </si>
-  <si>
-    <t>2017-06-02</t>
-  </si>
-  <si>
-    <t>2017-06-05</t>
-  </si>
-  <si>
-    <t>2017-06-06</t>
-  </si>
-  <si>
-    <t>2017-06-07</t>
-  </si>
-  <si>
-    <t>2017-07-20</t>
-  </si>
-  <si>
-    <t>2017-07-21</t>
-  </si>
-  <si>
-    <t>2017-07-24</t>
-  </si>
-  <si>
-    <t>2017-07-31</t>
-  </si>
-  <si>
-    <t>2017-08-28</t>
-  </si>
-  <si>
-    <t>2017-08-31</t>
-  </si>
-  <si>
-    <t>2017-11-07</t>
-  </si>
-  <si>
-    <t>2017-11-08</t>
-  </si>
-  <si>
-    <t>2017-11-09</t>
-  </si>
-  <si>
-    <t>2017-11-10</t>
-  </si>
-  <si>
-    <t>2017-11-16</t>
-  </si>
-  <si>
-    <t>2017-11-21</t>
-  </si>
-  <si>
-    <t>2017-11-22</t>
-  </si>
-  <si>
-    <t>2017-11-23</t>
-  </si>
-  <si>
-    <t>2017-11-24</t>
-  </si>
-  <si>
-    <t>2017-11-27</t>
-  </si>
-  <si>
-    <t>2017-11-28</t>
-  </si>
-  <si>
-    <t>2017-11-29</t>
-  </si>
-  <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
-    <t>2017-12-01</t>
-  </si>
-  <si>
-    <t>2017-12-04</t>
-  </si>
-  <si>
-    <t>2017-12-05</t>
-  </si>
-  <si>
-    <t>2017-12-07</t>
-  </si>
-  <si>
-    <t>2018-04-27</t>
-  </si>
-  <si>
-    <t>2018-05-02</t>
-  </si>
-  <si>
-    <t>2018-05-03</t>
-  </si>
-  <si>
-    <t>2018-05-04</t>
-  </si>
-  <si>
-    <t>2018-05-07</t>
-  </si>
-  <si>
-    <t>2018-05-08</t>
-  </si>
-  <si>
-    <t>2018-05-18</t>
-  </si>
-  <si>
-    <t>2018-05-21</t>
-  </si>
-  <si>
-    <t>2018-05-23</t>
-  </si>
-  <si>
-    <t>2018-05-24</t>
-  </si>
-  <si>
-    <t>2018-05-31</t>
-  </si>
-  <si>
-    <t>2018-06-01</t>
-  </si>
-  <si>
-    <t>2018-06-04</t>
-  </si>
-  <si>
-    <t>2018-06-05</t>
-  </si>
-  <si>
-    <t>2018-06-20</t>
-  </si>
-  <si>
-    <t>2018-06-21</t>
-  </si>
-  <si>
-    <t>2018-08-06</t>
-  </si>
-  <si>
-    <t>2018-08-07</t>
-  </si>
-  <si>
-    <t>2018-08-13</t>
-  </si>
-  <si>
-    <t>2018-08-14</t>
-  </si>
-  <si>
-    <t>2018-08-15</t>
-  </si>
-  <si>
-    <t>2018-08-16</t>
-  </si>
-  <si>
-    <t>2018-08-17</t>
-  </si>
-  <si>
-    <t>2018-08-20</t>
-  </si>
-  <si>
-    <t>2019-06-24</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-06-26</t>
-  </si>
-  <si>
-    <t>2019-06-27</t>
-  </si>
-  <si>
-    <t>2019-11-13</t>
-  </si>
-  <si>
-    <t>2019-11-15</t>
-  </si>
-  <si>
-    <t>2019-11-19</t>
-  </si>
-  <si>
-    <t>2019-11-20</t>
-  </si>
-  <si>
-    <t>2019-11-21</t>
-  </si>
-  <si>
-    <t>2019-11-22</t>
-  </si>
-  <si>
-    <t>2019-11-25</t>
-  </si>
-  <si>
-    <t>2019-11-26</t>
-  </si>
-  <si>
-    <t>2019-11-27</t>
-  </si>
-  <si>
-    <t>2019-11-28</t>
-  </si>
-  <si>
-    <t>2019-11-29</t>
-  </si>
-  <si>
-    <t>2019-12-02</t>
-  </si>
-  <si>
-    <t>2019-12-03</t>
-  </si>
-  <si>
-    <t>2019-12-04</t>
-  </si>
-  <si>
-    <t>2019-12-05</t>
-  </si>
-  <si>
-    <t>2019-12-09</t>
-  </si>
-  <si>
-    <t>2019-12-11</t>
-  </si>
-  <si>
-    <t>2019-12-12</t>
-  </si>
-  <si>
-    <t>2019-12-13</t>
-  </si>
-  <si>
-    <t>2019-12-16</t>
-  </si>
-  <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
-    <t>2019-12-18</t>
-  </si>
-  <si>
-    <t>2019-12-19</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2019-12-23</t>
-  </si>
-  <si>
-    <t>2020-04-09</t>
-  </si>
-  <si>
-    <t>2020-04-21</t>
-  </si>
-  <si>
-    <t>2020-04-22</t>
-  </si>
-  <si>
-    <t>2020-04-23</t>
-  </si>
-  <si>
-    <t>2020-04-24</t>
-  </si>
-  <si>
-    <t>2020-04-27</t>
-  </si>
-  <si>
-    <t>2020-04-28</t>
-  </si>
-  <si>
-    <t>2020-04-29</t>
-  </si>
-  <si>
-    <t>2020-05-06</t>
-  </si>
-  <si>
-    <t>2020-05-07</t>
-  </si>
-  <si>
-    <t>2020-05-08</t>
-  </si>
-  <si>
-    <t>2020-05-11</t>
-  </si>
-  <si>
-    <t>2020-05-12</t>
-  </si>
-  <si>
-    <t>2020-05-13</t>
-  </si>
-  <si>
-    <t>2020-05-14</t>
-  </si>
-  <si>
-    <t>2020-05-15</t>
-  </si>
-  <si>
-    <t>2020-05-18</t>
-  </si>
-  <si>
-    <t>2020-05-19</t>
-  </si>
-  <si>
-    <t>2020-05-20</t>
-  </si>
-  <si>
-    <t>2020-05-21</t>
-  </si>
-  <si>
-    <t>2020-05-22</t>
-  </si>
-  <si>
-    <t>2020-05-25</t>
-  </si>
-  <si>
-    <t>2020-05-26</t>
-  </si>
-  <si>
-    <t>2020-05-27</t>
-  </si>
-  <si>
-    <t>2020-05-28</t>
-  </si>
-  <si>
-    <t>2020-06-01</t>
-  </si>
-  <si>
-    <t>2020-06-02</t>
-  </si>
-  <si>
-    <t>2020-06-03</t>
-  </si>
-  <si>
-    <t>2020-06-05</t>
-  </si>
-  <si>
-    <t>2020-06-08</t>
-  </si>
-  <si>
-    <t>2020-06-09</t>
-  </si>
-  <si>
-    <t>2020-06-11</t>
-  </si>
-  <si>
-    <t>2020-06-12</t>
-  </si>
-  <si>
-    <t>2020-06-16</t>
-  </si>
-  <si>
-    <t>2020-06-18</t>
-  </si>
-  <si>
-    <t>2020-06-19</t>
-  </si>
-  <si>
-    <t>2020-06-22</t>
-  </si>
-  <si>
-    <t>2020-06-24</t>
-  </si>
-  <si>
-    <t>2020-06-30</t>
-  </si>
-  <si>
-    <t>2020-07-02</t>
-  </si>
-  <si>
-    <t>2020-07-03</t>
-  </si>
-  <si>
-    <t>2020-07-07</t>
-  </si>
-  <si>
-    <t>2020-07-13</t>
-  </si>
-  <si>
-    <t>2020-07-15</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-07-20</t>
-  </si>
-  <si>
-    <t>2020-07-24</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>2020-07-28</t>
-  </si>
-  <si>
-    <t>2020-07-29</t>
-  </si>
-  <si>
-    <t>2020-07-30</t>
-  </si>
-  <si>
-    <t>2020-07-31</t>
-  </si>
-  <si>
-    <t>2020-11-10</t>
-  </si>
-  <si>
-    <t>2020-11-11</t>
-  </si>
-  <si>
-    <t>2020-11-12</t>
-  </si>
-  <si>
-    <t>2020-11-13</t>
-  </si>
-  <si>
-    <t>2020-12-17</t>
-  </si>
-  <si>
-    <t>2020-12-18</t>
-  </si>
-  <si>
-    <t>2021-05-31</t>
-  </si>
-  <si>
-    <t>2021-08-18</t>
-  </si>
-  <si>
-    <t>2021-08-20</t>
-  </si>
-  <si>
-    <t>2021-08-27</t>
-  </si>
-  <si>
-    <t>2021-08-31</t>
   </si>
   <si>
     <t>2021-09-03</t>
@@ -1634,7 +1631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P527"/>
+  <dimension ref="A1:P525"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1731,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1781,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1831,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1881,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1931,7 +1928,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1981,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2031,7 +2028,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2081,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2131,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2181,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2231,7 +2228,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2281,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2331,7 +2328,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2381,7 +2378,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2431,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2481,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2531,7 +2528,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2581,7 +2578,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2631,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2681,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2731,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2781,7 +2778,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2831,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2881,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2931,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2981,7 +2978,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3031,7 +3028,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3081,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3131,7 +3128,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3181,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3231,7 +3228,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3281,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3331,7 +3328,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3381,7 +3378,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3431,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3481,7 +3478,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3531,7 +3528,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3581,7 +3578,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3631,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3681,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3731,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3781,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3831,7 +3828,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3881,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3931,7 +3928,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3981,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4031,7 +4028,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4081,7 +4078,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4131,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4181,7 +4178,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4231,7 +4228,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4281,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4331,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4381,7 +4378,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4431,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4481,7 +4478,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4531,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4581,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4631,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4681,7 +4678,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4731,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4781,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4831,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4881,7 +4878,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4931,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4981,7 +4978,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5031,7 +5028,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5081,7 +5078,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5131,7 +5128,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5181,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5231,7 +5228,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5281,7 +5278,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5331,7 +5328,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5381,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5431,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5481,7 +5478,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5531,7 +5528,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5581,7 +5578,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5631,7 +5628,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5681,7 +5678,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5731,7 +5728,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5781,7 +5778,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5831,7 +5828,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5881,7 +5878,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5931,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5981,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6031,7 +6028,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6081,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6131,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6181,7 +6178,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6231,7 +6228,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6281,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6331,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6381,7 +6378,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6431,7 +6428,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6481,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6531,7 +6528,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6581,7 +6578,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6631,7 +6628,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6681,7 +6678,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6731,7 +6728,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6781,7 +6778,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6831,7 +6828,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6881,7 +6878,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6931,7 +6928,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6981,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7031,7 +7028,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7081,7 +7078,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7131,7 +7128,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7181,7 +7178,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7231,7 +7228,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7281,7 +7278,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7331,7 +7328,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7381,7 +7378,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7431,7 +7428,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7581,7 +7578,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7631,7 +7628,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7681,7 +7678,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7731,7 +7728,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7781,7 +7778,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7831,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7881,7 +7878,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7931,7 +7928,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7981,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -8031,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8081,7 +8078,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8131,7 +8128,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8181,7 +8178,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8231,7 +8228,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8431,7 +8428,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8481,7 +8478,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8531,7 +8528,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8581,7 +8578,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8631,7 +8628,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8681,7 +8678,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8731,7 +8728,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8781,7 +8778,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8831,7 +8828,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8881,7 +8878,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8931,7 +8928,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8981,7 +8978,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9031,7 +9028,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9081,7 +9078,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9131,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9181,7 +9178,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9231,7 +9228,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9281,7 +9278,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9331,7 +9328,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9381,7 +9378,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9431,7 +9428,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9481,7 +9478,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9531,7 +9528,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9581,7 +9578,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9631,7 +9628,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9681,7 +9678,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9731,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9781,7 +9778,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10081,7 +10078,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10131,7 +10128,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10281,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10331,7 +10328,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10731,7 +10728,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10781,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10831,7 +10828,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10881,7 +10878,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10931,7 +10928,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10981,7 +10978,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11031,7 +11028,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11081,7 +11078,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11131,7 +11128,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11181,7 +11178,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11231,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11281,7 +11278,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11331,7 +11328,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11381,7 +11378,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11831,7 +11828,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11881,7 +11878,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11931,7 +11928,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12131,7 +12128,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12181,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12231,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12281,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12331,7 +12328,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12381,7 +12378,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12431,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12481,7 +12478,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12531,7 +12528,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12581,7 +12578,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12631,7 +12628,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12681,7 +12678,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12731,7 +12728,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12781,7 +12778,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12831,7 +12828,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12881,7 +12878,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12931,7 +12928,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12981,7 +12978,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13031,7 +13028,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13081,7 +13078,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13131,7 +13128,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13181,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13231,7 +13228,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13281,7 +13278,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13331,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13381,7 +13378,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13431,7 +13428,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13481,7 +13478,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13531,7 +13528,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13581,7 +13578,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13631,7 +13628,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13681,7 +13678,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13731,7 +13728,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13781,7 +13778,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13831,7 +13828,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13881,7 +13878,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13931,7 +13928,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13981,7 +13978,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14031,7 +14028,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14081,7 +14078,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14131,7 +14128,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14181,7 +14178,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14231,7 +14228,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14281,7 +14278,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14331,7 +14328,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14381,7 +14378,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14431,7 +14428,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14481,7 +14478,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14531,7 +14528,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14581,7 +14578,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14631,7 +14628,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14681,7 +14678,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14731,7 +14728,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14781,7 +14778,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14831,7 +14828,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15031,7 +15028,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15081,7 +15078,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15131,7 +15128,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15181,7 +15178,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15231,7 +15228,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15281,7 +15278,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15331,7 +15328,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15381,7 +15378,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15431,7 +15428,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15481,7 +15478,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15531,7 +15528,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15581,7 +15578,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15631,7 +15628,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15681,7 +15678,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15731,7 +15728,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15781,7 +15778,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15831,7 +15828,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15881,7 +15878,7 @@
         <v>1</v>
       </c>
       <c r="P285" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -15931,7 +15928,7 @@
         <v>1</v>
       </c>
       <c r="P286" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -15981,7 +15978,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16031,7 +16028,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16081,7 +16078,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16131,7 +16128,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16181,7 +16178,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16231,7 +16228,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16281,7 +16278,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16331,7 +16328,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16381,7 +16378,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16431,7 +16428,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16481,7 +16478,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16531,7 +16528,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16581,7 +16578,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16631,7 +16628,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16681,7 +16678,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16731,7 +16728,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16781,7 +16778,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16831,7 +16828,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16881,7 +16878,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16931,7 +16928,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16981,7 +16978,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17031,7 +17028,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17081,7 +17078,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17131,7 +17128,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17181,7 +17178,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17231,7 +17228,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17281,7 +17278,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17331,7 +17328,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17381,7 +17378,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17431,7 +17428,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17481,7 +17478,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17531,7 +17528,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17581,7 +17578,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17631,7 +17628,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17681,7 +17678,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17731,7 +17728,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17781,7 +17778,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17831,7 +17828,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18031,7 +18028,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18081,7 +18078,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18131,7 +18128,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18181,7 +18178,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18231,7 +18228,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18281,7 +18278,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18331,7 +18328,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18381,7 +18378,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -18531,7 +18528,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18581,7 +18578,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18631,7 +18628,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18681,7 +18678,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18731,7 +18728,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18781,7 +18778,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18831,7 +18828,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18881,7 +18878,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -18931,7 +18928,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -18981,7 +18978,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19031,7 +19028,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19081,7 +19078,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19131,7 +19128,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19181,7 +19178,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19231,7 +19228,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19281,7 +19278,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19331,7 +19328,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19381,7 +19378,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19431,7 +19428,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19481,7 +19478,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19531,7 +19528,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19581,7 +19578,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19631,7 +19628,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19681,7 +19678,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19731,7 +19728,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19781,7 +19778,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -19831,7 +19828,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19881,7 +19878,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19931,7 +19928,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19981,7 +19978,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20031,7 +20028,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20081,7 +20078,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20131,7 +20128,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20181,7 +20178,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20231,7 +20228,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20281,7 +20278,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20331,7 +20328,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20381,7 +20378,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20431,7 +20428,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20481,7 +20478,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -20531,7 +20528,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -20581,7 +20578,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20631,7 +20628,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20681,7 +20678,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20731,7 +20728,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20781,7 +20778,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20831,7 +20828,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20881,7 +20878,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20931,7 +20928,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20981,7 +20978,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21031,7 +21028,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21081,7 +21078,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21131,7 +21128,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21181,7 +21178,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21231,7 +21228,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21281,7 +21278,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21331,7 +21328,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21381,7 +21378,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21431,7 +21428,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21481,7 +21478,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21531,7 +21528,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21581,7 +21578,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21631,7 +21628,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21681,7 +21678,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21731,7 +21728,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21781,7 +21778,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21831,7 +21828,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21881,7 +21878,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21931,7 +21928,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21981,7 +21978,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22031,7 +22028,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22081,7 +22078,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22181,7 +22178,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22231,7 +22228,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22281,7 +22278,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22331,7 +22328,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22381,7 +22378,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22431,7 +22428,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22481,7 +22478,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22531,7 +22528,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22581,7 +22578,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -22631,7 +22628,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -22681,7 +22678,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -22731,7 +22728,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -22781,7 +22778,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -22831,7 +22828,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22881,7 +22878,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22931,7 +22928,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22981,7 +22978,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23031,7 +23028,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23081,7 +23078,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23131,7 +23128,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23181,7 +23178,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23231,7 +23228,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23431,7 +23428,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23481,7 +23478,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23531,7 +23528,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -23631,7 +23628,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -23731,7 +23728,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23781,7 +23778,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23831,7 +23828,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23881,7 +23878,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -23931,7 +23928,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -23981,7 +23978,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24131,7 +24128,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24231,7 +24228,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24281,7 +24278,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24331,7 +24328,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24381,7 +24378,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24431,7 +24428,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24481,7 +24478,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -24531,7 +24528,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24581,7 +24578,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -24731,7 +24728,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24781,7 +24778,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24831,7 +24828,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25031,7 +25028,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25081,7 +25078,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25131,7 +25128,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25181,7 +25178,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25231,7 +25228,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25281,7 +25278,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25331,7 +25328,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25381,7 +25378,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25431,7 +25428,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25781,7 +25778,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25831,7 +25828,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25881,7 +25878,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25931,7 +25928,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25981,7 +25978,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26031,7 +26028,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26081,7 +26078,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26131,7 +26128,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26181,7 +26178,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26231,7 +26228,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26281,7 +26278,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26331,7 +26328,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26381,7 +26378,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26431,7 +26428,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26481,7 +26478,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26531,7 +26528,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26581,7 +26578,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26631,7 +26628,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26681,7 +26678,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26731,7 +26728,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26781,7 +26778,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26831,7 +26828,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26881,7 +26878,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26931,7 +26928,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26981,7 +26978,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27031,7 +27028,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27081,7 +27078,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27131,7 +27128,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27181,7 +27178,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27231,7 +27228,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27281,7 +27278,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27331,7 +27328,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27381,7 +27378,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27431,7 +27428,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27442,46 +27439,46 @@
         <v>96</v>
       </c>
       <c r="C517">
-        <v>4.58724487239736</v>
+        <v>3.636162821270968</v>
       </c>
       <c r="D517" t="s">
         <v>210</v>
       </c>
       <c r="E517">
-        <v>6.152553191940676</v>
+        <v>3.242747996025667</v>
       </c>
       <c r="F517">
         <v>1</v>
       </c>
       <c r="G517">
-        <v>0.05259275512760264</v>
+        <v>0.05594383717872903</v>
       </c>
       <c r="H517">
-        <v>0.05548744680805932</v>
+        <v>0.05539725200397433</v>
       </c>
       <c r="I517">
-        <v>1.565308319543316</v>
+        <v>-0.3934148252453014</v>
       </c>
       <c r="J517">
-        <v>1.846365779046357</v>
+        <v>1.914629368867425</v>
       </c>
       <c r="K517">
-        <v>13</v>
+        <v>13.66</v>
       </c>
       <c r="L517">
-        <v>28.59</v>
+        <v>29.79</v>
       </c>
       <c r="M517">
-        <v>13.36</v>
+        <v>13.62</v>
       </c>
       <c r="N517">
-        <v>30.82</v>
+        <v>29.32</v>
       </c>
       <c r="O517">
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27492,46 +27489,46 @@
         <v>96</v>
       </c>
       <c r="C518">
-        <v>4.212040637078079</v>
+        <v>3.54795850797905</v>
       </c>
       <c r="D518" t="s">
         <v>210</v>
       </c>
       <c r="E518">
-        <v>5.766958685489474</v>
+        <v>3.154801967692148</v>
       </c>
       <c r="F518">
         <v>1</v>
       </c>
       <c r="G518">
-        <v>0.05296795936292192</v>
+        <v>0.05603204149202095</v>
       </c>
       <c r="H518">
-        <v>0.05587304131451053</v>
+        <v>0.05548519803230785</v>
       </c>
       <c r="I518">
-        <v>1.554918048411395</v>
+        <v>-0.3931565402869026</v>
       </c>
       <c r="J518">
-        <v>1.875227643301686</v>
+        <v>1.921086492827302</v>
       </c>
       <c r="K518">
-        <v>13</v>
+        <v>13.66</v>
       </c>
       <c r="L518">
-        <v>28.59</v>
+        <v>29.79</v>
       </c>
       <c r="M518">
-        <v>13.36</v>
+        <v>13.62</v>
       </c>
       <c r="N518">
-        <v>30.82</v>
+        <v>29.32</v>
       </c>
       <c r="O518">
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27542,46 +27539,46 @@
         <v>96</v>
       </c>
       <c r="C519">
-        <v>3.699818204723471</v>
+        <v>3.309209395176509</v>
       </c>
       <c r="D519" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E519">
-        <v>5.312259044553848</v>
+        <v>2.916751973814357</v>
       </c>
       <c r="F519">
         <v>1</v>
       </c>
       <c r="G519">
-        <v>0.05348018179527653</v>
+        <v>0.05627079060482349</v>
       </c>
       <c r="H519">
-        <v>0.05654774095544615</v>
+        <v>0.05572324802618565</v>
       </c>
       <c r="I519">
-        <v>1.612440839830377</v>
+        <v>-0.3924574213621526</v>
       </c>
       <c r="J519">
-        <v>1.914629368867425</v>
+        <v>1.938564465946083</v>
       </c>
       <c r="K519">
-        <v>13</v>
+        <v>13.66</v>
       </c>
       <c r="L519">
-        <v>28.59</v>
+        <v>29.79</v>
       </c>
       <c r="M519">
-        <v>13.38</v>
+        <v>13.62</v>
       </c>
       <c r="N519">
-        <v>30.93</v>
+        <v>29.32</v>
       </c>
       <c r="O519">
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -27592,28 +27589,28 @@
         <v>97</v>
       </c>
       <c r="C520">
-        <v>3.750067157261782</v>
+        <v>3.24573243394747</v>
       </c>
       <c r="D520" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E520">
-        <v>3.54795850797905</v>
+        <v>2.648235674805647</v>
       </c>
       <c r="F520">
         <v>1</v>
       </c>
       <c r="G520">
-        <v>0.05584993284273822</v>
+        <v>0.05635426756605253</v>
       </c>
       <c r="H520">
-        <v>0.05603204149202095</v>
+        <v>0.05599176432519436</v>
       </c>
       <c r="I520">
-        <v>-0.2021086492827315</v>
+        <v>-0.5974967591418228</v>
       </c>
       <c r="J520">
-        <v>1.921086492827302</v>
+        <v>1.958279319030422</v>
       </c>
       <c r="K520">
         <v>13.56</v>
@@ -27622,16 +27619,16 @@
         <v>29.8</v>
       </c>
       <c r="M520">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="N520">
-        <v>29.79</v>
+        <v>29.32</v>
       </c>
       <c r="O520">
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>96</v>
+        <v>414</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27642,28 +27639,28 @@
         <v>97</v>
       </c>
       <c r="C521">
-        <v>3.51306584177112</v>
+        <v>3.079127322899144</v>
       </c>
       <c r="D521" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E521">
-        <v>3.309209395176509</v>
+        <v>2.48089337300047</v>
       </c>
       <c r="F521">
         <v>1</v>
       </c>
       <c r="G521">
-        <v>0.05608693415822889</v>
+        <v>0.05652087267710085</v>
       </c>
       <c r="H521">
-        <v>0.05627079060482349</v>
+        <v>0.05615910662699953</v>
       </c>
       <c r="I521">
-        <v>-0.2038564465946102</v>
+        <v>-0.598233949898674</v>
       </c>
       <c r="J521">
-        <v>1.938564465946083</v>
+        <v>1.970565831644606</v>
       </c>
       <c r="K521">
         <v>13.56</v>
@@ -27672,16 +27669,16 @@
         <v>29.8</v>
       </c>
       <c r="M521">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="N521">
-        <v>29.79</v>
+        <v>29.32</v>
       </c>
       <c r="O521">
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -27689,49 +27686,49 @@
         <v>0</v>
       </c>
       <c r="B522" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C522">
-        <v>3.24573243394747</v>
+        <v>2.602050801104053</v>
       </c>
       <c r="D522" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E522">
-        <v>3.039904502044429</v>
+        <v>2.211664122330692</v>
       </c>
       <c r="F522">
         <v>1</v>
       </c>
       <c r="G522">
-        <v>0.05635426756605253</v>
+        <v>0.05697794919889594</v>
       </c>
       <c r="H522">
-        <v>0.05654009549795557</v>
+        <v>0.05642833587766932</v>
       </c>
       <c r="I522">
-        <v>-0.2058279319030412</v>
+        <v>-0.3903866787733605</v>
       </c>
       <c r="J522">
-        <v>1.958279319030422</v>
+        <v>1.990333030665882</v>
       </c>
       <c r="K522">
-        <v>13.56</v>
+        <v>13.66</v>
       </c>
       <c r="L522">
-        <v>29.8</v>
+        <v>29.79</v>
       </c>
       <c r="M522">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="N522">
-        <v>29.79</v>
+        <v>29.32</v>
       </c>
       <c r="O522">
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>210</v>
+        <v>416</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -27739,49 +27736,49 @@
         <v>0</v>
       </c>
       <c r="B523" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C523">
-        <v>3.079127322899144</v>
+        <v>2.497796565752207</v>
       </c>
       <c r="D523" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E523">
-        <v>2.872070739734681</v>
+        <v>2.107715170244884</v>
       </c>
       <c r="F523">
         <v>1</v>
       </c>
       <c r="G523">
-        <v>0.05652087267710085</v>
+        <v>0.05708220343424779</v>
       </c>
       <c r="H523">
-        <v>0.05670792926026532</v>
+        <v>0.05653228482975511</v>
       </c>
       <c r="I523">
-        <v>-0.2070565831644622</v>
+        <v>-0.3900813955073232</v>
       </c>
       <c r="J523">
-        <v>1.970565831644606</v>
+        <v>1.997965112316822</v>
       </c>
       <c r="K523">
-        <v>13.56</v>
+        <v>13.66</v>
       </c>
       <c r="L523">
-        <v>29.8</v>
+        <v>29.79</v>
       </c>
       <c r="M523">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="N523">
-        <v>29.79</v>
+        <v>29.32</v>
       </c>
       <c r="O523">
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>211</v>
+        <v>417</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -27789,49 +27786,49 @@
         <v>0</v>
       </c>
       <c r="B524" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C524">
-        <v>2.811084104170643</v>
+        <v>2.405493706648535</v>
       </c>
       <c r="D524" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E524">
-        <v>2.602050801104053</v>
+        <v>2.015682597697886</v>
       </c>
       <c r="F524">
         <v>1</v>
       </c>
       <c r="G524">
-        <v>0.05678891589582936</v>
+        <v>0.05717450629335146</v>
       </c>
       <c r="H524">
-        <v>0.05697794919889594</v>
+        <v>0.05662431740230212</v>
       </c>
       <c r="I524">
-        <v>-0.2090333030665903</v>
+        <v>-0.3898111089506493</v>
       </c>
       <c r="J524">
-        <v>1.990333030665882</v>
+        <v>2.004722276233636</v>
       </c>
       <c r="K524">
-        <v>13.56</v>
+        <v>13.66</v>
       </c>
       <c r="L524">
-        <v>29.8</v>
+        <v>29.79</v>
       </c>
       <c r="M524">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="N524">
-        <v>29.79</v>
+        <v>29.32</v>
       </c>
       <c r="O524">
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -27839,149 +27836,49 @@
         <v>0</v>
       </c>
       <c r="B525" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C525">
-        <v>2.707593076983891</v>
+        <v>2.377964414334638</v>
       </c>
       <c r="D525" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E525">
-        <v>2.497796565752207</v>
+        <v>1.988233918245815</v>
       </c>
       <c r="F525">
         <v>1</v>
       </c>
       <c r="G525">
-        <v>0.05689240692301611</v>
+        <v>0.05720203558566535</v>
       </c>
       <c r="H525">
-        <v>0.05708220343424779</v>
+        <v>0.05665176608175419</v>
       </c>
       <c r="I525">
-        <v>-0.2097965112316835</v>
+        <v>-0.3897304960888235</v>
       </c>
       <c r="J525">
-        <v>1.997965112316822</v>
+        <v>2.006737597779309</v>
       </c>
       <c r="K525">
-        <v>13.56</v>
+        <v>13.66</v>
       </c>
       <c r="L525">
-        <v>29.8</v>
+        <v>29.79</v>
       </c>
       <c r="M525">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="N525">
-        <v>29.79</v>
+        <v>29.32</v>
       </c>
       <c r="O525">
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="526" spans="1:16">
-      <c r="A526" s="1">
-        <v>0</v>
-      </c>
-      <c r="B526" t="s">
-        <v>97</v>
-      </c>
-      <c r="C526">
-        <v>2.615965934271902</v>
-      </c>
-      <c r="D526" t="s">
-        <v>212</v>
-      </c>
-      <c r="E526">
-        <v>2.405493706648535</v>
-      </c>
-      <c r="F526">
-        <v>1</v>
-      </c>
-      <c r="G526">
-        <v>0.0569840340657281</v>
-      </c>
-      <c r="H526">
-        <v>0.05717450629335146</v>
-      </c>
-      <c r="I526">
-        <v>-0.2104722276233666</v>
-      </c>
-      <c r="J526">
-        <v>2.004722276233636</v>
-      </c>
-      <c r="K526">
-        <v>13.56</v>
-      </c>
-      <c r="L526">
-        <v>29.8</v>
-      </c>
-      <c r="M526">
-        <v>13.66</v>
-      </c>
-      <c r="N526">
-        <v>29.79</v>
-      </c>
-      <c r="O526">
-        <v>1</v>
-      </c>
-      <c r="P526" t="s">
         <v>419</v>
-      </c>
-    </row>
-    <row r="527" spans="1:16">
-      <c r="A527" s="1">
-        <v>0</v>
-      </c>
-      <c r="B527" t="s">
-        <v>97</v>
-      </c>
-      <c r="C527">
-        <v>2.588638174112571</v>
-      </c>
-      <c r="D527" t="s">
-        <v>212</v>
-      </c>
-      <c r="E527">
-        <v>2.377964414334638</v>
-      </c>
-      <c r="F527">
-        <v>1</v>
-      </c>
-      <c r="G527">
-        <v>0.05701136182588744</v>
-      </c>
-      <c r="H527">
-        <v>0.05720203558566535</v>
-      </c>
-      <c r="I527">
-        <v>-0.2106737597779329</v>
-      </c>
-      <c r="J527">
-        <v>2.006737597779309</v>
-      </c>
-      <c r="K527">
-        <v>13.56</v>
-      </c>
-      <c r="L527">
-        <v>29.8</v>
-      </c>
-      <c r="M527">
-        <v>13.66</v>
-      </c>
-      <c r="N527">
-        <v>29.79</v>
-      </c>
-      <c r="O527">
-        <v>1</v>
-      </c>
-      <c r="P527" t="s">
-        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="422">
   <si>
     <t>trade_time</t>
   </si>
@@ -304,12 +304,12 @@
     <t>2021-07-02</t>
   </si>
   <si>
+    <t>2021-11-02</t>
+  </si>
+  <si>
     <t>2021-11-01</t>
   </si>
   <si>
-    <t>2021-10-29</t>
-  </si>
-  <si>
     <t>2016-11-11</t>
   </si>
   <si>
@@ -646,7 +646,7 @@
     <t>2021-07-07</t>
   </si>
   <si>
-    <t>2021-11-02</t>
+    <t>2021-11-03</t>
   </si>
   <si>
     <t>2016-05-17</t>
@@ -1247,6 +1247,12 @@
   </si>
   <si>
     <t>2021-05-31</t>
+  </si>
+  <si>
+    <t>2021-08-18</t>
+  </si>
+  <si>
+    <t>2021-08-20</t>
   </si>
   <si>
     <t>2021-08-27</t>
@@ -1631,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P525"/>
+  <dimension ref="A1:P527"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -27439,40 +27445,40 @@
         <v>96</v>
       </c>
       <c r="C517">
-        <v>3.636162821270968</v>
+        <v>4.172498089388622</v>
       </c>
       <c r="D517" t="s">
         <v>210</v>
       </c>
       <c r="E517">
-        <v>3.242747996025667</v>
+        <v>4.323280036131401</v>
       </c>
       <c r="F517">
         <v>1</v>
       </c>
       <c r="G517">
-        <v>0.05594383717872903</v>
+        <v>0.05446750191061138</v>
       </c>
       <c r="H517">
-        <v>0.05539725200397433</v>
+        <v>0.0543967199638686</v>
       </c>
       <c r="I517">
-        <v>-0.3934148252453014</v>
+        <v>0.1507819467427787</v>
       </c>
       <c r="J517">
-        <v>1.914629368867425</v>
+        <v>1.846365779046357</v>
       </c>
       <c r="K517">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="L517">
-        <v>29.79</v>
+        <v>29.32</v>
       </c>
       <c r="M517">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="N517">
-        <v>29.32</v>
+        <v>29.36</v>
       </c>
       <c r="O517">
         <v>1</v>
@@ -27489,40 +27495,40 @@
         <v>96</v>
       </c>
       <c r="C518">
-        <v>3.54795850797905</v>
+        <v>3.779399498231037</v>
       </c>
       <c r="D518" t="s">
         <v>210</v>
       </c>
       <c r="E518">
-        <v>3.154801967692148</v>
+        <v>3.931913156829136</v>
       </c>
       <c r="F518">
         <v>1</v>
       </c>
       <c r="G518">
-        <v>0.05603204149202095</v>
+        <v>0.05486060050176896</v>
       </c>
       <c r="H518">
-        <v>0.05548519803230785</v>
+        <v>0.05478808684317086</v>
       </c>
       <c r="I518">
-        <v>-0.3931565402869026</v>
+        <v>0.1525136585980995</v>
       </c>
       <c r="J518">
-        <v>1.921086492827302</v>
+        <v>1.875227643301686</v>
       </c>
       <c r="K518">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="L518">
-        <v>29.79</v>
+        <v>29.32</v>
       </c>
       <c r="M518">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="N518">
-        <v>29.32</v>
+        <v>29.36</v>
       </c>
       <c r="O518">
         <v>1</v>
@@ -27539,40 +27545,40 @@
         <v>96</v>
       </c>
       <c r="C519">
-        <v>3.309209395176509</v>
+        <v>3.242747996025667</v>
       </c>
       <c r="D519" t="s">
         <v>210</v>
       </c>
       <c r="E519">
-        <v>2.916751973814357</v>
+        <v>3.397625758157709</v>
       </c>
       <c r="F519">
         <v>1</v>
       </c>
       <c r="G519">
-        <v>0.05627079060482349</v>
+        <v>0.05539725200397433</v>
       </c>
       <c r="H519">
-        <v>0.05572324802618565</v>
+        <v>0.05532237424184229</v>
       </c>
       <c r="I519">
-        <v>-0.3924574213621526</v>
+        <v>0.1548777621320419</v>
       </c>
       <c r="J519">
-        <v>1.938564465946083</v>
+        <v>1.914629368867425</v>
       </c>
       <c r="K519">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="L519">
-        <v>29.79</v>
+        <v>29.32</v>
       </c>
       <c r="M519">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="N519">
-        <v>29.32</v>
+        <v>29.36</v>
       </c>
       <c r="O519">
         <v>1</v>
@@ -27586,43 +27592,43 @@
         <v>0</v>
       </c>
       <c r="B520" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C520">
-        <v>3.24573243394747</v>
+        <v>3.154801967692148</v>
       </c>
       <c r="D520" t="s">
         <v>210</v>
       </c>
       <c r="E520">
-        <v>2.648235674805647</v>
+        <v>3.310067157261781</v>
       </c>
       <c r="F520">
         <v>1</v>
       </c>
       <c r="G520">
-        <v>0.05635426756605253</v>
+        <v>0.05548519803230785</v>
       </c>
       <c r="H520">
-        <v>0.05599176432519436</v>
+        <v>0.05540993284273821</v>
       </c>
       <c r="I520">
-        <v>-0.5974967591418228</v>
+        <v>0.1552651895696329</v>
       </c>
       <c r="J520">
-        <v>1.958279319030422</v>
+        <v>1.921086492827302</v>
       </c>
       <c r="K520">
+        <v>13.62</v>
+      </c>
+      <c r="L520">
+        <v>29.32</v>
+      </c>
+      <c r="M520">
         <v>13.56</v>
       </c>
-      <c r="L520">
-        <v>29.8</v>
-      </c>
-      <c r="M520">
-        <v>13.62</v>
-      </c>
       <c r="N520">
-        <v>29.32</v>
+        <v>29.36</v>
       </c>
       <c r="O520">
         <v>1</v>
@@ -27639,40 +27645,40 @@
         <v>97</v>
       </c>
       <c r="C521">
-        <v>3.079127322899144</v>
+        <v>3.309209395176509</v>
       </c>
       <c r="D521" t="s">
         <v>210</v>
       </c>
       <c r="E521">
-        <v>2.48089337300047</v>
+        <v>3.073065841771118</v>
       </c>
       <c r="F521">
         <v>1</v>
       </c>
       <c r="G521">
-        <v>0.05652087267710085</v>
+        <v>0.05627079060482349</v>
       </c>
       <c r="H521">
-        <v>0.05615910662699953</v>
+        <v>0.05564693415822888</v>
       </c>
       <c r="I521">
-        <v>-0.598233949898674</v>
+        <v>-0.2361435534053911</v>
       </c>
       <c r="J521">
-        <v>1.970565831644606</v>
+        <v>1.938564465946083</v>
       </c>
       <c r="K521">
+        <v>13.66</v>
+      </c>
+      <c r="L521">
+        <v>29.79</v>
+      </c>
+      <c r="M521">
         <v>13.56</v>
       </c>
-      <c r="L521">
-        <v>29.8</v>
-      </c>
-      <c r="M521">
-        <v>13.62</v>
-      </c>
       <c r="N521">
-        <v>29.32</v>
+        <v>29.36</v>
       </c>
       <c r="O521">
         <v>1</v>
@@ -27686,31 +27692,31 @@
         <v>0</v>
       </c>
       <c r="B522" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C522">
-        <v>2.602050801104053</v>
+        <v>3.039904502044429</v>
       </c>
       <c r="D522" t="s">
         <v>210</v>
       </c>
       <c r="E522">
-        <v>2.211664122330692</v>
+        <v>2.805732433947469</v>
       </c>
       <c r="F522">
         <v>1</v>
       </c>
       <c r="G522">
-        <v>0.05697794919889594</v>
+        <v>0.05654009549795557</v>
       </c>
       <c r="H522">
-        <v>0.05642833587766932</v>
+        <v>0.05591426756605253</v>
       </c>
       <c r="I522">
-        <v>-0.3903866787733605</v>
+        <v>-0.2341720680969601</v>
       </c>
       <c r="J522">
-        <v>1.990333030665882</v>
+        <v>1.958279319030422</v>
       </c>
       <c r="K522">
         <v>13.66</v>
@@ -27719,10 +27725,10 @@
         <v>29.79</v>
       </c>
       <c r="M522">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="N522">
-        <v>29.32</v>
+        <v>29.36</v>
       </c>
       <c r="O522">
         <v>1</v>
@@ -27736,31 +27742,31 @@
         <v>0</v>
       </c>
       <c r="B523" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C523">
-        <v>2.497796565752207</v>
+        <v>2.872070739734681</v>
       </c>
       <c r="D523" t="s">
         <v>210</v>
       </c>
       <c r="E523">
-        <v>2.107715170244884</v>
+        <v>2.639127322899142</v>
       </c>
       <c r="F523">
         <v>1</v>
       </c>
       <c r="G523">
-        <v>0.05708220343424779</v>
+        <v>0.05670792926026532</v>
       </c>
       <c r="H523">
-        <v>0.05653228482975511</v>
+        <v>0.05608087267710086</v>
       </c>
       <c r="I523">
-        <v>-0.3900813955073232</v>
+        <v>-0.2329434168355391</v>
       </c>
       <c r="J523">
-        <v>1.997965112316822</v>
+        <v>1.970565831644606</v>
       </c>
       <c r="K523">
         <v>13.66</v>
@@ -27769,10 +27775,10 @@
         <v>29.79</v>
       </c>
       <c r="M523">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="N523">
-        <v>29.32</v>
+        <v>29.36</v>
       </c>
       <c r="O523">
         <v>1</v>
@@ -27786,31 +27792,31 @@
         <v>0</v>
       </c>
       <c r="B524" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C524">
-        <v>2.405493706648535</v>
+        <v>2.602050801104053</v>
       </c>
       <c r="D524" t="s">
         <v>210</v>
       </c>
       <c r="E524">
-        <v>2.015682597697886</v>
+        <v>2.371084104170642</v>
       </c>
       <c r="F524">
         <v>1</v>
       </c>
       <c r="G524">
-        <v>0.05717450629335146</v>
+        <v>0.05697794919889594</v>
       </c>
       <c r="H524">
-        <v>0.05662431740230212</v>
+        <v>0.05634891589582936</v>
       </c>
       <c r="I524">
-        <v>-0.3898111089506493</v>
+        <v>-0.230966696933411</v>
       </c>
       <c r="J524">
-        <v>2.004722276233636</v>
+        <v>1.990333030665882</v>
       </c>
       <c r="K524">
         <v>13.66</v>
@@ -27819,10 +27825,10 @@
         <v>29.79</v>
       </c>
       <c r="M524">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="N524">
-        <v>29.32</v>
+        <v>29.36</v>
       </c>
       <c r="O524">
         <v>1</v>
@@ -27839,46 +27845,146 @@
         <v>96</v>
       </c>
       <c r="C525">
-        <v>2.377964414334638</v>
+        <v>2.107715170244884</v>
       </c>
       <c r="D525" t="s">
         <v>210</v>
       </c>
       <c r="E525">
-        <v>1.988233918245815</v>
+        <v>2.267593076983889</v>
       </c>
       <c r="F525">
         <v>1</v>
       </c>
       <c r="G525">
-        <v>0.05720203558566535</v>
+        <v>0.05653228482975511</v>
       </c>
       <c r="H525">
-        <v>0.05665176608175419</v>
+        <v>0.05645240692301611</v>
       </c>
       <c r="I525">
-        <v>-0.3897304960888235</v>
+        <v>0.1598779067390055</v>
       </c>
       <c r="J525">
-        <v>2.006737597779309</v>
+        <v>1.997965112316822</v>
       </c>
       <c r="K525">
-        <v>13.66</v>
+        <v>13.62</v>
       </c>
       <c r="L525">
-        <v>29.79</v>
+        <v>29.32</v>
       </c>
       <c r="M525">
-        <v>13.62</v>
+        <v>13.56</v>
       </c>
       <c r="N525">
-        <v>29.32</v>
+        <v>29.36</v>
       </c>
       <c r="O525">
         <v>1</v>
       </c>
       <c r="P525" t="s">
         <v>419</v>
+      </c>
+    </row>
+    <row r="526" spans="1:16">
+      <c r="A526" s="1">
+        <v>0</v>
+      </c>
+      <c r="B526" t="s">
+        <v>96</v>
+      </c>
+      <c r="C526">
+        <v>2.015682597697886</v>
+      </c>
+      <c r="D526" t="s">
+        <v>210</v>
+      </c>
+      <c r="E526">
+        <v>2.1759659342719</v>
+      </c>
+      <c r="F526">
+        <v>1</v>
+      </c>
+      <c r="G526">
+        <v>0.05662431740230212</v>
+      </c>
+      <c r="H526">
+        <v>0.0565440340657281</v>
+      </c>
+      <c r="I526">
+        <v>0.1602833365740146</v>
+      </c>
+      <c r="J526">
+        <v>2.004722276233636</v>
+      </c>
+      <c r="K526">
+        <v>13.62</v>
+      </c>
+      <c r="L526">
+        <v>29.32</v>
+      </c>
+      <c r="M526">
+        <v>13.56</v>
+      </c>
+      <c r="N526">
+        <v>29.36</v>
+      </c>
+      <c r="O526">
+        <v>1</v>
+      </c>
+      <c r="P526" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="527" spans="1:16">
+      <c r="A527" s="1">
+        <v>0</v>
+      </c>
+      <c r="B527" t="s">
+        <v>96</v>
+      </c>
+      <c r="C527">
+        <v>1.988233918245815</v>
+      </c>
+      <c r="D527" t="s">
+        <v>210</v>
+      </c>
+      <c r="E527">
+        <v>2.14863817411257</v>
+      </c>
+      <c r="F527">
+        <v>1</v>
+      </c>
+      <c r="G527">
+        <v>0.05665176608175419</v>
+      </c>
+      <c r="H527">
+        <v>0.05657136182588743</v>
+      </c>
+      <c r="I527">
+        <v>0.1604042558667551</v>
+      </c>
+      <c r="J527">
+        <v>2.006737597779309</v>
+      </c>
+      <c r="K527">
+        <v>13.62</v>
+      </c>
+      <c r="L527">
+        <v>29.32</v>
+      </c>
+      <c r="M527">
+        <v>13.56</v>
+      </c>
+      <c r="N527">
+        <v>29.36</v>
+      </c>
+      <c r="O527">
+        <v>1</v>
+      </c>
+      <c r="P527" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-02628-601628.xlsx
+++ b/s60_signal/position-02628-601628.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="421">
   <si>
     <t>trade_time</t>
   </si>
@@ -307,9 +307,6 @@
     <t>2021-11-02</t>
   </si>
   <si>
-    <t>2021-11-01</t>
-  </si>
-  <si>
     <t>2016-11-11</t>
   </si>
   <si>
@@ -646,7 +643,7 @@
     <t>2021-07-07</t>
   </si>
   <si>
-    <t>2021-11-03</t>
+    <t>2021-11-04</t>
   </si>
   <si>
     <t>2016-05-17</t>
@@ -1698,7 +1695,7 @@
         <v>2.844772647031224</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2">
         <v>5.373230386726174</v>
@@ -1734,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1748,7 +1745,7 @@
         <v>2.344935136036042</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E3">
         <v>5.373230386726174</v>
@@ -1784,7 +1781,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1798,7 +1795,7 @@
         <v>2.953797713002309</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E4">
         <v>5.373230386726174</v>
@@ -1834,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1848,7 +1845,7 @@
         <v>2.944122691011945</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E5">
         <v>5.373230386726174</v>
@@ -1884,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1898,7 +1895,7 @@
         <v>2.973635223997491</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E6">
         <v>5.373230386726174</v>
@@ -1934,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1948,7 +1945,7 @@
         <v>3.003635223997492</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7">
         <v>5.373230386726174</v>
@@ -1984,7 +1981,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1998,7 +1995,7 @@
         <v>7.289203935514355</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E8">
         <v>5.128184916132415</v>
@@ -2034,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2048,7 +2045,7 @@
         <v>-2.117497474419014</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E9">
         <v>0.8991929718719938</v>
@@ -2084,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2098,7 +2095,7 @@
         <v>-2.80975033090947</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E10">
         <v>0.2758434229577951</v>
@@ -2134,7 +2131,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2148,7 +2145,7 @@
         <v>-2.902998496046035</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E11">
         <v>0.1918767030952893</v>
@@ -2184,7 +2181,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2198,7 +2195,7 @@
         <v>-2.830339867902396</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E12">
         <v>0.2573032631353307</v>
@@ -2234,7 +2231,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2248,7 +2245,7 @@
         <v>-2.537341046304341</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E13">
         <v>0.5211384810952531</v>
@@ -2284,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2298,7 +2295,7 @@
         <v>-2.336644974997025</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E14">
         <v>0.7018582922817487</v>
@@ -2334,7 +2331,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2348,7 +2345,7 @@
         <v>-2.249226521683095</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E15">
         <v>0.7018582922817487</v>
@@ -2384,7 +2381,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2398,7 +2395,7 @@
         <v>-1.845740644766149</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E16">
         <v>1.143900517084994</v>
@@ -2434,7 +2431,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2448,7 +2445,7 @@
         <v>-1.76174710538406</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E17">
         <v>1.143900517084994</v>
@@ -2484,7 +2481,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2534,7 +2531,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2548,7 +2545,7 @@
         <v>-1.483754394543759</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E19">
         <v>1.469856507982922</v>
@@ -2584,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -2598,7 +2595,7 @@
         <v>-1.402286340628343</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20">
         <v>1.469856507982922</v>
@@ -2634,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2684,7 +2681,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2698,7 +2695,7 @@
         <v>-1.119201343261796</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22">
         <v>1.798123813695423</v>
@@ -2734,7 +2731,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2748,7 +2745,7 @@
         <v>-1.040276682727416</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E23">
         <v>1.798123813695423</v>
@@ -2784,7 +2781,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2798,7 +2795,7 @@
         <v>-0.970418309242234</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>-1.315795006570312</v>
@@ -2834,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2848,7 +2845,7 @@
         <v>-1.094604783790125</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E25">
         <v>1.627274602785022</v>
@@ -2884,7 +2881,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2898,7 +2895,7 @@
         <v>-1.015851727159035</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E26">
         <v>1.627274602785022</v>
@@ -2934,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2948,7 +2945,7 @@
         <v>-1.190513514023774</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E27">
         <v>-1.147995174237213</v>
@@ -2984,7 +2981,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2998,7 +2995,7 @@
         <v>-1.15006863091817</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E28">
         <v>1.577640908889972</v>
@@ -3034,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3048,7 +3045,7 @@
         <v>-1.255522302285485</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E29">
         <v>-0.5624021926528435</v>
@@ -3084,7 +3081,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3098,7 +3095,7 @@
         <v>-1.320960230949986</v>
       </c>
       <c r="D30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E30">
         <v>1.424712797977779</v>
@@ -3134,7 +3131,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3148,7 +3145,7 @@
         <v>-1.455823154415796</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31">
         <v>-0.3493885347260317</v>
@@ -3184,7 +3181,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3198,7 +3195,7 @@
         <v>-1.605480846937454</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E32">
         <v>-0.7894370781288025</v>
@@ -3234,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3248,7 +3245,7 @@
         <v>-1.761773123733541</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E33">
         <v>-1.128596969277446</v>
@@ -3284,7 +3281,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3298,7 +3295,7 @@
         <v>-1.457944364792599</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E34">
         <v>-0.8017368070151889</v>
@@ -3334,7 +3331,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3348,7 +3345,7 @@
         <v>-1.234076514305805</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E35">
         <v>0.01703472753200685</v>
@@ -3384,7 +3381,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3398,7 +3395,7 @@
         <v>-0.7963224235233177</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E36">
         <v>0.2870665855800212</v>
@@ -3434,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3448,7 +3445,7 @@
         <v>-0.8942517780380754</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E37">
         <v>0.59890656545236</v>
@@ -3484,7 +3481,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3498,7 +3495,7 @@
         <v>-0.899307304101125</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E38">
         <v>0.6876116265245429</v>
@@ -3534,7 +3531,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3548,7 +3545,7 @@
         <v>-0.8589383918075626</v>
       </c>
       <c r="D39" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E39">
         <v>0.8335609313842731</v>
@@ -3584,7 +3581,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3598,7 +3595,7 @@
         <v>-0.6533981903373771</v>
       </c>
       <c r="D40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E40">
         <v>1.169788560028703</v>
@@ -3634,7 +3631,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -3648,7 +3645,7 @@
         <v>4.835153534210221</v>
       </c>
       <c r="D41" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E41">
         <v>2.04429947322755</v>
@@ -3684,7 +3681,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -3698,7 +3695,7 @@
         <v>-0.406918334342155</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E42">
         <v>1.312995819177061</v>
@@ -3734,7 +3731,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -3748,7 +3745,7 @@
         <v>0.04130730968482865</v>
       </c>
       <c r="D43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E43">
         <v>2.64378384364354</v>
@@ -3784,7 +3781,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3798,7 +3795,7 @@
         <v>5.033791575296075</v>
       </c>
       <c r="D44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E44">
         <v>2.275021568455536</v>
@@ -3834,7 +3831,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3848,7 +3845,7 @@
         <v>-0.1691188742298735</v>
       </c>
       <c r="D45" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E45">
         <v>1.79275039480164</v>
@@ -3884,7 +3881,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3898,7 +3895,7 @@
         <v>0.2293541709380591</v>
       </c>
       <c r="D46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E46">
         <v>2.812063918551083</v>
@@ -3934,7 +3931,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3948,7 +3945,7 @@
         <v>5.217902572011447</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E47">
         <v>2.488870208345837</v>
@@ -3984,7 +3981,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3998,7 +3995,7 @@
         <v>0.0512895398901918</v>
       </c>
       <c r="D48" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E48">
         <v>1.57274123510015</v>
@@ -4034,7 +4031,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4048,7 +4045,7 @@
         <v>0.3237189931323456</v>
       </c>
       <c r="D49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E49">
         <v>2.896509461761223</v>
@@ -4084,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4098,7 +4095,7 @@
         <v>5.3102923165319</v>
       </c>
       <c r="D50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E50">
         <v>2.596182761957483</v>
@@ -4134,7 +4131,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4148,7 +4145,7 @@
         <v>0.161893889624892</v>
       </c>
       <c r="D51" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E51">
         <v>1.501333830022219</v>
@@ -4184,7 +4181,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4198,7 +4195,7 @@
         <v>5.33023415169577</v>
       </c>
       <c r="D52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E52">
         <v>2.619345606126444</v>
@@ -4234,7 +4231,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4248,7 +4245,7 @@
         <v>0.1857672504861512</v>
       </c>
       <c r="D53" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E53">
         <v>1.155646098159064</v>
@@ -4284,7 +4281,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4298,7 +4295,7 @@
         <v>5.37850629613547</v>
       </c>
       <c r="D54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E54">
         <v>2.675414676508897</v>
@@ -4334,7 +4331,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4348,7 +4345,7 @@
         <v>0.243556231003037</v>
       </c>
       <c r="D55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E55">
         <v>1.799674337820232</v>
@@ -4384,7 +4381,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4398,7 +4395,7 @@
         <v>5.505970450595548</v>
       </c>
       <c r="D56" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E56">
         <v>2.823466865418581</v>
@@ -4434,7 +4431,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4448,7 +4445,7 @@
         <v>0.3961498981001377</v>
       </c>
       <c r="D57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E57">
         <v>1.846556155176511</v>
@@ -4484,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4498,7 +4495,7 @@
         <v>5.552898822755296</v>
       </c>
       <c r="D58" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E58">
         <v>2.877975117167079</v>
@@ -4534,7 +4531,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4548,7 +4545,7 @@
         <v>0.4523301821108561</v>
       </c>
       <c r="D59" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E59">
         <v>2.714577056552891</v>
@@ -4584,7 +4581,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4598,7 +4595,7 @@
         <v>0.844003460842476</v>
       </c>
       <c r="D60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E60">
         <v>3.182739844457025</v>
@@ -4634,7 +4631,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -4648,7 +4645,7 @@
         <v>5.819687109336471</v>
       </c>
       <c r="D61" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E61">
         <v>2.897855098492958</v>
@@ -4684,7 +4681,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -4698,7 +4695,7 @@
         <v>0.7717156843363</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E62">
         <v>3.232403806926722</v>
@@ -4734,7 +4731,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -4748,7 +4745,7 @@
         <v>2.174557955758587</v>
       </c>
       <c r="D63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E63">
         <v>4.552795119478848</v>
@@ -4784,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -4798,7 +4795,7 @@
         <v>2.230502900253292</v>
       </c>
       <c r="D64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E64">
         <v>4.552795119478848</v>
@@ -4834,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4848,7 +4845,7 @@
         <v>7.122392789242706</v>
       </c>
       <c r="D65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E65">
         <v>4.410974047362672</v>
@@ -4884,7 +4881,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4898,7 +4895,7 @@
         <v>3.377229031968387</v>
       </c>
       <c r="D66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E66">
         <v>5.847002514367812</v>
@@ -4934,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4948,7 +4945,7 @@
         <v>3.424783248024418</v>
       </c>
       <c r="D67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E67">
         <v>5.847002514367812</v>
@@ -4984,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4998,7 +4995,7 @@
         <v>8.29989168013649</v>
       </c>
       <c r="D68" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E68">
         <v>5.631180854885052</v>
@@ -5034,7 +5031,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5048,7 +5045,7 @@
         <v>4.683694888843547</v>
       </c>
       <c r="D69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E69">
         <v>7.023429444093537</v>
@@ -5084,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5098,7 +5095,7 @@
         <v>4.722134226828356</v>
       </c>
       <c r="D70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E70">
         <v>7.023429444093537</v>
@@ -5134,7 +5131,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5148,7 +5145,7 @@
         <v>9.579012902797984</v>
       </c>
       <c r="D71" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E71">
         <v>6.893347467132109</v>
@@ -5184,7 +5181,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5198,7 +5195,7 @@
         <v>3.961474621504259</v>
       </c>
       <c r="D72" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E72">
         <v>6.476706188649629</v>
@@ -5234,7 +5231,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5248,7 +5245,7 @@
         <v>8.320444610292363</v>
       </c>
       <c r="D73" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E73">
         <v>7.021567248362409</v>
@@ -5284,7 +5281,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5298,7 +5295,7 @@
         <v>8.530866989040167</v>
       </c>
       <c r="D74" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E74">
         <v>7.021567248362409</v>
@@ -5334,7 +5331,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5348,7 +5345,7 @@
         <v>3.2890165208482</v>
       </c>
       <c r="D75" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E75">
         <v>5.857937357507026</v>
@@ -5384,7 +5381,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5398,7 +5395,7 @@
         <v>7.698991315674085</v>
       </c>
       <c r="D76" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E76">
         <v>6.277165792762322</v>
@@ -5434,7 +5431,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5448,7 +5445,7 @@
         <v>7.862435583597616</v>
       </c>
       <c r="D77" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E77">
         <v>6.277165792762322</v>
@@ -5484,7 +5481,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5498,7 +5495,7 @@
         <v>2.706415003086228</v>
       </c>
       <c r="D78" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E78">
         <v>5.321850930983533</v>
@@ -5534,7 +5531,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5548,7 +5545,7 @@
         <v>7.160579134588669</v>
       </c>
       <c r="D79" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E79">
         <v>5.783497068837448</v>
@@ -5584,7 +5581,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5598,7 +5595,7 @@
         <v>7.283322697678528</v>
       </c>
       <c r="D80" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E80">
         <v>5.783497068837448</v>
@@ -5634,7 +5631,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5648,7 +5645,7 @@
         <v>2.25250194719996</v>
       </c>
       <c r="D81" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E81">
         <v>4.90417843844148</v>
@@ -5684,7 +5681,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5698,7 +5695,7 @@
         <v>6.741094613879405</v>
       </c>
       <c r="D82" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E82">
         <v>5.766049754225914</v>
@@ -5734,7 +5731,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5748,7 +5745,7 @@
         <v>6.83212768404308</v>
       </c>
       <c r="D83" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E83">
         <v>5.766049754225914</v>
@@ -5784,7 +5781,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5798,7 +5795,7 @@
         <v>1.648635956687475</v>
       </c>
       <c r="D84" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E84">
         <v>4.348525301462924</v>
@@ -5834,7 +5831,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5848,7 +5845,7 @@
         <v>6.183030834224155</v>
       </c>
       <c r="D85" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E85">
         <v>5.350064030791522</v>
@@ -5884,7 +5881,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5898,7 +5895,7 @@
         <v>6.231877657545638</v>
       </c>
       <c r="D86" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E86">
         <v>5.350064030791522</v>
@@ -5934,7 +5931,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5948,7 +5945,7 @@
         <v>1.432518806234409</v>
       </c>
       <c r="D87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E87">
         <v>4.149663013321483</v>
@@ -5984,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -5998,7 +5995,7 @@
         <v>5.983305802967131</v>
       </c>
       <c r="D88" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E88">
         <v>4.577912304600769</v>
@@ -6034,7 +6031,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6048,7 +6045,7 @@
         <v>6.017054621765944</v>
       </c>
       <c r="D89" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E89">
         <v>4.577912304600769</v>
@@ -6084,7 +6081,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6098,7 +6095,7 @@
         <v>1.226728012835469</v>
       </c>
       <c r="D90" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E90">
         <v>3.960302622589126</v>
@@ -6134,7 +6131,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6148,7 +6145,7 @@
         <v>5.793123892101445</v>
       </c>
       <c r="D91" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E91">
         <v>4.612872778687663</v>
@@ -6184,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6198,7 +6195,7 @@
         <v>5.812496108566997</v>
       </c>
       <c r="D92" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E92">
         <v>4.612872778687663</v>
@@ -6234,7 +6231,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6248,7 +6245,7 @@
         <v>1.216947853386511</v>
       </c>
       <c r="D93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E93">
         <v>3.951303314193975</v>
@@ -6284,7 +6281,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6298,7 +6295,7 @@
         <v>5.802774512947074</v>
       </c>
       <c r="D94" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E94">
         <v>4.403561129870987</v>
@@ -6334,7 +6331,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6348,7 +6345,7 @@
         <v>1.177523163430447</v>
       </c>
       <c r="D95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E95">
         <v>3.915026304074722</v>
@@ -6384,7 +6381,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6398,7 +6395,7 @@
         <v>5.763585898978771</v>
       </c>
       <c r="D96" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E96">
         <v>4.466025047817013</v>
@@ -6434,7 +6431,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6448,7 +6445,7 @@
         <v>0.9680478903759173</v>
       </c>
       <c r="D97" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E97">
         <v>3.722275603719158</v>
@@ -6484,7 +6481,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6498,7 +6495,7 @@
         <v>0.8515262832029507</v>
       </c>
       <c r="D98" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E98">
         <v>3.61505711887537</v>
@@ -6534,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6548,7 +6545,7 @@
         <v>0.6675490824101864</v>
       </c>
       <c r="D99" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E99">
         <v>3.445768716549093</v>
@@ -6584,7 +6581,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6598,7 +6595,7 @@
         <v>0.2453647773980379</v>
       </c>
       <c r="D100" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E100">
         <v>3.057291741278434</v>
@@ -6634,7 +6631,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -6648,7 +6645,7 @@
         <v>-0.1442597189068877</v>
       </c>
       <c r="D101" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E101">
         <v>2.69877498918947</v>
@@ -6684,7 +6681,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6698,7 +6695,7 @@
         <v>3.671796227407118</v>
       </c>
       <c r="D102" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E102">
         <v>1.089748757437874</v>
@@ -6734,7 +6731,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -6748,7 +6745,7 @@
         <v>-1.239097601114093</v>
       </c>
       <c r="D103" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E103">
         <v>1.261882831716061</v>
@@ -6784,7 +6781,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -6798,7 +6795,7 @@
         <v>3.066548753992304</v>
       </c>
       <c r="D104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E104">
         <v>0.4140568037443764</v>
@@ -6834,7 +6831,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -6848,7 +6845,7 @@
         <v>-1.959356470902271</v>
       </c>
       <c r="D105" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E105">
         <v>0.6034425874785647</v>
@@ -6884,7 +6881,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -6898,7 +6895,7 @@
         <v>2.434653904799742</v>
       </c>
       <c r="D106" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E106">
         <v>-0.2913840017675113</v>
@@ -6934,7 +6931,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6948,7 +6945,7 @@
         <v>-2.711326350820261</v>
       </c>
       <c r="D107" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E107">
         <v>-0.08398696342450762</v>
@@ -6984,7 +6981,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6998,7 +6995,7 @@
         <v>2.046949385277987</v>
       </c>
       <c r="D108" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E108">
         <v>-0.7242132753428656</v>
@@ -7034,7 +7031,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7048,7 +7045,7 @@
         <v>-3.172703938184629</v>
       </c>
       <c r="D109" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E109">
         <v>-0.5057652768234711</v>
@@ -7084,7 +7081,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7098,7 +7095,7 @@
         <v>1.727381390460117</v>
       </c>
       <c r="D110" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E110">
         <v>0.5925973930511788</v>
@@ -7134,7 +7131,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7148,7 +7145,7 @@
         <v>1.685047495782005</v>
       </c>
       <c r="D111" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E111">
         <v>-1.128236762428639</v>
@@ -7184,7 +7181,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7198,7 +7195,7 @@
         <v>-3.603375782929252</v>
       </c>
       <c r="D112" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E112">
         <v>-0.8994732706219501</v>
@@ -7234,7 +7231,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7248,7 +7245,7 @@
         <v>1.329375274458599</v>
       </c>
       <c r="D113" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E113">
         <v>-0.02169112718700106</v>
@@ -7284,7 +7281,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7298,7 +7295,7 @@
         <v>1.370767088004978</v>
       </c>
       <c r="D114" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E114">
         <v>-1.479096125030072</v>
@@ -7334,7 +7331,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7348,7 +7345,7 @@
         <v>-3.977376933276734</v>
       </c>
       <c r="D115" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E115">
         <v>-1.241374521837809</v>
@@ -7384,7 +7381,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7398,7 +7395,7 @@
         <v>0.9837414768320834</v>
       </c>
       <c r="D116" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E116">
         <v>-0.5624929319466254</v>
@@ -7434,7 +7431,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7448,7 +7445,7 @@
         <v>-4.274892307557078</v>
       </c>
       <c r="D117" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E117">
         <v>-1.513354644433413</v>
@@ -7498,7 +7495,7 @@
         <v>0.7087921389242986</v>
       </c>
       <c r="D118" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E118">
         <v>-0.01219137097330147</v>
@@ -7548,7 +7545,7 @@
         <v>-6.600419867221269</v>
       </c>
       <c r="D119" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E119">
         <v>-3.935750603200287</v>
@@ -7584,7 +7581,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7598,7 +7595,7 @@
         <v>-1.740049190571469</v>
       </c>
       <c r="D120" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E120">
         <v>-3.803035064283293</v>
@@ -7634,7 +7631,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7648,7 +7645,7 @@
         <v>-7.356943655480499</v>
       </c>
       <c r="D121" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E121">
         <v>-4.634314907681588</v>
@@ -7684,7 +7681,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7698,7 +7695,7 @@
         <v>-2.446239742918287</v>
       </c>
       <c r="D122" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E122">
         <v>-3.284642996427294</v>
@@ -7734,7 +7731,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -7748,7 +7745,7 @@
         <v>-2.764549545202325</v>
       </c>
       <c r="D123" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E123">
         <v>-3.284642996427294</v>
@@ -7784,7 +7781,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -7798,7 +7795,7 @@
         <v>-8.273062059554213</v>
       </c>
       <c r="D124" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E124">
         <v>-5.480246821120623</v>
@@ -7834,7 +7831,7 @@
         <v>1</v>
       </c>
       <c r="P124" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -7848,7 +7845,7 @@
         <v>-3.301406720914517</v>
       </c>
       <c r="D125" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E125">
         <v>-3.80770165872979</v>
@@ -7884,7 +7881,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7898,7 +7895,7 @@
         <v>-3.640798600667189</v>
       </c>
       <c r="D126" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E126">
         <v>-3.80770165872979</v>
@@ -7934,7 +7931,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7948,7 +7945,7 @@
         <v>-9.028638086965721</v>
       </c>
       <c r="D127" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E127">
         <v>-6.177935975464312</v>
@@ -7984,7 +7981,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7998,7 +7995,7 @@
         <v>-4.006712569082914</v>
       </c>
       <c r="D128" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E128">
         <v>-5.764446572941544</v>
@@ -8034,7 +8031,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8048,7 +8045,7 @@
         <v>-4.355244481425245</v>
       </c>
       <c r="D129" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E129">
         <v>-5.764446572941544</v>
@@ -8084,7 +8081,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8098,7 +8095,7 @@
         <v>-9.288472736223071</v>
       </c>
       <c r="D130" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E130">
         <v>-6.4178639378834</v>
@@ -8134,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8148,7 +8145,7 @@
         <v>-4.249259832401776</v>
       </c>
       <c r="D131" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E131">
         <v>-5.572990039214197</v>
@@ -8184,7 +8181,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8198,7 +8195,7 @@
         <v>-4.600934905823827</v>
       </c>
       <c r="D132" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E132">
         <v>-5.572990039214197</v>
@@ -8234,7 +8231,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8248,7 +8245,7 @@
         <v>-8.391360480599353</v>
       </c>
       <c r="D133" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E133">
         <v>-5.589482056682467</v>
@@ -8284,7 +8281,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8298,7 +8295,7 @@
         <v>-3.41183448088206</v>
       </c>
       <c r="D134" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E134">
         <v>-4.236414237755341</v>
@@ -8334,7 +8331,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8348,7 +8345,7 @@
         <v>-3.752657389921566</v>
       </c>
       <c r="D135" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E135">
         <v>-4.236414237755341</v>
@@ -8384,7 +8381,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8398,7 +8395,7 @@
         <v>-7.284701623181299</v>
       </c>
       <c r="D136" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E136">
         <v>-4.567607547211761</v>
@@ -8434,7 +8431,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8448,7 +8445,7 @@
         <v>-2.378804136155122</v>
       </c>
       <c r="D137" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E137">
         <v>-3.182992288094191</v>
@@ -8484,7 +8481,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8534,7 +8531,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8584,7 +8581,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -8598,7 +8595,7 @@
         <v>15.30025538505301</v>
       </c>
       <c r="D140" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E140">
         <v>12.2194473505381</v>
@@ -8634,7 +8631,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -8648,7 +8645,7 @@
         <v>16.08154605938966</v>
       </c>
       <c r="D141" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E141">
         <v>12.2194473505381</v>
@@ -8684,7 +8681,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -8734,7 +8731,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8784,7 +8781,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8834,7 +8831,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8884,7 +8881,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8934,7 +8931,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8984,7 +8981,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9034,7 +9031,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9084,7 +9081,7 @@
         <v>1</v>
       </c>
       <c r="P149" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -9134,7 +9131,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -9184,7 +9181,7 @@
         <v>1</v>
       </c>
       <c r="P151" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -9198,7 +9195,7 @@
         <v>-2.965774048910724</v>
       </c>
       <c r="D152" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E152">
         <v>-6.323583762599906</v>
@@ -9234,7 +9231,7 @@
         <v>1</v>
       </c>
       <c r="P152" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -9248,7 +9245,7 @@
         <v>-3.841273412039687</v>
       </c>
       <c r="D153" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E153">
         <v>-6.323583762599906</v>
@@ -9284,7 +9281,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -9334,7 +9331,7 @@
         <v>1</v>
       </c>
       <c r="P154" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -9348,7 +9345,7 @@
         <v>-4.596644143057084</v>
       </c>
       <c r="D155" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E155">
         <v>-7.87451662725034</v>
@@ -9384,7 +9381,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9398,7 +9395,7 @@
         <v>-5.499155847289916</v>
       </c>
       <c r="D156" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E156">
         <v>-7.87451662725034</v>
@@ -9434,7 +9431,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9484,7 +9481,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -9498,7 +9495,7 @@
         <v>-6.176260919928573</v>
       </c>
       <c r="D158" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E158">
         <v>-9.588220956609884</v>
@@ -9534,7 +9531,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9548,7 +9545,7 @@
         <v>-7.104936049037125</v>
       </c>
       <c r="D159" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E159">
         <v>-9.588220956609884</v>
@@ -9584,7 +9581,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -9634,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -9684,7 +9681,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9698,7 +9695,7 @@
         <v>-5.957065888688689</v>
       </c>
       <c r="D162" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E162">
         <v>-9.35041930781134</v>
@@ -9734,7 +9731,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9748,7 +9745,7 @@
         <v>-6.882110458273605</v>
       </c>
       <c r="D163" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E163">
         <v>-9.35041930781134</v>
@@ -9784,7 +9781,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -9798,7 +9795,7 @@
         <v>-5.75373473480284</v>
       </c>
       <c r="D164" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E164">
         <v>-9.129828159496252</v>
@@ -9848,7 +9845,7 @@
         <v>-6.675411500596677</v>
       </c>
       <c r="D165" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E165">
         <v>-9.129828159496252</v>
@@ -9898,7 +9895,7 @@
         <v>4.036863233290944</v>
       </c>
       <c r="D166" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E166">
         <v>1.091137151603181</v>
@@ -9948,7 +9945,7 @@
         <v>4.353212181898559</v>
       </c>
       <c r="D167" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E167">
         <v>1.091137151603181</v>
@@ -9998,7 +9995,7 @@
         <v>4.092859462531468</v>
       </c>
       <c r="D168" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E168">
         <v>1.091137151603181</v>
@@ -10084,7 +10081,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10134,7 +10131,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10284,7 +10281,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10334,7 +10331,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10384,7 +10381,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10434,7 +10431,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10484,7 +10481,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10534,7 +10531,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10584,7 +10581,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10634,7 +10631,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -10684,7 +10681,7 @@
         <v>1</v>
       </c>
       <c r="P181" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -10734,7 +10731,7 @@
         <v>1</v>
       </c>
       <c r="P182" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -10784,7 +10781,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10834,7 +10831,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10884,7 +10881,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10934,7 +10931,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10984,7 +10981,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10998,7 +10995,7 @@
         <v>2.797016608461103</v>
       </c>
       <c r="D188" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E188">
         <v>-0.1302387600075896</v>
@@ -11034,7 +11031,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11048,7 +11045,7 @@
         <v>3.23804287129742</v>
       </c>
       <c r="D189" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E189">
         <v>-0.1302387600075896</v>
@@ -11084,7 +11081,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11098,7 +11095,7 @@
         <v>2.97076363447318</v>
       </c>
       <c r="D190" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E190">
         <v>-0.1302387600075896</v>
@@ -11134,7 +11131,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11148,7 +11145,7 @@
         <v>-2.735537076225839</v>
       </c>
       <c r="D191" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E191">
         <v>-0.06446785034954416</v>
@@ -11184,7 +11181,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11198,7 +11195,7 @@
         <v>2.142297248198716</v>
       </c>
       <c r="D192" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E192">
         <v>-0.7752043867837592</v>
@@ -11234,7 +11231,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11248,7 +11245,7 @@
         <v>2.649161212067007</v>
       </c>
       <c r="D193" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E193">
         <v>-0.7752043867837592</v>
@@ -11284,7 +11281,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11298,7 +11295,7 @@
         <v>1.866662847049479</v>
       </c>
       <c r="D194" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E194">
         <v>-0.7752043867837592</v>
@@ -11334,7 +11331,7 @@
         <v>1</v>
       </c>
       <c r="P194" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -11348,7 +11345,7 @@
         <v>-3.292719101626048</v>
       </c>
       <c r="D195" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E195">
         <v>-0.5316716843393898</v>
@@ -11384,7 +11381,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -11398,7 +11395,7 @@
         <v>0.7343076746441</v>
       </c>
       <c r="D196" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E196">
         <v>-2.162218324233283</v>
@@ -11448,7 +11445,7 @@
         <v>1.382757182221791</v>
       </c>
       <c r="D197" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E197">
         <v>-2.162218324233283</v>
@@ -11498,7 +11495,7 @@
         <v>0.5792831810991643</v>
       </c>
       <c r="D198" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E198">
         <v>-2.162218324233283</v>
@@ -11548,7 +11545,7 @@
         <v>-4.4909523141297</v>
       </c>
       <c r="D199" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E199">
         <v>-1.797099453998044</v>
@@ -11598,7 +11595,7 @@
         <v>-0.5271433345479153</v>
       </c>
       <c r="D200" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E200">
         <v>-3.404876767180344</v>
@@ -11648,7 +11645,7 @@
         <v>0.2481559951831649</v>
       </c>
       <c r="D201" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E201">
         <v>-3.404876767180344</v>
@@ -11698,7 +11695,7 @@
         <v>-0.5741105721844058</v>
       </c>
       <c r="D202" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E202">
         <v>-3.404876767180344</v>
@@ -11748,7 +11745,7 @@
         <v>-5.289194339951301</v>
       </c>
       <c r="D203" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E203">
         <v>-2.93597803324387</v>
@@ -11798,7 +11795,7 @@
         <v>-1.521590007004434</v>
       </c>
       <c r="D204" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E204">
         <v>-4.774748703164175</v>
@@ -11834,7 +11831,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11848,7 +11845,7 @@
         <v>-2.373169137555241</v>
       </c>
       <c r="D205" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E205">
         <v>-4.774748703164175</v>
@@ -11884,7 +11881,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -11898,7 +11895,7 @@
         <v>-6.960010441395497</v>
       </c>
       <c r="D206" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E206">
         <v>-4.500536093148853</v>
@@ -11934,7 +11931,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -11948,7 +11945,7 @@
         <v>-2.452340392521911</v>
       </c>
       <c r="D207" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E207">
         <v>-5.548191233294997</v>
@@ -11998,7 +11995,7 @@
         <v>-2.754963624773605</v>
       </c>
       <c r="D208" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E208">
         <v>-5.548191233294997</v>
@@ -12048,7 +12045,7 @@
         <v>-7.838731302256715</v>
       </c>
       <c r="D209" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E209">
         <v>-5.323373390490392</v>
@@ -12098,7 +12095,7 @@
         <v>-4.58678078170076</v>
       </c>
       <c r="D210" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E210">
         <v>-7.667945163513835</v>
@@ -12134,7 +12131,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12148,7 +12145,7 @@
         <v>-5.270890369576151</v>
       </c>
       <c r="D211" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E211">
         <v>-7.667945163513835</v>
@@ -12184,7 +12181,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12198,7 +12195,7 @@
         <v>-4.902661407674056</v>
       </c>
       <c r="D212" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E212">
         <v>-7.667945163513835</v>
@@ -12234,7 +12231,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12248,7 +12245,7 @@
         <v>-9.853855147941093</v>
       </c>
       <c r="D213" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E213">
         <v>-7.21034243019923</v>
@@ -12284,7 +12281,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12298,7 +12295,7 @@
         <v>-5.59817458645032</v>
       </c>
       <c r="D214" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E214">
         <v>-8.513312611948162</v>
@@ -12334,7 +12331,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12348,7 +12345,7 @@
         <v>-5.920337161521442</v>
       </c>
       <c r="D215" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E215">
         <v>-8.513312611948162</v>
@@ -12384,7 +12381,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12398,7 +12395,7 @@
         <v>-10.78187598777789</v>
       </c>
       <c r="D216" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E216">
         <v>-7.189437361711093</v>
@@ -12434,7 +12431,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12448,7 +12445,7 @@
         <v>-10.80871141081024</v>
       </c>
       <c r="D217" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E217">
         <v>-8.104473185122753</v>
@@ -12484,7 +12481,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -12498,7 +12495,7 @@
         <v>-5.98278744209609</v>
       </c>
       <c r="D218" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E218">
         <v>-8.914647765665489</v>
@@ -12534,7 +12531,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -12548,7 +12545,7 @@
         <v>-6.30733891689172</v>
       </c>
       <c r="D219" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E219">
         <v>-8.914647765665489</v>
@@ -12584,7 +12581,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -12598,7 +12595,7 @@
         <v>-11.21108163828114</v>
       </c>
       <c r="D220" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E220">
         <v>-7.582809516346728</v>
@@ -12634,7 +12631,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -12648,7 +12645,7 @@
         <v>-11.09924338896238</v>
       </c>
       <c r="D221" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E221">
         <v>-7.582809516346728</v>
@@ -12684,7 +12681,7 @@
         <v>1</v>
       </c>
       <c r="P221" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="222" spans="1:16">
@@ -12698,7 +12695,7 @@
         <v>-11.17182416893544</v>
       </c>
       <c r="D222" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E222">
         <v>-8.444493245911037</v>
@@ -12734,7 +12731,7 @@
         <v>1</v>
       </c>
       <c r="P222" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="223" spans="1:16">
@@ -12748,7 +12745,7 @@
         <v>-6.197743032286496</v>
       </c>
       <c r="D223" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E223">
         <v>-9.138949251081566</v>
@@ -12784,7 +12781,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12798,7 +12795,7 @@
         <v>-6.52362963497151</v>
       </c>
       <c r="D224" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E224">
         <v>-9.138949251081566</v>
@@ -12834,7 +12831,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12848,7 +12845,7 @@
         <v>-11.45095961574</v>
       </c>
       <c r="D225" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E225">
         <v>-7.802660575464863</v>
@@ -12884,7 +12881,7 @@
         <v>1</v>
       </c>
       <c r="P225" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="226" spans="1:16">
@@ -12898,7 +12895,7 @@
         <v>-11.33467094012331</v>
       </c>
       <c r="D226" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E226">
         <v>-7.802660575464863</v>
@@ -12934,7 +12931,7 @@
         <v>1</v>
       </c>
       <c r="P226" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="227" spans="1:16">
@@ -12948,7 +12945,7 @@
         <v>-11.37476360812142</v>
       </c>
       <c r="D227" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E227">
         <v>-8.63452644883299</v>
@@ -12984,7 +12981,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12998,7 +12995,7 @@
         <v>-6.365423262694474</v>
       </c>
       <c r="D228" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E228">
         <v>-6.712841826990488</v>
@@ -13034,7 +13031,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13048,7 +13045,7 @@
         <v>-6.180679040630039</v>
       </c>
       <c r="D229" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E229">
         <v>-9.121143346744393</v>
@@ -13084,7 +13081,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13098,7 +13095,7 @@
         <v>-6.506459655789232</v>
       </c>
       <c r="D230" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E230">
         <v>-9.121143346744393</v>
@@ -13134,7 +13131,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13148,7 +13145,7 @@
         <v>-11.43191719026831</v>
       </c>
       <c r="D231" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E231">
         <v>-7.785207962880413</v>
@@ -13184,7 +13181,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13198,7 +13195,7 @@
         <v>-11.31598180640433</v>
       </c>
       <c r="D232" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E232">
         <v>-7.785207962880413</v>
@@ -13234,7 +13231,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13248,7 +13245,7 @@
         <v>-11.3586535041973</v>
       </c>
       <c r="D233" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E233">
         <v>-8.619440890991779</v>
@@ -13284,7 +13281,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13298,7 +13295,7 @@
         <v>-6.352422126194313</v>
       </c>
       <c r="D234" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E234">
         <v>-7.002545941158143</v>
@@ -13334,7 +13331,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13348,7 +13345,7 @@
         <v>-6.259072586714403</v>
       </c>
       <c r="D235" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E235">
         <v>-9.202945307875904</v>
@@ -13384,7 +13381,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13398,7 +13395,7 @@
         <v>-6.58534011830891</v>
       </c>
       <c r="D236" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E236">
         <v>-9.202945307875904</v>
@@ -13434,7 +13431,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13448,7 +13445,7 @@
         <v>-11.51939984314506</v>
       </c>
       <c r="D237" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E237">
         <v>-7.865386869227571</v>
@@ -13484,7 +13481,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13498,7 +13495,7 @@
         <v>-11.40184140449673</v>
       </c>
       <c r="D238" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E238">
         <v>-7.865386869227571</v>
@@ -13534,7 +13531,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13548,7 +13545,7 @@
         <v>-11.43266480236391</v>
       </c>
       <c r="D239" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E239">
         <v>-8.688745330283755</v>
@@ -13584,7 +13581,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13598,7 +13595,7 @@
         <v>-6.412150542258594</v>
       </c>
       <c r="D240" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E240">
         <v>-6.792666905080129</v>
@@ -13634,7 +13631,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13648,7 +13645,7 @@
         <v>-6.321920167701883</v>
       </c>
       <c r="D241" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E241">
         <v>-9.268525392384579</v>
@@ -13684,7 +13681,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13698,7 +13695,7 @@
         <v>-11.58953410018906</v>
       </c>
       <c r="D242" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E242">
         <v>-7.929665761583294</v>
@@ -13734,7 +13731,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13748,7 +13745,7 @@
         <v>-11.47067446938778</v>
       </c>
       <c r="D243" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E243">
         <v>-7.929665761583294</v>
@@ -13784,7 +13781,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13798,7 +13795,7 @@
         <v>-11.49199916453843</v>
       </c>
       <c r="D244" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E244">
         <v>-8.744306235214712</v>
@@ -13834,7 +13831,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -13848,7 +13845,7 @@
         <v>-6.460034413487151</v>
       </c>
       <c r="D245" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E245">
         <v>-6.681381790702538</v>
@@ -13884,7 +13881,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -13898,7 +13895,7 @@
         <v>-6.550476318984671</v>
       </c>
       <c r="D246" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E246">
         <v>-9.507018767636186</v>
@@ -13934,7 +13931,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -13948,7 +13945,7 @@
         <v>-11.8445895153887</v>
       </c>
       <c r="D247" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E247">
         <v>-8.16342712542118</v>
@@ -13984,7 +13981,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13998,7 +13995,7 @@
         <v>-11.72099787317369</v>
       </c>
       <c r="D248" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E248">
         <v>-8.16342712542118</v>
@@ -14034,7 +14031,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14048,7 +14045,7 @@
         <v>-11.70777888500417</v>
       </c>
       <c r="D249" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E249">
         <v>-8.94636312258066</v>
@@ -14084,7 +14081,7 @@
         <v>1</v>
       </c>
       <c r="P249" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -14134,7 +14131,7 @@
         <v>1</v>
       </c>
       <c r="P250" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -14148,7 +14145,7 @@
         <v>-6.704638136207883</v>
       </c>
       <c r="D251" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E251">
         <v>-9.667883272564755</v>
@@ -14184,7 +14181,7 @@
         <v>1</v>
       </c>
       <c r="P251" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -14198,7 +14195,7 @@
         <v>-12.01662516649286</v>
       </c>
       <c r="D252" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E252">
         <v>-8.321099874299577</v>
@@ -14234,7 +14231,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14248,7 +14245,7 @@
         <v>-11.88984176822768</v>
       </c>
       <c r="D253" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E253">
         <v>-8.321099874299577</v>
@@ -14284,7 +14281,7 @@
         <v>1</v>
       </c>
       <c r="P253" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -14298,7 +14295,7 @@
         <v>-12.14300130071843</v>
       </c>
       <c r="D254" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E254">
         <v>-9.082651105922917</v>
@@ -14334,7 +14331,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14348,7 +14345,7 @@
         <v>-6.751629056158386</v>
       </c>
       <c r="D255" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E255">
         <v>-6.181746306378969</v>
@@ -14384,7 +14381,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14398,7 +14395,7 @@
         <v>-6.169874970448358</v>
       </c>
       <c r="D256" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E256">
         <v>-6.181746306378969</v>
@@ -14434,7 +14431,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14448,7 +14445,7 @@
         <v>-6.791555990766213</v>
       </c>
       <c r="D257" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E257">
         <v>-9.758580164277792</v>
@@ -14484,7 +14481,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14498,7 +14495,7 @@
         <v>-12.11362045346375</v>
       </c>
       <c r="D258" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E258">
         <v>-8.40999722451037</v>
@@ -14534,7 +14531,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14548,7 +14545,7 @@
         <v>-12.22524034737093</v>
       </c>
       <c r="D259" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E259">
         <v>-9.159491528068681</v>
@@ -14584,7 +14581,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14598,7 +14595,7 @@
         <v>-6.817852183440923</v>
       </c>
       <c r="D260" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E260">
         <v>-6.265382608492114</v>
@@ -14634,7 +14631,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14648,7 +14645,7 @@
         <v>-6.233722702947933</v>
       </c>
       <c r="D261" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E261">
         <v>-6.265382608492114</v>
@@ -14684,7 +14681,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14698,7 +14695,7 @@
         <v>-12.15514825489226</v>
       </c>
       <c r="D262" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E262">
         <v>-8.448057955318696</v>
@@ -14734,7 +14731,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14748,7 +14745,7 @@
         <v>-12.26045037566933</v>
       </c>
       <c r="D263" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E263">
         <v>-9.192390175953609</v>
@@ -14784,7 +14781,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14798,7 +14795,7 @@
         <v>-6.261058628637798</v>
       </c>
       <c r="D264" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E264">
         <v>-6.075524180706029</v>
@@ -14834,7 +14831,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14848,7 +14845,7 @@
         <v>-12.2145658985059</v>
       </c>
       <c r="D265" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E265">
         <v>-8.502514942229901</v>
@@ -14898,7 +14895,7 @@
         <v>-12.31082860040297</v>
       </c>
       <c r="D266" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E266">
         <v>-9.239461296218966</v>
@@ -14948,7 +14945,7 @@
         <v>-6.300170650816128</v>
       </c>
       <c r="D267" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E267">
         <v>-5.649532575530262</v>
@@ -14998,7 +14995,7 @@
         <v>-11.84108439837907</v>
       </c>
       <c r="D268" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E268">
         <v>-8.80055369389029</v>
@@ -15034,7 +15031,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15048,7 +15045,7 @@
         <v>-5.935476465087291</v>
       </c>
       <c r="D269" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E269">
         <v>-5.137979270573577</v>
@@ -15084,7 +15081,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15134,7 +15131,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15184,7 +15181,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15234,7 +15231,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15284,7 +15281,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15334,7 +15331,7 @@
         <v>1</v>
       </c>
       <c r="P274" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -15384,7 +15381,7 @@
         <v>1</v>
       </c>
       <c r="P275" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -15434,7 +15431,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15448,7 +15445,7 @@
         <v>-0.3501812538917548</v>
       </c>
       <c r="D277" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E277">
         <v>-4.299167540216818</v>
@@ -15484,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15534,7 +15531,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15548,7 +15545,7 @@
         <v>-0.2510998261771533</v>
       </c>
       <c r="D279" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E279">
         <v>-4.192512218904984</v>
@@ -15584,7 +15581,7 @@
         <v>1</v>
       </c>
       <c r="P279" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="280" spans="1:16">
@@ -15634,7 +15631,7 @@
         <v>1</v>
       </c>
       <c r="P280" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -15648,7 +15645,7 @@
         <v>-0.1528009024453745</v>
       </c>
       <c r="D281" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E281">
         <v>-4.086699217043329</v>
@@ -15684,7 +15681,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -15734,7 +15731,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15748,7 +15745,7 @@
         <v>0.06625268284449959</v>
       </c>
       <c r="D283" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E283">
         <v>-3